--- a/Shop_Tracker_2065_2026.xlsx
+++ b/Shop_Tracker_2065_2026.xlsx
@@ -1101,7 +1101,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G14" s="29" t="n"/>
+      <c r="G14" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="H14" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$G$7,C14:G14,"Y"),"")</f>
         <v/>
@@ -1136,11 +1140,7 @@
         </is>
       </c>
       <c r="F15" s="29" t="n"/>
-      <c r="G15" s="28" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="G15" s="29" t="n"/>
       <c r="H15" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$G$7,C15:G15,"Y"),"")</f>
         <v/>
@@ -1167,11 +1167,7 @@
       <c r="D16" s="29" t="n"/>
       <c r="E16" s="29" t="n"/>
       <c r="F16" s="29" t="n"/>
-      <c r="G16" s="28" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="G16" s="29" t="n"/>
       <c r="H16" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$G$7,C16:G16,"Y"),"")</f>
         <v/>
@@ -1198,11 +1194,7 @@
       <c r="D17" s="29" t="n"/>
       <c r="E17" s="29" t="n"/>
       <c r="F17" s="29" t="n"/>
-      <c r="G17" s="28" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="G17" s="29" t="n"/>
       <c r="H17" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$G$7,C17:G17,"Y"),"")</f>
         <v/>
@@ -1522,11 +1514,7 @@
       <c r="D29" s="18" t="n"/>
       <c r="E29" s="18" t="n"/>
       <c r="F29" s="18" t="n"/>
-      <c r="G29" s="28" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="G29" s="18" t="n"/>
       <c r="H29" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$G$7,C29:G29,"Y"),"")</f>
         <v/>
@@ -2282,7 +2270,11 @@
           <t>Vicki L.</t>
         </is>
       </c>
-      <c r="C15" s="29" t="n"/>
+      <c r="C15" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="D15" s="28" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2326,7 +2318,11 @@
           <t>Kasey W.</t>
         </is>
       </c>
-      <c r="C16" s="29" t="n"/>
+      <c r="C16" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="D16" s="29" t="n"/>
       <c r="E16" s="29" t="n"/>
       <c r="F16" s="28" t="inlineStr">
@@ -2362,7 +2358,11 @@
           <t>Nathan R.</t>
         </is>
       </c>
-      <c r="C17" s="29" t="n"/>
+      <c r="C17" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="D17" s="29" t="n"/>
       <c r="E17" s="29" t="n"/>
       <c r="F17" s="29" t="n"/>
@@ -2684,7 +2684,11 @@
           <t>Jeremiah</t>
         </is>
       </c>
-      <c r="C29" s="18" t="n"/>
+      <c r="C29" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="D29" s="18" t="n"/>
       <c r="E29" s="28" t="inlineStr">
         <is>
@@ -2900,11 +2904,7 @@
           <t>Mike</t>
         </is>
       </c>
-      <c r="C35" s="28" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="C35" s="18" t="n"/>
       <c r="D35" s="18" t="n"/>
       <c r="E35" s="28" t="inlineStr">
         <is>

--- a/Shop_Tracker_2065_2026.xlsx
+++ b/Shop_Tracker_2065_2026.xlsx
@@ -1134,11 +1134,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="E15" s="28" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="E15" s="29" t="n"/>
       <c r="F15" s="29" t="n"/>
       <c r="G15" s="29" t="n"/>
       <c r="H15" s="17">
@@ -1254,17 +1250,9 @@
           <t>Ash</t>
         </is>
       </c>
-      <c r="C21" s="28" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="C21" s="18" t="n"/>
       <c r="D21" s="18" t="n"/>
-      <c r="E21" s="28" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="E21" s="18" t="n"/>
       <c r="F21" s="18" t="n"/>
       <c r="G21" s="18" t="n"/>
       <c r="H21" s="17">
@@ -1420,11 +1408,7 @@
         </is>
       </c>
       <c r="E26" s="35" t="n"/>
-      <c r="F26" s="28" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="F26" s="35" t="n"/>
       <c r="G26" s="28" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1618,26 +1602,14 @@
           <t>Lidy</t>
         </is>
       </c>
-      <c r="C33" s="28" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="C33" s="18" t="n"/>
       <c r="D33" s="28" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="E33" s="28" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F33" s="28" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="E33" s="18" t="n"/>
+      <c r="F33" s="18" t="n"/>
       <c r="G33" s="28" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2243,11 +2215,7 @@
         </is>
       </c>
       <c r="G14" s="29" t="n"/>
-      <c r="H14" s="28" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="H14" s="29" t="n"/>
       <c r="I14" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$H$7,C14:H14,"Y"),"")</f>
         <v/>
@@ -2275,21 +2243,13 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D15" s="28" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D15" s="29" t="n"/>
       <c r="E15" s="28" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F15" s="28" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="F15" s="29" t="n"/>
       <c r="G15" s="28" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2577,21 +2537,13 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D26" s="28" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D26" s="35" t="n"/>
       <c r="E26" s="28" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F26" s="28" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="F26" s="35" t="n"/>
       <c r="G26" s="28" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2651,11 +2603,7 @@
       <c r="C28" s="35" t="n"/>
       <c r="D28" s="35" t="n"/>
       <c r="E28" s="35" t="n"/>
-      <c r="F28" s="28" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="F28" s="35" t="n"/>
       <c r="G28" s="35" t="n"/>
       <c r="H28" s="28" t="inlineStr">
         <is>
@@ -2690,11 +2638,7 @@
         </is>
       </c>
       <c r="D29" s="18" t="n"/>
-      <c r="E29" s="28" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="E29" s="18" t="n"/>
       <c r="F29" s="28" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2731,17 +2675,9 @@
       <c r="C30" s="35" t="n"/>
       <c r="D30" s="35" t="n"/>
       <c r="E30" s="35" t="n"/>
-      <c r="F30" s="28" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="F30" s="35" t="n"/>
       <c r="G30" s="35" t="n"/>
-      <c r="H30" s="28" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="H30" s="35" t="n"/>
       <c r="I30" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$H$7,C30:H30,"Y"),"")</f>
         <v/>
@@ -2825,11 +2761,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D33" s="28" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D33" s="18" t="n"/>
       <c r="E33" s="28" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2841,11 +2773,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H33" s="28" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="H33" s="18" t="n"/>
       <c r="I33" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$H$7,C33:H33,"Y"),"")</f>
         <v/>
@@ -3446,11 +3374,7 @@
           <t>Vicki L.</t>
         </is>
       </c>
-      <c r="C15" s="28" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="C15" s="29" t="n"/>
       <c r="D15" s="29" t="n"/>
       <c r="E15" s="28" t="inlineStr">
         <is>
@@ -3944,11 +3868,7 @@
           <t>Lidy</t>
         </is>
       </c>
-      <c r="C33" s="28" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="C33" s="18" t="n"/>
       <c r="D33" s="28" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4576,11 +4496,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G15" s="28" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="G15" s="29" t="n"/>
       <c r="H15" s="29" t="n"/>
       <c r="I15" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$H$7,C15:H15,"Y"),"")</f>
@@ -4644,11 +4560,7 @@
           <t>Nathan R.</t>
         </is>
       </c>
-      <c r="C17" s="28" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="C17" s="29" t="n"/>
       <c r="D17" s="29" t="n"/>
       <c r="E17" s="28" t="inlineStr">
         <is>
@@ -4656,11 +4568,7 @@
         </is>
       </c>
       <c r="F17" s="29" t="n"/>
-      <c r="G17" s="28" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="G17" s="29" t="n"/>
       <c r="H17" s="28" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5106,31 +5014,19 @@
           <t>Lidy</t>
         </is>
       </c>
-      <c r="C33" s="28" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="C33" s="18" t="n"/>
       <c r="D33" s="28" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="E33" s="28" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="E33" s="18" t="n"/>
       <c r="F33" s="28" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="G33" s="28" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="G33" s="18" t="n"/>
       <c r="H33" s="28" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5228,11 +5124,7 @@
         </is>
       </c>
       <c r="D36" s="35" t="n"/>
-      <c r="E36" s="28" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="E36" s="35" t="n"/>
       <c r="F36" s="28" t="inlineStr">
         <is>
           <t>Y</t>

--- a/Shop_Tracker_2065_2026.xlsx
+++ b/Shop_Tracker_2065_2026.xlsx
@@ -1252,7 +1252,11 @@
       </c>
       <c r="C21" s="18" t="n"/>
       <c r="D21" s="18" t="n"/>
-      <c r="E21" s="18" t="n"/>
+      <c r="E21" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F21" s="18" t="n"/>
       <c r="G21" s="18" t="n"/>
       <c r="H21" s="17">
@@ -2215,7 +2219,11 @@
         </is>
       </c>
       <c r="G14" s="29" t="n"/>
-      <c r="H14" s="29" t="n"/>
+      <c r="H14" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I14" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$H$7,C14:H14,"Y"),"")</f>
         <v/>
@@ -2603,7 +2611,11 @@
       <c r="C28" s="35" t="n"/>
       <c r="D28" s="35" t="n"/>
       <c r="E28" s="35" t="n"/>
-      <c r="F28" s="35" t="n"/>
+      <c r="F28" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="G28" s="35" t="n"/>
       <c r="H28" s="28" t="inlineStr">
         <is>
@@ -4560,7 +4572,11 @@
           <t>Nathan R.</t>
         </is>
       </c>
-      <c r="C17" s="29" t="n"/>
+      <c r="C17" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="D17" s="29" t="n"/>
       <c r="E17" s="28" t="inlineStr">
         <is>
@@ -4568,7 +4584,11 @@
         </is>
       </c>
       <c r="F17" s="29" t="n"/>
-      <c r="G17" s="29" t="n"/>
+      <c r="G17" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="H17" s="28" t="inlineStr">
         <is>
           <t>Y</t>

--- a/Shop_Tracker_2065_2026.xlsx
+++ b/Shop_Tracker_2065_2026.xlsx
@@ -364,13 +364,13 @@
     <xf numFmtId="0" fontId="11" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="20" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1090,7 +1090,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D14" s="29" t="n"/>
+      <c r="D14" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E14" s="28" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1110,11 +1114,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$G$7,C14:G14,"Y"),"")</f>
         <v/>
       </c>
-      <c r="I14" s="30">
+      <c r="I14" s="29">
         <f>COUNTIF(C14:G14,"Y")</f>
         <v/>
       </c>
-      <c r="J14" s="31">
+      <c r="J14" s="30">
         <f>SUMPRODUCT((C$7:$G$7=1)*(C14:G14="Y"))*50</f>
         <v/>
       </c>
@@ -1128,24 +1132,24 @@
           <t>Vicki L.</t>
         </is>
       </c>
-      <c r="C15" s="29" t="n"/>
+      <c r="C15" s="31" t="n"/>
       <c r="D15" s="28" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="E15" s="29" t="n"/>
-      <c r="F15" s="29" t="n"/>
-      <c r="G15" s="29" t="n"/>
+      <c r="E15" s="31" t="n"/>
+      <c r="F15" s="31" t="n"/>
+      <c r="G15" s="31" t="n"/>
       <c r="H15" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$G$7,C15:G15,"Y"),"")</f>
         <v/>
       </c>
-      <c r="I15" s="30">
+      <c r="I15" s="29">
         <f>COUNTIF(C15:G15,"Y")</f>
         <v/>
       </c>
-      <c r="J15" s="31">
+      <c r="J15" s="30">
         <f>SUMPRODUCT((C$7:$G$7=1)*(C15:G15="Y"))*50</f>
         <v/>
       </c>
@@ -1159,20 +1163,20 @@
           <t>Kasey W.</t>
         </is>
       </c>
-      <c r="C16" s="29" t="n"/>
-      <c r="D16" s="29" t="n"/>
-      <c r="E16" s="29" t="n"/>
-      <c r="F16" s="29" t="n"/>
-      <c r="G16" s="29" t="n"/>
+      <c r="C16" s="31" t="n"/>
+      <c r="D16" s="31" t="n"/>
+      <c r="E16" s="31" t="n"/>
+      <c r="F16" s="31" t="n"/>
+      <c r="G16" s="31" t="n"/>
       <c r="H16" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$G$7,C16:G16,"Y"),"")</f>
         <v/>
       </c>
-      <c r="I16" s="30">
+      <c r="I16" s="29">
         <f>COUNTIF(C16:G16,"Y")</f>
         <v/>
       </c>
-      <c r="J16" s="31">
+      <c r="J16" s="30">
         <f>SUMPRODUCT((C$7:$G$7=1)*(C16:G16="Y"))*50</f>
         <v/>
       </c>
@@ -1186,20 +1190,20 @@
           <t>Nathan R.</t>
         </is>
       </c>
-      <c r="C17" s="29" t="n"/>
-      <c r="D17" s="29" t="n"/>
-      <c r="E17" s="29" t="n"/>
-      <c r="F17" s="29" t="n"/>
-      <c r="G17" s="29" t="n"/>
+      <c r="C17" s="31" t="n"/>
+      <c r="D17" s="31" t="n"/>
+      <c r="E17" s="31" t="n"/>
+      <c r="F17" s="31" t="n"/>
+      <c r="G17" s="31" t="n"/>
       <c r="H17" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$G$7,C17:G17,"Y"),"")</f>
         <v/>
       </c>
-      <c r="I17" s="30">
+      <c r="I17" s="29">
         <f>COUNTIF(C17:G17,"Y")</f>
         <v/>
       </c>
-      <c r="J17" s="31">
+      <c r="J17" s="30">
         <f>SUMPRODUCT((C$7:$G$7=1)*(C17:G17="Y"))*50</f>
         <v/>
       </c>
@@ -1232,11 +1236,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$G$7,C20:G20,"Y"),"")</f>
         <v/>
       </c>
-      <c r="I20" s="30">
+      <c r="I20" s="29">
         <f>COUNTIF(C20:G20,"Y")</f>
         <v/>
       </c>
-      <c r="J20" s="31">
+      <c r="J20" s="30">
         <f>SUMPRODUCT((C$7:$G$7=1)*(C20:G20="Y"))*50</f>
         <v/>
       </c>
@@ -1263,11 +1267,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$G$7,C21:G21,"Y"),"")</f>
         <v/>
       </c>
-      <c r="I21" s="30">
+      <c r="I21" s="29">
         <f>COUNTIF(C21:G21,"Y")</f>
         <v/>
       </c>
-      <c r="J21" s="31">
+      <c r="J21" s="30">
         <f>SUMPRODUCT((C$7:$G$7=1)*(C21:G21="Y"))*50</f>
         <v/>
       </c>
@@ -1298,11 +1302,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$G$7,C22:G22,"Y"),"")</f>
         <v/>
       </c>
-      <c r="I22" s="30">
+      <c r="I22" s="29">
         <f>COUNTIF(C22:G22,"Y")</f>
         <v/>
       </c>
-      <c r="J22" s="31">
+      <c r="J22" s="30">
         <f>SUMPRODUCT((C$7:$G$7=1)*(C22:G22="Y"))*50</f>
         <v/>
       </c>
@@ -1329,11 +1333,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$G$7,C23:G23,"Y"),"")</f>
         <v/>
       </c>
-      <c r="I23" s="30">
+      <c r="I23" s="29">
         <f>COUNTIF(C23:G23,"Y")</f>
         <v/>
       </c>
-      <c r="J23" s="31">
+      <c r="J23" s="30">
         <f>SUMPRODUCT((C$7:$G$7=1)*(C23:G23="Y"))*50</f>
         <v/>
       </c>
@@ -1356,11 +1360,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$G$7,C24:G24,"Y"),"")</f>
         <v/>
       </c>
-      <c r="I24" s="30">
+      <c r="I24" s="29">
         <f>COUNTIF(C24:G24,"Y")</f>
         <v/>
       </c>
-      <c r="J24" s="31">
+      <c r="J24" s="30">
         <f>SUMPRODUCT((C$7:$G$7=1)*(C24:G24="Y"))*50</f>
         <v/>
       </c>
@@ -1383,11 +1387,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$G$7,C25:G25,"Y"),"")</f>
         <v/>
       </c>
-      <c r="I25" s="30">
+      <c r="I25" s="29">
         <f>COUNTIF(C25:G25,"Y")</f>
         <v/>
       </c>
-      <c r="J25" s="31">
+      <c r="J25" s="30">
         <f>SUMPRODUCT((C$7:$G$7=1)*(C25:G25="Y"))*50</f>
         <v/>
       </c>
@@ -1422,11 +1426,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$G$7,C26:G26,"Y"),"")</f>
         <v/>
       </c>
-      <c r="I26" s="30">
+      <c r="I26" s="29">
         <f>COUNTIF(C26:G26,"Y")</f>
         <v/>
       </c>
-      <c r="J26" s="31">
+      <c r="J26" s="30">
         <f>SUMPRODUCT((C$7:$G$7=1)*(C26:G26="Y"))*50</f>
         <v/>
       </c>
@@ -1449,11 +1453,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$G$7,C27:G27,"Y"),"")</f>
         <v/>
       </c>
-      <c r="I27" s="30">
+      <c r="I27" s="29">
         <f>COUNTIF(C27:G27,"Y")</f>
         <v/>
       </c>
-      <c r="J27" s="31">
+      <c r="J27" s="30">
         <f>SUMPRODUCT((C$7:$G$7=1)*(C27:G27="Y"))*50</f>
         <v/>
       </c>
@@ -1476,11 +1480,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$G$7,C28:G28,"Y"),"")</f>
         <v/>
       </c>
-      <c r="I28" s="30">
+      <c r="I28" s="29">
         <f>COUNTIF(C28:G28,"Y")</f>
         <v/>
       </c>
-      <c r="J28" s="31">
+      <c r="J28" s="30">
         <f>SUMPRODUCT((C$7:$G$7=1)*(C28:G28="Y"))*50</f>
         <v/>
       </c>
@@ -1499,19 +1503,27 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D29" s="18" t="n"/>
+      <c r="D29" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E29" s="18" t="n"/>
       <c r="F29" s="18" t="n"/>
-      <c r="G29" s="18" t="n"/>
+      <c r="G29" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="H29" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$G$7,C29:G29,"Y"),"")</f>
         <v/>
       </c>
-      <c r="I29" s="30">
+      <c r="I29" s="29">
         <f>COUNTIF(C29:G29,"Y")</f>
         <v/>
       </c>
-      <c r="J29" s="31">
+      <c r="J29" s="30">
         <f>SUMPRODUCT((C$7:$G$7=1)*(C29:G29="Y"))*50</f>
         <v/>
       </c>
@@ -1534,11 +1546,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$G$7,C30:G30,"Y"),"")</f>
         <v/>
       </c>
-      <c r="I30" s="30">
+      <c r="I30" s="29">
         <f>COUNTIF(C30:G30,"Y")</f>
         <v/>
       </c>
-      <c r="J30" s="31">
+      <c r="J30" s="30">
         <f>SUMPRODUCT((C$7:$G$7=1)*(C30:G30="Y"))*50</f>
         <v/>
       </c>
@@ -1561,11 +1573,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$G$7,C31:G31,"Y"),"")</f>
         <v/>
       </c>
-      <c r="I31" s="30">
+      <c r="I31" s="29">
         <f>COUNTIF(C31:G31,"Y")</f>
         <v/>
       </c>
-      <c r="J31" s="31">
+      <c r="J31" s="30">
         <f>SUMPRODUCT((C$7:$G$7=1)*(C31:G31="Y"))*50</f>
         <v/>
       </c>
@@ -1588,11 +1600,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$G$7,C32:G32,"Y"),"")</f>
         <v/>
       </c>
-      <c r="I32" s="30">
+      <c r="I32" s="29">
         <f>COUNTIF(C32:G32,"Y")</f>
         <v/>
       </c>
-      <c r="J32" s="31">
+      <c r="J32" s="30">
         <f>SUMPRODUCT((C$7:$G$7=1)*(C32:G32="Y"))*50</f>
         <v/>
       </c>
@@ -1623,11 +1635,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$G$7,C33:G33,"Y"),"")</f>
         <v/>
       </c>
-      <c r="I33" s="30">
+      <c r="I33" s="29">
         <f>COUNTIF(C33:G33,"Y")</f>
         <v/>
       </c>
-      <c r="J33" s="31">
+      <c r="J33" s="30">
         <f>SUMPRODUCT((C$7:$G$7=1)*(C33:G33="Y"))*50</f>
         <v/>
       </c>
@@ -1646,7 +1658,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D34" s="35" t="n"/>
+      <c r="D34" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E34" s="35" t="n"/>
       <c r="F34" s="28" t="inlineStr">
         <is>
@@ -1658,11 +1674,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$G$7,C34:G34,"Y"),"")</f>
         <v/>
       </c>
-      <c r="I34" s="30">
+      <c r="I34" s="29">
         <f>COUNTIF(C34:G34,"Y")</f>
         <v/>
       </c>
-      <c r="J34" s="31">
+      <c r="J34" s="30">
         <f>SUMPRODUCT((C$7:$G$7=1)*(C34:G34="Y"))*50</f>
         <v/>
       </c>
@@ -1688,16 +1704,20 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G35" s="18" t="n"/>
+      <c r="G35" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="H35" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$G$7,C35:G35,"Y"),"")</f>
         <v/>
       </c>
-      <c r="I35" s="30">
+      <c r="I35" s="29">
         <f>COUNTIF(C35:G35,"Y")</f>
         <v/>
       </c>
-      <c r="J35" s="31">
+      <c r="J35" s="30">
         <f>SUMPRODUCT((C$7:$G$7=1)*(C35:G35="Y"))*50</f>
         <v/>
       </c>
@@ -1720,11 +1740,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$G$7,C36:G36,"Y"),"")</f>
         <v/>
       </c>
-      <c r="I36" s="30">
+      <c r="I36" s="29">
         <f>COUNTIF(C36:G36,"Y")</f>
         <v/>
       </c>
-      <c r="J36" s="31">
+      <c r="J36" s="30">
         <f>SUMPRODUCT((C$7:$G$7=1)*(C36:G36="Y"))*50</f>
         <v/>
       </c>
@@ -1759,11 +1779,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$G$7,C37:G37,"Y"),"")</f>
         <v/>
       </c>
-      <c r="I37" s="30">
+      <c r="I37" s="29">
         <f>COUNTIF(C37:G37,"Y")</f>
         <v/>
       </c>
-      <c r="J37" s="31">
+      <c r="J37" s="30">
         <f>SUMPRODUCT((C$7:$G$7=1)*(C37:G37="Y"))*50</f>
         <v/>
       </c>
@@ -1786,11 +1806,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$G$7,C38:G38,"Y"),"")</f>
         <v/>
       </c>
-      <c r="I38" s="30">
+      <c r="I38" s="29">
         <f>COUNTIF(C38:G38,"Y")</f>
         <v/>
       </c>
-      <c r="J38" s="31">
+      <c r="J38" s="30">
         <f>SUMPRODUCT((C$7:$G$7=1)*(C38:G38="Y"))*50</f>
         <v/>
       </c>
@@ -2206,19 +2226,23 @@
           <t>Madison C.</t>
         </is>
       </c>
-      <c r="C14" s="29" t="n"/>
+      <c r="C14" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="D14" s="28" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="E14" s="29" t="n"/>
+      <c r="E14" s="31" t="n"/>
       <c r="F14" s="28" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="G14" s="29" t="n"/>
+      <c r="G14" s="31" t="n"/>
       <c r="H14" s="28" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2228,11 +2252,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$H$7,C14:H14,"Y"),"")</f>
         <v/>
       </c>
-      <c r="J14" s="30">
+      <c r="J14" s="29">
         <f>COUNTIF(C14:H14,"Y")</f>
         <v/>
       </c>
-      <c r="K14" s="31">
+      <c r="K14" s="30">
         <f>SUMPRODUCT((C$7:$H$7=1)*(C14:H14="Y"))*50</f>
         <v/>
       </c>
@@ -2251,28 +2275,28 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D15" s="29" t="n"/>
+      <c r="D15" s="31" t="n"/>
       <c r="E15" s="28" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F15" s="29" t="n"/>
+      <c r="F15" s="31" t="n"/>
       <c r="G15" s="28" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H15" s="29" t="n"/>
+      <c r="H15" s="31" t="n"/>
       <c r="I15" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$H$7,C15:H15,"Y"),"")</f>
         <v/>
       </c>
-      <c r="J15" s="30">
+      <c r="J15" s="29">
         <f>COUNTIF(C15:H15,"Y")</f>
         <v/>
       </c>
-      <c r="K15" s="31">
+      <c r="K15" s="30">
         <f>SUMPRODUCT((C$7:$H$7=1)*(C15:H15="Y"))*50</f>
         <v/>
       </c>
@@ -2291,14 +2315,14 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D16" s="29" t="n"/>
-      <c r="E16" s="29" t="n"/>
+      <c r="D16" s="31" t="n"/>
+      <c r="E16" s="31" t="n"/>
       <c r="F16" s="28" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="G16" s="29" t="n"/>
+      <c r="G16" s="31" t="n"/>
       <c r="H16" s="28" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2308,11 +2332,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$H$7,C16:H16,"Y"),"")</f>
         <v/>
       </c>
-      <c r="J16" s="30">
+      <c r="J16" s="29">
         <f>COUNTIF(C16:H16,"Y")</f>
         <v/>
       </c>
-      <c r="K16" s="31">
+      <c r="K16" s="30">
         <f>SUMPRODUCT((C$7:$H$7=1)*(C16:H16="Y"))*50</f>
         <v/>
       </c>
@@ -2331,20 +2355,20 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D17" s="29" t="n"/>
-      <c r="E17" s="29" t="n"/>
-      <c r="F17" s="29" t="n"/>
-      <c r="G17" s="29" t="n"/>
-      <c r="H17" s="29" t="n"/>
+      <c r="D17" s="31" t="n"/>
+      <c r="E17" s="31" t="n"/>
+      <c r="F17" s="31" t="n"/>
+      <c r="G17" s="31" t="n"/>
+      <c r="H17" s="31" t="n"/>
       <c r="I17" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$H$7,C17:H17,"Y"),"")</f>
         <v/>
       </c>
-      <c r="J17" s="30">
+      <c r="J17" s="29">
         <f>COUNTIF(C17:H17,"Y")</f>
         <v/>
       </c>
-      <c r="K17" s="31">
+      <c r="K17" s="30">
         <f>SUMPRODUCT((C$7:$H$7=1)*(C17:H17="Y"))*50</f>
         <v/>
       </c>
@@ -2378,11 +2402,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$H$7,C20:H20,"Y"),"")</f>
         <v/>
       </c>
-      <c r="J20" s="30">
+      <c r="J20" s="29">
         <f>COUNTIF(C20:H20,"Y")</f>
         <v/>
       </c>
-      <c r="K20" s="31">
+      <c r="K20" s="30">
         <f>SUMPRODUCT((C$7:$H$7=1)*(C20:H20="Y"))*50</f>
         <v/>
       </c>
@@ -2406,11 +2430,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$H$7,C21:H21,"Y"),"")</f>
         <v/>
       </c>
-      <c r="J21" s="30">
+      <c r="J21" s="29">
         <f>COUNTIF(C21:H21,"Y")</f>
         <v/>
       </c>
-      <c r="K21" s="31">
+      <c r="K21" s="30">
         <f>SUMPRODUCT((C$7:$H$7=1)*(C21:H21="Y"))*50</f>
         <v/>
       </c>
@@ -2438,11 +2462,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$H$7,C22:H22,"Y"),"")</f>
         <v/>
       </c>
-      <c r="J22" s="30">
+      <c r="J22" s="29">
         <f>COUNTIF(C22:H22,"Y")</f>
         <v/>
       </c>
-      <c r="K22" s="31">
+      <c r="K22" s="30">
         <f>SUMPRODUCT((C$7:$H$7=1)*(C22:H22="Y"))*50</f>
         <v/>
       </c>
@@ -2466,11 +2490,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$H$7,C23:H23,"Y"),"")</f>
         <v/>
       </c>
-      <c r="J23" s="30">
+      <c r="J23" s="29">
         <f>COUNTIF(C23:H23,"Y")</f>
         <v/>
       </c>
-      <c r="K23" s="31">
+      <c r="K23" s="30">
         <f>SUMPRODUCT((C$7:$H$7=1)*(C23:H23="Y"))*50</f>
         <v/>
       </c>
@@ -2494,11 +2518,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$H$7,C24:H24,"Y"),"")</f>
         <v/>
       </c>
-      <c r="J24" s="30">
+      <c r="J24" s="29">
         <f>COUNTIF(C24:H24,"Y")</f>
         <v/>
       </c>
-      <c r="K24" s="31">
+      <c r="K24" s="30">
         <f>SUMPRODUCT((C$7:$H$7=1)*(C24:H24="Y"))*50</f>
         <v/>
       </c>
@@ -2522,11 +2546,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$H$7,C25:H25,"Y"),"")</f>
         <v/>
       </c>
-      <c r="J25" s="30">
+      <c r="J25" s="29">
         <f>COUNTIF(C25:H25,"Y")</f>
         <v/>
       </c>
-      <c r="K25" s="31">
+      <c r="K25" s="30">
         <f>SUMPRODUCT((C$7:$H$7=1)*(C25:H25="Y"))*50</f>
         <v/>
       </c>
@@ -2562,11 +2586,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$H$7,C26:H26,"Y"),"")</f>
         <v/>
       </c>
-      <c r="J26" s="30">
+      <c r="J26" s="29">
         <f>COUNTIF(C26:H26,"Y")</f>
         <v/>
       </c>
-      <c r="K26" s="31">
+      <c r="K26" s="30">
         <f>SUMPRODUCT((C$7:$H$7=1)*(C26:H26="Y"))*50</f>
         <v/>
       </c>
@@ -2590,11 +2614,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$H$7,C27:H27,"Y"),"")</f>
         <v/>
       </c>
-      <c r="J27" s="30">
+      <c r="J27" s="29">
         <f>COUNTIF(C27:H27,"Y")</f>
         <v/>
       </c>
-      <c r="K27" s="31">
+      <c r="K27" s="30">
         <f>SUMPRODUCT((C$7:$H$7=1)*(C27:H27="Y"))*50</f>
         <v/>
       </c>
@@ -2626,11 +2650,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$H$7,C28:H28,"Y"),"")</f>
         <v/>
       </c>
-      <c r="J28" s="30">
+      <c r="J28" s="29">
         <f>COUNTIF(C28:H28,"Y")</f>
         <v/>
       </c>
-      <c r="K28" s="31">
+      <c r="K28" s="30">
         <f>SUMPRODUCT((C$7:$H$7=1)*(C28:H28="Y"))*50</f>
         <v/>
       </c>
@@ -2656,7 +2680,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G29" s="18" t="n"/>
+      <c r="G29" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="H29" s="28" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2666,11 +2694,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$H$7,C29:H29,"Y"),"")</f>
         <v/>
       </c>
-      <c r="J29" s="30">
+      <c r="J29" s="29">
         <f>COUNTIF(C29:H29,"Y")</f>
         <v/>
       </c>
-      <c r="K29" s="31">
+      <c r="K29" s="30">
         <f>SUMPRODUCT((C$7:$H$7=1)*(C29:H29="Y"))*50</f>
         <v/>
       </c>
@@ -2694,11 +2722,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$H$7,C30:H30,"Y"),"")</f>
         <v/>
       </c>
-      <c r="J30" s="30">
+      <c r="J30" s="29">
         <f>COUNTIF(C30:H30,"Y")</f>
         <v/>
       </c>
-      <c r="K30" s="31">
+      <c r="K30" s="30">
         <f>SUMPRODUCT((C$7:$H$7=1)*(C30:H30="Y"))*50</f>
         <v/>
       </c>
@@ -2722,11 +2750,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$H$7,C31:H31,"Y"),"")</f>
         <v/>
       </c>
-      <c r="J31" s="30">
+      <c r="J31" s="29">
         <f>COUNTIF(C31:H31,"Y")</f>
         <v/>
       </c>
-      <c r="K31" s="31">
+      <c r="K31" s="30">
         <f>SUMPRODUCT((C$7:$H$7=1)*(C31:H31="Y"))*50</f>
         <v/>
       </c>
@@ -2750,11 +2778,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$H$7,C32:H32,"Y"),"")</f>
         <v/>
       </c>
-      <c r="J32" s="30">
+      <c r="J32" s="29">
         <f>COUNTIF(C32:H32,"Y")</f>
         <v/>
       </c>
-      <c r="K32" s="31">
+      <c r="K32" s="30">
         <f>SUMPRODUCT((C$7:$H$7=1)*(C32:H32="Y"))*50</f>
         <v/>
       </c>
@@ -2790,11 +2818,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$H$7,C33:H33,"Y"),"")</f>
         <v/>
       </c>
-      <c r="J33" s="30">
+      <c r="J33" s="29">
         <f>COUNTIF(C33:H33,"Y")</f>
         <v/>
       </c>
-      <c r="K33" s="31">
+      <c r="K33" s="30">
         <f>SUMPRODUCT((C$7:$H$7=1)*(C33:H33="Y"))*50</f>
         <v/>
       </c>
@@ -2808,29 +2836,41 @@
           <t>Maylin</t>
         </is>
       </c>
-      <c r="C34" s="35" t="n"/>
+      <c r="C34" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="D34" s="28" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="E34" s="35" t="n"/>
+      <c r="E34" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F34" s="28" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="G34" s="35" t="n"/>
+      <c r="G34" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="H34" s="35" t="n"/>
       <c r="I34" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$H$7,C34:H34,"Y"),"")</f>
         <v/>
       </c>
-      <c r="J34" s="30">
+      <c r="J34" s="29">
         <f>COUNTIF(C34:H34,"Y")</f>
         <v/>
       </c>
-      <c r="K34" s="31">
+      <c r="K34" s="30">
         <f>SUMPRODUCT((C$7:$H$7=1)*(C34:H34="Y"))*50</f>
         <v/>
       </c>
@@ -2866,11 +2906,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$H$7,C35:H35,"Y"),"")</f>
         <v/>
       </c>
-      <c r="J35" s="30">
+      <c r="J35" s="29">
         <f>COUNTIF(C35:H35,"Y")</f>
         <v/>
       </c>
-      <c r="K35" s="31">
+      <c r="K35" s="30">
         <f>SUMPRODUCT((C$7:$H$7=1)*(C35:H35="Y"))*50</f>
         <v/>
       </c>
@@ -2884,7 +2924,11 @@
           <t>Richard</t>
         </is>
       </c>
-      <c r="C36" s="35" t="n"/>
+      <c r="C36" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="D36" s="35" t="n"/>
       <c r="E36" s="35" t="n"/>
       <c r="F36" s="35" t="n"/>
@@ -2894,11 +2938,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$H$7,C36:H36,"Y"),"")</f>
         <v/>
       </c>
-      <c r="J36" s="30">
+      <c r="J36" s="29">
         <f>COUNTIF(C36:H36,"Y")</f>
         <v/>
       </c>
-      <c r="K36" s="31">
+      <c r="K36" s="30">
         <f>SUMPRODUCT((C$7:$H$7=1)*(C36:H36="Y"))*50</f>
         <v/>
       </c>
@@ -2930,11 +2974,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$H$7,C37:H37,"Y"),"")</f>
         <v/>
       </c>
-      <c r="J37" s="30">
+      <c r="J37" s="29">
         <f>COUNTIF(C37:H37,"Y")</f>
         <v/>
       </c>
-      <c r="K37" s="31">
+      <c r="K37" s="30">
         <f>SUMPRODUCT((C$7:$H$7=1)*(C37:H37="Y"))*50</f>
         <v/>
       </c>
@@ -2958,11 +3002,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$H$7,C38:H38,"Y"),"")</f>
         <v/>
       </c>
-      <c r="J38" s="30">
+      <c r="J38" s="29">
         <f>COUNTIF(C38:H38,"Y")</f>
         <v/>
       </c>
-      <c r="K38" s="31">
+      <c r="K38" s="30">
         <f>SUMPRODUCT((C$7:$H$7=1)*(C38:H38="Y"))*50</f>
         <v/>
       </c>
@@ -3356,23 +3400,31 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D14" s="29" t="n"/>
-      <c r="E14" s="29" t="n"/>
+      <c r="D14" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E14" s="31" t="n"/>
       <c r="F14" s="28" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="G14" s="29" t="n"/>
+      <c r="G14" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="H14" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$G$7,C14:G14,"Y"),"")</f>
         <v/>
       </c>
-      <c r="I14" s="30">
+      <c r="I14" s="29">
         <f>COUNTIF(C14:G14,"Y")</f>
         <v/>
       </c>
-      <c r="J14" s="31">
+      <c r="J14" s="30">
         <f>SUMPRODUCT((C$7:$G$7=1)*(C14:G14="Y"))*50</f>
         <v/>
       </c>
@@ -3386,14 +3438,14 @@
           <t>Vicki L.</t>
         </is>
       </c>
-      <c r="C15" s="29" t="n"/>
-      <c r="D15" s="29" t="n"/>
+      <c r="C15" s="31" t="n"/>
+      <c r="D15" s="31" t="n"/>
       <c r="E15" s="28" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F15" s="29" t="n"/>
+      <c r="F15" s="31" t="n"/>
       <c r="G15" s="28" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3403,11 +3455,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$G$7,C15:G15,"Y"),"")</f>
         <v/>
       </c>
-      <c r="I15" s="30">
+      <c r="I15" s="29">
         <f>COUNTIF(C15:G15,"Y")</f>
         <v/>
       </c>
-      <c r="J15" s="31">
+      <c r="J15" s="30">
         <f>SUMPRODUCT((C$7:$G$7=1)*(C15:G15="Y"))*50</f>
         <v/>
       </c>
@@ -3426,19 +3478,23 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D16" s="29" t="n"/>
-      <c r="E16" s="29" t="n"/>
-      <c r="F16" s="29" t="n"/>
-      <c r="G16" s="29" t="n"/>
+      <c r="D16" s="31" t="n"/>
+      <c r="E16" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F16" s="31" t="n"/>
+      <c r="G16" s="31" t="n"/>
       <c r="H16" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$G$7,C16:G16,"Y"),"")</f>
         <v/>
       </c>
-      <c r="I16" s="30">
+      <c r="I16" s="29">
         <f>COUNTIF(C16:G16,"Y")</f>
         <v/>
       </c>
-      <c r="J16" s="31">
+      <c r="J16" s="30">
         <f>SUMPRODUCT((C$7:$G$7=1)*(C16:G16="Y"))*50</f>
         <v/>
       </c>
@@ -3452,10 +3508,10 @@
           <t>Nathan R.</t>
         </is>
       </c>
-      <c r="C17" s="29" t="n"/>
-      <c r="D17" s="29" t="n"/>
-      <c r="E17" s="29" t="n"/>
-      <c r="F17" s="29" t="n"/>
+      <c r="C17" s="31" t="n"/>
+      <c r="D17" s="31" t="n"/>
+      <c r="E17" s="31" t="n"/>
+      <c r="F17" s="31" t="n"/>
       <c r="G17" s="28" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3465,11 +3521,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$G$7,C17:G17,"Y"),"")</f>
         <v/>
       </c>
-      <c r="I17" s="30">
+      <c r="I17" s="29">
         <f>COUNTIF(C17:G17,"Y")</f>
         <v/>
       </c>
-      <c r="J17" s="31">
+      <c r="J17" s="30">
         <f>SUMPRODUCT((C$7:$G$7=1)*(C17:G17="Y"))*50</f>
         <v/>
       </c>
@@ -3502,11 +3558,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$G$7,C20:G20,"Y"),"")</f>
         <v/>
       </c>
-      <c r="I20" s="30">
+      <c r="I20" s="29">
         <f>COUNTIF(C20:G20,"Y")</f>
         <v/>
       </c>
-      <c r="J20" s="31">
+      <c r="J20" s="30">
         <f>SUMPRODUCT((C$7:$G$7=1)*(C20:G20="Y"))*50</f>
         <v/>
       </c>
@@ -3529,11 +3585,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$G$7,C21:G21,"Y"),"")</f>
         <v/>
       </c>
-      <c r="I21" s="30">
+      <c r="I21" s="29">
         <f>COUNTIF(C21:G21,"Y")</f>
         <v/>
       </c>
-      <c r="J21" s="31">
+      <c r="J21" s="30">
         <f>SUMPRODUCT((C$7:$G$7=1)*(C21:G21="Y"))*50</f>
         <v/>
       </c>
@@ -3564,11 +3620,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$G$7,C22:G22,"Y"),"")</f>
         <v/>
       </c>
-      <c r="I22" s="30">
+      <c r="I22" s="29">
         <f>COUNTIF(C22:G22,"Y")</f>
         <v/>
       </c>
-      <c r="J22" s="31">
+      <c r="J22" s="30">
         <f>SUMPRODUCT((C$7:$G$7=1)*(C22:G22="Y"))*50</f>
         <v/>
       </c>
@@ -3595,11 +3651,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$G$7,C23:G23,"Y"),"")</f>
         <v/>
       </c>
-      <c r="I23" s="30">
+      <c r="I23" s="29">
         <f>COUNTIF(C23:G23,"Y")</f>
         <v/>
       </c>
-      <c r="J23" s="31">
+      <c r="J23" s="30">
         <f>SUMPRODUCT((C$7:$G$7=1)*(C23:G23="Y"))*50</f>
         <v/>
       </c>
@@ -3622,11 +3678,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$G$7,C24:G24,"Y"),"")</f>
         <v/>
       </c>
-      <c r="I24" s="30">
+      <c r="I24" s="29">
         <f>COUNTIF(C24:G24,"Y")</f>
         <v/>
       </c>
-      <c r="J24" s="31">
+      <c r="J24" s="30">
         <f>SUMPRODUCT((C$7:$G$7=1)*(C24:G24="Y"))*50</f>
         <v/>
       </c>
@@ -3649,11 +3705,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$G$7,C25:G25,"Y"),"")</f>
         <v/>
       </c>
-      <c r="I25" s="30">
+      <c r="I25" s="29">
         <f>COUNTIF(C25:G25,"Y")</f>
         <v/>
       </c>
-      <c r="J25" s="31">
+      <c r="J25" s="30">
         <f>SUMPRODUCT((C$7:$G$7=1)*(C25:G25="Y"))*50</f>
         <v/>
       </c>
@@ -3692,11 +3748,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$G$7,C26:G26,"Y"),"")</f>
         <v/>
       </c>
-      <c r="I26" s="30">
+      <c r="I26" s="29">
         <f>COUNTIF(C26:G26,"Y")</f>
         <v/>
       </c>
-      <c r="J26" s="31">
+      <c r="J26" s="30">
         <f>SUMPRODUCT((C$7:$G$7=1)*(C26:G26="Y"))*50</f>
         <v/>
       </c>
@@ -3719,11 +3775,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$G$7,C27:G27,"Y"),"")</f>
         <v/>
       </c>
-      <c r="I27" s="30">
+      <c r="I27" s="29">
         <f>COUNTIF(C27:G27,"Y")</f>
         <v/>
       </c>
-      <c r="J27" s="31">
+      <c r="J27" s="30">
         <f>SUMPRODUCT((C$7:$G$7=1)*(C27:G27="Y"))*50</f>
         <v/>
       </c>
@@ -3754,11 +3810,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$G$7,C28:G28,"Y"),"")</f>
         <v/>
       </c>
-      <c r="I28" s="30">
+      <c r="I28" s="29">
         <f>COUNTIF(C28:G28,"Y")</f>
         <v/>
       </c>
-      <c r="J28" s="31">
+      <c r="J28" s="30">
         <f>SUMPRODUCT((C$7:$G$7=1)*(C28:G28="Y"))*50</f>
         <v/>
       </c>
@@ -3774,18 +3830,22 @@
       </c>
       <c r="C29" s="18" t="n"/>
       <c r="D29" s="18" t="n"/>
-      <c r="E29" s="18" t="n"/>
+      <c r="E29" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F29" s="18" t="n"/>
       <c r="G29" s="18" t="n"/>
       <c r="H29" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$G$7,C29:G29,"Y"),"")</f>
         <v/>
       </c>
-      <c r="I29" s="30">
+      <c r="I29" s="29">
         <f>COUNTIF(C29:G29,"Y")</f>
         <v/>
       </c>
-      <c r="J29" s="31">
+      <c r="J29" s="30">
         <f>SUMPRODUCT((C$7:$G$7=1)*(C29:G29="Y"))*50</f>
         <v/>
       </c>
@@ -3808,11 +3868,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$G$7,C30:G30,"Y"),"")</f>
         <v/>
       </c>
-      <c r="I30" s="30">
+      <c r="I30" s="29">
         <f>COUNTIF(C30:G30,"Y")</f>
         <v/>
       </c>
-      <c r="J30" s="31">
+      <c r="J30" s="30">
         <f>SUMPRODUCT((C$7:$G$7=1)*(C30:G30="Y"))*50</f>
         <v/>
       </c>
@@ -3835,11 +3895,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$G$7,C31:G31,"Y"),"")</f>
         <v/>
       </c>
-      <c r="I31" s="30">
+      <c r="I31" s="29">
         <f>COUNTIF(C31:G31,"Y")</f>
         <v/>
       </c>
-      <c r="J31" s="31">
+      <c r="J31" s="30">
         <f>SUMPRODUCT((C$7:$G$7=1)*(C31:G31="Y"))*50</f>
         <v/>
       </c>
@@ -3862,11 +3922,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$G$7,C32:G32,"Y"),"")</f>
         <v/>
       </c>
-      <c r="I32" s="30">
+      <c r="I32" s="29">
         <f>COUNTIF(C32:G32,"Y")</f>
         <v/>
       </c>
-      <c r="J32" s="31">
+      <c r="J32" s="30">
         <f>SUMPRODUCT((C$7:$G$7=1)*(C32:G32="Y"))*50</f>
         <v/>
       </c>
@@ -3897,11 +3957,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$G$7,C33:G33,"Y"),"")</f>
         <v/>
       </c>
-      <c r="I33" s="30">
+      <c r="I33" s="29">
         <f>COUNTIF(C33:G33,"Y")</f>
         <v/>
       </c>
-      <c r="J33" s="31">
+      <c r="J33" s="30">
         <f>SUMPRODUCT((C$7:$G$7=1)*(C33:G33="Y"))*50</f>
         <v/>
       </c>
@@ -3920,23 +3980,35 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D34" s="35" t="n"/>
-      <c r="E34" s="35" t="n"/>
+      <c r="D34" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E34" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F34" s="28" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="G34" s="35" t="n"/>
+      <c r="G34" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="H34" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$G$7,C34:G34,"Y"),"")</f>
         <v/>
       </c>
-      <c r="I34" s="30">
+      <c r="I34" s="29">
         <f>COUNTIF(C34:G34,"Y")</f>
         <v/>
       </c>
-      <c r="J34" s="31">
+      <c r="J34" s="30">
         <f>SUMPRODUCT((C$7:$G$7=1)*(C34:G34="Y"))*50</f>
         <v/>
       </c>
@@ -3959,11 +4031,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$G$7,C35:G35,"Y"),"")</f>
         <v/>
       </c>
-      <c r="I35" s="30">
+      <c r="I35" s="29">
         <f>COUNTIF(C35:G35,"Y")</f>
         <v/>
       </c>
-      <c r="J35" s="31">
+      <c r="J35" s="30">
         <f>SUMPRODUCT((C$7:$G$7=1)*(C35:G35="Y"))*50</f>
         <v/>
       </c>
@@ -3986,11 +4058,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$G$7,C36:G36,"Y"),"")</f>
         <v/>
       </c>
-      <c r="I36" s="30">
+      <c r="I36" s="29">
         <f>COUNTIF(C36:G36,"Y")</f>
         <v/>
       </c>
-      <c r="J36" s="31">
+      <c r="J36" s="30">
         <f>SUMPRODUCT((C$7:$G$7=1)*(C36:G36="Y"))*50</f>
         <v/>
       </c>
@@ -4017,11 +4089,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$G$7,C37:G37,"Y"),"")</f>
         <v/>
       </c>
-      <c r="I37" s="30">
+      <c r="I37" s="29">
         <f>COUNTIF(C37:G37,"Y")</f>
         <v/>
       </c>
-      <c r="J37" s="31">
+      <c r="J37" s="30">
         <f>SUMPRODUCT((C$7:$G$7=1)*(C37:G37="Y"))*50</f>
         <v/>
       </c>
@@ -4044,11 +4116,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$G$7,C38:G38,"Y"),"")</f>
         <v/>
       </c>
-      <c r="I38" s="30">
+      <c r="I38" s="29">
         <f>COUNTIF(C38:G38,"Y")</f>
         <v/>
       </c>
-      <c r="J38" s="31">
+      <c r="J38" s="30">
         <f>SUMPRODUCT((C$7:$G$7=1)*(C38:G38="Y"))*50</f>
         <v/>
       </c>
@@ -4469,20 +4541,24 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D14" s="29" t="n"/>
-      <c r="E14" s="29" t="n"/>
-      <c r="F14" s="29" t="n"/>
-      <c r="G14" s="29" t="n"/>
-      <c r="H14" s="29" t="n"/>
+      <c r="D14" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E14" s="31" t="n"/>
+      <c r="F14" s="31" t="n"/>
+      <c r="G14" s="31" t="n"/>
+      <c r="H14" s="31" t="n"/>
       <c r="I14" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$H$7,C14:H14,"Y"),"")</f>
         <v/>
       </c>
-      <c r="J14" s="30">
+      <c r="J14" s="29">
         <f>COUNTIF(C14:H14,"Y")</f>
         <v/>
       </c>
-      <c r="K14" s="31">
+      <c r="K14" s="30">
         <f>SUMPRODUCT((C$7:$H$7=1)*(C14:H14="Y"))*50</f>
         <v/>
       </c>
@@ -4496,29 +4572,29 @@
           <t>Vicki L.</t>
         </is>
       </c>
-      <c r="C15" s="29" t="n"/>
+      <c r="C15" s="31" t="n"/>
       <c r="D15" s="28" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="E15" s="29" t="n"/>
+      <c r="E15" s="31" t="n"/>
       <c r="F15" s="28" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="G15" s="29" t="n"/>
-      <c r="H15" s="29" t="n"/>
+      <c r="G15" s="31" t="n"/>
+      <c r="H15" s="31" t="n"/>
       <c r="I15" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$H$7,C15:H15,"Y"),"")</f>
         <v/>
       </c>
-      <c r="J15" s="30">
+      <c r="J15" s="29">
         <f>COUNTIF(C15:H15,"Y")</f>
         <v/>
       </c>
-      <c r="K15" s="31">
+      <c r="K15" s="30">
         <f>SUMPRODUCT((C$7:$H$7=1)*(C15:H15="Y"))*50</f>
         <v/>
       </c>
@@ -4542,23 +4618,27 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="E16" s="29" t="n"/>
-      <c r="F16" s="29" t="n"/>
+      <c r="E16" s="31" t="n"/>
+      <c r="F16" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="G16" s="28" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H16" s="29" t="n"/>
+      <c r="H16" s="31" t="n"/>
       <c r="I16" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$H$7,C16:H16,"Y"),"")</f>
         <v/>
       </c>
-      <c r="J16" s="30">
+      <c r="J16" s="29">
         <f>COUNTIF(C16:H16,"Y")</f>
         <v/>
       </c>
-      <c r="K16" s="31">
+      <c r="K16" s="30">
         <f>SUMPRODUCT((C$7:$H$7=1)*(C16:H16="Y"))*50</f>
         <v/>
       </c>
@@ -4577,13 +4657,17 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D17" s="29" t="n"/>
+      <c r="D17" s="31" t="n"/>
       <c r="E17" s="28" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F17" s="29" t="n"/>
+      <c r="F17" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="G17" s="28" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4598,11 +4682,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$H$7,C17:H17,"Y"),"")</f>
         <v/>
       </c>
-      <c r="J17" s="30">
+      <c r="J17" s="29">
         <f>COUNTIF(C17:H17,"Y")</f>
         <v/>
       </c>
-      <c r="K17" s="31">
+      <c r="K17" s="30">
         <f>SUMPRODUCT((C$7:$H$7=1)*(C17:H17="Y"))*50</f>
         <v/>
       </c>
@@ -4636,11 +4720,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$H$7,C20:H20,"Y"),"")</f>
         <v/>
       </c>
-      <c r="J20" s="30">
+      <c r="J20" s="29">
         <f>COUNTIF(C20:H20,"Y")</f>
         <v/>
       </c>
-      <c r="K20" s="31">
+      <c r="K20" s="30">
         <f>SUMPRODUCT((C$7:$H$7=1)*(C20:H20="Y"))*50</f>
         <v/>
       </c>
@@ -4664,11 +4748,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$H$7,C21:H21,"Y"),"")</f>
         <v/>
       </c>
-      <c r="J21" s="30">
+      <c r="J21" s="29">
         <f>COUNTIF(C21:H21,"Y")</f>
         <v/>
       </c>
-      <c r="K21" s="31">
+      <c r="K21" s="30">
         <f>SUMPRODUCT((C$7:$H$7=1)*(C21:H21="Y"))*50</f>
         <v/>
       </c>
@@ -4700,11 +4784,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$H$7,C22:H22,"Y"),"")</f>
         <v/>
       </c>
-      <c r="J22" s="30">
+      <c r="J22" s="29">
         <f>COUNTIF(C22:H22,"Y")</f>
         <v/>
       </c>
-      <c r="K22" s="31">
+      <c r="K22" s="30">
         <f>SUMPRODUCT((C$7:$H$7=1)*(C22:H22="Y"))*50</f>
         <v/>
       </c>
@@ -4732,11 +4816,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$H$7,C23:H23,"Y"),"")</f>
         <v/>
       </c>
-      <c r="J23" s="30">
+      <c r="J23" s="29">
         <f>COUNTIF(C23:H23,"Y")</f>
         <v/>
       </c>
-      <c r="K23" s="31">
+      <c r="K23" s="30">
         <f>SUMPRODUCT((C$7:$H$7=1)*(C23:H23="Y"))*50</f>
         <v/>
       </c>
@@ -4764,11 +4848,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$H$7,C24:H24,"Y"),"")</f>
         <v/>
       </c>
-      <c r="J24" s="30">
+      <c r="J24" s="29">
         <f>COUNTIF(C24:H24,"Y")</f>
         <v/>
       </c>
-      <c r="K24" s="31">
+      <c r="K24" s="30">
         <f>SUMPRODUCT((C$7:$H$7=1)*(C24:H24="Y"))*50</f>
         <v/>
       </c>
@@ -4792,11 +4876,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$H$7,C25:H25,"Y"),"")</f>
         <v/>
       </c>
-      <c r="J25" s="30">
+      <c r="J25" s="29">
         <f>COUNTIF(C25:H25,"Y")</f>
         <v/>
       </c>
-      <c r="K25" s="31">
+      <c r="K25" s="30">
         <f>SUMPRODUCT((C$7:$H$7=1)*(C25:H25="Y"))*50</f>
         <v/>
       </c>
@@ -4832,11 +4916,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$H$7,C26:H26,"Y"),"")</f>
         <v/>
       </c>
-      <c r="J26" s="30">
+      <c r="J26" s="29">
         <f>COUNTIF(C26:H26,"Y")</f>
         <v/>
       </c>
-      <c r="K26" s="31">
+      <c r="K26" s="30">
         <f>SUMPRODUCT((C$7:$H$7=1)*(C26:H26="Y"))*50</f>
         <v/>
       </c>
@@ -4860,11 +4944,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$H$7,C27:H27,"Y"),"")</f>
         <v/>
       </c>
-      <c r="J27" s="30">
+      <c r="J27" s="29">
         <f>COUNTIF(C27:H27,"Y")</f>
         <v/>
       </c>
-      <c r="K27" s="31">
+      <c r="K27" s="30">
         <f>SUMPRODUCT((C$7:$H$7=1)*(C27:H27="Y"))*50</f>
         <v/>
       </c>
@@ -4892,11 +4976,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$H$7,C28:H28,"Y"),"")</f>
         <v/>
       </c>
-      <c r="J28" s="30">
+      <c r="J28" s="29">
         <f>COUNTIF(C28:H28,"Y")</f>
         <v/>
       </c>
-      <c r="K28" s="31">
+      <c r="K28" s="30">
         <f>SUMPRODUCT((C$7:$H$7=1)*(C28:H28="Y"))*50</f>
         <v/>
       </c>
@@ -4925,18 +5009,22 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="F29" s="18" t="n"/>
+      <c r="F29" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="G29" s="18" t="n"/>
       <c r="H29" s="18" t="n"/>
       <c r="I29" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$H$7,C29:H29,"Y"),"")</f>
         <v/>
       </c>
-      <c r="J29" s="30">
+      <c r="J29" s="29">
         <f>COUNTIF(C29:H29,"Y")</f>
         <v/>
       </c>
-      <c r="K29" s="31">
+      <c r="K29" s="30">
         <f>SUMPRODUCT((C$7:$H$7=1)*(C29:H29="Y"))*50</f>
         <v/>
       </c>
@@ -4960,11 +5048,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$H$7,C30:H30,"Y"),"")</f>
         <v/>
       </c>
-      <c r="J30" s="30">
+      <c r="J30" s="29">
         <f>COUNTIF(C30:H30,"Y")</f>
         <v/>
       </c>
-      <c r="K30" s="31">
+      <c r="K30" s="30">
         <f>SUMPRODUCT((C$7:$H$7=1)*(C30:H30="Y"))*50</f>
         <v/>
       </c>
@@ -4988,11 +5076,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$H$7,C31:H31,"Y"),"")</f>
         <v/>
       </c>
-      <c r="J31" s="30">
+      <c r="J31" s="29">
         <f>COUNTIF(C31:H31,"Y")</f>
         <v/>
       </c>
-      <c r="K31" s="31">
+      <c r="K31" s="30">
         <f>SUMPRODUCT((C$7:$H$7=1)*(C31:H31="Y"))*50</f>
         <v/>
       </c>
@@ -5016,11 +5104,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$H$7,C32:H32,"Y"),"")</f>
         <v/>
       </c>
-      <c r="J32" s="30">
+      <c r="J32" s="29">
         <f>COUNTIF(C32:H32,"Y")</f>
         <v/>
       </c>
-      <c r="K32" s="31">
+      <c r="K32" s="30">
         <f>SUMPRODUCT((C$7:$H$7=1)*(C32:H32="Y"))*50</f>
         <v/>
       </c>
@@ -5056,11 +5144,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$H$7,C33:H33,"Y"),"")</f>
         <v/>
       </c>
-      <c r="J33" s="30">
+      <c r="J33" s="29">
         <f>COUNTIF(C33:H33,"Y")</f>
         <v/>
       </c>
-      <c r="K33" s="31">
+      <c r="K33" s="30">
         <f>SUMPRODUCT((C$7:$H$7=1)*(C33:H33="Y"))*50</f>
         <v/>
       </c>
@@ -5079,9 +5167,17 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D34" s="35" t="n"/>
+      <c r="D34" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E34" s="35" t="n"/>
-      <c r="F34" s="35" t="n"/>
+      <c r="F34" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="G34" s="28" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5092,11 +5188,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$H$7,C34:H34,"Y"),"")</f>
         <v/>
       </c>
-      <c r="J34" s="30">
+      <c r="J34" s="29">
         <f>COUNTIF(C34:H34,"Y")</f>
         <v/>
       </c>
-      <c r="K34" s="31">
+      <c r="K34" s="30">
         <f>SUMPRODUCT((C$7:$H$7=1)*(C34:H34="Y"))*50</f>
         <v/>
       </c>
@@ -5120,11 +5216,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$H$7,C35:H35,"Y"),"")</f>
         <v/>
       </c>
-      <c r="J35" s="30">
+      <c r="J35" s="29">
         <f>COUNTIF(C35:H35,"Y")</f>
         <v/>
       </c>
-      <c r="K35" s="31">
+      <c r="K35" s="30">
         <f>SUMPRODUCT((C$7:$H$7=1)*(C35:H35="Y"))*50</f>
         <v/>
       </c>
@@ -5143,7 +5239,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D36" s="35" t="n"/>
+      <c r="D36" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E36" s="35" t="n"/>
       <c r="F36" s="28" t="inlineStr">
         <is>
@@ -5160,11 +5260,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$H$7,C36:H36,"Y"),"")</f>
         <v/>
       </c>
-      <c r="J36" s="30">
+      <c r="J36" s="29">
         <f>COUNTIF(C36:H36,"Y")</f>
         <v/>
       </c>
-      <c r="K36" s="31">
+      <c r="K36" s="30">
         <f>SUMPRODUCT((C$7:$H$7=1)*(C36:H36="Y"))*50</f>
         <v/>
       </c>
@@ -5192,11 +5292,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$H$7,C37:H37,"Y"),"")</f>
         <v/>
       </c>
-      <c r="J37" s="30">
+      <c r="J37" s="29">
         <f>COUNTIF(C37:H37,"Y")</f>
         <v/>
       </c>
-      <c r="K37" s="31">
+      <c r="K37" s="30">
         <f>SUMPRODUCT((C$7:$H$7=1)*(C37:H37="Y"))*50</f>
         <v/>
       </c>
@@ -5220,11 +5320,11 @@
         <f>IFERROR(AVERAGEIFS($C$7:$H$7,C38:H38,"Y"),"")</f>
         <v/>
       </c>
-      <c r="J38" s="30">
+      <c r="J38" s="29">
         <f>COUNTIF(C38:H38,"Y")</f>
         <v/>
       </c>
-      <c r="K38" s="31">
+      <c r="K38" s="30">
         <f>SUMPRODUCT((C$7:$H$7=1)*(C38:H38="Y"))*50</f>
         <v/>
       </c>

--- a/Shop_Tracker_2065_2026.xlsx
+++ b/Shop_Tracker_2065_2026.xlsx
@@ -4541,11 +4541,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D14" s="28" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D14" s="31" t="n"/>
       <c r="E14" s="31" t="n"/>
       <c r="F14" s="31" t="n"/>
       <c r="G14" s="31" t="n"/>
@@ -4608,22 +4604,14 @@
           <t>Kasey W.</t>
         </is>
       </c>
-      <c r="C16" s="28" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="C16" s="31" t="n"/>
       <c r="D16" s="28" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
       <c r="E16" s="31" t="n"/>
-      <c r="F16" s="28" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="F16" s="31" t="n"/>
       <c r="G16" s="28" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4652,22 +4640,14 @@
           <t>Nathan R.</t>
         </is>
       </c>
-      <c r="C17" s="28" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="C17" s="31" t="n"/>
       <c r="D17" s="31" t="n"/>
       <c r="E17" s="28" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F17" s="28" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="F17" s="31" t="n"/>
       <c r="G17" s="28" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4894,11 +4874,7 @@
           <t>Francisco</t>
         </is>
       </c>
-      <c r="C26" s="28" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="C26" s="35" t="n"/>
       <c r="D26" s="28" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5009,11 +4985,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="F29" s="28" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="F29" s="18" t="n"/>
       <c r="G29" s="18" t="n"/>
       <c r="H29" s="18" t="n"/>
       <c r="I29" s="17">
@@ -5167,17 +5139,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D34" s="28" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D34" s="35" t="n"/>
       <c r="E34" s="35" t="n"/>
-      <c r="F34" s="28" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="F34" s="35" t="n"/>
       <c r="G34" s="28" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5239,12 +5203,12 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D36" s="28" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E36" s="35" t="n"/>
+      <c r="D36" s="35" t="n"/>
+      <c r="E36" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F36" s="28" t="inlineStr">
         <is>
           <t>Y</t>

--- a/Shop_Tracker_2065_2026.xlsx
+++ b/Shop_Tracker_2065_2026.xlsx
@@ -2270,11 +2270,7 @@
           <t>Vicki L.</t>
         </is>
       </c>
-      <c r="C15" s="28" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="C15" s="31" t="n"/>
       <c r="D15" s="31" t="n"/>
       <c r="E15" s="28" t="inlineStr">
         <is>
@@ -2310,11 +2306,7 @@
           <t>Kasey W.</t>
         </is>
       </c>
-      <c r="C16" s="28" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="C16" s="31" t="n"/>
       <c r="D16" s="31" t="n"/>
       <c r="E16" s="31" t="n"/>
       <c r="F16" s="28" t="inlineStr">
@@ -2350,11 +2342,7 @@
           <t>Nathan R.</t>
         </is>
       </c>
-      <c r="C17" s="28" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="C17" s="31" t="n"/>
       <c r="D17" s="31" t="n"/>
       <c r="E17" s="31" t="n"/>
       <c r="F17" s="31" t="n"/>
@@ -2836,11 +2824,7 @@
           <t>Maylin</t>
         </is>
       </c>
-      <c r="C34" s="28" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="C34" s="35" t="n"/>
       <c r="D34" s="28" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2884,7 +2868,11 @@
           <t>Mike</t>
         </is>
       </c>
-      <c r="C35" s="18" t="n"/>
+      <c r="C35" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="D35" s="18" t="n"/>
       <c r="E35" s="28" t="inlineStr">
         <is>
@@ -2924,11 +2912,7 @@
           <t>Richard</t>
         </is>
       </c>
-      <c r="C36" s="28" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="C36" s="35" t="n"/>
       <c r="D36" s="35" t="n"/>
       <c r="E36" s="35" t="n"/>
       <c r="F36" s="35" t="n"/>

--- a/Shop_Tracker_2065_2026.xlsx
+++ b/Shop_Tracker_2065_2026.xlsx
@@ -105,33 +105,12 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="004A7A0F"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
       <color rgb="001A1A1A"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
       <color rgb="00595959"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="00C8102E"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="002E7D32"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="00D4A017"/>
       <sz val="8"/>
     </font>
     <font>
@@ -165,7 +144,28 @@
     </font>
     <font>
       <name val="Arial"/>
+      <b val="1"/>
       <color rgb="004A7A0F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="002E7D32"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00C8102E"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="004A7A0F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00D4A017"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -220,12 +220,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EFF8E8"/>
-        <bgColor rgb="00EFF8E8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00F9F9F9"/>
         <bgColor rgb="00F9F9F9"/>
       </patternFill>
@@ -252,6 +246,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFF8E8"/>
+        <bgColor rgb="00EFF8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -331,80 +331,80 @@
     <xf numFmtId="9" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="13" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="16" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="17" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="17" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="18" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="24" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="20" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="21" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="22" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="23" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="24" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -772,7 +772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:W40"/>
+  <dimension ref="A1:O40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -787,17 +787,9 @@
     <col width="7" customWidth="1" min="10" max="10"/>
     <col width="7" customWidth="1" min="11" max="11"/>
     <col width="7" customWidth="1" min="12" max="12"/>
-    <col width="7" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
     <col width="7" customWidth="1" min="14" max="14"/>
-    <col width="7" customWidth="1" min="15" max="15"/>
-    <col width="7" customWidth="1" min="16" max="16"/>
-    <col width="7" customWidth="1" min="17" max="17"/>
-    <col width="7" customWidth="1" min="18" max="18"/>
-    <col width="7" customWidth="1" min="19" max="19"/>
-    <col width="7" customWidth="1" min="20" max="20"/>
-    <col width="9" customWidth="1" min="21" max="21"/>
-    <col width="7" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -810,7 +802,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Five Guys Store 2065 · Louisville, KY · 18 shops · Source: Marketforce + CrunchTime</t>
+          <t>Five Guys Store 2065 · Louisville, KY · 10 shops · Source: Marketforce + CrunchTime</t>
         </is>
       </c>
     </row>
@@ -872,57 +864,17 @@
           <t>#10</t>
         </is>
       </c>
-      <c r="M4" s="5" t="inlineStr">
-        <is>
-          <t>#11</t>
-        </is>
-      </c>
-      <c r="N4" s="5" t="inlineStr">
-        <is>
-          <t>#12</t>
-        </is>
-      </c>
-      <c r="O4" s="5" t="inlineStr">
-        <is>
-          <t>#13</t>
-        </is>
-      </c>
-      <c r="P4" s="5" t="inlineStr">
-        <is>
-          <t>#14</t>
-        </is>
-      </c>
-      <c r="Q4" s="5" t="inlineStr">
-        <is>
-          <t>#15</t>
-        </is>
-      </c>
-      <c r="R4" s="5" t="inlineStr">
-        <is>
-          <t>#16</t>
-        </is>
-      </c>
-      <c r="S4" s="5" t="inlineStr">
-        <is>
-          <t>#17</t>
-        </is>
-      </c>
-      <c r="T4" s="5" t="inlineStr">
-        <is>
-          <t>#18</t>
-        </is>
-      </c>
-      <c r="U4" s="6" t="inlineStr">
+      <c r="M4" s="6" t="inlineStr">
         <is>
           <t>AVG</t>
         </is>
       </c>
-      <c r="V4" s="6" t="inlineStr">
+      <c r="N4" s="6" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="W4" s="6" t="inlineStr">
+      <c r="O4" s="6" t="inlineStr">
         <is>
           <t>BONUS</t>
         </is>
@@ -985,49 +937,9 @@
           <t>01/31</t>
         </is>
       </c>
-      <c r="M5" s="9" t="inlineStr">
-        <is>
-          <t>01/05</t>
-        </is>
-      </c>
-      <c r="N5" s="9" t="inlineStr">
-        <is>
-          <t>01/09</t>
-        </is>
-      </c>
-      <c r="O5" s="9" t="inlineStr">
-        <is>
-          <t>01/10</t>
-        </is>
-      </c>
-      <c r="P5" s="9" t="inlineStr">
-        <is>
-          <t>01/16</t>
-        </is>
-      </c>
-      <c r="Q5" s="9" t="inlineStr">
-        <is>
-          <t>01/23</t>
-        </is>
-      </c>
-      <c r="R5" s="9" t="inlineStr">
-        <is>
-          <t>01/28</t>
-        </is>
-      </c>
-      <c r="S5" s="9" t="inlineStr">
-        <is>
-          <t>01/29</t>
-        </is>
-      </c>
-      <c r="T5" s="9" t="inlineStr">
-        <is>
-          <t>01/31</t>
-        </is>
-      </c>
-      <c r="U5" s="7" t="inlineStr"/>
-      <c r="V5" s="7" t="inlineStr"/>
-      <c r="W5" s="7" t="inlineStr"/>
+      <c r="M5" s="7" t="inlineStr"/>
+      <c r="N5" s="7" t="inlineStr"/>
+      <c r="O5" s="7" t="inlineStr"/>
     </row>
     <row r="6" ht="14" customHeight="1">
       <c r="A6" s="7" t="inlineStr"/>
@@ -1086,49 +998,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="M6" s="11" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="N6" s="10" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="O6" s="11" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="P6" s="10" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="Q6" s="11" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="R6" s="10" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="T6" s="11" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="U6" s="7" t="inlineStr"/>
-      <c r="V6" s="7" t="inlineStr"/>
-      <c r="W6" s="7" t="inlineStr"/>
+      <c r="M6" s="7" t="inlineStr"/>
+      <c r="N6" s="7" t="inlineStr"/>
+      <c r="O6" s="7" t="inlineStr"/>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="12" t="inlineStr"/>
@@ -1167,1256 +1039,868 @@
       <c r="L7" s="16" t="n">
         <v>0.48</v>
       </c>
-      <c r="M7" s="17" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="N7" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="15" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="P7" s="16" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="Q7" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" s="15" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="T7" s="15" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="U7" s="18">
-        <f>IFERROR(AVERAGE(C7:T7),"")</f>
-        <v/>
-      </c>
-      <c r="V7" s="12" t="inlineStr"/>
-      <c r="W7" s="12" t="inlineStr"/>
+      <c r="M7" s="17">
+        <f>IFERROR(AVERAGE(C7:L7),"")</f>
+        <v/>
+      </c>
+      <c r="N7" s="12" t="inlineStr"/>
+      <c r="O7" s="12" t="inlineStr"/>
     </row>
     <row r="8" ht="13" customHeight="1">
-      <c r="A8" s="19" t="inlineStr"/>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr"/>
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr"/>
-      <c r="D8" s="19" t="inlineStr"/>
-      <c r="E8" s="19" t="inlineStr"/>
-      <c r="F8" s="19" t="inlineStr"/>
-      <c r="G8" s="19" t="inlineStr"/>
-      <c r="H8" s="19" t="inlineStr"/>
-      <c r="I8" s="19" t="inlineStr"/>
-      <c r="J8" s="19" t="inlineStr"/>
-      <c r="K8" s="19" t="inlineStr"/>
-      <c r="L8" s="19" t="inlineStr"/>
-      <c r="M8" s="19" t="inlineStr"/>
-      <c r="N8" s="19" t="inlineStr"/>
-      <c r="O8" s="19" t="inlineStr"/>
-      <c r="P8" s="21" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="Q8" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="T8" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="U8" s="23">
-        <f>IFERROR(AVERAGE(C8:T8),"")</f>
-        <v/>
-      </c>
-      <c r="V8" s="19" t="inlineStr"/>
-      <c r="W8" s="19" t="inlineStr"/>
+      <c r="C8" s="18" t="inlineStr"/>
+      <c r="D8" s="18" t="inlineStr"/>
+      <c r="E8" s="18" t="inlineStr"/>
+      <c r="F8" s="18" t="inlineStr"/>
+      <c r="G8" s="18" t="inlineStr"/>
+      <c r="H8" s="18" t="inlineStr"/>
+      <c r="I8" s="18" t="inlineStr"/>
+      <c r="J8" s="18" t="inlineStr"/>
+      <c r="K8" s="18" t="inlineStr"/>
+      <c r="L8" s="18" t="inlineStr"/>
+      <c r="M8" s="20">
+        <f>IFERROR(AVERAGE(C8:L8),"")</f>
+        <v/>
+      </c>
+      <c r="N8" s="18" t="inlineStr"/>
+      <c r="O8" s="18" t="inlineStr"/>
     </row>
     <row r="9" ht="13" customHeight="1">
-      <c r="A9" s="19" t="inlineStr"/>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="A9" s="18" t="inlineStr"/>
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>Quality</t>
         </is>
       </c>
-      <c r="C9" s="19" t="inlineStr"/>
-      <c r="D9" s="19" t="inlineStr"/>
-      <c r="E9" s="19" t="inlineStr"/>
-      <c r="F9" s="19" t="inlineStr"/>
-      <c r="G9" s="19" t="inlineStr"/>
-      <c r="H9" s="19" t="inlineStr"/>
-      <c r="I9" s="19" t="inlineStr"/>
-      <c r="J9" s="19" t="inlineStr"/>
-      <c r="K9" s="19" t="inlineStr"/>
-      <c r="L9" s="19" t="inlineStr"/>
-      <c r="M9" s="19" t="inlineStr"/>
-      <c r="N9" s="19" t="inlineStr"/>
-      <c r="O9" s="19" t="inlineStr"/>
-      <c r="P9" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="T9" s="24" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="U9" s="23">
-        <f>IFERROR(AVERAGE(C9:T9),"")</f>
-        <v/>
-      </c>
-      <c r="V9" s="19" t="inlineStr"/>
-      <c r="W9" s="19" t="inlineStr"/>
+      <c r="C9" s="18" t="inlineStr"/>
+      <c r="D9" s="18" t="inlineStr"/>
+      <c r="E9" s="18" t="inlineStr"/>
+      <c r="F9" s="18" t="inlineStr"/>
+      <c r="G9" s="18" t="inlineStr"/>
+      <c r="H9" s="18" t="inlineStr"/>
+      <c r="I9" s="18" t="inlineStr"/>
+      <c r="J9" s="18" t="inlineStr"/>
+      <c r="K9" s="18" t="inlineStr"/>
+      <c r="L9" s="18" t="inlineStr"/>
+      <c r="M9" s="20">
+        <f>IFERROR(AVERAGE(C9:L9),"")</f>
+        <v/>
+      </c>
+      <c r="N9" s="18" t="inlineStr"/>
+      <c r="O9" s="18" t="inlineStr"/>
     </row>
     <row r="10" ht="13" customHeight="1">
-      <c r="A10" s="19" t="inlineStr"/>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="A10" s="18" t="inlineStr"/>
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>Cleanliness</t>
         </is>
       </c>
-      <c r="C10" s="19" t="inlineStr"/>
-      <c r="D10" s="19" t="inlineStr"/>
-      <c r="E10" s="19" t="inlineStr"/>
-      <c r="F10" s="19" t="inlineStr"/>
-      <c r="G10" s="19" t="inlineStr"/>
-      <c r="H10" s="19" t="inlineStr"/>
-      <c r="I10" s="19" t="inlineStr"/>
-      <c r="J10" s="19" t="inlineStr"/>
-      <c r="K10" s="19" t="inlineStr"/>
-      <c r="L10" s="19" t="inlineStr"/>
-      <c r="M10" s="19" t="inlineStr"/>
-      <c r="N10" s="19" t="inlineStr"/>
-      <c r="O10" s="19" t="inlineStr"/>
-      <c r="P10" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" s="24" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="T10" s="24" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="U10" s="23">
-        <f>IFERROR(AVERAGE(C10:T10),"")</f>
-        <v/>
-      </c>
-      <c r="V10" s="19" t="inlineStr"/>
-      <c r="W10" s="19" t="inlineStr"/>
+      <c r="C10" s="18" t="inlineStr"/>
+      <c r="D10" s="18" t="inlineStr"/>
+      <c r="E10" s="18" t="inlineStr"/>
+      <c r="F10" s="18" t="inlineStr"/>
+      <c r="G10" s="18" t="inlineStr"/>
+      <c r="H10" s="18" t="inlineStr"/>
+      <c r="I10" s="18" t="inlineStr"/>
+      <c r="J10" s="18" t="inlineStr"/>
+      <c r="K10" s="18" t="inlineStr"/>
+      <c r="L10" s="18" t="inlineStr"/>
+      <c r="M10" s="20">
+        <f>IFERROR(AVERAGE(C10:L10),"")</f>
+        <v/>
+      </c>
+      <c r="N10" s="18" t="inlineStr"/>
+      <c r="O10" s="18" t="inlineStr"/>
     </row>
     <row r="11" ht="13" customHeight="1">
-      <c r="A11" s="19" t="inlineStr"/>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr"/>
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>Customer Sat</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr"/>
-      <c r="D11" s="19" t="inlineStr"/>
-      <c r="E11" s="19" t="inlineStr"/>
-      <c r="F11" s="19" t="inlineStr"/>
-      <c r="G11" s="19" t="inlineStr"/>
-      <c r="H11" s="19" t="inlineStr"/>
-      <c r="I11" s="19" t="inlineStr"/>
-      <c r="J11" s="19" t="inlineStr"/>
-      <c r="K11" s="19" t="inlineStr"/>
-      <c r="L11" s="19" t="inlineStr"/>
-      <c r="M11" s="19" t="inlineStr"/>
-      <c r="N11" s="19" t="inlineStr"/>
-      <c r="O11" s="19" t="inlineStr"/>
-      <c r="P11" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q11" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="T11" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" s="23">
-        <f>IFERROR(AVERAGE(C11:T11),"")</f>
-        <v/>
-      </c>
-      <c r="V11" s="19" t="inlineStr"/>
-      <c r="W11" s="19" t="inlineStr"/>
+      <c r="C11" s="18" t="inlineStr"/>
+      <c r="D11" s="18" t="inlineStr"/>
+      <c r="E11" s="18" t="inlineStr"/>
+      <c r="F11" s="18" t="inlineStr"/>
+      <c r="G11" s="18" t="inlineStr"/>
+      <c r="H11" s="18" t="inlineStr"/>
+      <c r="I11" s="18" t="inlineStr"/>
+      <c r="J11" s="18" t="inlineStr"/>
+      <c r="K11" s="18" t="inlineStr"/>
+      <c r="L11" s="18" t="inlineStr"/>
+      <c r="M11" s="20">
+        <f>IFERROR(AVERAGE(C11:L11),"")</f>
+        <v/>
+      </c>
+      <c r="N11" s="18" t="inlineStr"/>
+      <c r="O11" s="18" t="inlineStr"/>
     </row>
     <row r="12" ht="6" customHeight="1">
-      <c r="A12" s="25" t="n"/>
+      <c r="A12" s="21" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="26" t="inlineStr">
+      <c r="A13" s="22" t="inlineStr">
         <is>
           <t>MANAGERS</t>
         </is>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="B14" s="28" t="inlineStr">
+      <c r="A14" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
         <is>
           <t>Madison C.</t>
         </is>
       </c>
-      <c r="C14" s="29" t="n"/>
-      <c r="D14" s="29" t="n"/>
-      <c r="E14" s="29" t="n"/>
-      <c r="F14" s="29" t="n"/>
-      <c r="G14" s="29" t="n"/>
-      <c r="H14" s="29" t="n"/>
-      <c r="I14" s="29" t="n"/>
-      <c r="J14" s="29" t="n"/>
-      <c r="K14" s="29" t="n"/>
-      <c r="L14" s="29" t="n"/>
-      <c r="M14" s="29" t="n"/>
-      <c r="N14" s="29" t="n"/>
-      <c r="O14" s="29" t="n"/>
-      <c r="P14" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="Q14" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="R14" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="S14" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="T14" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="U14" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$T$7,C14:T14,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="V14" s="31">
-        <f>COUNTIF(C14:T14,"Y")</f>
-        <v/>
-      </c>
-      <c r="W14" s="32">
-        <f>SUMPRODUCT((C$7:$T$7=1)*(C14:T14="Y"))*50</f>
+      <c r="C14" s="25" t="n"/>
+      <c r="D14" s="25" t="n"/>
+      <c r="E14" s="25" t="n"/>
+      <c r="F14" s="25" t="n"/>
+      <c r="G14" s="25" t="n"/>
+      <c r="H14" s="25" t="n"/>
+      <c r="I14" s="25" t="n"/>
+      <c r="J14" s="25" t="n"/>
+      <c r="K14" s="25" t="n"/>
+      <c r="L14" s="25" t="n"/>
+      <c r="M14" s="17">
+        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C14:L14,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="N14" s="26">
+        <f>COUNTIF(C14:L14,"Y")</f>
+        <v/>
+      </c>
+      <c r="O14" s="27">
+        <f>SUMPRODUCT((C$7:$L$7=1)*(C14:L14="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="27" t="n">
+      <c r="A15" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="B15" s="28" t="inlineStr">
+      <c r="B15" s="24" t="inlineStr">
         <is>
           <t>Vicki L.</t>
         </is>
       </c>
-      <c r="C15" s="29" t="n"/>
-      <c r="D15" s="29" t="n"/>
-      <c r="E15" s="29" t="n"/>
-      <c r="F15" s="29" t="n"/>
-      <c r="G15" s="29" t="n"/>
-      <c r="H15" s="29" t="n"/>
-      <c r="I15" s="29" t="n"/>
-      <c r="J15" s="29" t="n"/>
-      <c r="K15" s="29" t="n"/>
-      <c r="L15" s="29" t="n"/>
-      <c r="M15" s="29" t="n"/>
-      <c r="N15" s="29" t="n"/>
-      <c r="O15" s="29" t="n"/>
-      <c r="P15" s="29" t="n"/>
-      <c r="Q15" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="R15" s="29" t="n"/>
-      <c r="S15" s="29" t="n"/>
-      <c r="T15" s="29" t="n"/>
-      <c r="U15" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$T$7,C15:T15,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="V15" s="31">
-        <f>COUNTIF(C15:T15,"Y")</f>
-        <v/>
-      </c>
-      <c r="W15" s="32">
-        <f>SUMPRODUCT((C$7:$T$7=1)*(C15:T15="Y"))*50</f>
+      <c r="C15" s="25" t="n"/>
+      <c r="D15" s="25" t="n"/>
+      <c r="E15" s="25" t="n"/>
+      <c r="F15" s="25" t="n"/>
+      <c r="G15" s="25" t="n"/>
+      <c r="H15" s="25" t="n"/>
+      <c r="I15" s="25" t="n"/>
+      <c r="J15" s="25" t="n"/>
+      <c r="K15" s="25" t="n"/>
+      <c r="L15" s="25" t="n"/>
+      <c r="M15" s="17">
+        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C15:L15,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="N15" s="26">
+        <f>COUNTIF(C15:L15,"Y")</f>
+        <v/>
+      </c>
+      <c r="O15" s="27">
+        <f>SUMPRODUCT((C$7:$L$7=1)*(C15:L15="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
-      <c r="A16" s="27" t="n">
+      <c r="A16" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="B16" s="28" t="inlineStr">
+      <c r="B16" s="24" t="inlineStr">
         <is>
           <t>Kasey W.</t>
         </is>
       </c>
-      <c r="C16" s="29" t="n"/>
-      <c r="D16" s="29" t="n"/>
-      <c r="E16" s="29" t="n"/>
-      <c r="F16" s="29" t="n"/>
-      <c r="G16" s="29" t="n"/>
-      <c r="H16" s="29" t="n"/>
-      <c r="I16" s="29" t="n"/>
-      <c r="J16" s="29" t="n"/>
-      <c r="K16" s="29" t="n"/>
-      <c r="L16" s="29" t="n"/>
-      <c r="M16" s="29" t="n"/>
-      <c r="N16" s="29" t="n"/>
-      <c r="O16" s="29" t="n"/>
-      <c r="P16" s="29" t="n"/>
-      <c r="Q16" s="29" t="n"/>
-      <c r="R16" s="29" t="n"/>
-      <c r="S16" s="29" t="n"/>
-      <c r="T16" s="29" t="n"/>
-      <c r="U16" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$T$7,C16:T16,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="V16" s="31">
-        <f>COUNTIF(C16:T16,"Y")</f>
-        <v/>
-      </c>
-      <c r="W16" s="32">
-        <f>SUMPRODUCT((C$7:$T$7=1)*(C16:T16="Y"))*50</f>
+      <c r="C16" s="25" t="n"/>
+      <c r="D16" s="25" t="n"/>
+      <c r="E16" s="25" t="n"/>
+      <c r="F16" s="25" t="n"/>
+      <c r="G16" s="25" t="n"/>
+      <c r="H16" s="25" t="n"/>
+      <c r="I16" s="25" t="n"/>
+      <c r="J16" s="25" t="n"/>
+      <c r="K16" s="25" t="n"/>
+      <c r="L16" s="25" t="n"/>
+      <c r="M16" s="17">
+        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C16:L16,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="N16" s="26">
+        <f>COUNTIF(C16:L16,"Y")</f>
+        <v/>
+      </c>
+      <c r="O16" s="27">
+        <f>SUMPRODUCT((C$7:$L$7=1)*(C16:L16="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
-      <c r="A17" s="27" t="n">
+      <c r="A17" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="B17" s="28" t="inlineStr">
+      <c r="B17" s="24" t="inlineStr">
         <is>
           <t>Nathan R.</t>
         </is>
       </c>
-      <c r="C17" s="29" t="n"/>
-      <c r="D17" s="29" t="n"/>
-      <c r="E17" s="29" t="n"/>
-      <c r="F17" s="29" t="n"/>
-      <c r="G17" s="29" t="n"/>
-      <c r="H17" s="29" t="n"/>
-      <c r="I17" s="29" t="n"/>
-      <c r="J17" s="29" t="n"/>
-      <c r="K17" s="29" t="n"/>
-      <c r="L17" s="29" t="n"/>
-      <c r="M17" s="29" t="n"/>
-      <c r="N17" s="29" t="n"/>
-      <c r="O17" s="29" t="n"/>
-      <c r="P17" s="29" t="n"/>
-      <c r="Q17" s="29" t="n"/>
-      <c r="R17" s="29" t="n"/>
-      <c r="S17" s="29" t="n"/>
-      <c r="T17" s="29" t="n"/>
-      <c r="U17" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$T$7,C17:T17,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="V17" s="31">
-        <f>COUNTIF(C17:T17,"Y")</f>
-        <v/>
-      </c>
-      <c r="W17" s="32">
-        <f>SUMPRODUCT((C$7:$T$7=1)*(C17:T17="Y"))*50</f>
+      <c r="C17" s="25" t="n"/>
+      <c r="D17" s="25" t="n"/>
+      <c r="E17" s="25" t="n"/>
+      <c r="F17" s="25" t="n"/>
+      <c r="G17" s="25" t="n"/>
+      <c r="H17" s="25" t="n"/>
+      <c r="I17" s="25" t="n"/>
+      <c r="J17" s="25" t="n"/>
+      <c r="K17" s="25" t="n"/>
+      <c r="L17" s="25" t="n"/>
+      <c r="M17" s="17">
+        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C17:L17,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="N17" s="26">
+        <f>COUNTIF(C17:L17,"Y")</f>
+        <v/>
+      </c>
+      <c r="O17" s="27">
+        <f>SUMPRODUCT((C$7:$L$7=1)*(C17:L17="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="6" customHeight="1">
-      <c r="A18" s="25" t="n"/>
+      <c r="A18" s="21" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="33" t="inlineStr">
+      <c r="A19" s="28" t="inlineStr">
         <is>
           <t>CREW</t>
         </is>
       </c>
     </row>
     <row r="20" ht="17" customHeight="1">
-      <c r="A20" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="B20" s="35" t="inlineStr">
+      <c r="A20" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
         <is>
           <t>Alen</t>
         </is>
       </c>
-      <c r="C20" s="36" t="n"/>
-      <c r="D20" s="36" t="n"/>
-      <c r="E20" s="36" t="n"/>
-      <c r="F20" s="36" t="n"/>
-      <c r="G20" s="36" t="n"/>
-      <c r="H20" s="36" t="n"/>
-      <c r="I20" s="36" t="n"/>
-      <c r="J20" s="36" t="n"/>
-      <c r="K20" s="36" t="n"/>
-      <c r="L20" s="36" t="n"/>
-      <c r="M20" s="36" t="n"/>
-      <c r="N20" s="36" t="n"/>
-      <c r="O20" s="36" t="n"/>
-      <c r="P20" s="36" t="n"/>
-      <c r="Q20" s="36" t="n"/>
-      <c r="R20" s="36" t="n"/>
-      <c r="S20" s="36" t="n"/>
-      <c r="T20" s="36" t="n"/>
-      <c r="U20" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$T$7,C20:T20,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="V20" s="31">
-        <f>COUNTIF(C20:T20,"Y")</f>
-        <v/>
-      </c>
-      <c r="W20" s="32">
-        <f>SUMPRODUCT((C$7:$T$7=1)*(C20:T20="Y"))*50</f>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+      <c r="E20" s="31" t="n"/>
+      <c r="F20" s="31" t="n"/>
+      <c r="G20" s="31" t="n"/>
+      <c r="H20" s="31" t="n"/>
+      <c r="I20" s="31" t="n"/>
+      <c r="J20" s="31" t="n"/>
+      <c r="K20" s="31" t="n"/>
+      <c r="L20" s="31" t="n"/>
+      <c r="M20" s="17">
+        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C20:L20,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="N20" s="26">
+        <f>COUNTIF(C20:L20,"Y")</f>
+        <v/>
+      </c>
+      <c r="O20" s="27">
+        <f>SUMPRODUCT((C$7:$L$7=1)*(C20:L20="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="17" customHeight="1">
-      <c r="A21" s="37" t="n">
+      <c r="A21" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="B21" s="38" t="inlineStr">
+      <c r="B21" s="33" t="inlineStr">
         <is>
           <t>Ash</t>
         </is>
       </c>
-      <c r="C21" s="19" t="n"/>
-      <c r="D21" s="19" t="n"/>
-      <c r="E21" s="19" t="n"/>
-      <c r="F21" s="19" t="n"/>
-      <c r="G21" s="19" t="n"/>
-      <c r="H21" s="19" t="n"/>
-      <c r="I21" s="19" t="n"/>
-      <c r="J21" s="19" t="n"/>
-      <c r="K21" s="19" t="n"/>
-      <c r="L21" s="19" t="n"/>
-      <c r="M21" s="19" t="n"/>
-      <c r="N21" s="19" t="n"/>
-      <c r="O21" s="19" t="n"/>
-      <c r="P21" s="19" t="n"/>
-      <c r="Q21" s="19" t="n"/>
-      <c r="R21" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="S21" s="19" t="n"/>
-      <c r="T21" s="19" t="n"/>
-      <c r="U21" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$T$7,C21:T21,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="V21" s="31">
-        <f>COUNTIF(C21:T21,"Y")</f>
-        <v/>
-      </c>
-      <c r="W21" s="32">
-        <f>SUMPRODUCT((C$7:$T$7=1)*(C21:T21="Y"))*50</f>
+      <c r="C21" s="18" t="n"/>
+      <c r="D21" s="18" t="n"/>
+      <c r="E21" s="18" t="n"/>
+      <c r="F21" s="18" t="n"/>
+      <c r="G21" s="18" t="n"/>
+      <c r="H21" s="18" t="n"/>
+      <c r="I21" s="18" t="n"/>
+      <c r="J21" s="18" t="n"/>
+      <c r="K21" s="18" t="n"/>
+      <c r="L21" s="18" t="n"/>
+      <c r="M21" s="17">
+        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C21:L21,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="N21" s="26">
+        <f>COUNTIF(C21:L21,"Y")</f>
+        <v/>
+      </c>
+      <c r="O21" s="27">
+        <f>SUMPRODUCT((C$7:$L$7=1)*(C21:L21="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="17" customHeight="1">
-      <c r="A22" s="34" t="n">
+      <c r="A22" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B22" s="35" t="inlineStr">
+      <c r="B22" s="30" t="inlineStr">
         <is>
           <t>Autumn</t>
         </is>
       </c>
-      <c r="C22" s="36" t="n"/>
-      <c r="D22" s="36" t="n"/>
-      <c r="E22" s="36" t="n"/>
-      <c r="F22" s="36" t="n"/>
-      <c r="G22" s="36" t="n"/>
-      <c r="H22" s="36" t="n"/>
-      <c r="I22" s="36" t="n"/>
-      <c r="J22" s="36" t="n"/>
-      <c r="K22" s="36" t="n"/>
-      <c r="L22" s="36" t="n"/>
-      <c r="M22" s="36" t="n"/>
-      <c r="N22" s="36" t="n"/>
-      <c r="O22" s="36" t="n"/>
-      <c r="P22" s="36" t="n"/>
-      <c r="Q22" s="36" t="n"/>
-      <c r="R22" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="S22" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="T22" s="36" t="n"/>
-      <c r="U22" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$T$7,C22:T22,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="V22" s="31">
-        <f>COUNTIF(C22:T22,"Y")</f>
-        <v/>
-      </c>
-      <c r="W22" s="32">
-        <f>SUMPRODUCT((C$7:$T$7=1)*(C22:T22="Y"))*50</f>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+      <c r="E22" s="31" t="n"/>
+      <c r="F22" s="31" t="n"/>
+      <c r="G22" s="31" t="n"/>
+      <c r="H22" s="31" t="n"/>
+      <c r="I22" s="31" t="n"/>
+      <c r="J22" s="31" t="n"/>
+      <c r="K22" s="31" t="n"/>
+      <c r="L22" s="31" t="n"/>
+      <c r="M22" s="17">
+        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C22:L22,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="N22" s="26">
+        <f>COUNTIF(C22:L22,"Y")</f>
+        <v/>
+      </c>
+      <c r="O22" s="27">
+        <f>SUMPRODUCT((C$7:$L$7=1)*(C22:L22="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="17" customHeight="1">
-      <c r="A23" s="37" t="n">
+      <c r="A23" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="B23" s="38" t="inlineStr">
+      <c r="B23" s="33" t="inlineStr">
         <is>
           <t>Bri</t>
         </is>
       </c>
-      <c r="C23" s="19" t="n"/>
-      <c r="D23" s="19" t="n"/>
-      <c r="E23" s="19" t="n"/>
-      <c r="F23" s="19" t="n"/>
-      <c r="G23" s="19" t="n"/>
-      <c r="H23" s="19" t="n"/>
-      <c r="I23" s="19" t="n"/>
-      <c r="J23" s="19" t="n"/>
-      <c r="K23" s="19" t="n"/>
-      <c r="L23" s="19" t="n"/>
-      <c r="M23" s="19" t="n"/>
-      <c r="N23" s="19" t="n"/>
-      <c r="O23" s="19" t="n"/>
-      <c r="P23" s="19" t="n"/>
-      <c r="Q23" s="19" t="n"/>
-      <c r="R23" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="S23" s="19" t="n"/>
-      <c r="T23" s="19" t="n"/>
-      <c r="U23" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$T$7,C23:T23,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="V23" s="31">
-        <f>COUNTIF(C23:T23,"Y")</f>
-        <v/>
-      </c>
-      <c r="W23" s="32">
-        <f>SUMPRODUCT((C$7:$T$7=1)*(C23:T23="Y"))*50</f>
+      <c r="C23" s="18" t="n"/>
+      <c r="D23" s="18" t="n"/>
+      <c r="E23" s="18" t="n"/>
+      <c r="F23" s="18" t="n"/>
+      <c r="G23" s="18" t="n"/>
+      <c r="H23" s="18" t="n"/>
+      <c r="I23" s="18" t="n"/>
+      <c r="J23" s="18" t="n"/>
+      <c r="K23" s="18" t="n"/>
+      <c r="L23" s="18" t="n"/>
+      <c r="M23" s="17">
+        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C23:L23,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="N23" s="26">
+        <f>COUNTIF(C23:L23,"Y")</f>
+        <v/>
+      </c>
+      <c r="O23" s="27">
+        <f>SUMPRODUCT((C$7:$L$7=1)*(C23:L23="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="17" customHeight="1">
-      <c r="A24" s="34" t="n">
+      <c r="A24" s="29" t="n">
         <v>5</v>
       </c>
-      <c r="B24" s="35" t="inlineStr">
+      <c r="B24" s="30" t="inlineStr">
         <is>
           <t>Dakayla</t>
         </is>
       </c>
-      <c r="C24" s="36" t="n"/>
-      <c r="D24" s="36" t="n"/>
-      <c r="E24" s="36" t="n"/>
-      <c r="F24" s="36" t="n"/>
-      <c r="G24" s="36" t="n"/>
-      <c r="H24" s="36" t="n"/>
-      <c r="I24" s="36" t="n"/>
-      <c r="J24" s="36" t="n"/>
-      <c r="K24" s="36" t="n"/>
-      <c r="L24" s="36" t="n"/>
-      <c r="M24" s="36" t="n"/>
-      <c r="N24" s="36" t="n"/>
-      <c r="O24" s="36" t="n"/>
-      <c r="P24" s="36" t="n"/>
-      <c r="Q24" s="36" t="n"/>
-      <c r="R24" s="36" t="n"/>
-      <c r="S24" s="36" t="n"/>
-      <c r="T24" s="36" t="n"/>
-      <c r="U24" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$T$7,C24:T24,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="V24" s="31">
-        <f>COUNTIF(C24:T24,"Y")</f>
-        <v/>
-      </c>
-      <c r="W24" s="32">
-        <f>SUMPRODUCT((C$7:$T$7=1)*(C24:T24="Y"))*50</f>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+      <c r="E24" s="31" t="n"/>
+      <c r="F24" s="31" t="n"/>
+      <c r="G24" s="31" t="n"/>
+      <c r="H24" s="31" t="n"/>
+      <c r="I24" s="31" t="n"/>
+      <c r="J24" s="31" t="n"/>
+      <c r="K24" s="31" t="n"/>
+      <c r="L24" s="31" t="n"/>
+      <c r="M24" s="17">
+        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C24:L24,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="N24" s="26">
+        <f>COUNTIF(C24:L24,"Y")</f>
+        <v/>
+      </c>
+      <c r="O24" s="27">
+        <f>SUMPRODUCT((C$7:$L$7=1)*(C24:L24="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="17" customHeight="1">
-      <c r="A25" s="37" t="n">
+      <c r="A25" s="32" t="n">
         <v>6</v>
       </c>
-      <c r="B25" s="38" t="inlineStr">
+      <c r="B25" s="33" t="inlineStr">
         <is>
           <t>Divan</t>
         </is>
       </c>
-      <c r="C25" s="19" t="n"/>
-      <c r="D25" s="19" t="n"/>
-      <c r="E25" s="19" t="n"/>
-      <c r="F25" s="19" t="n"/>
-      <c r="G25" s="19" t="n"/>
-      <c r="H25" s="19" t="n"/>
-      <c r="I25" s="19" t="n"/>
-      <c r="J25" s="19" t="n"/>
-      <c r="K25" s="19" t="n"/>
-      <c r="L25" s="19" t="n"/>
-      <c r="M25" s="19" t="n"/>
-      <c r="N25" s="19" t="n"/>
-      <c r="O25" s="19" t="n"/>
-      <c r="P25" s="19" t="n"/>
-      <c r="Q25" s="19" t="n"/>
-      <c r="R25" s="19" t="n"/>
-      <c r="S25" s="19" t="n"/>
-      <c r="T25" s="19" t="n"/>
-      <c r="U25" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$T$7,C25:T25,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="V25" s="31">
-        <f>COUNTIF(C25:T25,"Y")</f>
-        <v/>
-      </c>
-      <c r="W25" s="32">
-        <f>SUMPRODUCT((C$7:$T$7=1)*(C25:T25="Y"))*50</f>
+      <c r="C25" s="18" t="n"/>
+      <c r="D25" s="18" t="n"/>
+      <c r="E25" s="18" t="n"/>
+      <c r="F25" s="18" t="n"/>
+      <c r="G25" s="18" t="n"/>
+      <c r="H25" s="18" t="n"/>
+      <c r="I25" s="18" t="n"/>
+      <c r="J25" s="18" t="n"/>
+      <c r="K25" s="18" t="n"/>
+      <c r="L25" s="18" t="n"/>
+      <c r="M25" s="17">
+        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C25:L25,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="N25" s="26">
+        <f>COUNTIF(C25:L25,"Y")</f>
+        <v/>
+      </c>
+      <c r="O25" s="27">
+        <f>SUMPRODUCT((C$7:$L$7=1)*(C25:L25="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="17" customHeight="1">
-      <c r="A26" s="34" t="n">
+      <c r="A26" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="B26" s="35" t="inlineStr">
+      <c r="B26" s="30" t="inlineStr">
         <is>
           <t>Francisco</t>
         </is>
       </c>
-      <c r="C26" s="36" t="n"/>
-      <c r="D26" s="36" t="n"/>
-      <c r="E26" s="36" t="n"/>
-      <c r="F26" s="36" t="n"/>
-      <c r="G26" s="36" t="n"/>
-      <c r="H26" s="36" t="n"/>
-      <c r="I26" s="36" t="n"/>
-      <c r="J26" s="36" t="n"/>
-      <c r="K26" s="36" t="n"/>
-      <c r="L26" s="36" t="n"/>
-      <c r="M26" s="36" t="n"/>
-      <c r="N26" s="36" t="n"/>
-      <c r="O26" s="36" t="n"/>
-      <c r="P26" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="Q26" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="R26" s="36" t="n"/>
-      <c r="S26" s="36" t="n"/>
-      <c r="T26" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="U26" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$T$7,C26:T26,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="V26" s="31">
-        <f>COUNTIF(C26:T26,"Y")</f>
-        <v/>
-      </c>
-      <c r="W26" s="32">
-        <f>SUMPRODUCT((C$7:$T$7=1)*(C26:T26="Y"))*50</f>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+      <c r="E26" s="31" t="n"/>
+      <c r="F26" s="31" t="n"/>
+      <c r="G26" s="31" t="n"/>
+      <c r="H26" s="31" t="n"/>
+      <c r="I26" s="31" t="n"/>
+      <c r="J26" s="31" t="n"/>
+      <c r="K26" s="31" t="n"/>
+      <c r="L26" s="31" t="n"/>
+      <c r="M26" s="17">
+        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C26:L26,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="N26" s="26">
+        <f>COUNTIF(C26:L26,"Y")</f>
+        <v/>
+      </c>
+      <c r="O26" s="27">
+        <f>SUMPRODUCT((C$7:$L$7=1)*(C26:L26="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="17" customHeight="1">
-      <c r="A27" s="37" t="n">
+      <c r="A27" s="32" t="n">
         <v>8</v>
       </c>
-      <c r="B27" s="38" t="inlineStr">
+      <c r="B27" s="33" t="inlineStr">
         <is>
           <t>Grace</t>
         </is>
       </c>
-      <c r="C27" s="19" t="n"/>
-      <c r="D27" s="19" t="n"/>
-      <c r="E27" s="19" t="n"/>
-      <c r="F27" s="19" t="n"/>
-      <c r="G27" s="19" t="n"/>
-      <c r="H27" s="19" t="n"/>
-      <c r="I27" s="19" t="n"/>
-      <c r="J27" s="19" t="n"/>
-      <c r="K27" s="19" t="n"/>
-      <c r="L27" s="19" t="n"/>
-      <c r="M27" s="19" t="n"/>
-      <c r="N27" s="19" t="n"/>
-      <c r="O27" s="19" t="n"/>
-      <c r="P27" s="19" t="n"/>
-      <c r="Q27" s="19" t="n"/>
-      <c r="R27" s="19" t="n"/>
-      <c r="S27" s="19" t="n"/>
-      <c r="T27" s="19" t="n"/>
-      <c r="U27" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$T$7,C27:T27,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="V27" s="31">
-        <f>COUNTIF(C27:T27,"Y")</f>
-        <v/>
-      </c>
-      <c r="W27" s="32">
-        <f>SUMPRODUCT((C$7:$T$7=1)*(C27:T27="Y"))*50</f>
+      <c r="C27" s="18" t="n"/>
+      <c r="D27" s="18" t="n"/>
+      <c r="E27" s="18" t="n"/>
+      <c r="F27" s="18" t="n"/>
+      <c r="G27" s="18" t="n"/>
+      <c r="H27" s="18" t="n"/>
+      <c r="I27" s="18" t="n"/>
+      <c r="J27" s="18" t="n"/>
+      <c r="K27" s="18" t="n"/>
+      <c r="L27" s="18" t="n"/>
+      <c r="M27" s="17">
+        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C27:L27,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="N27" s="26">
+        <f>COUNTIF(C27:L27,"Y")</f>
+        <v/>
+      </c>
+      <c r="O27" s="27">
+        <f>SUMPRODUCT((C$7:$L$7=1)*(C27:L27="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="17" customHeight="1">
-      <c r="A28" s="34" t="n">
+      <c r="A28" s="29" t="n">
         <v>9</v>
       </c>
-      <c r="B28" s="35" t="inlineStr">
+      <c r="B28" s="30" t="inlineStr">
         <is>
           <t>Jada</t>
         </is>
       </c>
-      <c r="C28" s="36" t="n"/>
-      <c r="D28" s="36" t="n"/>
-      <c r="E28" s="36" t="n"/>
-      <c r="F28" s="36" t="n"/>
-      <c r="G28" s="36" t="n"/>
-      <c r="H28" s="36" t="n"/>
-      <c r="I28" s="36" t="n"/>
-      <c r="J28" s="36" t="n"/>
-      <c r="K28" s="36" t="n"/>
-      <c r="L28" s="36" t="n"/>
-      <c r="M28" s="36" t="n"/>
-      <c r="N28" s="36" t="n"/>
-      <c r="O28" s="36" t="n"/>
-      <c r="P28" s="36" t="n"/>
-      <c r="Q28" s="36" t="n"/>
-      <c r="R28" s="36" t="n"/>
-      <c r="S28" s="36" t="n"/>
-      <c r="T28" s="36" t="n"/>
-      <c r="U28" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$T$7,C28:T28,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="V28" s="31">
-        <f>COUNTIF(C28:T28,"Y")</f>
-        <v/>
-      </c>
-      <c r="W28" s="32">
-        <f>SUMPRODUCT((C$7:$T$7=1)*(C28:T28="Y"))*50</f>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+      <c r="E28" s="31" t="n"/>
+      <c r="F28" s="31" t="n"/>
+      <c r="G28" s="31" t="n"/>
+      <c r="H28" s="31" t="n"/>
+      <c r="I28" s="31" t="n"/>
+      <c r="J28" s="31" t="n"/>
+      <c r="K28" s="31" t="n"/>
+      <c r="L28" s="31" t="n"/>
+      <c r="M28" s="17">
+        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C28:L28,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="N28" s="26">
+        <f>COUNTIF(C28:L28,"Y")</f>
+        <v/>
+      </c>
+      <c r="O28" s="27">
+        <f>SUMPRODUCT((C$7:$L$7=1)*(C28:L28="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="17" customHeight="1">
-      <c r="A29" s="37" t="n">
+      <c r="A29" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="B29" s="38" t="inlineStr">
+      <c r="B29" s="33" t="inlineStr">
         <is>
           <t>Jeremiah</t>
         </is>
       </c>
-      <c r="C29" s="19" t="n"/>
-      <c r="D29" s="19" t="n"/>
-      <c r="E29" s="19" t="n"/>
-      <c r="F29" s="19" t="n"/>
-      <c r="G29" s="19" t="n"/>
-      <c r="H29" s="19" t="n"/>
-      <c r="I29" s="19" t="n"/>
-      <c r="J29" s="19" t="n"/>
-      <c r="K29" s="19" t="n"/>
-      <c r="L29" s="19" t="n"/>
-      <c r="M29" s="19" t="n"/>
-      <c r="N29" s="19" t="n"/>
-      <c r="O29" s="19" t="n"/>
-      <c r="P29" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="Q29" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="R29" s="19" t="n"/>
-      <c r="S29" s="19" t="n"/>
-      <c r="T29" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="U29" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$T$7,C29:T29,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="V29" s="31">
-        <f>COUNTIF(C29:T29,"Y")</f>
-        <v/>
-      </c>
-      <c r="W29" s="32">
-        <f>SUMPRODUCT((C$7:$T$7=1)*(C29:T29="Y"))*50</f>
+      <c r="C29" s="18" t="n"/>
+      <c r="D29" s="18" t="n"/>
+      <c r="E29" s="18" t="n"/>
+      <c r="F29" s="18" t="n"/>
+      <c r="G29" s="18" t="n"/>
+      <c r="H29" s="18" t="n"/>
+      <c r="I29" s="18" t="n"/>
+      <c r="J29" s="18" t="n"/>
+      <c r="K29" s="18" t="n"/>
+      <c r="L29" s="18" t="n"/>
+      <c r="M29" s="17">
+        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C29:L29,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="N29" s="26">
+        <f>COUNTIF(C29:L29,"Y")</f>
+        <v/>
+      </c>
+      <c r="O29" s="27">
+        <f>SUMPRODUCT((C$7:$L$7=1)*(C29:L29="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="17" customHeight="1">
-      <c r="A30" s="34" t="n">
+      <c r="A30" s="29" t="n">
         <v>11</v>
       </c>
-      <c r="B30" s="35" t="inlineStr">
+      <c r="B30" s="30" t="inlineStr">
         <is>
           <t>Kable</t>
         </is>
       </c>
-      <c r="C30" s="36" t="n"/>
-      <c r="D30" s="36" t="n"/>
-      <c r="E30" s="36" t="n"/>
-      <c r="F30" s="36" t="n"/>
-      <c r="G30" s="36" t="n"/>
-      <c r="H30" s="36" t="n"/>
-      <c r="I30" s="36" t="n"/>
-      <c r="J30" s="36" t="n"/>
-      <c r="K30" s="36" t="n"/>
-      <c r="L30" s="36" t="n"/>
-      <c r="M30" s="36" t="n"/>
-      <c r="N30" s="36" t="n"/>
-      <c r="O30" s="36" t="n"/>
-      <c r="P30" s="36" t="n"/>
-      <c r="Q30" s="36" t="n"/>
-      <c r="R30" s="36" t="n"/>
-      <c r="S30" s="36" t="n"/>
-      <c r="T30" s="36" t="n"/>
-      <c r="U30" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$T$7,C30:T30,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="V30" s="31">
-        <f>COUNTIF(C30:T30,"Y")</f>
-        <v/>
-      </c>
-      <c r="W30" s="32">
-        <f>SUMPRODUCT((C$7:$T$7=1)*(C30:T30="Y"))*50</f>
+      <c r="C30" s="31" t="n"/>
+      <c r="D30" s="31" t="n"/>
+      <c r="E30" s="31" t="n"/>
+      <c r="F30" s="31" t="n"/>
+      <c r="G30" s="31" t="n"/>
+      <c r="H30" s="31" t="n"/>
+      <c r="I30" s="31" t="n"/>
+      <c r="J30" s="31" t="n"/>
+      <c r="K30" s="31" t="n"/>
+      <c r="L30" s="31" t="n"/>
+      <c r="M30" s="17">
+        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C30:L30,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="N30" s="26">
+        <f>COUNTIF(C30:L30,"Y")</f>
+        <v/>
+      </c>
+      <c r="O30" s="27">
+        <f>SUMPRODUCT((C$7:$L$7=1)*(C30:L30="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="17" customHeight="1">
-      <c r="A31" s="37" t="n">
+      <c r="A31" s="32" t="n">
         <v>12</v>
       </c>
-      <c r="B31" s="38" t="inlineStr">
+      <c r="B31" s="33" t="inlineStr">
         <is>
           <t>Kayla</t>
         </is>
       </c>
-      <c r="C31" s="19" t="n"/>
-      <c r="D31" s="19" t="n"/>
-      <c r="E31" s="19" t="n"/>
-      <c r="F31" s="19" t="n"/>
-      <c r="G31" s="19" t="n"/>
-      <c r="H31" s="19" t="n"/>
-      <c r="I31" s="19" t="n"/>
-      <c r="J31" s="19" t="n"/>
-      <c r="K31" s="19" t="n"/>
-      <c r="L31" s="19" t="n"/>
-      <c r="M31" s="19" t="n"/>
-      <c r="N31" s="19" t="n"/>
-      <c r="O31" s="19" t="n"/>
-      <c r="P31" s="19" t="n"/>
-      <c r="Q31" s="19" t="n"/>
-      <c r="R31" s="19" t="n"/>
-      <c r="S31" s="19" t="n"/>
-      <c r="T31" s="19" t="n"/>
-      <c r="U31" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$T$7,C31:T31,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="V31" s="31">
-        <f>COUNTIF(C31:T31,"Y")</f>
-        <v/>
-      </c>
-      <c r="W31" s="32">
-        <f>SUMPRODUCT((C$7:$T$7=1)*(C31:T31="Y"))*50</f>
+      <c r="C31" s="18" t="n"/>
+      <c r="D31" s="18" t="n"/>
+      <c r="E31" s="18" t="n"/>
+      <c r="F31" s="18" t="n"/>
+      <c r="G31" s="18" t="n"/>
+      <c r="H31" s="18" t="n"/>
+      <c r="I31" s="18" t="n"/>
+      <c r="J31" s="18" t="n"/>
+      <c r="K31" s="18" t="n"/>
+      <c r="L31" s="18" t="n"/>
+      <c r="M31" s="17">
+        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C31:L31,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="N31" s="26">
+        <f>COUNTIF(C31:L31,"Y")</f>
+        <v/>
+      </c>
+      <c r="O31" s="27">
+        <f>SUMPRODUCT((C$7:$L$7=1)*(C31:L31="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="17" customHeight="1">
-      <c r="A32" s="34" t="n">
+      <c r="A32" s="29" t="n">
         <v>13</v>
       </c>
-      <c r="B32" s="35" t="inlineStr">
+      <c r="B32" s="30" t="inlineStr">
         <is>
           <t>Kenzie</t>
         </is>
       </c>
-      <c r="C32" s="36" t="n"/>
-      <c r="D32" s="36" t="n"/>
-      <c r="E32" s="36" t="n"/>
-      <c r="F32" s="36" t="n"/>
-      <c r="G32" s="36" t="n"/>
-      <c r="H32" s="36" t="n"/>
-      <c r="I32" s="36" t="n"/>
-      <c r="J32" s="36" t="n"/>
-      <c r="K32" s="36" t="n"/>
-      <c r="L32" s="36" t="n"/>
-      <c r="M32" s="36" t="n"/>
-      <c r="N32" s="36" t="n"/>
-      <c r="O32" s="36" t="n"/>
-      <c r="P32" s="36" t="n"/>
-      <c r="Q32" s="36" t="n"/>
-      <c r="R32" s="36" t="n"/>
-      <c r="S32" s="36" t="n"/>
-      <c r="T32" s="36" t="n"/>
-      <c r="U32" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$T$7,C32:T32,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="V32" s="31">
-        <f>COUNTIF(C32:T32,"Y")</f>
-        <v/>
-      </c>
-      <c r="W32" s="32">
-        <f>SUMPRODUCT((C$7:$T$7=1)*(C32:T32="Y"))*50</f>
+      <c r="C32" s="31" t="n"/>
+      <c r="D32" s="31" t="n"/>
+      <c r="E32" s="31" t="n"/>
+      <c r="F32" s="31" t="n"/>
+      <c r="G32" s="31" t="n"/>
+      <c r="H32" s="31" t="n"/>
+      <c r="I32" s="31" t="n"/>
+      <c r="J32" s="31" t="n"/>
+      <c r="K32" s="31" t="n"/>
+      <c r="L32" s="31" t="n"/>
+      <c r="M32" s="17">
+        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C32:L32,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="N32" s="26">
+        <f>COUNTIF(C32:L32,"Y")</f>
+        <v/>
+      </c>
+      <c r="O32" s="27">
+        <f>SUMPRODUCT((C$7:$L$7=1)*(C32:L32="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="17" customHeight="1">
-      <c r="A33" s="37" t="n">
+      <c r="A33" s="32" t="n">
         <v>14</v>
       </c>
-      <c r="B33" s="38" t="inlineStr">
+      <c r="B33" s="33" t="inlineStr">
         <is>
           <t>Lidy</t>
         </is>
       </c>
-      <c r="C33" s="19" t="n"/>
-      <c r="D33" s="19" t="n"/>
-      <c r="E33" s="19" t="n"/>
-      <c r="F33" s="19" t="n"/>
-      <c r="G33" s="19" t="n"/>
-      <c r="H33" s="19" t="n"/>
-      <c r="I33" s="19" t="n"/>
-      <c r="J33" s="19" t="n"/>
-      <c r="K33" s="19" t="n"/>
-      <c r="L33" s="19" t="n"/>
-      <c r="M33" s="19" t="n"/>
-      <c r="N33" s="19" t="n"/>
-      <c r="O33" s="19" t="n"/>
-      <c r="P33" s="19" t="n"/>
-      <c r="Q33" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="R33" s="19" t="n"/>
-      <c r="S33" s="19" t="n"/>
-      <c r="T33" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="U33" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$T$7,C33:T33,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="V33" s="31">
-        <f>COUNTIF(C33:T33,"Y")</f>
-        <v/>
-      </c>
-      <c r="W33" s="32">
-        <f>SUMPRODUCT((C$7:$T$7=1)*(C33:T33="Y"))*50</f>
+      <c r="C33" s="18" t="n"/>
+      <c r="D33" s="18" t="n"/>
+      <c r="E33" s="18" t="n"/>
+      <c r="F33" s="18" t="n"/>
+      <c r="G33" s="18" t="n"/>
+      <c r="H33" s="18" t="n"/>
+      <c r="I33" s="18" t="n"/>
+      <c r="J33" s="18" t="n"/>
+      <c r="K33" s="18" t="n"/>
+      <c r="L33" s="18" t="n"/>
+      <c r="M33" s="17">
+        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C33:L33,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="N33" s="26">
+        <f>COUNTIF(C33:L33,"Y")</f>
+        <v/>
+      </c>
+      <c r="O33" s="27">
+        <f>SUMPRODUCT((C$7:$L$7=1)*(C33:L33="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="17" customHeight="1">
-      <c r="A34" s="34" t="n">
+      <c r="A34" s="29" t="n">
         <v>15</v>
       </c>
-      <c r="B34" s="35" t="inlineStr">
+      <c r="B34" s="30" t="inlineStr">
         <is>
           <t>Maylin</t>
         </is>
       </c>
-      <c r="C34" s="36" t="n"/>
-      <c r="D34" s="36" t="n"/>
-      <c r="E34" s="36" t="n"/>
-      <c r="F34" s="36" t="n"/>
-      <c r="G34" s="36" t="n"/>
-      <c r="H34" s="36" t="n"/>
-      <c r="I34" s="36" t="n"/>
-      <c r="J34" s="36" t="n"/>
-      <c r="K34" s="36" t="n"/>
-      <c r="L34" s="36" t="n"/>
-      <c r="M34" s="36" t="n"/>
-      <c r="N34" s="36" t="n"/>
-      <c r="O34" s="36" t="n"/>
-      <c r="P34" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="Q34" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="R34" s="36" t="n"/>
-      <c r="S34" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="T34" s="36" t="n"/>
-      <c r="U34" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$T$7,C34:T34,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="V34" s="31">
-        <f>COUNTIF(C34:T34,"Y")</f>
-        <v/>
-      </c>
-      <c r="W34" s="32">
-        <f>SUMPRODUCT((C$7:$T$7=1)*(C34:T34="Y"))*50</f>
+      <c r="C34" s="31" t="n"/>
+      <c r="D34" s="31" t="n"/>
+      <c r="E34" s="31" t="n"/>
+      <c r="F34" s="31" t="n"/>
+      <c r="G34" s="31" t="n"/>
+      <c r="H34" s="31" t="n"/>
+      <c r="I34" s="31" t="n"/>
+      <c r="J34" s="31" t="n"/>
+      <c r="K34" s="31" t="n"/>
+      <c r="L34" s="31" t="n"/>
+      <c r="M34" s="17">
+        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C34:L34,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="N34" s="26">
+        <f>COUNTIF(C34:L34,"Y")</f>
+        <v/>
+      </c>
+      <c r="O34" s="27">
+        <f>SUMPRODUCT((C$7:$L$7=1)*(C34:L34="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="17" customHeight="1">
-      <c r="A35" s="37" t="n">
+      <c r="A35" s="32" t="n">
         <v>16</v>
       </c>
-      <c r="B35" s="38" t="inlineStr">
+      <c r="B35" s="33" t="inlineStr">
         <is>
           <t>Mike</t>
         </is>
       </c>
-      <c r="C35" s="19" t="n"/>
-      <c r="D35" s="19" t="n"/>
-      <c r="E35" s="19" t="n"/>
-      <c r="F35" s="19" t="n"/>
-      <c r="G35" s="19" t="n"/>
-      <c r="H35" s="19" t="n"/>
-      <c r="I35" s="19" t="n"/>
-      <c r="J35" s="19" t="n"/>
-      <c r="K35" s="19" t="n"/>
-      <c r="L35" s="19" t="n"/>
-      <c r="M35" s="19" t="n"/>
-      <c r="N35" s="19" t="n"/>
-      <c r="O35" s="19" t="n"/>
-      <c r="P35" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="Q35" s="19" t="n"/>
-      <c r="R35" s="19" t="n"/>
-      <c r="S35" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="T35" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="U35" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$T$7,C35:T35,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="V35" s="31">
-        <f>COUNTIF(C35:T35,"Y")</f>
-        <v/>
-      </c>
-      <c r="W35" s="32">
-        <f>SUMPRODUCT((C$7:$T$7=1)*(C35:T35="Y"))*50</f>
+      <c r="C35" s="18" t="n"/>
+      <c r="D35" s="18" t="n"/>
+      <c r="E35" s="18" t="n"/>
+      <c r="F35" s="18" t="n"/>
+      <c r="G35" s="18" t="n"/>
+      <c r="H35" s="18" t="n"/>
+      <c r="I35" s="18" t="n"/>
+      <c r="J35" s="18" t="n"/>
+      <c r="K35" s="18" t="n"/>
+      <c r="L35" s="18" t="n"/>
+      <c r="M35" s="17">
+        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C35:L35,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="N35" s="26">
+        <f>COUNTIF(C35:L35,"Y")</f>
+        <v/>
+      </c>
+      <c r="O35" s="27">
+        <f>SUMPRODUCT((C$7:$L$7=1)*(C35:L35="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="17" customHeight="1">
-      <c r="A36" s="34" t="n">
+      <c r="A36" s="29" t="n">
         <v>17</v>
       </c>
-      <c r="B36" s="35" t="inlineStr">
+      <c r="B36" s="30" t="inlineStr">
         <is>
           <t>Richard</t>
         </is>
       </c>
-      <c r="C36" s="36" t="n"/>
-      <c r="D36" s="36" t="n"/>
-      <c r="E36" s="36" t="n"/>
-      <c r="F36" s="36" t="n"/>
-      <c r="G36" s="36" t="n"/>
-      <c r="H36" s="36" t="n"/>
-      <c r="I36" s="36" t="n"/>
-      <c r="J36" s="36" t="n"/>
-      <c r="K36" s="36" t="n"/>
-      <c r="L36" s="36" t="n"/>
-      <c r="M36" s="36" t="n"/>
-      <c r="N36" s="36" t="n"/>
-      <c r="O36" s="36" t="n"/>
-      <c r="P36" s="36" t="n"/>
-      <c r="Q36" s="36" t="n"/>
-      <c r="R36" s="36" t="n"/>
-      <c r="S36" s="36" t="n"/>
-      <c r="T36" s="36" t="n"/>
-      <c r="U36" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$T$7,C36:T36,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="V36" s="31">
-        <f>COUNTIF(C36:T36,"Y")</f>
-        <v/>
-      </c>
-      <c r="W36" s="32">
-        <f>SUMPRODUCT((C$7:$T$7=1)*(C36:T36="Y"))*50</f>
+      <c r="C36" s="31" t="n"/>
+      <c r="D36" s="31" t="n"/>
+      <c r="E36" s="31" t="n"/>
+      <c r="F36" s="31" t="n"/>
+      <c r="G36" s="31" t="n"/>
+      <c r="H36" s="31" t="n"/>
+      <c r="I36" s="31" t="n"/>
+      <c r="J36" s="31" t="n"/>
+      <c r="K36" s="31" t="n"/>
+      <c r="L36" s="31" t="n"/>
+      <c r="M36" s="17">
+        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C36:L36,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="N36" s="26">
+        <f>COUNTIF(C36:L36,"Y")</f>
+        <v/>
+      </c>
+      <c r="O36" s="27">
+        <f>SUMPRODUCT((C$7:$L$7=1)*(C36:L36="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="17" customHeight="1">
-      <c r="A37" s="37" t="n">
+      <c r="A37" s="32" t="n">
         <v>18</v>
       </c>
-      <c r="B37" s="38" t="inlineStr">
+      <c r="B37" s="33" t="inlineStr">
         <is>
           <t>Samuel</t>
         </is>
       </c>
-      <c r="C37" s="19" t="n"/>
-      <c r="D37" s="19" t="n"/>
-      <c r="E37" s="19" t="n"/>
-      <c r="F37" s="19" t="n"/>
-      <c r="G37" s="19" t="n"/>
-      <c r="H37" s="19" t="n"/>
-      <c r="I37" s="19" t="n"/>
-      <c r="J37" s="19" t="n"/>
-      <c r="K37" s="19" t="n"/>
-      <c r="L37" s="19" t="n"/>
-      <c r="M37" s="19" t="n"/>
-      <c r="N37" s="19" t="n"/>
-      <c r="O37" s="19" t="n"/>
-      <c r="P37" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="Q37" s="19" t="n"/>
-      <c r="R37" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="S37" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="T37" s="19" t="n"/>
-      <c r="U37" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$T$7,C37:T37,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="V37" s="31">
-        <f>COUNTIF(C37:T37,"Y")</f>
-        <v/>
-      </c>
-      <c r="W37" s="32">
-        <f>SUMPRODUCT((C$7:$T$7=1)*(C37:T37="Y"))*50</f>
+      <c r="C37" s="18" t="n"/>
+      <c r="D37" s="18" t="n"/>
+      <c r="E37" s="18" t="n"/>
+      <c r="F37" s="18" t="n"/>
+      <c r="G37" s="18" t="n"/>
+      <c r="H37" s="18" t="n"/>
+      <c r="I37" s="18" t="n"/>
+      <c r="J37" s="18" t="n"/>
+      <c r="K37" s="18" t="n"/>
+      <c r="L37" s="18" t="n"/>
+      <c r="M37" s="17">
+        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C37:L37,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="N37" s="26">
+        <f>COUNTIF(C37:L37,"Y")</f>
+        <v/>
+      </c>
+      <c r="O37" s="27">
+        <f>SUMPRODUCT((C$7:$L$7=1)*(C37:L37="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="17" customHeight="1">
-      <c r="A38" s="34" t="n">
+      <c r="A38" s="29" t="n">
         <v>19</v>
       </c>
-      <c r="B38" s="35" t="inlineStr">
+      <c r="B38" s="30" t="inlineStr">
         <is>
           <t>Zach</t>
         </is>
       </c>
-      <c r="C38" s="36" t="n"/>
-      <c r="D38" s="36" t="n"/>
-      <c r="E38" s="36" t="n"/>
-      <c r="F38" s="36" t="n"/>
-      <c r="G38" s="36" t="n"/>
-      <c r="H38" s="36" t="n"/>
-      <c r="I38" s="36" t="n"/>
-      <c r="J38" s="36" t="n"/>
-      <c r="K38" s="36" t="n"/>
-      <c r="L38" s="36" t="n"/>
-      <c r="M38" s="36" t="n"/>
-      <c r="N38" s="36" t="n"/>
-      <c r="O38" s="36" t="n"/>
-      <c r="P38" s="36" t="n"/>
-      <c r="Q38" s="36" t="n"/>
-      <c r="R38" s="36" t="n"/>
-      <c r="S38" s="36" t="n"/>
-      <c r="T38" s="36" t="n"/>
-      <c r="U38" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$T$7,C38:T38,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="V38" s="31">
-        <f>COUNTIF(C38:T38,"Y")</f>
-        <v/>
-      </c>
-      <c r="W38" s="32">
-        <f>SUMPRODUCT((C$7:$T$7=1)*(C38:T38="Y"))*50</f>
+      <c r="C38" s="31" t="n"/>
+      <c r="D38" s="31" t="n"/>
+      <c r="E38" s="31" t="n"/>
+      <c r="F38" s="31" t="n"/>
+      <c r="G38" s="31" t="n"/>
+      <c r="H38" s="31" t="n"/>
+      <c r="I38" s="31" t="n"/>
+      <c r="J38" s="31" t="n"/>
+      <c r="K38" s="31" t="n"/>
+      <c r="L38" s="31" t="n"/>
+      <c r="M38" s="17">
+        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C38:L38,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="N38" s="26">
+        <f>COUNTIF(C38:L38,"Y")</f>
+        <v/>
+      </c>
+      <c r="O38" s="27">
+        <f>SUMPRODUCT((C$7:$L$7=1)*(C38:L38="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="3" t="inlineStr"/>
-      <c r="B39" s="39" t="inlineStr">
+      <c r="B39" s="34" t="inlineStr">
         <is>
           <t>Total on shift</t>
         </is>
@@ -2461,50 +1945,18 @@
         <f>COUNTIF(L14:L38,"Y")</f>
         <v/>
       </c>
-      <c r="M39" s="6">
-        <f>COUNTIF(M14:M38,"Y")</f>
-        <v/>
-      </c>
+      <c r="M39" s="3" t="inlineStr"/>
       <c r="N39" s="6">
-        <f>COUNTIF(N14:N38,"Y")</f>
-        <v/>
-      </c>
-      <c r="O39" s="6">
-        <f>COUNTIF(O14:O38,"Y")</f>
-        <v/>
-      </c>
-      <c r="P39" s="6">
-        <f>COUNTIF(P14:P38,"Y")</f>
-        <v/>
-      </c>
-      <c r="Q39" s="6">
-        <f>COUNTIF(Q14:Q38,"Y")</f>
-        <v/>
-      </c>
-      <c r="R39" s="6">
-        <f>COUNTIF(R14:R38,"Y")</f>
-        <v/>
-      </c>
-      <c r="S39" s="6">
-        <f>COUNTIF(S14:S38,"Y")</f>
-        <v/>
-      </c>
-      <c r="T39" s="6">
-        <f>COUNTIF(T14:T38,"Y")</f>
-        <v/>
-      </c>
-      <c r="U39" s="3" t="inlineStr"/>
-      <c r="V39" s="6">
-        <f>SUM(V14:V38)</f>
-        <v/>
-      </c>
-      <c r="W39" s="40">
-        <f>SUM(W14:W38)</f>
+        <f>SUM(N14:N38)</f>
+        <v/>
+      </c>
+      <c r="O39" s="35">
+        <f>SUM(O14:O38)</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="12" customHeight="1">
-      <c r="A40" s="41" t="inlineStr">
+      <c r="A40" s="36" t="inlineStr">
         <is>
           <t>Y = on shift during shop's meal window. Personal Avg = average score of shops worked. Bonus = $50 per 100% shop worked.</t>
         </is>
@@ -2512,13 +1964,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A13:W13"/>
-    <mergeCell ref="A1:W1"/>
-    <mergeCell ref="A40:W40"/>
-    <mergeCell ref="A18:W18"/>
-    <mergeCell ref="A12:W12"/>
-    <mergeCell ref="A2:W2"/>
-    <mergeCell ref="A19:W19"/>
+    <mergeCell ref="A12:O12"/>
+    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="A13:O13"/>
+    <mergeCell ref="A19:O19"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A40:O40"/>
+    <mergeCell ref="A18:O18"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2801,7 +2253,7 @@
           <t>Total Score</t>
         </is>
       </c>
-      <c r="C7" s="17" t="n">
+      <c r="C7" s="37" t="n">
         <v>0.95</v>
       </c>
       <c r="D7" s="16" t="n">
@@ -2810,7 +2262,7 @@
       <c r="E7" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="17" t="n">
+      <c r="F7" s="37" t="n">
         <v>0.9</v>
       </c>
       <c r="G7" s="16" t="n">
@@ -2834,10 +2286,10 @@
       <c r="M7" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="N7" s="17" t="n">
+      <c r="N7" s="37" t="n">
         <v>0.95</v>
       </c>
-      <c r="O7" s="18">
+      <c r="O7" s="17">
         <f>IFERROR(AVERAGE(C7:N7),"")</f>
         <v/>
       </c>
@@ -2845,1086 +2297,1086 @@
       <c r="Q7" s="12" t="inlineStr"/>
     </row>
     <row r="8" ht="13" customHeight="1">
-      <c r="A8" s="19" t="inlineStr"/>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr"/>
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr"/>
-      <c r="D8" s="19" t="inlineStr"/>
-      <c r="E8" s="19" t="inlineStr"/>
-      <c r="F8" s="19" t="inlineStr"/>
-      <c r="G8" s="19" t="inlineStr"/>
-      <c r="H8" s="19" t="inlineStr"/>
-      <c r="I8" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" s="21" t="n">
+      <c r="C8" s="18" t="inlineStr"/>
+      <c r="D8" s="18" t="inlineStr"/>
+      <c r="E8" s="18" t="inlineStr"/>
+      <c r="F8" s="18" t="inlineStr"/>
+      <c r="G8" s="18" t="inlineStr"/>
+      <c r="H8" s="18" t="inlineStr"/>
+      <c r="I8" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" s="39" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="L8" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" s="42" t="n">
+      <c r="L8" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" s="40" t="n">
         <v>0.95</v>
       </c>
-      <c r="O8" s="23">
+      <c r="O8" s="20">
         <f>IFERROR(AVERAGE(C8:N8),"")</f>
         <v/>
       </c>
-      <c r="P8" s="19" t="inlineStr"/>
-      <c r="Q8" s="19" t="inlineStr"/>
+      <c r="P8" s="18" t="inlineStr"/>
+      <c r="Q8" s="18" t="inlineStr"/>
     </row>
     <row r="9" ht="13" customHeight="1">
-      <c r="A9" s="19" t="inlineStr"/>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="A9" s="18" t="inlineStr"/>
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>Quality</t>
         </is>
       </c>
-      <c r="C9" s="19" t="inlineStr"/>
-      <c r="D9" s="19" t="inlineStr"/>
-      <c r="E9" s="19" t="inlineStr"/>
-      <c r="F9" s="19" t="inlineStr"/>
-      <c r="G9" s="19" t="inlineStr"/>
-      <c r="H9" s="19" t="inlineStr"/>
-      <c r="I9" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" s="23">
+      <c r="C9" s="18" t="inlineStr"/>
+      <c r="D9" s="18" t="inlineStr"/>
+      <c r="E9" s="18" t="inlineStr"/>
+      <c r="F9" s="18" t="inlineStr"/>
+      <c r="G9" s="18" t="inlineStr"/>
+      <c r="H9" s="18" t="inlineStr"/>
+      <c r="I9" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" s="20">
         <f>IFERROR(AVERAGE(C9:N9),"")</f>
         <v/>
       </c>
-      <c r="P9" s="19" t="inlineStr"/>
-      <c r="Q9" s="19" t="inlineStr"/>
+      <c r="P9" s="18" t="inlineStr"/>
+      <c r="Q9" s="18" t="inlineStr"/>
     </row>
     <row r="10" ht="13" customHeight="1">
-      <c r="A10" s="19" t="inlineStr"/>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="A10" s="18" t="inlineStr"/>
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>Cleanliness</t>
         </is>
       </c>
-      <c r="C10" s="19" t="inlineStr"/>
-      <c r="D10" s="19" t="inlineStr"/>
-      <c r="E10" s="19" t="inlineStr"/>
-      <c r="F10" s="19" t="inlineStr"/>
-      <c r="G10" s="19" t="inlineStr"/>
-      <c r="H10" s="19" t="inlineStr"/>
-      <c r="I10" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" s="23">
+      <c r="C10" s="18" t="inlineStr"/>
+      <c r="D10" s="18" t="inlineStr"/>
+      <c r="E10" s="18" t="inlineStr"/>
+      <c r="F10" s="18" t="inlineStr"/>
+      <c r="G10" s="18" t="inlineStr"/>
+      <c r="H10" s="18" t="inlineStr"/>
+      <c r="I10" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" s="20">
         <f>IFERROR(AVERAGE(C10:N10),"")</f>
         <v/>
       </c>
-      <c r="P10" s="19" t="inlineStr"/>
-      <c r="Q10" s="19" t="inlineStr"/>
+      <c r="P10" s="18" t="inlineStr"/>
+      <c r="Q10" s="18" t="inlineStr"/>
     </row>
     <row r="11" ht="13" customHeight="1">
-      <c r="A11" s="19" t="inlineStr"/>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr"/>
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>Customer Sat</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr"/>
-      <c r="D11" s="19" t="inlineStr"/>
-      <c r="E11" s="19" t="inlineStr"/>
-      <c r="F11" s="19" t="inlineStr"/>
-      <c r="G11" s="19" t="inlineStr"/>
-      <c r="H11" s="19" t="inlineStr"/>
-      <c r="I11" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" s="23">
+      <c r="C11" s="18" t="inlineStr"/>
+      <c r="D11" s="18" t="inlineStr"/>
+      <c r="E11" s="18" t="inlineStr"/>
+      <c r="F11" s="18" t="inlineStr"/>
+      <c r="G11" s="18" t="inlineStr"/>
+      <c r="H11" s="18" t="inlineStr"/>
+      <c r="I11" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" s="20">
         <f>IFERROR(AVERAGE(C11:N11),"")</f>
         <v/>
       </c>
-      <c r="P11" s="19" t="inlineStr"/>
-      <c r="Q11" s="19" t="inlineStr"/>
+      <c r="P11" s="18" t="inlineStr"/>
+      <c r="Q11" s="18" t="inlineStr"/>
     </row>
     <row r="12" ht="6" customHeight="1">
-      <c r="A12" s="25" t="n"/>
+      <c r="A12" s="21" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="26" t="inlineStr">
+      <c r="A13" s="22" t="inlineStr">
         <is>
           <t>MANAGERS</t>
         </is>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="B14" s="28" t="inlineStr">
+      <c r="A14" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
         <is>
           <t>Madison C.</t>
         </is>
       </c>
-      <c r="C14" s="29" t="n"/>
-      <c r="D14" s="29" t="n"/>
-      <c r="E14" s="29" t="n"/>
-      <c r="F14" s="29" t="n"/>
-      <c r="G14" s="29" t="n"/>
-      <c r="H14" s="29" t="n"/>
-      <c r="I14" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J14" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K14" s="29" t="n"/>
-      <c r="L14" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M14" s="29" t="n"/>
-      <c r="N14" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O14" s="18">
+      <c r="C14" s="25" t="n"/>
+      <c r="D14" s="25" t="n"/>
+      <c r="E14" s="25" t="n"/>
+      <c r="F14" s="25" t="n"/>
+      <c r="G14" s="25" t="n"/>
+      <c r="H14" s="25" t="n"/>
+      <c r="I14" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J14" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K14" s="25" t="n"/>
+      <c r="L14" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M14" s="25" t="n"/>
+      <c r="N14" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O14" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$N$7,C14:N14,"Y"),"")</f>
         <v/>
       </c>
-      <c r="P14" s="31">
+      <c r="P14" s="26">
         <f>COUNTIF(C14:N14,"Y")</f>
         <v/>
       </c>
-      <c r="Q14" s="32">
+      <c r="Q14" s="27">
         <f>SUMPRODUCT((C$7:$N$7=1)*(C14:N14="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="27" t="n">
+      <c r="A15" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="B15" s="28" t="inlineStr">
+      <c r="B15" s="24" t="inlineStr">
         <is>
           <t>Vicki L.</t>
         </is>
       </c>
-      <c r="C15" s="29" t="n"/>
-      <c r="D15" s="29" t="n"/>
-      <c r="E15" s="29" t="n"/>
-      <c r="F15" s="29" t="n"/>
-      <c r="G15" s="29" t="n"/>
-      <c r="H15" s="29" t="n"/>
-      <c r="I15" s="29" t="n"/>
-      <c r="J15" s="29" t="n"/>
-      <c r="K15" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L15" s="29" t="n"/>
-      <c r="M15" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N15" s="29" t="n"/>
-      <c r="O15" s="18">
+      <c r="C15" s="25" t="n"/>
+      <c r="D15" s="25" t="n"/>
+      <c r="E15" s="25" t="n"/>
+      <c r="F15" s="25" t="n"/>
+      <c r="G15" s="25" t="n"/>
+      <c r="H15" s="25" t="n"/>
+      <c r="I15" s="25" t="n"/>
+      <c r="J15" s="25" t="n"/>
+      <c r="K15" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L15" s="25" t="n"/>
+      <c r="M15" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N15" s="25" t="n"/>
+      <c r="O15" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$N$7,C15:N15,"Y"),"")</f>
         <v/>
       </c>
-      <c r="P15" s="31">
+      <c r="P15" s="26">
         <f>COUNTIF(C15:N15,"Y")</f>
         <v/>
       </c>
-      <c r="Q15" s="32">
+      <c r="Q15" s="27">
         <f>SUMPRODUCT((C$7:$N$7=1)*(C15:N15="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
-      <c r="A16" s="27" t="n">
+      <c r="A16" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="B16" s="28" t="inlineStr">
+      <c r="B16" s="24" t="inlineStr">
         <is>
           <t>Kasey W.</t>
         </is>
       </c>
-      <c r="C16" s="29" t="n"/>
-      <c r="D16" s="29" t="n"/>
-      <c r="E16" s="29" t="n"/>
-      <c r="F16" s="29" t="n"/>
-      <c r="G16" s="29" t="n"/>
-      <c r="H16" s="29" t="n"/>
-      <c r="I16" s="29" t="n"/>
-      <c r="J16" s="29" t="n"/>
-      <c r="K16" s="29" t="n"/>
-      <c r="L16" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M16" s="29" t="n"/>
-      <c r="N16" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O16" s="18">
+      <c r="C16" s="25" t="n"/>
+      <c r="D16" s="25" t="n"/>
+      <c r="E16" s="25" t="n"/>
+      <c r="F16" s="25" t="n"/>
+      <c r="G16" s="25" t="n"/>
+      <c r="H16" s="25" t="n"/>
+      <c r="I16" s="25" t="n"/>
+      <c r="J16" s="25" t="n"/>
+      <c r="K16" s="25" t="n"/>
+      <c r="L16" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M16" s="25" t="n"/>
+      <c r="N16" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O16" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$N$7,C16:N16,"Y"),"")</f>
         <v/>
       </c>
-      <c r="P16" s="31">
+      <c r="P16" s="26">
         <f>COUNTIF(C16:N16,"Y")</f>
         <v/>
       </c>
-      <c r="Q16" s="32">
+      <c r="Q16" s="27">
         <f>SUMPRODUCT((C$7:$N$7=1)*(C16:N16="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
-      <c r="A17" s="27" t="n">
+      <c r="A17" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="B17" s="28" t="inlineStr">
+      <c r="B17" s="24" t="inlineStr">
         <is>
           <t>Nathan R.</t>
         </is>
       </c>
-      <c r="C17" s="29" t="n"/>
-      <c r="D17" s="29" t="n"/>
-      <c r="E17" s="29" t="n"/>
-      <c r="F17" s="29" t="n"/>
-      <c r="G17" s="29" t="n"/>
-      <c r="H17" s="29" t="n"/>
-      <c r="I17" s="29" t="n"/>
-      <c r="J17" s="29" t="n"/>
-      <c r="K17" s="29" t="n"/>
-      <c r="L17" s="29" t="n"/>
-      <c r="M17" s="29" t="n"/>
-      <c r="N17" s="29" t="n"/>
-      <c r="O17" s="18">
+      <c r="C17" s="25" t="n"/>
+      <c r="D17" s="25" t="n"/>
+      <c r="E17" s="25" t="n"/>
+      <c r="F17" s="25" t="n"/>
+      <c r="G17" s="25" t="n"/>
+      <c r="H17" s="25" t="n"/>
+      <c r="I17" s="25" t="n"/>
+      <c r="J17" s="25" t="n"/>
+      <c r="K17" s="25" t="n"/>
+      <c r="L17" s="25" t="n"/>
+      <c r="M17" s="25" t="n"/>
+      <c r="N17" s="25" t="n"/>
+      <c r="O17" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$N$7,C17:N17,"Y"),"")</f>
         <v/>
       </c>
-      <c r="P17" s="31">
+      <c r="P17" s="26">
         <f>COUNTIF(C17:N17,"Y")</f>
         <v/>
       </c>
-      <c r="Q17" s="32">
+      <c r="Q17" s="27">
         <f>SUMPRODUCT((C$7:$N$7=1)*(C17:N17="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="6" customHeight="1">
-      <c r="A18" s="25" t="n"/>
+      <c r="A18" s="21" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="33" t="inlineStr">
+      <c r="A19" s="28" t="inlineStr">
         <is>
           <t>CREW</t>
         </is>
       </c>
     </row>
     <row r="20" ht="17" customHeight="1">
-      <c r="A20" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="B20" s="35" t="inlineStr">
+      <c r="A20" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
         <is>
           <t>Alen</t>
         </is>
       </c>
-      <c r="C20" s="36" t="n"/>
-      <c r="D20" s="36" t="n"/>
-      <c r="E20" s="36" t="n"/>
-      <c r="F20" s="36" t="n"/>
-      <c r="G20" s="36" t="n"/>
-      <c r="H20" s="36" t="n"/>
-      <c r="I20" s="36" t="n"/>
-      <c r="J20" s="36" t="n"/>
-      <c r="K20" s="36" t="n"/>
-      <c r="L20" s="36" t="n"/>
-      <c r="M20" s="36" t="n"/>
-      <c r="N20" s="36" t="n"/>
-      <c r="O20" s="18">
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+      <c r="E20" s="31" t="n"/>
+      <c r="F20" s="31" t="n"/>
+      <c r="G20" s="31" t="n"/>
+      <c r="H20" s="31" t="n"/>
+      <c r="I20" s="31" t="n"/>
+      <c r="J20" s="31" t="n"/>
+      <c r="K20" s="31" t="n"/>
+      <c r="L20" s="31" t="n"/>
+      <c r="M20" s="31" t="n"/>
+      <c r="N20" s="31" t="n"/>
+      <c r="O20" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$N$7,C20:N20,"Y"),"")</f>
         <v/>
       </c>
-      <c r="P20" s="31">
+      <c r="P20" s="26">
         <f>COUNTIF(C20:N20,"Y")</f>
         <v/>
       </c>
-      <c r="Q20" s="32">
+      <c r="Q20" s="27">
         <f>SUMPRODUCT((C$7:$N$7=1)*(C20:N20="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="17" customHeight="1">
-      <c r="A21" s="37" t="n">
+      <c r="A21" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="B21" s="38" t="inlineStr">
+      <c r="B21" s="33" t="inlineStr">
         <is>
           <t>Ash</t>
         </is>
       </c>
-      <c r="C21" s="19" t="n"/>
-      <c r="D21" s="19" t="n"/>
-      <c r="E21" s="19" t="n"/>
-      <c r="F21" s="19" t="n"/>
-      <c r="G21" s="19" t="n"/>
-      <c r="H21" s="19" t="n"/>
-      <c r="I21" s="19" t="n"/>
-      <c r="J21" s="19" t="n"/>
-      <c r="K21" s="19" t="n"/>
-      <c r="L21" s="19" t="n"/>
-      <c r="M21" s="19" t="n"/>
-      <c r="N21" s="19" t="n"/>
-      <c r="O21" s="18">
+      <c r="C21" s="18" t="n"/>
+      <c r="D21" s="18" t="n"/>
+      <c r="E21" s="18" t="n"/>
+      <c r="F21" s="18" t="n"/>
+      <c r="G21" s="18" t="n"/>
+      <c r="H21" s="18" t="n"/>
+      <c r="I21" s="18" t="n"/>
+      <c r="J21" s="18" t="n"/>
+      <c r="K21" s="18" t="n"/>
+      <c r="L21" s="18" t="n"/>
+      <c r="M21" s="18" t="n"/>
+      <c r="N21" s="18" t="n"/>
+      <c r="O21" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$N$7,C21:N21,"Y"),"")</f>
         <v/>
       </c>
-      <c r="P21" s="31">
+      <c r="P21" s="26">
         <f>COUNTIF(C21:N21,"Y")</f>
         <v/>
       </c>
-      <c r="Q21" s="32">
+      <c r="Q21" s="27">
         <f>SUMPRODUCT((C$7:$N$7=1)*(C21:N21="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="17" customHeight="1">
-      <c r="A22" s="34" t="n">
+      <c r="A22" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B22" s="35" t="inlineStr">
+      <c r="B22" s="30" t="inlineStr">
         <is>
           <t>Autumn</t>
         </is>
       </c>
-      <c r="C22" s="36" t="n"/>
-      <c r="D22" s="36" t="n"/>
-      <c r="E22" s="36" t="n"/>
-      <c r="F22" s="36" t="n"/>
-      <c r="G22" s="36" t="n"/>
-      <c r="H22" s="36" t="n"/>
-      <c r="I22" s="36" t="n"/>
-      <c r="J22" s="36" t="n"/>
-      <c r="K22" s="36" t="n"/>
-      <c r="L22" s="36" t="n"/>
-      <c r="M22" s="36" t="n"/>
-      <c r="N22" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O22" s="18">
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+      <c r="E22" s="31" t="n"/>
+      <c r="F22" s="31" t="n"/>
+      <c r="G22" s="31" t="n"/>
+      <c r="H22" s="31" t="n"/>
+      <c r="I22" s="31" t="n"/>
+      <c r="J22" s="31" t="n"/>
+      <c r="K22" s="31" t="n"/>
+      <c r="L22" s="31" t="n"/>
+      <c r="M22" s="31" t="n"/>
+      <c r="N22" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O22" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$N$7,C22:N22,"Y"),"")</f>
         <v/>
       </c>
-      <c r="P22" s="31">
+      <c r="P22" s="26">
         <f>COUNTIF(C22:N22,"Y")</f>
         <v/>
       </c>
-      <c r="Q22" s="32">
+      <c r="Q22" s="27">
         <f>SUMPRODUCT((C$7:$N$7=1)*(C22:N22="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="17" customHeight="1">
-      <c r="A23" s="37" t="n">
+      <c r="A23" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="B23" s="38" t="inlineStr">
+      <c r="B23" s="33" t="inlineStr">
         <is>
           <t>Bri</t>
         </is>
       </c>
-      <c r="C23" s="19" t="n"/>
-      <c r="D23" s="19" t="n"/>
-      <c r="E23" s="19" t="n"/>
-      <c r="F23" s="19" t="n"/>
-      <c r="G23" s="19" t="n"/>
-      <c r="H23" s="19" t="n"/>
-      <c r="I23" s="19" t="n"/>
-      <c r="J23" s="19" t="n"/>
-      <c r="K23" s="19" t="n"/>
-      <c r="L23" s="19" t="n"/>
-      <c r="M23" s="19" t="n"/>
-      <c r="N23" s="19" t="n"/>
-      <c r="O23" s="18">
+      <c r="C23" s="18" t="n"/>
+      <c r="D23" s="18" t="n"/>
+      <c r="E23" s="18" t="n"/>
+      <c r="F23" s="18" t="n"/>
+      <c r="G23" s="18" t="n"/>
+      <c r="H23" s="18" t="n"/>
+      <c r="I23" s="18" t="n"/>
+      <c r="J23" s="18" t="n"/>
+      <c r="K23" s="18" t="n"/>
+      <c r="L23" s="18" t="n"/>
+      <c r="M23" s="18" t="n"/>
+      <c r="N23" s="18" t="n"/>
+      <c r="O23" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$N$7,C23:N23,"Y"),"")</f>
         <v/>
       </c>
-      <c r="P23" s="31">
+      <c r="P23" s="26">
         <f>COUNTIF(C23:N23,"Y")</f>
         <v/>
       </c>
-      <c r="Q23" s="32">
+      <c r="Q23" s="27">
         <f>SUMPRODUCT((C$7:$N$7=1)*(C23:N23="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="17" customHeight="1">
-      <c r="A24" s="34" t="n">
+      <c r="A24" s="29" t="n">
         <v>5</v>
       </c>
-      <c r="B24" s="35" t="inlineStr">
+      <c r="B24" s="30" t="inlineStr">
         <is>
           <t>Dakayla</t>
         </is>
       </c>
-      <c r="C24" s="36" t="n"/>
-      <c r="D24" s="36" t="n"/>
-      <c r="E24" s="36" t="n"/>
-      <c r="F24" s="36" t="n"/>
-      <c r="G24" s="36" t="n"/>
-      <c r="H24" s="36" t="n"/>
-      <c r="I24" s="36" t="n"/>
-      <c r="J24" s="36" t="n"/>
-      <c r="K24" s="36" t="n"/>
-      <c r="L24" s="36" t="n"/>
-      <c r="M24" s="36" t="n"/>
-      <c r="N24" s="36" t="n"/>
-      <c r="O24" s="18">
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+      <c r="E24" s="31" t="n"/>
+      <c r="F24" s="31" t="n"/>
+      <c r="G24" s="31" t="n"/>
+      <c r="H24" s="31" t="n"/>
+      <c r="I24" s="31" t="n"/>
+      <c r="J24" s="31" t="n"/>
+      <c r="K24" s="31" t="n"/>
+      <c r="L24" s="31" t="n"/>
+      <c r="M24" s="31" t="n"/>
+      <c r="N24" s="31" t="n"/>
+      <c r="O24" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$N$7,C24:N24,"Y"),"")</f>
         <v/>
       </c>
-      <c r="P24" s="31">
+      <c r="P24" s="26">
         <f>COUNTIF(C24:N24,"Y")</f>
         <v/>
       </c>
-      <c r="Q24" s="32">
+      <c r="Q24" s="27">
         <f>SUMPRODUCT((C$7:$N$7=1)*(C24:N24="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="17" customHeight="1">
-      <c r="A25" s="37" t="n">
+      <c r="A25" s="32" t="n">
         <v>6</v>
       </c>
-      <c r="B25" s="38" t="inlineStr">
+      <c r="B25" s="33" t="inlineStr">
         <is>
           <t>Divan</t>
         </is>
       </c>
-      <c r="C25" s="19" t="n"/>
-      <c r="D25" s="19" t="n"/>
-      <c r="E25" s="19" t="n"/>
-      <c r="F25" s="19" t="n"/>
-      <c r="G25" s="19" t="n"/>
-      <c r="H25" s="19" t="n"/>
-      <c r="I25" s="19" t="n"/>
-      <c r="J25" s="19" t="n"/>
-      <c r="K25" s="19" t="n"/>
-      <c r="L25" s="19" t="n"/>
-      <c r="M25" s="19" t="n"/>
-      <c r="N25" s="19" t="n"/>
-      <c r="O25" s="18">
+      <c r="C25" s="18" t="n"/>
+      <c r="D25" s="18" t="n"/>
+      <c r="E25" s="18" t="n"/>
+      <c r="F25" s="18" t="n"/>
+      <c r="G25" s="18" t="n"/>
+      <c r="H25" s="18" t="n"/>
+      <c r="I25" s="18" t="n"/>
+      <c r="J25" s="18" t="n"/>
+      <c r="K25" s="18" t="n"/>
+      <c r="L25" s="18" t="n"/>
+      <c r="M25" s="18" t="n"/>
+      <c r="N25" s="18" t="n"/>
+      <c r="O25" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$N$7,C25:N25,"Y"),"")</f>
         <v/>
       </c>
-      <c r="P25" s="31">
+      <c r="P25" s="26">
         <f>COUNTIF(C25:N25,"Y")</f>
         <v/>
       </c>
-      <c r="Q25" s="32">
+      <c r="Q25" s="27">
         <f>SUMPRODUCT((C$7:$N$7=1)*(C25:N25="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="17" customHeight="1">
-      <c r="A26" s="34" t="n">
+      <c r="A26" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="B26" s="35" t="inlineStr">
+      <c r="B26" s="30" t="inlineStr">
         <is>
           <t>Francisco</t>
         </is>
       </c>
-      <c r="C26" s="36" t="n"/>
-      <c r="D26" s="36" t="n"/>
-      <c r="E26" s="36" t="n"/>
-      <c r="F26" s="36" t="n"/>
-      <c r="G26" s="36" t="n"/>
-      <c r="H26" s="36" t="n"/>
-      <c r="I26" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J26" s="36" t="n"/>
-      <c r="K26" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L26" s="36" t="n"/>
-      <c r="M26" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N26" s="36" t="n"/>
-      <c r="O26" s="18">
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+      <c r="E26" s="31" t="n"/>
+      <c r="F26" s="31" t="n"/>
+      <c r="G26" s="31" t="n"/>
+      <c r="H26" s="31" t="n"/>
+      <c r="I26" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J26" s="31" t="n"/>
+      <c r="K26" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L26" s="31" t="n"/>
+      <c r="M26" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N26" s="31" t="n"/>
+      <c r="O26" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$N$7,C26:N26,"Y"),"")</f>
         <v/>
       </c>
-      <c r="P26" s="31">
+      <c r="P26" s="26">
         <f>COUNTIF(C26:N26,"Y")</f>
         <v/>
       </c>
-      <c r="Q26" s="32">
+      <c r="Q26" s="27">
         <f>SUMPRODUCT((C$7:$N$7=1)*(C26:N26="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="17" customHeight="1">
-      <c r="A27" s="37" t="n">
+      <c r="A27" s="32" t="n">
         <v>8</v>
       </c>
-      <c r="B27" s="38" t="inlineStr">
+      <c r="B27" s="33" t="inlineStr">
         <is>
           <t>Grace</t>
         </is>
       </c>
-      <c r="C27" s="19" t="n"/>
-      <c r="D27" s="19" t="n"/>
-      <c r="E27" s="19" t="n"/>
-      <c r="F27" s="19" t="n"/>
-      <c r="G27" s="19" t="n"/>
-      <c r="H27" s="19" t="n"/>
-      <c r="I27" s="19" t="n"/>
-      <c r="J27" s="19" t="n"/>
-      <c r="K27" s="19" t="n"/>
-      <c r="L27" s="19" t="n"/>
-      <c r="M27" s="19" t="n"/>
-      <c r="N27" s="19" t="n"/>
-      <c r="O27" s="18">
+      <c r="C27" s="18" t="n"/>
+      <c r="D27" s="18" t="n"/>
+      <c r="E27" s="18" t="n"/>
+      <c r="F27" s="18" t="n"/>
+      <c r="G27" s="18" t="n"/>
+      <c r="H27" s="18" t="n"/>
+      <c r="I27" s="18" t="n"/>
+      <c r="J27" s="18" t="n"/>
+      <c r="K27" s="18" t="n"/>
+      <c r="L27" s="18" t="n"/>
+      <c r="M27" s="18" t="n"/>
+      <c r="N27" s="18" t="n"/>
+      <c r="O27" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$N$7,C27:N27,"Y"),"")</f>
         <v/>
       </c>
-      <c r="P27" s="31">
+      <c r="P27" s="26">
         <f>COUNTIF(C27:N27,"Y")</f>
         <v/>
       </c>
-      <c r="Q27" s="32">
+      <c r="Q27" s="27">
         <f>SUMPRODUCT((C$7:$N$7=1)*(C27:N27="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="17" customHeight="1">
-      <c r="A28" s="34" t="n">
+      <c r="A28" s="29" t="n">
         <v>9</v>
       </c>
-      <c r="B28" s="35" t="inlineStr">
+      <c r="B28" s="30" t="inlineStr">
         <is>
           <t>Jada</t>
         </is>
       </c>
-      <c r="C28" s="36" t="n"/>
-      <c r="D28" s="36" t="n"/>
-      <c r="E28" s="36" t="n"/>
-      <c r="F28" s="36" t="n"/>
-      <c r="G28" s="36" t="n"/>
-      <c r="H28" s="36" t="n"/>
-      <c r="I28" s="36" t="n"/>
-      <c r="J28" s="36" t="n"/>
-      <c r="K28" s="36" t="n"/>
-      <c r="L28" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M28" s="36" t="n"/>
-      <c r="N28" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O28" s="18">
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+      <c r="E28" s="31" t="n"/>
+      <c r="F28" s="31" t="n"/>
+      <c r="G28" s="31" t="n"/>
+      <c r="H28" s="31" t="n"/>
+      <c r="I28" s="31" t="n"/>
+      <c r="J28" s="31" t="n"/>
+      <c r="K28" s="31" t="n"/>
+      <c r="L28" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M28" s="31" t="n"/>
+      <c r="N28" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O28" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$N$7,C28:N28,"Y"),"")</f>
         <v/>
       </c>
-      <c r="P28" s="31">
+      <c r="P28" s="26">
         <f>COUNTIF(C28:N28,"Y")</f>
         <v/>
       </c>
-      <c r="Q28" s="32">
+      <c r="Q28" s="27">
         <f>SUMPRODUCT((C$7:$N$7=1)*(C28:N28="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="17" customHeight="1">
-      <c r="A29" s="37" t="n">
+      <c r="A29" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="B29" s="38" t="inlineStr">
+      <c r="B29" s="33" t="inlineStr">
         <is>
           <t>Jeremiah</t>
         </is>
       </c>
-      <c r="C29" s="19" t="n"/>
-      <c r="D29" s="19" t="n"/>
-      <c r="E29" s="19" t="n"/>
-      <c r="F29" s="19" t="n"/>
-      <c r="G29" s="19" t="n"/>
-      <c r="H29" s="19" t="n"/>
-      <c r="I29" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J29" s="19" t="n"/>
-      <c r="K29" s="19" t="n"/>
-      <c r="L29" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M29" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N29" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O29" s="18">
+      <c r="C29" s="18" t="n"/>
+      <c r="D29" s="18" t="n"/>
+      <c r="E29" s="18" t="n"/>
+      <c r="F29" s="18" t="n"/>
+      <c r="G29" s="18" t="n"/>
+      <c r="H29" s="18" t="n"/>
+      <c r="I29" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J29" s="18" t="n"/>
+      <c r="K29" s="18" t="n"/>
+      <c r="L29" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M29" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N29" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O29" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$N$7,C29:N29,"Y"),"")</f>
         <v/>
       </c>
-      <c r="P29" s="31">
+      <c r="P29" s="26">
         <f>COUNTIF(C29:N29,"Y")</f>
         <v/>
       </c>
-      <c r="Q29" s="32">
+      <c r="Q29" s="27">
         <f>SUMPRODUCT((C$7:$N$7=1)*(C29:N29="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="17" customHeight="1">
-      <c r="A30" s="34" t="n">
+      <c r="A30" s="29" t="n">
         <v>11</v>
       </c>
-      <c r="B30" s="35" t="inlineStr">
+      <c r="B30" s="30" t="inlineStr">
         <is>
           <t>Kable</t>
         </is>
       </c>
-      <c r="C30" s="36" t="n"/>
-      <c r="D30" s="36" t="n"/>
-      <c r="E30" s="36" t="n"/>
-      <c r="F30" s="36" t="n"/>
-      <c r="G30" s="36" t="n"/>
-      <c r="H30" s="36" t="n"/>
-      <c r="I30" s="36" t="n"/>
-      <c r="J30" s="36" t="n"/>
-      <c r="K30" s="36" t="n"/>
-      <c r="L30" s="36" t="n"/>
-      <c r="M30" s="36" t="n"/>
-      <c r="N30" s="36" t="n"/>
-      <c r="O30" s="18">
+      <c r="C30" s="31" t="n"/>
+      <c r="D30" s="31" t="n"/>
+      <c r="E30" s="31" t="n"/>
+      <c r="F30" s="31" t="n"/>
+      <c r="G30" s="31" t="n"/>
+      <c r="H30" s="31" t="n"/>
+      <c r="I30" s="31" t="n"/>
+      <c r="J30" s="31" t="n"/>
+      <c r="K30" s="31" t="n"/>
+      <c r="L30" s="31" t="n"/>
+      <c r="M30" s="31" t="n"/>
+      <c r="N30" s="31" t="n"/>
+      <c r="O30" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$N$7,C30:N30,"Y"),"")</f>
         <v/>
       </c>
-      <c r="P30" s="31">
+      <c r="P30" s="26">
         <f>COUNTIF(C30:N30,"Y")</f>
         <v/>
       </c>
-      <c r="Q30" s="32">
+      <c r="Q30" s="27">
         <f>SUMPRODUCT((C$7:$N$7=1)*(C30:N30="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="17" customHeight="1">
-      <c r="A31" s="37" t="n">
+      <c r="A31" s="32" t="n">
         <v>12</v>
       </c>
-      <c r="B31" s="38" t="inlineStr">
+      <c r="B31" s="33" t="inlineStr">
         <is>
           <t>Kayla</t>
         </is>
       </c>
-      <c r="C31" s="19" t="n"/>
-      <c r="D31" s="19" t="n"/>
-      <c r="E31" s="19" t="n"/>
-      <c r="F31" s="19" t="n"/>
-      <c r="G31" s="19" t="n"/>
-      <c r="H31" s="19" t="n"/>
-      <c r="I31" s="19" t="n"/>
-      <c r="J31" s="19" t="n"/>
-      <c r="K31" s="19" t="n"/>
-      <c r="L31" s="19" t="n"/>
-      <c r="M31" s="19" t="n"/>
-      <c r="N31" s="19" t="n"/>
-      <c r="O31" s="18">
+      <c r="C31" s="18" t="n"/>
+      <c r="D31" s="18" t="n"/>
+      <c r="E31" s="18" t="n"/>
+      <c r="F31" s="18" t="n"/>
+      <c r="G31" s="18" t="n"/>
+      <c r="H31" s="18" t="n"/>
+      <c r="I31" s="18" t="n"/>
+      <c r="J31" s="18" t="n"/>
+      <c r="K31" s="18" t="n"/>
+      <c r="L31" s="18" t="n"/>
+      <c r="M31" s="18" t="n"/>
+      <c r="N31" s="18" t="n"/>
+      <c r="O31" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$N$7,C31:N31,"Y"),"")</f>
         <v/>
       </c>
-      <c r="P31" s="31">
+      <c r="P31" s="26">
         <f>COUNTIF(C31:N31,"Y")</f>
         <v/>
       </c>
-      <c r="Q31" s="32">
+      <c r="Q31" s="27">
         <f>SUMPRODUCT((C$7:$N$7=1)*(C31:N31="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="17" customHeight="1">
-      <c r="A32" s="34" t="n">
+      <c r="A32" s="29" t="n">
         <v>13</v>
       </c>
-      <c r="B32" s="35" t="inlineStr">
+      <c r="B32" s="30" t="inlineStr">
         <is>
           <t>Kenzie</t>
         </is>
       </c>
-      <c r="C32" s="36" t="n"/>
-      <c r="D32" s="36" t="n"/>
-      <c r="E32" s="36" t="n"/>
-      <c r="F32" s="36" t="n"/>
-      <c r="G32" s="36" t="n"/>
-      <c r="H32" s="36" t="n"/>
-      <c r="I32" s="36" t="n"/>
-      <c r="J32" s="36" t="n"/>
-      <c r="K32" s="36" t="n"/>
-      <c r="L32" s="36" t="n"/>
-      <c r="M32" s="36" t="n"/>
-      <c r="N32" s="36" t="n"/>
-      <c r="O32" s="18">
+      <c r="C32" s="31" t="n"/>
+      <c r="D32" s="31" t="n"/>
+      <c r="E32" s="31" t="n"/>
+      <c r="F32" s="31" t="n"/>
+      <c r="G32" s="31" t="n"/>
+      <c r="H32" s="31" t="n"/>
+      <c r="I32" s="31" t="n"/>
+      <c r="J32" s="31" t="n"/>
+      <c r="K32" s="31" t="n"/>
+      <c r="L32" s="31" t="n"/>
+      <c r="M32" s="31" t="n"/>
+      <c r="N32" s="31" t="n"/>
+      <c r="O32" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$N$7,C32:N32,"Y"),"")</f>
         <v/>
       </c>
-      <c r="P32" s="31">
+      <c r="P32" s="26">
         <f>COUNTIF(C32:N32,"Y")</f>
         <v/>
       </c>
-      <c r="Q32" s="32">
+      <c r="Q32" s="27">
         <f>SUMPRODUCT((C$7:$N$7=1)*(C32:N32="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="17" customHeight="1">
-      <c r="A33" s="37" t="n">
+      <c r="A33" s="32" t="n">
         <v>14</v>
       </c>
-      <c r="B33" s="38" t="inlineStr">
+      <c r="B33" s="33" t="inlineStr">
         <is>
           <t>Lidy</t>
         </is>
       </c>
-      <c r="C33" s="19" t="n"/>
-      <c r="D33" s="19" t="n"/>
-      <c r="E33" s="19" t="n"/>
-      <c r="F33" s="19" t="n"/>
-      <c r="G33" s="19" t="n"/>
-      <c r="H33" s="19" t="n"/>
-      <c r="I33" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J33" s="19" t="n"/>
-      <c r="K33" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L33" s="19" t="n"/>
-      <c r="M33" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N33" s="19" t="n"/>
-      <c r="O33" s="18">
+      <c r="C33" s="18" t="n"/>
+      <c r="D33" s="18" t="n"/>
+      <c r="E33" s="18" t="n"/>
+      <c r="F33" s="18" t="n"/>
+      <c r="G33" s="18" t="n"/>
+      <c r="H33" s="18" t="n"/>
+      <c r="I33" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J33" s="18" t="n"/>
+      <c r="K33" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L33" s="18" t="n"/>
+      <c r="M33" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N33" s="18" t="n"/>
+      <c r="O33" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$N$7,C33:N33,"Y"),"")</f>
         <v/>
       </c>
-      <c r="P33" s="31">
+      <c r="P33" s="26">
         <f>COUNTIF(C33:N33,"Y")</f>
         <v/>
       </c>
-      <c r="Q33" s="32">
+      <c r="Q33" s="27">
         <f>SUMPRODUCT((C$7:$N$7=1)*(C33:N33="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="17" customHeight="1">
-      <c r="A34" s="34" t="n">
+      <c r="A34" s="29" t="n">
         <v>15</v>
       </c>
-      <c r="B34" s="35" t="inlineStr">
+      <c r="B34" s="30" t="inlineStr">
         <is>
           <t>Maylin</t>
         </is>
       </c>
-      <c r="C34" s="36" t="n"/>
-      <c r="D34" s="36" t="n"/>
-      <c r="E34" s="36" t="n"/>
-      <c r="F34" s="36" t="n"/>
-      <c r="G34" s="36" t="n"/>
-      <c r="H34" s="36" t="n"/>
-      <c r="I34" s="36" t="n"/>
-      <c r="J34" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K34" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L34" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M34" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N34" s="36" t="n"/>
-      <c r="O34" s="18">
+      <c r="C34" s="31" t="n"/>
+      <c r="D34" s="31" t="n"/>
+      <c r="E34" s="31" t="n"/>
+      <c r="F34" s="31" t="n"/>
+      <c r="G34" s="31" t="n"/>
+      <c r="H34" s="31" t="n"/>
+      <c r="I34" s="31" t="n"/>
+      <c r="J34" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K34" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L34" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M34" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N34" s="31" t="n"/>
+      <c r="O34" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$N$7,C34:N34,"Y"),"")</f>
         <v/>
       </c>
-      <c r="P34" s="31">
+      <c r="P34" s="26">
         <f>COUNTIF(C34:N34,"Y")</f>
         <v/>
       </c>
-      <c r="Q34" s="32">
+      <c r="Q34" s="27">
         <f>SUMPRODUCT((C$7:$N$7=1)*(C34:N34="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="17" customHeight="1">
-      <c r="A35" s="37" t="n">
+      <c r="A35" s="32" t="n">
         <v>16</v>
       </c>
-      <c r="B35" s="38" t="inlineStr">
+      <c r="B35" s="33" t="inlineStr">
         <is>
           <t>Mike</t>
         </is>
       </c>
-      <c r="C35" s="19" t="n"/>
-      <c r="D35" s="19" t="n"/>
-      <c r="E35" s="19" t="n"/>
-      <c r="F35" s="19" t="n"/>
-      <c r="G35" s="19" t="n"/>
-      <c r="H35" s="19" t="n"/>
-      <c r="I35" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J35" s="19" t="n"/>
-      <c r="K35" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L35" s="19" t="n"/>
-      <c r="M35" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N35" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O35" s="18">
+      <c r="C35" s="18" t="n"/>
+      <c r="D35" s="18" t="n"/>
+      <c r="E35" s="18" t="n"/>
+      <c r="F35" s="18" t="n"/>
+      <c r="G35" s="18" t="n"/>
+      <c r="H35" s="18" t="n"/>
+      <c r="I35" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J35" s="18" t="n"/>
+      <c r="K35" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L35" s="18" t="n"/>
+      <c r="M35" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N35" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O35" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$N$7,C35:N35,"Y"),"")</f>
         <v/>
       </c>
-      <c r="P35" s="31">
+      <c r="P35" s="26">
         <f>COUNTIF(C35:N35,"Y")</f>
         <v/>
       </c>
-      <c r="Q35" s="32">
+      <c r="Q35" s="27">
         <f>SUMPRODUCT((C$7:$N$7=1)*(C35:N35="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="17" customHeight="1">
-      <c r="A36" s="34" t="n">
+      <c r="A36" s="29" t="n">
         <v>17</v>
       </c>
-      <c r="B36" s="35" t="inlineStr">
+      <c r="B36" s="30" t="inlineStr">
         <is>
           <t>Richard</t>
         </is>
       </c>
-      <c r="C36" s="36" t="n"/>
-      <c r="D36" s="36" t="n"/>
-      <c r="E36" s="36" t="n"/>
-      <c r="F36" s="36" t="n"/>
-      <c r="G36" s="36" t="n"/>
-      <c r="H36" s="36" t="n"/>
-      <c r="I36" s="36" t="n"/>
-      <c r="J36" s="36" t="n"/>
-      <c r="K36" s="36" t="n"/>
-      <c r="L36" s="36" t="n"/>
-      <c r="M36" s="36" t="n"/>
-      <c r="N36" s="36" t="n"/>
-      <c r="O36" s="18">
+      <c r="C36" s="31" t="n"/>
+      <c r="D36" s="31" t="n"/>
+      <c r="E36" s="31" t="n"/>
+      <c r="F36" s="31" t="n"/>
+      <c r="G36" s="31" t="n"/>
+      <c r="H36" s="31" t="n"/>
+      <c r="I36" s="31" t="n"/>
+      <c r="J36" s="31" t="n"/>
+      <c r="K36" s="31" t="n"/>
+      <c r="L36" s="31" t="n"/>
+      <c r="M36" s="31" t="n"/>
+      <c r="N36" s="31" t="n"/>
+      <c r="O36" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$N$7,C36:N36,"Y"),"")</f>
         <v/>
       </c>
-      <c r="P36" s="31">
+      <c r="P36" s="26">
         <f>COUNTIF(C36:N36,"Y")</f>
         <v/>
       </c>
-      <c r="Q36" s="32">
+      <c r="Q36" s="27">
         <f>SUMPRODUCT((C$7:$N$7=1)*(C36:N36="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="17" customHeight="1">
-      <c r="A37" s="37" t="n">
+      <c r="A37" s="32" t="n">
         <v>18</v>
       </c>
-      <c r="B37" s="38" t="inlineStr">
+      <c r="B37" s="33" t="inlineStr">
         <is>
           <t>Samuel</t>
         </is>
       </c>
-      <c r="C37" s="19" t="n"/>
-      <c r="D37" s="19" t="n"/>
-      <c r="E37" s="19" t="n"/>
-      <c r="F37" s="19" t="n"/>
-      <c r="G37" s="19" t="n"/>
-      <c r="H37" s="19" t="n"/>
-      <c r="I37" s="19" t="n"/>
-      <c r="J37" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K37" s="19" t="n"/>
-      <c r="L37" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M37" s="19" t="n"/>
-      <c r="N37" s="19" t="n"/>
-      <c r="O37" s="18">
+      <c r="C37" s="18" t="n"/>
+      <c r="D37" s="18" t="n"/>
+      <c r="E37" s="18" t="n"/>
+      <c r="F37" s="18" t="n"/>
+      <c r="G37" s="18" t="n"/>
+      <c r="H37" s="18" t="n"/>
+      <c r="I37" s="18" t="n"/>
+      <c r="J37" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K37" s="18" t="n"/>
+      <c r="L37" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M37" s="18" t="n"/>
+      <c r="N37" s="18" t="n"/>
+      <c r="O37" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$N$7,C37:N37,"Y"),"")</f>
         <v/>
       </c>
-      <c r="P37" s="31">
+      <c r="P37" s="26">
         <f>COUNTIF(C37:N37,"Y")</f>
         <v/>
       </c>
-      <c r="Q37" s="32">
+      <c r="Q37" s="27">
         <f>SUMPRODUCT((C$7:$N$7=1)*(C37:N37="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="17" customHeight="1">
-      <c r="A38" s="34" t="n">
+      <c r="A38" s="29" t="n">
         <v>19</v>
       </c>
-      <c r="B38" s="35" t="inlineStr">
+      <c r="B38" s="30" t="inlineStr">
         <is>
           <t>Zach</t>
         </is>
       </c>
-      <c r="C38" s="36" t="n"/>
-      <c r="D38" s="36" t="n"/>
-      <c r="E38" s="36" t="n"/>
-      <c r="F38" s="36" t="n"/>
-      <c r="G38" s="36" t="n"/>
-      <c r="H38" s="36" t="n"/>
-      <c r="I38" s="36" t="n"/>
-      <c r="J38" s="36" t="n"/>
-      <c r="K38" s="36" t="n"/>
-      <c r="L38" s="36" t="n"/>
-      <c r="M38" s="36" t="n"/>
-      <c r="N38" s="36" t="n"/>
-      <c r="O38" s="18">
+      <c r="C38" s="31" t="n"/>
+      <c r="D38" s="31" t="n"/>
+      <c r="E38" s="31" t="n"/>
+      <c r="F38" s="31" t="n"/>
+      <c r="G38" s="31" t="n"/>
+      <c r="H38" s="31" t="n"/>
+      <c r="I38" s="31" t="n"/>
+      <c r="J38" s="31" t="n"/>
+      <c r="K38" s="31" t="n"/>
+      <c r="L38" s="31" t="n"/>
+      <c r="M38" s="31" t="n"/>
+      <c r="N38" s="31" t="n"/>
+      <c r="O38" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$N$7,C38:N38,"Y"),"")</f>
         <v/>
       </c>
-      <c r="P38" s="31">
+      <c r="P38" s="26">
         <f>COUNTIF(C38:N38,"Y")</f>
         <v/>
       </c>
-      <c r="Q38" s="32">
+      <c r="Q38" s="27">
         <f>SUMPRODUCT((C$7:$N$7=1)*(C38:N38="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="3" t="inlineStr"/>
-      <c r="B39" s="39" t="inlineStr">
+      <c r="B39" s="34" t="inlineStr">
         <is>
           <t>Total on shift</t>
         </is>
@@ -3982,13 +3434,13 @@
         <f>SUM(P14:P38)</f>
         <v/>
       </c>
-      <c r="Q39" s="40">
+      <c r="Q39" s="35">
         <f>SUM(Q14:Q38)</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="12" customHeight="1">
-      <c r="A40" s="41" t="inlineStr">
+      <c r="A40" s="36" t="inlineStr">
         <is>
           <t>Y = on shift during shop's meal window. Personal Avg = average score of shops worked. Bonus = $50 per 100% shop worked.</t>
         </is>
@@ -4359,7 +3811,7 @@
       <c r="P7" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="Q7" s="18">
+      <c r="Q7" s="17">
         <f>IFERROR(AVERAGE(C7:P7),"")</f>
         <v/>
       </c>
@@ -4367,1116 +3819,1116 @@
       <c r="S7" s="12" t="inlineStr"/>
     </row>
     <row r="8" ht="13" customHeight="1">
-      <c r="A8" s="19" t="inlineStr"/>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr"/>
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr"/>
-      <c r="D8" s="19" t="inlineStr"/>
-      <c r="E8" s="19" t="inlineStr"/>
-      <c r="F8" s="19" t="inlineStr"/>
-      <c r="G8" s="19" t="inlineStr"/>
-      <c r="H8" s="19" t="inlineStr"/>
-      <c r="I8" s="19" t="inlineStr"/>
-      <c r="J8" s="19" t="inlineStr"/>
-      <c r="K8" s="19" t="inlineStr"/>
-      <c r="L8" s="21" t="n">
+      <c r="C8" s="18" t="inlineStr"/>
+      <c r="D8" s="18" t="inlineStr"/>
+      <c r="E8" s="18" t="inlineStr"/>
+      <c r="F8" s="18" t="inlineStr"/>
+      <c r="G8" s="18" t="inlineStr"/>
+      <c r="H8" s="18" t="inlineStr"/>
+      <c r="I8" s="18" t="inlineStr"/>
+      <c r="J8" s="18" t="inlineStr"/>
+      <c r="K8" s="18" t="inlineStr"/>
+      <c r="L8" s="39" t="n">
         <v>0.72</v>
       </c>
-      <c r="M8" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" s="21" t="n">
+      <c r="M8" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" s="39" t="n">
         <v>0.72</v>
       </c>
-      <c r="O8" s="21" t="n">
+      <c r="O8" s="39" t="n">
         <v>0.77</v>
       </c>
-      <c r="P8" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="23">
+      <c r="P8" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="20">
         <f>IFERROR(AVERAGE(C8:P8),"")</f>
         <v/>
       </c>
-      <c r="R8" s="19" t="inlineStr"/>
-      <c r="S8" s="19" t="inlineStr"/>
+      <c r="R8" s="18" t="inlineStr"/>
+      <c r="S8" s="18" t="inlineStr"/>
     </row>
     <row r="9" ht="13" customHeight="1">
-      <c r="A9" s="19" t="inlineStr"/>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="A9" s="18" t="inlineStr"/>
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>Quality</t>
         </is>
       </c>
-      <c r="C9" s="19" t="inlineStr"/>
-      <c r="D9" s="19" t="inlineStr"/>
-      <c r="E9" s="19" t="inlineStr"/>
-      <c r="F9" s="19" t="inlineStr"/>
-      <c r="G9" s="19" t="inlineStr"/>
-      <c r="H9" s="19" t="inlineStr"/>
-      <c r="I9" s="19" t="inlineStr"/>
-      <c r="J9" s="19" t="inlineStr"/>
-      <c r="K9" s="19" t="inlineStr"/>
-      <c r="L9" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="P9" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="23">
+      <c r="C9" s="18" t="inlineStr"/>
+      <c r="D9" s="18" t="inlineStr"/>
+      <c r="E9" s="18" t="inlineStr"/>
+      <c r="F9" s="18" t="inlineStr"/>
+      <c r="G9" s="18" t="inlineStr"/>
+      <c r="H9" s="18" t="inlineStr"/>
+      <c r="I9" s="18" t="inlineStr"/>
+      <c r="J9" s="18" t="inlineStr"/>
+      <c r="K9" s="18" t="inlineStr"/>
+      <c r="L9" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="20">
         <f>IFERROR(AVERAGE(C9:P9),"")</f>
         <v/>
       </c>
-      <c r="R9" s="19" t="inlineStr"/>
-      <c r="S9" s="19" t="inlineStr"/>
+      <c r="R9" s="18" t="inlineStr"/>
+      <c r="S9" s="18" t="inlineStr"/>
     </row>
     <row r="10" ht="13" customHeight="1">
-      <c r="A10" s="19" t="inlineStr"/>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="A10" s="18" t="inlineStr"/>
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>Cleanliness</t>
         </is>
       </c>
-      <c r="C10" s="19" t="inlineStr"/>
-      <c r="D10" s="19" t="inlineStr"/>
-      <c r="E10" s="19" t="inlineStr"/>
-      <c r="F10" s="19" t="inlineStr"/>
-      <c r="G10" s="19" t="inlineStr"/>
-      <c r="H10" s="19" t="inlineStr"/>
-      <c r="I10" s="19" t="inlineStr"/>
-      <c r="J10" s="19" t="inlineStr"/>
-      <c r="K10" s="19" t="inlineStr"/>
-      <c r="L10" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" s="24" t="n">
+      <c r="C10" s="18" t="inlineStr"/>
+      <c r="D10" s="18" t="inlineStr"/>
+      <c r="E10" s="18" t="inlineStr"/>
+      <c r="F10" s="18" t="inlineStr"/>
+      <c r="G10" s="18" t="inlineStr"/>
+      <c r="H10" s="18" t="inlineStr"/>
+      <c r="I10" s="18" t="inlineStr"/>
+      <c r="J10" s="18" t="inlineStr"/>
+      <c r="K10" s="18" t="inlineStr"/>
+      <c r="L10" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" s="42" t="n">
         <v>0.8</v>
       </c>
-      <c r="N10" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" s="21" t="n">
+      <c r="N10" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" s="39" t="n">
         <v>0.72</v>
       </c>
-      <c r="P10" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="23">
+      <c r="P10" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="20">
         <f>IFERROR(AVERAGE(C10:P10),"")</f>
         <v/>
       </c>
-      <c r="R10" s="19" t="inlineStr"/>
-      <c r="S10" s="19" t="inlineStr"/>
+      <c r="R10" s="18" t="inlineStr"/>
+      <c r="S10" s="18" t="inlineStr"/>
     </row>
     <row r="11" ht="13" customHeight="1">
-      <c r="A11" s="19" t="inlineStr"/>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr"/>
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>Customer Sat</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr"/>
-      <c r="D11" s="19" t="inlineStr"/>
-      <c r="E11" s="19" t="inlineStr"/>
-      <c r="F11" s="19" t="inlineStr"/>
-      <c r="G11" s="19" t="inlineStr"/>
-      <c r="H11" s="19" t="inlineStr"/>
-      <c r="I11" s="19" t="inlineStr"/>
-      <c r="J11" s="19" t="inlineStr"/>
-      <c r="K11" s="19" t="inlineStr"/>
-      <c r="L11" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="P11" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q11" s="23">
+      <c r="C11" s="18" t="inlineStr"/>
+      <c r="D11" s="18" t="inlineStr"/>
+      <c r="E11" s="18" t="inlineStr"/>
+      <c r="F11" s="18" t="inlineStr"/>
+      <c r="G11" s="18" t="inlineStr"/>
+      <c r="H11" s="18" t="inlineStr"/>
+      <c r="I11" s="18" t="inlineStr"/>
+      <c r="J11" s="18" t="inlineStr"/>
+      <c r="K11" s="18" t="inlineStr"/>
+      <c r="L11" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="P11" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="20">
         <f>IFERROR(AVERAGE(C11:P11),"")</f>
         <v/>
       </c>
-      <c r="R11" s="19" t="inlineStr"/>
-      <c r="S11" s="19" t="inlineStr"/>
+      <c r="R11" s="18" t="inlineStr"/>
+      <c r="S11" s="18" t="inlineStr"/>
     </row>
     <row r="12" ht="6" customHeight="1">
-      <c r="A12" s="25" t="n"/>
+      <c r="A12" s="21" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="26" t="inlineStr">
+      <c r="A13" s="22" t="inlineStr">
         <is>
           <t>MANAGERS</t>
         </is>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="B14" s="28" t="inlineStr">
+      <c r="A14" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
         <is>
           <t>Madison C.</t>
         </is>
       </c>
-      <c r="C14" s="29" t="n"/>
-      <c r="D14" s="29" t="n"/>
-      <c r="E14" s="29" t="n"/>
-      <c r="F14" s="29" t="n"/>
-      <c r="G14" s="29" t="n"/>
-      <c r="H14" s="29" t="n"/>
-      <c r="I14" s="29" t="n"/>
-      <c r="J14" s="29" t="n"/>
-      <c r="K14" s="29" t="n"/>
-      <c r="L14" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M14" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N14" s="29" t="n"/>
-      <c r="O14" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="P14" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="Q14" s="18">
+      <c r="C14" s="25" t="n"/>
+      <c r="D14" s="25" t="n"/>
+      <c r="E14" s="25" t="n"/>
+      <c r="F14" s="25" t="n"/>
+      <c r="G14" s="25" t="n"/>
+      <c r="H14" s="25" t="n"/>
+      <c r="I14" s="25" t="n"/>
+      <c r="J14" s="25" t="n"/>
+      <c r="K14" s="25" t="n"/>
+      <c r="L14" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M14" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N14" s="25" t="n"/>
+      <c r="O14" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P14" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q14" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$P$7,C14:P14,"Y"),"")</f>
         <v/>
       </c>
-      <c r="R14" s="31">
+      <c r="R14" s="26">
         <f>COUNTIF(C14:P14,"Y")</f>
         <v/>
       </c>
-      <c r="S14" s="32">
+      <c r="S14" s="27">
         <f>SUMPRODUCT((C$7:$P$7=1)*(C14:P14="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="27" t="n">
+      <c r="A15" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="B15" s="28" t="inlineStr">
+      <c r="B15" s="24" t="inlineStr">
         <is>
           <t>Vicki L.</t>
         </is>
       </c>
-      <c r="C15" s="29" t="n"/>
-      <c r="D15" s="29" t="n"/>
-      <c r="E15" s="29" t="n"/>
-      <c r="F15" s="29" t="n"/>
-      <c r="G15" s="29" t="n"/>
-      <c r="H15" s="29" t="n"/>
-      <c r="I15" s="29" t="n"/>
-      <c r="J15" s="29" t="n"/>
-      <c r="K15" s="29" t="n"/>
-      <c r="L15" s="29" t="n"/>
-      <c r="M15" s="29" t="n"/>
-      <c r="N15" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O15" s="29" t="n"/>
-      <c r="P15" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="Q15" s="18">
+      <c r="C15" s="25" t="n"/>
+      <c r="D15" s="25" t="n"/>
+      <c r="E15" s="25" t="n"/>
+      <c r="F15" s="25" t="n"/>
+      <c r="G15" s="25" t="n"/>
+      <c r="H15" s="25" t="n"/>
+      <c r="I15" s="25" t="n"/>
+      <c r="J15" s="25" t="n"/>
+      <c r="K15" s="25" t="n"/>
+      <c r="L15" s="25" t="n"/>
+      <c r="M15" s="25" t="n"/>
+      <c r="N15" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O15" s="25" t="n"/>
+      <c r="P15" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q15" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$P$7,C15:P15,"Y"),"")</f>
         <v/>
       </c>
-      <c r="R15" s="31">
+      <c r="R15" s="26">
         <f>COUNTIF(C15:P15,"Y")</f>
         <v/>
       </c>
-      <c r="S15" s="32">
+      <c r="S15" s="27">
         <f>SUMPRODUCT((C$7:$P$7=1)*(C15:P15="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
-      <c r="A16" s="27" t="n">
+      <c r="A16" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="B16" s="28" t="inlineStr">
+      <c r="B16" s="24" t="inlineStr">
         <is>
           <t>Kasey W.</t>
         </is>
       </c>
-      <c r="C16" s="29" t="n"/>
-      <c r="D16" s="29" t="n"/>
-      <c r="E16" s="29" t="n"/>
-      <c r="F16" s="29" t="n"/>
-      <c r="G16" s="29" t="n"/>
-      <c r="H16" s="29" t="n"/>
-      <c r="I16" s="29" t="n"/>
-      <c r="J16" s="29" t="n"/>
-      <c r="K16" s="29" t="n"/>
-      <c r="L16" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M16" s="29" t="n"/>
-      <c r="N16" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O16" s="29" t="n"/>
-      <c r="P16" s="29" t="n"/>
-      <c r="Q16" s="18">
+      <c r="C16" s="25" t="n"/>
+      <c r="D16" s="25" t="n"/>
+      <c r="E16" s="25" t="n"/>
+      <c r="F16" s="25" t="n"/>
+      <c r="G16" s="25" t="n"/>
+      <c r="H16" s="25" t="n"/>
+      <c r="I16" s="25" t="n"/>
+      <c r="J16" s="25" t="n"/>
+      <c r="K16" s="25" t="n"/>
+      <c r="L16" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M16" s="25" t="n"/>
+      <c r="N16" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O16" s="25" t="n"/>
+      <c r="P16" s="25" t="n"/>
+      <c r="Q16" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$P$7,C16:P16,"Y"),"")</f>
         <v/>
       </c>
-      <c r="R16" s="31">
+      <c r="R16" s="26">
         <f>COUNTIF(C16:P16,"Y")</f>
         <v/>
       </c>
-      <c r="S16" s="32">
+      <c r="S16" s="27">
         <f>SUMPRODUCT((C$7:$P$7=1)*(C16:P16="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
-      <c r="A17" s="27" t="n">
+      <c r="A17" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="B17" s="28" t="inlineStr">
+      <c r="B17" s="24" t="inlineStr">
         <is>
           <t>Nathan R.</t>
         </is>
       </c>
-      <c r="C17" s="29" t="n"/>
-      <c r="D17" s="29" t="n"/>
-      <c r="E17" s="29" t="n"/>
-      <c r="F17" s="29" t="n"/>
-      <c r="G17" s="29" t="n"/>
-      <c r="H17" s="29" t="n"/>
-      <c r="I17" s="29" t="n"/>
-      <c r="J17" s="29" t="n"/>
-      <c r="K17" s="29" t="n"/>
-      <c r="L17" s="29" t="n"/>
-      <c r="M17" s="29" t="n"/>
-      <c r="N17" s="29" t="n"/>
-      <c r="O17" s="29" t="n"/>
-      <c r="P17" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="Q17" s="18">
+      <c r="C17" s="25" t="n"/>
+      <c r="D17" s="25" t="n"/>
+      <c r="E17" s="25" t="n"/>
+      <c r="F17" s="25" t="n"/>
+      <c r="G17" s="25" t="n"/>
+      <c r="H17" s="25" t="n"/>
+      <c r="I17" s="25" t="n"/>
+      <c r="J17" s="25" t="n"/>
+      <c r="K17" s="25" t="n"/>
+      <c r="L17" s="25" t="n"/>
+      <c r="M17" s="25" t="n"/>
+      <c r="N17" s="25" t="n"/>
+      <c r="O17" s="25" t="n"/>
+      <c r="P17" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q17" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$P$7,C17:P17,"Y"),"")</f>
         <v/>
       </c>
-      <c r="R17" s="31">
+      <c r="R17" s="26">
         <f>COUNTIF(C17:P17,"Y")</f>
         <v/>
       </c>
-      <c r="S17" s="32">
+      <c r="S17" s="27">
         <f>SUMPRODUCT((C$7:$P$7=1)*(C17:P17="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="6" customHeight="1">
-      <c r="A18" s="25" t="n"/>
+      <c r="A18" s="21" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="33" t="inlineStr">
+      <c r="A19" s="28" t="inlineStr">
         <is>
           <t>CREW</t>
         </is>
       </c>
     </row>
     <row r="20" ht="17" customHeight="1">
-      <c r="A20" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="B20" s="35" t="inlineStr">
+      <c r="A20" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
         <is>
           <t>Alen</t>
         </is>
       </c>
-      <c r="C20" s="36" t="n"/>
-      <c r="D20" s="36" t="n"/>
-      <c r="E20" s="36" t="n"/>
-      <c r="F20" s="36" t="n"/>
-      <c r="G20" s="36" t="n"/>
-      <c r="H20" s="36" t="n"/>
-      <c r="I20" s="36" t="n"/>
-      <c r="J20" s="36" t="n"/>
-      <c r="K20" s="36" t="n"/>
-      <c r="L20" s="36" t="n"/>
-      <c r="M20" s="36" t="n"/>
-      <c r="N20" s="36" t="n"/>
-      <c r="O20" s="36" t="n"/>
-      <c r="P20" s="36" t="n"/>
-      <c r="Q20" s="18">
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+      <c r="E20" s="31" t="n"/>
+      <c r="F20" s="31" t="n"/>
+      <c r="G20" s="31" t="n"/>
+      <c r="H20" s="31" t="n"/>
+      <c r="I20" s="31" t="n"/>
+      <c r="J20" s="31" t="n"/>
+      <c r="K20" s="31" t="n"/>
+      <c r="L20" s="31" t="n"/>
+      <c r="M20" s="31" t="n"/>
+      <c r="N20" s="31" t="n"/>
+      <c r="O20" s="31" t="n"/>
+      <c r="P20" s="31" t="n"/>
+      <c r="Q20" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$P$7,C20:P20,"Y"),"")</f>
         <v/>
       </c>
-      <c r="R20" s="31">
+      <c r="R20" s="26">
         <f>COUNTIF(C20:P20,"Y")</f>
         <v/>
       </c>
-      <c r="S20" s="32">
+      <c r="S20" s="27">
         <f>SUMPRODUCT((C$7:$P$7=1)*(C20:P20="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="17" customHeight="1">
-      <c r="A21" s="37" t="n">
+      <c r="A21" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="B21" s="38" t="inlineStr">
+      <c r="B21" s="33" t="inlineStr">
         <is>
           <t>Ash</t>
         </is>
       </c>
-      <c r="C21" s="19" t="n"/>
-      <c r="D21" s="19" t="n"/>
-      <c r="E21" s="19" t="n"/>
-      <c r="F21" s="19" t="n"/>
-      <c r="G21" s="19" t="n"/>
-      <c r="H21" s="19" t="n"/>
-      <c r="I21" s="19" t="n"/>
-      <c r="J21" s="19" t="n"/>
-      <c r="K21" s="19" t="n"/>
-      <c r="L21" s="19" t="n"/>
-      <c r="M21" s="19" t="n"/>
-      <c r="N21" s="19" t="n"/>
-      <c r="O21" s="19" t="n"/>
-      <c r="P21" s="19" t="n"/>
-      <c r="Q21" s="18">
+      <c r="C21" s="18" t="n"/>
+      <c r="D21" s="18" t="n"/>
+      <c r="E21" s="18" t="n"/>
+      <c r="F21" s="18" t="n"/>
+      <c r="G21" s="18" t="n"/>
+      <c r="H21" s="18" t="n"/>
+      <c r="I21" s="18" t="n"/>
+      <c r="J21" s="18" t="n"/>
+      <c r="K21" s="18" t="n"/>
+      <c r="L21" s="18" t="n"/>
+      <c r="M21" s="18" t="n"/>
+      <c r="N21" s="18" t="n"/>
+      <c r="O21" s="18" t="n"/>
+      <c r="P21" s="18" t="n"/>
+      <c r="Q21" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$P$7,C21:P21,"Y"),"")</f>
         <v/>
       </c>
-      <c r="R21" s="31">
+      <c r="R21" s="26">
         <f>COUNTIF(C21:P21,"Y")</f>
         <v/>
       </c>
-      <c r="S21" s="32">
+      <c r="S21" s="27">
         <f>SUMPRODUCT((C$7:$P$7=1)*(C21:P21="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="17" customHeight="1">
-      <c r="A22" s="34" t="n">
+      <c r="A22" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B22" s="35" t="inlineStr">
+      <c r="B22" s="30" t="inlineStr">
         <is>
           <t>Autumn</t>
         </is>
       </c>
-      <c r="C22" s="36" t="n"/>
-      <c r="D22" s="36" t="n"/>
-      <c r="E22" s="36" t="n"/>
-      <c r="F22" s="36" t="n"/>
-      <c r="G22" s="36" t="n"/>
-      <c r="H22" s="36" t="n"/>
-      <c r="I22" s="36" t="n"/>
-      <c r="J22" s="36" t="n"/>
-      <c r="K22" s="36" t="n"/>
-      <c r="L22" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M22" s="36" t="n"/>
-      <c r="N22" s="36" t="n"/>
-      <c r="O22" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="P22" s="36" t="n"/>
-      <c r="Q22" s="18">
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+      <c r="E22" s="31" t="n"/>
+      <c r="F22" s="31" t="n"/>
+      <c r="G22" s="31" t="n"/>
+      <c r="H22" s="31" t="n"/>
+      <c r="I22" s="31" t="n"/>
+      <c r="J22" s="31" t="n"/>
+      <c r="K22" s="31" t="n"/>
+      <c r="L22" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M22" s="31" t="n"/>
+      <c r="N22" s="31" t="n"/>
+      <c r="O22" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P22" s="31" t="n"/>
+      <c r="Q22" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$P$7,C22:P22,"Y"),"")</f>
         <v/>
       </c>
-      <c r="R22" s="31">
+      <c r="R22" s="26">
         <f>COUNTIF(C22:P22,"Y")</f>
         <v/>
       </c>
-      <c r="S22" s="32">
+      <c r="S22" s="27">
         <f>SUMPRODUCT((C$7:$P$7=1)*(C22:P22="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="17" customHeight="1">
-      <c r="A23" s="37" t="n">
+      <c r="A23" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="B23" s="38" t="inlineStr">
+      <c r="B23" s="33" t="inlineStr">
         <is>
           <t>Bri</t>
         </is>
       </c>
-      <c r="C23" s="19" t="n"/>
-      <c r="D23" s="19" t="n"/>
-      <c r="E23" s="19" t="n"/>
-      <c r="F23" s="19" t="n"/>
-      <c r="G23" s="19" t="n"/>
-      <c r="H23" s="19" t="n"/>
-      <c r="I23" s="19" t="n"/>
-      <c r="J23" s="19" t="n"/>
-      <c r="K23" s="19" t="n"/>
-      <c r="L23" s="19" t="n"/>
-      <c r="M23" s="19" t="n"/>
-      <c r="N23" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O23" s="19" t="n"/>
-      <c r="P23" s="19" t="n"/>
-      <c r="Q23" s="18">
+      <c r="C23" s="18" t="n"/>
+      <c r="D23" s="18" t="n"/>
+      <c r="E23" s="18" t="n"/>
+      <c r="F23" s="18" t="n"/>
+      <c r="G23" s="18" t="n"/>
+      <c r="H23" s="18" t="n"/>
+      <c r="I23" s="18" t="n"/>
+      <c r="J23" s="18" t="n"/>
+      <c r="K23" s="18" t="n"/>
+      <c r="L23" s="18" t="n"/>
+      <c r="M23" s="18" t="n"/>
+      <c r="N23" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O23" s="18" t="n"/>
+      <c r="P23" s="18" t="n"/>
+      <c r="Q23" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$P$7,C23:P23,"Y"),"")</f>
         <v/>
       </c>
-      <c r="R23" s="31">
+      <c r="R23" s="26">
         <f>COUNTIF(C23:P23,"Y")</f>
         <v/>
       </c>
-      <c r="S23" s="32">
+      <c r="S23" s="27">
         <f>SUMPRODUCT((C$7:$P$7=1)*(C23:P23="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="17" customHeight="1">
-      <c r="A24" s="34" t="n">
+      <c r="A24" s="29" t="n">
         <v>5</v>
       </c>
-      <c r="B24" s="35" t="inlineStr">
+      <c r="B24" s="30" t="inlineStr">
         <is>
           <t>Dakayla</t>
         </is>
       </c>
-      <c r="C24" s="36" t="n"/>
-      <c r="D24" s="36" t="n"/>
-      <c r="E24" s="36" t="n"/>
-      <c r="F24" s="36" t="n"/>
-      <c r="G24" s="36" t="n"/>
-      <c r="H24" s="36" t="n"/>
-      <c r="I24" s="36" t="n"/>
-      <c r="J24" s="36" t="n"/>
-      <c r="K24" s="36" t="n"/>
-      <c r="L24" s="36" t="n"/>
-      <c r="M24" s="36" t="n"/>
-      <c r="N24" s="36" t="n"/>
-      <c r="O24" s="36" t="n"/>
-      <c r="P24" s="36" t="n"/>
-      <c r="Q24" s="18">
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+      <c r="E24" s="31" t="n"/>
+      <c r="F24" s="31" t="n"/>
+      <c r="G24" s="31" t="n"/>
+      <c r="H24" s="31" t="n"/>
+      <c r="I24" s="31" t="n"/>
+      <c r="J24" s="31" t="n"/>
+      <c r="K24" s="31" t="n"/>
+      <c r="L24" s="31" t="n"/>
+      <c r="M24" s="31" t="n"/>
+      <c r="N24" s="31" t="n"/>
+      <c r="O24" s="31" t="n"/>
+      <c r="P24" s="31" t="n"/>
+      <c r="Q24" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$P$7,C24:P24,"Y"),"")</f>
         <v/>
       </c>
-      <c r="R24" s="31">
+      <c r="R24" s="26">
         <f>COUNTIF(C24:P24,"Y")</f>
         <v/>
       </c>
-      <c r="S24" s="32">
+      <c r="S24" s="27">
         <f>SUMPRODUCT((C$7:$P$7=1)*(C24:P24="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="17" customHeight="1">
-      <c r="A25" s="37" t="n">
+      <c r="A25" s="32" t="n">
         <v>6</v>
       </c>
-      <c r="B25" s="38" t="inlineStr">
+      <c r="B25" s="33" t="inlineStr">
         <is>
           <t>Divan</t>
         </is>
       </c>
-      <c r="C25" s="19" t="n"/>
-      <c r="D25" s="19" t="n"/>
-      <c r="E25" s="19" t="n"/>
-      <c r="F25" s="19" t="n"/>
-      <c r="G25" s="19" t="n"/>
-      <c r="H25" s="19" t="n"/>
-      <c r="I25" s="19" t="n"/>
-      <c r="J25" s="19" t="n"/>
-      <c r="K25" s="19" t="n"/>
-      <c r="L25" s="19" t="n"/>
-      <c r="M25" s="19" t="n"/>
-      <c r="N25" s="19" t="n"/>
-      <c r="O25" s="19" t="n"/>
-      <c r="P25" s="19" t="n"/>
-      <c r="Q25" s="18">
+      <c r="C25" s="18" t="n"/>
+      <c r="D25" s="18" t="n"/>
+      <c r="E25" s="18" t="n"/>
+      <c r="F25" s="18" t="n"/>
+      <c r="G25" s="18" t="n"/>
+      <c r="H25" s="18" t="n"/>
+      <c r="I25" s="18" t="n"/>
+      <c r="J25" s="18" t="n"/>
+      <c r="K25" s="18" t="n"/>
+      <c r="L25" s="18" t="n"/>
+      <c r="M25" s="18" t="n"/>
+      <c r="N25" s="18" t="n"/>
+      <c r="O25" s="18" t="n"/>
+      <c r="P25" s="18" t="n"/>
+      <c r="Q25" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$P$7,C25:P25,"Y"),"")</f>
         <v/>
       </c>
-      <c r="R25" s="31">
+      <c r="R25" s="26">
         <f>COUNTIF(C25:P25,"Y")</f>
         <v/>
       </c>
-      <c r="S25" s="32">
+      <c r="S25" s="27">
         <f>SUMPRODUCT((C$7:$P$7=1)*(C25:P25="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="17" customHeight="1">
-      <c r="A26" s="34" t="n">
+      <c r="A26" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="B26" s="35" t="inlineStr">
+      <c r="B26" s="30" t="inlineStr">
         <is>
           <t>Francisco</t>
         </is>
       </c>
-      <c r="C26" s="36" t="n"/>
-      <c r="D26" s="36" t="n"/>
-      <c r="E26" s="36" t="n"/>
-      <c r="F26" s="36" t="n"/>
-      <c r="G26" s="36" t="n"/>
-      <c r="H26" s="36" t="n"/>
-      <c r="I26" s="36" t="n"/>
-      <c r="J26" s="36" t="n"/>
-      <c r="K26" s="36" t="n"/>
-      <c r="L26" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M26" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N26" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O26" s="36" t="n"/>
-      <c r="P26" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="Q26" s="18">
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+      <c r="E26" s="31" t="n"/>
+      <c r="F26" s="31" t="n"/>
+      <c r="G26" s="31" t="n"/>
+      <c r="H26" s="31" t="n"/>
+      <c r="I26" s="31" t="n"/>
+      <c r="J26" s="31" t="n"/>
+      <c r="K26" s="31" t="n"/>
+      <c r="L26" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M26" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N26" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O26" s="31" t="n"/>
+      <c r="P26" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q26" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$P$7,C26:P26,"Y"),"")</f>
         <v/>
       </c>
-      <c r="R26" s="31">
+      <c r="R26" s="26">
         <f>COUNTIF(C26:P26,"Y")</f>
         <v/>
       </c>
-      <c r="S26" s="32">
+      <c r="S26" s="27">
         <f>SUMPRODUCT((C$7:$P$7=1)*(C26:P26="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="17" customHeight="1">
-      <c r="A27" s="37" t="n">
+      <c r="A27" s="32" t="n">
         <v>8</v>
       </c>
-      <c r="B27" s="38" t="inlineStr">
+      <c r="B27" s="33" t="inlineStr">
         <is>
           <t>Grace</t>
         </is>
       </c>
-      <c r="C27" s="19" t="n"/>
-      <c r="D27" s="19" t="n"/>
-      <c r="E27" s="19" t="n"/>
-      <c r="F27" s="19" t="n"/>
-      <c r="G27" s="19" t="n"/>
-      <c r="H27" s="19" t="n"/>
-      <c r="I27" s="19" t="n"/>
-      <c r="J27" s="19" t="n"/>
-      <c r="K27" s="19" t="n"/>
-      <c r="L27" s="19" t="n"/>
-      <c r="M27" s="19" t="n"/>
-      <c r="N27" s="19" t="n"/>
-      <c r="O27" s="19" t="n"/>
-      <c r="P27" s="19" t="n"/>
-      <c r="Q27" s="18">
+      <c r="C27" s="18" t="n"/>
+      <c r="D27" s="18" t="n"/>
+      <c r="E27" s="18" t="n"/>
+      <c r="F27" s="18" t="n"/>
+      <c r="G27" s="18" t="n"/>
+      <c r="H27" s="18" t="n"/>
+      <c r="I27" s="18" t="n"/>
+      <c r="J27" s="18" t="n"/>
+      <c r="K27" s="18" t="n"/>
+      <c r="L27" s="18" t="n"/>
+      <c r="M27" s="18" t="n"/>
+      <c r="N27" s="18" t="n"/>
+      <c r="O27" s="18" t="n"/>
+      <c r="P27" s="18" t="n"/>
+      <c r="Q27" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$P$7,C27:P27,"Y"),"")</f>
         <v/>
       </c>
-      <c r="R27" s="31">
+      <c r="R27" s="26">
         <f>COUNTIF(C27:P27,"Y")</f>
         <v/>
       </c>
-      <c r="S27" s="32">
+      <c r="S27" s="27">
         <f>SUMPRODUCT((C$7:$P$7=1)*(C27:P27="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="17" customHeight="1">
-      <c r="A28" s="34" t="n">
+      <c r="A28" s="29" t="n">
         <v>9</v>
       </c>
-      <c r="B28" s="35" t="inlineStr">
+      <c r="B28" s="30" t="inlineStr">
         <is>
           <t>Jada</t>
         </is>
       </c>
-      <c r="C28" s="36" t="n"/>
-      <c r="D28" s="36" t="n"/>
-      <c r="E28" s="36" t="n"/>
-      <c r="F28" s="36" t="n"/>
-      <c r="G28" s="36" t="n"/>
-      <c r="H28" s="36" t="n"/>
-      <c r="I28" s="36" t="n"/>
-      <c r="J28" s="36" t="n"/>
-      <c r="K28" s="36" t="n"/>
-      <c r="L28" s="36" t="n"/>
-      <c r="M28" s="36" t="n"/>
-      <c r="N28" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O28" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="P28" s="36" t="n"/>
-      <c r="Q28" s="18">
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+      <c r="E28" s="31" t="n"/>
+      <c r="F28" s="31" t="n"/>
+      <c r="G28" s="31" t="n"/>
+      <c r="H28" s="31" t="n"/>
+      <c r="I28" s="31" t="n"/>
+      <c r="J28" s="31" t="n"/>
+      <c r="K28" s="31" t="n"/>
+      <c r="L28" s="31" t="n"/>
+      <c r="M28" s="31" t="n"/>
+      <c r="N28" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O28" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P28" s="31" t="n"/>
+      <c r="Q28" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$P$7,C28:P28,"Y"),"")</f>
         <v/>
       </c>
-      <c r="R28" s="31">
+      <c r="R28" s="26">
         <f>COUNTIF(C28:P28,"Y")</f>
         <v/>
       </c>
-      <c r="S28" s="32">
+      <c r="S28" s="27">
         <f>SUMPRODUCT((C$7:$P$7=1)*(C28:P28="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="17" customHeight="1">
-      <c r="A29" s="37" t="n">
+      <c r="A29" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="B29" s="38" t="inlineStr">
+      <c r="B29" s="33" t="inlineStr">
         <is>
           <t>Jeremiah</t>
         </is>
       </c>
-      <c r="C29" s="19" t="n"/>
-      <c r="D29" s="19" t="n"/>
-      <c r="E29" s="19" t="n"/>
-      <c r="F29" s="19" t="n"/>
-      <c r="G29" s="19" t="n"/>
-      <c r="H29" s="19" t="n"/>
-      <c r="I29" s="19" t="n"/>
-      <c r="J29" s="19" t="n"/>
-      <c r="K29" s="19" t="n"/>
-      <c r="L29" s="19" t="n"/>
-      <c r="M29" s="19" t="n"/>
-      <c r="N29" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O29" s="19" t="n"/>
-      <c r="P29" s="19" t="n"/>
-      <c r="Q29" s="18">
+      <c r="C29" s="18" t="n"/>
+      <c r="D29" s="18" t="n"/>
+      <c r="E29" s="18" t="n"/>
+      <c r="F29" s="18" t="n"/>
+      <c r="G29" s="18" t="n"/>
+      <c r="H29" s="18" t="n"/>
+      <c r="I29" s="18" t="n"/>
+      <c r="J29" s="18" t="n"/>
+      <c r="K29" s="18" t="n"/>
+      <c r="L29" s="18" t="n"/>
+      <c r="M29" s="18" t="n"/>
+      <c r="N29" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O29" s="18" t="n"/>
+      <c r="P29" s="18" t="n"/>
+      <c r="Q29" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$P$7,C29:P29,"Y"),"")</f>
         <v/>
       </c>
-      <c r="R29" s="31">
+      <c r="R29" s="26">
         <f>COUNTIF(C29:P29,"Y")</f>
         <v/>
       </c>
-      <c r="S29" s="32">
+      <c r="S29" s="27">
         <f>SUMPRODUCT((C$7:$P$7=1)*(C29:P29="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="17" customHeight="1">
-      <c r="A30" s="34" t="n">
+      <c r="A30" s="29" t="n">
         <v>11</v>
       </c>
-      <c r="B30" s="35" t="inlineStr">
+      <c r="B30" s="30" t="inlineStr">
         <is>
           <t>Kable</t>
         </is>
       </c>
-      <c r="C30" s="36" t="n"/>
-      <c r="D30" s="36" t="n"/>
-      <c r="E30" s="36" t="n"/>
-      <c r="F30" s="36" t="n"/>
-      <c r="G30" s="36" t="n"/>
-      <c r="H30" s="36" t="n"/>
-      <c r="I30" s="36" t="n"/>
-      <c r="J30" s="36" t="n"/>
-      <c r="K30" s="36" t="n"/>
-      <c r="L30" s="36" t="n"/>
-      <c r="M30" s="36" t="n"/>
-      <c r="N30" s="36" t="n"/>
-      <c r="O30" s="36" t="n"/>
-      <c r="P30" s="36" t="n"/>
-      <c r="Q30" s="18">
+      <c r="C30" s="31" t="n"/>
+      <c r="D30" s="31" t="n"/>
+      <c r="E30" s="31" t="n"/>
+      <c r="F30" s="31" t="n"/>
+      <c r="G30" s="31" t="n"/>
+      <c r="H30" s="31" t="n"/>
+      <c r="I30" s="31" t="n"/>
+      <c r="J30" s="31" t="n"/>
+      <c r="K30" s="31" t="n"/>
+      <c r="L30" s="31" t="n"/>
+      <c r="M30" s="31" t="n"/>
+      <c r="N30" s="31" t="n"/>
+      <c r="O30" s="31" t="n"/>
+      <c r="P30" s="31" t="n"/>
+      <c r="Q30" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$P$7,C30:P30,"Y"),"")</f>
         <v/>
       </c>
-      <c r="R30" s="31">
+      <c r="R30" s="26">
         <f>COUNTIF(C30:P30,"Y")</f>
         <v/>
       </c>
-      <c r="S30" s="32">
+      <c r="S30" s="27">
         <f>SUMPRODUCT((C$7:$P$7=1)*(C30:P30="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="17" customHeight="1">
-      <c r="A31" s="37" t="n">
+      <c r="A31" s="32" t="n">
         <v>12</v>
       </c>
-      <c r="B31" s="38" t="inlineStr">
+      <c r="B31" s="33" t="inlineStr">
         <is>
           <t>Kayla</t>
         </is>
       </c>
-      <c r="C31" s="19" t="n"/>
-      <c r="D31" s="19" t="n"/>
-      <c r="E31" s="19" t="n"/>
-      <c r="F31" s="19" t="n"/>
-      <c r="G31" s="19" t="n"/>
-      <c r="H31" s="19" t="n"/>
-      <c r="I31" s="19" t="n"/>
-      <c r="J31" s="19" t="n"/>
-      <c r="K31" s="19" t="n"/>
-      <c r="L31" s="19" t="n"/>
-      <c r="M31" s="19" t="n"/>
-      <c r="N31" s="19" t="n"/>
-      <c r="O31" s="19" t="n"/>
-      <c r="P31" s="19" t="n"/>
-      <c r="Q31" s="18">
+      <c r="C31" s="18" t="n"/>
+      <c r="D31" s="18" t="n"/>
+      <c r="E31" s="18" t="n"/>
+      <c r="F31" s="18" t="n"/>
+      <c r="G31" s="18" t="n"/>
+      <c r="H31" s="18" t="n"/>
+      <c r="I31" s="18" t="n"/>
+      <c r="J31" s="18" t="n"/>
+      <c r="K31" s="18" t="n"/>
+      <c r="L31" s="18" t="n"/>
+      <c r="M31" s="18" t="n"/>
+      <c r="N31" s="18" t="n"/>
+      <c r="O31" s="18" t="n"/>
+      <c r="P31" s="18" t="n"/>
+      <c r="Q31" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$P$7,C31:P31,"Y"),"")</f>
         <v/>
       </c>
-      <c r="R31" s="31">
+      <c r="R31" s="26">
         <f>COUNTIF(C31:P31,"Y")</f>
         <v/>
       </c>
-      <c r="S31" s="32">
+      <c r="S31" s="27">
         <f>SUMPRODUCT((C$7:$P$7=1)*(C31:P31="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="17" customHeight="1">
-      <c r="A32" s="34" t="n">
+      <c r="A32" s="29" t="n">
         <v>13</v>
       </c>
-      <c r="B32" s="35" t="inlineStr">
+      <c r="B32" s="30" t="inlineStr">
         <is>
           <t>Kenzie</t>
         </is>
       </c>
-      <c r="C32" s="36" t="n"/>
-      <c r="D32" s="36" t="n"/>
-      <c r="E32" s="36" t="n"/>
-      <c r="F32" s="36" t="n"/>
-      <c r="G32" s="36" t="n"/>
-      <c r="H32" s="36" t="n"/>
-      <c r="I32" s="36" t="n"/>
-      <c r="J32" s="36" t="n"/>
-      <c r="K32" s="36" t="n"/>
-      <c r="L32" s="36" t="n"/>
-      <c r="M32" s="36" t="n"/>
-      <c r="N32" s="36" t="n"/>
-      <c r="O32" s="36" t="n"/>
-      <c r="P32" s="36" t="n"/>
-      <c r="Q32" s="18">
+      <c r="C32" s="31" t="n"/>
+      <c r="D32" s="31" t="n"/>
+      <c r="E32" s="31" t="n"/>
+      <c r="F32" s="31" t="n"/>
+      <c r="G32" s="31" t="n"/>
+      <c r="H32" s="31" t="n"/>
+      <c r="I32" s="31" t="n"/>
+      <c r="J32" s="31" t="n"/>
+      <c r="K32" s="31" t="n"/>
+      <c r="L32" s="31" t="n"/>
+      <c r="M32" s="31" t="n"/>
+      <c r="N32" s="31" t="n"/>
+      <c r="O32" s="31" t="n"/>
+      <c r="P32" s="31" t="n"/>
+      <c r="Q32" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$P$7,C32:P32,"Y"),"")</f>
         <v/>
       </c>
-      <c r="R32" s="31">
+      <c r="R32" s="26">
         <f>COUNTIF(C32:P32,"Y")</f>
         <v/>
       </c>
-      <c r="S32" s="32">
+      <c r="S32" s="27">
         <f>SUMPRODUCT((C$7:$P$7=1)*(C32:P32="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="17" customHeight="1">
-      <c r="A33" s="37" t="n">
+      <c r="A33" s="32" t="n">
         <v>14</v>
       </c>
-      <c r="B33" s="38" t="inlineStr">
+      <c r="B33" s="33" t="inlineStr">
         <is>
           <t>Lidy</t>
         </is>
       </c>
-      <c r="C33" s="19" t="n"/>
-      <c r="D33" s="19" t="n"/>
-      <c r="E33" s="19" t="n"/>
-      <c r="F33" s="19" t="n"/>
-      <c r="G33" s="19" t="n"/>
-      <c r="H33" s="19" t="n"/>
-      <c r="I33" s="19" t="n"/>
-      <c r="J33" s="19" t="n"/>
-      <c r="K33" s="19" t="n"/>
-      <c r="L33" s="19" t="n"/>
-      <c r="M33" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N33" s="19" t="n"/>
-      <c r="O33" s="19" t="n"/>
-      <c r="P33" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="Q33" s="18">
+      <c r="C33" s="18" t="n"/>
+      <c r="D33" s="18" t="n"/>
+      <c r="E33" s="18" t="n"/>
+      <c r="F33" s="18" t="n"/>
+      <c r="G33" s="18" t="n"/>
+      <c r="H33" s="18" t="n"/>
+      <c r="I33" s="18" t="n"/>
+      <c r="J33" s="18" t="n"/>
+      <c r="K33" s="18" t="n"/>
+      <c r="L33" s="18" t="n"/>
+      <c r="M33" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N33" s="18" t="n"/>
+      <c r="O33" s="18" t="n"/>
+      <c r="P33" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q33" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$P$7,C33:P33,"Y"),"")</f>
         <v/>
       </c>
-      <c r="R33" s="31">
+      <c r="R33" s="26">
         <f>COUNTIF(C33:P33,"Y")</f>
         <v/>
       </c>
-      <c r="S33" s="32">
+      <c r="S33" s="27">
         <f>SUMPRODUCT((C$7:$P$7=1)*(C33:P33="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="17" customHeight="1">
-      <c r="A34" s="34" t="n">
+      <c r="A34" s="29" t="n">
         <v>15</v>
       </c>
-      <c r="B34" s="35" t="inlineStr">
+      <c r="B34" s="30" t="inlineStr">
         <is>
           <t>Maylin</t>
         </is>
       </c>
-      <c r="C34" s="36" t="n"/>
-      <c r="D34" s="36" t="n"/>
-      <c r="E34" s="36" t="n"/>
-      <c r="F34" s="36" t="n"/>
-      <c r="G34" s="36" t="n"/>
-      <c r="H34" s="36" t="n"/>
-      <c r="I34" s="36" t="n"/>
-      <c r="J34" s="36" t="n"/>
-      <c r="K34" s="36" t="n"/>
-      <c r="L34" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M34" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N34" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O34" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="P34" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="Q34" s="18">
+      <c r="C34" s="31" t="n"/>
+      <c r="D34" s="31" t="n"/>
+      <c r="E34" s="31" t="n"/>
+      <c r="F34" s="31" t="n"/>
+      <c r="G34" s="31" t="n"/>
+      <c r="H34" s="31" t="n"/>
+      <c r="I34" s="31" t="n"/>
+      <c r="J34" s="31" t="n"/>
+      <c r="K34" s="31" t="n"/>
+      <c r="L34" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M34" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N34" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O34" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P34" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q34" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$P$7,C34:P34,"Y"),"")</f>
         <v/>
       </c>
-      <c r="R34" s="31">
+      <c r="R34" s="26">
         <f>COUNTIF(C34:P34,"Y")</f>
         <v/>
       </c>
-      <c r="S34" s="32">
+      <c r="S34" s="27">
         <f>SUMPRODUCT((C$7:$P$7=1)*(C34:P34="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="17" customHeight="1">
-      <c r="A35" s="37" t="n">
+      <c r="A35" s="32" t="n">
         <v>16</v>
       </c>
-      <c r="B35" s="38" t="inlineStr">
+      <c r="B35" s="33" t="inlineStr">
         <is>
           <t>Mike</t>
         </is>
       </c>
-      <c r="C35" s="19" t="n"/>
-      <c r="D35" s="19" t="n"/>
-      <c r="E35" s="19" t="n"/>
-      <c r="F35" s="19" t="n"/>
-      <c r="G35" s="19" t="n"/>
-      <c r="H35" s="19" t="n"/>
-      <c r="I35" s="19" t="n"/>
-      <c r="J35" s="19" t="n"/>
-      <c r="K35" s="19" t="n"/>
-      <c r="L35" s="19" t="n"/>
-      <c r="M35" s="19" t="n"/>
-      <c r="N35" s="19" t="n"/>
-      <c r="O35" s="19" t="n"/>
-      <c r="P35" s="19" t="n"/>
-      <c r="Q35" s="18">
+      <c r="C35" s="18" t="n"/>
+      <c r="D35" s="18" t="n"/>
+      <c r="E35" s="18" t="n"/>
+      <c r="F35" s="18" t="n"/>
+      <c r="G35" s="18" t="n"/>
+      <c r="H35" s="18" t="n"/>
+      <c r="I35" s="18" t="n"/>
+      <c r="J35" s="18" t="n"/>
+      <c r="K35" s="18" t="n"/>
+      <c r="L35" s="18" t="n"/>
+      <c r="M35" s="18" t="n"/>
+      <c r="N35" s="18" t="n"/>
+      <c r="O35" s="18" t="n"/>
+      <c r="P35" s="18" t="n"/>
+      <c r="Q35" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$P$7,C35:P35,"Y"),"")</f>
         <v/>
       </c>
-      <c r="R35" s="31">
+      <c r="R35" s="26">
         <f>COUNTIF(C35:P35,"Y")</f>
         <v/>
       </c>
-      <c r="S35" s="32">
+      <c r="S35" s="27">
         <f>SUMPRODUCT((C$7:$P$7=1)*(C35:P35="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="17" customHeight="1">
-      <c r="A36" s="34" t="n">
+      <c r="A36" s="29" t="n">
         <v>17</v>
       </c>
-      <c r="B36" s="35" t="inlineStr">
+      <c r="B36" s="30" t="inlineStr">
         <is>
           <t>Richard</t>
         </is>
       </c>
-      <c r="C36" s="36" t="n"/>
-      <c r="D36" s="36" t="n"/>
-      <c r="E36" s="36" t="n"/>
-      <c r="F36" s="36" t="n"/>
-      <c r="G36" s="36" t="n"/>
-      <c r="H36" s="36" t="n"/>
-      <c r="I36" s="36" t="n"/>
-      <c r="J36" s="36" t="n"/>
-      <c r="K36" s="36" t="n"/>
-      <c r="L36" s="36" t="n"/>
-      <c r="M36" s="36" t="n"/>
-      <c r="N36" s="36" t="n"/>
-      <c r="O36" s="36" t="n"/>
-      <c r="P36" s="36" t="n"/>
-      <c r="Q36" s="18">
+      <c r="C36" s="31" t="n"/>
+      <c r="D36" s="31" t="n"/>
+      <c r="E36" s="31" t="n"/>
+      <c r="F36" s="31" t="n"/>
+      <c r="G36" s="31" t="n"/>
+      <c r="H36" s="31" t="n"/>
+      <c r="I36" s="31" t="n"/>
+      <c r="J36" s="31" t="n"/>
+      <c r="K36" s="31" t="n"/>
+      <c r="L36" s="31" t="n"/>
+      <c r="M36" s="31" t="n"/>
+      <c r="N36" s="31" t="n"/>
+      <c r="O36" s="31" t="n"/>
+      <c r="P36" s="31" t="n"/>
+      <c r="Q36" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$P$7,C36:P36,"Y"),"")</f>
         <v/>
       </c>
-      <c r="R36" s="31">
+      <c r="R36" s="26">
         <f>COUNTIF(C36:P36,"Y")</f>
         <v/>
       </c>
-      <c r="S36" s="32">
+      <c r="S36" s="27">
         <f>SUMPRODUCT((C$7:$P$7=1)*(C36:P36="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="17" customHeight="1">
-      <c r="A37" s="37" t="n">
+      <c r="A37" s="32" t="n">
         <v>18</v>
       </c>
-      <c r="B37" s="38" t="inlineStr">
+      <c r="B37" s="33" t="inlineStr">
         <is>
           <t>Samuel</t>
         </is>
       </c>
-      <c r="C37" s="19" t="n"/>
-      <c r="D37" s="19" t="n"/>
-      <c r="E37" s="19" t="n"/>
-      <c r="F37" s="19" t="n"/>
-      <c r="G37" s="19" t="n"/>
-      <c r="H37" s="19" t="n"/>
-      <c r="I37" s="19" t="n"/>
-      <c r="J37" s="19" t="n"/>
-      <c r="K37" s="19" t="n"/>
-      <c r="L37" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M37" s="19" t="n"/>
-      <c r="N37" s="19" t="n"/>
-      <c r="O37" s="19" t="n"/>
-      <c r="P37" s="19" t="n"/>
-      <c r="Q37" s="18">
+      <c r="C37" s="18" t="n"/>
+      <c r="D37" s="18" t="n"/>
+      <c r="E37" s="18" t="n"/>
+      <c r="F37" s="18" t="n"/>
+      <c r="G37" s="18" t="n"/>
+      <c r="H37" s="18" t="n"/>
+      <c r="I37" s="18" t="n"/>
+      <c r="J37" s="18" t="n"/>
+      <c r="K37" s="18" t="n"/>
+      <c r="L37" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M37" s="18" t="n"/>
+      <c r="N37" s="18" t="n"/>
+      <c r="O37" s="18" t="n"/>
+      <c r="P37" s="18" t="n"/>
+      <c r="Q37" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$P$7,C37:P37,"Y"),"")</f>
         <v/>
       </c>
-      <c r="R37" s="31">
+      <c r="R37" s="26">
         <f>COUNTIF(C37:P37,"Y")</f>
         <v/>
       </c>
-      <c r="S37" s="32">
+      <c r="S37" s="27">
         <f>SUMPRODUCT((C$7:$P$7=1)*(C37:P37="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="17" customHeight="1">
-      <c r="A38" s="34" t="n">
+      <c r="A38" s="29" t="n">
         <v>19</v>
       </c>
-      <c r="B38" s="35" t="inlineStr">
+      <c r="B38" s="30" t="inlineStr">
         <is>
           <t>Zach</t>
         </is>
       </c>
-      <c r="C38" s="36" t="n"/>
-      <c r="D38" s="36" t="n"/>
-      <c r="E38" s="36" t="n"/>
-      <c r="F38" s="36" t="n"/>
-      <c r="G38" s="36" t="n"/>
-      <c r="H38" s="36" t="n"/>
-      <c r="I38" s="36" t="n"/>
-      <c r="J38" s="36" t="n"/>
-      <c r="K38" s="36" t="n"/>
-      <c r="L38" s="36" t="n"/>
-      <c r="M38" s="36" t="n"/>
-      <c r="N38" s="36" t="n"/>
-      <c r="O38" s="36" t="n"/>
-      <c r="P38" s="36" t="n"/>
-      <c r="Q38" s="18">
+      <c r="C38" s="31" t="n"/>
+      <c r="D38" s="31" t="n"/>
+      <c r="E38" s="31" t="n"/>
+      <c r="F38" s="31" t="n"/>
+      <c r="G38" s="31" t="n"/>
+      <c r="H38" s="31" t="n"/>
+      <c r="I38" s="31" t="n"/>
+      <c r="J38" s="31" t="n"/>
+      <c r="K38" s="31" t="n"/>
+      <c r="L38" s="31" t="n"/>
+      <c r="M38" s="31" t="n"/>
+      <c r="N38" s="31" t="n"/>
+      <c r="O38" s="31" t="n"/>
+      <c r="P38" s="31" t="n"/>
+      <c r="Q38" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$P$7,C38:P38,"Y"),"")</f>
         <v/>
       </c>
-      <c r="R38" s="31">
+      <c r="R38" s="26">
         <f>COUNTIF(C38:P38,"Y")</f>
         <v/>
       </c>
-      <c r="S38" s="32">
+      <c r="S38" s="27">
         <f>SUMPRODUCT((C$7:$P$7=1)*(C38:P38="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="3" t="inlineStr"/>
-      <c r="B39" s="39" t="inlineStr">
+      <c r="B39" s="34" t="inlineStr">
         <is>
           <t>Total on shift</t>
         </is>
@@ -5542,13 +4994,13 @@
         <f>SUM(R14:R38)</f>
         <v/>
       </c>
-      <c r="S39" s="40">
+      <c r="S39" s="35">
         <f>SUM(S14:S38)</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="12" customHeight="1">
-      <c r="A40" s="41" t="inlineStr">
+      <c r="A40" s="36" t="inlineStr">
         <is>
           <t>Y = on shift during shop's meal window. Personal Avg = average score of shops worked. Bonus = $50 per 100% shop worked.</t>
         </is>
@@ -5882,13 +5334,13 @@
       <c r="I7" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="J7" s="17" t="n">
+      <c r="J7" s="37" t="n">
         <v>0.97</v>
       </c>
       <c r="K7" s="15" t="n">
         <v>0.87</v>
       </c>
-      <c r="L7" s="17" t="n">
+      <c r="L7" s="37" t="n">
         <v>0.95</v>
       </c>
       <c r="M7" s="16" t="n">
@@ -5900,7 +5352,7 @@
       <c r="O7" s="15" t="n">
         <v>0.87</v>
       </c>
-      <c r="P7" s="18">
+      <c r="P7" s="17">
         <f>IFERROR(AVERAGE(C7:O7),"")</f>
         <v/>
       </c>
@@ -5908,1101 +5360,1101 @@
       <c r="R7" s="12" t="inlineStr"/>
     </row>
     <row r="8" ht="13" customHeight="1">
-      <c r="A8" s="19" t="inlineStr"/>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr"/>
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr"/>
-      <c r="D8" s="19" t="inlineStr"/>
-      <c r="E8" s="19" t="inlineStr"/>
-      <c r="F8" s="19" t="inlineStr"/>
-      <c r="G8" s="19" t="inlineStr"/>
-      <c r="H8" s="19" t="inlineStr"/>
-      <c r="I8" s="19" t="inlineStr"/>
-      <c r="J8" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" s="24" t="n">
+      <c r="C8" s="18" t="inlineStr"/>
+      <c r="D8" s="18" t="inlineStr"/>
+      <c r="E8" s="18" t="inlineStr"/>
+      <c r="F8" s="18" t="inlineStr"/>
+      <c r="G8" s="18" t="inlineStr"/>
+      <c r="H8" s="18" t="inlineStr"/>
+      <c r="I8" s="18" t="inlineStr"/>
+      <c r="J8" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" s="42" t="n">
         <v>0.87</v>
       </c>
-      <c r="L8" s="42" t="n">
+      <c r="L8" s="40" t="n">
         <v>0.95</v>
       </c>
-      <c r="M8" s="21" t="n">
+      <c r="M8" s="39" t="n">
         <v>0.77</v>
       </c>
-      <c r="N8" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" s="24" t="n">
+      <c r="N8" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" s="42" t="n">
         <v>0.87</v>
       </c>
-      <c r="P8" s="23">
+      <c r="P8" s="20">
         <f>IFERROR(AVERAGE(C8:O8),"")</f>
         <v/>
       </c>
-      <c r="Q8" s="19" t="inlineStr"/>
-      <c r="R8" s="19" t="inlineStr"/>
+      <c r="Q8" s="18" t="inlineStr"/>
+      <c r="R8" s="18" t="inlineStr"/>
     </row>
     <row r="9" ht="13" customHeight="1">
-      <c r="A9" s="19" t="inlineStr"/>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="A9" s="18" t="inlineStr"/>
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>Quality</t>
         </is>
       </c>
-      <c r="C9" s="19" t="inlineStr"/>
-      <c r="D9" s="19" t="inlineStr"/>
-      <c r="E9" s="19" t="inlineStr"/>
-      <c r="F9" s="19" t="inlineStr"/>
-      <c r="G9" s="19" t="inlineStr"/>
-      <c r="H9" s="19" t="inlineStr"/>
-      <c r="I9" s="19" t="inlineStr"/>
-      <c r="J9" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="P9" s="23">
+      <c r="C9" s="18" t="inlineStr"/>
+      <c r="D9" s="18" t="inlineStr"/>
+      <c r="E9" s="18" t="inlineStr"/>
+      <c r="F9" s="18" t="inlineStr"/>
+      <c r="G9" s="18" t="inlineStr"/>
+      <c r="H9" s="18" t="inlineStr"/>
+      <c r="I9" s="18" t="inlineStr"/>
+      <c r="J9" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" s="20">
         <f>IFERROR(AVERAGE(C9:O9),"")</f>
         <v/>
       </c>
-      <c r="Q9" s="19" t="inlineStr"/>
-      <c r="R9" s="19" t="inlineStr"/>
+      <c r="Q9" s="18" t="inlineStr"/>
+      <c r="R9" s="18" t="inlineStr"/>
     </row>
     <row r="10" ht="13" customHeight="1">
-      <c r="A10" s="19" t="inlineStr"/>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="A10" s="18" t="inlineStr"/>
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>Cleanliness</t>
         </is>
       </c>
-      <c r="C10" s="19" t="inlineStr"/>
-      <c r="D10" s="19" t="inlineStr"/>
-      <c r="E10" s="19" t="inlineStr"/>
-      <c r="F10" s="19" t="inlineStr"/>
-      <c r="G10" s="19" t="inlineStr"/>
-      <c r="H10" s="19" t="inlineStr"/>
-      <c r="I10" s="19" t="inlineStr"/>
-      <c r="J10" s="42" t="n">
+      <c r="C10" s="18" t="inlineStr"/>
+      <c r="D10" s="18" t="inlineStr"/>
+      <c r="E10" s="18" t="inlineStr"/>
+      <c r="F10" s="18" t="inlineStr"/>
+      <c r="G10" s="18" t="inlineStr"/>
+      <c r="H10" s="18" t="inlineStr"/>
+      <c r="I10" s="18" t="inlineStr"/>
+      <c r="J10" s="40" t="n">
         <v>0.97</v>
       </c>
-      <c r="K10" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" s="24" t="n">
+      <c r="K10" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" s="42" t="n">
         <v>0.8</v>
       </c>
-      <c r="N10" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="P10" s="23">
+      <c r="N10" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" s="20">
         <f>IFERROR(AVERAGE(C10:O10),"")</f>
         <v/>
       </c>
-      <c r="Q10" s="19" t="inlineStr"/>
-      <c r="R10" s="19" t="inlineStr"/>
+      <c r="Q10" s="18" t="inlineStr"/>
+      <c r="R10" s="18" t="inlineStr"/>
     </row>
     <row r="11" ht="13" customHeight="1">
-      <c r="A11" s="19" t="inlineStr"/>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr"/>
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>Customer Sat</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr"/>
-      <c r="D11" s="19" t="inlineStr"/>
-      <c r="E11" s="19" t="inlineStr"/>
-      <c r="F11" s="19" t="inlineStr"/>
-      <c r="G11" s="19" t="inlineStr"/>
-      <c r="H11" s="19" t="inlineStr"/>
-      <c r="I11" s="19" t="inlineStr"/>
-      <c r="J11" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" s="42" t="n">
+      <c r="C11" s="18" t="inlineStr"/>
+      <c r="D11" s="18" t="inlineStr"/>
+      <c r="E11" s="18" t="inlineStr"/>
+      <c r="F11" s="18" t="inlineStr"/>
+      <c r="G11" s="18" t="inlineStr"/>
+      <c r="H11" s="18" t="inlineStr"/>
+      <c r="I11" s="18" t="inlineStr"/>
+      <c r="J11" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="40" t="n">
         <v>0.9</v>
       </c>
-      <c r="N11" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="P11" s="23">
+      <c r="N11" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="P11" s="20">
         <f>IFERROR(AVERAGE(C11:O11),"")</f>
         <v/>
       </c>
-      <c r="Q11" s="19" t="inlineStr"/>
-      <c r="R11" s="19" t="inlineStr"/>
+      <c r="Q11" s="18" t="inlineStr"/>
+      <c r="R11" s="18" t="inlineStr"/>
     </row>
     <row r="12" ht="6" customHeight="1">
-      <c r="A12" s="25" t="n"/>
+      <c r="A12" s="21" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="26" t="inlineStr">
+      <c r="A13" s="22" t="inlineStr">
         <is>
           <t>MANAGERS</t>
         </is>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="B14" s="28" t="inlineStr">
+      <c r="A14" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
         <is>
           <t>Madison C.</t>
         </is>
       </c>
-      <c r="C14" s="29" t="n"/>
-      <c r="D14" s="29" t="n"/>
-      <c r="E14" s="29" t="n"/>
-      <c r="F14" s="29" t="n"/>
-      <c r="G14" s="29" t="n"/>
-      <c r="H14" s="29" t="n"/>
-      <c r="I14" s="29" t="n"/>
-      <c r="J14" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K14" s="29" t="n"/>
-      <c r="L14" s="29" t="n"/>
-      <c r="M14" s="29" t="n"/>
-      <c r="N14" s="29" t="n"/>
-      <c r="O14" s="29" t="n"/>
-      <c r="P14" s="18">
+      <c r="C14" s="25" t="n"/>
+      <c r="D14" s="25" t="n"/>
+      <c r="E14" s="25" t="n"/>
+      <c r="F14" s="25" t="n"/>
+      <c r="G14" s="25" t="n"/>
+      <c r="H14" s="25" t="n"/>
+      <c r="I14" s="25" t="n"/>
+      <c r="J14" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K14" s="25" t="n"/>
+      <c r="L14" s="25" t="n"/>
+      <c r="M14" s="25" t="n"/>
+      <c r="N14" s="25" t="n"/>
+      <c r="O14" s="25" t="n"/>
+      <c r="P14" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$O$7,C14:O14,"Y"),"")</f>
         <v/>
       </c>
-      <c r="Q14" s="31">
+      <c r="Q14" s="26">
         <f>COUNTIF(C14:O14,"Y")</f>
         <v/>
       </c>
-      <c r="R14" s="32">
+      <c r="R14" s="27">
         <f>SUMPRODUCT((C$7:$O$7=1)*(C14:O14="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="27" t="n">
+      <c r="A15" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="B15" s="28" t="inlineStr">
+      <c r="B15" s="24" t="inlineStr">
         <is>
           <t>Vicki L.</t>
         </is>
       </c>
-      <c r="C15" s="29" t="n"/>
-      <c r="D15" s="29" t="n"/>
-      <c r="E15" s="29" t="n"/>
-      <c r="F15" s="29" t="n"/>
-      <c r="G15" s="29" t="n"/>
-      <c r="H15" s="29" t="n"/>
-      <c r="I15" s="29" t="n"/>
-      <c r="J15" s="29" t="n"/>
-      <c r="K15" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L15" s="29" t="n"/>
-      <c r="M15" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N15" s="29" t="n"/>
-      <c r="O15" s="29" t="n"/>
-      <c r="P15" s="18">
+      <c r="C15" s="25" t="n"/>
+      <c r="D15" s="25" t="n"/>
+      <c r="E15" s="25" t="n"/>
+      <c r="F15" s="25" t="n"/>
+      <c r="G15" s="25" t="n"/>
+      <c r="H15" s="25" t="n"/>
+      <c r="I15" s="25" t="n"/>
+      <c r="J15" s="25" t="n"/>
+      <c r="K15" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L15" s="25" t="n"/>
+      <c r="M15" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N15" s="25" t="n"/>
+      <c r="O15" s="25" t="n"/>
+      <c r="P15" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$O$7,C15:O15,"Y"),"")</f>
         <v/>
       </c>
-      <c r="Q15" s="31">
+      <c r="Q15" s="26">
         <f>COUNTIF(C15:O15,"Y")</f>
         <v/>
       </c>
-      <c r="R15" s="32">
+      <c r="R15" s="27">
         <f>SUMPRODUCT((C$7:$O$7=1)*(C15:O15="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
-      <c r="A16" s="27" t="n">
+      <c r="A16" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="B16" s="28" t="inlineStr">
+      <c r="B16" s="24" t="inlineStr">
         <is>
           <t>Kasey W.</t>
         </is>
       </c>
-      <c r="C16" s="29" t="n"/>
-      <c r="D16" s="29" t="n"/>
-      <c r="E16" s="29" t="n"/>
-      <c r="F16" s="29" t="n"/>
-      <c r="G16" s="29" t="n"/>
-      <c r="H16" s="29" t="n"/>
-      <c r="I16" s="29" t="n"/>
-      <c r="J16" s="29" t="n"/>
-      <c r="K16" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L16" s="29" t="n"/>
-      <c r="M16" s="29" t="n"/>
-      <c r="N16" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O16" s="29" t="n"/>
-      <c r="P16" s="18">
+      <c r="C16" s="25" t="n"/>
+      <c r="D16" s="25" t="n"/>
+      <c r="E16" s="25" t="n"/>
+      <c r="F16" s="25" t="n"/>
+      <c r="G16" s="25" t="n"/>
+      <c r="H16" s="25" t="n"/>
+      <c r="I16" s="25" t="n"/>
+      <c r="J16" s="25" t="n"/>
+      <c r="K16" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L16" s="25" t="n"/>
+      <c r="M16" s="25" t="n"/>
+      <c r="N16" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O16" s="25" t="n"/>
+      <c r="P16" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$O$7,C16:O16,"Y"),"")</f>
         <v/>
       </c>
-      <c r="Q16" s="31">
+      <c r="Q16" s="26">
         <f>COUNTIF(C16:O16,"Y")</f>
         <v/>
       </c>
-      <c r="R16" s="32">
+      <c r="R16" s="27">
         <f>SUMPRODUCT((C$7:$O$7=1)*(C16:O16="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
-      <c r="A17" s="27" t="n">
+      <c r="A17" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="B17" s="28" t="inlineStr">
+      <c r="B17" s="24" t="inlineStr">
         <is>
           <t>Nathan R.</t>
         </is>
       </c>
-      <c r="C17" s="29" t="n"/>
-      <c r="D17" s="29" t="n"/>
-      <c r="E17" s="29" t="n"/>
-      <c r="F17" s="29" t="n"/>
-      <c r="G17" s="29" t="n"/>
-      <c r="H17" s="29" t="n"/>
-      <c r="I17" s="29" t="n"/>
-      <c r="J17" s="29" t="n"/>
-      <c r="K17" s="29" t="n"/>
-      <c r="L17" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M17" s="29" t="n"/>
-      <c r="N17" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O17" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="P17" s="18">
+      <c r="C17" s="25" t="n"/>
+      <c r="D17" s="25" t="n"/>
+      <c r="E17" s="25" t="n"/>
+      <c r="F17" s="25" t="n"/>
+      <c r="G17" s="25" t="n"/>
+      <c r="H17" s="25" t="n"/>
+      <c r="I17" s="25" t="n"/>
+      <c r="J17" s="25" t="n"/>
+      <c r="K17" s="25" t="n"/>
+      <c r="L17" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M17" s="25" t="n"/>
+      <c r="N17" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O17" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P17" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$O$7,C17:O17,"Y"),"")</f>
         <v/>
       </c>
-      <c r="Q17" s="31">
+      <c r="Q17" s="26">
         <f>COUNTIF(C17:O17,"Y")</f>
         <v/>
       </c>
-      <c r="R17" s="32">
+      <c r="R17" s="27">
         <f>SUMPRODUCT((C$7:$O$7=1)*(C17:O17="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="6" customHeight="1">
-      <c r="A18" s="25" t="n"/>
+      <c r="A18" s="21" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="33" t="inlineStr">
+      <c r="A19" s="28" t="inlineStr">
         <is>
           <t>CREW</t>
         </is>
       </c>
     </row>
     <row r="20" ht="17" customHeight="1">
-      <c r="A20" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="B20" s="35" t="inlineStr">
+      <c r="A20" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
         <is>
           <t>Alen</t>
         </is>
       </c>
-      <c r="C20" s="36" t="n"/>
-      <c r="D20" s="36" t="n"/>
-      <c r="E20" s="36" t="n"/>
-      <c r="F20" s="36" t="n"/>
-      <c r="G20" s="36" t="n"/>
-      <c r="H20" s="36" t="n"/>
-      <c r="I20" s="36" t="n"/>
-      <c r="J20" s="36" t="n"/>
-      <c r="K20" s="36" t="n"/>
-      <c r="L20" s="36" t="n"/>
-      <c r="M20" s="36" t="n"/>
-      <c r="N20" s="36" t="n"/>
-      <c r="O20" s="36" t="n"/>
-      <c r="P20" s="18">
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+      <c r="E20" s="31" t="n"/>
+      <c r="F20" s="31" t="n"/>
+      <c r="G20" s="31" t="n"/>
+      <c r="H20" s="31" t="n"/>
+      <c r="I20" s="31" t="n"/>
+      <c r="J20" s="31" t="n"/>
+      <c r="K20" s="31" t="n"/>
+      <c r="L20" s="31" t="n"/>
+      <c r="M20" s="31" t="n"/>
+      <c r="N20" s="31" t="n"/>
+      <c r="O20" s="31" t="n"/>
+      <c r="P20" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$O$7,C20:O20,"Y"),"")</f>
         <v/>
       </c>
-      <c r="Q20" s="31">
+      <c r="Q20" s="26">
         <f>COUNTIF(C20:O20,"Y")</f>
         <v/>
       </c>
-      <c r="R20" s="32">
+      <c r="R20" s="27">
         <f>SUMPRODUCT((C$7:$O$7=1)*(C20:O20="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="17" customHeight="1">
-      <c r="A21" s="37" t="n">
+      <c r="A21" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="B21" s="38" t="inlineStr">
+      <c r="B21" s="33" t="inlineStr">
         <is>
           <t>Ash</t>
         </is>
       </c>
-      <c r="C21" s="19" t="n"/>
-      <c r="D21" s="19" t="n"/>
-      <c r="E21" s="19" t="n"/>
-      <c r="F21" s="19" t="n"/>
-      <c r="G21" s="19" t="n"/>
-      <c r="H21" s="19" t="n"/>
-      <c r="I21" s="19" t="n"/>
-      <c r="J21" s="19" t="n"/>
-      <c r="K21" s="19" t="n"/>
-      <c r="L21" s="19" t="n"/>
-      <c r="M21" s="19" t="n"/>
-      <c r="N21" s="19" t="n"/>
-      <c r="O21" s="19" t="n"/>
-      <c r="P21" s="18">
+      <c r="C21" s="18" t="n"/>
+      <c r="D21" s="18" t="n"/>
+      <c r="E21" s="18" t="n"/>
+      <c r="F21" s="18" t="n"/>
+      <c r="G21" s="18" t="n"/>
+      <c r="H21" s="18" t="n"/>
+      <c r="I21" s="18" t="n"/>
+      <c r="J21" s="18" t="n"/>
+      <c r="K21" s="18" t="n"/>
+      <c r="L21" s="18" t="n"/>
+      <c r="M21" s="18" t="n"/>
+      <c r="N21" s="18" t="n"/>
+      <c r="O21" s="18" t="n"/>
+      <c r="P21" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$O$7,C21:O21,"Y"),"")</f>
         <v/>
       </c>
-      <c r="Q21" s="31">
+      <c r="Q21" s="26">
         <f>COUNTIF(C21:O21,"Y")</f>
         <v/>
       </c>
-      <c r="R21" s="32">
+      <c r="R21" s="27">
         <f>SUMPRODUCT((C$7:$O$7=1)*(C21:O21="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="17" customHeight="1">
-      <c r="A22" s="34" t="n">
+      <c r="A22" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B22" s="35" t="inlineStr">
+      <c r="B22" s="30" t="inlineStr">
         <is>
           <t>Autumn</t>
         </is>
       </c>
-      <c r="C22" s="36" t="n"/>
-      <c r="D22" s="36" t="n"/>
-      <c r="E22" s="36" t="n"/>
-      <c r="F22" s="36" t="n"/>
-      <c r="G22" s="36" t="n"/>
-      <c r="H22" s="36" t="n"/>
-      <c r="I22" s="36" t="n"/>
-      <c r="J22" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K22" s="36" t="n"/>
-      <c r="L22" s="36" t="n"/>
-      <c r="M22" s="36" t="n"/>
-      <c r="N22" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O22" s="36" t="n"/>
-      <c r="P22" s="18">
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+      <c r="E22" s="31" t="n"/>
+      <c r="F22" s="31" t="n"/>
+      <c r="G22" s="31" t="n"/>
+      <c r="H22" s="31" t="n"/>
+      <c r="I22" s="31" t="n"/>
+      <c r="J22" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K22" s="31" t="n"/>
+      <c r="L22" s="31" t="n"/>
+      <c r="M22" s="31" t="n"/>
+      <c r="N22" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O22" s="31" t="n"/>
+      <c r="P22" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$O$7,C22:O22,"Y"),"")</f>
         <v/>
       </c>
-      <c r="Q22" s="31">
+      <c r="Q22" s="26">
         <f>COUNTIF(C22:O22,"Y")</f>
         <v/>
       </c>
-      <c r="R22" s="32">
+      <c r="R22" s="27">
         <f>SUMPRODUCT((C$7:$O$7=1)*(C22:O22="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="17" customHeight="1">
-      <c r="A23" s="37" t="n">
+      <c r="A23" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="B23" s="38" t="inlineStr">
+      <c r="B23" s="33" t="inlineStr">
         <is>
           <t>Bri</t>
         </is>
       </c>
-      <c r="C23" s="19" t="n"/>
-      <c r="D23" s="19" t="n"/>
-      <c r="E23" s="19" t="n"/>
-      <c r="F23" s="19" t="n"/>
-      <c r="G23" s="19" t="n"/>
-      <c r="H23" s="19" t="n"/>
-      <c r="I23" s="19" t="n"/>
-      <c r="J23" s="19" t="n"/>
-      <c r="K23" s="19" t="n"/>
-      <c r="L23" s="19" t="n"/>
-      <c r="M23" s="19" t="n"/>
-      <c r="N23" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O23" s="19" t="n"/>
-      <c r="P23" s="18">
+      <c r="C23" s="18" t="n"/>
+      <c r="D23" s="18" t="n"/>
+      <c r="E23" s="18" t="n"/>
+      <c r="F23" s="18" t="n"/>
+      <c r="G23" s="18" t="n"/>
+      <c r="H23" s="18" t="n"/>
+      <c r="I23" s="18" t="n"/>
+      <c r="J23" s="18" t="n"/>
+      <c r="K23" s="18" t="n"/>
+      <c r="L23" s="18" t="n"/>
+      <c r="M23" s="18" t="n"/>
+      <c r="N23" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O23" s="18" t="n"/>
+      <c r="P23" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$O$7,C23:O23,"Y"),"")</f>
         <v/>
       </c>
-      <c r="Q23" s="31">
+      <c r="Q23" s="26">
         <f>COUNTIF(C23:O23,"Y")</f>
         <v/>
       </c>
-      <c r="R23" s="32">
+      <c r="R23" s="27">
         <f>SUMPRODUCT((C$7:$O$7=1)*(C23:O23="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="17" customHeight="1">
-      <c r="A24" s="34" t="n">
+      <c r="A24" s="29" t="n">
         <v>5</v>
       </c>
-      <c r="B24" s="35" t="inlineStr">
+      <c r="B24" s="30" t="inlineStr">
         <is>
           <t>Dakayla</t>
         </is>
       </c>
-      <c r="C24" s="36" t="n"/>
-      <c r="D24" s="36" t="n"/>
-      <c r="E24" s="36" t="n"/>
-      <c r="F24" s="36" t="n"/>
-      <c r="G24" s="36" t="n"/>
-      <c r="H24" s="36" t="n"/>
-      <c r="I24" s="36" t="n"/>
-      <c r="J24" s="36" t="n"/>
-      <c r="K24" s="36" t="n"/>
-      <c r="L24" s="36" t="n"/>
-      <c r="M24" s="36" t="n"/>
-      <c r="N24" s="36" t="n"/>
-      <c r="O24" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="P24" s="18">
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+      <c r="E24" s="31" t="n"/>
+      <c r="F24" s="31" t="n"/>
+      <c r="G24" s="31" t="n"/>
+      <c r="H24" s="31" t="n"/>
+      <c r="I24" s="31" t="n"/>
+      <c r="J24" s="31" t="n"/>
+      <c r="K24" s="31" t="n"/>
+      <c r="L24" s="31" t="n"/>
+      <c r="M24" s="31" t="n"/>
+      <c r="N24" s="31" t="n"/>
+      <c r="O24" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P24" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$O$7,C24:O24,"Y"),"")</f>
         <v/>
       </c>
-      <c r="Q24" s="31">
+      <c r="Q24" s="26">
         <f>COUNTIF(C24:O24,"Y")</f>
         <v/>
       </c>
-      <c r="R24" s="32">
+      <c r="R24" s="27">
         <f>SUMPRODUCT((C$7:$O$7=1)*(C24:O24="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="17" customHeight="1">
-      <c r="A25" s="37" t="n">
+      <c r="A25" s="32" t="n">
         <v>6</v>
       </c>
-      <c r="B25" s="38" t="inlineStr">
+      <c r="B25" s="33" t="inlineStr">
         <is>
           <t>Divan</t>
         </is>
       </c>
-      <c r="C25" s="19" t="n"/>
-      <c r="D25" s="19" t="n"/>
-      <c r="E25" s="19" t="n"/>
-      <c r="F25" s="19" t="n"/>
-      <c r="G25" s="19" t="n"/>
-      <c r="H25" s="19" t="n"/>
-      <c r="I25" s="19" t="n"/>
-      <c r="J25" s="19" t="n"/>
-      <c r="K25" s="19" t="n"/>
-      <c r="L25" s="19" t="n"/>
-      <c r="M25" s="19" t="n"/>
-      <c r="N25" s="19" t="n"/>
-      <c r="O25" s="19" t="n"/>
-      <c r="P25" s="18">
+      <c r="C25" s="18" t="n"/>
+      <c r="D25" s="18" t="n"/>
+      <c r="E25" s="18" t="n"/>
+      <c r="F25" s="18" t="n"/>
+      <c r="G25" s="18" t="n"/>
+      <c r="H25" s="18" t="n"/>
+      <c r="I25" s="18" t="n"/>
+      <c r="J25" s="18" t="n"/>
+      <c r="K25" s="18" t="n"/>
+      <c r="L25" s="18" t="n"/>
+      <c r="M25" s="18" t="n"/>
+      <c r="N25" s="18" t="n"/>
+      <c r="O25" s="18" t="n"/>
+      <c r="P25" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$O$7,C25:O25,"Y"),"")</f>
         <v/>
       </c>
-      <c r="Q25" s="31">
+      <c r="Q25" s="26">
         <f>COUNTIF(C25:O25,"Y")</f>
         <v/>
       </c>
-      <c r="R25" s="32">
+      <c r="R25" s="27">
         <f>SUMPRODUCT((C$7:$O$7=1)*(C25:O25="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="17" customHeight="1">
-      <c r="A26" s="34" t="n">
+      <c r="A26" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="B26" s="35" t="inlineStr">
+      <c r="B26" s="30" t="inlineStr">
         <is>
           <t>Francisco</t>
         </is>
       </c>
-      <c r="C26" s="36" t="n"/>
-      <c r="D26" s="36" t="n"/>
-      <c r="E26" s="36" t="n"/>
-      <c r="F26" s="36" t="n"/>
-      <c r="G26" s="36" t="n"/>
-      <c r="H26" s="36" t="n"/>
-      <c r="I26" s="36" t="n"/>
-      <c r="J26" s="36" t="n"/>
-      <c r="K26" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L26" s="36" t="n"/>
-      <c r="M26" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N26" s="36" t="n"/>
-      <c r="O26" s="36" t="n"/>
-      <c r="P26" s="18">
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+      <c r="E26" s="31" t="n"/>
+      <c r="F26" s="31" t="n"/>
+      <c r="G26" s="31" t="n"/>
+      <c r="H26" s="31" t="n"/>
+      <c r="I26" s="31" t="n"/>
+      <c r="J26" s="31" t="n"/>
+      <c r="K26" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L26" s="31" t="n"/>
+      <c r="M26" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N26" s="31" t="n"/>
+      <c r="O26" s="31" t="n"/>
+      <c r="P26" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$O$7,C26:O26,"Y"),"")</f>
         <v/>
       </c>
-      <c r="Q26" s="31">
+      <c r="Q26" s="26">
         <f>COUNTIF(C26:O26,"Y")</f>
         <v/>
       </c>
-      <c r="R26" s="32">
+      <c r="R26" s="27">
         <f>SUMPRODUCT((C$7:$O$7=1)*(C26:O26="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="17" customHeight="1">
-      <c r="A27" s="37" t="n">
+      <c r="A27" s="32" t="n">
         <v>8</v>
       </c>
-      <c r="B27" s="38" t="inlineStr">
+      <c r="B27" s="33" t="inlineStr">
         <is>
           <t>Grace</t>
         </is>
       </c>
-      <c r="C27" s="19" t="n"/>
-      <c r="D27" s="19" t="n"/>
-      <c r="E27" s="19" t="n"/>
-      <c r="F27" s="19" t="n"/>
-      <c r="G27" s="19" t="n"/>
-      <c r="H27" s="19" t="n"/>
-      <c r="I27" s="19" t="n"/>
-      <c r="J27" s="19" t="n"/>
-      <c r="K27" s="19" t="n"/>
-      <c r="L27" s="19" t="n"/>
-      <c r="M27" s="19" t="n"/>
-      <c r="N27" s="19" t="n"/>
-      <c r="O27" s="19" t="n"/>
-      <c r="P27" s="18">
+      <c r="C27" s="18" t="n"/>
+      <c r="D27" s="18" t="n"/>
+      <c r="E27" s="18" t="n"/>
+      <c r="F27" s="18" t="n"/>
+      <c r="G27" s="18" t="n"/>
+      <c r="H27" s="18" t="n"/>
+      <c r="I27" s="18" t="n"/>
+      <c r="J27" s="18" t="n"/>
+      <c r="K27" s="18" t="n"/>
+      <c r="L27" s="18" t="n"/>
+      <c r="M27" s="18" t="n"/>
+      <c r="N27" s="18" t="n"/>
+      <c r="O27" s="18" t="n"/>
+      <c r="P27" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$O$7,C27:O27,"Y"),"")</f>
         <v/>
       </c>
-      <c r="Q27" s="31">
+      <c r="Q27" s="26">
         <f>COUNTIF(C27:O27,"Y")</f>
         <v/>
       </c>
-      <c r="R27" s="32">
+      <c r="R27" s="27">
         <f>SUMPRODUCT((C$7:$O$7=1)*(C27:O27="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="17" customHeight="1">
-      <c r="A28" s="34" t="n">
+      <c r="A28" s="29" t="n">
         <v>9</v>
       </c>
-      <c r="B28" s="35" t="inlineStr">
+      <c r="B28" s="30" t="inlineStr">
         <is>
           <t>Jada</t>
         </is>
       </c>
-      <c r="C28" s="36" t="n"/>
-      <c r="D28" s="36" t="n"/>
-      <c r="E28" s="36" t="n"/>
-      <c r="F28" s="36" t="n"/>
-      <c r="G28" s="36" t="n"/>
-      <c r="H28" s="36" t="n"/>
-      <c r="I28" s="36" t="n"/>
-      <c r="J28" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K28" s="36" t="n"/>
-      <c r="L28" s="36" t="n"/>
-      <c r="M28" s="36" t="n"/>
-      <c r="N28" s="36" t="n"/>
-      <c r="O28" s="36" t="n"/>
-      <c r="P28" s="18">
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+      <c r="E28" s="31" t="n"/>
+      <c r="F28" s="31" t="n"/>
+      <c r="G28" s="31" t="n"/>
+      <c r="H28" s="31" t="n"/>
+      <c r="I28" s="31" t="n"/>
+      <c r="J28" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K28" s="31" t="n"/>
+      <c r="L28" s="31" t="n"/>
+      <c r="M28" s="31" t="n"/>
+      <c r="N28" s="31" t="n"/>
+      <c r="O28" s="31" t="n"/>
+      <c r="P28" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$O$7,C28:O28,"Y"),"")</f>
         <v/>
       </c>
-      <c r="Q28" s="31">
+      <c r="Q28" s="26">
         <f>COUNTIF(C28:O28,"Y")</f>
         <v/>
       </c>
-      <c r="R28" s="32">
+      <c r="R28" s="27">
         <f>SUMPRODUCT((C$7:$O$7=1)*(C28:O28="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="17" customHeight="1">
-      <c r="A29" s="37" t="n">
+      <c r="A29" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="B29" s="38" t="inlineStr">
+      <c r="B29" s="33" t="inlineStr">
         <is>
           <t>Jeremiah</t>
         </is>
       </c>
-      <c r="C29" s="19" t="n"/>
-      <c r="D29" s="19" t="n"/>
-      <c r="E29" s="19" t="n"/>
-      <c r="F29" s="19" t="n"/>
-      <c r="G29" s="19" t="n"/>
-      <c r="H29" s="19" t="n"/>
-      <c r="I29" s="19" t="n"/>
-      <c r="J29" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K29" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L29" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M29" s="19" t="n"/>
-      <c r="N29" s="19" t="n"/>
-      <c r="O29" s="19" t="n"/>
-      <c r="P29" s="18">
+      <c r="C29" s="18" t="n"/>
+      <c r="D29" s="18" t="n"/>
+      <c r="E29" s="18" t="n"/>
+      <c r="F29" s="18" t="n"/>
+      <c r="G29" s="18" t="n"/>
+      <c r="H29" s="18" t="n"/>
+      <c r="I29" s="18" t="n"/>
+      <c r="J29" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K29" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L29" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M29" s="18" t="n"/>
+      <c r="N29" s="18" t="n"/>
+      <c r="O29" s="18" t="n"/>
+      <c r="P29" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$O$7,C29:O29,"Y"),"")</f>
         <v/>
       </c>
-      <c r="Q29" s="31">
+      <c r="Q29" s="26">
         <f>COUNTIF(C29:O29,"Y")</f>
         <v/>
       </c>
-      <c r="R29" s="32">
+      <c r="R29" s="27">
         <f>SUMPRODUCT((C$7:$O$7=1)*(C29:O29="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="17" customHeight="1">
-      <c r="A30" s="34" t="n">
+      <c r="A30" s="29" t="n">
         <v>11</v>
       </c>
-      <c r="B30" s="35" t="inlineStr">
+      <c r="B30" s="30" t="inlineStr">
         <is>
           <t>Kable</t>
         </is>
       </c>
-      <c r="C30" s="36" t="n"/>
-      <c r="D30" s="36" t="n"/>
-      <c r="E30" s="36" t="n"/>
-      <c r="F30" s="36" t="n"/>
-      <c r="G30" s="36" t="n"/>
-      <c r="H30" s="36" t="n"/>
-      <c r="I30" s="36" t="n"/>
-      <c r="J30" s="36" t="n"/>
-      <c r="K30" s="36" t="n"/>
-      <c r="L30" s="36" t="n"/>
-      <c r="M30" s="36" t="n"/>
-      <c r="N30" s="36" t="n"/>
-      <c r="O30" s="36" t="n"/>
-      <c r="P30" s="18">
+      <c r="C30" s="31" t="n"/>
+      <c r="D30" s="31" t="n"/>
+      <c r="E30" s="31" t="n"/>
+      <c r="F30" s="31" t="n"/>
+      <c r="G30" s="31" t="n"/>
+      <c r="H30" s="31" t="n"/>
+      <c r="I30" s="31" t="n"/>
+      <c r="J30" s="31" t="n"/>
+      <c r="K30" s="31" t="n"/>
+      <c r="L30" s="31" t="n"/>
+      <c r="M30" s="31" t="n"/>
+      <c r="N30" s="31" t="n"/>
+      <c r="O30" s="31" t="n"/>
+      <c r="P30" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$O$7,C30:O30,"Y"),"")</f>
         <v/>
       </c>
-      <c r="Q30" s="31">
+      <c r="Q30" s="26">
         <f>COUNTIF(C30:O30,"Y")</f>
         <v/>
       </c>
-      <c r="R30" s="32">
+      <c r="R30" s="27">
         <f>SUMPRODUCT((C$7:$O$7=1)*(C30:O30="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="17" customHeight="1">
-      <c r="A31" s="37" t="n">
+      <c r="A31" s="32" t="n">
         <v>12</v>
       </c>
-      <c r="B31" s="38" t="inlineStr">
+      <c r="B31" s="33" t="inlineStr">
         <is>
           <t>Kayla</t>
         </is>
       </c>
-      <c r="C31" s="19" t="n"/>
-      <c r="D31" s="19" t="n"/>
-      <c r="E31" s="19" t="n"/>
-      <c r="F31" s="19" t="n"/>
-      <c r="G31" s="19" t="n"/>
-      <c r="H31" s="19" t="n"/>
-      <c r="I31" s="19" t="n"/>
-      <c r="J31" s="19" t="n"/>
-      <c r="K31" s="19" t="n"/>
-      <c r="L31" s="19" t="n"/>
-      <c r="M31" s="19" t="n"/>
-      <c r="N31" s="19" t="n"/>
-      <c r="O31" s="19" t="n"/>
-      <c r="P31" s="18">
+      <c r="C31" s="18" t="n"/>
+      <c r="D31" s="18" t="n"/>
+      <c r="E31" s="18" t="n"/>
+      <c r="F31" s="18" t="n"/>
+      <c r="G31" s="18" t="n"/>
+      <c r="H31" s="18" t="n"/>
+      <c r="I31" s="18" t="n"/>
+      <c r="J31" s="18" t="n"/>
+      <c r="K31" s="18" t="n"/>
+      <c r="L31" s="18" t="n"/>
+      <c r="M31" s="18" t="n"/>
+      <c r="N31" s="18" t="n"/>
+      <c r="O31" s="18" t="n"/>
+      <c r="P31" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$O$7,C31:O31,"Y"),"")</f>
         <v/>
       </c>
-      <c r="Q31" s="31">
+      <c r="Q31" s="26">
         <f>COUNTIF(C31:O31,"Y")</f>
         <v/>
       </c>
-      <c r="R31" s="32">
+      <c r="R31" s="27">
         <f>SUMPRODUCT((C$7:$O$7=1)*(C31:O31="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="17" customHeight="1">
-      <c r="A32" s="34" t="n">
+      <c r="A32" s="29" t="n">
         <v>13</v>
       </c>
-      <c r="B32" s="35" t="inlineStr">
+      <c r="B32" s="30" t="inlineStr">
         <is>
           <t>Kenzie</t>
         </is>
       </c>
-      <c r="C32" s="36" t="n"/>
-      <c r="D32" s="36" t="n"/>
-      <c r="E32" s="36" t="n"/>
-      <c r="F32" s="36" t="n"/>
-      <c r="G32" s="36" t="n"/>
-      <c r="H32" s="36" t="n"/>
-      <c r="I32" s="36" t="n"/>
-      <c r="J32" s="36" t="n"/>
-      <c r="K32" s="36" t="n"/>
-      <c r="L32" s="36" t="n"/>
-      <c r="M32" s="36" t="n"/>
-      <c r="N32" s="36" t="n"/>
-      <c r="O32" s="36" t="n"/>
-      <c r="P32" s="18">
+      <c r="C32" s="31" t="n"/>
+      <c r="D32" s="31" t="n"/>
+      <c r="E32" s="31" t="n"/>
+      <c r="F32" s="31" t="n"/>
+      <c r="G32" s="31" t="n"/>
+      <c r="H32" s="31" t="n"/>
+      <c r="I32" s="31" t="n"/>
+      <c r="J32" s="31" t="n"/>
+      <c r="K32" s="31" t="n"/>
+      <c r="L32" s="31" t="n"/>
+      <c r="M32" s="31" t="n"/>
+      <c r="N32" s="31" t="n"/>
+      <c r="O32" s="31" t="n"/>
+      <c r="P32" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$O$7,C32:O32,"Y"),"")</f>
         <v/>
       </c>
-      <c r="Q32" s="31">
+      <c r="Q32" s="26">
         <f>COUNTIF(C32:O32,"Y")</f>
         <v/>
       </c>
-      <c r="R32" s="32">
+      <c r="R32" s="27">
         <f>SUMPRODUCT((C$7:$O$7=1)*(C32:O32="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="17" customHeight="1">
-      <c r="A33" s="37" t="n">
+      <c r="A33" s="32" t="n">
         <v>14</v>
       </c>
-      <c r="B33" s="38" t="inlineStr">
+      <c r="B33" s="33" t="inlineStr">
         <is>
           <t>Lidy</t>
         </is>
       </c>
-      <c r="C33" s="19" t="n"/>
-      <c r="D33" s="19" t="n"/>
-      <c r="E33" s="19" t="n"/>
-      <c r="F33" s="19" t="n"/>
-      <c r="G33" s="19" t="n"/>
-      <c r="H33" s="19" t="n"/>
-      <c r="I33" s="19" t="n"/>
-      <c r="J33" s="19" t="n"/>
-      <c r="K33" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L33" s="19" t="n"/>
-      <c r="M33" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N33" s="19" t="n"/>
-      <c r="O33" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="P33" s="18">
+      <c r="C33" s="18" t="n"/>
+      <c r="D33" s="18" t="n"/>
+      <c r="E33" s="18" t="n"/>
+      <c r="F33" s="18" t="n"/>
+      <c r="G33" s="18" t="n"/>
+      <c r="H33" s="18" t="n"/>
+      <c r="I33" s="18" t="n"/>
+      <c r="J33" s="18" t="n"/>
+      <c r="K33" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L33" s="18" t="n"/>
+      <c r="M33" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N33" s="18" t="n"/>
+      <c r="O33" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P33" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$O$7,C33:O33,"Y"),"")</f>
         <v/>
       </c>
-      <c r="Q33" s="31">
+      <c r="Q33" s="26">
         <f>COUNTIF(C33:O33,"Y")</f>
         <v/>
       </c>
-      <c r="R33" s="32">
+      <c r="R33" s="27">
         <f>SUMPRODUCT((C$7:$O$7=1)*(C33:O33="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="17" customHeight="1">
-      <c r="A34" s="34" t="n">
+      <c r="A34" s="29" t="n">
         <v>15</v>
       </c>
-      <c r="B34" s="35" t="inlineStr">
+      <c r="B34" s="30" t="inlineStr">
         <is>
           <t>Maylin</t>
         </is>
       </c>
-      <c r="C34" s="36" t="n"/>
-      <c r="D34" s="36" t="n"/>
-      <c r="E34" s="36" t="n"/>
-      <c r="F34" s="36" t="n"/>
-      <c r="G34" s="36" t="n"/>
-      <c r="H34" s="36" t="n"/>
-      <c r="I34" s="36" t="n"/>
-      <c r="J34" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K34" s="36" t="n"/>
-      <c r="L34" s="36" t="n"/>
-      <c r="M34" s="36" t="n"/>
-      <c r="N34" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O34" s="36" t="n"/>
-      <c r="P34" s="18">
+      <c r="C34" s="31" t="n"/>
+      <c r="D34" s="31" t="n"/>
+      <c r="E34" s="31" t="n"/>
+      <c r="F34" s="31" t="n"/>
+      <c r="G34" s="31" t="n"/>
+      <c r="H34" s="31" t="n"/>
+      <c r="I34" s="31" t="n"/>
+      <c r="J34" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K34" s="31" t="n"/>
+      <c r="L34" s="31" t="n"/>
+      <c r="M34" s="31" t="n"/>
+      <c r="N34" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O34" s="31" t="n"/>
+      <c r="P34" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$O$7,C34:O34,"Y"),"")</f>
         <v/>
       </c>
-      <c r="Q34" s="31">
+      <c r="Q34" s="26">
         <f>COUNTIF(C34:O34,"Y")</f>
         <v/>
       </c>
-      <c r="R34" s="32">
+      <c r="R34" s="27">
         <f>SUMPRODUCT((C$7:$O$7=1)*(C34:O34="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="17" customHeight="1">
-      <c r="A35" s="37" t="n">
+      <c r="A35" s="32" t="n">
         <v>16</v>
       </c>
-      <c r="B35" s="38" t="inlineStr">
+      <c r="B35" s="33" t="inlineStr">
         <is>
           <t>Mike</t>
         </is>
       </c>
-      <c r="C35" s="19" t="n"/>
-      <c r="D35" s="19" t="n"/>
-      <c r="E35" s="19" t="n"/>
-      <c r="F35" s="19" t="n"/>
-      <c r="G35" s="19" t="n"/>
-      <c r="H35" s="19" t="n"/>
-      <c r="I35" s="19" t="n"/>
-      <c r="J35" s="19" t="n"/>
-      <c r="K35" s="19" t="n"/>
-      <c r="L35" s="19" t="n"/>
-      <c r="M35" s="19" t="n"/>
-      <c r="N35" s="19" t="n"/>
-      <c r="O35" s="19" t="n"/>
-      <c r="P35" s="18">
+      <c r="C35" s="18" t="n"/>
+      <c r="D35" s="18" t="n"/>
+      <c r="E35" s="18" t="n"/>
+      <c r="F35" s="18" t="n"/>
+      <c r="G35" s="18" t="n"/>
+      <c r="H35" s="18" t="n"/>
+      <c r="I35" s="18" t="n"/>
+      <c r="J35" s="18" t="n"/>
+      <c r="K35" s="18" t="n"/>
+      <c r="L35" s="18" t="n"/>
+      <c r="M35" s="18" t="n"/>
+      <c r="N35" s="18" t="n"/>
+      <c r="O35" s="18" t="n"/>
+      <c r="P35" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$O$7,C35:O35,"Y"),"")</f>
         <v/>
       </c>
-      <c r="Q35" s="31">
+      <c r="Q35" s="26">
         <f>COUNTIF(C35:O35,"Y")</f>
         <v/>
       </c>
-      <c r="R35" s="32">
+      <c r="R35" s="27">
         <f>SUMPRODUCT((C$7:$O$7=1)*(C35:O35="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="17" customHeight="1">
-      <c r="A36" s="34" t="n">
+      <c r="A36" s="29" t="n">
         <v>17</v>
       </c>
-      <c r="B36" s="35" t="inlineStr">
+      <c r="B36" s="30" t="inlineStr">
         <is>
           <t>Richard</t>
         </is>
       </c>
-      <c r="C36" s="36" t="n"/>
-      <c r="D36" s="36" t="n"/>
-      <c r="E36" s="36" t="n"/>
-      <c r="F36" s="36" t="n"/>
-      <c r="G36" s="36" t="n"/>
-      <c r="H36" s="36" t="n"/>
-      <c r="I36" s="36" t="n"/>
-      <c r="J36" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K36" s="36" t="n"/>
-      <c r="L36" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M36" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N36" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O36" s="36" t="n"/>
-      <c r="P36" s="18">
+      <c r="C36" s="31" t="n"/>
+      <c r="D36" s="31" t="n"/>
+      <c r="E36" s="31" t="n"/>
+      <c r="F36" s="31" t="n"/>
+      <c r="G36" s="31" t="n"/>
+      <c r="H36" s="31" t="n"/>
+      <c r="I36" s="31" t="n"/>
+      <c r="J36" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K36" s="31" t="n"/>
+      <c r="L36" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M36" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N36" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O36" s="31" t="n"/>
+      <c r="P36" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$O$7,C36:O36,"Y"),"")</f>
         <v/>
       </c>
-      <c r="Q36" s="31">
+      <c r="Q36" s="26">
         <f>COUNTIF(C36:O36,"Y")</f>
         <v/>
       </c>
-      <c r="R36" s="32">
+      <c r="R36" s="27">
         <f>SUMPRODUCT((C$7:$O$7=1)*(C36:O36="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="17" customHeight="1">
-      <c r="A37" s="37" t="n">
+      <c r="A37" s="32" t="n">
         <v>18</v>
       </c>
-      <c r="B37" s="38" t="inlineStr">
+      <c r="B37" s="33" t="inlineStr">
         <is>
           <t>Samuel</t>
         </is>
       </c>
-      <c r="C37" s="19" t="n"/>
-      <c r="D37" s="19" t="n"/>
-      <c r="E37" s="19" t="n"/>
-      <c r="F37" s="19" t="n"/>
-      <c r="G37" s="19" t="n"/>
-      <c r="H37" s="19" t="n"/>
-      <c r="I37" s="19" t="n"/>
-      <c r="J37" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K37" s="19" t="n"/>
-      <c r="L37" s="19" t="n"/>
-      <c r="M37" s="19" t="n"/>
-      <c r="N37" s="19" t="n"/>
-      <c r="O37" s="19" t="n"/>
-      <c r="P37" s="18">
+      <c r="C37" s="18" t="n"/>
+      <c r="D37" s="18" t="n"/>
+      <c r="E37" s="18" t="n"/>
+      <c r="F37" s="18" t="n"/>
+      <c r="G37" s="18" t="n"/>
+      <c r="H37" s="18" t="n"/>
+      <c r="I37" s="18" t="n"/>
+      <c r="J37" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K37" s="18" t="n"/>
+      <c r="L37" s="18" t="n"/>
+      <c r="M37" s="18" t="n"/>
+      <c r="N37" s="18" t="n"/>
+      <c r="O37" s="18" t="n"/>
+      <c r="P37" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$O$7,C37:O37,"Y"),"")</f>
         <v/>
       </c>
-      <c r="Q37" s="31">
+      <c r="Q37" s="26">
         <f>COUNTIF(C37:O37,"Y")</f>
         <v/>
       </c>
-      <c r="R37" s="32">
+      <c r="R37" s="27">
         <f>SUMPRODUCT((C$7:$O$7=1)*(C37:O37="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="17" customHeight="1">
-      <c r="A38" s="34" t="n">
+      <c r="A38" s="29" t="n">
         <v>19</v>
       </c>
-      <c r="B38" s="35" t="inlineStr">
+      <c r="B38" s="30" t="inlineStr">
         <is>
           <t>Zach</t>
         </is>
       </c>
-      <c r="C38" s="36" t="n"/>
-      <c r="D38" s="36" t="n"/>
-      <c r="E38" s="36" t="n"/>
-      <c r="F38" s="36" t="n"/>
-      <c r="G38" s="36" t="n"/>
-      <c r="H38" s="36" t="n"/>
-      <c r="I38" s="36" t="n"/>
-      <c r="J38" s="36" t="n"/>
-      <c r="K38" s="36" t="n"/>
-      <c r="L38" s="36" t="n"/>
-      <c r="M38" s="36" t="n"/>
-      <c r="N38" s="36" t="n"/>
-      <c r="O38" s="36" t="n"/>
-      <c r="P38" s="18">
+      <c r="C38" s="31" t="n"/>
+      <c r="D38" s="31" t="n"/>
+      <c r="E38" s="31" t="n"/>
+      <c r="F38" s="31" t="n"/>
+      <c r="G38" s="31" t="n"/>
+      <c r="H38" s="31" t="n"/>
+      <c r="I38" s="31" t="n"/>
+      <c r="J38" s="31" t="n"/>
+      <c r="K38" s="31" t="n"/>
+      <c r="L38" s="31" t="n"/>
+      <c r="M38" s="31" t="n"/>
+      <c r="N38" s="31" t="n"/>
+      <c r="O38" s="31" t="n"/>
+      <c r="P38" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$O$7,C38:O38,"Y"),"")</f>
         <v/>
       </c>
-      <c r="Q38" s="31">
+      <c r="Q38" s="26">
         <f>COUNTIF(C38:O38,"Y")</f>
         <v/>
       </c>
-      <c r="R38" s="32">
+      <c r="R38" s="27">
         <f>SUMPRODUCT((C$7:$O$7=1)*(C38:O38="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="3" t="inlineStr"/>
-      <c r="B39" s="39" t="inlineStr">
+      <c r="B39" s="34" t="inlineStr">
         <is>
           <t>Total on shift</t>
         </is>
@@ -7064,13 +6516,13 @@
         <f>SUM(Q14:Q38)</f>
         <v/>
       </c>
-      <c r="R39" s="40">
+      <c r="R39" s="35">
         <f>SUM(R14:R38)</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="12" customHeight="1">
-      <c r="A40" s="41" t="inlineStr">
+      <c r="A40" s="36" t="inlineStr">
         <is>
           <t>Y = on shift during shop's meal window. Personal Avg = average score of shops worked. Bonus = $50 per 100% shop worked.</t>
         </is>
@@ -7334,10 +6786,10 @@
       <c r="G7" s="16" t="n">
         <v>0.77</v>
       </c>
-      <c r="H7" s="17" t="n">
+      <c r="H7" s="37" t="n">
         <v>0.92</v>
       </c>
-      <c r="I7" s="17" t="n">
+      <c r="I7" s="37" t="n">
         <v>0.95</v>
       </c>
       <c r="J7" s="15" t="n">
@@ -7346,7 +6798,7 @@
       <c r="K7" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="L7" s="18">
+      <c r="L7" s="17">
         <f>IFERROR(AVERAGE(C7:K7),"")</f>
         <v/>
       </c>
@@ -7354,849 +6806,849 @@
       <c r="N7" s="12" t="inlineStr"/>
     </row>
     <row r="8" ht="13" customHeight="1">
-      <c r="A8" s="19" t="inlineStr"/>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr"/>
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr"/>
-      <c r="D8" s="19" t="inlineStr"/>
-      <c r="E8" s="19" t="inlineStr"/>
-      <c r="F8" s="19" t="inlineStr"/>
-      <c r="G8" s="19" t="inlineStr"/>
-      <c r="H8" s="19" t="inlineStr"/>
-      <c r="I8" s="19" t="inlineStr"/>
-      <c r="J8" s="19" t="inlineStr"/>
-      <c r="K8" s="19" t="inlineStr"/>
-      <c r="L8" s="23">
+      <c r="C8" s="18" t="inlineStr"/>
+      <c r="D8" s="18" t="inlineStr"/>
+      <c r="E8" s="18" t="inlineStr"/>
+      <c r="F8" s="18" t="inlineStr"/>
+      <c r="G8" s="18" t="inlineStr"/>
+      <c r="H8" s="18" t="inlineStr"/>
+      <c r="I8" s="18" t="inlineStr"/>
+      <c r="J8" s="18" t="inlineStr"/>
+      <c r="K8" s="18" t="inlineStr"/>
+      <c r="L8" s="20">
         <f>IFERROR(AVERAGE(C8:K8),"")</f>
         <v/>
       </c>
-      <c r="M8" s="19" t="inlineStr"/>
-      <c r="N8" s="19" t="inlineStr"/>
+      <c r="M8" s="18" t="inlineStr"/>
+      <c r="N8" s="18" t="inlineStr"/>
     </row>
     <row r="9" ht="13" customHeight="1">
-      <c r="A9" s="19" t="inlineStr"/>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="A9" s="18" t="inlineStr"/>
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>Quality</t>
         </is>
       </c>
-      <c r="C9" s="19" t="inlineStr"/>
-      <c r="D9" s="19" t="inlineStr"/>
-      <c r="E9" s="19" t="inlineStr"/>
-      <c r="F9" s="19" t="inlineStr"/>
-      <c r="G9" s="19" t="inlineStr"/>
-      <c r="H9" s="19" t="inlineStr"/>
-      <c r="I9" s="19" t="inlineStr"/>
-      <c r="J9" s="19" t="inlineStr"/>
-      <c r="K9" s="19" t="inlineStr"/>
-      <c r="L9" s="23">
+      <c r="C9" s="18" t="inlineStr"/>
+      <c r="D9" s="18" t="inlineStr"/>
+      <c r="E9" s="18" t="inlineStr"/>
+      <c r="F9" s="18" t="inlineStr"/>
+      <c r="G9" s="18" t="inlineStr"/>
+      <c r="H9" s="18" t="inlineStr"/>
+      <c r="I9" s="18" t="inlineStr"/>
+      <c r="J9" s="18" t="inlineStr"/>
+      <c r="K9" s="18" t="inlineStr"/>
+      <c r="L9" s="20">
         <f>IFERROR(AVERAGE(C9:K9),"")</f>
         <v/>
       </c>
-      <c r="M9" s="19" t="inlineStr"/>
-      <c r="N9" s="19" t="inlineStr"/>
+      <c r="M9" s="18" t="inlineStr"/>
+      <c r="N9" s="18" t="inlineStr"/>
     </row>
     <row r="10" ht="13" customHeight="1">
-      <c r="A10" s="19" t="inlineStr"/>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="A10" s="18" t="inlineStr"/>
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>Cleanliness</t>
         </is>
       </c>
-      <c r="C10" s="19" t="inlineStr"/>
-      <c r="D10" s="19" t="inlineStr"/>
-      <c r="E10" s="19" t="inlineStr"/>
-      <c r="F10" s="19" t="inlineStr"/>
-      <c r="G10" s="19" t="inlineStr"/>
-      <c r="H10" s="19" t="inlineStr"/>
-      <c r="I10" s="19" t="inlineStr"/>
-      <c r="J10" s="19" t="inlineStr"/>
-      <c r="K10" s="19" t="inlineStr"/>
-      <c r="L10" s="23">
+      <c r="C10" s="18" t="inlineStr"/>
+      <c r="D10" s="18" t="inlineStr"/>
+      <c r="E10" s="18" t="inlineStr"/>
+      <c r="F10" s="18" t="inlineStr"/>
+      <c r="G10" s="18" t="inlineStr"/>
+      <c r="H10" s="18" t="inlineStr"/>
+      <c r="I10" s="18" t="inlineStr"/>
+      <c r="J10" s="18" t="inlineStr"/>
+      <c r="K10" s="18" t="inlineStr"/>
+      <c r="L10" s="20">
         <f>IFERROR(AVERAGE(C10:K10),"")</f>
         <v/>
       </c>
-      <c r="M10" s="19" t="inlineStr"/>
-      <c r="N10" s="19" t="inlineStr"/>
+      <c r="M10" s="18" t="inlineStr"/>
+      <c r="N10" s="18" t="inlineStr"/>
     </row>
     <row r="11" ht="13" customHeight="1">
-      <c r="A11" s="19" t="inlineStr"/>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr"/>
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>Customer Sat</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr"/>
-      <c r="D11" s="19" t="inlineStr"/>
-      <c r="E11" s="19" t="inlineStr"/>
-      <c r="F11" s="19" t="inlineStr"/>
-      <c r="G11" s="19" t="inlineStr"/>
-      <c r="H11" s="19" t="inlineStr"/>
-      <c r="I11" s="19" t="inlineStr"/>
-      <c r="J11" s="19" t="inlineStr"/>
-      <c r="K11" s="19" t="inlineStr"/>
-      <c r="L11" s="23">
+      <c r="C11" s="18" t="inlineStr"/>
+      <c r="D11" s="18" t="inlineStr"/>
+      <c r="E11" s="18" t="inlineStr"/>
+      <c r="F11" s="18" t="inlineStr"/>
+      <c r="G11" s="18" t="inlineStr"/>
+      <c r="H11" s="18" t="inlineStr"/>
+      <c r="I11" s="18" t="inlineStr"/>
+      <c r="J11" s="18" t="inlineStr"/>
+      <c r="K11" s="18" t="inlineStr"/>
+      <c r="L11" s="20">
         <f>IFERROR(AVERAGE(C11:K11),"")</f>
         <v/>
       </c>
-      <c r="M11" s="19" t="inlineStr"/>
-      <c r="N11" s="19" t="inlineStr"/>
+      <c r="M11" s="18" t="inlineStr"/>
+      <c r="N11" s="18" t="inlineStr"/>
     </row>
     <row r="12" ht="6" customHeight="1">
-      <c r="A12" s="25" t="n"/>
+      <c r="A12" s="21" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="26" t="inlineStr">
+      <c r="A13" s="22" t="inlineStr">
         <is>
           <t>MANAGERS</t>
         </is>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="B14" s="28" t="inlineStr">
+      <c r="A14" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
         <is>
           <t>Madison C.</t>
         </is>
       </c>
-      <c r="C14" s="29" t="n"/>
-      <c r="D14" s="29" t="n"/>
-      <c r="E14" s="29" t="n"/>
-      <c r="F14" s="29" t="n"/>
-      <c r="G14" s="29" t="n"/>
-      <c r="H14" s="29" t="n"/>
-      <c r="I14" s="29" t="n"/>
-      <c r="J14" s="29" t="n"/>
-      <c r="K14" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L14" s="18">
+      <c r="C14" s="25" t="n"/>
+      <c r="D14" s="25" t="n"/>
+      <c r="E14" s="25" t="n"/>
+      <c r="F14" s="25" t="n"/>
+      <c r="G14" s="25" t="n"/>
+      <c r="H14" s="25" t="n"/>
+      <c r="I14" s="25" t="n"/>
+      <c r="J14" s="25" t="n"/>
+      <c r="K14" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L14" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$K$7,C14:K14,"Y"),"")</f>
         <v/>
       </c>
-      <c r="M14" s="31">
+      <c r="M14" s="26">
         <f>COUNTIF(C14:K14,"Y")</f>
         <v/>
       </c>
-      <c r="N14" s="32">
+      <c r="N14" s="27">
         <f>SUMPRODUCT((C$7:$K$7=1)*(C14:K14="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="27" t="n">
+      <c r="A15" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="B15" s="28" t="inlineStr">
+      <c r="B15" s="24" t="inlineStr">
         <is>
           <t>Vicki L.</t>
         </is>
       </c>
-      <c r="C15" s="29" t="n"/>
-      <c r="D15" s="29" t="n"/>
-      <c r="E15" s="29" t="n"/>
-      <c r="F15" s="29" t="n"/>
-      <c r="G15" s="29" t="n"/>
-      <c r="H15" s="29" t="n"/>
-      <c r="I15" s="29" t="n"/>
-      <c r="J15" s="29" t="n"/>
-      <c r="K15" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L15" s="18">
+      <c r="C15" s="25" t="n"/>
+      <c r="D15" s="25" t="n"/>
+      <c r="E15" s="25" t="n"/>
+      <c r="F15" s="25" t="n"/>
+      <c r="G15" s="25" t="n"/>
+      <c r="H15" s="25" t="n"/>
+      <c r="I15" s="25" t="n"/>
+      <c r="J15" s="25" t="n"/>
+      <c r="K15" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L15" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$K$7,C15:K15,"Y"),"")</f>
         <v/>
       </c>
-      <c r="M15" s="31">
+      <c r="M15" s="26">
         <f>COUNTIF(C15:K15,"Y")</f>
         <v/>
       </c>
-      <c r="N15" s="32">
+      <c r="N15" s="27">
         <f>SUMPRODUCT((C$7:$K$7=1)*(C15:K15="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
-      <c r="A16" s="27" t="n">
+      <c r="A16" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="B16" s="28" t="inlineStr">
+      <c r="B16" s="24" t="inlineStr">
         <is>
           <t>Kasey W.</t>
         </is>
       </c>
-      <c r="C16" s="29" t="n"/>
-      <c r="D16" s="29" t="n"/>
-      <c r="E16" s="29" t="n"/>
-      <c r="F16" s="29" t="n"/>
-      <c r="G16" s="29" t="n"/>
-      <c r="H16" s="29" t="n"/>
-      <c r="I16" s="29" t="n"/>
-      <c r="J16" s="29" t="n"/>
-      <c r="K16" s="29" t="n"/>
-      <c r="L16" s="18">
+      <c r="C16" s="25" t="n"/>
+      <c r="D16" s="25" t="n"/>
+      <c r="E16" s="25" t="n"/>
+      <c r="F16" s="25" t="n"/>
+      <c r="G16" s="25" t="n"/>
+      <c r="H16" s="25" t="n"/>
+      <c r="I16" s="25" t="n"/>
+      <c r="J16" s="25" t="n"/>
+      <c r="K16" s="25" t="n"/>
+      <c r="L16" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$K$7,C16:K16,"Y"),"")</f>
         <v/>
       </c>
-      <c r="M16" s="31">
+      <c r="M16" s="26">
         <f>COUNTIF(C16:K16,"Y")</f>
         <v/>
       </c>
-      <c r="N16" s="32">
+      <c r="N16" s="27">
         <f>SUMPRODUCT((C$7:$K$7=1)*(C16:K16="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
-      <c r="A17" s="27" t="n">
+      <c r="A17" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="B17" s="28" t="inlineStr">
+      <c r="B17" s="24" t="inlineStr">
         <is>
           <t>Nathan R.</t>
         </is>
       </c>
-      <c r="C17" s="29" t="n"/>
-      <c r="D17" s="29" t="n"/>
-      <c r="E17" s="29" t="n"/>
-      <c r="F17" s="29" t="n"/>
-      <c r="G17" s="29" t="n"/>
-      <c r="H17" s="29" t="n"/>
-      <c r="I17" s="29" t="n"/>
-      <c r="J17" s="29" t="n"/>
-      <c r="K17" s="29" t="n"/>
-      <c r="L17" s="18">
+      <c r="C17" s="25" t="n"/>
+      <c r="D17" s="25" t="n"/>
+      <c r="E17" s="25" t="n"/>
+      <c r="F17" s="25" t="n"/>
+      <c r="G17" s="25" t="n"/>
+      <c r="H17" s="25" t="n"/>
+      <c r="I17" s="25" t="n"/>
+      <c r="J17" s="25" t="n"/>
+      <c r="K17" s="25" t="n"/>
+      <c r="L17" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$K$7,C17:K17,"Y"),"")</f>
         <v/>
       </c>
-      <c r="M17" s="31">
+      <c r="M17" s="26">
         <f>COUNTIF(C17:K17,"Y")</f>
         <v/>
       </c>
-      <c r="N17" s="32">
+      <c r="N17" s="27">
         <f>SUMPRODUCT((C$7:$K$7=1)*(C17:K17="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="6" customHeight="1">
-      <c r="A18" s="25" t="n"/>
+      <c r="A18" s="21" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="33" t="inlineStr">
+      <c r="A19" s="28" t="inlineStr">
         <is>
           <t>CREW</t>
         </is>
       </c>
     </row>
     <row r="20" ht="17" customHeight="1">
-      <c r="A20" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="B20" s="35" t="inlineStr">
+      <c r="A20" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
         <is>
           <t>Alen</t>
         </is>
       </c>
-      <c r="C20" s="36" t="n"/>
-      <c r="D20" s="36" t="n"/>
-      <c r="E20" s="36" t="n"/>
-      <c r="F20" s="36" t="n"/>
-      <c r="G20" s="36" t="n"/>
-      <c r="H20" s="36" t="n"/>
-      <c r="I20" s="36" t="n"/>
-      <c r="J20" s="36" t="n"/>
-      <c r="K20" s="36" t="n"/>
-      <c r="L20" s="18">
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+      <c r="E20" s="31" t="n"/>
+      <c r="F20" s="31" t="n"/>
+      <c r="G20" s="31" t="n"/>
+      <c r="H20" s="31" t="n"/>
+      <c r="I20" s="31" t="n"/>
+      <c r="J20" s="31" t="n"/>
+      <c r="K20" s="31" t="n"/>
+      <c r="L20" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$K$7,C20:K20,"Y"),"")</f>
         <v/>
       </c>
-      <c r="M20" s="31">
+      <c r="M20" s="26">
         <f>COUNTIF(C20:K20,"Y")</f>
         <v/>
       </c>
-      <c r="N20" s="32">
+      <c r="N20" s="27">
         <f>SUMPRODUCT((C$7:$K$7=1)*(C20:K20="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="17" customHeight="1">
-      <c r="A21" s="37" t="n">
+      <c r="A21" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="B21" s="38" t="inlineStr">
+      <c r="B21" s="33" t="inlineStr">
         <is>
           <t>Ash</t>
         </is>
       </c>
-      <c r="C21" s="19" t="n"/>
-      <c r="D21" s="19" t="n"/>
-      <c r="E21" s="19" t="n"/>
-      <c r="F21" s="19" t="n"/>
-      <c r="G21" s="19" t="n"/>
-      <c r="H21" s="19" t="n"/>
-      <c r="I21" s="19" t="n"/>
-      <c r="J21" s="19" t="n"/>
-      <c r="K21" s="19" t="n"/>
-      <c r="L21" s="18">
+      <c r="C21" s="18" t="n"/>
+      <c r="D21" s="18" t="n"/>
+      <c r="E21" s="18" t="n"/>
+      <c r="F21" s="18" t="n"/>
+      <c r="G21" s="18" t="n"/>
+      <c r="H21" s="18" t="n"/>
+      <c r="I21" s="18" t="n"/>
+      <c r="J21" s="18" t="n"/>
+      <c r="K21" s="18" t="n"/>
+      <c r="L21" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$K$7,C21:K21,"Y"),"")</f>
         <v/>
       </c>
-      <c r="M21" s="31">
+      <c r="M21" s="26">
         <f>COUNTIF(C21:K21,"Y")</f>
         <v/>
       </c>
-      <c r="N21" s="32">
+      <c r="N21" s="27">
         <f>SUMPRODUCT((C$7:$K$7=1)*(C21:K21="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="17" customHeight="1">
-      <c r="A22" s="34" t="n">
+      <c r="A22" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B22" s="35" t="inlineStr">
+      <c r="B22" s="30" t="inlineStr">
         <is>
           <t>Autumn</t>
         </is>
       </c>
-      <c r="C22" s="36" t="n"/>
-      <c r="D22" s="36" t="n"/>
-      <c r="E22" s="36" t="n"/>
-      <c r="F22" s="36" t="n"/>
-      <c r="G22" s="36" t="n"/>
-      <c r="H22" s="36" t="n"/>
-      <c r="I22" s="36" t="n"/>
-      <c r="J22" s="36" t="n"/>
-      <c r="K22" s="36" t="n"/>
-      <c r="L22" s="18">
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+      <c r="E22" s="31" t="n"/>
+      <c r="F22" s="31" t="n"/>
+      <c r="G22" s="31" t="n"/>
+      <c r="H22" s="31" t="n"/>
+      <c r="I22" s="31" t="n"/>
+      <c r="J22" s="31" t="n"/>
+      <c r="K22" s="31" t="n"/>
+      <c r="L22" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$K$7,C22:K22,"Y"),"")</f>
         <v/>
       </c>
-      <c r="M22" s="31">
+      <c r="M22" s="26">
         <f>COUNTIF(C22:K22,"Y")</f>
         <v/>
       </c>
-      <c r="N22" s="32">
+      <c r="N22" s="27">
         <f>SUMPRODUCT((C$7:$K$7=1)*(C22:K22="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="17" customHeight="1">
-      <c r="A23" s="37" t="n">
+      <c r="A23" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="B23" s="38" t="inlineStr">
+      <c r="B23" s="33" t="inlineStr">
         <is>
           <t>Bri</t>
         </is>
       </c>
-      <c r="C23" s="19" t="n"/>
-      <c r="D23" s="19" t="n"/>
-      <c r="E23" s="19" t="n"/>
-      <c r="F23" s="19" t="n"/>
-      <c r="G23" s="19" t="n"/>
-      <c r="H23" s="19" t="n"/>
-      <c r="I23" s="19" t="n"/>
-      <c r="J23" s="19" t="n"/>
-      <c r="K23" s="19" t="n"/>
-      <c r="L23" s="18">
+      <c r="C23" s="18" t="n"/>
+      <c r="D23" s="18" t="n"/>
+      <c r="E23" s="18" t="n"/>
+      <c r="F23" s="18" t="n"/>
+      <c r="G23" s="18" t="n"/>
+      <c r="H23" s="18" t="n"/>
+      <c r="I23" s="18" t="n"/>
+      <c r="J23" s="18" t="n"/>
+      <c r="K23" s="18" t="n"/>
+      <c r="L23" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$K$7,C23:K23,"Y"),"")</f>
         <v/>
       </c>
-      <c r="M23" s="31">
+      <c r="M23" s="26">
         <f>COUNTIF(C23:K23,"Y")</f>
         <v/>
       </c>
-      <c r="N23" s="32">
+      <c r="N23" s="27">
         <f>SUMPRODUCT((C$7:$K$7=1)*(C23:K23="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="17" customHeight="1">
-      <c r="A24" s="34" t="n">
+      <c r="A24" s="29" t="n">
         <v>5</v>
       </c>
-      <c r="B24" s="35" t="inlineStr">
+      <c r="B24" s="30" t="inlineStr">
         <is>
           <t>Dakayla</t>
         </is>
       </c>
-      <c r="C24" s="36" t="n"/>
-      <c r="D24" s="36" t="n"/>
-      <c r="E24" s="36" t="n"/>
-      <c r="F24" s="36" t="n"/>
-      <c r="G24" s="36" t="n"/>
-      <c r="H24" s="36" t="n"/>
-      <c r="I24" s="36" t="n"/>
-      <c r="J24" s="36" t="n"/>
-      <c r="K24" s="36" t="n"/>
-      <c r="L24" s="18">
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+      <c r="E24" s="31" t="n"/>
+      <c r="F24" s="31" t="n"/>
+      <c r="G24" s="31" t="n"/>
+      <c r="H24" s="31" t="n"/>
+      <c r="I24" s="31" t="n"/>
+      <c r="J24" s="31" t="n"/>
+      <c r="K24" s="31" t="n"/>
+      <c r="L24" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$K$7,C24:K24,"Y"),"")</f>
         <v/>
       </c>
-      <c r="M24" s="31">
+      <c r="M24" s="26">
         <f>COUNTIF(C24:K24,"Y")</f>
         <v/>
       </c>
-      <c r="N24" s="32">
+      <c r="N24" s="27">
         <f>SUMPRODUCT((C$7:$K$7=1)*(C24:K24="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="17" customHeight="1">
-      <c r="A25" s="37" t="n">
+      <c r="A25" s="32" t="n">
         <v>6</v>
       </c>
-      <c r="B25" s="38" t="inlineStr">
+      <c r="B25" s="33" t="inlineStr">
         <is>
           <t>Divan</t>
         </is>
       </c>
-      <c r="C25" s="19" t="n"/>
-      <c r="D25" s="19" t="n"/>
-      <c r="E25" s="19" t="n"/>
-      <c r="F25" s="19" t="n"/>
-      <c r="G25" s="19" t="n"/>
-      <c r="H25" s="19" t="n"/>
-      <c r="I25" s="19" t="n"/>
-      <c r="J25" s="19" t="n"/>
-      <c r="K25" s="19" t="n"/>
-      <c r="L25" s="18">
+      <c r="C25" s="18" t="n"/>
+      <c r="D25" s="18" t="n"/>
+      <c r="E25" s="18" t="n"/>
+      <c r="F25" s="18" t="n"/>
+      <c r="G25" s="18" t="n"/>
+      <c r="H25" s="18" t="n"/>
+      <c r="I25" s="18" t="n"/>
+      <c r="J25" s="18" t="n"/>
+      <c r="K25" s="18" t="n"/>
+      <c r="L25" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$K$7,C25:K25,"Y"),"")</f>
         <v/>
       </c>
-      <c r="M25" s="31">
+      <c r="M25" s="26">
         <f>COUNTIF(C25:K25,"Y")</f>
         <v/>
       </c>
-      <c r="N25" s="32">
+      <c r="N25" s="27">
         <f>SUMPRODUCT((C$7:$K$7=1)*(C25:K25="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="17" customHeight="1">
-      <c r="A26" s="34" t="n">
+      <c r="A26" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="B26" s="35" t="inlineStr">
+      <c r="B26" s="30" t="inlineStr">
         <is>
           <t>Francisco</t>
         </is>
       </c>
-      <c r="C26" s="36" t="n"/>
-      <c r="D26" s="36" t="n"/>
-      <c r="E26" s="36" t="n"/>
-      <c r="F26" s="36" t="n"/>
-      <c r="G26" s="36" t="n"/>
-      <c r="H26" s="36" t="n"/>
-      <c r="I26" s="36" t="n"/>
-      <c r="J26" s="36" t="n"/>
-      <c r="K26" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L26" s="18">
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+      <c r="E26" s="31" t="n"/>
+      <c r="F26" s="31" t="n"/>
+      <c r="G26" s="31" t="n"/>
+      <c r="H26" s="31" t="n"/>
+      <c r="I26" s="31" t="n"/>
+      <c r="J26" s="31" t="n"/>
+      <c r="K26" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L26" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$K$7,C26:K26,"Y"),"")</f>
         <v/>
       </c>
-      <c r="M26" s="31">
+      <c r="M26" s="26">
         <f>COUNTIF(C26:K26,"Y")</f>
         <v/>
       </c>
-      <c r="N26" s="32">
+      <c r="N26" s="27">
         <f>SUMPRODUCT((C$7:$K$7=1)*(C26:K26="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="17" customHeight="1">
-      <c r="A27" s="37" t="n">
+      <c r="A27" s="32" t="n">
         <v>8</v>
       </c>
-      <c r="B27" s="38" t="inlineStr">
+      <c r="B27" s="33" t="inlineStr">
         <is>
           <t>Grace</t>
         </is>
       </c>
-      <c r="C27" s="19" t="n"/>
-      <c r="D27" s="19" t="n"/>
-      <c r="E27" s="19" t="n"/>
-      <c r="F27" s="19" t="n"/>
-      <c r="G27" s="19" t="n"/>
-      <c r="H27" s="19" t="n"/>
-      <c r="I27" s="19" t="n"/>
-      <c r="J27" s="19" t="n"/>
-      <c r="K27" s="19" t="n"/>
-      <c r="L27" s="18">
+      <c r="C27" s="18" t="n"/>
+      <c r="D27" s="18" t="n"/>
+      <c r="E27" s="18" t="n"/>
+      <c r="F27" s="18" t="n"/>
+      <c r="G27" s="18" t="n"/>
+      <c r="H27" s="18" t="n"/>
+      <c r="I27" s="18" t="n"/>
+      <c r="J27" s="18" t="n"/>
+      <c r="K27" s="18" t="n"/>
+      <c r="L27" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$K$7,C27:K27,"Y"),"")</f>
         <v/>
       </c>
-      <c r="M27" s="31">
+      <c r="M27" s="26">
         <f>COUNTIF(C27:K27,"Y")</f>
         <v/>
       </c>
-      <c r="N27" s="32">
+      <c r="N27" s="27">
         <f>SUMPRODUCT((C$7:$K$7=1)*(C27:K27="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="17" customHeight="1">
-      <c r="A28" s="34" t="n">
+      <c r="A28" s="29" t="n">
         <v>9</v>
       </c>
-      <c r="B28" s="35" t="inlineStr">
+      <c r="B28" s="30" t="inlineStr">
         <is>
           <t>Jada</t>
         </is>
       </c>
-      <c r="C28" s="36" t="n"/>
-      <c r="D28" s="36" t="n"/>
-      <c r="E28" s="36" t="n"/>
-      <c r="F28" s="36" t="n"/>
-      <c r="G28" s="36" t="n"/>
-      <c r="H28" s="36" t="n"/>
-      <c r="I28" s="36" t="n"/>
-      <c r="J28" s="36" t="n"/>
-      <c r="K28" s="36" t="n"/>
-      <c r="L28" s="18">
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+      <c r="E28" s="31" t="n"/>
+      <c r="F28" s="31" t="n"/>
+      <c r="G28" s="31" t="n"/>
+      <c r="H28" s="31" t="n"/>
+      <c r="I28" s="31" t="n"/>
+      <c r="J28" s="31" t="n"/>
+      <c r="K28" s="31" t="n"/>
+      <c r="L28" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$K$7,C28:K28,"Y"),"")</f>
         <v/>
       </c>
-      <c r="M28" s="31">
+      <c r="M28" s="26">
         <f>COUNTIF(C28:K28,"Y")</f>
         <v/>
       </c>
-      <c r="N28" s="32">
+      <c r="N28" s="27">
         <f>SUMPRODUCT((C$7:$K$7=1)*(C28:K28="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="17" customHeight="1">
-      <c r="A29" s="37" t="n">
+      <c r="A29" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="B29" s="38" t="inlineStr">
+      <c r="B29" s="33" t="inlineStr">
         <is>
           <t>Jeremiah</t>
         </is>
       </c>
-      <c r="C29" s="19" t="n"/>
-      <c r="D29" s="19" t="n"/>
-      <c r="E29" s="19" t="n"/>
-      <c r="F29" s="19" t="n"/>
-      <c r="G29" s="19" t="n"/>
-      <c r="H29" s="19" t="n"/>
-      <c r="I29" s="19" t="n"/>
-      <c r="J29" s="19" t="n"/>
-      <c r="K29" s="19" t="n"/>
-      <c r="L29" s="18">
+      <c r="C29" s="18" t="n"/>
+      <c r="D29" s="18" t="n"/>
+      <c r="E29" s="18" t="n"/>
+      <c r="F29" s="18" t="n"/>
+      <c r="G29" s="18" t="n"/>
+      <c r="H29" s="18" t="n"/>
+      <c r="I29" s="18" t="n"/>
+      <c r="J29" s="18" t="n"/>
+      <c r="K29" s="18" t="n"/>
+      <c r="L29" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$K$7,C29:K29,"Y"),"")</f>
         <v/>
       </c>
-      <c r="M29" s="31">
+      <c r="M29" s="26">
         <f>COUNTIF(C29:K29,"Y")</f>
         <v/>
       </c>
-      <c r="N29" s="32">
+      <c r="N29" s="27">
         <f>SUMPRODUCT((C$7:$K$7=1)*(C29:K29="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="17" customHeight="1">
-      <c r="A30" s="34" t="n">
+      <c r="A30" s="29" t="n">
         <v>11</v>
       </c>
-      <c r="B30" s="35" t="inlineStr">
+      <c r="B30" s="30" t="inlineStr">
         <is>
           <t>Kable</t>
         </is>
       </c>
-      <c r="C30" s="36" t="n"/>
-      <c r="D30" s="36" t="n"/>
-      <c r="E30" s="36" t="n"/>
-      <c r="F30" s="36" t="n"/>
-      <c r="G30" s="36" t="n"/>
-      <c r="H30" s="36" t="n"/>
-      <c r="I30" s="36" t="n"/>
-      <c r="J30" s="36" t="n"/>
-      <c r="K30" s="36" t="n"/>
-      <c r="L30" s="18">
+      <c r="C30" s="31" t="n"/>
+      <c r="D30" s="31" t="n"/>
+      <c r="E30" s="31" t="n"/>
+      <c r="F30" s="31" t="n"/>
+      <c r="G30" s="31" t="n"/>
+      <c r="H30" s="31" t="n"/>
+      <c r="I30" s="31" t="n"/>
+      <c r="J30" s="31" t="n"/>
+      <c r="K30" s="31" t="n"/>
+      <c r="L30" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$K$7,C30:K30,"Y"),"")</f>
         <v/>
       </c>
-      <c r="M30" s="31">
+      <c r="M30" s="26">
         <f>COUNTIF(C30:K30,"Y")</f>
         <v/>
       </c>
-      <c r="N30" s="32">
+      <c r="N30" s="27">
         <f>SUMPRODUCT((C$7:$K$7=1)*(C30:K30="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="17" customHeight="1">
-      <c r="A31" s="37" t="n">
+      <c r="A31" s="32" t="n">
         <v>12</v>
       </c>
-      <c r="B31" s="38" t="inlineStr">
+      <c r="B31" s="33" t="inlineStr">
         <is>
           <t>Kayla</t>
         </is>
       </c>
-      <c r="C31" s="19" t="n"/>
-      <c r="D31" s="19" t="n"/>
-      <c r="E31" s="19" t="n"/>
-      <c r="F31" s="19" t="n"/>
-      <c r="G31" s="19" t="n"/>
-      <c r="H31" s="19" t="n"/>
-      <c r="I31" s="19" t="n"/>
-      <c r="J31" s="19" t="n"/>
-      <c r="K31" s="19" t="n"/>
-      <c r="L31" s="18">
+      <c r="C31" s="18" t="n"/>
+      <c r="D31" s="18" t="n"/>
+      <c r="E31" s="18" t="n"/>
+      <c r="F31" s="18" t="n"/>
+      <c r="G31" s="18" t="n"/>
+      <c r="H31" s="18" t="n"/>
+      <c r="I31" s="18" t="n"/>
+      <c r="J31" s="18" t="n"/>
+      <c r="K31" s="18" t="n"/>
+      <c r="L31" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$K$7,C31:K31,"Y"),"")</f>
         <v/>
       </c>
-      <c r="M31" s="31">
+      <c r="M31" s="26">
         <f>COUNTIF(C31:K31,"Y")</f>
         <v/>
       </c>
-      <c r="N31" s="32">
+      <c r="N31" s="27">
         <f>SUMPRODUCT((C$7:$K$7=1)*(C31:K31="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="17" customHeight="1">
-      <c r="A32" s="34" t="n">
+      <c r="A32" s="29" t="n">
         <v>13</v>
       </c>
-      <c r="B32" s="35" t="inlineStr">
+      <c r="B32" s="30" t="inlineStr">
         <is>
           <t>Kenzie</t>
         </is>
       </c>
-      <c r="C32" s="36" t="n"/>
-      <c r="D32" s="36" t="n"/>
-      <c r="E32" s="36" t="n"/>
-      <c r="F32" s="36" t="n"/>
-      <c r="G32" s="36" t="n"/>
-      <c r="H32" s="36" t="n"/>
-      <c r="I32" s="36" t="n"/>
-      <c r="J32" s="36" t="n"/>
-      <c r="K32" s="36" t="n"/>
-      <c r="L32" s="18">
+      <c r="C32" s="31" t="n"/>
+      <c r="D32" s="31" t="n"/>
+      <c r="E32" s="31" t="n"/>
+      <c r="F32" s="31" t="n"/>
+      <c r="G32" s="31" t="n"/>
+      <c r="H32" s="31" t="n"/>
+      <c r="I32" s="31" t="n"/>
+      <c r="J32" s="31" t="n"/>
+      <c r="K32" s="31" t="n"/>
+      <c r="L32" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$K$7,C32:K32,"Y"),"")</f>
         <v/>
       </c>
-      <c r="M32" s="31">
+      <c r="M32" s="26">
         <f>COUNTIF(C32:K32,"Y")</f>
         <v/>
       </c>
-      <c r="N32" s="32">
+      <c r="N32" s="27">
         <f>SUMPRODUCT((C$7:$K$7=1)*(C32:K32="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="17" customHeight="1">
-      <c r="A33" s="37" t="n">
+      <c r="A33" s="32" t="n">
         <v>14</v>
       </c>
-      <c r="B33" s="38" t="inlineStr">
+      <c r="B33" s="33" t="inlineStr">
         <is>
           <t>Lidy</t>
         </is>
       </c>
-      <c r="C33" s="19" t="n"/>
-      <c r="D33" s="19" t="n"/>
-      <c r="E33" s="19" t="n"/>
-      <c r="F33" s="19" t="n"/>
-      <c r="G33" s="19" t="n"/>
-      <c r="H33" s="19" t="n"/>
-      <c r="I33" s="19" t="n"/>
-      <c r="J33" s="19" t="n"/>
-      <c r="K33" s="30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L33" s="18">
+      <c r="C33" s="18" t="n"/>
+      <c r="D33" s="18" t="n"/>
+      <c r="E33" s="18" t="n"/>
+      <c r="F33" s="18" t="n"/>
+      <c r="G33" s="18" t="n"/>
+      <c r="H33" s="18" t="n"/>
+      <c r="I33" s="18" t="n"/>
+      <c r="J33" s="18" t="n"/>
+      <c r="K33" s="41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L33" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$K$7,C33:K33,"Y"),"")</f>
         <v/>
       </c>
-      <c r="M33" s="31">
+      <c r="M33" s="26">
         <f>COUNTIF(C33:K33,"Y")</f>
         <v/>
       </c>
-      <c r="N33" s="32">
+      <c r="N33" s="27">
         <f>SUMPRODUCT((C$7:$K$7=1)*(C33:K33="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="17" customHeight="1">
-      <c r="A34" s="34" t="n">
+      <c r="A34" s="29" t="n">
         <v>15</v>
       </c>
-      <c r="B34" s="35" t="inlineStr">
+      <c r="B34" s="30" t="inlineStr">
         <is>
           <t>Maylin</t>
         </is>
       </c>
-      <c r="C34" s="36" t="n"/>
-      <c r="D34" s="36" t="n"/>
-      <c r="E34" s="36" t="n"/>
-      <c r="F34" s="36" t="n"/>
-      <c r="G34" s="36" t="n"/>
-      <c r="H34" s="36" t="n"/>
-      <c r="I34" s="36" t="n"/>
-      <c r="J34" s="36" t="n"/>
-      <c r="K34" s="36" t="n"/>
-      <c r="L34" s="18">
+      <c r="C34" s="31" t="n"/>
+      <c r="D34" s="31" t="n"/>
+      <c r="E34" s="31" t="n"/>
+      <c r="F34" s="31" t="n"/>
+      <c r="G34" s="31" t="n"/>
+      <c r="H34" s="31" t="n"/>
+      <c r="I34" s="31" t="n"/>
+      <c r="J34" s="31" t="n"/>
+      <c r="K34" s="31" t="n"/>
+      <c r="L34" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$K$7,C34:K34,"Y"),"")</f>
         <v/>
       </c>
-      <c r="M34" s="31">
+      <c r="M34" s="26">
         <f>COUNTIF(C34:K34,"Y")</f>
         <v/>
       </c>
-      <c r="N34" s="32">
+      <c r="N34" s="27">
         <f>SUMPRODUCT((C$7:$K$7=1)*(C34:K34="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="17" customHeight="1">
-      <c r="A35" s="37" t="n">
+      <c r="A35" s="32" t="n">
         <v>16</v>
       </c>
-      <c r="B35" s="38" t="inlineStr">
+      <c r="B35" s="33" t="inlineStr">
         <is>
           <t>Mike</t>
         </is>
       </c>
-      <c r="C35" s="19" t="n"/>
-      <c r="D35" s="19" t="n"/>
-      <c r="E35" s="19" t="n"/>
-      <c r="F35" s="19" t="n"/>
-      <c r="G35" s="19" t="n"/>
-      <c r="H35" s="19" t="n"/>
-      <c r="I35" s="19" t="n"/>
-      <c r="J35" s="19" t="n"/>
-      <c r="K35" s="19" t="n"/>
-      <c r="L35" s="18">
+      <c r="C35" s="18" t="n"/>
+      <c r="D35" s="18" t="n"/>
+      <c r="E35" s="18" t="n"/>
+      <c r="F35" s="18" t="n"/>
+      <c r="G35" s="18" t="n"/>
+      <c r="H35" s="18" t="n"/>
+      <c r="I35" s="18" t="n"/>
+      <c r="J35" s="18" t="n"/>
+      <c r="K35" s="18" t="n"/>
+      <c r="L35" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$K$7,C35:K35,"Y"),"")</f>
         <v/>
       </c>
-      <c r="M35" s="31">
+      <c r="M35" s="26">
         <f>COUNTIF(C35:K35,"Y")</f>
         <v/>
       </c>
-      <c r="N35" s="32">
+      <c r="N35" s="27">
         <f>SUMPRODUCT((C$7:$K$7=1)*(C35:K35="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="17" customHeight="1">
-      <c r="A36" s="34" t="n">
+      <c r="A36" s="29" t="n">
         <v>17</v>
       </c>
-      <c r="B36" s="35" t="inlineStr">
+      <c r="B36" s="30" t="inlineStr">
         <is>
           <t>Richard</t>
         </is>
       </c>
-      <c r="C36" s="36" t="n"/>
-      <c r="D36" s="36" t="n"/>
-      <c r="E36" s="36" t="n"/>
-      <c r="F36" s="36" t="n"/>
-      <c r="G36" s="36" t="n"/>
-      <c r="H36" s="36" t="n"/>
-      <c r="I36" s="36" t="n"/>
-      <c r="J36" s="36" t="n"/>
-      <c r="K36" s="36" t="n"/>
-      <c r="L36" s="18">
+      <c r="C36" s="31" t="n"/>
+      <c r="D36" s="31" t="n"/>
+      <c r="E36" s="31" t="n"/>
+      <c r="F36" s="31" t="n"/>
+      <c r="G36" s="31" t="n"/>
+      <c r="H36" s="31" t="n"/>
+      <c r="I36" s="31" t="n"/>
+      <c r="J36" s="31" t="n"/>
+      <c r="K36" s="31" t="n"/>
+      <c r="L36" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$K$7,C36:K36,"Y"),"")</f>
         <v/>
       </c>
-      <c r="M36" s="31">
+      <c r="M36" s="26">
         <f>COUNTIF(C36:K36,"Y")</f>
         <v/>
       </c>
-      <c r="N36" s="32">
+      <c r="N36" s="27">
         <f>SUMPRODUCT((C$7:$K$7=1)*(C36:K36="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="17" customHeight="1">
-      <c r="A37" s="37" t="n">
+      <c r="A37" s="32" t="n">
         <v>18</v>
       </c>
-      <c r="B37" s="38" t="inlineStr">
+      <c r="B37" s="33" t="inlineStr">
         <is>
           <t>Samuel</t>
         </is>
       </c>
-      <c r="C37" s="19" t="n"/>
-      <c r="D37" s="19" t="n"/>
-      <c r="E37" s="19" t="n"/>
-      <c r="F37" s="19" t="n"/>
-      <c r="G37" s="19" t="n"/>
-      <c r="H37" s="19" t="n"/>
-      <c r="I37" s="19" t="n"/>
-      <c r="J37" s="19" t="n"/>
-      <c r="K37" s="19" t="n"/>
-      <c r="L37" s="18">
+      <c r="C37" s="18" t="n"/>
+      <c r="D37" s="18" t="n"/>
+      <c r="E37" s="18" t="n"/>
+      <c r="F37" s="18" t="n"/>
+      <c r="G37" s="18" t="n"/>
+      <c r="H37" s="18" t="n"/>
+      <c r="I37" s="18" t="n"/>
+      <c r="J37" s="18" t="n"/>
+      <c r="K37" s="18" t="n"/>
+      <c r="L37" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$K$7,C37:K37,"Y"),"")</f>
         <v/>
       </c>
-      <c r="M37" s="31">
+      <c r="M37" s="26">
         <f>COUNTIF(C37:K37,"Y")</f>
         <v/>
       </c>
-      <c r="N37" s="32">
+      <c r="N37" s="27">
         <f>SUMPRODUCT((C$7:$K$7=1)*(C37:K37="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="17" customHeight="1">
-      <c r="A38" s="34" t="n">
+      <c r="A38" s="29" t="n">
         <v>19</v>
       </c>
-      <c r="B38" s="35" t="inlineStr">
+      <c r="B38" s="30" t="inlineStr">
         <is>
           <t>Zach</t>
         </is>
       </c>
-      <c r="C38" s="36" t="n"/>
-      <c r="D38" s="36" t="n"/>
-      <c r="E38" s="36" t="n"/>
-      <c r="F38" s="36" t="n"/>
-      <c r="G38" s="36" t="n"/>
-      <c r="H38" s="36" t="n"/>
-      <c r="I38" s="36" t="n"/>
-      <c r="J38" s="36" t="n"/>
-      <c r="K38" s="36" t="n"/>
-      <c r="L38" s="18">
+      <c r="C38" s="31" t="n"/>
+      <c r="D38" s="31" t="n"/>
+      <c r="E38" s="31" t="n"/>
+      <c r="F38" s="31" t="n"/>
+      <c r="G38" s="31" t="n"/>
+      <c r="H38" s="31" t="n"/>
+      <c r="I38" s="31" t="n"/>
+      <c r="J38" s="31" t="n"/>
+      <c r="K38" s="31" t="n"/>
+      <c r="L38" s="17">
         <f>IFERROR(AVERAGEIFS($C$7:$K$7,C38:K38,"Y"),"")</f>
         <v/>
       </c>
-      <c r="M38" s="31">
+      <c r="M38" s="26">
         <f>COUNTIF(C38:K38,"Y")</f>
         <v/>
       </c>
-      <c r="N38" s="32">
+      <c r="N38" s="27">
         <f>SUMPRODUCT((C$7:$K$7=1)*(C38:K38="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="3" t="inlineStr"/>
-      <c r="B39" s="39" t="inlineStr">
+      <c r="B39" s="34" t="inlineStr">
         <is>
           <t>Total on shift</t>
         </is>
@@ -8242,13 +7694,13 @@
         <f>SUM(M14:M38)</f>
         <v/>
       </c>
-      <c r="N39" s="40">
+      <c r="N39" s="35">
         <f>SUM(N14:N38)</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="12" customHeight="1">
-      <c r="A40" s="41" t="inlineStr">
+      <c r="A40" s="36" t="inlineStr">
         <is>
           <t>Y = on shift during shop's meal window. Personal Avg = average score of shops worked. Bonus = $50 per 100% shop worked.</t>
         </is>

--- a/Shop_Tracker_2065_2026.xlsx
+++ b/Shop_Tracker_2065_2026.xlsx
@@ -105,6 +105,12 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="004A7A0F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <color rgb="001A1A1A"/>
       <sz val="9"/>
     </font>
@@ -141,12 +147,6 @@
       <i val="1"/>
       <color rgb="00595959"/>
       <sz val="7"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="004A7A0F"/>
-      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -220,6 +220,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00EFF8E8"/>
+        <bgColor rgb="00EFF8E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00F9F9F9"/>
         <bgColor rgb="00F9F9F9"/>
       </patternFill>
@@ -246,12 +252,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EFF8E8"/>
-        <bgColor rgb="00EFF8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -331,80 +331,80 @@
     <xf numFmtId="9" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="13" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="20" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="21" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="21" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="22" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="22" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="23" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="23" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="24" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="24" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -772,7 +772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O40"/>
+  <dimension ref="A1:W40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -787,9 +787,17 @@
     <col width="7" customWidth="1" min="10" max="10"/>
     <col width="7" customWidth="1" min="11" max="11"/>
     <col width="7" customWidth="1" min="12" max="12"/>
-    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="7" customWidth="1" min="13" max="13"/>
     <col width="7" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="7" customWidth="1" min="15" max="15"/>
+    <col width="7" customWidth="1" min="16" max="16"/>
+    <col width="7" customWidth="1" min="17" max="17"/>
+    <col width="7" customWidth="1" min="18" max="18"/>
+    <col width="7" customWidth="1" min="19" max="19"/>
+    <col width="7" customWidth="1" min="20" max="20"/>
+    <col width="9" customWidth="1" min="21" max="21"/>
+    <col width="7" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -802,7 +810,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Five Guys Store 2065 · Louisville, KY · 10 shops · Source: Marketforce + CrunchTime</t>
+          <t>Five Guys Store 2065 · Louisville, KY · 18 shops · Source: Marketforce + CrunchTime</t>
         </is>
       </c>
     </row>
@@ -864,17 +872,57 @@
           <t>#10</t>
         </is>
       </c>
-      <c r="M4" s="6" t="inlineStr">
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>#11</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t>#12</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="inlineStr">
+        <is>
+          <t>#13</t>
+        </is>
+      </c>
+      <c r="P4" s="5" t="inlineStr">
+        <is>
+          <t>#14</t>
+        </is>
+      </c>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t>#15</t>
+        </is>
+      </c>
+      <c r="R4" s="5" t="inlineStr">
+        <is>
+          <t>#16</t>
+        </is>
+      </c>
+      <c r="S4" s="5" t="inlineStr">
+        <is>
+          <t>#17</t>
+        </is>
+      </c>
+      <c r="T4" s="5" t="inlineStr">
+        <is>
+          <t>#18</t>
+        </is>
+      </c>
+      <c r="U4" s="6" t="inlineStr">
         <is>
           <t>AVG</t>
         </is>
       </c>
-      <c r="N4" s="6" t="inlineStr">
+      <c r="V4" s="6" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="O4" s="6" t="inlineStr">
+      <c r="W4" s="6" t="inlineStr">
         <is>
           <t>BONUS</t>
         </is>
@@ -937,9 +985,49 @@
           <t>01/31</t>
         </is>
       </c>
-      <c r="M5" s="7" t="inlineStr"/>
-      <c r="N5" s="7" t="inlineStr"/>
-      <c r="O5" s="7" t="inlineStr"/>
+      <c r="M5" s="9" t="inlineStr">
+        <is>
+          <t>01/05</t>
+        </is>
+      </c>
+      <c r="N5" s="9" t="inlineStr">
+        <is>
+          <t>01/09</t>
+        </is>
+      </c>
+      <c r="O5" s="9" t="inlineStr">
+        <is>
+          <t>01/10</t>
+        </is>
+      </c>
+      <c r="P5" s="9" t="inlineStr">
+        <is>
+          <t>01/16</t>
+        </is>
+      </c>
+      <c r="Q5" s="9" t="inlineStr">
+        <is>
+          <t>01/23</t>
+        </is>
+      </c>
+      <c r="R5" s="9" t="inlineStr">
+        <is>
+          <t>01/28</t>
+        </is>
+      </c>
+      <c r="S5" s="9" t="inlineStr">
+        <is>
+          <t>01/29</t>
+        </is>
+      </c>
+      <c r="T5" s="9" t="inlineStr">
+        <is>
+          <t>01/31</t>
+        </is>
+      </c>
+      <c r="U5" s="7" t="inlineStr"/>
+      <c r="V5" s="7" t="inlineStr"/>
+      <c r="W5" s="7" t="inlineStr"/>
     </row>
     <row r="6" ht="14" customHeight="1">
       <c r="A6" s="7" t="inlineStr"/>
@@ -998,9 +1086,49 @@
           <t>D</t>
         </is>
       </c>
-      <c r="M6" s="7" t="inlineStr"/>
-      <c r="N6" s="7" t="inlineStr"/>
-      <c r="O6" s="7" t="inlineStr"/>
+      <c r="M6" s="11" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="O6" s="11" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="P6" s="10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Q6" s="11" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R6" s="10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="T6" s="11" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="U6" s="7" t="inlineStr"/>
+      <c r="V6" s="7" t="inlineStr"/>
+      <c r="W6" s="7" t="inlineStr"/>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="12" t="inlineStr"/>
@@ -1039,868 +1167,1376 @@
       <c r="L7" s="16" t="n">
         <v>0.48</v>
       </c>
-      <c r="M7" s="17">
-        <f>IFERROR(AVERAGE(C7:L7),"")</f>
-        <v/>
-      </c>
-      <c r="N7" s="12" t="inlineStr"/>
-      <c r="O7" s="12" t="inlineStr"/>
+      <c r="M7" s="17" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="N7" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="15" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P7" s="16" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="Q7" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" s="15" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="T7" s="15" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="U7" s="18">
+        <f>IFERROR(AVERAGE(C7:T7),"")</f>
+        <v/>
+      </c>
+      <c r="V7" s="12" t="inlineStr"/>
+      <c r="W7" s="12" t="inlineStr"/>
     </row>
     <row r="8" ht="13" customHeight="1">
-      <c r="A8" s="18" t="inlineStr"/>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr"/>
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr"/>
-      <c r="D8" s="18" t="inlineStr"/>
-      <c r="E8" s="18" t="inlineStr"/>
-      <c r="F8" s="18" t="inlineStr"/>
-      <c r="G8" s="18" t="inlineStr"/>
-      <c r="H8" s="18" t="inlineStr"/>
-      <c r="I8" s="18" t="inlineStr"/>
-      <c r="J8" s="18" t="inlineStr"/>
-      <c r="K8" s="18" t="inlineStr"/>
-      <c r="L8" s="18" t="inlineStr"/>
-      <c r="M8" s="20">
-        <f>IFERROR(AVERAGE(C8:L8),"")</f>
-        <v/>
-      </c>
-      <c r="N8" s="18" t="inlineStr"/>
-      <c r="O8" s="18" t="inlineStr"/>
+      <c r="C8" s="19" t="inlineStr"/>
+      <c r="D8" s="19" t="inlineStr"/>
+      <c r="E8" s="19" t="inlineStr"/>
+      <c r="F8" s="19" t="inlineStr"/>
+      <c r="G8" s="19" t="inlineStr"/>
+      <c r="H8" s="19" t="inlineStr"/>
+      <c r="I8" s="19" t="inlineStr"/>
+      <c r="J8" s="19" t="inlineStr"/>
+      <c r="K8" s="19" t="inlineStr"/>
+      <c r="L8" s="19" t="inlineStr"/>
+      <c r="M8" s="19" t="inlineStr"/>
+      <c r="N8" s="19" t="inlineStr"/>
+      <c r="O8" s="19" t="inlineStr"/>
+      <c r="P8" s="19" t="inlineStr"/>
+      <c r="Q8" s="19" t="inlineStr"/>
+      <c r="R8" s="19" t="inlineStr"/>
+      <c r="S8" s="19" t="inlineStr"/>
+      <c r="T8" s="19" t="inlineStr"/>
+      <c r="U8" s="21">
+        <f>IFERROR(AVERAGE(C8:T8),"")</f>
+        <v/>
+      </c>
+      <c r="V8" s="19" t="inlineStr"/>
+      <c r="W8" s="19" t="inlineStr"/>
     </row>
     <row r="9" ht="13" customHeight="1">
-      <c r="A9" s="18" t="inlineStr"/>
-      <c r="B9" s="19" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr"/>
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>Quality</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr"/>
-      <c r="D9" s="18" t="inlineStr"/>
-      <c r="E9" s="18" t="inlineStr"/>
-      <c r="F9" s="18" t="inlineStr"/>
-      <c r="G9" s="18" t="inlineStr"/>
-      <c r="H9" s="18" t="inlineStr"/>
-      <c r="I9" s="18" t="inlineStr"/>
-      <c r="J9" s="18" t="inlineStr"/>
-      <c r="K9" s="18" t="inlineStr"/>
-      <c r="L9" s="18" t="inlineStr"/>
-      <c r="M9" s="20">
-        <f>IFERROR(AVERAGE(C9:L9),"")</f>
-        <v/>
-      </c>
-      <c r="N9" s="18" t="inlineStr"/>
-      <c r="O9" s="18" t="inlineStr"/>
+      <c r="C9" s="19" t="inlineStr"/>
+      <c r="D9" s="19" t="inlineStr"/>
+      <c r="E9" s="19" t="inlineStr"/>
+      <c r="F9" s="19" t="inlineStr"/>
+      <c r="G9" s="19" t="inlineStr"/>
+      <c r="H9" s="19" t="inlineStr"/>
+      <c r="I9" s="19" t="inlineStr"/>
+      <c r="J9" s="19" t="inlineStr"/>
+      <c r="K9" s="19" t="inlineStr"/>
+      <c r="L9" s="19" t="inlineStr"/>
+      <c r="M9" s="19" t="inlineStr"/>
+      <c r="N9" s="19" t="inlineStr"/>
+      <c r="O9" s="19" t="inlineStr"/>
+      <c r="P9" s="19" t="inlineStr"/>
+      <c r="Q9" s="19" t="inlineStr"/>
+      <c r="R9" s="19" t="inlineStr"/>
+      <c r="S9" s="19" t="inlineStr"/>
+      <c r="T9" s="19" t="inlineStr"/>
+      <c r="U9" s="21">
+        <f>IFERROR(AVERAGE(C9:T9),"")</f>
+        <v/>
+      </c>
+      <c r="V9" s="19" t="inlineStr"/>
+      <c r="W9" s="19" t="inlineStr"/>
     </row>
     <row r="10" ht="13" customHeight="1">
-      <c r="A10" s="18" t="inlineStr"/>
-      <c r="B10" s="19" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr"/>
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>Cleanliness</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr"/>
-      <c r="D10" s="18" t="inlineStr"/>
-      <c r="E10" s="18" t="inlineStr"/>
-      <c r="F10" s="18" t="inlineStr"/>
-      <c r="G10" s="18" t="inlineStr"/>
-      <c r="H10" s="18" t="inlineStr"/>
-      <c r="I10" s="18" t="inlineStr"/>
-      <c r="J10" s="18" t="inlineStr"/>
-      <c r="K10" s="18" t="inlineStr"/>
-      <c r="L10" s="18" t="inlineStr"/>
-      <c r="M10" s="20">
-        <f>IFERROR(AVERAGE(C10:L10),"")</f>
-        <v/>
-      </c>
-      <c r="N10" s="18" t="inlineStr"/>
-      <c r="O10" s="18" t="inlineStr"/>
+      <c r="C10" s="19" t="inlineStr"/>
+      <c r="D10" s="19" t="inlineStr"/>
+      <c r="E10" s="19" t="inlineStr"/>
+      <c r="F10" s="19" t="inlineStr"/>
+      <c r="G10" s="19" t="inlineStr"/>
+      <c r="H10" s="19" t="inlineStr"/>
+      <c r="I10" s="19" t="inlineStr"/>
+      <c r="J10" s="19" t="inlineStr"/>
+      <c r="K10" s="19" t="inlineStr"/>
+      <c r="L10" s="19" t="inlineStr"/>
+      <c r="M10" s="19" t="inlineStr"/>
+      <c r="N10" s="19" t="inlineStr"/>
+      <c r="O10" s="19" t="inlineStr"/>
+      <c r="P10" s="19" t="inlineStr"/>
+      <c r="Q10" s="19" t="inlineStr"/>
+      <c r="R10" s="19" t="inlineStr"/>
+      <c r="S10" s="19" t="inlineStr"/>
+      <c r="T10" s="19" t="inlineStr"/>
+      <c r="U10" s="21">
+        <f>IFERROR(AVERAGE(C10:T10),"")</f>
+        <v/>
+      </c>
+      <c r="V10" s="19" t="inlineStr"/>
+      <c r="W10" s="19" t="inlineStr"/>
     </row>
     <row r="11" ht="13" customHeight="1">
-      <c r="A11" s="18" t="inlineStr"/>
-      <c r="B11" s="19" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr"/>
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>Customer Sat</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr"/>
-      <c r="D11" s="18" t="inlineStr"/>
-      <c r="E11" s="18" t="inlineStr"/>
-      <c r="F11" s="18" t="inlineStr"/>
-      <c r="G11" s="18" t="inlineStr"/>
-      <c r="H11" s="18" t="inlineStr"/>
-      <c r="I11" s="18" t="inlineStr"/>
-      <c r="J11" s="18" t="inlineStr"/>
-      <c r="K11" s="18" t="inlineStr"/>
-      <c r="L11" s="18" t="inlineStr"/>
-      <c r="M11" s="20">
-        <f>IFERROR(AVERAGE(C11:L11),"")</f>
-        <v/>
-      </c>
-      <c r="N11" s="18" t="inlineStr"/>
-      <c r="O11" s="18" t="inlineStr"/>
+      <c r="C11" s="19" t="inlineStr"/>
+      <c r="D11" s="19" t="inlineStr"/>
+      <c r="E11" s="19" t="inlineStr"/>
+      <c r="F11" s="19" t="inlineStr"/>
+      <c r="G11" s="19" t="inlineStr"/>
+      <c r="H11" s="19" t="inlineStr"/>
+      <c r="I11" s="19" t="inlineStr"/>
+      <c r="J11" s="19" t="inlineStr"/>
+      <c r="K11" s="19" t="inlineStr"/>
+      <c r="L11" s="19" t="inlineStr"/>
+      <c r="M11" s="19" t="inlineStr"/>
+      <c r="N11" s="19" t="inlineStr"/>
+      <c r="O11" s="19" t="inlineStr"/>
+      <c r="P11" s="19" t="inlineStr"/>
+      <c r="Q11" s="19" t="inlineStr"/>
+      <c r="R11" s="19" t="inlineStr"/>
+      <c r="S11" s="19" t="inlineStr"/>
+      <c r="T11" s="19" t="inlineStr"/>
+      <c r="U11" s="21">
+        <f>IFERROR(AVERAGE(C11:T11),"")</f>
+        <v/>
+      </c>
+      <c r="V11" s="19" t="inlineStr"/>
+      <c r="W11" s="19" t="inlineStr"/>
     </row>
     <row r="12" ht="6" customHeight="1">
-      <c r="A12" s="21" t="n"/>
+      <c r="A12" s="22" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="22" t="inlineStr">
+      <c r="A13" s="23" t="inlineStr">
         <is>
           <t>MANAGERS</t>
         </is>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="B14" s="24" t="inlineStr">
+      <c r="A14" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" s="25" t="inlineStr">
         <is>
           <t>Madison C.</t>
         </is>
       </c>
-      <c r="C14" s="25" t="n"/>
-      <c r="D14" s="25" t="n"/>
-      <c r="E14" s="25" t="n"/>
-      <c r="F14" s="25" t="n"/>
-      <c r="G14" s="25" t="n"/>
-      <c r="H14" s="25" t="n"/>
-      <c r="I14" s="25" t="n"/>
-      <c r="J14" s="25" t="n"/>
-      <c r="K14" s="25" t="n"/>
-      <c r="L14" s="25" t="n"/>
-      <c r="M14" s="17">
-        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C14:L14,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="N14" s="26">
-        <f>COUNTIF(C14:L14,"Y")</f>
-        <v/>
-      </c>
-      <c r="O14" s="27">
-        <f>SUMPRODUCT((C$7:$L$7=1)*(C14:L14="Y"))*50</f>
+      <c r="C14" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D14" s="27" t="n"/>
+      <c r="E14" s="27" t="n"/>
+      <c r="F14" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G14" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H14" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I14" s="27" t="n"/>
+      <c r="J14" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K14" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L14" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M14" s="27" t="n"/>
+      <c r="N14" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O14" s="27" t="n"/>
+      <c r="P14" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q14" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R14" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S14" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T14" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="U14" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$T$7,C14:T14,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="V14" s="28">
+        <f>COUNTIF(C14:T14,"Y")</f>
+        <v/>
+      </c>
+      <c r="W14" s="29">
+        <f>SUMPRODUCT((C$7:$T$7=1)*(C14:T14="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="23" t="n">
+      <c r="A15" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="B15" s="24" t="inlineStr">
+      <c r="B15" s="25" t="inlineStr">
         <is>
           <t>Vicki L.</t>
         </is>
       </c>
-      <c r="C15" s="25" t="n"/>
-      <c r="D15" s="25" t="n"/>
-      <c r="E15" s="25" t="n"/>
-      <c r="F15" s="25" t="n"/>
-      <c r="G15" s="25" t="n"/>
-      <c r="H15" s="25" t="n"/>
-      <c r="I15" s="25" t="n"/>
-      <c r="J15" s="25" t="n"/>
-      <c r="K15" s="25" t="n"/>
-      <c r="L15" s="25" t="n"/>
-      <c r="M15" s="17">
-        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C15:L15,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="N15" s="26">
-        <f>COUNTIF(C15:L15,"Y")</f>
-        <v/>
-      </c>
-      <c r="O15" s="27">
-        <f>SUMPRODUCT((C$7:$L$7=1)*(C15:L15="Y"))*50</f>
+      <c r="C15" s="27" t="n"/>
+      <c r="D15" s="27" t="n"/>
+      <c r="E15" s="27" t="n"/>
+      <c r="F15" s="27" t="n"/>
+      <c r="G15" s="27" t="n"/>
+      <c r="H15" s="27" t="n"/>
+      <c r="I15" s="27" t="n"/>
+      <c r="J15" s="27" t="n"/>
+      <c r="K15" s="27" t="n"/>
+      <c r="L15" s="27" t="n"/>
+      <c r="M15" s="27" t="n"/>
+      <c r="N15" s="27" t="n"/>
+      <c r="O15" s="27" t="n"/>
+      <c r="P15" s="27" t="n"/>
+      <c r="Q15" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R15" s="27" t="n"/>
+      <c r="S15" s="27" t="n"/>
+      <c r="T15" s="27" t="n"/>
+      <c r="U15" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$T$7,C15:T15,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="V15" s="28">
+        <f>COUNTIF(C15:T15,"Y")</f>
+        <v/>
+      </c>
+      <c r="W15" s="29">
+        <f>SUMPRODUCT((C$7:$T$7=1)*(C15:T15="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
-      <c r="A16" s="23" t="n">
+      <c r="A16" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="B16" s="24" t="inlineStr">
+      <c r="B16" s="25" t="inlineStr">
         <is>
           <t>Kasey W.</t>
         </is>
       </c>
-      <c r="C16" s="25" t="n"/>
-      <c r="D16" s="25" t="n"/>
-      <c r="E16" s="25" t="n"/>
-      <c r="F16" s="25" t="n"/>
-      <c r="G16" s="25" t="n"/>
-      <c r="H16" s="25" t="n"/>
-      <c r="I16" s="25" t="n"/>
-      <c r="J16" s="25" t="n"/>
-      <c r="K16" s="25" t="n"/>
-      <c r="L16" s="25" t="n"/>
-      <c r="M16" s="17">
-        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C16:L16,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="N16" s="26">
-        <f>COUNTIF(C16:L16,"Y")</f>
-        <v/>
-      </c>
-      <c r="O16" s="27">
-        <f>SUMPRODUCT((C$7:$L$7=1)*(C16:L16="Y"))*50</f>
+      <c r="C16" s="27" t="n"/>
+      <c r="D16" s="27" t="n"/>
+      <c r="E16" s="27" t="n"/>
+      <c r="F16" s="27" t="n"/>
+      <c r="G16" s="27" t="n"/>
+      <c r="H16" s="27" t="n"/>
+      <c r="I16" s="27" t="n"/>
+      <c r="J16" s="27" t="n"/>
+      <c r="K16" s="27" t="n"/>
+      <c r="L16" s="27" t="n"/>
+      <c r="M16" s="27" t="n"/>
+      <c r="N16" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O16" s="27" t="n"/>
+      <c r="P16" s="27" t="n"/>
+      <c r="Q16" s="27" t="n"/>
+      <c r="R16" s="27" t="n"/>
+      <c r="S16" s="27" t="n"/>
+      <c r="T16" s="27" t="n"/>
+      <c r="U16" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$T$7,C16:T16,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="V16" s="28">
+        <f>COUNTIF(C16:T16,"Y")</f>
+        <v/>
+      </c>
+      <c r="W16" s="29">
+        <f>SUMPRODUCT((C$7:$T$7=1)*(C16:T16="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
-      <c r="A17" s="23" t="n">
+      <c r="A17" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="B17" s="24" t="inlineStr">
+      <c r="B17" s="25" t="inlineStr">
         <is>
           <t>Nathan R.</t>
         </is>
       </c>
-      <c r="C17" s="25" t="n"/>
-      <c r="D17" s="25" t="n"/>
-      <c r="E17" s="25" t="n"/>
-      <c r="F17" s="25" t="n"/>
-      <c r="G17" s="25" t="n"/>
-      <c r="H17" s="25" t="n"/>
-      <c r="I17" s="25" t="n"/>
-      <c r="J17" s="25" t="n"/>
-      <c r="K17" s="25" t="n"/>
-      <c r="L17" s="25" t="n"/>
-      <c r="M17" s="17">
-        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C17:L17,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="N17" s="26">
-        <f>COUNTIF(C17:L17,"Y")</f>
-        <v/>
-      </c>
-      <c r="O17" s="27">
-        <f>SUMPRODUCT((C$7:$L$7=1)*(C17:L17="Y"))*50</f>
+      <c r="C17" s="27" t="n"/>
+      <c r="D17" s="27" t="n"/>
+      <c r="E17" s="27" t="n"/>
+      <c r="F17" s="27" t="n"/>
+      <c r="G17" s="27" t="n"/>
+      <c r="H17" s="27" t="n"/>
+      <c r="I17" s="27" t="n"/>
+      <c r="J17" s="27" t="n"/>
+      <c r="K17" s="27" t="n"/>
+      <c r="L17" s="27" t="n"/>
+      <c r="M17" s="27" t="n"/>
+      <c r="N17" s="27" t="n"/>
+      <c r="O17" s="27" t="n"/>
+      <c r="P17" s="27" t="n"/>
+      <c r="Q17" s="27" t="n"/>
+      <c r="R17" s="27" t="n"/>
+      <c r="S17" s="27" t="n"/>
+      <c r="T17" s="27" t="n"/>
+      <c r="U17" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$T$7,C17:T17,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="V17" s="28">
+        <f>COUNTIF(C17:T17,"Y")</f>
+        <v/>
+      </c>
+      <c r="W17" s="29">
+        <f>SUMPRODUCT((C$7:$T$7=1)*(C17:T17="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="6" customHeight="1">
-      <c r="A18" s="21" t="n"/>
+      <c r="A18" s="22" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="28" t="inlineStr">
+      <c r="A19" s="30" t="inlineStr">
         <is>
           <t>CREW</t>
         </is>
       </c>
     </row>
     <row r="20" ht="17" customHeight="1">
-      <c r="A20" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="B20" s="30" t="inlineStr">
+      <c r="A20" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" s="32" t="inlineStr">
         <is>
           <t>Alen</t>
         </is>
       </c>
-      <c r="C20" s="31" t="n"/>
-      <c r="D20" s="31" t="n"/>
-      <c r="E20" s="31" t="n"/>
-      <c r="F20" s="31" t="n"/>
-      <c r="G20" s="31" t="n"/>
-      <c r="H20" s="31" t="n"/>
-      <c r="I20" s="31" t="n"/>
-      <c r="J20" s="31" t="n"/>
-      <c r="K20" s="31" t="n"/>
-      <c r="L20" s="31" t="n"/>
-      <c r="M20" s="17">
-        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C20:L20,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="N20" s="26">
-        <f>COUNTIF(C20:L20,"Y")</f>
-        <v/>
-      </c>
-      <c r="O20" s="27">
-        <f>SUMPRODUCT((C$7:$L$7=1)*(C20:L20="Y"))*50</f>
+      <c r="C20" s="33" t="n"/>
+      <c r="D20" s="33" t="n"/>
+      <c r="E20" s="33" t="n"/>
+      <c r="F20" s="33" t="n"/>
+      <c r="G20" s="33" t="n"/>
+      <c r="H20" s="33" t="n"/>
+      <c r="I20" s="33" t="n"/>
+      <c r="J20" s="33" t="n"/>
+      <c r="K20" s="33" t="n"/>
+      <c r="L20" s="33" t="n"/>
+      <c r="M20" s="33" t="n"/>
+      <c r="N20" s="33" t="n"/>
+      <c r="O20" s="33" t="n"/>
+      <c r="P20" s="33" t="n"/>
+      <c r="Q20" s="33" t="n"/>
+      <c r="R20" s="33" t="n"/>
+      <c r="S20" s="33" t="n"/>
+      <c r="T20" s="33" t="n"/>
+      <c r="U20" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$T$7,C20:T20,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="V20" s="28">
+        <f>COUNTIF(C20:T20,"Y")</f>
+        <v/>
+      </c>
+      <c r="W20" s="29">
+        <f>SUMPRODUCT((C$7:$T$7=1)*(C20:T20="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="17" customHeight="1">
-      <c r="A21" s="32" t="n">
+      <c r="A21" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="B21" s="33" t="inlineStr">
+      <c r="B21" s="35" t="inlineStr">
         <is>
           <t>Ash</t>
         </is>
       </c>
-      <c r="C21" s="18" t="n"/>
-      <c r="D21" s="18" t="n"/>
-      <c r="E21" s="18" t="n"/>
-      <c r="F21" s="18" t="n"/>
-      <c r="G21" s="18" t="n"/>
-      <c r="H21" s="18" t="n"/>
-      <c r="I21" s="18" t="n"/>
-      <c r="J21" s="18" t="n"/>
-      <c r="K21" s="18" t="n"/>
-      <c r="L21" s="18" t="n"/>
-      <c r="M21" s="17">
-        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C21:L21,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="N21" s="26">
-        <f>COUNTIF(C21:L21,"Y")</f>
-        <v/>
-      </c>
-      <c r="O21" s="27">
-        <f>SUMPRODUCT((C$7:$L$7=1)*(C21:L21="Y"))*50</f>
+      <c r="C21" s="19" t="n"/>
+      <c r="D21" s="19" t="n"/>
+      <c r="E21" s="19" t="n"/>
+      <c r="F21" s="19" t="n"/>
+      <c r="G21" s="19" t="n"/>
+      <c r="H21" s="19" t="n"/>
+      <c r="I21" s="19" t="n"/>
+      <c r="J21" s="19" t="n"/>
+      <c r="K21" s="19" t="n"/>
+      <c r="L21" s="19" t="n"/>
+      <c r="M21" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N21" s="19" t="n"/>
+      <c r="O21" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P21" s="19" t="n"/>
+      <c r="Q21" s="19" t="n"/>
+      <c r="R21" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S21" s="19" t="n"/>
+      <c r="T21" s="19" t="n"/>
+      <c r="U21" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$T$7,C21:T21,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="V21" s="28">
+        <f>COUNTIF(C21:T21,"Y")</f>
+        <v/>
+      </c>
+      <c r="W21" s="29">
+        <f>SUMPRODUCT((C$7:$T$7=1)*(C21:T21="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="17" customHeight="1">
-      <c r="A22" s="29" t="n">
+      <c r="A22" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="B22" s="30" t="inlineStr">
+      <c r="B22" s="32" t="inlineStr">
         <is>
           <t>Autumn</t>
         </is>
       </c>
-      <c r="C22" s="31" t="n"/>
-      <c r="D22" s="31" t="n"/>
-      <c r="E22" s="31" t="n"/>
-      <c r="F22" s="31" t="n"/>
-      <c r="G22" s="31" t="n"/>
-      <c r="H22" s="31" t="n"/>
-      <c r="I22" s="31" t="n"/>
-      <c r="J22" s="31" t="n"/>
-      <c r="K22" s="31" t="n"/>
-      <c r="L22" s="31" t="n"/>
-      <c r="M22" s="17">
-        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C22:L22,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="N22" s="26">
-        <f>COUNTIF(C22:L22,"Y")</f>
-        <v/>
-      </c>
-      <c r="O22" s="27">
-        <f>SUMPRODUCT((C$7:$L$7=1)*(C22:L22="Y"))*50</f>
+      <c r="C22" s="33" t="n"/>
+      <c r="D22" s="33" t="n"/>
+      <c r="E22" s="33" t="n"/>
+      <c r="F22" s="33" t="n"/>
+      <c r="G22" s="33" t="n"/>
+      <c r="H22" s="33" t="n"/>
+      <c r="I22" s="33" t="n"/>
+      <c r="J22" s="33" t="n"/>
+      <c r="K22" s="33" t="n"/>
+      <c r="L22" s="33" t="n"/>
+      <c r="M22" s="33" t="n"/>
+      <c r="N22" s="33" t="n"/>
+      <c r="O22" s="33" t="n"/>
+      <c r="P22" s="33" t="n"/>
+      <c r="Q22" s="33" t="n"/>
+      <c r="R22" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S22" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T22" s="33" t="n"/>
+      <c r="U22" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$T$7,C22:T22,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="V22" s="28">
+        <f>COUNTIF(C22:T22,"Y")</f>
+        <v/>
+      </c>
+      <c r="W22" s="29">
+        <f>SUMPRODUCT((C$7:$T$7=1)*(C22:T22="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="17" customHeight="1">
-      <c r="A23" s="32" t="n">
+      <c r="A23" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="B23" s="33" t="inlineStr">
+      <c r="B23" s="35" t="inlineStr">
         <is>
           <t>Bri</t>
         </is>
       </c>
-      <c r="C23" s="18" t="n"/>
-      <c r="D23" s="18" t="n"/>
-      <c r="E23" s="18" t="n"/>
-      <c r="F23" s="18" t="n"/>
-      <c r="G23" s="18" t="n"/>
-      <c r="H23" s="18" t="n"/>
-      <c r="I23" s="18" t="n"/>
-      <c r="J23" s="18" t="n"/>
-      <c r="K23" s="18" t="n"/>
-      <c r="L23" s="18" t="n"/>
-      <c r="M23" s="17">
-        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C23:L23,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="N23" s="26">
-        <f>COUNTIF(C23:L23,"Y")</f>
-        <v/>
-      </c>
-      <c r="O23" s="27">
-        <f>SUMPRODUCT((C$7:$L$7=1)*(C23:L23="Y"))*50</f>
+      <c r="C23" s="19" t="n"/>
+      <c r="D23" s="19" t="n"/>
+      <c r="E23" s="19" t="n"/>
+      <c r="F23" s="19" t="n"/>
+      <c r="G23" s="19" t="n"/>
+      <c r="H23" s="19" t="n"/>
+      <c r="I23" s="19" t="n"/>
+      <c r="J23" s="19" t="n"/>
+      <c r="K23" s="19" t="n"/>
+      <c r="L23" s="19" t="n"/>
+      <c r="M23" s="19" t="n"/>
+      <c r="N23" s="19" t="n"/>
+      <c r="O23" s="19" t="n"/>
+      <c r="P23" s="19" t="n"/>
+      <c r="Q23" s="19" t="n"/>
+      <c r="R23" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S23" s="19" t="n"/>
+      <c r="T23" s="19" t="n"/>
+      <c r="U23" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$T$7,C23:T23,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="V23" s="28">
+        <f>COUNTIF(C23:T23,"Y")</f>
+        <v/>
+      </c>
+      <c r="W23" s="29">
+        <f>SUMPRODUCT((C$7:$T$7=1)*(C23:T23="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="17" customHeight="1">
-      <c r="A24" s="29" t="n">
+      <c r="A24" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="B24" s="30" t="inlineStr">
+      <c r="B24" s="32" t="inlineStr">
         <is>
           <t>Dakayla</t>
         </is>
       </c>
-      <c r="C24" s="31" t="n"/>
-      <c r="D24" s="31" t="n"/>
-      <c r="E24" s="31" t="n"/>
-      <c r="F24" s="31" t="n"/>
-      <c r="G24" s="31" t="n"/>
-      <c r="H24" s="31" t="n"/>
-      <c r="I24" s="31" t="n"/>
-      <c r="J24" s="31" t="n"/>
-      <c r="K24" s="31" t="n"/>
-      <c r="L24" s="31" t="n"/>
-      <c r="M24" s="17">
-        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C24:L24,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="N24" s="26">
-        <f>COUNTIF(C24:L24,"Y")</f>
-        <v/>
-      </c>
-      <c r="O24" s="27">
-        <f>SUMPRODUCT((C$7:$L$7=1)*(C24:L24="Y"))*50</f>
+      <c r="C24" s="33" t="n"/>
+      <c r="D24" s="33" t="n"/>
+      <c r="E24" s="33" t="n"/>
+      <c r="F24" s="33" t="n"/>
+      <c r="G24" s="33" t="n"/>
+      <c r="H24" s="33" t="n"/>
+      <c r="I24" s="33" t="n"/>
+      <c r="J24" s="33" t="n"/>
+      <c r="K24" s="33" t="n"/>
+      <c r="L24" s="33" t="n"/>
+      <c r="M24" s="33" t="n"/>
+      <c r="N24" s="33" t="n"/>
+      <c r="O24" s="33" t="n"/>
+      <c r="P24" s="33" t="n"/>
+      <c r="Q24" s="33" t="n"/>
+      <c r="R24" s="33" t="n"/>
+      <c r="S24" s="33" t="n"/>
+      <c r="T24" s="33" t="n"/>
+      <c r="U24" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$T$7,C24:T24,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="V24" s="28">
+        <f>COUNTIF(C24:T24,"Y")</f>
+        <v/>
+      </c>
+      <c r="W24" s="29">
+        <f>SUMPRODUCT((C$7:$T$7=1)*(C24:T24="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="17" customHeight="1">
-      <c r="A25" s="32" t="n">
+      <c r="A25" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="B25" s="33" t="inlineStr">
+      <c r="B25" s="35" t="inlineStr">
         <is>
           <t>Divan</t>
         </is>
       </c>
-      <c r="C25" s="18" t="n"/>
-      <c r="D25" s="18" t="n"/>
-      <c r="E25" s="18" t="n"/>
-      <c r="F25" s="18" t="n"/>
-      <c r="G25" s="18" t="n"/>
-      <c r="H25" s="18" t="n"/>
-      <c r="I25" s="18" t="n"/>
-      <c r="J25" s="18" t="n"/>
-      <c r="K25" s="18" t="n"/>
-      <c r="L25" s="18" t="n"/>
-      <c r="M25" s="17">
-        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C25:L25,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="N25" s="26">
-        <f>COUNTIF(C25:L25,"Y")</f>
-        <v/>
-      </c>
-      <c r="O25" s="27">
-        <f>SUMPRODUCT((C$7:$L$7=1)*(C25:L25="Y"))*50</f>
+      <c r="C25" s="19" t="n"/>
+      <c r="D25" s="19" t="n"/>
+      <c r="E25" s="19" t="n"/>
+      <c r="F25" s="19" t="n"/>
+      <c r="G25" s="19" t="n"/>
+      <c r="H25" s="19" t="n"/>
+      <c r="I25" s="19" t="n"/>
+      <c r="J25" s="19" t="n"/>
+      <c r="K25" s="19" t="n"/>
+      <c r="L25" s="19" t="n"/>
+      <c r="M25" s="19" t="n"/>
+      <c r="N25" s="19" t="n"/>
+      <c r="O25" s="19" t="n"/>
+      <c r="P25" s="19" t="n"/>
+      <c r="Q25" s="19" t="n"/>
+      <c r="R25" s="19" t="n"/>
+      <c r="S25" s="19" t="n"/>
+      <c r="T25" s="19" t="n"/>
+      <c r="U25" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$T$7,C25:T25,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="V25" s="28">
+        <f>COUNTIF(C25:T25,"Y")</f>
+        <v/>
+      </c>
+      <c r="W25" s="29">
+        <f>SUMPRODUCT((C$7:$T$7=1)*(C25:T25="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="17" customHeight="1">
-      <c r="A26" s="29" t="n">
+      <c r="A26" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="B26" s="30" t="inlineStr">
+      <c r="B26" s="32" t="inlineStr">
         <is>
           <t>Francisco</t>
         </is>
       </c>
-      <c r="C26" s="31" t="n"/>
-      <c r="D26" s="31" t="n"/>
-      <c r="E26" s="31" t="n"/>
-      <c r="F26" s="31" t="n"/>
-      <c r="G26" s="31" t="n"/>
-      <c r="H26" s="31" t="n"/>
-      <c r="I26" s="31" t="n"/>
-      <c r="J26" s="31" t="n"/>
-      <c r="K26" s="31" t="n"/>
-      <c r="L26" s="31" t="n"/>
-      <c r="M26" s="17">
-        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C26:L26,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="N26" s="26">
-        <f>COUNTIF(C26:L26,"Y")</f>
-        <v/>
-      </c>
-      <c r="O26" s="27">
-        <f>SUMPRODUCT((C$7:$L$7=1)*(C26:L26="Y"))*50</f>
+      <c r="C26" s="33" t="n"/>
+      <c r="D26" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E26" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F26" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G26" s="33" t="n"/>
+      <c r="H26" s="33" t="n"/>
+      <c r="I26" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J26" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K26" s="33" t="n"/>
+      <c r="L26" s="33" t="n"/>
+      <c r="M26" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N26" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O26" s="33" t="n"/>
+      <c r="P26" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q26" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R26" s="33" t="n"/>
+      <c r="S26" s="33" t="n"/>
+      <c r="T26" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="U26" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$T$7,C26:T26,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="V26" s="28">
+        <f>COUNTIF(C26:T26,"Y")</f>
+        <v/>
+      </c>
+      <c r="W26" s="29">
+        <f>SUMPRODUCT((C$7:$T$7=1)*(C26:T26="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="17" customHeight="1">
-      <c r="A27" s="32" t="n">
+      <c r="A27" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="B27" s="33" t="inlineStr">
+      <c r="B27" s="35" t="inlineStr">
         <is>
           <t>Grace</t>
         </is>
       </c>
-      <c r="C27" s="18" t="n"/>
-      <c r="D27" s="18" t="n"/>
-      <c r="E27" s="18" t="n"/>
-      <c r="F27" s="18" t="n"/>
-      <c r="G27" s="18" t="n"/>
-      <c r="H27" s="18" t="n"/>
-      <c r="I27" s="18" t="n"/>
-      <c r="J27" s="18" t="n"/>
-      <c r="K27" s="18" t="n"/>
-      <c r="L27" s="18" t="n"/>
-      <c r="M27" s="17">
-        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C27:L27,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="N27" s="26">
-        <f>COUNTIF(C27:L27,"Y")</f>
-        <v/>
-      </c>
-      <c r="O27" s="27">
-        <f>SUMPRODUCT((C$7:$L$7=1)*(C27:L27="Y"))*50</f>
+      <c r="C27" s="19" t="n"/>
+      <c r="D27" s="19" t="n"/>
+      <c r="E27" s="19" t="n"/>
+      <c r="F27" s="19" t="n"/>
+      <c r="G27" s="19" t="n"/>
+      <c r="H27" s="19" t="n"/>
+      <c r="I27" s="19" t="n"/>
+      <c r="J27" s="19" t="n"/>
+      <c r="K27" s="19" t="n"/>
+      <c r="L27" s="19" t="n"/>
+      <c r="M27" s="19" t="n"/>
+      <c r="N27" s="19" t="n"/>
+      <c r="O27" s="19" t="n"/>
+      <c r="P27" s="19" t="n"/>
+      <c r="Q27" s="19" t="n"/>
+      <c r="R27" s="19" t="n"/>
+      <c r="S27" s="19" t="n"/>
+      <c r="T27" s="19" t="n"/>
+      <c r="U27" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$T$7,C27:T27,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="V27" s="28">
+        <f>COUNTIF(C27:T27,"Y")</f>
+        <v/>
+      </c>
+      <c r="W27" s="29">
+        <f>SUMPRODUCT((C$7:$T$7=1)*(C27:T27="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="17" customHeight="1">
-      <c r="A28" s="29" t="n">
+      <c r="A28" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="B28" s="30" t="inlineStr">
+      <c r="B28" s="32" t="inlineStr">
         <is>
           <t>Jada</t>
         </is>
       </c>
-      <c r="C28" s="31" t="n"/>
-      <c r="D28" s="31" t="n"/>
-      <c r="E28" s="31" t="n"/>
-      <c r="F28" s="31" t="n"/>
-      <c r="G28" s="31" t="n"/>
-      <c r="H28" s="31" t="n"/>
-      <c r="I28" s="31" t="n"/>
-      <c r="J28" s="31" t="n"/>
-      <c r="K28" s="31" t="n"/>
-      <c r="L28" s="31" t="n"/>
-      <c r="M28" s="17">
-        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C28:L28,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="N28" s="26">
-        <f>COUNTIF(C28:L28,"Y")</f>
-        <v/>
-      </c>
-      <c r="O28" s="27">
-        <f>SUMPRODUCT((C$7:$L$7=1)*(C28:L28="Y"))*50</f>
+      <c r="C28" s="33" t="n"/>
+      <c r="D28" s="33" t="n"/>
+      <c r="E28" s="33" t="n"/>
+      <c r="F28" s="33" t="n"/>
+      <c r="G28" s="33" t="n"/>
+      <c r="H28" s="33" t="n"/>
+      <c r="I28" s="33" t="n"/>
+      <c r="J28" s="33" t="n"/>
+      <c r="K28" s="33" t="n"/>
+      <c r="L28" s="33" t="n"/>
+      <c r="M28" s="33" t="n"/>
+      <c r="N28" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O28" s="33" t="n"/>
+      <c r="P28" s="33" t="n"/>
+      <c r="Q28" s="33" t="n"/>
+      <c r="R28" s="33" t="n"/>
+      <c r="S28" s="33" t="n"/>
+      <c r="T28" s="33" t="n"/>
+      <c r="U28" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$T$7,C28:T28,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="V28" s="28">
+        <f>COUNTIF(C28:T28,"Y")</f>
+        <v/>
+      </c>
+      <c r="W28" s="29">
+        <f>SUMPRODUCT((C$7:$T$7=1)*(C28:T28="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="17" customHeight="1">
-      <c r="A29" s="32" t="n">
+      <c r="A29" s="34" t="n">
         <v>10</v>
       </c>
-      <c r="B29" s="33" t="inlineStr">
+      <c r="B29" s="35" t="inlineStr">
         <is>
           <t>Jeremiah</t>
         </is>
       </c>
-      <c r="C29" s="18" t="n"/>
-      <c r="D29" s="18" t="n"/>
-      <c r="E29" s="18" t="n"/>
-      <c r="F29" s="18" t="n"/>
-      <c r="G29" s="18" t="n"/>
-      <c r="H29" s="18" t="n"/>
-      <c r="I29" s="18" t="n"/>
-      <c r="J29" s="18" t="n"/>
-      <c r="K29" s="18" t="n"/>
-      <c r="L29" s="18" t="n"/>
-      <c r="M29" s="17">
-        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C29:L29,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="N29" s="26">
-        <f>COUNTIF(C29:L29,"Y")</f>
-        <v/>
-      </c>
-      <c r="O29" s="27">
-        <f>SUMPRODUCT((C$7:$L$7=1)*(C29:L29="Y"))*50</f>
+      <c r="C29" s="19" t="n"/>
+      <c r="D29" s="19" t="n"/>
+      <c r="E29" s="19" t="n"/>
+      <c r="F29" s="19" t="n"/>
+      <c r="G29" s="19" t="n"/>
+      <c r="H29" s="19" t="n"/>
+      <c r="I29" s="19" t="n"/>
+      <c r="J29" s="19" t="n"/>
+      <c r="K29" s="19" t="n"/>
+      <c r="L29" s="19" t="n"/>
+      <c r="M29" s="19" t="n"/>
+      <c r="N29" s="19" t="n"/>
+      <c r="O29" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P29" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q29" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R29" s="19" t="n"/>
+      <c r="S29" s="19" t="n"/>
+      <c r="T29" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="U29" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$T$7,C29:T29,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="V29" s="28">
+        <f>COUNTIF(C29:T29,"Y")</f>
+        <v/>
+      </c>
+      <c r="W29" s="29">
+        <f>SUMPRODUCT((C$7:$T$7=1)*(C29:T29="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="17" customHeight="1">
-      <c r="A30" s="29" t="n">
+      <c r="A30" s="31" t="n">
         <v>11</v>
       </c>
-      <c r="B30" s="30" t="inlineStr">
+      <c r="B30" s="32" t="inlineStr">
         <is>
           <t>Kable</t>
         </is>
       </c>
-      <c r="C30" s="31" t="n"/>
-      <c r="D30" s="31" t="n"/>
-      <c r="E30" s="31" t="n"/>
-      <c r="F30" s="31" t="n"/>
-      <c r="G30" s="31" t="n"/>
-      <c r="H30" s="31" t="n"/>
-      <c r="I30" s="31" t="n"/>
-      <c r="J30" s="31" t="n"/>
-      <c r="K30" s="31" t="n"/>
-      <c r="L30" s="31" t="n"/>
-      <c r="M30" s="17">
-        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C30:L30,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="N30" s="26">
-        <f>COUNTIF(C30:L30,"Y")</f>
-        <v/>
-      </c>
-      <c r="O30" s="27">
-        <f>SUMPRODUCT((C$7:$L$7=1)*(C30:L30="Y"))*50</f>
+      <c r="C30" s="33" t="n"/>
+      <c r="D30" s="33" t="n"/>
+      <c r="E30" s="33" t="n"/>
+      <c r="F30" s="33" t="n"/>
+      <c r="G30" s="33" t="n"/>
+      <c r="H30" s="33" t="n"/>
+      <c r="I30" s="33" t="n"/>
+      <c r="J30" s="33" t="n"/>
+      <c r="K30" s="33" t="n"/>
+      <c r="L30" s="33" t="n"/>
+      <c r="M30" s="33" t="n"/>
+      <c r="N30" s="33" t="n"/>
+      <c r="O30" s="33" t="n"/>
+      <c r="P30" s="33" t="n"/>
+      <c r="Q30" s="33" t="n"/>
+      <c r="R30" s="33" t="n"/>
+      <c r="S30" s="33" t="n"/>
+      <c r="T30" s="33" t="n"/>
+      <c r="U30" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$T$7,C30:T30,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="V30" s="28">
+        <f>COUNTIF(C30:T30,"Y")</f>
+        <v/>
+      </c>
+      <c r="W30" s="29">
+        <f>SUMPRODUCT((C$7:$T$7=1)*(C30:T30="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="17" customHeight="1">
-      <c r="A31" s="32" t="n">
+      <c r="A31" s="34" t="n">
         <v>12</v>
       </c>
-      <c r="B31" s="33" t="inlineStr">
+      <c r="B31" s="35" t="inlineStr">
         <is>
           <t>Kayla</t>
         </is>
       </c>
-      <c r="C31" s="18" t="n"/>
-      <c r="D31" s="18" t="n"/>
-      <c r="E31" s="18" t="n"/>
-      <c r="F31" s="18" t="n"/>
-      <c r="G31" s="18" t="n"/>
-      <c r="H31" s="18" t="n"/>
-      <c r="I31" s="18" t="n"/>
-      <c r="J31" s="18" t="n"/>
-      <c r="K31" s="18" t="n"/>
-      <c r="L31" s="18" t="n"/>
-      <c r="M31" s="17">
-        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C31:L31,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="N31" s="26">
-        <f>COUNTIF(C31:L31,"Y")</f>
-        <v/>
-      </c>
-      <c r="O31" s="27">
-        <f>SUMPRODUCT((C$7:$L$7=1)*(C31:L31="Y"))*50</f>
+      <c r="C31" s="19" t="n"/>
+      <c r="D31" s="19" t="n"/>
+      <c r="E31" s="19" t="n"/>
+      <c r="F31" s="19" t="n"/>
+      <c r="G31" s="19" t="n"/>
+      <c r="H31" s="19" t="n"/>
+      <c r="I31" s="19" t="n"/>
+      <c r="J31" s="19" t="n"/>
+      <c r="K31" s="19" t="n"/>
+      <c r="L31" s="19" t="n"/>
+      <c r="M31" s="19" t="n"/>
+      <c r="N31" s="19" t="n"/>
+      <c r="O31" s="19" t="n"/>
+      <c r="P31" s="19" t="n"/>
+      <c r="Q31" s="19" t="n"/>
+      <c r="R31" s="19" t="n"/>
+      <c r="S31" s="19" t="n"/>
+      <c r="T31" s="19" t="n"/>
+      <c r="U31" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$T$7,C31:T31,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="V31" s="28">
+        <f>COUNTIF(C31:T31,"Y")</f>
+        <v/>
+      </c>
+      <c r="W31" s="29">
+        <f>SUMPRODUCT((C$7:$T$7=1)*(C31:T31="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="17" customHeight="1">
-      <c r="A32" s="29" t="n">
+      <c r="A32" s="31" t="n">
         <v>13</v>
       </c>
-      <c r="B32" s="30" t="inlineStr">
+      <c r="B32" s="32" t="inlineStr">
         <is>
           <t>Kenzie</t>
         </is>
       </c>
-      <c r="C32" s="31" t="n"/>
-      <c r="D32" s="31" t="n"/>
-      <c r="E32" s="31" t="n"/>
-      <c r="F32" s="31" t="n"/>
-      <c r="G32" s="31" t="n"/>
-      <c r="H32" s="31" t="n"/>
-      <c r="I32" s="31" t="n"/>
-      <c r="J32" s="31" t="n"/>
-      <c r="K32" s="31" t="n"/>
-      <c r="L32" s="31" t="n"/>
-      <c r="M32" s="17">
-        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C32:L32,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="N32" s="26">
-        <f>COUNTIF(C32:L32,"Y")</f>
-        <v/>
-      </c>
-      <c r="O32" s="27">
-        <f>SUMPRODUCT((C$7:$L$7=1)*(C32:L32="Y"))*50</f>
+      <c r="C32" s="33" t="n"/>
+      <c r="D32" s="33" t="n"/>
+      <c r="E32" s="33" t="n"/>
+      <c r="F32" s="33" t="n"/>
+      <c r="G32" s="33" t="n"/>
+      <c r="H32" s="33" t="n"/>
+      <c r="I32" s="33" t="n"/>
+      <c r="J32" s="33" t="n"/>
+      <c r="K32" s="33" t="n"/>
+      <c r="L32" s="33" t="n"/>
+      <c r="M32" s="33" t="n"/>
+      <c r="N32" s="33" t="n"/>
+      <c r="O32" s="33" t="n"/>
+      <c r="P32" s="33" t="n"/>
+      <c r="Q32" s="33" t="n"/>
+      <c r="R32" s="33" t="n"/>
+      <c r="S32" s="33" t="n"/>
+      <c r="T32" s="33" t="n"/>
+      <c r="U32" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$T$7,C32:T32,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="V32" s="28">
+        <f>COUNTIF(C32:T32,"Y")</f>
+        <v/>
+      </c>
+      <c r="W32" s="29">
+        <f>SUMPRODUCT((C$7:$T$7=1)*(C32:T32="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="17" customHeight="1">
-      <c r="A33" s="32" t="n">
+      <c r="A33" s="34" t="n">
         <v>14</v>
       </c>
-      <c r="B33" s="33" t="inlineStr">
+      <c r="B33" s="35" t="inlineStr">
         <is>
           <t>Lidy</t>
         </is>
       </c>
-      <c r="C33" s="18" t="n"/>
-      <c r="D33" s="18" t="n"/>
-      <c r="E33" s="18" t="n"/>
-      <c r="F33" s="18" t="n"/>
-      <c r="G33" s="18" t="n"/>
-      <c r="H33" s="18" t="n"/>
-      <c r="I33" s="18" t="n"/>
-      <c r="J33" s="18" t="n"/>
-      <c r="K33" s="18" t="n"/>
-      <c r="L33" s="18" t="n"/>
-      <c r="M33" s="17">
-        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C33:L33,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="N33" s="26">
-        <f>COUNTIF(C33:L33,"Y")</f>
-        <v/>
-      </c>
-      <c r="O33" s="27">
-        <f>SUMPRODUCT((C$7:$L$7=1)*(C33:L33="Y"))*50</f>
+      <c r="C33" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D33" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E33" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F33" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G33" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H33" s="19" t="n"/>
+      <c r="I33" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J33" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K33" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L33" s="19" t="n"/>
+      <c r="M33" s="19" t="n"/>
+      <c r="N33" s="19" t="n"/>
+      <c r="O33" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P33" s="19" t="n"/>
+      <c r="Q33" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R33" s="19" t="n"/>
+      <c r="S33" s="19" t="n"/>
+      <c r="T33" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="U33" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$T$7,C33:T33,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="V33" s="28">
+        <f>COUNTIF(C33:T33,"Y")</f>
+        <v/>
+      </c>
+      <c r="W33" s="29">
+        <f>SUMPRODUCT((C$7:$T$7=1)*(C33:T33="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="17" customHeight="1">
-      <c r="A34" s="29" t="n">
+      <c r="A34" s="31" t="n">
         <v>15</v>
       </c>
-      <c r="B34" s="30" t="inlineStr">
+      <c r="B34" s="32" t="inlineStr">
         <is>
           <t>Maylin</t>
         </is>
       </c>
-      <c r="C34" s="31" t="n"/>
-      <c r="D34" s="31" t="n"/>
-      <c r="E34" s="31" t="n"/>
-      <c r="F34" s="31" t="n"/>
-      <c r="G34" s="31" t="n"/>
-      <c r="H34" s="31" t="n"/>
-      <c r="I34" s="31" t="n"/>
-      <c r="J34" s="31" t="n"/>
-      <c r="K34" s="31" t="n"/>
-      <c r="L34" s="31" t="n"/>
-      <c r="M34" s="17">
-        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C34:L34,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="N34" s="26">
-        <f>COUNTIF(C34:L34,"Y")</f>
-        <v/>
-      </c>
-      <c r="O34" s="27">
-        <f>SUMPRODUCT((C$7:$L$7=1)*(C34:L34="Y"))*50</f>
+      <c r="C34" s="33" t="n"/>
+      <c r="D34" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E34" s="33" t="n"/>
+      <c r="F34" s="33" t="n"/>
+      <c r="G34" s="33" t="n"/>
+      <c r="H34" s="33" t="n"/>
+      <c r="I34" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J34" s="33" t="n"/>
+      <c r="K34" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L34" s="33" t="n"/>
+      <c r="M34" s="33" t="n"/>
+      <c r="N34" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O34" s="33" t="n"/>
+      <c r="P34" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q34" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R34" s="33" t="n"/>
+      <c r="S34" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T34" s="33" t="n"/>
+      <c r="U34" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$T$7,C34:T34,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="V34" s="28">
+        <f>COUNTIF(C34:T34,"Y")</f>
+        <v/>
+      </c>
+      <c r="W34" s="29">
+        <f>SUMPRODUCT((C$7:$T$7=1)*(C34:T34="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="17" customHeight="1">
-      <c r="A35" s="32" t="n">
+      <c r="A35" s="34" t="n">
         <v>16</v>
       </c>
-      <c r="B35" s="33" t="inlineStr">
+      <c r="B35" s="35" t="inlineStr">
         <is>
           <t>Mike</t>
         </is>
       </c>
-      <c r="C35" s="18" t="n"/>
-      <c r="D35" s="18" t="n"/>
-      <c r="E35" s="18" t="n"/>
-      <c r="F35" s="18" t="n"/>
-      <c r="G35" s="18" t="n"/>
-      <c r="H35" s="18" t="n"/>
-      <c r="I35" s="18" t="n"/>
-      <c r="J35" s="18" t="n"/>
-      <c r="K35" s="18" t="n"/>
-      <c r="L35" s="18" t="n"/>
-      <c r="M35" s="17">
-        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C35:L35,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="N35" s="26">
-        <f>COUNTIF(C35:L35,"Y")</f>
-        <v/>
-      </c>
-      <c r="O35" s="27">
-        <f>SUMPRODUCT((C$7:$L$7=1)*(C35:L35="Y"))*50</f>
+      <c r="C35" s="19" t="n"/>
+      <c r="D35" s="19" t="n"/>
+      <c r="E35" s="19" t="n"/>
+      <c r="F35" s="19" t="n"/>
+      <c r="G35" s="19" t="n"/>
+      <c r="H35" s="19" t="n"/>
+      <c r="I35" s="19" t="n"/>
+      <c r="J35" s="19" t="n"/>
+      <c r="K35" s="19" t="n"/>
+      <c r="L35" s="19" t="n"/>
+      <c r="M35" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N35" s="19" t="n"/>
+      <c r="O35" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P35" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q35" s="19" t="n"/>
+      <c r="R35" s="19" t="n"/>
+      <c r="S35" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T35" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="U35" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$T$7,C35:T35,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="V35" s="28">
+        <f>COUNTIF(C35:T35,"Y")</f>
+        <v/>
+      </c>
+      <c r="W35" s="29">
+        <f>SUMPRODUCT((C$7:$T$7=1)*(C35:T35="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="17" customHeight="1">
-      <c r="A36" s="29" t="n">
+      <c r="A36" s="31" t="n">
         <v>17</v>
       </c>
-      <c r="B36" s="30" t="inlineStr">
+      <c r="B36" s="32" t="inlineStr">
         <is>
           <t>Richard</t>
         </is>
       </c>
-      <c r="C36" s="31" t="n"/>
-      <c r="D36" s="31" t="n"/>
-      <c r="E36" s="31" t="n"/>
-      <c r="F36" s="31" t="n"/>
-      <c r="G36" s="31" t="n"/>
-      <c r="H36" s="31" t="n"/>
-      <c r="I36" s="31" t="n"/>
-      <c r="J36" s="31" t="n"/>
-      <c r="K36" s="31" t="n"/>
-      <c r="L36" s="31" t="n"/>
-      <c r="M36" s="17">
-        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C36:L36,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="N36" s="26">
-        <f>COUNTIF(C36:L36,"Y")</f>
-        <v/>
-      </c>
-      <c r="O36" s="27">
-        <f>SUMPRODUCT((C$7:$L$7=1)*(C36:L36="Y"))*50</f>
+      <c r="C36" s="33" t="n"/>
+      <c r="D36" s="33" t="n"/>
+      <c r="E36" s="33" t="n"/>
+      <c r="F36" s="33" t="n"/>
+      <c r="G36" s="33" t="n"/>
+      <c r="H36" s="33" t="n"/>
+      <c r="I36" s="33" t="n"/>
+      <c r="J36" s="33" t="n"/>
+      <c r="K36" s="33" t="n"/>
+      <c r="L36" s="33" t="n"/>
+      <c r="M36" s="33" t="n"/>
+      <c r="N36" s="33" t="n"/>
+      <c r="O36" s="33" t="n"/>
+      <c r="P36" s="33" t="n"/>
+      <c r="Q36" s="33" t="n"/>
+      <c r="R36" s="33" t="n"/>
+      <c r="S36" s="33" t="n"/>
+      <c r="T36" s="33" t="n"/>
+      <c r="U36" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$T$7,C36:T36,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="V36" s="28">
+        <f>COUNTIF(C36:T36,"Y")</f>
+        <v/>
+      </c>
+      <c r="W36" s="29">
+        <f>SUMPRODUCT((C$7:$T$7=1)*(C36:T36="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="17" customHeight="1">
-      <c r="A37" s="32" t="n">
+      <c r="A37" s="34" t="n">
         <v>18</v>
       </c>
-      <c r="B37" s="33" t="inlineStr">
+      <c r="B37" s="35" t="inlineStr">
         <is>
           <t>Samuel</t>
         </is>
       </c>
-      <c r="C37" s="18" t="n"/>
-      <c r="D37" s="18" t="n"/>
-      <c r="E37" s="18" t="n"/>
-      <c r="F37" s="18" t="n"/>
-      <c r="G37" s="18" t="n"/>
-      <c r="H37" s="18" t="n"/>
-      <c r="I37" s="18" t="n"/>
-      <c r="J37" s="18" t="n"/>
-      <c r="K37" s="18" t="n"/>
-      <c r="L37" s="18" t="n"/>
-      <c r="M37" s="17">
-        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C37:L37,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="N37" s="26">
-        <f>COUNTIF(C37:L37,"Y")</f>
-        <v/>
-      </c>
-      <c r="O37" s="27">
-        <f>SUMPRODUCT((C$7:$L$7=1)*(C37:L37="Y"))*50</f>
+      <c r="C37" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D37" s="19" t="n"/>
+      <c r="E37" s="19" t="n"/>
+      <c r="F37" s="19" t="n"/>
+      <c r="G37" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H37" s="19" t="n"/>
+      <c r="I37" s="19" t="n"/>
+      <c r="J37" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K37" s="19" t="n"/>
+      <c r="L37" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M37" s="19" t="n"/>
+      <c r="N37" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O37" s="19" t="n"/>
+      <c r="P37" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q37" s="19" t="n"/>
+      <c r="R37" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S37" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T37" s="19" t="n"/>
+      <c r="U37" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$T$7,C37:T37,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="V37" s="28">
+        <f>COUNTIF(C37:T37,"Y")</f>
+        <v/>
+      </c>
+      <c r="W37" s="29">
+        <f>SUMPRODUCT((C$7:$T$7=1)*(C37:T37="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="17" customHeight="1">
-      <c r="A38" s="29" t="n">
+      <c r="A38" s="31" t="n">
         <v>19</v>
       </c>
-      <c r="B38" s="30" t="inlineStr">
+      <c r="B38" s="32" t="inlineStr">
         <is>
           <t>Zach</t>
         </is>
       </c>
-      <c r="C38" s="31" t="n"/>
-      <c r="D38" s="31" t="n"/>
-      <c r="E38" s="31" t="n"/>
-      <c r="F38" s="31" t="n"/>
-      <c r="G38" s="31" t="n"/>
-      <c r="H38" s="31" t="n"/>
-      <c r="I38" s="31" t="n"/>
-      <c r="J38" s="31" t="n"/>
-      <c r="K38" s="31" t="n"/>
-      <c r="L38" s="31" t="n"/>
-      <c r="M38" s="17">
-        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C38:L38,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="N38" s="26">
-        <f>COUNTIF(C38:L38,"Y")</f>
-        <v/>
-      </c>
-      <c r="O38" s="27">
-        <f>SUMPRODUCT((C$7:$L$7=1)*(C38:L38="Y"))*50</f>
+      <c r="C38" s="33" t="n"/>
+      <c r="D38" s="33" t="n"/>
+      <c r="E38" s="33" t="n"/>
+      <c r="F38" s="33" t="n"/>
+      <c r="G38" s="33" t="n"/>
+      <c r="H38" s="33" t="n"/>
+      <c r="I38" s="33" t="n"/>
+      <c r="J38" s="33" t="n"/>
+      <c r="K38" s="33" t="n"/>
+      <c r="L38" s="33" t="n"/>
+      <c r="M38" s="33" t="n"/>
+      <c r="N38" s="33" t="n"/>
+      <c r="O38" s="33" t="n"/>
+      <c r="P38" s="33" t="n"/>
+      <c r="Q38" s="33" t="n"/>
+      <c r="R38" s="33" t="n"/>
+      <c r="S38" s="33" t="n"/>
+      <c r="T38" s="33" t="n"/>
+      <c r="U38" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$T$7,C38:T38,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="V38" s="28">
+        <f>COUNTIF(C38:T38,"Y")</f>
+        <v/>
+      </c>
+      <c r="W38" s="29">
+        <f>SUMPRODUCT((C$7:$T$7=1)*(C38:T38="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="3" t="inlineStr"/>
-      <c r="B39" s="34" t="inlineStr">
+      <c r="B39" s="36" t="inlineStr">
         <is>
           <t>Total on shift</t>
         </is>
@@ -1945,18 +2581,50 @@
         <f>COUNTIF(L14:L38,"Y")</f>
         <v/>
       </c>
-      <c r="M39" s="3" t="inlineStr"/>
+      <c r="M39" s="6">
+        <f>COUNTIF(M14:M38,"Y")</f>
+        <v/>
+      </c>
       <c r="N39" s="6">
-        <f>SUM(N14:N38)</f>
-        <v/>
-      </c>
-      <c r="O39" s="35">
-        <f>SUM(O14:O38)</f>
+        <f>COUNTIF(N14:N38,"Y")</f>
+        <v/>
+      </c>
+      <c r="O39" s="6">
+        <f>COUNTIF(O14:O38,"Y")</f>
+        <v/>
+      </c>
+      <c r="P39" s="6">
+        <f>COUNTIF(P14:P38,"Y")</f>
+        <v/>
+      </c>
+      <c r="Q39" s="6">
+        <f>COUNTIF(Q14:Q38,"Y")</f>
+        <v/>
+      </c>
+      <c r="R39" s="6">
+        <f>COUNTIF(R14:R38,"Y")</f>
+        <v/>
+      </c>
+      <c r="S39" s="6">
+        <f>COUNTIF(S14:S38,"Y")</f>
+        <v/>
+      </c>
+      <c r="T39" s="6">
+        <f>COUNTIF(T14:T38,"Y")</f>
+        <v/>
+      </c>
+      <c r="U39" s="3" t="inlineStr"/>
+      <c r="V39" s="6">
+        <f>SUM(V14:V38)</f>
+        <v/>
+      </c>
+      <c r="W39" s="37">
+        <f>SUM(W14:W38)</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="12" customHeight="1">
-      <c r="A40" s="36" t="inlineStr">
+      <c r="A40" s="38" t="inlineStr">
         <is>
           <t>Y = on shift during shop's meal window. Personal Avg = average score of shops worked. Bonus = $50 per 100% shop worked.</t>
         </is>
@@ -1964,13 +2632,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A12:O12"/>
-    <mergeCell ref="A2:O2"/>
-    <mergeCell ref="A13:O13"/>
-    <mergeCell ref="A19:O19"/>
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A40:O40"/>
-    <mergeCell ref="A18:O18"/>
+    <mergeCell ref="A13:W13"/>
+    <mergeCell ref="A1:W1"/>
+    <mergeCell ref="A40:W40"/>
+    <mergeCell ref="A18:W18"/>
+    <mergeCell ref="A12:W12"/>
+    <mergeCell ref="A2:W2"/>
+    <mergeCell ref="A19:W19"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2253,7 +2921,7 @@
           <t>Total Score</t>
         </is>
       </c>
-      <c r="C7" s="37" t="n">
+      <c r="C7" s="17" t="n">
         <v>0.95</v>
       </c>
       <c r="D7" s="16" t="n">
@@ -2262,7 +2930,7 @@
       <c r="E7" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="37" t="n">
+      <c r="F7" s="17" t="n">
         <v>0.9</v>
       </c>
       <c r="G7" s="16" t="n">
@@ -2286,10 +2954,10 @@
       <c r="M7" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="N7" s="37" t="n">
+      <c r="N7" s="17" t="n">
         <v>0.95</v>
       </c>
-      <c r="O7" s="17">
+      <c r="O7" s="18">
         <f>IFERROR(AVERAGE(C7:N7),"")</f>
         <v/>
       </c>
@@ -2297,1086 +2965,1134 @@
       <c r="Q7" s="12" t="inlineStr"/>
     </row>
     <row r="8" ht="13" customHeight="1">
-      <c r="A8" s="18" t="inlineStr"/>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr"/>
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr"/>
-      <c r="D8" s="18" t="inlineStr"/>
-      <c r="E8" s="18" t="inlineStr"/>
-      <c r="F8" s="18" t="inlineStr"/>
-      <c r="G8" s="18" t="inlineStr"/>
-      <c r="H8" s="18" t="inlineStr"/>
-      <c r="I8" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" s="39" t="n">
+      <c r="C8" s="19" t="inlineStr"/>
+      <c r="D8" s="19" t="inlineStr"/>
+      <c r="E8" s="19" t="inlineStr"/>
+      <c r="F8" s="19" t="inlineStr"/>
+      <c r="G8" s="19" t="inlineStr"/>
+      <c r="H8" s="19" t="inlineStr"/>
+      <c r="I8" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" s="40" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="L8" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" s="40" t="n">
+      <c r="L8" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" s="41" t="n">
         <v>0.95</v>
       </c>
-      <c r="O8" s="20">
+      <c r="O8" s="21">
         <f>IFERROR(AVERAGE(C8:N8),"")</f>
         <v/>
       </c>
-      <c r="P8" s="18" t="inlineStr"/>
-      <c r="Q8" s="18" t="inlineStr"/>
+      <c r="P8" s="19" t="inlineStr"/>
+      <c r="Q8" s="19" t="inlineStr"/>
     </row>
     <row r="9" ht="13" customHeight="1">
-      <c r="A9" s="18" t="inlineStr"/>
-      <c r="B9" s="19" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr"/>
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>Quality</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr"/>
-      <c r="D9" s="18" t="inlineStr"/>
-      <c r="E9" s="18" t="inlineStr"/>
-      <c r="F9" s="18" t="inlineStr"/>
-      <c r="G9" s="18" t="inlineStr"/>
-      <c r="H9" s="18" t="inlineStr"/>
-      <c r="I9" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" s="20">
+      <c r="C9" s="19" t="inlineStr"/>
+      <c r="D9" s="19" t="inlineStr"/>
+      <c r="E9" s="19" t="inlineStr"/>
+      <c r="F9" s="19" t="inlineStr"/>
+      <c r="G9" s="19" t="inlineStr"/>
+      <c r="H9" s="19" t="inlineStr"/>
+      <c r="I9" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" s="21">
         <f>IFERROR(AVERAGE(C9:N9),"")</f>
         <v/>
       </c>
-      <c r="P9" s="18" t="inlineStr"/>
-      <c r="Q9" s="18" t="inlineStr"/>
+      <c r="P9" s="19" t="inlineStr"/>
+      <c r="Q9" s="19" t="inlineStr"/>
     </row>
     <row r="10" ht="13" customHeight="1">
-      <c r="A10" s="18" t="inlineStr"/>
-      <c r="B10" s="19" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr"/>
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>Cleanliness</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr"/>
-      <c r="D10" s="18" t="inlineStr"/>
-      <c r="E10" s="18" t="inlineStr"/>
-      <c r="F10" s="18" t="inlineStr"/>
-      <c r="G10" s="18" t="inlineStr"/>
-      <c r="H10" s="18" t="inlineStr"/>
-      <c r="I10" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" s="20">
+      <c r="C10" s="19" t="inlineStr"/>
+      <c r="D10" s="19" t="inlineStr"/>
+      <c r="E10" s="19" t="inlineStr"/>
+      <c r="F10" s="19" t="inlineStr"/>
+      <c r="G10" s="19" t="inlineStr"/>
+      <c r="H10" s="19" t="inlineStr"/>
+      <c r="I10" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" s="21">
         <f>IFERROR(AVERAGE(C10:N10),"")</f>
         <v/>
       </c>
-      <c r="P10" s="18" t="inlineStr"/>
-      <c r="Q10" s="18" t="inlineStr"/>
+      <c r="P10" s="19" t="inlineStr"/>
+      <c r="Q10" s="19" t="inlineStr"/>
     </row>
     <row r="11" ht="13" customHeight="1">
-      <c r="A11" s="18" t="inlineStr"/>
-      <c r="B11" s="19" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr"/>
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>Customer Sat</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr"/>
-      <c r="D11" s="18" t="inlineStr"/>
-      <c r="E11" s="18" t="inlineStr"/>
-      <c r="F11" s="18" t="inlineStr"/>
-      <c r="G11" s="18" t="inlineStr"/>
-      <c r="H11" s="18" t="inlineStr"/>
-      <c r="I11" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" s="20">
+      <c r="C11" s="19" t="inlineStr"/>
+      <c r="D11" s="19" t="inlineStr"/>
+      <c r="E11" s="19" t="inlineStr"/>
+      <c r="F11" s="19" t="inlineStr"/>
+      <c r="G11" s="19" t="inlineStr"/>
+      <c r="H11" s="19" t="inlineStr"/>
+      <c r="I11" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" s="21">
         <f>IFERROR(AVERAGE(C11:N11),"")</f>
         <v/>
       </c>
-      <c r="P11" s="18" t="inlineStr"/>
-      <c r="Q11" s="18" t="inlineStr"/>
+      <c r="P11" s="19" t="inlineStr"/>
+      <c r="Q11" s="19" t="inlineStr"/>
     </row>
     <row r="12" ht="6" customHeight="1">
-      <c r="A12" s="21" t="n"/>
+      <c r="A12" s="22" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="22" t="inlineStr">
+      <c r="A13" s="23" t="inlineStr">
         <is>
           <t>MANAGERS</t>
         </is>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="B14" s="24" t="inlineStr">
+      <c r="A14" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" s="25" t="inlineStr">
         <is>
           <t>Madison C.</t>
         </is>
       </c>
-      <c r="C14" s="25" t="n"/>
-      <c r="D14" s="25" t="n"/>
-      <c r="E14" s="25" t="n"/>
-      <c r="F14" s="25" t="n"/>
-      <c r="G14" s="25" t="n"/>
-      <c r="H14" s="25" t="n"/>
-      <c r="I14" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J14" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K14" s="25" t="n"/>
-      <c r="L14" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M14" s="25" t="n"/>
-      <c r="N14" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O14" s="17">
+      <c r="C14" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D14" s="27" t="n"/>
+      <c r="E14" s="27" t="n"/>
+      <c r="F14" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G14" s="27" t="n"/>
+      <c r="H14" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I14" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J14" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K14" s="27" t="n"/>
+      <c r="L14" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M14" s="27" t="n"/>
+      <c r="N14" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O14" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$N$7,C14:N14,"Y"),"")</f>
         <v/>
       </c>
-      <c r="P14" s="26">
+      <c r="P14" s="28">
         <f>COUNTIF(C14:N14,"Y")</f>
         <v/>
       </c>
-      <c r="Q14" s="27">
+      <c r="Q14" s="29">
         <f>SUMPRODUCT((C$7:$N$7=1)*(C14:N14="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="23" t="n">
+      <c r="A15" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="B15" s="24" t="inlineStr">
+      <c r="B15" s="25" t="inlineStr">
         <is>
           <t>Vicki L.</t>
         </is>
       </c>
-      <c r="C15" s="25" t="n"/>
-      <c r="D15" s="25" t="n"/>
-      <c r="E15" s="25" t="n"/>
-      <c r="F15" s="25" t="n"/>
-      <c r="G15" s="25" t="n"/>
-      <c r="H15" s="25" t="n"/>
-      <c r="I15" s="25" t="n"/>
-      <c r="J15" s="25" t="n"/>
-      <c r="K15" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L15" s="25" t="n"/>
-      <c r="M15" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N15" s="25" t="n"/>
-      <c r="O15" s="17">
+      <c r="C15" s="27" t="n"/>
+      <c r="D15" s="27" t="n"/>
+      <c r="E15" s="27" t="n"/>
+      <c r="F15" s="27" t="n"/>
+      <c r="G15" s="27" t="n"/>
+      <c r="H15" s="27" t="n"/>
+      <c r="I15" s="27" t="n"/>
+      <c r="J15" s="27" t="n"/>
+      <c r="K15" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L15" s="27" t="n"/>
+      <c r="M15" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N15" s="27" t="n"/>
+      <c r="O15" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$N$7,C15:N15,"Y"),"")</f>
         <v/>
       </c>
-      <c r="P15" s="26">
+      <c r="P15" s="28">
         <f>COUNTIF(C15:N15,"Y")</f>
         <v/>
       </c>
-      <c r="Q15" s="27">
+      <c r="Q15" s="29">
         <f>SUMPRODUCT((C$7:$N$7=1)*(C15:N15="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
-      <c r="A16" s="23" t="n">
+      <c r="A16" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="B16" s="24" t="inlineStr">
+      <c r="B16" s="25" t="inlineStr">
         <is>
           <t>Kasey W.</t>
         </is>
       </c>
-      <c r="C16" s="25" t="n"/>
-      <c r="D16" s="25" t="n"/>
-      <c r="E16" s="25" t="n"/>
-      <c r="F16" s="25" t="n"/>
-      <c r="G16" s="25" t="n"/>
-      <c r="H16" s="25" t="n"/>
-      <c r="I16" s="25" t="n"/>
-      <c r="J16" s="25" t="n"/>
-      <c r="K16" s="25" t="n"/>
-      <c r="L16" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M16" s="25" t="n"/>
-      <c r="N16" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O16" s="17">
+      <c r="C16" s="27" t="n"/>
+      <c r="D16" s="27" t="n"/>
+      <c r="E16" s="27" t="n"/>
+      <c r="F16" s="27" t="n"/>
+      <c r="G16" s="27" t="n"/>
+      <c r="H16" s="27" t="n"/>
+      <c r="I16" s="27" t="n"/>
+      <c r="J16" s="27" t="n"/>
+      <c r="K16" s="27" t="n"/>
+      <c r="L16" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M16" s="27" t="n"/>
+      <c r="N16" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O16" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$N$7,C16:N16,"Y"),"")</f>
         <v/>
       </c>
-      <c r="P16" s="26">
+      <c r="P16" s="28">
         <f>COUNTIF(C16:N16,"Y")</f>
         <v/>
       </c>
-      <c r="Q16" s="27">
+      <c r="Q16" s="29">
         <f>SUMPRODUCT((C$7:$N$7=1)*(C16:N16="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
-      <c r="A17" s="23" t="n">
+      <c r="A17" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="B17" s="24" t="inlineStr">
+      <c r="B17" s="25" t="inlineStr">
         <is>
           <t>Nathan R.</t>
         </is>
       </c>
-      <c r="C17" s="25" t="n"/>
-      <c r="D17" s="25" t="n"/>
-      <c r="E17" s="25" t="n"/>
-      <c r="F17" s="25" t="n"/>
-      <c r="G17" s="25" t="n"/>
-      <c r="H17" s="25" t="n"/>
-      <c r="I17" s="25" t="n"/>
-      <c r="J17" s="25" t="n"/>
-      <c r="K17" s="25" t="n"/>
-      <c r="L17" s="25" t="n"/>
-      <c r="M17" s="25" t="n"/>
-      <c r="N17" s="25" t="n"/>
-      <c r="O17" s="17">
+      <c r="C17" s="27" t="n"/>
+      <c r="D17" s="27" t="n"/>
+      <c r="E17" s="27" t="n"/>
+      <c r="F17" s="27" t="n"/>
+      <c r="G17" s="27" t="n"/>
+      <c r="H17" s="27" t="n"/>
+      <c r="I17" s="27" t="n"/>
+      <c r="J17" s="27" t="n"/>
+      <c r="K17" s="27" t="n"/>
+      <c r="L17" s="27" t="n"/>
+      <c r="M17" s="27" t="n"/>
+      <c r="N17" s="27" t="n"/>
+      <c r="O17" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$N$7,C17:N17,"Y"),"")</f>
         <v/>
       </c>
-      <c r="P17" s="26">
+      <c r="P17" s="28">
         <f>COUNTIF(C17:N17,"Y")</f>
         <v/>
       </c>
-      <c r="Q17" s="27">
+      <c r="Q17" s="29">
         <f>SUMPRODUCT((C$7:$N$7=1)*(C17:N17="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="6" customHeight="1">
-      <c r="A18" s="21" t="n"/>
+      <c r="A18" s="22" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="28" t="inlineStr">
+      <c r="A19" s="30" t="inlineStr">
         <is>
           <t>CREW</t>
         </is>
       </c>
     </row>
     <row r="20" ht="17" customHeight="1">
-      <c r="A20" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="B20" s="30" t="inlineStr">
+      <c r="A20" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" s="32" t="inlineStr">
         <is>
           <t>Alen</t>
         </is>
       </c>
-      <c r="C20" s="31" t="n"/>
-      <c r="D20" s="31" t="n"/>
-      <c r="E20" s="31" t="n"/>
-      <c r="F20" s="31" t="n"/>
-      <c r="G20" s="31" t="n"/>
-      <c r="H20" s="31" t="n"/>
-      <c r="I20" s="31" t="n"/>
-      <c r="J20" s="31" t="n"/>
-      <c r="K20" s="31" t="n"/>
-      <c r="L20" s="31" t="n"/>
-      <c r="M20" s="31" t="n"/>
-      <c r="N20" s="31" t="n"/>
-      <c r="O20" s="17">
+      <c r="C20" s="33" t="n"/>
+      <c r="D20" s="33" t="n"/>
+      <c r="E20" s="33" t="n"/>
+      <c r="F20" s="33" t="n"/>
+      <c r="G20" s="33" t="n"/>
+      <c r="H20" s="33" t="n"/>
+      <c r="I20" s="33" t="n"/>
+      <c r="J20" s="33" t="n"/>
+      <c r="K20" s="33" t="n"/>
+      <c r="L20" s="33" t="n"/>
+      <c r="M20" s="33" t="n"/>
+      <c r="N20" s="33" t="n"/>
+      <c r="O20" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$N$7,C20:N20,"Y"),"")</f>
         <v/>
       </c>
-      <c r="P20" s="26">
+      <c r="P20" s="28">
         <f>COUNTIF(C20:N20,"Y")</f>
         <v/>
       </c>
-      <c r="Q20" s="27">
+      <c r="Q20" s="29">
         <f>SUMPRODUCT((C$7:$N$7=1)*(C20:N20="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="17" customHeight="1">
-      <c r="A21" s="32" t="n">
+      <c r="A21" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="B21" s="33" t="inlineStr">
+      <c r="B21" s="35" t="inlineStr">
         <is>
           <t>Ash</t>
         </is>
       </c>
-      <c r="C21" s="18" t="n"/>
-      <c r="D21" s="18" t="n"/>
-      <c r="E21" s="18" t="n"/>
-      <c r="F21" s="18" t="n"/>
-      <c r="G21" s="18" t="n"/>
-      <c r="H21" s="18" t="n"/>
-      <c r="I21" s="18" t="n"/>
-      <c r="J21" s="18" t="n"/>
-      <c r="K21" s="18" t="n"/>
-      <c r="L21" s="18" t="n"/>
-      <c r="M21" s="18" t="n"/>
-      <c r="N21" s="18" t="n"/>
-      <c r="O21" s="17">
+      <c r="C21" s="19" t="n"/>
+      <c r="D21" s="19" t="n"/>
+      <c r="E21" s="19" t="n"/>
+      <c r="F21" s="19" t="n"/>
+      <c r="G21" s="19" t="n"/>
+      <c r="H21" s="19" t="n"/>
+      <c r="I21" s="19" t="n"/>
+      <c r="J21" s="19" t="n"/>
+      <c r="K21" s="19" t="n"/>
+      <c r="L21" s="19" t="n"/>
+      <c r="M21" s="19" t="n"/>
+      <c r="N21" s="19" t="n"/>
+      <c r="O21" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$N$7,C21:N21,"Y"),"")</f>
         <v/>
       </c>
-      <c r="P21" s="26">
+      <c r="P21" s="28">
         <f>COUNTIF(C21:N21,"Y")</f>
         <v/>
       </c>
-      <c r="Q21" s="27">
+      <c r="Q21" s="29">
         <f>SUMPRODUCT((C$7:$N$7=1)*(C21:N21="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="17" customHeight="1">
-      <c r="A22" s="29" t="n">
+      <c r="A22" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="B22" s="30" t="inlineStr">
+      <c r="B22" s="32" t="inlineStr">
         <is>
           <t>Autumn</t>
         </is>
       </c>
-      <c r="C22" s="31" t="n"/>
-      <c r="D22" s="31" t="n"/>
-      <c r="E22" s="31" t="n"/>
-      <c r="F22" s="31" t="n"/>
-      <c r="G22" s="31" t="n"/>
-      <c r="H22" s="31" t="n"/>
-      <c r="I22" s="31" t="n"/>
-      <c r="J22" s="31" t="n"/>
-      <c r="K22" s="31" t="n"/>
-      <c r="L22" s="31" t="n"/>
-      <c r="M22" s="31" t="n"/>
-      <c r="N22" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O22" s="17">
+      <c r="C22" s="33" t="n"/>
+      <c r="D22" s="33" t="n"/>
+      <c r="E22" s="33" t="n"/>
+      <c r="F22" s="33" t="n"/>
+      <c r="G22" s="33" t="n"/>
+      <c r="H22" s="33" t="n"/>
+      <c r="I22" s="33" t="n"/>
+      <c r="J22" s="33" t="n"/>
+      <c r="K22" s="33" t="n"/>
+      <c r="L22" s="33" t="n"/>
+      <c r="M22" s="33" t="n"/>
+      <c r="N22" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O22" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$N$7,C22:N22,"Y"),"")</f>
         <v/>
       </c>
-      <c r="P22" s="26">
+      <c r="P22" s="28">
         <f>COUNTIF(C22:N22,"Y")</f>
         <v/>
       </c>
-      <c r="Q22" s="27">
+      <c r="Q22" s="29">
         <f>SUMPRODUCT((C$7:$N$7=1)*(C22:N22="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="17" customHeight="1">
-      <c r="A23" s="32" t="n">
+      <c r="A23" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="B23" s="33" t="inlineStr">
+      <c r="B23" s="35" t="inlineStr">
         <is>
           <t>Bri</t>
         </is>
       </c>
-      <c r="C23" s="18" t="n"/>
-      <c r="D23" s="18" t="n"/>
-      <c r="E23" s="18" t="n"/>
-      <c r="F23" s="18" t="n"/>
-      <c r="G23" s="18" t="n"/>
-      <c r="H23" s="18" t="n"/>
-      <c r="I23" s="18" t="n"/>
-      <c r="J23" s="18" t="n"/>
-      <c r="K23" s="18" t="n"/>
-      <c r="L23" s="18" t="n"/>
-      <c r="M23" s="18" t="n"/>
-      <c r="N23" s="18" t="n"/>
-      <c r="O23" s="17">
+      <c r="C23" s="19" t="n"/>
+      <c r="D23" s="19" t="n"/>
+      <c r="E23" s="19" t="n"/>
+      <c r="F23" s="19" t="n"/>
+      <c r="G23" s="19" t="n"/>
+      <c r="H23" s="19" t="n"/>
+      <c r="I23" s="19" t="n"/>
+      <c r="J23" s="19" t="n"/>
+      <c r="K23" s="19" t="n"/>
+      <c r="L23" s="19" t="n"/>
+      <c r="M23" s="19" t="n"/>
+      <c r="N23" s="19" t="n"/>
+      <c r="O23" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$N$7,C23:N23,"Y"),"")</f>
         <v/>
       </c>
-      <c r="P23" s="26">
+      <c r="P23" s="28">
         <f>COUNTIF(C23:N23,"Y")</f>
         <v/>
       </c>
-      <c r="Q23" s="27">
+      <c r="Q23" s="29">
         <f>SUMPRODUCT((C$7:$N$7=1)*(C23:N23="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="17" customHeight="1">
-      <c r="A24" s="29" t="n">
+      <c r="A24" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="B24" s="30" t="inlineStr">
+      <c r="B24" s="32" t="inlineStr">
         <is>
           <t>Dakayla</t>
         </is>
       </c>
-      <c r="C24" s="31" t="n"/>
-      <c r="D24" s="31" t="n"/>
-      <c r="E24" s="31" t="n"/>
-      <c r="F24" s="31" t="n"/>
-      <c r="G24" s="31" t="n"/>
-      <c r="H24" s="31" t="n"/>
-      <c r="I24" s="31" t="n"/>
-      <c r="J24" s="31" t="n"/>
-      <c r="K24" s="31" t="n"/>
-      <c r="L24" s="31" t="n"/>
-      <c r="M24" s="31" t="n"/>
-      <c r="N24" s="31" t="n"/>
-      <c r="O24" s="17">
+      <c r="C24" s="33" t="n"/>
+      <c r="D24" s="33" t="n"/>
+      <c r="E24" s="33" t="n"/>
+      <c r="F24" s="33" t="n"/>
+      <c r="G24" s="33" t="n"/>
+      <c r="H24" s="33" t="n"/>
+      <c r="I24" s="33" t="n"/>
+      <c r="J24" s="33" t="n"/>
+      <c r="K24" s="33" t="n"/>
+      <c r="L24" s="33" t="n"/>
+      <c r="M24" s="33" t="n"/>
+      <c r="N24" s="33" t="n"/>
+      <c r="O24" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$N$7,C24:N24,"Y"),"")</f>
         <v/>
       </c>
-      <c r="P24" s="26">
+      <c r="P24" s="28">
         <f>COUNTIF(C24:N24,"Y")</f>
         <v/>
       </c>
-      <c r="Q24" s="27">
+      <c r="Q24" s="29">
         <f>SUMPRODUCT((C$7:$N$7=1)*(C24:N24="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="17" customHeight="1">
-      <c r="A25" s="32" t="n">
+      <c r="A25" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="B25" s="33" t="inlineStr">
+      <c r="B25" s="35" t="inlineStr">
         <is>
           <t>Divan</t>
         </is>
       </c>
-      <c r="C25" s="18" t="n"/>
-      <c r="D25" s="18" t="n"/>
-      <c r="E25" s="18" t="n"/>
-      <c r="F25" s="18" t="n"/>
-      <c r="G25" s="18" t="n"/>
-      <c r="H25" s="18" t="n"/>
-      <c r="I25" s="18" t="n"/>
-      <c r="J25" s="18" t="n"/>
-      <c r="K25" s="18" t="n"/>
-      <c r="L25" s="18" t="n"/>
-      <c r="M25" s="18" t="n"/>
-      <c r="N25" s="18" t="n"/>
-      <c r="O25" s="17">
+      <c r="C25" s="19" t="n"/>
+      <c r="D25" s="19" t="n"/>
+      <c r="E25" s="19" t="n"/>
+      <c r="F25" s="19" t="n"/>
+      <c r="G25" s="19" t="n"/>
+      <c r="H25" s="19" t="n"/>
+      <c r="I25" s="19" t="n"/>
+      <c r="J25" s="19" t="n"/>
+      <c r="K25" s="19" t="n"/>
+      <c r="L25" s="19" t="n"/>
+      <c r="M25" s="19" t="n"/>
+      <c r="N25" s="19" t="n"/>
+      <c r="O25" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$N$7,C25:N25,"Y"),"")</f>
         <v/>
       </c>
-      <c r="P25" s="26">
+      <c r="P25" s="28">
         <f>COUNTIF(C25:N25,"Y")</f>
         <v/>
       </c>
-      <c r="Q25" s="27">
+      <c r="Q25" s="29">
         <f>SUMPRODUCT((C$7:$N$7=1)*(C25:N25="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="17" customHeight="1">
-      <c r="A26" s="29" t="n">
+      <c r="A26" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="B26" s="30" t="inlineStr">
+      <c r="B26" s="32" t="inlineStr">
         <is>
           <t>Francisco</t>
         </is>
       </c>
-      <c r="C26" s="31" t="n"/>
-      <c r="D26" s="31" t="n"/>
-      <c r="E26" s="31" t="n"/>
-      <c r="F26" s="31" t="n"/>
-      <c r="G26" s="31" t="n"/>
-      <c r="H26" s="31" t="n"/>
-      <c r="I26" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J26" s="31" t="n"/>
-      <c r="K26" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L26" s="31" t="n"/>
-      <c r="M26" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N26" s="31" t="n"/>
-      <c r="O26" s="17">
+      <c r="C26" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D26" s="33" t="n"/>
+      <c r="E26" s="33" t="n"/>
+      <c r="F26" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G26" s="33" t="n"/>
+      <c r="H26" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I26" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J26" s="33" t="n"/>
+      <c r="K26" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L26" s="33" t="n"/>
+      <c r="M26" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N26" s="33" t="n"/>
+      <c r="O26" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$N$7,C26:N26,"Y"),"")</f>
         <v/>
       </c>
-      <c r="P26" s="26">
+      <c r="P26" s="28">
         <f>COUNTIF(C26:N26,"Y")</f>
         <v/>
       </c>
-      <c r="Q26" s="27">
+      <c r="Q26" s="29">
         <f>SUMPRODUCT((C$7:$N$7=1)*(C26:N26="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="17" customHeight="1">
-      <c r="A27" s="32" t="n">
+      <c r="A27" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="B27" s="33" t="inlineStr">
+      <c r="B27" s="35" t="inlineStr">
         <is>
           <t>Grace</t>
         </is>
       </c>
-      <c r="C27" s="18" t="n"/>
-      <c r="D27" s="18" t="n"/>
-      <c r="E27" s="18" t="n"/>
-      <c r="F27" s="18" t="n"/>
-      <c r="G27" s="18" t="n"/>
-      <c r="H27" s="18" t="n"/>
-      <c r="I27" s="18" t="n"/>
-      <c r="J27" s="18" t="n"/>
-      <c r="K27" s="18" t="n"/>
-      <c r="L27" s="18" t="n"/>
-      <c r="M27" s="18" t="n"/>
-      <c r="N27" s="18" t="n"/>
-      <c r="O27" s="17">
+      <c r="C27" s="19" t="n"/>
+      <c r="D27" s="19" t="n"/>
+      <c r="E27" s="19" t="n"/>
+      <c r="F27" s="19" t="n"/>
+      <c r="G27" s="19" t="n"/>
+      <c r="H27" s="19" t="n"/>
+      <c r="I27" s="19" t="n"/>
+      <c r="J27" s="19" t="n"/>
+      <c r="K27" s="19" t="n"/>
+      <c r="L27" s="19" t="n"/>
+      <c r="M27" s="19" t="n"/>
+      <c r="N27" s="19" t="n"/>
+      <c r="O27" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$N$7,C27:N27,"Y"),"")</f>
         <v/>
       </c>
-      <c r="P27" s="26">
+      <c r="P27" s="28">
         <f>COUNTIF(C27:N27,"Y")</f>
         <v/>
       </c>
-      <c r="Q27" s="27">
+      <c r="Q27" s="29">
         <f>SUMPRODUCT((C$7:$N$7=1)*(C27:N27="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="17" customHeight="1">
-      <c r="A28" s="29" t="n">
+      <c r="A28" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="B28" s="30" t="inlineStr">
+      <c r="B28" s="32" t="inlineStr">
         <is>
           <t>Jada</t>
         </is>
       </c>
-      <c r="C28" s="31" t="n"/>
-      <c r="D28" s="31" t="n"/>
-      <c r="E28" s="31" t="n"/>
-      <c r="F28" s="31" t="n"/>
-      <c r="G28" s="31" t="n"/>
-      <c r="H28" s="31" t="n"/>
-      <c r="I28" s="31" t="n"/>
-      <c r="J28" s="31" t="n"/>
-      <c r="K28" s="31" t="n"/>
-      <c r="L28" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M28" s="31" t="n"/>
-      <c r="N28" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O28" s="17">
+      <c r="C28" s="33" t="n"/>
+      <c r="D28" s="33" t="n"/>
+      <c r="E28" s="33" t="n"/>
+      <c r="F28" s="33" t="n"/>
+      <c r="G28" s="33" t="n"/>
+      <c r="H28" s="33" t="n"/>
+      <c r="I28" s="33" t="n"/>
+      <c r="J28" s="33" t="n"/>
+      <c r="K28" s="33" t="n"/>
+      <c r="L28" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M28" s="33" t="n"/>
+      <c r="N28" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O28" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$N$7,C28:N28,"Y"),"")</f>
         <v/>
       </c>
-      <c r="P28" s="26">
+      <c r="P28" s="28">
         <f>COUNTIF(C28:N28,"Y")</f>
         <v/>
       </c>
-      <c r="Q28" s="27">
+      <c r="Q28" s="29">
         <f>SUMPRODUCT((C$7:$N$7=1)*(C28:N28="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="17" customHeight="1">
-      <c r="A29" s="32" t="n">
+      <c r="A29" s="34" t="n">
         <v>10</v>
       </c>
-      <c r="B29" s="33" t="inlineStr">
+      <c r="B29" s="35" t="inlineStr">
         <is>
           <t>Jeremiah</t>
         </is>
       </c>
-      <c r="C29" s="18" t="n"/>
-      <c r="D29" s="18" t="n"/>
-      <c r="E29" s="18" t="n"/>
-      <c r="F29" s="18" t="n"/>
-      <c r="G29" s="18" t="n"/>
-      <c r="H29" s="18" t="n"/>
-      <c r="I29" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J29" s="18" t="n"/>
-      <c r="K29" s="18" t="n"/>
-      <c r="L29" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M29" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N29" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O29" s="17">
+      <c r="C29" s="19" t="n"/>
+      <c r="D29" s="19" t="n"/>
+      <c r="E29" s="19" t="n"/>
+      <c r="F29" s="19" t="n"/>
+      <c r="G29" s="19" t="n"/>
+      <c r="H29" s="19" t="n"/>
+      <c r="I29" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J29" s="19" t="n"/>
+      <c r="K29" s="19" t="n"/>
+      <c r="L29" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M29" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N29" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O29" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$N$7,C29:N29,"Y"),"")</f>
         <v/>
       </c>
-      <c r="P29" s="26">
+      <c r="P29" s="28">
         <f>COUNTIF(C29:N29,"Y")</f>
         <v/>
       </c>
-      <c r="Q29" s="27">
+      <c r="Q29" s="29">
         <f>SUMPRODUCT((C$7:$N$7=1)*(C29:N29="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="17" customHeight="1">
-      <c r="A30" s="29" t="n">
+      <c r="A30" s="31" t="n">
         <v>11</v>
       </c>
-      <c r="B30" s="30" t="inlineStr">
+      <c r="B30" s="32" t="inlineStr">
         <is>
           <t>Kable</t>
         </is>
       </c>
-      <c r="C30" s="31" t="n"/>
-      <c r="D30" s="31" t="n"/>
-      <c r="E30" s="31" t="n"/>
-      <c r="F30" s="31" t="n"/>
-      <c r="G30" s="31" t="n"/>
-      <c r="H30" s="31" t="n"/>
-      <c r="I30" s="31" t="n"/>
-      <c r="J30" s="31" t="n"/>
-      <c r="K30" s="31" t="n"/>
-      <c r="L30" s="31" t="n"/>
-      <c r="M30" s="31" t="n"/>
-      <c r="N30" s="31" t="n"/>
-      <c r="O30" s="17">
+      <c r="C30" s="33" t="n"/>
+      <c r="D30" s="33" t="n"/>
+      <c r="E30" s="33" t="n"/>
+      <c r="F30" s="33" t="n"/>
+      <c r="G30" s="33" t="n"/>
+      <c r="H30" s="33" t="n"/>
+      <c r="I30" s="33" t="n"/>
+      <c r="J30" s="33" t="n"/>
+      <c r="K30" s="33" t="n"/>
+      <c r="L30" s="33" t="n"/>
+      <c r="M30" s="33" t="n"/>
+      <c r="N30" s="33" t="n"/>
+      <c r="O30" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$N$7,C30:N30,"Y"),"")</f>
         <v/>
       </c>
-      <c r="P30" s="26">
+      <c r="P30" s="28">
         <f>COUNTIF(C30:N30,"Y")</f>
         <v/>
       </c>
-      <c r="Q30" s="27">
+      <c r="Q30" s="29">
         <f>SUMPRODUCT((C$7:$N$7=1)*(C30:N30="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="17" customHeight="1">
-      <c r="A31" s="32" t="n">
+      <c r="A31" s="34" t="n">
         <v>12</v>
       </c>
-      <c r="B31" s="33" t="inlineStr">
+      <c r="B31" s="35" t="inlineStr">
         <is>
           <t>Kayla</t>
         </is>
       </c>
-      <c r="C31" s="18" t="n"/>
-      <c r="D31" s="18" t="n"/>
-      <c r="E31" s="18" t="n"/>
-      <c r="F31" s="18" t="n"/>
-      <c r="G31" s="18" t="n"/>
-      <c r="H31" s="18" t="n"/>
-      <c r="I31" s="18" t="n"/>
-      <c r="J31" s="18" t="n"/>
-      <c r="K31" s="18" t="n"/>
-      <c r="L31" s="18" t="n"/>
-      <c r="M31" s="18" t="n"/>
-      <c r="N31" s="18" t="n"/>
-      <c r="O31" s="17">
+      <c r="C31" s="19" t="n"/>
+      <c r="D31" s="19" t="n"/>
+      <c r="E31" s="19" t="n"/>
+      <c r="F31" s="19" t="n"/>
+      <c r="G31" s="19" t="n"/>
+      <c r="H31" s="19" t="n"/>
+      <c r="I31" s="19" t="n"/>
+      <c r="J31" s="19" t="n"/>
+      <c r="K31" s="19" t="n"/>
+      <c r="L31" s="19" t="n"/>
+      <c r="M31" s="19" t="n"/>
+      <c r="N31" s="19" t="n"/>
+      <c r="O31" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$N$7,C31:N31,"Y"),"")</f>
         <v/>
       </c>
-      <c r="P31" s="26">
+      <c r="P31" s="28">
         <f>COUNTIF(C31:N31,"Y")</f>
         <v/>
       </c>
-      <c r="Q31" s="27">
+      <c r="Q31" s="29">
         <f>SUMPRODUCT((C$7:$N$7=1)*(C31:N31="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="17" customHeight="1">
-      <c r="A32" s="29" t="n">
+      <c r="A32" s="31" t="n">
         <v>13</v>
       </c>
-      <c r="B32" s="30" t="inlineStr">
+      <c r="B32" s="32" t="inlineStr">
         <is>
           <t>Kenzie</t>
         </is>
       </c>
-      <c r="C32" s="31" t="n"/>
-      <c r="D32" s="31" t="n"/>
-      <c r="E32" s="31" t="n"/>
-      <c r="F32" s="31" t="n"/>
-      <c r="G32" s="31" t="n"/>
-      <c r="H32" s="31" t="n"/>
-      <c r="I32" s="31" t="n"/>
-      <c r="J32" s="31" t="n"/>
-      <c r="K32" s="31" t="n"/>
-      <c r="L32" s="31" t="n"/>
-      <c r="M32" s="31" t="n"/>
-      <c r="N32" s="31" t="n"/>
-      <c r="O32" s="17">
+      <c r="C32" s="33" t="n"/>
+      <c r="D32" s="33" t="n"/>
+      <c r="E32" s="33" t="n"/>
+      <c r="F32" s="33" t="n"/>
+      <c r="G32" s="33" t="n"/>
+      <c r="H32" s="33" t="n"/>
+      <c r="I32" s="33" t="n"/>
+      <c r="J32" s="33" t="n"/>
+      <c r="K32" s="33" t="n"/>
+      <c r="L32" s="33" t="n"/>
+      <c r="M32" s="33" t="n"/>
+      <c r="N32" s="33" t="n"/>
+      <c r="O32" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$N$7,C32:N32,"Y"),"")</f>
         <v/>
       </c>
-      <c r="P32" s="26">
+      <c r="P32" s="28">
         <f>COUNTIF(C32:N32,"Y")</f>
         <v/>
       </c>
-      <c r="Q32" s="27">
+      <c r="Q32" s="29">
         <f>SUMPRODUCT((C$7:$N$7=1)*(C32:N32="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="17" customHeight="1">
-      <c r="A33" s="32" t="n">
+      <c r="A33" s="34" t="n">
         <v>14</v>
       </c>
-      <c r="B33" s="33" t="inlineStr">
+      <c r="B33" s="35" t="inlineStr">
         <is>
           <t>Lidy</t>
         </is>
       </c>
-      <c r="C33" s="18" t="n"/>
-      <c r="D33" s="18" t="n"/>
-      <c r="E33" s="18" t="n"/>
-      <c r="F33" s="18" t="n"/>
-      <c r="G33" s="18" t="n"/>
-      <c r="H33" s="18" t="n"/>
-      <c r="I33" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J33" s="18" t="n"/>
-      <c r="K33" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L33" s="18" t="n"/>
-      <c r="M33" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N33" s="18" t="n"/>
-      <c r="O33" s="17">
+      <c r="C33" s="19" t="n"/>
+      <c r="D33" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E33" s="19" t="n"/>
+      <c r="F33" s="19" t="n"/>
+      <c r="G33" s="19" t="n"/>
+      <c r="H33" s="19" t="n"/>
+      <c r="I33" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J33" s="19" t="n"/>
+      <c r="K33" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L33" s="19" t="n"/>
+      <c r="M33" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N33" s="19" t="n"/>
+      <c r="O33" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$N$7,C33:N33,"Y"),"")</f>
         <v/>
       </c>
-      <c r="P33" s="26">
+      <c r="P33" s="28">
         <f>COUNTIF(C33:N33,"Y")</f>
         <v/>
       </c>
-      <c r="Q33" s="27">
+      <c r="Q33" s="29">
         <f>SUMPRODUCT((C$7:$N$7=1)*(C33:N33="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="17" customHeight="1">
-      <c r="A34" s="29" t="n">
+      <c r="A34" s="31" t="n">
         <v>15</v>
       </c>
-      <c r="B34" s="30" t="inlineStr">
+      <c r="B34" s="32" t="inlineStr">
         <is>
           <t>Maylin</t>
         </is>
       </c>
-      <c r="C34" s="31" t="n"/>
-      <c r="D34" s="31" t="n"/>
-      <c r="E34" s="31" t="n"/>
-      <c r="F34" s="31" t="n"/>
-      <c r="G34" s="31" t="n"/>
-      <c r="H34" s="31" t="n"/>
-      <c r="I34" s="31" t="n"/>
-      <c r="J34" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K34" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L34" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M34" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N34" s="31" t="n"/>
-      <c r="O34" s="17">
+      <c r="C34" s="33" t="n"/>
+      <c r="D34" s="33" t="n"/>
+      <c r="E34" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F34" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G34" s="33" t="n"/>
+      <c r="H34" s="33" t="n"/>
+      <c r="I34" s="33" t="n"/>
+      <c r="J34" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K34" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L34" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M34" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N34" s="33" t="n"/>
+      <c r="O34" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$N$7,C34:N34,"Y"),"")</f>
         <v/>
       </c>
-      <c r="P34" s="26">
+      <c r="P34" s="28">
         <f>COUNTIF(C34:N34,"Y")</f>
         <v/>
       </c>
-      <c r="Q34" s="27">
+      <c r="Q34" s="29">
         <f>SUMPRODUCT((C$7:$N$7=1)*(C34:N34="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="17" customHeight="1">
-      <c r="A35" s="32" t="n">
+      <c r="A35" s="34" t="n">
         <v>16</v>
       </c>
-      <c r="B35" s="33" t="inlineStr">
+      <c r="B35" s="35" t="inlineStr">
         <is>
           <t>Mike</t>
         </is>
       </c>
-      <c r="C35" s="18" t="n"/>
-      <c r="D35" s="18" t="n"/>
-      <c r="E35" s="18" t="n"/>
-      <c r="F35" s="18" t="n"/>
-      <c r="G35" s="18" t="n"/>
-      <c r="H35" s="18" t="n"/>
-      <c r="I35" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J35" s="18" t="n"/>
-      <c r="K35" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L35" s="18" t="n"/>
-      <c r="M35" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N35" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O35" s="17">
+      <c r="C35" s="19" t="n"/>
+      <c r="D35" s="19" t="n"/>
+      <c r="E35" s="19" t="n"/>
+      <c r="F35" s="19" t="n"/>
+      <c r="G35" s="19" t="n"/>
+      <c r="H35" s="19" t="n"/>
+      <c r="I35" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J35" s="19" t="n"/>
+      <c r="K35" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L35" s="19" t="n"/>
+      <c r="M35" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N35" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O35" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$N$7,C35:N35,"Y"),"")</f>
         <v/>
       </c>
-      <c r="P35" s="26">
+      <c r="P35" s="28">
         <f>COUNTIF(C35:N35,"Y")</f>
         <v/>
       </c>
-      <c r="Q35" s="27">
+      <c r="Q35" s="29">
         <f>SUMPRODUCT((C$7:$N$7=1)*(C35:N35="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="17" customHeight="1">
-      <c r="A36" s="29" t="n">
+      <c r="A36" s="31" t="n">
         <v>17</v>
       </c>
-      <c r="B36" s="30" t="inlineStr">
+      <c r="B36" s="32" t="inlineStr">
         <is>
           <t>Richard</t>
         </is>
       </c>
-      <c r="C36" s="31" t="n"/>
-      <c r="D36" s="31" t="n"/>
-      <c r="E36" s="31" t="n"/>
-      <c r="F36" s="31" t="n"/>
-      <c r="G36" s="31" t="n"/>
-      <c r="H36" s="31" t="n"/>
-      <c r="I36" s="31" t="n"/>
-      <c r="J36" s="31" t="n"/>
-      <c r="K36" s="31" t="n"/>
-      <c r="L36" s="31" t="n"/>
-      <c r="M36" s="31" t="n"/>
-      <c r="N36" s="31" t="n"/>
-      <c r="O36" s="17">
+      <c r="C36" s="33" t="n"/>
+      <c r="D36" s="33" t="n"/>
+      <c r="E36" s="33" t="n"/>
+      <c r="F36" s="33" t="n"/>
+      <c r="G36" s="33" t="n"/>
+      <c r="H36" s="33" t="n"/>
+      <c r="I36" s="33" t="n"/>
+      <c r="J36" s="33" t="n"/>
+      <c r="K36" s="33" t="n"/>
+      <c r="L36" s="33" t="n"/>
+      <c r="M36" s="33" t="n"/>
+      <c r="N36" s="33" t="n"/>
+      <c r="O36" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$N$7,C36:N36,"Y"),"")</f>
         <v/>
       </c>
-      <c r="P36" s="26">
+      <c r="P36" s="28">
         <f>COUNTIF(C36:N36,"Y")</f>
         <v/>
       </c>
-      <c r="Q36" s="27">
+      <c r="Q36" s="29">
         <f>SUMPRODUCT((C$7:$N$7=1)*(C36:N36="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="17" customHeight="1">
-      <c r="A37" s="32" t="n">
+      <c r="A37" s="34" t="n">
         <v>18</v>
       </c>
-      <c r="B37" s="33" t="inlineStr">
+      <c r="B37" s="35" t="inlineStr">
         <is>
           <t>Samuel</t>
         </is>
       </c>
-      <c r="C37" s="18" t="n"/>
-      <c r="D37" s="18" t="n"/>
-      <c r="E37" s="18" t="n"/>
-      <c r="F37" s="18" t="n"/>
-      <c r="G37" s="18" t="n"/>
-      <c r="H37" s="18" t="n"/>
-      <c r="I37" s="18" t="n"/>
-      <c r="J37" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K37" s="18" t="n"/>
-      <c r="L37" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M37" s="18" t="n"/>
-      <c r="N37" s="18" t="n"/>
-      <c r="O37" s="17">
+      <c r="C37" s="19" t="n"/>
+      <c r="D37" s="19" t="n"/>
+      <c r="E37" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F37" s="19" t="n"/>
+      <c r="G37" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H37" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I37" s="19" t="n"/>
+      <c r="J37" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K37" s="19" t="n"/>
+      <c r="L37" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M37" s="19" t="n"/>
+      <c r="N37" s="19" t="n"/>
+      <c r="O37" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$N$7,C37:N37,"Y"),"")</f>
         <v/>
       </c>
-      <c r="P37" s="26">
+      <c r="P37" s="28">
         <f>COUNTIF(C37:N37,"Y")</f>
         <v/>
       </c>
-      <c r="Q37" s="27">
+      <c r="Q37" s="29">
         <f>SUMPRODUCT((C$7:$N$7=1)*(C37:N37="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="17" customHeight="1">
-      <c r="A38" s="29" t="n">
+      <c r="A38" s="31" t="n">
         <v>19</v>
       </c>
-      <c r="B38" s="30" t="inlineStr">
+      <c r="B38" s="32" t="inlineStr">
         <is>
           <t>Zach</t>
         </is>
       </c>
-      <c r="C38" s="31" t="n"/>
-      <c r="D38" s="31" t="n"/>
-      <c r="E38" s="31" t="n"/>
-      <c r="F38" s="31" t="n"/>
-      <c r="G38" s="31" t="n"/>
-      <c r="H38" s="31" t="n"/>
-      <c r="I38" s="31" t="n"/>
-      <c r="J38" s="31" t="n"/>
-      <c r="K38" s="31" t="n"/>
-      <c r="L38" s="31" t="n"/>
-      <c r="M38" s="31" t="n"/>
-      <c r="N38" s="31" t="n"/>
-      <c r="O38" s="17">
+      <c r="C38" s="33" t="n"/>
+      <c r="D38" s="33" t="n"/>
+      <c r="E38" s="33" t="n"/>
+      <c r="F38" s="33" t="n"/>
+      <c r="G38" s="33" t="n"/>
+      <c r="H38" s="33" t="n"/>
+      <c r="I38" s="33" t="n"/>
+      <c r="J38" s="33" t="n"/>
+      <c r="K38" s="33" t="n"/>
+      <c r="L38" s="33" t="n"/>
+      <c r="M38" s="33" t="n"/>
+      <c r="N38" s="33" t="n"/>
+      <c r="O38" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$N$7,C38:N38,"Y"),"")</f>
         <v/>
       </c>
-      <c r="P38" s="26">
+      <c r="P38" s="28">
         <f>COUNTIF(C38:N38,"Y")</f>
         <v/>
       </c>
-      <c r="Q38" s="27">
+      <c r="Q38" s="29">
         <f>SUMPRODUCT((C$7:$N$7=1)*(C38:N38="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="3" t="inlineStr"/>
-      <c r="B39" s="34" t="inlineStr">
+      <c r="B39" s="36" t="inlineStr">
         <is>
           <t>Total on shift</t>
         </is>
@@ -3434,13 +4150,13 @@
         <f>SUM(P14:P38)</f>
         <v/>
       </c>
-      <c r="Q39" s="35">
+      <c r="Q39" s="37">
         <f>SUM(Q14:Q38)</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="12" customHeight="1">
-      <c r="A40" s="36" t="inlineStr">
+      <c r="A40" s="38" t="inlineStr">
         <is>
           <t>Y = on shift during shop's meal window. Personal Avg = average score of shops worked. Bonus = $50 per 100% shop worked.</t>
         </is>
@@ -3811,7 +4527,7 @@
       <c r="P7" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="Q7" s="17">
+      <c r="Q7" s="18">
         <f>IFERROR(AVERAGE(C7:P7),"")</f>
         <v/>
       </c>
@@ -3819,1116 +4535,1200 @@
       <c r="S7" s="12" t="inlineStr"/>
     </row>
     <row r="8" ht="13" customHeight="1">
-      <c r="A8" s="18" t="inlineStr"/>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr"/>
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr"/>
-      <c r="D8" s="18" t="inlineStr"/>
-      <c r="E8" s="18" t="inlineStr"/>
-      <c r="F8" s="18" t="inlineStr"/>
-      <c r="G8" s="18" t="inlineStr"/>
-      <c r="H8" s="18" t="inlineStr"/>
-      <c r="I8" s="18" t="inlineStr"/>
-      <c r="J8" s="18" t="inlineStr"/>
-      <c r="K8" s="18" t="inlineStr"/>
-      <c r="L8" s="39" t="n">
+      <c r="C8" s="19" t="inlineStr"/>
+      <c r="D8" s="19" t="inlineStr"/>
+      <c r="E8" s="19" t="inlineStr"/>
+      <c r="F8" s="19" t="inlineStr"/>
+      <c r="G8" s="19" t="inlineStr"/>
+      <c r="H8" s="19" t="inlineStr"/>
+      <c r="I8" s="19" t="inlineStr"/>
+      <c r="J8" s="19" t="inlineStr"/>
+      <c r="K8" s="19" t="inlineStr"/>
+      <c r="L8" s="40" t="n">
         <v>0.72</v>
       </c>
-      <c r="M8" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" s="39" t="n">
+      <c r="M8" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" s="40" t="n">
         <v>0.72</v>
       </c>
-      <c r="O8" s="39" t="n">
+      <c r="O8" s="40" t="n">
         <v>0.77</v>
       </c>
-      <c r="P8" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="20">
+      <c r="P8" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="21">
         <f>IFERROR(AVERAGE(C8:P8),"")</f>
         <v/>
       </c>
-      <c r="R8" s="18" t="inlineStr"/>
-      <c r="S8" s="18" t="inlineStr"/>
+      <c r="R8" s="19" t="inlineStr"/>
+      <c r="S8" s="19" t="inlineStr"/>
     </row>
     <row r="9" ht="13" customHeight="1">
-      <c r="A9" s="18" t="inlineStr"/>
-      <c r="B9" s="19" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr"/>
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>Quality</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr"/>
-      <c r="D9" s="18" t="inlineStr"/>
-      <c r="E9" s="18" t="inlineStr"/>
-      <c r="F9" s="18" t="inlineStr"/>
-      <c r="G9" s="18" t="inlineStr"/>
-      <c r="H9" s="18" t="inlineStr"/>
-      <c r="I9" s="18" t="inlineStr"/>
-      <c r="J9" s="18" t="inlineStr"/>
-      <c r="K9" s="18" t="inlineStr"/>
-      <c r="L9" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="P9" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="20">
+      <c r="C9" s="19" t="inlineStr"/>
+      <c r="D9" s="19" t="inlineStr"/>
+      <c r="E9" s="19" t="inlineStr"/>
+      <c r="F9" s="19" t="inlineStr"/>
+      <c r="G9" s="19" t="inlineStr"/>
+      <c r="H9" s="19" t="inlineStr"/>
+      <c r="I9" s="19" t="inlineStr"/>
+      <c r="J9" s="19" t="inlineStr"/>
+      <c r="K9" s="19" t="inlineStr"/>
+      <c r="L9" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="21">
         <f>IFERROR(AVERAGE(C9:P9),"")</f>
         <v/>
       </c>
-      <c r="R9" s="18" t="inlineStr"/>
-      <c r="S9" s="18" t="inlineStr"/>
+      <c r="R9" s="19" t="inlineStr"/>
+      <c r="S9" s="19" t="inlineStr"/>
     </row>
     <row r="10" ht="13" customHeight="1">
-      <c r="A10" s="18" t="inlineStr"/>
-      <c r="B10" s="19" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr"/>
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>Cleanliness</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr"/>
-      <c r="D10" s="18" t="inlineStr"/>
-      <c r="E10" s="18" t="inlineStr"/>
-      <c r="F10" s="18" t="inlineStr"/>
-      <c r="G10" s="18" t="inlineStr"/>
-      <c r="H10" s="18" t="inlineStr"/>
-      <c r="I10" s="18" t="inlineStr"/>
-      <c r="J10" s="18" t="inlineStr"/>
-      <c r="K10" s="18" t="inlineStr"/>
-      <c r="L10" s="38" t="n">
+      <c r="C10" s="19" t="inlineStr"/>
+      <c r="D10" s="19" t="inlineStr"/>
+      <c r="E10" s="19" t="inlineStr"/>
+      <c r="F10" s="19" t="inlineStr"/>
+      <c r="G10" s="19" t="inlineStr"/>
+      <c r="H10" s="19" t="inlineStr"/>
+      <c r="I10" s="19" t="inlineStr"/>
+      <c r="J10" s="19" t="inlineStr"/>
+      <c r="K10" s="19" t="inlineStr"/>
+      <c r="L10" s="39" t="n">
         <v>1</v>
       </c>
       <c r="M10" s="42" t="n">
         <v>0.8</v>
       </c>
-      <c r="N10" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" s="39" t="n">
+      <c r="N10" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" s="40" t="n">
         <v>0.72</v>
       </c>
-      <c r="P10" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="20">
+      <c r="P10" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="21">
         <f>IFERROR(AVERAGE(C10:P10),"")</f>
         <v/>
       </c>
-      <c r="R10" s="18" t="inlineStr"/>
-      <c r="S10" s="18" t="inlineStr"/>
+      <c r="R10" s="19" t="inlineStr"/>
+      <c r="S10" s="19" t="inlineStr"/>
     </row>
     <row r="11" ht="13" customHeight="1">
-      <c r="A11" s="18" t="inlineStr"/>
-      <c r="B11" s="19" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr"/>
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>Customer Sat</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr"/>
-      <c r="D11" s="18" t="inlineStr"/>
-      <c r="E11" s="18" t="inlineStr"/>
-      <c r="F11" s="18" t="inlineStr"/>
-      <c r="G11" s="18" t="inlineStr"/>
-      <c r="H11" s="18" t="inlineStr"/>
-      <c r="I11" s="18" t="inlineStr"/>
-      <c r="J11" s="18" t="inlineStr"/>
-      <c r="K11" s="18" t="inlineStr"/>
-      <c r="L11" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="P11" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q11" s="20">
+      <c r="C11" s="19" t="inlineStr"/>
+      <c r="D11" s="19" t="inlineStr"/>
+      <c r="E11" s="19" t="inlineStr"/>
+      <c r="F11" s="19" t="inlineStr"/>
+      <c r="G11" s="19" t="inlineStr"/>
+      <c r="H11" s="19" t="inlineStr"/>
+      <c r="I11" s="19" t="inlineStr"/>
+      <c r="J11" s="19" t="inlineStr"/>
+      <c r="K11" s="19" t="inlineStr"/>
+      <c r="L11" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="P11" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="21">
         <f>IFERROR(AVERAGE(C11:P11),"")</f>
         <v/>
       </c>
-      <c r="R11" s="18" t="inlineStr"/>
-      <c r="S11" s="18" t="inlineStr"/>
+      <c r="R11" s="19" t="inlineStr"/>
+      <c r="S11" s="19" t="inlineStr"/>
     </row>
     <row r="12" ht="6" customHeight="1">
-      <c r="A12" s="21" t="n"/>
+      <c r="A12" s="22" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="22" t="inlineStr">
+      <c r="A13" s="23" t="inlineStr">
         <is>
           <t>MANAGERS</t>
         </is>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="B14" s="24" t="inlineStr">
+      <c r="A14" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" s="25" t="inlineStr">
         <is>
           <t>Madison C.</t>
         </is>
       </c>
-      <c r="C14" s="25" t="n"/>
-      <c r="D14" s="25" t="n"/>
-      <c r="E14" s="25" t="n"/>
-      <c r="F14" s="25" t="n"/>
-      <c r="G14" s="25" t="n"/>
-      <c r="H14" s="25" t="n"/>
-      <c r="I14" s="25" t="n"/>
-      <c r="J14" s="25" t="n"/>
-      <c r="K14" s="25" t="n"/>
-      <c r="L14" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M14" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N14" s="25" t="n"/>
-      <c r="O14" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="P14" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="Q14" s="17">
+      <c r="C14" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D14" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E14" s="27" t="n"/>
+      <c r="F14" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G14" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H14" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I14" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J14" s="27" t="n"/>
+      <c r="K14" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L14" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M14" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N14" s="27" t="n"/>
+      <c r="O14" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P14" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q14" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$P$7,C14:P14,"Y"),"")</f>
         <v/>
       </c>
-      <c r="R14" s="26">
+      <c r="R14" s="28">
         <f>COUNTIF(C14:P14,"Y")</f>
         <v/>
       </c>
-      <c r="S14" s="27">
+      <c r="S14" s="29">
         <f>SUMPRODUCT((C$7:$P$7=1)*(C14:P14="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="23" t="n">
+      <c r="A15" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="B15" s="24" t="inlineStr">
+      <c r="B15" s="25" t="inlineStr">
         <is>
           <t>Vicki L.</t>
         </is>
       </c>
-      <c r="C15" s="25" t="n"/>
-      <c r="D15" s="25" t="n"/>
-      <c r="E15" s="25" t="n"/>
-      <c r="F15" s="25" t="n"/>
-      <c r="G15" s="25" t="n"/>
-      <c r="H15" s="25" t="n"/>
-      <c r="I15" s="25" t="n"/>
-      <c r="J15" s="25" t="n"/>
-      <c r="K15" s="25" t="n"/>
-      <c r="L15" s="25" t="n"/>
-      <c r="M15" s="25" t="n"/>
-      <c r="N15" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O15" s="25" t="n"/>
-      <c r="P15" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="Q15" s="17">
+      <c r="C15" s="27" t="n"/>
+      <c r="D15" s="27" t="n"/>
+      <c r="E15" s="27" t="n"/>
+      <c r="F15" s="27" t="n"/>
+      <c r="G15" s="27" t="n"/>
+      <c r="H15" s="27" t="n"/>
+      <c r="I15" s="27" t="n"/>
+      <c r="J15" s="27" t="n"/>
+      <c r="K15" s="27" t="n"/>
+      <c r="L15" s="27" t="n"/>
+      <c r="M15" s="27" t="n"/>
+      <c r="N15" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O15" s="27" t="n"/>
+      <c r="P15" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q15" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$P$7,C15:P15,"Y"),"")</f>
         <v/>
       </c>
-      <c r="R15" s="26">
+      <c r="R15" s="28">
         <f>COUNTIF(C15:P15,"Y")</f>
         <v/>
       </c>
-      <c r="S15" s="27">
+      <c r="S15" s="29">
         <f>SUMPRODUCT((C$7:$P$7=1)*(C15:P15="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
-      <c r="A16" s="23" t="n">
+      <c r="A16" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="B16" s="24" t="inlineStr">
+      <c r="B16" s="25" t="inlineStr">
         <is>
           <t>Kasey W.</t>
         </is>
       </c>
-      <c r="C16" s="25" t="n"/>
-      <c r="D16" s="25" t="n"/>
-      <c r="E16" s="25" t="n"/>
-      <c r="F16" s="25" t="n"/>
-      <c r="G16" s="25" t="n"/>
-      <c r="H16" s="25" t="n"/>
-      <c r="I16" s="25" t="n"/>
-      <c r="J16" s="25" t="n"/>
-      <c r="K16" s="25" t="n"/>
-      <c r="L16" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M16" s="25" t="n"/>
-      <c r="N16" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O16" s="25" t="n"/>
-      <c r="P16" s="25" t="n"/>
-      <c r="Q16" s="17">
+      <c r="C16" s="27" t="n"/>
+      <c r="D16" s="27" t="n"/>
+      <c r="E16" s="27" t="n"/>
+      <c r="F16" s="27" t="n"/>
+      <c r="G16" s="27" t="n"/>
+      <c r="H16" s="27" t="n"/>
+      <c r="I16" s="27" t="n"/>
+      <c r="J16" s="27" t="n"/>
+      <c r="K16" s="27" t="n"/>
+      <c r="L16" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M16" s="27" t="n"/>
+      <c r="N16" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O16" s="27" t="n"/>
+      <c r="P16" s="27" t="n"/>
+      <c r="Q16" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$P$7,C16:P16,"Y"),"")</f>
         <v/>
       </c>
-      <c r="R16" s="26">
+      <c r="R16" s="28">
         <f>COUNTIF(C16:P16,"Y")</f>
         <v/>
       </c>
-      <c r="S16" s="27">
+      <c r="S16" s="29">
         <f>SUMPRODUCT((C$7:$P$7=1)*(C16:P16="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
-      <c r="A17" s="23" t="n">
+      <c r="A17" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="B17" s="24" t="inlineStr">
+      <c r="B17" s="25" t="inlineStr">
         <is>
           <t>Nathan R.</t>
         </is>
       </c>
-      <c r="C17" s="25" t="n"/>
-      <c r="D17" s="25" t="n"/>
-      <c r="E17" s="25" t="n"/>
-      <c r="F17" s="25" t="n"/>
-      <c r="G17" s="25" t="n"/>
-      <c r="H17" s="25" t="n"/>
-      <c r="I17" s="25" t="n"/>
-      <c r="J17" s="25" t="n"/>
-      <c r="K17" s="25" t="n"/>
-      <c r="L17" s="25" t="n"/>
-      <c r="M17" s="25" t="n"/>
-      <c r="N17" s="25" t="n"/>
-      <c r="O17" s="25" t="n"/>
-      <c r="P17" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="Q17" s="17">
+      <c r="C17" s="27" t="n"/>
+      <c r="D17" s="27" t="n"/>
+      <c r="E17" s="27" t="n"/>
+      <c r="F17" s="27" t="n"/>
+      <c r="G17" s="27" t="n"/>
+      <c r="H17" s="27" t="n"/>
+      <c r="I17" s="27" t="n"/>
+      <c r="J17" s="27" t="n"/>
+      <c r="K17" s="27" t="n"/>
+      <c r="L17" s="27" t="n"/>
+      <c r="M17" s="27" t="n"/>
+      <c r="N17" s="27" t="n"/>
+      <c r="O17" s="27" t="n"/>
+      <c r="P17" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q17" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$P$7,C17:P17,"Y"),"")</f>
         <v/>
       </c>
-      <c r="R17" s="26">
+      <c r="R17" s="28">
         <f>COUNTIF(C17:P17,"Y")</f>
         <v/>
       </c>
-      <c r="S17" s="27">
+      <c r="S17" s="29">
         <f>SUMPRODUCT((C$7:$P$7=1)*(C17:P17="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="6" customHeight="1">
-      <c r="A18" s="21" t="n"/>
+      <c r="A18" s="22" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="28" t="inlineStr">
+      <c r="A19" s="30" t="inlineStr">
         <is>
           <t>CREW</t>
         </is>
       </c>
     </row>
     <row r="20" ht="17" customHeight="1">
-      <c r="A20" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="B20" s="30" t="inlineStr">
+      <c r="A20" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" s="32" t="inlineStr">
         <is>
           <t>Alen</t>
         </is>
       </c>
-      <c r="C20" s="31" t="n"/>
-      <c r="D20" s="31" t="n"/>
-      <c r="E20" s="31" t="n"/>
-      <c r="F20" s="31" t="n"/>
-      <c r="G20" s="31" t="n"/>
-      <c r="H20" s="31" t="n"/>
-      <c r="I20" s="31" t="n"/>
-      <c r="J20" s="31" t="n"/>
-      <c r="K20" s="31" t="n"/>
-      <c r="L20" s="31" t="n"/>
-      <c r="M20" s="31" t="n"/>
-      <c r="N20" s="31" t="n"/>
-      <c r="O20" s="31" t="n"/>
-      <c r="P20" s="31" t="n"/>
-      <c r="Q20" s="17">
+      <c r="C20" s="33" t="n"/>
+      <c r="D20" s="33" t="n"/>
+      <c r="E20" s="33" t="n"/>
+      <c r="F20" s="33" t="n"/>
+      <c r="G20" s="33" t="n"/>
+      <c r="H20" s="33" t="n"/>
+      <c r="I20" s="33" t="n"/>
+      <c r="J20" s="33" t="n"/>
+      <c r="K20" s="33" t="n"/>
+      <c r="L20" s="33" t="n"/>
+      <c r="M20" s="33" t="n"/>
+      <c r="N20" s="33" t="n"/>
+      <c r="O20" s="33" t="n"/>
+      <c r="P20" s="33" t="n"/>
+      <c r="Q20" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$P$7,C20:P20,"Y"),"")</f>
         <v/>
       </c>
-      <c r="R20" s="26">
+      <c r="R20" s="28">
         <f>COUNTIF(C20:P20,"Y")</f>
         <v/>
       </c>
-      <c r="S20" s="27">
+      <c r="S20" s="29">
         <f>SUMPRODUCT((C$7:$P$7=1)*(C20:P20="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="17" customHeight="1">
-      <c r="A21" s="32" t="n">
+      <c r="A21" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="B21" s="33" t="inlineStr">
+      <c r="B21" s="35" t="inlineStr">
         <is>
           <t>Ash</t>
         </is>
       </c>
-      <c r="C21" s="18" t="n"/>
-      <c r="D21" s="18" t="n"/>
-      <c r="E21" s="18" t="n"/>
-      <c r="F21" s="18" t="n"/>
-      <c r="G21" s="18" t="n"/>
-      <c r="H21" s="18" t="n"/>
-      <c r="I21" s="18" t="n"/>
-      <c r="J21" s="18" t="n"/>
-      <c r="K21" s="18" t="n"/>
-      <c r="L21" s="18" t="n"/>
-      <c r="M21" s="18" t="n"/>
-      <c r="N21" s="18" t="n"/>
-      <c r="O21" s="18" t="n"/>
-      <c r="P21" s="18" t="n"/>
-      <c r="Q21" s="17">
+      <c r="C21" s="19" t="n"/>
+      <c r="D21" s="19" t="n"/>
+      <c r="E21" s="19" t="n"/>
+      <c r="F21" s="19" t="n"/>
+      <c r="G21" s="19" t="n"/>
+      <c r="H21" s="19" t="n"/>
+      <c r="I21" s="19" t="n"/>
+      <c r="J21" s="19" t="n"/>
+      <c r="K21" s="19" t="n"/>
+      <c r="L21" s="19" t="n"/>
+      <c r="M21" s="19" t="n"/>
+      <c r="N21" s="19" t="n"/>
+      <c r="O21" s="19" t="n"/>
+      <c r="P21" s="19" t="n"/>
+      <c r="Q21" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$P$7,C21:P21,"Y"),"")</f>
         <v/>
       </c>
-      <c r="R21" s="26">
+      <c r="R21" s="28">
         <f>COUNTIF(C21:P21,"Y")</f>
         <v/>
       </c>
-      <c r="S21" s="27">
+      <c r="S21" s="29">
         <f>SUMPRODUCT((C$7:$P$7=1)*(C21:P21="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="17" customHeight="1">
-      <c r="A22" s="29" t="n">
+      <c r="A22" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="B22" s="30" t="inlineStr">
+      <c r="B22" s="32" t="inlineStr">
         <is>
           <t>Autumn</t>
         </is>
       </c>
-      <c r="C22" s="31" t="n"/>
-      <c r="D22" s="31" t="n"/>
-      <c r="E22" s="31" t="n"/>
-      <c r="F22" s="31" t="n"/>
-      <c r="G22" s="31" t="n"/>
-      <c r="H22" s="31" t="n"/>
-      <c r="I22" s="31" t="n"/>
-      <c r="J22" s="31" t="n"/>
-      <c r="K22" s="31" t="n"/>
-      <c r="L22" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M22" s="31" t="n"/>
-      <c r="N22" s="31" t="n"/>
-      <c r="O22" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="P22" s="31" t="n"/>
-      <c r="Q22" s="17">
+      <c r="C22" s="33" t="n"/>
+      <c r="D22" s="33" t="n"/>
+      <c r="E22" s="33" t="n"/>
+      <c r="F22" s="33" t="n"/>
+      <c r="G22" s="33" t="n"/>
+      <c r="H22" s="33" t="n"/>
+      <c r="I22" s="33" t="n"/>
+      <c r="J22" s="33" t="n"/>
+      <c r="K22" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L22" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M22" s="33" t="n"/>
+      <c r="N22" s="33" t="n"/>
+      <c r="O22" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P22" s="33" t="n"/>
+      <c r="Q22" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$P$7,C22:P22,"Y"),"")</f>
         <v/>
       </c>
-      <c r="R22" s="26">
+      <c r="R22" s="28">
         <f>COUNTIF(C22:P22,"Y")</f>
         <v/>
       </c>
-      <c r="S22" s="27">
+      <c r="S22" s="29">
         <f>SUMPRODUCT((C$7:$P$7=1)*(C22:P22="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="17" customHeight="1">
-      <c r="A23" s="32" t="n">
+      <c r="A23" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="B23" s="33" t="inlineStr">
+      <c r="B23" s="35" t="inlineStr">
         <is>
           <t>Bri</t>
         </is>
       </c>
-      <c r="C23" s="18" t="n"/>
-      <c r="D23" s="18" t="n"/>
-      <c r="E23" s="18" t="n"/>
-      <c r="F23" s="18" t="n"/>
-      <c r="G23" s="18" t="n"/>
-      <c r="H23" s="18" t="n"/>
-      <c r="I23" s="18" t="n"/>
-      <c r="J23" s="18" t="n"/>
-      <c r="K23" s="18" t="n"/>
-      <c r="L23" s="18" t="n"/>
-      <c r="M23" s="18" t="n"/>
-      <c r="N23" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O23" s="18" t="n"/>
-      <c r="P23" s="18" t="n"/>
-      <c r="Q23" s="17">
+      <c r="C23" s="19" t="n"/>
+      <c r="D23" s="19" t="n"/>
+      <c r="E23" s="19" t="n"/>
+      <c r="F23" s="19" t="n"/>
+      <c r="G23" s="19" t="n"/>
+      <c r="H23" s="19" t="n"/>
+      <c r="I23" s="19" t="n"/>
+      <c r="J23" s="19" t="n"/>
+      <c r="K23" s="19" t="n"/>
+      <c r="L23" s="19" t="n"/>
+      <c r="M23" s="19" t="n"/>
+      <c r="N23" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O23" s="19" t="n"/>
+      <c r="P23" s="19" t="n"/>
+      <c r="Q23" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$P$7,C23:P23,"Y"),"")</f>
         <v/>
       </c>
-      <c r="R23" s="26">
+      <c r="R23" s="28">
         <f>COUNTIF(C23:P23,"Y")</f>
         <v/>
       </c>
-      <c r="S23" s="27">
+      <c r="S23" s="29">
         <f>SUMPRODUCT((C$7:$P$7=1)*(C23:P23="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="17" customHeight="1">
-      <c r="A24" s="29" t="n">
+      <c r="A24" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="B24" s="30" t="inlineStr">
+      <c r="B24" s="32" t="inlineStr">
         <is>
           <t>Dakayla</t>
         </is>
       </c>
-      <c r="C24" s="31" t="n"/>
-      <c r="D24" s="31" t="n"/>
-      <c r="E24" s="31" t="n"/>
-      <c r="F24" s="31" t="n"/>
-      <c r="G24" s="31" t="n"/>
-      <c r="H24" s="31" t="n"/>
-      <c r="I24" s="31" t="n"/>
-      <c r="J24" s="31" t="n"/>
-      <c r="K24" s="31" t="n"/>
-      <c r="L24" s="31" t="n"/>
-      <c r="M24" s="31" t="n"/>
-      <c r="N24" s="31" t="n"/>
-      <c r="O24" s="31" t="n"/>
-      <c r="P24" s="31" t="n"/>
-      <c r="Q24" s="17">
+      <c r="C24" s="33" t="n"/>
+      <c r="D24" s="33" t="n"/>
+      <c r="E24" s="33" t="n"/>
+      <c r="F24" s="33" t="n"/>
+      <c r="G24" s="33" t="n"/>
+      <c r="H24" s="33" t="n"/>
+      <c r="I24" s="33" t="n"/>
+      <c r="J24" s="33" t="n"/>
+      <c r="K24" s="33" t="n"/>
+      <c r="L24" s="33" t="n"/>
+      <c r="M24" s="33" t="n"/>
+      <c r="N24" s="33" t="n"/>
+      <c r="O24" s="33" t="n"/>
+      <c r="P24" s="33" t="n"/>
+      <c r="Q24" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$P$7,C24:P24,"Y"),"")</f>
         <v/>
       </c>
-      <c r="R24" s="26">
+      <c r="R24" s="28">
         <f>COUNTIF(C24:P24,"Y")</f>
         <v/>
       </c>
-      <c r="S24" s="27">
+      <c r="S24" s="29">
         <f>SUMPRODUCT((C$7:$P$7=1)*(C24:P24="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="17" customHeight="1">
-      <c r="A25" s="32" t="n">
+      <c r="A25" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="B25" s="33" t="inlineStr">
+      <c r="B25" s="35" t="inlineStr">
         <is>
           <t>Divan</t>
         </is>
       </c>
-      <c r="C25" s="18" t="n"/>
-      <c r="D25" s="18" t="n"/>
-      <c r="E25" s="18" t="n"/>
-      <c r="F25" s="18" t="n"/>
-      <c r="G25" s="18" t="n"/>
-      <c r="H25" s="18" t="n"/>
-      <c r="I25" s="18" t="n"/>
-      <c r="J25" s="18" t="n"/>
-      <c r="K25" s="18" t="n"/>
-      <c r="L25" s="18" t="n"/>
-      <c r="M25" s="18" t="n"/>
-      <c r="N25" s="18" t="n"/>
-      <c r="O25" s="18" t="n"/>
-      <c r="P25" s="18" t="n"/>
-      <c r="Q25" s="17">
+      <c r="C25" s="19" t="n"/>
+      <c r="D25" s="19" t="n"/>
+      <c r="E25" s="19" t="n"/>
+      <c r="F25" s="19" t="n"/>
+      <c r="G25" s="19" t="n"/>
+      <c r="H25" s="19" t="n"/>
+      <c r="I25" s="19" t="n"/>
+      <c r="J25" s="19" t="n"/>
+      <c r="K25" s="19" t="n"/>
+      <c r="L25" s="19" t="n"/>
+      <c r="M25" s="19" t="n"/>
+      <c r="N25" s="19" t="n"/>
+      <c r="O25" s="19" t="n"/>
+      <c r="P25" s="19" t="n"/>
+      <c r="Q25" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$P$7,C25:P25,"Y"),"")</f>
         <v/>
       </c>
-      <c r="R25" s="26">
+      <c r="R25" s="28">
         <f>COUNTIF(C25:P25,"Y")</f>
         <v/>
       </c>
-      <c r="S25" s="27">
+      <c r="S25" s="29">
         <f>SUMPRODUCT((C$7:$P$7=1)*(C25:P25="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="17" customHeight="1">
-      <c r="A26" s="29" t="n">
+      <c r="A26" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="B26" s="30" t="inlineStr">
+      <c r="B26" s="32" t="inlineStr">
         <is>
           <t>Francisco</t>
         </is>
       </c>
-      <c r="C26" s="31" t="n"/>
-      <c r="D26" s="31" t="n"/>
-      <c r="E26" s="31" t="n"/>
-      <c r="F26" s="31" t="n"/>
-      <c r="G26" s="31" t="n"/>
-      <c r="H26" s="31" t="n"/>
-      <c r="I26" s="31" t="n"/>
-      <c r="J26" s="31" t="n"/>
-      <c r="K26" s="31" t="n"/>
-      <c r="L26" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M26" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N26" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O26" s="31" t="n"/>
-      <c r="P26" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="Q26" s="17">
+      <c r="C26" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D26" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E26" s="33" t="n"/>
+      <c r="F26" s="33" t="n"/>
+      <c r="G26" s="33" t="n"/>
+      <c r="H26" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I26" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J26" s="33" t="n"/>
+      <c r="K26" s="33" t="n"/>
+      <c r="L26" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M26" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N26" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O26" s="33" t="n"/>
+      <c r="P26" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q26" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$P$7,C26:P26,"Y"),"")</f>
         <v/>
       </c>
-      <c r="R26" s="26">
+      <c r="R26" s="28">
         <f>COUNTIF(C26:P26,"Y")</f>
         <v/>
       </c>
-      <c r="S26" s="27">
+      <c r="S26" s="29">
         <f>SUMPRODUCT((C$7:$P$7=1)*(C26:P26="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="17" customHeight="1">
-      <c r="A27" s="32" t="n">
+      <c r="A27" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="B27" s="33" t="inlineStr">
+      <c r="B27" s="35" t="inlineStr">
         <is>
           <t>Grace</t>
         </is>
       </c>
-      <c r="C27" s="18" t="n"/>
-      <c r="D27" s="18" t="n"/>
-      <c r="E27" s="18" t="n"/>
-      <c r="F27" s="18" t="n"/>
-      <c r="G27" s="18" t="n"/>
-      <c r="H27" s="18" t="n"/>
-      <c r="I27" s="18" t="n"/>
-      <c r="J27" s="18" t="n"/>
-      <c r="K27" s="18" t="n"/>
-      <c r="L27" s="18" t="n"/>
-      <c r="M27" s="18" t="n"/>
-      <c r="N27" s="18" t="n"/>
-      <c r="O27" s="18" t="n"/>
-      <c r="P27" s="18" t="n"/>
-      <c r="Q27" s="17">
+      <c r="C27" s="19" t="n"/>
+      <c r="D27" s="19" t="n"/>
+      <c r="E27" s="19" t="n"/>
+      <c r="F27" s="19" t="n"/>
+      <c r="G27" s="19" t="n"/>
+      <c r="H27" s="19" t="n"/>
+      <c r="I27" s="19" t="n"/>
+      <c r="J27" s="19" t="n"/>
+      <c r="K27" s="19" t="n"/>
+      <c r="L27" s="19" t="n"/>
+      <c r="M27" s="19" t="n"/>
+      <c r="N27" s="19" t="n"/>
+      <c r="O27" s="19" t="n"/>
+      <c r="P27" s="19" t="n"/>
+      <c r="Q27" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$P$7,C27:P27,"Y"),"")</f>
         <v/>
       </c>
-      <c r="R27" s="26">
+      <c r="R27" s="28">
         <f>COUNTIF(C27:P27,"Y")</f>
         <v/>
       </c>
-      <c r="S27" s="27">
+      <c r="S27" s="29">
         <f>SUMPRODUCT((C$7:$P$7=1)*(C27:P27="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="17" customHeight="1">
-      <c r="A28" s="29" t="n">
+      <c r="A28" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="B28" s="30" t="inlineStr">
+      <c r="B28" s="32" t="inlineStr">
         <is>
           <t>Jada</t>
         </is>
       </c>
-      <c r="C28" s="31" t="n"/>
-      <c r="D28" s="31" t="n"/>
-      <c r="E28" s="31" t="n"/>
-      <c r="F28" s="31" t="n"/>
-      <c r="G28" s="31" t="n"/>
-      <c r="H28" s="31" t="n"/>
-      <c r="I28" s="31" t="n"/>
-      <c r="J28" s="31" t="n"/>
-      <c r="K28" s="31" t="n"/>
-      <c r="L28" s="31" t="n"/>
-      <c r="M28" s="31" t="n"/>
-      <c r="N28" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O28" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="P28" s="31" t="n"/>
-      <c r="Q28" s="17">
+      <c r="C28" s="33" t="n"/>
+      <c r="D28" s="33" t="n"/>
+      <c r="E28" s="33" t="n"/>
+      <c r="F28" s="33" t="n"/>
+      <c r="G28" s="33" t="n"/>
+      <c r="H28" s="33" t="n"/>
+      <c r="I28" s="33" t="n"/>
+      <c r="J28" s="33" t="n"/>
+      <c r="K28" s="33" t="n"/>
+      <c r="L28" s="33" t="n"/>
+      <c r="M28" s="33" t="n"/>
+      <c r="N28" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O28" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P28" s="33" t="n"/>
+      <c r="Q28" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$P$7,C28:P28,"Y"),"")</f>
         <v/>
       </c>
-      <c r="R28" s="26">
+      <c r="R28" s="28">
         <f>COUNTIF(C28:P28,"Y")</f>
         <v/>
       </c>
-      <c r="S28" s="27">
+      <c r="S28" s="29">
         <f>SUMPRODUCT((C$7:$P$7=1)*(C28:P28="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="17" customHeight="1">
-      <c r="A29" s="32" t="n">
+      <c r="A29" s="34" t="n">
         <v>10</v>
       </c>
-      <c r="B29" s="33" t="inlineStr">
+      <c r="B29" s="35" t="inlineStr">
         <is>
           <t>Jeremiah</t>
         </is>
       </c>
-      <c r="C29" s="18" t="n"/>
-      <c r="D29" s="18" t="n"/>
-      <c r="E29" s="18" t="n"/>
-      <c r="F29" s="18" t="n"/>
-      <c r="G29" s="18" t="n"/>
-      <c r="H29" s="18" t="n"/>
-      <c r="I29" s="18" t="n"/>
-      <c r="J29" s="18" t="n"/>
-      <c r="K29" s="18" t="n"/>
-      <c r="L29" s="18" t="n"/>
-      <c r="M29" s="18" t="n"/>
-      <c r="N29" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O29" s="18" t="n"/>
-      <c r="P29" s="18" t="n"/>
-      <c r="Q29" s="17">
+      <c r="C29" s="19" t="n"/>
+      <c r="D29" s="19" t="n"/>
+      <c r="E29" s="19" t="n"/>
+      <c r="F29" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G29" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H29" s="19" t="n"/>
+      <c r="I29" s="19" t="n"/>
+      <c r="J29" s="19" t="n"/>
+      <c r="K29" s="19" t="n"/>
+      <c r="L29" s="19" t="n"/>
+      <c r="M29" s="19" t="n"/>
+      <c r="N29" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O29" s="19" t="n"/>
+      <c r="P29" s="19" t="n"/>
+      <c r="Q29" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$P$7,C29:P29,"Y"),"")</f>
         <v/>
       </c>
-      <c r="R29" s="26">
+      <c r="R29" s="28">
         <f>COUNTIF(C29:P29,"Y")</f>
         <v/>
       </c>
-      <c r="S29" s="27">
+      <c r="S29" s="29">
         <f>SUMPRODUCT((C$7:$P$7=1)*(C29:P29="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="17" customHeight="1">
-      <c r="A30" s="29" t="n">
+      <c r="A30" s="31" t="n">
         <v>11</v>
       </c>
-      <c r="B30" s="30" t="inlineStr">
+      <c r="B30" s="32" t="inlineStr">
         <is>
           <t>Kable</t>
         </is>
       </c>
-      <c r="C30" s="31" t="n"/>
-      <c r="D30" s="31" t="n"/>
-      <c r="E30" s="31" t="n"/>
-      <c r="F30" s="31" t="n"/>
-      <c r="G30" s="31" t="n"/>
-      <c r="H30" s="31" t="n"/>
-      <c r="I30" s="31" t="n"/>
-      <c r="J30" s="31" t="n"/>
-      <c r="K30" s="31" t="n"/>
-      <c r="L30" s="31" t="n"/>
-      <c r="M30" s="31" t="n"/>
-      <c r="N30" s="31" t="n"/>
-      <c r="O30" s="31" t="n"/>
-      <c r="P30" s="31" t="n"/>
-      <c r="Q30" s="17">
+      <c r="C30" s="33" t="n"/>
+      <c r="D30" s="33" t="n"/>
+      <c r="E30" s="33" t="n"/>
+      <c r="F30" s="33" t="n"/>
+      <c r="G30" s="33" t="n"/>
+      <c r="H30" s="33" t="n"/>
+      <c r="I30" s="33" t="n"/>
+      <c r="J30" s="33" t="n"/>
+      <c r="K30" s="33" t="n"/>
+      <c r="L30" s="33" t="n"/>
+      <c r="M30" s="33" t="n"/>
+      <c r="N30" s="33" t="n"/>
+      <c r="O30" s="33" t="n"/>
+      <c r="P30" s="33" t="n"/>
+      <c r="Q30" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$P$7,C30:P30,"Y"),"")</f>
         <v/>
       </c>
-      <c r="R30" s="26">
+      <c r="R30" s="28">
         <f>COUNTIF(C30:P30,"Y")</f>
         <v/>
       </c>
-      <c r="S30" s="27">
+      <c r="S30" s="29">
         <f>SUMPRODUCT((C$7:$P$7=1)*(C30:P30="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="17" customHeight="1">
-      <c r="A31" s="32" t="n">
+      <c r="A31" s="34" t="n">
         <v>12</v>
       </c>
-      <c r="B31" s="33" t="inlineStr">
+      <c r="B31" s="35" t="inlineStr">
         <is>
           <t>Kayla</t>
         </is>
       </c>
-      <c r="C31" s="18" t="n"/>
-      <c r="D31" s="18" t="n"/>
-      <c r="E31" s="18" t="n"/>
-      <c r="F31" s="18" t="n"/>
-      <c r="G31" s="18" t="n"/>
-      <c r="H31" s="18" t="n"/>
-      <c r="I31" s="18" t="n"/>
-      <c r="J31" s="18" t="n"/>
-      <c r="K31" s="18" t="n"/>
-      <c r="L31" s="18" t="n"/>
-      <c r="M31" s="18" t="n"/>
-      <c r="N31" s="18" t="n"/>
-      <c r="O31" s="18" t="n"/>
-      <c r="P31" s="18" t="n"/>
-      <c r="Q31" s="17">
+      <c r="C31" s="19" t="n"/>
+      <c r="D31" s="19" t="n"/>
+      <c r="E31" s="19" t="n"/>
+      <c r="F31" s="19" t="n"/>
+      <c r="G31" s="19" t="n"/>
+      <c r="H31" s="19" t="n"/>
+      <c r="I31" s="19" t="n"/>
+      <c r="J31" s="19" t="n"/>
+      <c r="K31" s="19" t="n"/>
+      <c r="L31" s="19" t="n"/>
+      <c r="M31" s="19" t="n"/>
+      <c r="N31" s="19" t="n"/>
+      <c r="O31" s="19" t="n"/>
+      <c r="P31" s="19" t="n"/>
+      <c r="Q31" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$P$7,C31:P31,"Y"),"")</f>
         <v/>
       </c>
-      <c r="R31" s="26">
+      <c r="R31" s="28">
         <f>COUNTIF(C31:P31,"Y")</f>
         <v/>
       </c>
-      <c r="S31" s="27">
+      <c r="S31" s="29">
         <f>SUMPRODUCT((C$7:$P$7=1)*(C31:P31="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="17" customHeight="1">
-      <c r="A32" s="29" t="n">
+      <c r="A32" s="31" t="n">
         <v>13</v>
       </c>
-      <c r="B32" s="30" t="inlineStr">
+      <c r="B32" s="32" t="inlineStr">
         <is>
           <t>Kenzie</t>
         </is>
       </c>
-      <c r="C32" s="31" t="n"/>
-      <c r="D32" s="31" t="n"/>
-      <c r="E32" s="31" t="n"/>
-      <c r="F32" s="31" t="n"/>
-      <c r="G32" s="31" t="n"/>
-      <c r="H32" s="31" t="n"/>
-      <c r="I32" s="31" t="n"/>
-      <c r="J32" s="31" t="n"/>
-      <c r="K32" s="31" t="n"/>
-      <c r="L32" s="31" t="n"/>
-      <c r="M32" s="31" t="n"/>
-      <c r="N32" s="31" t="n"/>
-      <c r="O32" s="31" t="n"/>
-      <c r="P32" s="31" t="n"/>
-      <c r="Q32" s="17">
+      <c r="C32" s="33" t="n"/>
+      <c r="D32" s="33" t="n"/>
+      <c r="E32" s="33" t="n"/>
+      <c r="F32" s="33" t="n"/>
+      <c r="G32" s="33" t="n"/>
+      <c r="H32" s="33" t="n"/>
+      <c r="I32" s="33" t="n"/>
+      <c r="J32" s="33" t="n"/>
+      <c r="K32" s="33" t="n"/>
+      <c r="L32" s="33" t="n"/>
+      <c r="M32" s="33" t="n"/>
+      <c r="N32" s="33" t="n"/>
+      <c r="O32" s="33" t="n"/>
+      <c r="P32" s="33" t="n"/>
+      <c r="Q32" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$P$7,C32:P32,"Y"),"")</f>
         <v/>
       </c>
-      <c r="R32" s="26">
+      <c r="R32" s="28">
         <f>COUNTIF(C32:P32,"Y")</f>
         <v/>
       </c>
-      <c r="S32" s="27">
+      <c r="S32" s="29">
         <f>SUMPRODUCT((C$7:$P$7=1)*(C32:P32="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="17" customHeight="1">
-      <c r="A33" s="32" t="n">
+      <c r="A33" s="34" t="n">
         <v>14</v>
       </c>
-      <c r="B33" s="33" t="inlineStr">
+      <c r="B33" s="35" t="inlineStr">
         <is>
           <t>Lidy</t>
         </is>
       </c>
-      <c r="C33" s="18" t="n"/>
-      <c r="D33" s="18" t="n"/>
-      <c r="E33" s="18" t="n"/>
-      <c r="F33" s="18" t="n"/>
-      <c r="G33" s="18" t="n"/>
-      <c r="H33" s="18" t="n"/>
-      <c r="I33" s="18" t="n"/>
-      <c r="J33" s="18" t="n"/>
-      <c r="K33" s="18" t="n"/>
-      <c r="L33" s="18" t="n"/>
-      <c r="M33" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N33" s="18" t="n"/>
-      <c r="O33" s="18" t="n"/>
-      <c r="P33" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="Q33" s="17">
+      <c r="C33" s="19" t="n"/>
+      <c r="D33" s="19" t="n"/>
+      <c r="E33" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F33" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G33" s="19" t="n"/>
+      <c r="H33" s="19" t="n"/>
+      <c r="I33" s="19" t="n"/>
+      <c r="J33" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K33" s="19" t="n"/>
+      <c r="L33" s="19" t="n"/>
+      <c r="M33" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N33" s="19" t="n"/>
+      <c r="O33" s="19" t="n"/>
+      <c r="P33" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q33" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$P$7,C33:P33,"Y"),"")</f>
         <v/>
       </c>
-      <c r="R33" s="26">
+      <c r="R33" s="28">
         <f>COUNTIF(C33:P33,"Y")</f>
         <v/>
       </c>
-      <c r="S33" s="27">
+      <c r="S33" s="29">
         <f>SUMPRODUCT((C$7:$P$7=1)*(C33:P33="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="17" customHeight="1">
-      <c r="A34" s="29" t="n">
+      <c r="A34" s="31" t="n">
         <v>15</v>
       </c>
-      <c r="B34" s="30" t="inlineStr">
+      <c r="B34" s="32" t="inlineStr">
         <is>
           <t>Maylin</t>
         </is>
       </c>
-      <c r="C34" s="31" t="n"/>
-      <c r="D34" s="31" t="n"/>
-      <c r="E34" s="31" t="n"/>
-      <c r="F34" s="31" t="n"/>
-      <c r="G34" s="31" t="n"/>
-      <c r="H34" s="31" t="n"/>
-      <c r="I34" s="31" t="n"/>
-      <c r="J34" s="31" t="n"/>
-      <c r="K34" s="31" t="n"/>
-      <c r="L34" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M34" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N34" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O34" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="P34" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="Q34" s="17">
+      <c r="C34" s="33" t="n"/>
+      <c r="D34" s="33" t="n"/>
+      <c r="E34" s="33" t="n"/>
+      <c r="F34" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G34" s="33" t="n"/>
+      <c r="H34" s="33" t="n"/>
+      <c r="I34" s="33" t="n"/>
+      <c r="J34" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K34" s="33" t="n"/>
+      <c r="L34" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M34" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N34" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O34" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P34" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q34" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$P$7,C34:P34,"Y"),"")</f>
         <v/>
       </c>
-      <c r="R34" s="26">
+      <c r="R34" s="28">
         <f>COUNTIF(C34:P34,"Y")</f>
         <v/>
       </c>
-      <c r="S34" s="27">
+      <c r="S34" s="29">
         <f>SUMPRODUCT((C$7:$P$7=1)*(C34:P34="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="17" customHeight="1">
-      <c r="A35" s="32" t="n">
+      <c r="A35" s="34" t="n">
         <v>16</v>
       </c>
-      <c r="B35" s="33" t="inlineStr">
+      <c r="B35" s="35" t="inlineStr">
         <is>
           <t>Mike</t>
         </is>
       </c>
-      <c r="C35" s="18" t="n"/>
-      <c r="D35" s="18" t="n"/>
-      <c r="E35" s="18" t="n"/>
-      <c r="F35" s="18" t="n"/>
-      <c r="G35" s="18" t="n"/>
-      <c r="H35" s="18" t="n"/>
-      <c r="I35" s="18" t="n"/>
-      <c r="J35" s="18" t="n"/>
-      <c r="K35" s="18" t="n"/>
-      <c r="L35" s="18" t="n"/>
-      <c r="M35" s="18" t="n"/>
-      <c r="N35" s="18" t="n"/>
-      <c r="O35" s="18" t="n"/>
-      <c r="P35" s="18" t="n"/>
-      <c r="Q35" s="17">
+      <c r="C35" s="19" t="n"/>
+      <c r="D35" s="19" t="n"/>
+      <c r="E35" s="19" t="n"/>
+      <c r="F35" s="19" t="n"/>
+      <c r="G35" s="19" t="n"/>
+      <c r="H35" s="19" t="n"/>
+      <c r="I35" s="19" t="n"/>
+      <c r="J35" s="19" t="n"/>
+      <c r="K35" s="19" t="n"/>
+      <c r="L35" s="19" t="n"/>
+      <c r="M35" s="19" t="n"/>
+      <c r="N35" s="19" t="n"/>
+      <c r="O35" s="19" t="n"/>
+      <c r="P35" s="19" t="n"/>
+      <c r="Q35" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$P$7,C35:P35,"Y"),"")</f>
         <v/>
       </c>
-      <c r="R35" s="26">
+      <c r="R35" s="28">
         <f>COUNTIF(C35:P35,"Y")</f>
         <v/>
       </c>
-      <c r="S35" s="27">
+      <c r="S35" s="29">
         <f>SUMPRODUCT((C$7:$P$7=1)*(C35:P35="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="17" customHeight="1">
-      <c r="A36" s="29" t="n">
+      <c r="A36" s="31" t="n">
         <v>17</v>
       </c>
-      <c r="B36" s="30" t="inlineStr">
+      <c r="B36" s="32" t="inlineStr">
         <is>
           <t>Richard</t>
         </is>
       </c>
-      <c r="C36" s="31" t="n"/>
-      <c r="D36" s="31" t="n"/>
-      <c r="E36" s="31" t="n"/>
-      <c r="F36" s="31" t="n"/>
-      <c r="G36" s="31" t="n"/>
-      <c r="H36" s="31" t="n"/>
-      <c r="I36" s="31" t="n"/>
-      <c r="J36" s="31" t="n"/>
-      <c r="K36" s="31" t="n"/>
-      <c r="L36" s="31" t="n"/>
-      <c r="M36" s="31" t="n"/>
-      <c r="N36" s="31" t="n"/>
-      <c r="O36" s="31" t="n"/>
-      <c r="P36" s="31" t="n"/>
-      <c r="Q36" s="17">
+      <c r="C36" s="33" t="n"/>
+      <c r="D36" s="33" t="n"/>
+      <c r="E36" s="33" t="n"/>
+      <c r="F36" s="33" t="n"/>
+      <c r="G36" s="33" t="n"/>
+      <c r="H36" s="33" t="n"/>
+      <c r="I36" s="33" t="n"/>
+      <c r="J36" s="33" t="n"/>
+      <c r="K36" s="33" t="n"/>
+      <c r="L36" s="33" t="n"/>
+      <c r="M36" s="33" t="n"/>
+      <c r="N36" s="33" t="n"/>
+      <c r="O36" s="33" t="n"/>
+      <c r="P36" s="33" t="n"/>
+      <c r="Q36" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$P$7,C36:P36,"Y"),"")</f>
         <v/>
       </c>
-      <c r="R36" s="26">
+      <c r="R36" s="28">
         <f>COUNTIF(C36:P36,"Y")</f>
         <v/>
       </c>
-      <c r="S36" s="27">
+      <c r="S36" s="29">
         <f>SUMPRODUCT((C$7:$P$7=1)*(C36:P36="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="17" customHeight="1">
-      <c r="A37" s="32" t="n">
+      <c r="A37" s="34" t="n">
         <v>18</v>
       </c>
-      <c r="B37" s="33" t="inlineStr">
+      <c r="B37" s="35" t="inlineStr">
         <is>
           <t>Samuel</t>
         </is>
       </c>
-      <c r="C37" s="18" t="n"/>
-      <c r="D37" s="18" t="n"/>
-      <c r="E37" s="18" t="n"/>
-      <c r="F37" s="18" t="n"/>
-      <c r="G37" s="18" t="n"/>
-      <c r="H37" s="18" t="n"/>
-      <c r="I37" s="18" t="n"/>
-      <c r="J37" s="18" t="n"/>
-      <c r="K37" s="18" t="n"/>
-      <c r="L37" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M37" s="18" t="n"/>
-      <c r="N37" s="18" t="n"/>
-      <c r="O37" s="18" t="n"/>
-      <c r="P37" s="18" t="n"/>
-      <c r="Q37" s="17">
+      <c r="C37" s="19" t="n"/>
+      <c r="D37" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E37" s="19" t="n"/>
+      <c r="F37" s="19" t="n"/>
+      <c r="G37" s="19" t="n"/>
+      <c r="H37" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I37" s="19" t="n"/>
+      <c r="J37" s="19" t="n"/>
+      <c r="K37" s="19" t="n"/>
+      <c r="L37" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M37" s="19" t="n"/>
+      <c r="N37" s="19" t="n"/>
+      <c r="O37" s="19" t="n"/>
+      <c r="P37" s="19" t="n"/>
+      <c r="Q37" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$P$7,C37:P37,"Y"),"")</f>
         <v/>
       </c>
-      <c r="R37" s="26">
+      <c r="R37" s="28">
         <f>COUNTIF(C37:P37,"Y")</f>
         <v/>
       </c>
-      <c r="S37" s="27">
+      <c r="S37" s="29">
         <f>SUMPRODUCT((C$7:$P$7=1)*(C37:P37="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="17" customHeight="1">
-      <c r="A38" s="29" t="n">
+      <c r="A38" s="31" t="n">
         <v>19</v>
       </c>
-      <c r="B38" s="30" t="inlineStr">
+      <c r="B38" s="32" t="inlineStr">
         <is>
           <t>Zach</t>
         </is>
       </c>
-      <c r="C38" s="31" t="n"/>
-      <c r="D38" s="31" t="n"/>
-      <c r="E38" s="31" t="n"/>
-      <c r="F38" s="31" t="n"/>
-      <c r="G38" s="31" t="n"/>
-      <c r="H38" s="31" t="n"/>
-      <c r="I38" s="31" t="n"/>
-      <c r="J38" s="31" t="n"/>
-      <c r="K38" s="31" t="n"/>
-      <c r="L38" s="31" t="n"/>
-      <c r="M38" s="31" t="n"/>
-      <c r="N38" s="31" t="n"/>
-      <c r="O38" s="31" t="n"/>
-      <c r="P38" s="31" t="n"/>
-      <c r="Q38" s="17">
+      <c r="C38" s="33" t="n"/>
+      <c r="D38" s="33" t="n"/>
+      <c r="E38" s="33" t="n"/>
+      <c r="F38" s="33" t="n"/>
+      <c r="G38" s="33" t="n"/>
+      <c r="H38" s="33" t="n"/>
+      <c r="I38" s="33" t="n"/>
+      <c r="J38" s="33" t="n"/>
+      <c r="K38" s="33" t="n"/>
+      <c r="L38" s="33" t="n"/>
+      <c r="M38" s="33" t="n"/>
+      <c r="N38" s="33" t="n"/>
+      <c r="O38" s="33" t="n"/>
+      <c r="P38" s="33" t="n"/>
+      <c r="Q38" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$P$7,C38:P38,"Y"),"")</f>
         <v/>
       </c>
-      <c r="R38" s="26">
+      <c r="R38" s="28">
         <f>COUNTIF(C38:P38,"Y")</f>
         <v/>
       </c>
-      <c r="S38" s="27">
+      <c r="S38" s="29">
         <f>SUMPRODUCT((C$7:$P$7=1)*(C38:P38="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="3" t="inlineStr"/>
-      <c r="B39" s="34" t="inlineStr">
+      <c r="B39" s="36" t="inlineStr">
         <is>
           <t>Total on shift</t>
         </is>
@@ -4994,13 +5794,13 @@
         <f>SUM(R14:R38)</f>
         <v/>
       </c>
-      <c r="S39" s="35">
+      <c r="S39" s="37">
         <f>SUM(S14:S38)</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="12" customHeight="1">
-      <c r="A40" s="36" t="inlineStr">
+      <c r="A40" s="38" t="inlineStr">
         <is>
           <t>Y = on shift during shop's meal window. Personal Avg = average score of shops worked. Bonus = $50 per 100% shop worked.</t>
         </is>
@@ -5334,13 +6134,13 @@
       <c r="I7" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="J7" s="37" t="n">
+      <c r="J7" s="17" t="n">
         <v>0.97</v>
       </c>
       <c r="K7" s="15" t="n">
         <v>0.87</v>
       </c>
-      <c r="L7" s="37" t="n">
+      <c r="L7" s="17" t="n">
         <v>0.95</v>
       </c>
       <c r="M7" s="16" t="n">
@@ -5352,7 +6152,7 @@
       <c r="O7" s="15" t="n">
         <v>0.87</v>
       </c>
-      <c r="P7" s="17">
+      <c r="P7" s="18">
         <f>IFERROR(AVERAGE(C7:O7),"")</f>
         <v/>
       </c>
@@ -5360,1101 +6160,1189 @@
       <c r="R7" s="12" t="inlineStr"/>
     </row>
     <row r="8" ht="13" customHeight="1">
-      <c r="A8" s="18" t="inlineStr"/>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr"/>
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr"/>
-      <c r="D8" s="18" t="inlineStr"/>
-      <c r="E8" s="18" t="inlineStr"/>
-      <c r="F8" s="18" t="inlineStr"/>
-      <c r="G8" s="18" t="inlineStr"/>
-      <c r="H8" s="18" t="inlineStr"/>
-      <c r="I8" s="18" t="inlineStr"/>
-      <c r="J8" s="38" t="n">
+      <c r="C8" s="19" t="inlineStr"/>
+      <c r="D8" s="19" t="inlineStr"/>
+      <c r="E8" s="19" t="inlineStr"/>
+      <c r="F8" s="19" t="inlineStr"/>
+      <c r="G8" s="19" t="inlineStr"/>
+      <c r="H8" s="19" t="inlineStr"/>
+      <c r="I8" s="19" t="inlineStr"/>
+      <c r="J8" s="39" t="n">
         <v>1</v>
       </c>
       <c r="K8" s="42" t="n">
         <v>0.87</v>
       </c>
-      <c r="L8" s="40" t="n">
+      <c r="L8" s="41" t="n">
         <v>0.95</v>
       </c>
-      <c r="M8" s="39" t="n">
+      <c r="M8" s="40" t="n">
         <v>0.77</v>
       </c>
-      <c r="N8" s="38" t="n">
+      <c r="N8" s="39" t="n">
         <v>1</v>
       </c>
       <c r="O8" s="42" t="n">
         <v>0.87</v>
       </c>
-      <c r="P8" s="20">
+      <c r="P8" s="21">
         <f>IFERROR(AVERAGE(C8:O8),"")</f>
         <v/>
       </c>
-      <c r="Q8" s="18" t="inlineStr"/>
-      <c r="R8" s="18" t="inlineStr"/>
+      <c r="Q8" s="19" t="inlineStr"/>
+      <c r="R8" s="19" t="inlineStr"/>
     </row>
     <row r="9" ht="13" customHeight="1">
-      <c r="A9" s="18" t="inlineStr"/>
-      <c r="B9" s="19" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr"/>
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>Quality</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr"/>
-      <c r="D9" s="18" t="inlineStr"/>
-      <c r="E9" s="18" t="inlineStr"/>
-      <c r="F9" s="18" t="inlineStr"/>
-      <c r="G9" s="18" t="inlineStr"/>
-      <c r="H9" s="18" t="inlineStr"/>
-      <c r="I9" s="18" t="inlineStr"/>
-      <c r="J9" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="P9" s="20">
+      <c r="C9" s="19" t="inlineStr"/>
+      <c r="D9" s="19" t="inlineStr"/>
+      <c r="E9" s="19" t="inlineStr"/>
+      <c r="F9" s="19" t="inlineStr"/>
+      <c r="G9" s="19" t="inlineStr"/>
+      <c r="H9" s="19" t="inlineStr"/>
+      <c r="I9" s="19" t="inlineStr"/>
+      <c r="J9" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" s="21">
         <f>IFERROR(AVERAGE(C9:O9),"")</f>
         <v/>
       </c>
-      <c r="Q9" s="18" t="inlineStr"/>
-      <c r="R9" s="18" t="inlineStr"/>
+      <c r="Q9" s="19" t="inlineStr"/>
+      <c r="R9" s="19" t="inlineStr"/>
     </row>
     <row r="10" ht="13" customHeight="1">
-      <c r="A10" s="18" t="inlineStr"/>
-      <c r="B10" s="19" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr"/>
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>Cleanliness</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr"/>
-      <c r="D10" s="18" t="inlineStr"/>
-      <c r="E10" s="18" t="inlineStr"/>
-      <c r="F10" s="18" t="inlineStr"/>
-      <c r="G10" s="18" t="inlineStr"/>
-      <c r="H10" s="18" t="inlineStr"/>
-      <c r="I10" s="18" t="inlineStr"/>
-      <c r="J10" s="40" t="n">
+      <c r="C10" s="19" t="inlineStr"/>
+      <c r="D10" s="19" t="inlineStr"/>
+      <c r="E10" s="19" t="inlineStr"/>
+      <c r="F10" s="19" t="inlineStr"/>
+      <c r="G10" s="19" t="inlineStr"/>
+      <c r="H10" s="19" t="inlineStr"/>
+      <c r="I10" s="19" t="inlineStr"/>
+      <c r="J10" s="41" t="n">
         <v>0.97</v>
       </c>
-      <c r="K10" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" s="38" t="n">
+      <c r="K10" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" s="39" t="n">
         <v>1</v>
       </c>
       <c r="M10" s="42" t="n">
         <v>0.8</v>
       </c>
-      <c r="N10" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="P10" s="20">
+      <c r="N10" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" s="21">
         <f>IFERROR(AVERAGE(C10:O10),"")</f>
         <v/>
       </c>
-      <c r="Q10" s="18" t="inlineStr"/>
-      <c r="R10" s="18" t="inlineStr"/>
+      <c r="Q10" s="19" t="inlineStr"/>
+      <c r="R10" s="19" t="inlineStr"/>
     </row>
     <row r="11" ht="13" customHeight="1">
-      <c r="A11" s="18" t="inlineStr"/>
-      <c r="B11" s="19" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr"/>
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>Customer Sat</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr"/>
-      <c r="D11" s="18" t="inlineStr"/>
-      <c r="E11" s="18" t="inlineStr"/>
-      <c r="F11" s="18" t="inlineStr"/>
-      <c r="G11" s="18" t="inlineStr"/>
-      <c r="H11" s="18" t="inlineStr"/>
-      <c r="I11" s="18" t="inlineStr"/>
-      <c r="J11" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" s="40" t="n">
+      <c r="C11" s="19" t="inlineStr"/>
+      <c r="D11" s="19" t="inlineStr"/>
+      <c r="E11" s="19" t="inlineStr"/>
+      <c r="F11" s="19" t="inlineStr"/>
+      <c r="G11" s="19" t="inlineStr"/>
+      <c r="H11" s="19" t="inlineStr"/>
+      <c r="I11" s="19" t="inlineStr"/>
+      <c r="J11" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="41" t="n">
         <v>0.9</v>
       </c>
-      <c r="N11" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="P11" s="20">
+      <c r="N11" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="P11" s="21">
         <f>IFERROR(AVERAGE(C11:O11),"")</f>
         <v/>
       </c>
-      <c r="Q11" s="18" t="inlineStr"/>
-      <c r="R11" s="18" t="inlineStr"/>
+      <c r="Q11" s="19" t="inlineStr"/>
+      <c r="R11" s="19" t="inlineStr"/>
     </row>
     <row r="12" ht="6" customHeight="1">
-      <c r="A12" s="21" t="n"/>
+      <c r="A12" s="22" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="22" t="inlineStr">
+      <c r="A13" s="23" t="inlineStr">
         <is>
           <t>MANAGERS</t>
         </is>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="B14" s="24" t="inlineStr">
+      <c r="A14" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" s="25" t="inlineStr">
         <is>
           <t>Madison C.</t>
         </is>
       </c>
-      <c r="C14" s="25" t="n"/>
-      <c r="D14" s="25" t="n"/>
-      <c r="E14" s="25" t="n"/>
-      <c r="F14" s="25" t="n"/>
-      <c r="G14" s="25" t="n"/>
-      <c r="H14" s="25" t="n"/>
-      <c r="I14" s="25" t="n"/>
-      <c r="J14" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K14" s="25" t="n"/>
-      <c r="L14" s="25" t="n"/>
-      <c r="M14" s="25" t="n"/>
-      <c r="N14" s="25" t="n"/>
-      <c r="O14" s="25" t="n"/>
-      <c r="P14" s="17">
+      <c r="C14" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D14" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E14" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F14" s="27" t="n"/>
+      <c r="G14" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H14" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I14" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J14" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K14" s="27" t="n"/>
+      <c r="L14" s="27" t="n"/>
+      <c r="M14" s="27" t="n"/>
+      <c r="N14" s="27" t="n"/>
+      <c r="O14" s="27" t="n"/>
+      <c r="P14" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$O$7,C14:O14,"Y"),"")</f>
         <v/>
       </c>
-      <c r="Q14" s="26">
+      <c r="Q14" s="28">
         <f>COUNTIF(C14:O14,"Y")</f>
         <v/>
       </c>
-      <c r="R14" s="27">
+      <c r="R14" s="29">
         <f>SUMPRODUCT((C$7:$O$7=1)*(C14:O14="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="23" t="n">
+      <c r="A15" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="B15" s="24" t="inlineStr">
+      <c r="B15" s="25" t="inlineStr">
         <is>
           <t>Vicki L.</t>
         </is>
       </c>
-      <c r="C15" s="25" t="n"/>
-      <c r="D15" s="25" t="n"/>
-      <c r="E15" s="25" t="n"/>
-      <c r="F15" s="25" t="n"/>
-      <c r="G15" s="25" t="n"/>
-      <c r="H15" s="25" t="n"/>
-      <c r="I15" s="25" t="n"/>
-      <c r="J15" s="25" t="n"/>
-      <c r="K15" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L15" s="25" t="n"/>
-      <c r="M15" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N15" s="25" t="n"/>
-      <c r="O15" s="25" t="n"/>
-      <c r="P15" s="17">
+      <c r="C15" s="27" t="n"/>
+      <c r="D15" s="27" t="n"/>
+      <c r="E15" s="27" t="n"/>
+      <c r="F15" s="27" t="n"/>
+      <c r="G15" s="27" t="n"/>
+      <c r="H15" s="27" t="n"/>
+      <c r="I15" s="27" t="n"/>
+      <c r="J15" s="27" t="n"/>
+      <c r="K15" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L15" s="27" t="n"/>
+      <c r="M15" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N15" s="27" t="n"/>
+      <c r="O15" s="27" t="n"/>
+      <c r="P15" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$O$7,C15:O15,"Y"),"")</f>
         <v/>
       </c>
-      <c r="Q15" s="26">
+      <c r="Q15" s="28">
         <f>COUNTIF(C15:O15,"Y")</f>
         <v/>
       </c>
-      <c r="R15" s="27">
+      <c r="R15" s="29">
         <f>SUMPRODUCT((C$7:$O$7=1)*(C15:O15="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
-      <c r="A16" s="23" t="n">
+      <c r="A16" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="B16" s="24" t="inlineStr">
+      <c r="B16" s="25" t="inlineStr">
         <is>
           <t>Kasey W.</t>
         </is>
       </c>
-      <c r="C16" s="25" t="n"/>
-      <c r="D16" s="25" t="n"/>
-      <c r="E16" s="25" t="n"/>
-      <c r="F16" s="25" t="n"/>
-      <c r="G16" s="25" t="n"/>
-      <c r="H16" s="25" t="n"/>
-      <c r="I16" s="25" t="n"/>
-      <c r="J16" s="25" t="n"/>
-      <c r="K16" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L16" s="25" t="n"/>
-      <c r="M16" s="25" t="n"/>
-      <c r="N16" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O16" s="25" t="n"/>
-      <c r="P16" s="17">
+      <c r="C16" s="27" t="n"/>
+      <c r="D16" s="27" t="n"/>
+      <c r="E16" s="27" t="n"/>
+      <c r="F16" s="27" t="n"/>
+      <c r="G16" s="27" t="n"/>
+      <c r="H16" s="27" t="n"/>
+      <c r="I16" s="27" t="n"/>
+      <c r="J16" s="27" t="n"/>
+      <c r="K16" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L16" s="27" t="n"/>
+      <c r="M16" s="27" t="n"/>
+      <c r="N16" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O16" s="27" t="n"/>
+      <c r="P16" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$O$7,C16:O16,"Y"),"")</f>
         <v/>
       </c>
-      <c r="Q16" s="26">
+      <c r="Q16" s="28">
         <f>COUNTIF(C16:O16,"Y")</f>
         <v/>
       </c>
-      <c r="R16" s="27">
+      <c r="R16" s="29">
         <f>SUMPRODUCT((C$7:$O$7=1)*(C16:O16="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
-      <c r="A17" s="23" t="n">
+      <c r="A17" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="B17" s="24" t="inlineStr">
+      <c r="B17" s="25" t="inlineStr">
         <is>
           <t>Nathan R.</t>
         </is>
       </c>
-      <c r="C17" s="25" t="n"/>
-      <c r="D17" s="25" t="n"/>
-      <c r="E17" s="25" t="n"/>
-      <c r="F17" s="25" t="n"/>
-      <c r="G17" s="25" t="n"/>
-      <c r="H17" s="25" t="n"/>
-      <c r="I17" s="25" t="n"/>
-      <c r="J17" s="25" t="n"/>
-      <c r="K17" s="25" t="n"/>
-      <c r="L17" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M17" s="25" t="n"/>
-      <c r="N17" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O17" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="P17" s="17">
+      <c r="C17" s="27" t="n"/>
+      <c r="D17" s="27" t="n"/>
+      <c r="E17" s="27" t="n"/>
+      <c r="F17" s="27" t="n"/>
+      <c r="G17" s="27" t="n"/>
+      <c r="H17" s="27" t="n"/>
+      <c r="I17" s="27" t="n"/>
+      <c r="J17" s="27" t="n"/>
+      <c r="K17" s="27" t="n"/>
+      <c r="L17" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M17" s="27" t="n"/>
+      <c r="N17" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O17" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P17" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$O$7,C17:O17,"Y"),"")</f>
         <v/>
       </c>
-      <c r="Q17" s="26">
+      <c r="Q17" s="28">
         <f>COUNTIF(C17:O17,"Y")</f>
         <v/>
       </c>
-      <c r="R17" s="27">
+      <c r="R17" s="29">
         <f>SUMPRODUCT((C$7:$O$7=1)*(C17:O17="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="6" customHeight="1">
-      <c r="A18" s="21" t="n"/>
+      <c r="A18" s="22" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="28" t="inlineStr">
+      <c r="A19" s="30" t="inlineStr">
         <is>
           <t>CREW</t>
         </is>
       </c>
     </row>
     <row r="20" ht="17" customHeight="1">
-      <c r="A20" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="B20" s="30" t="inlineStr">
+      <c r="A20" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" s="32" t="inlineStr">
         <is>
           <t>Alen</t>
         </is>
       </c>
-      <c r="C20" s="31" t="n"/>
-      <c r="D20" s="31" t="n"/>
-      <c r="E20" s="31" t="n"/>
-      <c r="F20" s="31" t="n"/>
-      <c r="G20" s="31" t="n"/>
-      <c r="H20" s="31" t="n"/>
-      <c r="I20" s="31" t="n"/>
-      <c r="J20" s="31" t="n"/>
-      <c r="K20" s="31" t="n"/>
-      <c r="L20" s="31" t="n"/>
-      <c r="M20" s="31" t="n"/>
-      <c r="N20" s="31" t="n"/>
-      <c r="O20" s="31" t="n"/>
-      <c r="P20" s="17">
+      <c r="C20" s="33" t="n"/>
+      <c r="D20" s="33" t="n"/>
+      <c r="E20" s="33" t="n"/>
+      <c r="F20" s="33" t="n"/>
+      <c r="G20" s="33" t="n"/>
+      <c r="H20" s="33" t="n"/>
+      <c r="I20" s="33" t="n"/>
+      <c r="J20" s="33" t="n"/>
+      <c r="K20" s="33" t="n"/>
+      <c r="L20" s="33" t="n"/>
+      <c r="M20" s="33" t="n"/>
+      <c r="N20" s="33" t="n"/>
+      <c r="O20" s="33" t="n"/>
+      <c r="P20" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$O$7,C20:O20,"Y"),"")</f>
         <v/>
       </c>
-      <c r="Q20" s="26">
+      <c r="Q20" s="28">
         <f>COUNTIF(C20:O20,"Y")</f>
         <v/>
       </c>
-      <c r="R20" s="27">
+      <c r="R20" s="29">
         <f>SUMPRODUCT((C$7:$O$7=1)*(C20:O20="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="17" customHeight="1">
-      <c r="A21" s="32" t="n">
+      <c r="A21" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="B21" s="33" t="inlineStr">
+      <c r="B21" s="35" t="inlineStr">
         <is>
           <t>Ash</t>
         </is>
       </c>
-      <c r="C21" s="18" t="n"/>
-      <c r="D21" s="18" t="n"/>
-      <c r="E21" s="18" t="n"/>
-      <c r="F21" s="18" t="n"/>
-      <c r="G21" s="18" t="n"/>
-      <c r="H21" s="18" t="n"/>
-      <c r="I21" s="18" t="n"/>
-      <c r="J21" s="18" t="n"/>
-      <c r="K21" s="18" t="n"/>
-      <c r="L21" s="18" t="n"/>
-      <c r="M21" s="18" t="n"/>
-      <c r="N21" s="18" t="n"/>
-      <c r="O21" s="18" t="n"/>
-      <c r="P21" s="17">
+      <c r="C21" s="19" t="n"/>
+      <c r="D21" s="19" t="n"/>
+      <c r="E21" s="19" t="n"/>
+      <c r="F21" s="19" t="n"/>
+      <c r="G21" s="19" t="n"/>
+      <c r="H21" s="19" t="n"/>
+      <c r="I21" s="19" t="n"/>
+      <c r="J21" s="19" t="n"/>
+      <c r="K21" s="19" t="n"/>
+      <c r="L21" s="19" t="n"/>
+      <c r="M21" s="19" t="n"/>
+      <c r="N21" s="19" t="n"/>
+      <c r="O21" s="19" t="n"/>
+      <c r="P21" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$O$7,C21:O21,"Y"),"")</f>
         <v/>
       </c>
-      <c r="Q21" s="26">
+      <c r="Q21" s="28">
         <f>COUNTIF(C21:O21,"Y")</f>
         <v/>
       </c>
-      <c r="R21" s="27">
+      <c r="R21" s="29">
         <f>SUMPRODUCT((C$7:$O$7=1)*(C21:O21="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="17" customHeight="1">
-      <c r="A22" s="29" t="n">
+      <c r="A22" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="B22" s="30" t="inlineStr">
+      <c r="B22" s="32" t="inlineStr">
         <is>
           <t>Autumn</t>
         </is>
       </c>
-      <c r="C22" s="31" t="n"/>
-      <c r="D22" s="31" t="n"/>
-      <c r="E22" s="31" t="n"/>
-      <c r="F22" s="31" t="n"/>
-      <c r="G22" s="31" t="n"/>
-      <c r="H22" s="31" t="n"/>
-      <c r="I22" s="31" t="n"/>
-      <c r="J22" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K22" s="31" t="n"/>
-      <c r="L22" s="31" t="n"/>
-      <c r="M22" s="31" t="n"/>
-      <c r="N22" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O22" s="31" t="n"/>
-      <c r="P22" s="17">
+      <c r="C22" s="33" t="n"/>
+      <c r="D22" s="33" t="n"/>
+      <c r="E22" s="33" t="n"/>
+      <c r="F22" s="33" t="n"/>
+      <c r="G22" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H22" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I22" s="33" t="n"/>
+      <c r="J22" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K22" s="33" t="n"/>
+      <c r="L22" s="33" t="n"/>
+      <c r="M22" s="33" t="n"/>
+      <c r="N22" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O22" s="33" t="n"/>
+      <c r="P22" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$O$7,C22:O22,"Y"),"")</f>
         <v/>
       </c>
-      <c r="Q22" s="26">
+      <c r="Q22" s="28">
         <f>COUNTIF(C22:O22,"Y")</f>
         <v/>
       </c>
-      <c r="R22" s="27">
+      <c r="R22" s="29">
         <f>SUMPRODUCT((C$7:$O$7=1)*(C22:O22="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="17" customHeight="1">
-      <c r="A23" s="32" t="n">
+      <c r="A23" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="B23" s="33" t="inlineStr">
+      <c r="B23" s="35" t="inlineStr">
         <is>
           <t>Bri</t>
         </is>
       </c>
-      <c r="C23" s="18" t="n"/>
-      <c r="D23" s="18" t="n"/>
-      <c r="E23" s="18" t="n"/>
-      <c r="F23" s="18" t="n"/>
-      <c r="G23" s="18" t="n"/>
-      <c r="H23" s="18" t="n"/>
-      <c r="I23" s="18" t="n"/>
-      <c r="J23" s="18" t="n"/>
-      <c r="K23" s="18" t="n"/>
-      <c r="L23" s="18" t="n"/>
-      <c r="M23" s="18" t="n"/>
-      <c r="N23" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O23" s="18" t="n"/>
-      <c r="P23" s="17">
+      <c r="C23" s="19" t="n"/>
+      <c r="D23" s="19" t="n"/>
+      <c r="E23" s="19" t="n"/>
+      <c r="F23" s="19" t="n"/>
+      <c r="G23" s="19" t="n"/>
+      <c r="H23" s="19" t="n"/>
+      <c r="I23" s="19" t="n"/>
+      <c r="J23" s="19" t="n"/>
+      <c r="K23" s="19" t="n"/>
+      <c r="L23" s="19" t="n"/>
+      <c r="M23" s="19" t="n"/>
+      <c r="N23" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O23" s="19" t="n"/>
+      <c r="P23" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$O$7,C23:O23,"Y"),"")</f>
         <v/>
       </c>
-      <c r="Q23" s="26">
+      <c r="Q23" s="28">
         <f>COUNTIF(C23:O23,"Y")</f>
         <v/>
       </c>
-      <c r="R23" s="27">
+      <c r="R23" s="29">
         <f>SUMPRODUCT((C$7:$O$7=1)*(C23:O23="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="17" customHeight="1">
-      <c r="A24" s="29" t="n">
+      <c r="A24" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="B24" s="30" t="inlineStr">
+      <c r="B24" s="32" t="inlineStr">
         <is>
           <t>Dakayla</t>
         </is>
       </c>
-      <c r="C24" s="31" t="n"/>
-      <c r="D24" s="31" t="n"/>
-      <c r="E24" s="31" t="n"/>
-      <c r="F24" s="31" t="n"/>
-      <c r="G24" s="31" t="n"/>
-      <c r="H24" s="31" t="n"/>
-      <c r="I24" s="31" t="n"/>
-      <c r="J24" s="31" t="n"/>
-      <c r="K24" s="31" t="n"/>
-      <c r="L24" s="31" t="n"/>
-      <c r="M24" s="31" t="n"/>
-      <c r="N24" s="31" t="n"/>
-      <c r="O24" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="P24" s="17">
+      <c r="C24" s="33" t="n"/>
+      <c r="D24" s="33" t="n"/>
+      <c r="E24" s="33" t="n"/>
+      <c r="F24" s="33" t="n"/>
+      <c r="G24" s="33" t="n"/>
+      <c r="H24" s="33" t="n"/>
+      <c r="I24" s="33" t="n"/>
+      <c r="J24" s="33" t="n"/>
+      <c r="K24" s="33" t="n"/>
+      <c r="L24" s="33" t="n"/>
+      <c r="M24" s="33" t="n"/>
+      <c r="N24" s="33" t="n"/>
+      <c r="O24" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P24" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$O$7,C24:O24,"Y"),"")</f>
         <v/>
       </c>
-      <c r="Q24" s="26">
+      <c r="Q24" s="28">
         <f>COUNTIF(C24:O24,"Y")</f>
         <v/>
       </c>
-      <c r="R24" s="27">
+      <c r="R24" s="29">
         <f>SUMPRODUCT((C$7:$O$7=1)*(C24:O24="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="17" customHeight="1">
-      <c r="A25" s="32" t="n">
+      <c r="A25" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="B25" s="33" t="inlineStr">
+      <c r="B25" s="35" t="inlineStr">
         <is>
           <t>Divan</t>
         </is>
       </c>
-      <c r="C25" s="18" t="n"/>
-      <c r="D25" s="18" t="n"/>
-      <c r="E25" s="18" t="n"/>
-      <c r="F25" s="18" t="n"/>
-      <c r="G25" s="18" t="n"/>
-      <c r="H25" s="18" t="n"/>
-      <c r="I25" s="18" t="n"/>
-      <c r="J25" s="18" t="n"/>
-      <c r="K25" s="18" t="n"/>
-      <c r="L25" s="18" t="n"/>
-      <c r="M25" s="18" t="n"/>
-      <c r="N25" s="18" t="n"/>
-      <c r="O25" s="18" t="n"/>
-      <c r="P25" s="17">
+      <c r="C25" s="19" t="n"/>
+      <c r="D25" s="19" t="n"/>
+      <c r="E25" s="19" t="n"/>
+      <c r="F25" s="19" t="n"/>
+      <c r="G25" s="19" t="n"/>
+      <c r="H25" s="19" t="n"/>
+      <c r="I25" s="19" t="n"/>
+      <c r="J25" s="19" t="n"/>
+      <c r="K25" s="19" t="n"/>
+      <c r="L25" s="19" t="n"/>
+      <c r="M25" s="19" t="n"/>
+      <c r="N25" s="19" t="n"/>
+      <c r="O25" s="19" t="n"/>
+      <c r="P25" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$O$7,C25:O25,"Y"),"")</f>
         <v/>
       </c>
-      <c r="Q25" s="26">
+      <c r="Q25" s="28">
         <f>COUNTIF(C25:O25,"Y")</f>
         <v/>
       </c>
-      <c r="R25" s="27">
+      <c r="R25" s="29">
         <f>SUMPRODUCT((C$7:$O$7=1)*(C25:O25="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="17" customHeight="1">
-      <c r="A26" s="29" t="n">
+      <c r="A26" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="B26" s="30" t="inlineStr">
+      <c r="B26" s="32" t="inlineStr">
         <is>
           <t>Francisco</t>
         </is>
       </c>
-      <c r="C26" s="31" t="n"/>
-      <c r="D26" s="31" t="n"/>
-      <c r="E26" s="31" t="n"/>
-      <c r="F26" s="31" t="n"/>
-      <c r="G26" s="31" t="n"/>
-      <c r="H26" s="31" t="n"/>
-      <c r="I26" s="31" t="n"/>
-      <c r="J26" s="31" t="n"/>
-      <c r="K26" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L26" s="31" t="n"/>
-      <c r="M26" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N26" s="31" t="n"/>
-      <c r="O26" s="31" t="n"/>
-      <c r="P26" s="17">
+      <c r="C26" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D26" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E26" s="33" t="n"/>
+      <c r="F26" s="33" t="n"/>
+      <c r="G26" s="33" t="n"/>
+      <c r="H26" s="33" t="n"/>
+      <c r="I26" s="33" t="n"/>
+      <c r="J26" s="33" t="n"/>
+      <c r="K26" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L26" s="33" t="n"/>
+      <c r="M26" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N26" s="33" t="n"/>
+      <c r="O26" s="33" t="n"/>
+      <c r="P26" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$O$7,C26:O26,"Y"),"")</f>
         <v/>
       </c>
-      <c r="Q26" s="26">
+      <c r="Q26" s="28">
         <f>COUNTIF(C26:O26,"Y")</f>
         <v/>
       </c>
-      <c r="R26" s="27">
+      <c r="R26" s="29">
         <f>SUMPRODUCT((C$7:$O$7=1)*(C26:O26="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="17" customHeight="1">
-      <c r="A27" s="32" t="n">
+      <c r="A27" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="B27" s="33" t="inlineStr">
+      <c r="B27" s="35" t="inlineStr">
         <is>
           <t>Grace</t>
         </is>
       </c>
-      <c r="C27" s="18" t="n"/>
-      <c r="D27" s="18" t="n"/>
-      <c r="E27" s="18" t="n"/>
-      <c r="F27" s="18" t="n"/>
-      <c r="G27" s="18" t="n"/>
-      <c r="H27" s="18" t="n"/>
-      <c r="I27" s="18" t="n"/>
-      <c r="J27" s="18" t="n"/>
-      <c r="K27" s="18" t="n"/>
-      <c r="L27" s="18" t="n"/>
-      <c r="M27" s="18" t="n"/>
-      <c r="N27" s="18" t="n"/>
-      <c r="O27" s="18" t="n"/>
-      <c r="P27" s="17">
+      <c r="C27" s="19" t="n"/>
+      <c r="D27" s="19" t="n"/>
+      <c r="E27" s="19" t="n"/>
+      <c r="F27" s="19" t="n"/>
+      <c r="G27" s="19" t="n"/>
+      <c r="H27" s="19" t="n"/>
+      <c r="I27" s="19" t="n"/>
+      <c r="J27" s="19" t="n"/>
+      <c r="K27" s="19" t="n"/>
+      <c r="L27" s="19" t="n"/>
+      <c r="M27" s="19" t="n"/>
+      <c r="N27" s="19" t="n"/>
+      <c r="O27" s="19" t="n"/>
+      <c r="P27" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$O$7,C27:O27,"Y"),"")</f>
         <v/>
       </c>
-      <c r="Q27" s="26">
+      <c r="Q27" s="28">
         <f>COUNTIF(C27:O27,"Y")</f>
         <v/>
       </c>
-      <c r="R27" s="27">
+      <c r="R27" s="29">
         <f>SUMPRODUCT((C$7:$O$7=1)*(C27:O27="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="17" customHeight="1">
-      <c r="A28" s="29" t="n">
+      <c r="A28" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="B28" s="30" t="inlineStr">
+      <c r="B28" s="32" t="inlineStr">
         <is>
           <t>Jada</t>
         </is>
       </c>
-      <c r="C28" s="31" t="n"/>
-      <c r="D28" s="31" t="n"/>
-      <c r="E28" s="31" t="n"/>
-      <c r="F28" s="31" t="n"/>
-      <c r="G28" s="31" t="n"/>
-      <c r="H28" s="31" t="n"/>
-      <c r="I28" s="31" t="n"/>
-      <c r="J28" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K28" s="31" t="n"/>
-      <c r="L28" s="31" t="n"/>
-      <c r="M28" s="31" t="n"/>
-      <c r="N28" s="31" t="n"/>
-      <c r="O28" s="31" t="n"/>
-      <c r="P28" s="17">
+      <c r="C28" s="33" t="n"/>
+      <c r="D28" s="33" t="n"/>
+      <c r="E28" s="33" t="n"/>
+      <c r="F28" s="33" t="n"/>
+      <c r="G28" s="33" t="n"/>
+      <c r="H28" s="33" t="n"/>
+      <c r="I28" s="33" t="n"/>
+      <c r="J28" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K28" s="33" t="n"/>
+      <c r="L28" s="33" t="n"/>
+      <c r="M28" s="33" t="n"/>
+      <c r="N28" s="33" t="n"/>
+      <c r="O28" s="33" t="n"/>
+      <c r="P28" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$O$7,C28:O28,"Y"),"")</f>
         <v/>
       </c>
-      <c r="Q28" s="26">
+      <c r="Q28" s="28">
         <f>COUNTIF(C28:O28,"Y")</f>
         <v/>
       </c>
-      <c r="R28" s="27">
+      <c r="R28" s="29">
         <f>SUMPRODUCT((C$7:$O$7=1)*(C28:O28="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="17" customHeight="1">
-      <c r="A29" s="32" t="n">
+      <c r="A29" s="34" t="n">
         <v>10</v>
       </c>
-      <c r="B29" s="33" t="inlineStr">
+      <c r="B29" s="35" t="inlineStr">
         <is>
           <t>Jeremiah</t>
         </is>
       </c>
-      <c r="C29" s="18" t="n"/>
-      <c r="D29" s="18" t="n"/>
-      <c r="E29" s="18" t="n"/>
-      <c r="F29" s="18" t="n"/>
-      <c r="G29" s="18" t="n"/>
-      <c r="H29" s="18" t="n"/>
-      <c r="I29" s="18" t="n"/>
-      <c r="J29" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K29" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L29" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M29" s="18" t="n"/>
-      <c r="N29" s="18" t="n"/>
-      <c r="O29" s="18" t="n"/>
-      <c r="P29" s="17">
+      <c r="C29" s="19" t="n"/>
+      <c r="D29" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E29" s="19" t="n"/>
+      <c r="F29" s="19" t="n"/>
+      <c r="G29" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H29" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I29" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J29" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K29" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L29" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M29" s="19" t="n"/>
+      <c r="N29" s="19" t="n"/>
+      <c r="O29" s="19" t="n"/>
+      <c r="P29" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$O$7,C29:O29,"Y"),"")</f>
         <v/>
       </c>
-      <c r="Q29" s="26">
+      <c r="Q29" s="28">
         <f>COUNTIF(C29:O29,"Y")</f>
         <v/>
       </c>
-      <c r="R29" s="27">
+      <c r="R29" s="29">
         <f>SUMPRODUCT((C$7:$O$7=1)*(C29:O29="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="17" customHeight="1">
-      <c r="A30" s="29" t="n">
+      <c r="A30" s="31" t="n">
         <v>11</v>
       </c>
-      <c r="B30" s="30" t="inlineStr">
+      <c r="B30" s="32" t="inlineStr">
         <is>
           <t>Kable</t>
         </is>
       </c>
-      <c r="C30" s="31" t="n"/>
-      <c r="D30" s="31" t="n"/>
-      <c r="E30" s="31" t="n"/>
-      <c r="F30" s="31" t="n"/>
-      <c r="G30" s="31" t="n"/>
-      <c r="H30" s="31" t="n"/>
-      <c r="I30" s="31" t="n"/>
-      <c r="J30" s="31" t="n"/>
-      <c r="K30" s="31" t="n"/>
-      <c r="L30" s="31" t="n"/>
-      <c r="M30" s="31" t="n"/>
-      <c r="N30" s="31" t="n"/>
-      <c r="O30" s="31" t="n"/>
-      <c r="P30" s="17">
+      <c r="C30" s="33" t="n"/>
+      <c r="D30" s="33" t="n"/>
+      <c r="E30" s="33" t="n"/>
+      <c r="F30" s="33" t="n"/>
+      <c r="G30" s="33" t="n"/>
+      <c r="H30" s="33" t="n"/>
+      <c r="I30" s="33" t="n"/>
+      <c r="J30" s="33" t="n"/>
+      <c r="K30" s="33" t="n"/>
+      <c r="L30" s="33" t="n"/>
+      <c r="M30" s="33" t="n"/>
+      <c r="N30" s="33" t="n"/>
+      <c r="O30" s="33" t="n"/>
+      <c r="P30" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$O$7,C30:O30,"Y"),"")</f>
         <v/>
       </c>
-      <c r="Q30" s="26">
+      <c r="Q30" s="28">
         <f>COUNTIF(C30:O30,"Y")</f>
         <v/>
       </c>
-      <c r="R30" s="27">
+      <c r="R30" s="29">
         <f>SUMPRODUCT((C$7:$O$7=1)*(C30:O30="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="17" customHeight="1">
-      <c r="A31" s="32" t="n">
+      <c r="A31" s="34" t="n">
         <v>12</v>
       </c>
-      <c r="B31" s="33" t="inlineStr">
+      <c r="B31" s="35" t="inlineStr">
         <is>
           <t>Kayla</t>
         </is>
       </c>
-      <c r="C31" s="18" t="n"/>
-      <c r="D31" s="18" t="n"/>
-      <c r="E31" s="18" t="n"/>
-      <c r="F31" s="18" t="n"/>
-      <c r="G31" s="18" t="n"/>
-      <c r="H31" s="18" t="n"/>
-      <c r="I31" s="18" t="n"/>
-      <c r="J31" s="18" t="n"/>
-      <c r="K31" s="18" t="n"/>
-      <c r="L31" s="18" t="n"/>
-      <c r="M31" s="18" t="n"/>
-      <c r="N31" s="18" t="n"/>
-      <c r="O31" s="18" t="n"/>
-      <c r="P31" s="17">
+      <c r="C31" s="19" t="n"/>
+      <c r="D31" s="19" t="n"/>
+      <c r="E31" s="19" t="n"/>
+      <c r="F31" s="19" t="n"/>
+      <c r="G31" s="19" t="n"/>
+      <c r="H31" s="19" t="n"/>
+      <c r="I31" s="19" t="n"/>
+      <c r="J31" s="19" t="n"/>
+      <c r="K31" s="19" t="n"/>
+      <c r="L31" s="19" t="n"/>
+      <c r="M31" s="19" t="n"/>
+      <c r="N31" s="19" t="n"/>
+      <c r="O31" s="19" t="n"/>
+      <c r="P31" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$O$7,C31:O31,"Y"),"")</f>
         <v/>
       </c>
-      <c r="Q31" s="26">
+      <c r="Q31" s="28">
         <f>COUNTIF(C31:O31,"Y")</f>
         <v/>
       </c>
-      <c r="R31" s="27">
+      <c r="R31" s="29">
         <f>SUMPRODUCT((C$7:$O$7=1)*(C31:O31="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="17" customHeight="1">
-      <c r="A32" s="29" t="n">
+      <c r="A32" s="31" t="n">
         <v>13</v>
       </c>
-      <c r="B32" s="30" t="inlineStr">
+      <c r="B32" s="32" t="inlineStr">
         <is>
           <t>Kenzie</t>
         </is>
       </c>
-      <c r="C32" s="31" t="n"/>
-      <c r="D32" s="31" t="n"/>
-      <c r="E32" s="31" t="n"/>
-      <c r="F32" s="31" t="n"/>
-      <c r="G32" s="31" t="n"/>
-      <c r="H32" s="31" t="n"/>
-      <c r="I32" s="31" t="n"/>
-      <c r="J32" s="31" t="n"/>
-      <c r="K32" s="31" t="n"/>
-      <c r="L32" s="31" t="n"/>
-      <c r="M32" s="31" t="n"/>
-      <c r="N32" s="31" t="n"/>
-      <c r="O32" s="31" t="n"/>
-      <c r="P32" s="17">
+      <c r="C32" s="33" t="n"/>
+      <c r="D32" s="33" t="n"/>
+      <c r="E32" s="33" t="n"/>
+      <c r="F32" s="33" t="n"/>
+      <c r="G32" s="33" t="n"/>
+      <c r="H32" s="33" t="n"/>
+      <c r="I32" s="33" t="n"/>
+      <c r="J32" s="33" t="n"/>
+      <c r="K32" s="33" t="n"/>
+      <c r="L32" s="33" t="n"/>
+      <c r="M32" s="33" t="n"/>
+      <c r="N32" s="33" t="n"/>
+      <c r="O32" s="33" t="n"/>
+      <c r="P32" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$O$7,C32:O32,"Y"),"")</f>
         <v/>
       </c>
-      <c r="Q32" s="26">
+      <c r="Q32" s="28">
         <f>COUNTIF(C32:O32,"Y")</f>
         <v/>
       </c>
-      <c r="R32" s="27">
+      <c r="R32" s="29">
         <f>SUMPRODUCT((C$7:$O$7=1)*(C32:O32="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="17" customHeight="1">
-      <c r="A33" s="32" t="n">
+      <c r="A33" s="34" t="n">
         <v>14</v>
       </c>
-      <c r="B33" s="33" t="inlineStr">
+      <c r="B33" s="35" t="inlineStr">
         <is>
           <t>Lidy</t>
         </is>
       </c>
-      <c r="C33" s="18" t="n"/>
-      <c r="D33" s="18" t="n"/>
-      <c r="E33" s="18" t="n"/>
-      <c r="F33" s="18" t="n"/>
-      <c r="G33" s="18" t="n"/>
-      <c r="H33" s="18" t="n"/>
-      <c r="I33" s="18" t="n"/>
-      <c r="J33" s="18" t="n"/>
-      <c r="K33" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L33" s="18" t="n"/>
-      <c r="M33" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N33" s="18" t="n"/>
-      <c r="O33" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="P33" s="17">
+      <c r="C33" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D33" s="19" t="n"/>
+      <c r="E33" s="19" t="n"/>
+      <c r="F33" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G33" s="19" t="n"/>
+      <c r="H33" s="19" t="n"/>
+      <c r="I33" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J33" s="19" t="n"/>
+      <c r="K33" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L33" s="19" t="n"/>
+      <c r="M33" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N33" s="19" t="n"/>
+      <c r="O33" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P33" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$O$7,C33:O33,"Y"),"")</f>
         <v/>
       </c>
-      <c r="Q33" s="26">
+      <c r="Q33" s="28">
         <f>COUNTIF(C33:O33,"Y")</f>
         <v/>
       </c>
-      <c r="R33" s="27">
+      <c r="R33" s="29">
         <f>SUMPRODUCT((C$7:$O$7=1)*(C33:O33="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="17" customHeight="1">
-      <c r="A34" s="29" t="n">
+      <c r="A34" s="31" t="n">
         <v>15</v>
       </c>
-      <c r="B34" s="30" t="inlineStr">
+      <c r="B34" s="32" t="inlineStr">
         <is>
           <t>Maylin</t>
         </is>
       </c>
-      <c r="C34" s="31" t="n"/>
-      <c r="D34" s="31" t="n"/>
-      <c r="E34" s="31" t="n"/>
-      <c r="F34" s="31" t="n"/>
-      <c r="G34" s="31" t="n"/>
-      <c r="H34" s="31" t="n"/>
-      <c r="I34" s="31" t="n"/>
-      <c r="J34" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K34" s="31" t="n"/>
-      <c r="L34" s="31" t="n"/>
-      <c r="M34" s="31" t="n"/>
-      <c r="N34" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O34" s="31" t="n"/>
-      <c r="P34" s="17">
+      <c r="C34" s="33" t="n"/>
+      <c r="D34" s="33" t="n"/>
+      <c r="E34" s="33" t="n"/>
+      <c r="F34" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G34" s="33" t="n"/>
+      <c r="H34" s="33" t="n"/>
+      <c r="I34" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J34" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K34" s="33" t="n"/>
+      <c r="L34" s="33" t="n"/>
+      <c r="M34" s="33" t="n"/>
+      <c r="N34" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O34" s="33" t="n"/>
+      <c r="P34" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$O$7,C34:O34,"Y"),"")</f>
         <v/>
       </c>
-      <c r="Q34" s="26">
+      <c r="Q34" s="28">
         <f>COUNTIF(C34:O34,"Y")</f>
         <v/>
       </c>
-      <c r="R34" s="27">
+      <c r="R34" s="29">
         <f>SUMPRODUCT((C$7:$O$7=1)*(C34:O34="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="17" customHeight="1">
-      <c r="A35" s="32" t="n">
+      <c r="A35" s="34" t="n">
         <v>16</v>
       </c>
-      <c r="B35" s="33" t="inlineStr">
+      <c r="B35" s="35" t="inlineStr">
         <is>
           <t>Mike</t>
         </is>
       </c>
-      <c r="C35" s="18" t="n"/>
-      <c r="D35" s="18" t="n"/>
-      <c r="E35" s="18" t="n"/>
-      <c r="F35" s="18" t="n"/>
-      <c r="G35" s="18" t="n"/>
-      <c r="H35" s="18" t="n"/>
-      <c r="I35" s="18" t="n"/>
-      <c r="J35" s="18" t="n"/>
-      <c r="K35" s="18" t="n"/>
-      <c r="L35" s="18" t="n"/>
-      <c r="M35" s="18" t="n"/>
-      <c r="N35" s="18" t="n"/>
-      <c r="O35" s="18" t="n"/>
-      <c r="P35" s="17">
+      <c r="C35" s="19" t="n"/>
+      <c r="D35" s="19" t="n"/>
+      <c r="E35" s="19" t="n"/>
+      <c r="F35" s="19" t="n"/>
+      <c r="G35" s="19" t="n"/>
+      <c r="H35" s="19" t="n"/>
+      <c r="I35" s="19" t="n"/>
+      <c r="J35" s="19" t="n"/>
+      <c r="K35" s="19" t="n"/>
+      <c r="L35" s="19" t="n"/>
+      <c r="M35" s="19" t="n"/>
+      <c r="N35" s="19" t="n"/>
+      <c r="O35" s="19" t="n"/>
+      <c r="P35" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$O$7,C35:O35,"Y"),"")</f>
         <v/>
       </c>
-      <c r="Q35" s="26">
+      <c r="Q35" s="28">
         <f>COUNTIF(C35:O35,"Y")</f>
         <v/>
       </c>
-      <c r="R35" s="27">
+      <c r="R35" s="29">
         <f>SUMPRODUCT((C$7:$O$7=1)*(C35:O35="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="17" customHeight="1">
-      <c r="A36" s="29" t="n">
+      <c r="A36" s="31" t="n">
         <v>17</v>
       </c>
-      <c r="B36" s="30" t="inlineStr">
+      <c r="B36" s="32" t="inlineStr">
         <is>
           <t>Richard</t>
         </is>
       </c>
-      <c r="C36" s="31" t="n"/>
-      <c r="D36" s="31" t="n"/>
-      <c r="E36" s="31" t="n"/>
-      <c r="F36" s="31" t="n"/>
-      <c r="G36" s="31" t="n"/>
-      <c r="H36" s="31" t="n"/>
-      <c r="I36" s="31" t="n"/>
-      <c r="J36" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K36" s="31" t="n"/>
-      <c r="L36" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M36" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N36" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O36" s="31" t="n"/>
-      <c r="P36" s="17">
+      <c r="C36" s="33" t="n"/>
+      <c r="D36" s="33" t="n"/>
+      <c r="E36" s="33" t="n"/>
+      <c r="F36" s="33" t="n"/>
+      <c r="G36" s="33" t="n"/>
+      <c r="H36" s="33" t="n"/>
+      <c r="I36" s="33" t="n"/>
+      <c r="J36" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K36" s="33" t="n"/>
+      <c r="L36" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M36" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N36" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O36" s="33" t="n"/>
+      <c r="P36" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$O$7,C36:O36,"Y"),"")</f>
         <v/>
       </c>
-      <c r="Q36" s="26">
+      <c r="Q36" s="28">
         <f>COUNTIF(C36:O36,"Y")</f>
         <v/>
       </c>
-      <c r="R36" s="27">
+      <c r="R36" s="29">
         <f>SUMPRODUCT((C$7:$O$7=1)*(C36:O36="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="17" customHeight="1">
-      <c r="A37" s="32" t="n">
+      <c r="A37" s="34" t="n">
         <v>18</v>
       </c>
-      <c r="B37" s="33" t="inlineStr">
+      <c r="B37" s="35" t="inlineStr">
         <is>
           <t>Samuel</t>
         </is>
       </c>
-      <c r="C37" s="18" t="n"/>
-      <c r="D37" s="18" t="n"/>
-      <c r="E37" s="18" t="n"/>
-      <c r="F37" s="18" t="n"/>
-      <c r="G37" s="18" t="n"/>
-      <c r="H37" s="18" t="n"/>
-      <c r="I37" s="18" t="n"/>
-      <c r="J37" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K37" s="18" t="n"/>
-      <c r="L37" s="18" t="n"/>
-      <c r="M37" s="18" t="n"/>
-      <c r="N37" s="18" t="n"/>
-      <c r="O37" s="18" t="n"/>
-      <c r="P37" s="17">
+      <c r="C37" s="19" t="n"/>
+      <c r="D37" s="19" t="n"/>
+      <c r="E37" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F37" s="19" t="n"/>
+      <c r="G37" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H37" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I37" s="19" t="n"/>
+      <c r="J37" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K37" s="19" t="n"/>
+      <c r="L37" s="19" t="n"/>
+      <c r="M37" s="19" t="n"/>
+      <c r="N37" s="19" t="n"/>
+      <c r="O37" s="19" t="n"/>
+      <c r="P37" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$O$7,C37:O37,"Y"),"")</f>
         <v/>
       </c>
-      <c r="Q37" s="26">
+      <c r="Q37" s="28">
         <f>COUNTIF(C37:O37,"Y")</f>
         <v/>
       </c>
-      <c r="R37" s="27">
+      <c r="R37" s="29">
         <f>SUMPRODUCT((C$7:$O$7=1)*(C37:O37="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="17" customHeight="1">
-      <c r="A38" s="29" t="n">
+      <c r="A38" s="31" t="n">
         <v>19</v>
       </c>
-      <c r="B38" s="30" t="inlineStr">
+      <c r="B38" s="32" t="inlineStr">
         <is>
           <t>Zach</t>
         </is>
       </c>
-      <c r="C38" s="31" t="n"/>
-      <c r="D38" s="31" t="n"/>
-      <c r="E38" s="31" t="n"/>
-      <c r="F38" s="31" t="n"/>
-      <c r="G38" s="31" t="n"/>
-      <c r="H38" s="31" t="n"/>
-      <c r="I38" s="31" t="n"/>
-      <c r="J38" s="31" t="n"/>
-      <c r="K38" s="31" t="n"/>
-      <c r="L38" s="31" t="n"/>
-      <c r="M38" s="31" t="n"/>
-      <c r="N38" s="31" t="n"/>
-      <c r="O38" s="31" t="n"/>
-      <c r="P38" s="17">
+      <c r="C38" s="33" t="n"/>
+      <c r="D38" s="33" t="n"/>
+      <c r="E38" s="33" t="n"/>
+      <c r="F38" s="33" t="n"/>
+      <c r="G38" s="33" t="n"/>
+      <c r="H38" s="33" t="n"/>
+      <c r="I38" s="33" t="n"/>
+      <c r="J38" s="33" t="n"/>
+      <c r="K38" s="33" t="n"/>
+      <c r="L38" s="33" t="n"/>
+      <c r="M38" s="33" t="n"/>
+      <c r="N38" s="33" t="n"/>
+      <c r="O38" s="33" t="n"/>
+      <c r="P38" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$O$7,C38:O38,"Y"),"")</f>
         <v/>
       </c>
-      <c r="Q38" s="26">
+      <c r="Q38" s="28">
         <f>COUNTIF(C38:O38,"Y")</f>
         <v/>
       </c>
-      <c r="R38" s="27">
+      <c r="R38" s="29">
         <f>SUMPRODUCT((C$7:$O$7=1)*(C38:O38="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="3" t="inlineStr"/>
-      <c r="B39" s="34" t="inlineStr">
+      <c r="B39" s="36" t="inlineStr">
         <is>
           <t>Total on shift</t>
         </is>
@@ -6516,13 +7404,13 @@
         <f>SUM(Q14:Q38)</f>
         <v/>
       </c>
-      <c r="R39" s="35">
+      <c r="R39" s="37">
         <f>SUM(R14:R38)</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="12" customHeight="1">
-      <c r="A40" s="36" t="inlineStr">
+      <c r="A40" s="38" t="inlineStr">
         <is>
           <t>Y = on shift during shop's meal window. Personal Avg = average score of shops worked. Bonus = $50 per 100% shop worked.</t>
         </is>
@@ -6786,10 +7674,10 @@
       <c r="G7" s="16" t="n">
         <v>0.77</v>
       </c>
-      <c r="H7" s="37" t="n">
+      <c r="H7" s="17" t="n">
         <v>0.92</v>
       </c>
-      <c r="I7" s="37" t="n">
+      <c r="I7" s="17" t="n">
         <v>0.95</v>
       </c>
       <c r="J7" s="15" t="n">
@@ -6798,7 +7686,7 @@
       <c r="K7" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="L7" s="17">
+      <c r="L7" s="18">
         <f>IFERROR(AVERAGE(C7:K7),"")</f>
         <v/>
       </c>
@@ -6806,849 +7694,937 @@
       <c r="N7" s="12" t="inlineStr"/>
     </row>
     <row r="8" ht="13" customHeight="1">
-      <c r="A8" s="18" t="inlineStr"/>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr"/>
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr"/>
-      <c r="D8" s="18" t="inlineStr"/>
-      <c r="E8" s="18" t="inlineStr"/>
-      <c r="F8" s="18" t="inlineStr"/>
-      <c r="G8" s="18" t="inlineStr"/>
-      <c r="H8" s="18" t="inlineStr"/>
-      <c r="I8" s="18" t="inlineStr"/>
-      <c r="J8" s="18" t="inlineStr"/>
-      <c r="K8" s="18" t="inlineStr"/>
-      <c r="L8" s="20">
+      <c r="C8" s="19" t="inlineStr"/>
+      <c r="D8" s="19" t="inlineStr"/>
+      <c r="E8" s="19" t="inlineStr"/>
+      <c r="F8" s="19" t="inlineStr"/>
+      <c r="G8" s="19" t="inlineStr"/>
+      <c r="H8" s="19" t="inlineStr"/>
+      <c r="I8" s="19" t="inlineStr"/>
+      <c r="J8" s="19" t="inlineStr"/>
+      <c r="K8" s="19" t="inlineStr"/>
+      <c r="L8" s="21">
         <f>IFERROR(AVERAGE(C8:K8),"")</f>
         <v/>
       </c>
-      <c r="M8" s="18" t="inlineStr"/>
-      <c r="N8" s="18" t="inlineStr"/>
+      <c r="M8" s="19" t="inlineStr"/>
+      <c r="N8" s="19" t="inlineStr"/>
     </row>
     <row r="9" ht="13" customHeight="1">
-      <c r="A9" s="18" t="inlineStr"/>
-      <c r="B9" s="19" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr"/>
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>Quality</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr"/>
-      <c r="D9" s="18" t="inlineStr"/>
-      <c r="E9" s="18" t="inlineStr"/>
-      <c r="F9" s="18" t="inlineStr"/>
-      <c r="G9" s="18" t="inlineStr"/>
-      <c r="H9" s="18" t="inlineStr"/>
-      <c r="I9" s="18" t="inlineStr"/>
-      <c r="J9" s="18" t="inlineStr"/>
-      <c r="K9" s="18" t="inlineStr"/>
-      <c r="L9" s="20">
+      <c r="C9" s="19" t="inlineStr"/>
+      <c r="D9" s="19" t="inlineStr"/>
+      <c r="E9" s="19" t="inlineStr"/>
+      <c r="F9" s="19" t="inlineStr"/>
+      <c r="G9" s="19" t="inlineStr"/>
+      <c r="H9" s="19" t="inlineStr"/>
+      <c r="I9" s="19" t="inlineStr"/>
+      <c r="J9" s="19" t="inlineStr"/>
+      <c r="K9" s="19" t="inlineStr"/>
+      <c r="L9" s="21">
         <f>IFERROR(AVERAGE(C9:K9),"")</f>
         <v/>
       </c>
-      <c r="M9" s="18" t="inlineStr"/>
-      <c r="N9" s="18" t="inlineStr"/>
+      <c r="M9" s="19" t="inlineStr"/>
+      <c r="N9" s="19" t="inlineStr"/>
     </row>
     <row r="10" ht="13" customHeight="1">
-      <c r="A10" s="18" t="inlineStr"/>
-      <c r="B10" s="19" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr"/>
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>Cleanliness</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr"/>
-      <c r="D10" s="18" t="inlineStr"/>
-      <c r="E10" s="18" t="inlineStr"/>
-      <c r="F10" s="18" t="inlineStr"/>
-      <c r="G10" s="18" t="inlineStr"/>
-      <c r="H10" s="18" t="inlineStr"/>
-      <c r="I10" s="18" t="inlineStr"/>
-      <c r="J10" s="18" t="inlineStr"/>
-      <c r="K10" s="18" t="inlineStr"/>
-      <c r="L10" s="20">
+      <c r="C10" s="19" t="inlineStr"/>
+      <c r="D10" s="19" t="inlineStr"/>
+      <c r="E10" s="19" t="inlineStr"/>
+      <c r="F10" s="19" t="inlineStr"/>
+      <c r="G10" s="19" t="inlineStr"/>
+      <c r="H10" s="19" t="inlineStr"/>
+      <c r="I10" s="19" t="inlineStr"/>
+      <c r="J10" s="19" t="inlineStr"/>
+      <c r="K10" s="19" t="inlineStr"/>
+      <c r="L10" s="21">
         <f>IFERROR(AVERAGE(C10:K10),"")</f>
         <v/>
       </c>
-      <c r="M10" s="18" t="inlineStr"/>
-      <c r="N10" s="18" t="inlineStr"/>
+      <c r="M10" s="19" t="inlineStr"/>
+      <c r="N10" s="19" t="inlineStr"/>
     </row>
     <row r="11" ht="13" customHeight="1">
-      <c r="A11" s="18" t="inlineStr"/>
-      <c r="B11" s="19" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr"/>
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>Customer Sat</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr"/>
-      <c r="D11" s="18" t="inlineStr"/>
-      <c r="E11" s="18" t="inlineStr"/>
-      <c r="F11" s="18" t="inlineStr"/>
-      <c r="G11" s="18" t="inlineStr"/>
-      <c r="H11" s="18" t="inlineStr"/>
-      <c r="I11" s="18" t="inlineStr"/>
-      <c r="J11" s="18" t="inlineStr"/>
-      <c r="K11" s="18" t="inlineStr"/>
-      <c r="L11" s="20">
+      <c r="C11" s="19" t="inlineStr"/>
+      <c r="D11" s="19" t="inlineStr"/>
+      <c r="E11" s="19" t="inlineStr"/>
+      <c r="F11" s="19" t="inlineStr"/>
+      <c r="G11" s="19" t="inlineStr"/>
+      <c r="H11" s="19" t="inlineStr"/>
+      <c r="I11" s="19" t="inlineStr"/>
+      <c r="J11" s="19" t="inlineStr"/>
+      <c r="K11" s="19" t="inlineStr"/>
+      <c r="L11" s="21">
         <f>IFERROR(AVERAGE(C11:K11),"")</f>
         <v/>
       </c>
-      <c r="M11" s="18" t="inlineStr"/>
-      <c r="N11" s="18" t="inlineStr"/>
+      <c r="M11" s="19" t="inlineStr"/>
+      <c r="N11" s="19" t="inlineStr"/>
     </row>
     <row r="12" ht="6" customHeight="1">
-      <c r="A12" s="21" t="n"/>
+      <c r="A12" s="22" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="22" t="inlineStr">
+      <c r="A13" s="23" t="inlineStr">
         <is>
           <t>MANAGERS</t>
         </is>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="B14" s="24" t="inlineStr">
+      <c r="A14" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" s="25" t="inlineStr">
         <is>
           <t>Madison C.</t>
         </is>
       </c>
-      <c r="C14" s="25" t="n"/>
-      <c r="D14" s="25" t="n"/>
-      <c r="E14" s="25" t="n"/>
-      <c r="F14" s="25" t="n"/>
-      <c r="G14" s="25" t="n"/>
-      <c r="H14" s="25" t="n"/>
-      <c r="I14" s="25" t="n"/>
-      <c r="J14" s="25" t="n"/>
-      <c r="K14" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L14" s="17">
+      <c r="C14" s="27" t="n"/>
+      <c r="D14" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E14" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F14" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G14" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H14" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I14" s="27" t="n"/>
+      <c r="J14" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K14" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L14" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$K$7,C14:K14,"Y"),"")</f>
         <v/>
       </c>
-      <c r="M14" s="26">
+      <c r="M14" s="28">
         <f>COUNTIF(C14:K14,"Y")</f>
         <v/>
       </c>
-      <c r="N14" s="27">
+      <c r="N14" s="29">
         <f>SUMPRODUCT((C$7:$K$7=1)*(C14:K14="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="23" t="n">
+      <c r="A15" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="B15" s="24" t="inlineStr">
+      <c r="B15" s="25" t="inlineStr">
         <is>
           <t>Vicki L.</t>
         </is>
       </c>
-      <c r="C15" s="25" t="n"/>
-      <c r="D15" s="25" t="n"/>
-      <c r="E15" s="25" t="n"/>
-      <c r="F15" s="25" t="n"/>
-      <c r="G15" s="25" t="n"/>
-      <c r="H15" s="25" t="n"/>
-      <c r="I15" s="25" t="n"/>
-      <c r="J15" s="25" t="n"/>
-      <c r="K15" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L15" s="17">
+      <c r="C15" s="27" t="n"/>
+      <c r="D15" s="27" t="n"/>
+      <c r="E15" s="27" t="n"/>
+      <c r="F15" s="27" t="n"/>
+      <c r="G15" s="27" t="n"/>
+      <c r="H15" s="27" t="n"/>
+      <c r="I15" s="27" t="n"/>
+      <c r="J15" s="27" t="n"/>
+      <c r="K15" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L15" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$K$7,C15:K15,"Y"),"")</f>
         <v/>
       </c>
-      <c r="M15" s="26">
+      <c r="M15" s="28">
         <f>COUNTIF(C15:K15,"Y")</f>
         <v/>
       </c>
-      <c r="N15" s="27">
+      <c r="N15" s="29">
         <f>SUMPRODUCT((C$7:$K$7=1)*(C15:K15="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
-      <c r="A16" s="23" t="n">
+      <c r="A16" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="B16" s="24" t="inlineStr">
+      <c r="B16" s="25" t="inlineStr">
         <is>
           <t>Kasey W.</t>
         </is>
       </c>
-      <c r="C16" s="25" t="n"/>
-      <c r="D16" s="25" t="n"/>
-      <c r="E16" s="25" t="n"/>
-      <c r="F16" s="25" t="n"/>
-      <c r="G16" s="25" t="n"/>
-      <c r="H16" s="25" t="n"/>
-      <c r="I16" s="25" t="n"/>
-      <c r="J16" s="25" t="n"/>
-      <c r="K16" s="25" t="n"/>
-      <c r="L16" s="17">
+      <c r="C16" s="27" t="n"/>
+      <c r="D16" s="27" t="n"/>
+      <c r="E16" s="27" t="n"/>
+      <c r="F16" s="27" t="n"/>
+      <c r="G16" s="27" t="n"/>
+      <c r="H16" s="27" t="n"/>
+      <c r="I16" s="27" t="n"/>
+      <c r="J16" s="27" t="n"/>
+      <c r="K16" s="27" t="n"/>
+      <c r="L16" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$K$7,C16:K16,"Y"),"")</f>
         <v/>
       </c>
-      <c r="M16" s="26">
+      <c r="M16" s="28">
         <f>COUNTIF(C16:K16,"Y")</f>
         <v/>
       </c>
-      <c r="N16" s="27">
+      <c r="N16" s="29">
         <f>SUMPRODUCT((C$7:$K$7=1)*(C16:K16="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
-      <c r="A17" s="23" t="n">
+      <c r="A17" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="B17" s="24" t="inlineStr">
+      <c r="B17" s="25" t="inlineStr">
         <is>
           <t>Nathan R.</t>
         </is>
       </c>
-      <c r="C17" s="25" t="n"/>
-      <c r="D17" s="25" t="n"/>
-      <c r="E17" s="25" t="n"/>
-      <c r="F17" s="25" t="n"/>
-      <c r="G17" s="25" t="n"/>
-      <c r="H17" s="25" t="n"/>
-      <c r="I17" s="25" t="n"/>
-      <c r="J17" s="25" t="n"/>
-      <c r="K17" s="25" t="n"/>
-      <c r="L17" s="17">
+      <c r="C17" s="27" t="n"/>
+      <c r="D17" s="27" t="n"/>
+      <c r="E17" s="27" t="n"/>
+      <c r="F17" s="27" t="n"/>
+      <c r="G17" s="27" t="n"/>
+      <c r="H17" s="27" t="n"/>
+      <c r="I17" s="27" t="n"/>
+      <c r="J17" s="27" t="n"/>
+      <c r="K17" s="27" t="n"/>
+      <c r="L17" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$K$7,C17:K17,"Y"),"")</f>
         <v/>
       </c>
-      <c r="M17" s="26">
+      <c r="M17" s="28">
         <f>COUNTIF(C17:K17,"Y")</f>
         <v/>
       </c>
-      <c r="N17" s="27">
+      <c r="N17" s="29">
         <f>SUMPRODUCT((C$7:$K$7=1)*(C17:K17="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="6" customHeight="1">
-      <c r="A18" s="21" t="n"/>
+      <c r="A18" s="22" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="28" t="inlineStr">
+      <c r="A19" s="30" t="inlineStr">
         <is>
           <t>CREW</t>
         </is>
       </c>
     </row>
     <row r="20" ht="17" customHeight="1">
-      <c r="A20" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="B20" s="30" t="inlineStr">
+      <c r="A20" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" s="32" t="inlineStr">
         <is>
           <t>Alen</t>
         </is>
       </c>
-      <c r="C20" s="31" t="n"/>
-      <c r="D20" s="31" t="n"/>
-      <c r="E20" s="31" t="n"/>
-      <c r="F20" s="31" t="n"/>
-      <c r="G20" s="31" t="n"/>
-      <c r="H20" s="31" t="n"/>
-      <c r="I20" s="31" t="n"/>
-      <c r="J20" s="31" t="n"/>
-      <c r="K20" s="31" t="n"/>
-      <c r="L20" s="17">
+      <c r="C20" s="33" t="n"/>
+      <c r="D20" s="33" t="n"/>
+      <c r="E20" s="33" t="n"/>
+      <c r="F20" s="33" t="n"/>
+      <c r="G20" s="33" t="n"/>
+      <c r="H20" s="33" t="n"/>
+      <c r="I20" s="33" t="n"/>
+      <c r="J20" s="33" t="n"/>
+      <c r="K20" s="33" t="n"/>
+      <c r="L20" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$K$7,C20:K20,"Y"),"")</f>
         <v/>
       </c>
-      <c r="M20" s="26">
+      <c r="M20" s="28">
         <f>COUNTIF(C20:K20,"Y")</f>
         <v/>
       </c>
-      <c r="N20" s="27">
+      <c r="N20" s="29">
         <f>SUMPRODUCT((C$7:$K$7=1)*(C20:K20="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="17" customHeight="1">
-      <c r="A21" s="32" t="n">
+      <c r="A21" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="B21" s="33" t="inlineStr">
+      <c r="B21" s="35" t="inlineStr">
         <is>
           <t>Ash</t>
         </is>
       </c>
-      <c r="C21" s="18" t="n"/>
-      <c r="D21" s="18" t="n"/>
-      <c r="E21" s="18" t="n"/>
-      <c r="F21" s="18" t="n"/>
-      <c r="G21" s="18" t="n"/>
-      <c r="H21" s="18" t="n"/>
-      <c r="I21" s="18" t="n"/>
-      <c r="J21" s="18" t="n"/>
-      <c r="K21" s="18" t="n"/>
-      <c r="L21" s="17">
+      <c r="C21" s="19" t="n"/>
+      <c r="D21" s="19" t="n"/>
+      <c r="E21" s="19" t="n"/>
+      <c r="F21" s="19" t="n"/>
+      <c r="G21" s="19" t="n"/>
+      <c r="H21" s="19" t="n"/>
+      <c r="I21" s="19" t="n"/>
+      <c r="J21" s="19" t="n"/>
+      <c r="K21" s="19" t="n"/>
+      <c r="L21" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$K$7,C21:K21,"Y"),"")</f>
         <v/>
       </c>
-      <c r="M21" s="26">
+      <c r="M21" s="28">
         <f>COUNTIF(C21:K21,"Y")</f>
         <v/>
       </c>
-      <c r="N21" s="27">
+      <c r="N21" s="29">
         <f>SUMPRODUCT((C$7:$K$7=1)*(C21:K21="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="17" customHeight="1">
-      <c r="A22" s="29" t="n">
+      <c r="A22" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="B22" s="30" t="inlineStr">
+      <c r="B22" s="32" t="inlineStr">
         <is>
           <t>Autumn</t>
         </is>
       </c>
-      <c r="C22" s="31" t="n"/>
-      <c r="D22" s="31" t="n"/>
-      <c r="E22" s="31" t="n"/>
-      <c r="F22" s="31" t="n"/>
-      <c r="G22" s="31" t="n"/>
-      <c r="H22" s="31" t="n"/>
-      <c r="I22" s="31" t="n"/>
-      <c r="J22" s="31" t="n"/>
-      <c r="K22" s="31" t="n"/>
-      <c r="L22" s="17">
+      <c r="C22" s="33" t="n"/>
+      <c r="D22" s="33" t="n"/>
+      <c r="E22" s="33" t="n"/>
+      <c r="F22" s="33" t="n"/>
+      <c r="G22" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H22" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I22" s="33" t="n"/>
+      <c r="J22" s="33" t="n"/>
+      <c r="K22" s="33" t="n"/>
+      <c r="L22" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$K$7,C22:K22,"Y"),"")</f>
         <v/>
       </c>
-      <c r="M22" s="26">
+      <c r="M22" s="28">
         <f>COUNTIF(C22:K22,"Y")</f>
         <v/>
       </c>
-      <c r="N22" s="27">
+      <c r="N22" s="29">
         <f>SUMPRODUCT((C$7:$K$7=1)*(C22:K22="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="17" customHeight="1">
-      <c r="A23" s="32" t="n">
+      <c r="A23" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="B23" s="33" t="inlineStr">
+      <c r="B23" s="35" t="inlineStr">
         <is>
           <t>Bri</t>
         </is>
       </c>
-      <c r="C23" s="18" t="n"/>
-      <c r="D23" s="18" t="n"/>
-      <c r="E23" s="18" t="n"/>
-      <c r="F23" s="18" t="n"/>
-      <c r="G23" s="18" t="n"/>
-      <c r="H23" s="18" t="n"/>
-      <c r="I23" s="18" t="n"/>
-      <c r="J23" s="18" t="n"/>
-      <c r="K23" s="18" t="n"/>
-      <c r="L23" s="17">
+      <c r="C23" s="19" t="n"/>
+      <c r="D23" s="19" t="n"/>
+      <c r="E23" s="19" t="n"/>
+      <c r="F23" s="19" t="n"/>
+      <c r="G23" s="19" t="n"/>
+      <c r="H23" s="19" t="n"/>
+      <c r="I23" s="19" t="n"/>
+      <c r="J23" s="19" t="n"/>
+      <c r="K23" s="19" t="n"/>
+      <c r="L23" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$K$7,C23:K23,"Y"),"")</f>
         <v/>
       </c>
-      <c r="M23" s="26">
+      <c r="M23" s="28">
         <f>COUNTIF(C23:K23,"Y")</f>
         <v/>
       </c>
-      <c r="N23" s="27">
+      <c r="N23" s="29">
         <f>SUMPRODUCT((C$7:$K$7=1)*(C23:K23="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="17" customHeight="1">
-      <c r="A24" s="29" t="n">
+      <c r="A24" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="B24" s="30" t="inlineStr">
+      <c r="B24" s="32" t="inlineStr">
         <is>
           <t>Dakayla</t>
         </is>
       </c>
-      <c r="C24" s="31" t="n"/>
-      <c r="D24" s="31" t="n"/>
-      <c r="E24" s="31" t="n"/>
-      <c r="F24" s="31" t="n"/>
-      <c r="G24" s="31" t="n"/>
-      <c r="H24" s="31" t="n"/>
-      <c r="I24" s="31" t="n"/>
-      <c r="J24" s="31" t="n"/>
-      <c r="K24" s="31" t="n"/>
-      <c r="L24" s="17">
+      <c r="C24" s="33" t="n"/>
+      <c r="D24" s="33" t="n"/>
+      <c r="E24" s="33" t="n"/>
+      <c r="F24" s="33" t="n"/>
+      <c r="G24" s="33" t="n"/>
+      <c r="H24" s="33" t="n"/>
+      <c r="I24" s="33" t="n"/>
+      <c r="J24" s="33" t="n"/>
+      <c r="K24" s="33" t="n"/>
+      <c r="L24" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$K$7,C24:K24,"Y"),"")</f>
         <v/>
       </c>
-      <c r="M24" s="26">
+      <c r="M24" s="28">
         <f>COUNTIF(C24:K24,"Y")</f>
         <v/>
       </c>
-      <c r="N24" s="27">
+      <c r="N24" s="29">
         <f>SUMPRODUCT((C$7:$K$7=1)*(C24:K24="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="17" customHeight="1">
-      <c r="A25" s="32" t="n">
+      <c r="A25" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="B25" s="33" t="inlineStr">
+      <c r="B25" s="35" t="inlineStr">
         <is>
           <t>Divan</t>
         </is>
       </c>
-      <c r="C25" s="18" t="n"/>
-      <c r="D25" s="18" t="n"/>
-      <c r="E25" s="18" t="n"/>
-      <c r="F25" s="18" t="n"/>
-      <c r="G25" s="18" t="n"/>
-      <c r="H25" s="18" t="n"/>
-      <c r="I25" s="18" t="n"/>
-      <c r="J25" s="18" t="n"/>
-      <c r="K25" s="18" t="n"/>
-      <c r="L25" s="17">
+      <c r="C25" s="19" t="n"/>
+      <c r="D25" s="19" t="n"/>
+      <c r="E25" s="19" t="n"/>
+      <c r="F25" s="19" t="n"/>
+      <c r="G25" s="19" t="n"/>
+      <c r="H25" s="19" t="n"/>
+      <c r="I25" s="19" t="n"/>
+      <c r="J25" s="19" t="n"/>
+      <c r="K25" s="19" t="n"/>
+      <c r="L25" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$K$7,C25:K25,"Y"),"")</f>
         <v/>
       </c>
-      <c r="M25" s="26">
+      <c r="M25" s="28">
         <f>COUNTIF(C25:K25,"Y")</f>
         <v/>
       </c>
-      <c r="N25" s="27">
+      <c r="N25" s="29">
         <f>SUMPRODUCT((C$7:$K$7=1)*(C25:K25="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="17" customHeight="1">
-      <c r="A26" s="29" t="n">
+      <c r="A26" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="B26" s="30" t="inlineStr">
+      <c r="B26" s="32" t="inlineStr">
         <is>
           <t>Francisco</t>
         </is>
       </c>
-      <c r="C26" s="31" t="n"/>
-      <c r="D26" s="31" t="n"/>
-      <c r="E26" s="31" t="n"/>
-      <c r="F26" s="31" t="n"/>
-      <c r="G26" s="31" t="n"/>
-      <c r="H26" s="31" t="n"/>
-      <c r="I26" s="31" t="n"/>
-      <c r="J26" s="31" t="n"/>
-      <c r="K26" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L26" s="17">
+      <c r="C26" s="33" t="n"/>
+      <c r="D26" s="33" t="n"/>
+      <c r="E26" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F26" s="33" t="n"/>
+      <c r="G26" s="33" t="n"/>
+      <c r="H26" s="33" t="n"/>
+      <c r="I26" s="33" t="n"/>
+      <c r="J26" s="33" t="n"/>
+      <c r="K26" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L26" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$K$7,C26:K26,"Y"),"")</f>
         <v/>
       </c>
-      <c r="M26" s="26">
+      <c r="M26" s="28">
         <f>COUNTIF(C26:K26,"Y")</f>
         <v/>
       </c>
-      <c r="N26" s="27">
+      <c r="N26" s="29">
         <f>SUMPRODUCT((C$7:$K$7=1)*(C26:K26="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="17" customHeight="1">
-      <c r="A27" s="32" t="n">
+      <c r="A27" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="B27" s="33" t="inlineStr">
+      <c r="B27" s="35" t="inlineStr">
         <is>
           <t>Grace</t>
         </is>
       </c>
-      <c r="C27" s="18" t="n"/>
-      <c r="D27" s="18" t="n"/>
-      <c r="E27" s="18" t="n"/>
-      <c r="F27" s="18" t="n"/>
-      <c r="G27" s="18" t="n"/>
-      <c r="H27" s="18" t="n"/>
-      <c r="I27" s="18" t="n"/>
-      <c r="J27" s="18" t="n"/>
-      <c r="K27" s="18" t="n"/>
-      <c r="L27" s="17">
+      <c r="C27" s="19" t="n"/>
+      <c r="D27" s="19" t="n"/>
+      <c r="E27" s="19" t="n"/>
+      <c r="F27" s="19" t="n"/>
+      <c r="G27" s="19" t="n"/>
+      <c r="H27" s="19" t="n"/>
+      <c r="I27" s="19" t="n"/>
+      <c r="J27" s="19" t="n"/>
+      <c r="K27" s="19" t="n"/>
+      <c r="L27" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$K$7,C27:K27,"Y"),"")</f>
         <v/>
       </c>
-      <c r="M27" s="26">
+      <c r="M27" s="28">
         <f>COUNTIF(C27:K27,"Y")</f>
         <v/>
       </c>
-      <c r="N27" s="27">
+      <c r="N27" s="29">
         <f>SUMPRODUCT((C$7:$K$7=1)*(C27:K27="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="17" customHeight="1">
-      <c r="A28" s="29" t="n">
+      <c r="A28" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="B28" s="30" t="inlineStr">
+      <c r="B28" s="32" t="inlineStr">
         <is>
           <t>Jada</t>
         </is>
       </c>
-      <c r="C28" s="31" t="n"/>
-      <c r="D28" s="31" t="n"/>
-      <c r="E28" s="31" t="n"/>
-      <c r="F28" s="31" t="n"/>
-      <c r="G28" s="31" t="n"/>
-      <c r="H28" s="31" t="n"/>
-      <c r="I28" s="31" t="n"/>
-      <c r="J28" s="31" t="n"/>
-      <c r="K28" s="31" t="n"/>
-      <c r="L28" s="17">
+      <c r="C28" s="33" t="n"/>
+      <c r="D28" s="33" t="n"/>
+      <c r="E28" s="33" t="n"/>
+      <c r="F28" s="33" t="n"/>
+      <c r="G28" s="33" t="n"/>
+      <c r="H28" s="33" t="n"/>
+      <c r="I28" s="33" t="n"/>
+      <c r="J28" s="33" t="n"/>
+      <c r="K28" s="33" t="n"/>
+      <c r="L28" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$K$7,C28:K28,"Y"),"")</f>
         <v/>
       </c>
-      <c r="M28" s="26">
+      <c r="M28" s="28">
         <f>COUNTIF(C28:K28,"Y")</f>
         <v/>
       </c>
-      <c r="N28" s="27">
+      <c r="N28" s="29">
         <f>SUMPRODUCT((C$7:$K$7=1)*(C28:K28="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="17" customHeight="1">
-      <c r="A29" s="32" t="n">
+      <c r="A29" s="34" t="n">
         <v>10</v>
       </c>
-      <c r="B29" s="33" t="inlineStr">
+      <c r="B29" s="35" t="inlineStr">
         <is>
           <t>Jeremiah</t>
         </is>
       </c>
-      <c r="C29" s="18" t="n"/>
-      <c r="D29" s="18" t="n"/>
-      <c r="E29" s="18" t="n"/>
-      <c r="F29" s="18" t="n"/>
-      <c r="G29" s="18" t="n"/>
-      <c r="H29" s="18" t="n"/>
-      <c r="I29" s="18" t="n"/>
-      <c r="J29" s="18" t="n"/>
-      <c r="K29" s="18" t="n"/>
-      <c r="L29" s="17">
+      <c r="C29" s="19" t="n"/>
+      <c r="D29" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E29" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F29" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G29" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H29" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I29" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J29" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K29" s="19" t="n"/>
+      <c r="L29" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$K$7,C29:K29,"Y"),"")</f>
         <v/>
       </c>
-      <c r="M29" s="26">
+      <c r="M29" s="28">
         <f>COUNTIF(C29:K29,"Y")</f>
         <v/>
       </c>
-      <c r="N29" s="27">
+      <c r="N29" s="29">
         <f>SUMPRODUCT((C$7:$K$7=1)*(C29:K29="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="17" customHeight="1">
-      <c r="A30" s="29" t="n">
+      <c r="A30" s="31" t="n">
         <v>11</v>
       </c>
-      <c r="B30" s="30" t="inlineStr">
+      <c r="B30" s="32" t="inlineStr">
         <is>
           <t>Kable</t>
         </is>
       </c>
-      <c r="C30" s="31" t="n"/>
-      <c r="D30" s="31" t="n"/>
-      <c r="E30" s="31" t="n"/>
-      <c r="F30" s="31" t="n"/>
-      <c r="G30" s="31" t="n"/>
-      <c r="H30" s="31" t="n"/>
-      <c r="I30" s="31" t="n"/>
-      <c r="J30" s="31" t="n"/>
-      <c r="K30" s="31" t="n"/>
-      <c r="L30" s="17">
+      <c r="C30" s="33" t="n"/>
+      <c r="D30" s="33" t="n"/>
+      <c r="E30" s="33" t="n"/>
+      <c r="F30" s="33" t="n"/>
+      <c r="G30" s="33" t="n"/>
+      <c r="H30" s="33" t="n"/>
+      <c r="I30" s="33" t="n"/>
+      <c r="J30" s="33" t="n"/>
+      <c r="K30" s="33" t="n"/>
+      <c r="L30" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$K$7,C30:K30,"Y"),"")</f>
         <v/>
       </c>
-      <c r="M30" s="26">
+      <c r="M30" s="28">
         <f>COUNTIF(C30:K30,"Y")</f>
         <v/>
       </c>
-      <c r="N30" s="27">
+      <c r="N30" s="29">
         <f>SUMPRODUCT((C$7:$K$7=1)*(C30:K30="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="17" customHeight="1">
-      <c r="A31" s="32" t="n">
+      <c r="A31" s="34" t="n">
         <v>12</v>
       </c>
-      <c r="B31" s="33" t="inlineStr">
+      <c r="B31" s="35" t="inlineStr">
         <is>
           <t>Kayla</t>
         </is>
       </c>
-      <c r="C31" s="18" t="n"/>
-      <c r="D31" s="18" t="n"/>
-      <c r="E31" s="18" t="n"/>
-      <c r="F31" s="18" t="n"/>
-      <c r="G31" s="18" t="n"/>
-      <c r="H31" s="18" t="n"/>
-      <c r="I31" s="18" t="n"/>
-      <c r="J31" s="18" t="n"/>
-      <c r="K31" s="18" t="n"/>
-      <c r="L31" s="17">
+      <c r="C31" s="19" t="n"/>
+      <c r="D31" s="19" t="n"/>
+      <c r="E31" s="19" t="n"/>
+      <c r="F31" s="19" t="n"/>
+      <c r="G31" s="19" t="n"/>
+      <c r="H31" s="19" t="n"/>
+      <c r="I31" s="19" t="n"/>
+      <c r="J31" s="19" t="n"/>
+      <c r="K31" s="19" t="n"/>
+      <c r="L31" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$K$7,C31:K31,"Y"),"")</f>
         <v/>
       </c>
-      <c r="M31" s="26">
+      <c r="M31" s="28">
         <f>COUNTIF(C31:K31,"Y")</f>
         <v/>
       </c>
-      <c r="N31" s="27">
+      <c r="N31" s="29">
         <f>SUMPRODUCT((C$7:$K$7=1)*(C31:K31="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="17" customHeight="1">
-      <c r="A32" s="29" t="n">
+      <c r="A32" s="31" t="n">
         <v>13</v>
       </c>
-      <c r="B32" s="30" t="inlineStr">
+      <c r="B32" s="32" t="inlineStr">
         <is>
           <t>Kenzie</t>
         </is>
       </c>
-      <c r="C32" s="31" t="n"/>
-      <c r="D32" s="31" t="n"/>
-      <c r="E32" s="31" t="n"/>
-      <c r="F32" s="31" t="n"/>
-      <c r="G32" s="31" t="n"/>
-      <c r="H32" s="31" t="n"/>
-      <c r="I32" s="31" t="n"/>
-      <c r="J32" s="31" t="n"/>
-      <c r="K32" s="31" t="n"/>
-      <c r="L32" s="17">
+      <c r="C32" s="33" t="n"/>
+      <c r="D32" s="33" t="n"/>
+      <c r="E32" s="33" t="n"/>
+      <c r="F32" s="33" t="n"/>
+      <c r="G32" s="33" t="n"/>
+      <c r="H32" s="33" t="n"/>
+      <c r="I32" s="33" t="n"/>
+      <c r="J32" s="33" t="n"/>
+      <c r="K32" s="33" t="n"/>
+      <c r="L32" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$K$7,C32:K32,"Y"),"")</f>
         <v/>
       </c>
-      <c r="M32" s="26">
+      <c r="M32" s="28">
         <f>COUNTIF(C32:K32,"Y")</f>
         <v/>
       </c>
-      <c r="N32" s="27">
+      <c r="N32" s="29">
         <f>SUMPRODUCT((C$7:$K$7=1)*(C32:K32="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="17" customHeight="1">
-      <c r="A33" s="32" t="n">
+      <c r="A33" s="34" t="n">
         <v>14</v>
       </c>
-      <c r="B33" s="33" t="inlineStr">
+      <c r="B33" s="35" t="inlineStr">
         <is>
           <t>Lidy</t>
         </is>
       </c>
-      <c r="C33" s="18" t="n"/>
-      <c r="D33" s="18" t="n"/>
-      <c r="E33" s="18" t="n"/>
-      <c r="F33" s="18" t="n"/>
-      <c r="G33" s="18" t="n"/>
-      <c r="H33" s="18" t="n"/>
-      <c r="I33" s="18" t="n"/>
-      <c r="J33" s="18" t="n"/>
-      <c r="K33" s="41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L33" s="17">
+      <c r="C33" s="19" t="n"/>
+      <c r="D33" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E33" s="19" t="n"/>
+      <c r="F33" s="19" t="n"/>
+      <c r="G33" s="19" t="n"/>
+      <c r="H33" s="19" t="n"/>
+      <c r="I33" s="19" t="n"/>
+      <c r="J33" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K33" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L33" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$K$7,C33:K33,"Y"),"")</f>
         <v/>
       </c>
-      <c r="M33" s="26">
+      <c r="M33" s="28">
         <f>COUNTIF(C33:K33,"Y")</f>
         <v/>
       </c>
-      <c r="N33" s="27">
+      <c r="N33" s="29">
         <f>SUMPRODUCT((C$7:$K$7=1)*(C33:K33="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="17" customHeight="1">
-      <c r="A34" s="29" t="n">
+      <c r="A34" s="31" t="n">
         <v>15</v>
       </c>
-      <c r="B34" s="30" t="inlineStr">
+      <c r="B34" s="32" t="inlineStr">
         <is>
           <t>Maylin</t>
         </is>
       </c>
-      <c r="C34" s="31" t="n"/>
-      <c r="D34" s="31" t="n"/>
-      <c r="E34" s="31" t="n"/>
-      <c r="F34" s="31" t="n"/>
-      <c r="G34" s="31" t="n"/>
-      <c r="H34" s="31" t="n"/>
-      <c r="I34" s="31" t="n"/>
-      <c r="J34" s="31" t="n"/>
-      <c r="K34" s="31" t="n"/>
-      <c r="L34" s="17">
+      <c r="C34" s="33" t="n"/>
+      <c r="D34" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E34" s="33" t="n"/>
+      <c r="F34" s="33" t="n"/>
+      <c r="G34" s="33" t="n"/>
+      <c r="H34" s="33" t="n"/>
+      <c r="I34" s="33" t="n"/>
+      <c r="J34" s="33" t="n"/>
+      <c r="K34" s="33" t="n"/>
+      <c r="L34" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$K$7,C34:K34,"Y"),"")</f>
         <v/>
       </c>
-      <c r="M34" s="26">
+      <c r="M34" s="28">
         <f>COUNTIF(C34:K34,"Y")</f>
         <v/>
       </c>
-      <c r="N34" s="27">
+      <c r="N34" s="29">
         <f>SUMPRODUCT((C$7:$K$7=1)*(C34:K34="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="17" customHeight="1">
-      <c r="A35" s="32" t="n">
+      <c r="A35" s="34" t="n">
         <v>16</v>
       </c>
-      <c r="B35" s="33" t="inlineStr">
+      <c r="B35" s="35" t="inlineStr">
         <is>
           <t>Mike</t>
         </is>
       </c>
-      <c r="C35" s="18" t="n"/>
-      <c r="D35" s="18" t="n"/>
-      <c r="E35" s="18" t="n"/>
-      <c r="F35" s="18" t="n"/>
-      <c r="G35" s="18" t="n"/>
-      <c r="H35" s="18" t="n"/>
-      <c r="I35" s="18" t="n"/>
-      <c r="J35" s="18" t="n"/>
-      <c r="K35" s="18" t="n"/>
-      <c r="L35" s="17">
+      <c r="C35" s="19" t="n"/>
+      <c r="D35" s="19" t="n"/>
+      <c r="E35" s="19" t="n"/>
+      <c r="F35" s="19" t="n"/>
+      <c r="G35" s="19" t="n"/>
+      <c r="H35" s="19" t="n"/>
+      <c r="I35" s="19" t="n"/>
+      <c r="J35" s="19" t="n"/>
+      <c r="K35" s="19" t="n"/>
+      <c r="L35" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$K$7,C35:K35,"Y"),"")</f>
         <v/>
       </c>
-      <c r="M35" s="26">
+      <c r="M35" s="28">
         <f>COUNTIF(C35:K35,"Y")</f>
         <v/>
       </c>
-      <c r="N35" s="27">
+      <c r="N35" s="29">
         <f>SUMPRODUCT((C$7:$K$7=1)*(C35:K35="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="17" customHeight="1">
-      <c r="A36" s="29" t="n">
+      <c r="A36" s="31" t="n">
         <v>17</v>
       </c>
-      <c r="B36" s="30" t="inlineStr">
+      <c r="B36" s="32" t="inlineStr">
         <is>
           <t>Richard</t>
         </is>
       </c>
-      <c r="C36" s="31" t="n"/>
-      <c r="D36" s="31" t="n"/>
-      <c r="E36" s="31" t="n"/>
-      <c r="F36" s="31" t="n"/>
-      <c r="G36" s="31" t="n"/>
-      <c r="H36" s="31" t="n"/>
-      <c r="I36" s="31" t="n"/>
-      <c r="J36" s="31" t="n"/>
-      <c r="K36" s="31" t="n"/>
-      <c r="L36" s="17">
+      <c r="C36" s="33" t="n"/>
+      <c r="D36" s="33" t="n"/>
+      <c r="E36" s="33" t="n"/>
+      <c r="F36" s="33" t="n"/>
+      <c r="G36" s="33" t="n"/>
+      <c r="H36" s="33" t="n"/>
+      <c r="I36" s="33" t="n"/>
+      <c r="J36" s="33" t="n"/>
+      <c r="K36" s="33" t="n"/>
+      <c r="L36" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$K$7,C36:K36,"Y"),"")</f>
         <v/>
       </c>
-      <c r="M36" s="26">
+      <c r="M36" s="28">
         <f>COUNTIF(C36:K36,"Y")</f>
         <v/>
       </c>
-      <c r="N36" s="27">
+      <c r="N36" s="29">
         <f>SUMPRODUCT((C$7:$K$7=1)*(C36:K36="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="17" customHeight="1">
-      <c r="A37" s="32" t="n">
+      <c r="A37" s="34" t="n">
         <v>18</v>
       </c>
-      <c r="B37" s="33" t="inlineStr">
+      <c r="B37" s="35" t="inlineStr">
         <is>
           <t>Samuel</t>
         </is>
       </c>
-      <c r="C37" s="18" t="n"/>
-      <c r="D37" s="18" t="n"/>
-      <c r="E37" s="18" t="n"/>
-      <c r="F37" s="18" t="n"/>
-      <c r="G37" s="18" t="n"/>
-      <c r="H37" s="18" t="n"/>
-      <c r="I37" s="18" t="n"/>
-      <c r="J37" s="18" t="n"/>
-      <c r="K37" s="18" t="n"/>
-      <c r="L37" s="17">
+      <c r="C37" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D37" s="19" t="n"/>
+      <c r="E37" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F37" s="19" t="n"/>
+      <c r="G37" s="19" t="n"/>
+      <c r="H37" s="19" t="n"/>
+      <c r="I37" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J37" s="19" t="n"/>
+      <c r="K37" s="19" t="n"/>
+      <c r="L37" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$K$7,C37:K37,"Y"),"")</f>
         <v/>
       </c>
-      <c r="M37" s="26">
+      <c r="M37" s="28">
         <f>COUNTIF(C37:K37,"Y")</f>
         <v/>
       </c>
-      <c r="N37" s="27">
+      <c r="N37" s="29">
         <f>SUMPRODUCT((C$7:$K$7=1)*(C37:K37="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="17" customHeight="1">
-      <c r="A38" s="29" t="n">
+      <c r="A38" s="31" t="n">
         <v>19</v>
       </c>
-      <c r="B38" s="30" t="inlineStr">
+      <c r="B38" s="32" t="inlineStr">
         <is>
           <t>Zach</t>
         </is>
       </c>
-      <c r="C38" s="31" t="n"/>
-      <c r="D38" s="31" t="n"/>
-      <c r="E38" s="31" t="n"/>
-      <c r="F38" s="31" t="n"/>
-      <c r="G38" s="31" t="n"/>
-      <c r="H38" s="31" t="n"/>
-      <c r="I38" s="31" t="n"/>
-      <c r="J38" s="31" t="n"/>
-      <c r="K38" s="31" t="n"/>
-      <c r="L38" s="17">
+      <c r="C38" s="33" t="n"/>
+      <c r="D38" s="33" t="n"/>
+      <c r="E38" s="33" t="n"/>
+      <c r="F38" s="33" t="n"/>
+      <c r="G38" s="33" t="n"/>
+      <c r="H38" s="33" t="n"/>
+      <c r="I38" s="33" t="n"/>
+      <c r="J38" s="33" t="n"/>
+      <c r="K38" s="33" t="n"/>
+      <c r="L38" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$K$7,C38:K38,"Y"),"")</f>
         <v/>
       </c>
-      <c r="M38" s="26">
+      <c r="M38" s="28">
         <f>COUNTIF(C38:K38,"Y")</f>
         <v/>
       </c>
-      <c r="N38" s="27">
+      <c r="N38" s="29">
         <f>SUMPRODUCT((C$7:$K$7=1)*(C38:K38="Y"))*50</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="3" t="inlineStr"/>
-      <c r="B39" s="34" t="inlineStr">
+      <c r="B39" s="36" t="inlineStr">
         <is>
           <t>Total on shift</t>
         </is>
@@ -7694,13 +8670,13 @@
         <f>SUM(M14:M38)</f>
         <v/>
       </c>
-      <c r="N39" s="35">
+      <c r="N39" s="37">
         <f>SUM(N14:N38)</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="12" customHeight="1">
-      <c r="A40" s="36" t="inlineStr">
+      <c r="A40" s="38" t="inlineStr">
         <is>
           <t>Y = on shift during shop's meal window. Personal Avg = average score of shops worked. Bonus = $50 per 100% shop worked.</t>
         </is>

--- a/Shop_Tracker_2065_2026.xlsx
+++ b/Shop_Tracker_2065_2026.xlsx
@@ -7438,7 +7438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N40"/>
+  <dimension ref="A1:O40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -7452,9 +7452,10 @@
     <col width="7" customWidth="1" min="9" max="9"/>
     <col width="7" customWidth="1" min="10" max="10"/>
     <col width="7" customWidth="1" min="11" max="11"/>
-    <col width="9" customWidth="1" min="12" max="12"/>
-    <col width="7" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="7" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="7" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -7467,7 +7468,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Five Guys Store 2065 · Louisville, KY · 9 shops · Source: Marketforce + CrunchTime</t>
+          <t>Five Guys Store 2065 · Louisville, KY · 10 shops · Source: Marketforce + CrunchTime</t>
         </is>
       </c>
     </row>
@@ -7524,17 +7525,22 @@
           <t>#9</t>
         </is>
       </c>
-      <c r="L4" s="6" t="inlineStr">
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
         <is>
           <t>AVG</t>
         </is>
       </c>
-      <c r="M4" s="6" t="inlineStr">
+      <c r="N4" s="6" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="N4" s="6" t="inlineStr">
+      <c r="O4" s="6" t="inlineStr">
         <is>
           <t>BONUS</t>
         </is>
@@ -7592,9 +7598,14 @@
           <t>05/01</t>
         </is>
       </c>
-      <c r="L5" s="7" t="inlineStr"/>
+      <c r="L5" s="9" t="inlineStr">
+        <is>
+          <t>05/11</t>
+        </is>
+      </c>
       <c r="M5" s="7" t="inlineStr"/>
       <c r="N5" s="7" t="inlineStr"/>
+      <c r="O5" s="7" t="inlineStr"/>
     </row>
     <row r="6" ht="14" customHeight="1">
       <c r="A6" s="7" t="inlineStr"/>
@@ -7648,9 +7659,14 @@
           <t>L</t>
         </is>
       </c>
-      <c r="L6" s="7" t="inlineStr"/>
+      <c r="L6" s="10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="M6" s="7" t="inlineStr"/>
       <c r="N6" s="7" t="inlineStr"/>
+      <c r="O6" s="7" t="inlineStr"/>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="12" t="inlineStr"/>
@@ -7686,12 +7702,15 @@
       <c r="K7" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="L7" s="18">
-        <f>IFERROR(AVERAGE(C7:K7),"")</f>
-        <v/>
-      </c>
-      <c r="M7" s="12" t="inlineStr"/>
+      <c r="L7" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" s="18">
+        <f>IFERROR(AVERAGE(C7:L7),"")</f>
+        <v/>
+      </c>
       <c r="N7" s="12" t="inlineStr"/>
+      <c r="O7" s="12" t="inlineStr"/>
     </row>
     <row r="8" ht="13" customHeight="1">
       <c r="A8" s="19" t="inlineStr"/>
@@ -7709,12 +7728,13 @@
       <c r="I8" s="19" t="inlineStr"/>
       <c r="J8" s="19" t="inlineStr"/>
       <c r="K8" s="19" t="inlineStr"/>
-      <c r="L8" s="21">
-        <f>IFERROR(AVERAGE(C8:K8),"")</f>
-        <v/>
-      </c>
-      <c r="M8" s="19" t="inlineStr"/>
+      <c r="L8" s="19" t="inlineStr"/>
+      <c r="M8" s="21">
+        <f>IFERROR(AVERAGE(C8:L8),"")</f>
+        <v/>
+      </c>
       <c r="N8" s="19" t="inlineStr"/>
+      <c r="O8" s="19" t="inlineStr"/>
     </row>
     <row r="9" ht="13" customHeight="1">
       <c r="A9" s="19" t="inlineStr"/>
@@ -7732,12 +7752,13 @@
       <c r="I9" s="19" t="inlineStr"/>
       <c r="J9" s="19" t="inlineStr"/>
       <c r="K9" s="19" t="inlineStr"/>
-      <c r="L9" s="21">
-        <f>IFERROR(AVERAGE(C9:K9),"")</f>
-        <v/>
-      </c>
-      <c r="M9" s="19" t="inlineStr"/>
+      <c r="L9" s="19" t="inlineStr"/>
+      <c r="M9" s="21">
+        <f>IFERROR(AVERAGE(C9:L9),"")</f>
+        <v/>
+      </c>
       <c r="N9" s="19" t="inlineStr"/>
+      <c r="O9" s="19" t="inlineStr"/>
     </row>
     <row r="10" ht="13" customHeight="1">
       <c r="A10" s="19" t="inlineStr"/>
@@ -7755,12 +7776,13 @@
       <c r="I10" s="19" t="inlineStr"/>
       <c r="J10" s="19" t="inlineStr"/>
       <c r="K10" s="19" t="inlineStr"/>
-      <c r="L10" s="21">
-        <f>IFERROR(AVERAGE(C10:K10),"")</f>
-        <v/>
-      </c>
-      <c r="M10" s="19" t="inlineStr"/>
+      <c r="L10" s="19" t="inlineStr"/>
+      <c r="M10" s="21">
+        <f>IFERROR(AVERAGE(C10:L10),"")</f>
+        <v/>
+      </c>
       <c r="N10" s="19" t="inlineStr"/>
+      <c r="O10" s="19" t="inlineStr"/>
     </row>
     <row r="11" ht="13" customHeight="1">
       <c r="A11" s="19" t="inlineStr"/>
@@ -7778,12 +7800,13 @@
       <c r="I11" s="19" t="inlineStr"/>
       <c r="J11" s="19" t="inlineStr"/>
       <c r="K11" s="19" t="inlineStr"/>
-      <c r="L11" s="21">
-        <f>IFERROR(AVERAGE(C11:K11),"")</f>
-        <v/>
-      </c>
-      <c r="M11" s="19" t="inlineStr"/>
+      <c r="L11" s="19" t="inlineStr"/>
+      <c r="M11" s="21">
+        <f>IFERROR(AVERAGE(C11:L11),"")</f>
+        <v/>
+      </c>
       <c r="N11" s="19" t="inlineStr"/>
+      <c r="O11" s="19" t="inlineStr"/>
     </row>
     <row r="12" ht="6" customHeight="1">
       <c r="A12" s="22" t="n"/>
@@ -7841,16 +7864,17 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L14" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$K$7,C14:K14,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="M14" s="28">
-        <f>COUNTIF(C14:K14,"Y")</f>
-        <v/>
-      </c>
-      <c r="N14" s="29">
-        <f>SUMPRODUCT((C$7:$K$7=1)*(C14:K14="Y"))*50</f>
+      <c r="L14" s="27" t="n"/>
+      <c r="M14" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C14:L14,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="N14" s="28">
+        <f>COUNTIF(C14:L14,"Y")</f>
+        <v/>
+      </c>
+      <c r="O14" s="29">
+        <f>SUMPRODUCT((C$7:$L$7=1)*(C14:L14="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -7876,16 +7900,17 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L15" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$K$7,C15:K15,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="M15" s="28">
-        <f>COUNTIF(C15:K15,"Y")</f>
-        <v/>
-      </c>
-      <c r="N15" s="29">
-        <f>SUMPRODUCT((C$7:$K$7=1)*(C15:K15="Y"))*50</f>
+      <c r="L15" s="27" t="n"/>
+      <c r="M15" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C15:L15,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="N15" s="28">
+        <f>COUNTIF(C15:L15,"Y")</f>
+        <v/>
+      </c>
+      <c r="O15" s="29">
+        <f>SUMPRODUCT((C$7:$L$7=1)*(C15:L15="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -7907,16 +7932,17 @@
       <c r="I16" s="27" t="n"/>
       <c r="J16" s="27" t="n"/>
       <c r="K16" s="27" t="n"/>
-      <c r="L16" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$K$7,C16:K16,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="M16" s="28">
-        <f>COUNTIF(C16:K16,"Y")</f>
-        <v/>
-      </c>
-      <c r="N16" s="29">
-        <f>SUMPRODUCT((C$7:$K$7=1)*(C16:K16="Y"))*50</f>
+      <c r="L16" s="27" t="n"/>
+      <c r="M16" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C16:L16,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="N16" s="28">
+        <f>COUNTIF(C16:L16,"Y")</f>
+        <v/>
+      </c>
+      <c r="O16" s="29">
+        <f>SUMPRODUCT((C$7:$L$7=1)*(C16:L16="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -7938,16 +7964,17 @@
       <c r="I17" s="27" t="n"/>
       <c r="J17" s="27" t="n"/>
       <c r="K17" s="27" t="n"/>
-      <c r="L17" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$K$7,C17:K17,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="M17" s="28">
-        <f>COUNTIF(C17:K17,"Y")</f>
-        <v/>
-      </c>
-      <c r="N17" s="29">
-        <f>SUMPRODUCT((C$7:$K$7=1)*(C17:K17="Y"))*50</f>
+      <c r="L17" s="27" t="n"/>
+      <c r="M17" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C17:L17,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="N17" s="28">
+        <f>COUNTIF(C17:L17,"Y")</f>
+        <v/>
+      </c>
+      <c r="O17" s="29">
+        <f>SUMPRODUCT((C$7:$L$7=1)*(C17:L17="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -7979,16 +8006,17 @@
       <c r="I20" s="33" t="n"/>
       <c r="J20" s="33" t="n"/>
       <c r="K20" s="33" t="n"/>
-      <c r="L20" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$K$7,C20:K20,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="M20" s="28">
-        <f>COUNTIF(C20:K20,"Y")</f>
-        <v/>
-      </c>
-      <c r="N20" s="29">
-        <f>SUMPRODUCT((C$7:$K$7=1)*(C20:K20="Y"))*50</f>
+      <c r="L20" s="33" t="n"/>
+      <c r="M20" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C20:L20,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="N20" s="28">
+        <f>COUNTIF(C20:L20,"Y")</f>
+        <v/>
+      </c>
+      <c r="O20" s="29">
+        <f>SUMPRODUCT((C$7:$L$7=1)*(C20:L20="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8010,16 +8038,17 @@
       <c r="I21" s="19" t="n"/>
       <c r="J21" s="19" t="n"/>
       <c r="K21" s="19" t="n"/>
-      <c r="L21" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$K$7,C21:K21,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="M21" s="28">
-        <f>COUNTIF(C21:K21,"Y")</f>
-        <v/>
-      </c>
-      <c r="N21" s="29">
-        <f>SUMPRODUCT((C$7:$K$7=1)*(C21:K21="Y"))*50</f>
+      <c r="L21" s="19" t="n"/>
+      <c r="M21" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C21:L21,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="N21" s="28">
+        <f>COUNTIF(C21:L21,"Y")</f>
+        <v/>
+      </c>
+      <c r="O21" s="29">
+        <f>SUMPRODUCT((C$7:$L$7=1)*(C21:L21="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8049,16 +8078,17 @@
       <c r="I22" s="33" t="n"/>
       <c r="J22" s="33" t="n"/>
       <c r="K22" s="33" t="n"/>
-      <c r="L22" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$K$7,C22:K22,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="M22" s="28">
-        <f>COUNTIF(C22:K22,"Y")</f>
-        <v/>
-      </c>
-      <c r="N22" s="29">
-        <f>SUMPRODUCT((C$7:$K$7=1)*(C22:K22="Y"))*50</f>
+      <c r="L22" s="33" t="n"/>
+      <c r="M22" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C22:L22,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="N22" s="28">
+        <f>COUNTIF(C22:L22,"Y")</f>
+        <v/>
+      </c>
+      <c r="O22" s="29">
+        <f>SUMPRODUCT((C$7:$L$7=1)*(C22:L22="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8080,16 +8110,17 @@
       <c r="I23" s="19" t="n"/>
       <c r="J23" s="19" t="n"/>
       <c r="K23" s="19" t="n"/>
-      <c r="L23" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$K$7,C23:K23,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="M23" s="28">
-        <f>COUNTIF(C23:K23,"Y")</f>
-        <v/>
-      </c>
-      <c r="N23" s="29">
-        <f>SUMPRODUCT((C$7:$K$7=1)*(C23:K23="Y"))*50</f>
+      <c r="L23" s="19" t="n"/>
+      <c r="M23" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C23:L23,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="N23" s="28">
+        <f>COUNTIF(C23:L23,"Y")</f>
+        <v/>
+      </c>
+      <c r="O23" s="29">
+        <f>SUMPRODUCT((C$7:$L$7=1)*(C23:L23="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8111,16 +8142,17 @@
       <c r="I24" s="33" t="n"/>
       <c r="J24" s="33" t="n"/>
       <c r="K24" s="33" t="n"/>
-      <c r="L24" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$K$7,C24:K24,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="M24" s="28">
-        <f>COUNTIF(C24:K24,"Y")</f>
-        <v/>
-      </c>
-      <c r="N24" s="29">
-        <f>SUMPRODUCT((C$7:$K$7=1)*(C24:K24="Y"))*50</f>
+      <c r="L24" s="33" t="n"/>
+      <c r="M24" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C24:L24,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="N24" s="28">
+        <f>COUNTIF(C24:L24,"Y")</f>
+        <v/>
+      </c>
+      <c r="O24" s="29">
+        <f>SUMPRODUCT((C$7:$L$7=1)*(C24:L24="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8142,16 +8174,17 @@
       <c r="I25" s="19" t="n"/>
       <c r="J25" s="19" t="n"/>
       <c r="K25" s="19" t="n"/>
-      <c r="L25" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$K$7,C25:K25,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="M25" s="28">
-        <f>COUNTIF(C25:K25,"Y")</f>
-        <v/>
-      </c>
-      <c r="N25" s="29">
-        <f>SUMPRODUCT((C$7:$K$7=1)*(C25:K25="Y"))*50</f>
+      <c r="L25" s="19" t="n"/>
+      <c r="M25" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C25:L25,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="N25" s="28">
+        <f>COUNTIF(C25:L25,"Y")</f>
+        <v/>
+      </c>
+      <c r="O25" s="29">
+        <f>SUMPRODUCT((C$7:$L$7=1)*(C25:L25="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8181,16 +8214,17 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L26" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$K$7,C26:K26,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="M26" s="28">
-        <f>COUNTIF(C26:K26,"Y")</f>
-        <v/>
-      </c>
-      <c r="N26" s="29">
-        <f>SUMPRODUCT((C$7:$K$7=1)*(C26:K26="Y"))*50</f>
+      <c r="L26" s="33" t="n"/>
+      <c r="M26" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C26:L26,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="N26" s="28">
+        <f>COUNTIF(C26:L26,"Y")</f>
+        <v/>
+      </c>
+      <c r="O26" s="29">
+        <f>SUMPRODUCT((C$7:$L$7=1)*(C26:L26="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8212,16 +8246,17 @@
       <c r="I27" s="19" t="n"/>
       <c r="J27" s="19" t="n"/>
       <c r="K27" s="19" t="n"/>
-      <c r="L27" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$K$7,C27:K27,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="M27" s="28">
-        <f>COUNTIF(C27:K27,"Y")</f>
-        <v/>
-      </c>
-      <c r="N27" s="29">
-        <f>SUMPRODUCT((C$7:$K$7=1)*(C27:K27="Y"))*50</f>
+      <c r="L27" s="19" t="n"/>
+      <c r="M27" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C27:L27,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="N27" s="28">
+        <f>COUNTIF(C27:L27,"Y")</f>
+        <v/>
+      </c>
+      <c r="O27" s="29">
+        <f>SUMPRODUCT((C$7:$L$7=1)*(C27:L27="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8243,16 +8278,17 @@
       <c r="I28" s="33" t="n"/>
       <c r="J28" s="33" t="n"/>
       <c r="K28" s="33" t="n"/>
-      <c r="L28" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$K$7,C28:K28,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="M28" s="28">
-        <f>COUNTIF(C28:K28,"Y")</f>
-        <v/>
-      </c>
-      <c r="N28" s="29">
-        <f>SUMPRODUCT((C$7:$K$7=1)*(C28:K28="Y"))*50</f>
+      <c r="L28" s="33" t="n"/>
+      <c r="M28" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C28:L28,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="N28" s="28">
+        <f>COUNTIF(C28:L28,"Y")</f>
+        <v/>
+      </c>
+      <c r="O28" s="29">
+        <f>SUMPRODUCT((C$7:$L$7=1)*(C28:L28="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8302,16 +8338,17 @@
         </is>
       </c>
       <c r="K29" s="19" t="n"/>
-      <c r="L29" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$K$7,C29:K29,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="M29" s="28">
-        <f>COUNTIF(C29:K29,"Y")</f>
-        <v/>
-      </c>
-      <c r="N29" s="29">
-        <f>SUMPRODUCT((C$7:$K$7=1)*(C29:K29="Y"))*50</f>
+      <c r="L29" s="19" t="n"/>
+      <c r="M29" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C29:L29,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="N29" s="28">
+        <f>COUNTIF(C29:L29,"Y")</f>
+        <v/>
+      </c>
+      <c r="O29" s="29">
+        <f>SUMPRODUCT((C$7:$L$7=1)*(C29:L29="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8333,16 +8370,17 @@
       <c r="I30" s="33" t="n"/>
       <c r="J30" s="33" t="n"/>
       <c r="K30" s="33" t="n"/>
-      <c r="L30" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$K$7,C30:K30,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="M30" s="28">
-        <f>COUNTIF(C30:K30,"Y")</f>
-        <v/>
-      </c>
-      <c r="N30" s="29">
-        <f>SUMPRODUCT((C$7:$K$7=1)*(C30:K30="Y"))*50</f>
+      <c r="L30" s="33" t="n"/>
+      <c r="M30" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C30:L30,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="N30" s="28">
+        <f>COUNTIF(C30:L30,"Y")</f>
+        <v/>
+      </c>
+      <c r="O30" s="29">
+        <f>SUMPRODUCT((C$7:$L$7=1)*(C30:L30="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8364,16 +8402,17 @@
       <c r="I31" s="19" t="n"/>
       <c r="J31" s="19" t="n"/>
       <c r="K31" s="19" t="n"/>
-      <c r="L31" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$K$7,C31:K31,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="M31" s="28">
-        <f>COUNTIF(C31:K31,"Y")</f>
-        <v/>
-      </c>
-      <c r="N31" s="29">
-        <f>SUMPRODUCT((C$7:$K$7=1)*(C31:K31="Y"))*50</f>
+      <c r="L31" s="19" t="n"/>
+      <c r="M31" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C31:L31,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="N31" s="28">
+        <f>COUNTIF(C31:L31,"Y")</f>
+        <v/>
+      </c>
+      <c r="O31" s="29">
+        <f>SUMPRODUCT((C$7:$L$7=1)*(C31:L31="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8395,16 +8434,17 @@
       <c r="I32" s="33" t="n"/>
       <c r="J32" s="33" t="n"/>
       <c r="K32" s="33" t="n"/>
-      <c r="L32" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$K$7,C32:K32,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="M32" s="28">
-        <f>COUNTIF(C32:K32,"Y")</f>
-        <v/>
-      </c>
-      <c r="N32" s="29">
-        <f>SUMPRODUCT((C$7:$K$7=1)*(C32:K32="Y"))*50</f>
+      <c r="L32" s="33" t="n"/>
+      <c r="M32" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C32:L32,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="N32" s="28">
+        <f>COUNTIF(C32:L32,"Y")</f>
+        <v/>
+      </c>
+      <c r="O32" s="29">
+        <f>SUMPRODUCT((C$7:$L$7=1)*(C32:L32="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8438,16 +8478,17 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L33" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$K$7,C33:K33,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="M33" s="28">
-        <f>COUNTIF(C33:K33,"Y")</f>
-        <v/>
-      </c>
-      <c r="N33" s="29">
-        <f>SUMPRODUCT((C$7:$K$7=1)*(C33:K33="Y"))*50</f>
+      <c r="L33" s="19" t="n"/>
+      <c r="M33" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C33:L33,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="N33" s="28">
+        <f>COUNTIF(C33:L33,"Y")</f>
+        <v/>
+      </c>
+      <c r="O33" s="29">
+        <f>SUMPRODUCT((C$7:$L$7=1)*(C33:L33="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8473,16 +8514,17 @@
       <c r="I34" s="33" t="n"/>
       <c r="J34" s="33" t="n"/>
       <c r="K34" s="33" t="n"/>
-      <c r="L34" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$K$7,C34:K34,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="M34" s="28">
-        <f>COUNTIF(C34:K34,"Y")</f>
-        <v/>
-      </c>
-      <c r="N34" s="29">
-        <f>SUMPRODUCT((C$7:$K$7=1)*(C34:K34="Y"))*50</f>
+      <c r="L34" s="33" t="n"/>
+      <c r="M34" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C34:L34,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="N34" s="28">
+        <f>COUNTIF(C34:L34,"Y")</f>
+        <v/>
+      </c>
+      <c r="O34" s="29">
+        <f>SUMPRODUCT((C$7:$L$7=1)*(C34:L34="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8504,16 +8546,17 @@
       <c r="I35" s="19" t="n"/>
       <c r="J35" s="19" t="n"/>
       <c r="K35" s="19" t="n"/>
-      <c r="L35" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$K$7,C35:K35,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="M35" s="28">
-        <f>COUNTIF(C35:K35,"Y")</f>
-        <v/>
-      </c>
-      <c r="N35" s="29">
-        <f>SUMPRODUCT((C$7:$K$7=1)*(C35:K35="Y"))*50</f>
+      <c r="L35" s="19" t="n"/>
+      <c r="M35" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C35:L35,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="N35" s="28">
+        <f>COUNTIF(C35:L35,"Y")</f>
+        <v/>
+      </c>
+      <c r="O35" s="29">
+        <f>SUMPRODUCT((C$7:$L$7=1)*(C35:L35="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8535,16 +8578,17 @@
       <c r="I36" s="33" t="n"/>
       <c r="J36" s="33" t="n"/>
       <c r="K36" s="33" t="n"/>
-      <c r="L36" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$K$7,C36:K36,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="M36" s="28">
-        <f>COUNTIF(C36:K36,"Y")</f>
-        <v/>
-      </c>
-      <c r="N36" s="29">
-        <f>SUMPRODUCT((C$7:$K$7=1)*(C36:K36="Y"))*50</f>
+      <c r="L36" s="33" t="n"/>
+      <c r="M36" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C36:L36,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="N36" s="28">
+        <f>COUNTIF(C36:L36,"Y")</f>
+        <v/>
+      </c>
+      <c r="O36" s="29">
+        <f>SUMPRODUCT((C$7:$L$7=1)*(C36:L36="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8578,16 +8622,17 @@
       </c>
       <c r="J37" s="19" t="n"/>
       <c r="K37" s="19" t="n"/>
-      <c r="L37" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$K$7,C37:K37,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="M37" s="28">
-        <f>COUNTIF(C37:K37,"Y")</f>
-        <v/>
-      </c>
-      <c r="N37" s="29">
-        <f>SUMPRODUCT((C$7:$K$7=1)*(C37:K37="Y"))*50</f>
+      <c r="L37" s="19" t="n"/>
+      <c r="M37" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C37:L37,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="N37" s="28">
+        <f>COUNTIF(C37:L37,"Y")</f>
+        <v/>
+      </c>
+      <c r="O37" s="29">
+        <f>SUMPRODUCT((C$7:$L$7=1)*(C37:L37="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8609,16 +8654,17 @@
       <c r="I38" s="33" t="n"/>
       <c r="J38" s="33" t="n"/>
       <c r="K38" s="33" t="n"/>
-      <c r="L38" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$K$7,C38:K38,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="M38" s="28">
-        <f>COUNTIF(C38:K38,"Y")</f>
-        <v/>
-      </c>
-      <c r="N38" s="29">
-        <f>SUMPRODUCT((C$7:$K$7=1)*(C38:K38="Y"))*50</f>
+      <c r="L38" s="33" t="n"/>
+      <c r="M38" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C38:L38,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="N38" s="28">
+        <f>COUNTIF(C38:L38,"Y")</f>
+        <v/>
+      </c>
+      <c r="O38" s="29">
+        <f>SUMPRODUCT((C$7:$L$7=1)*(C38:L38="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8665,13 +8711,17 @@
         <f>COUNTIF(K14:K38,"Y")</f>
         <v/>
       </c>
-      <c r="L39" s="3" t="inlineStr"/>
-      <c r="M39" s="6">
-        <f>SUM(M14:M38)</f>
-        <v/>
-      </c>
-      <c r="N39" s="37">
+      <c r="L39" s="6">
+        <f>COUNTIF(L14:L38,"Y")</f>
+        <v/>
+      </c>
+      <c r="M39" s="3" t="inlineStr"/>
+      <c r="N39" s="6">
         <f>SUM(N14:N38)</f>
+        <v/>
+      </c>
+      <c r="O39" s="37">
+        <f>SUM(O14:O38)</f>
         <v/>
       </c>
     </row>
@@ -8684,13 +8734,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A40:N40"/>
-    <mergeCell ref="A18:N18"/>
-    <mergeCell ref="A12:N12"/>
-    <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A19:N19"/>
-    <mergeCell ref="A13:N13"/>
-    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A12:O12"/>
+    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="A13:O13"/>
+    <mergeCell ref="A19:O19"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A40:O40"/>
+    <mergeCell ref="A18:O18"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Shop_Tracker_2065_2026.xlsx
+++ b/Shop_Tracker_2065_2026.xlsx
@@ -7864,7 +7864,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L14" s="27" t="n"/>
+      <c r="L14" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="M14" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$L$7,C14:L14,"Y"),"")</f>
         <v/>
@@ -8110,7 +8114,11 @@
       <c r="I23" s="19" t="n"/>
       <c r="J23" s="19" t="n"/>
       <c r="K23" s="19" t="n"/>
-      <c r="L23" s="19" t="n"/>
+      <c r="L23" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="M23" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$L$7,C23:L23,"Y"),"")</f>
         <v/>
@@ -8142,7 +8150,11 @@
       <c r="I24" s="33" t="n"/>
       <c r="J24" s="33" t="n"/>
       <c r="K24" s="33" t="n"/>
-      <c r="L24" s="33" t="n"/>
+      <c r="L24" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="M24" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$L$7,C24:L24,"Y"),"")</f>
         <v/>
@@ -8214,7 +8226,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L26" s="33" t="n"/>
+      <c r="L26" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="M26" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$L$7,C26:L26,"Y"),"")</f>
         <v/>
@@ -8514,7 +8530,11 @@
       <c r="I34" s="33" t="n"/>
       <c r="J34" s="33" t="n"/>
       <c r="K34" s="33" t="n"/>
-      <c r="L34" s="33" t="n"/>
+      <c r="L34" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="M34" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$L$7,C34:L34,"Y"),"")</f>
         <v/>

--- a/Shop_Tracker_2065_2026.xlsx
+++ b/Shop_Tracker_2065_2026.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="January" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="February" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="March" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="April" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="May" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="January" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="February" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="March" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="April" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="May" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/Shop_Tracker_2065_2026.xlsx
+++ b/Shop_Tracker_2065_2026.xlsx
@@ -7438,7 +7438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O40"/>
+  <dimension ref="A1:Q40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -7453,9 +7453,11 @@
     <col width="7" customWidth="1" min="10" max="10"/>
     <col width="7" customWidth="1" min="11" max="11"/>
     <col width="7" customWidth="1" min="12" max="12"/>
-    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="7" customWidth="1" min="13" max="13"/>
     <col width="7" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="7" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -7468,7 +7470,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Five Guys Store 2065 · Louisville, KY · 10 shops · Source: Marketforce + CrunchTime</t>
+          <t>Five Guys Store 2065 · Louisville, KY · 12 shops · Source: Marketforce + CrunchTime</t>
         </is>
       </c>
     </row>
@@ -7530,17 +7532,27 @@
           <t>#10</t>
         </is>
       </c>
-      <c r="M4" s="6" t="inlineStr">
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>#11</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t>#12</t>
+        </is>
+      </c>
+      <c r="O4" s="6" t="inlineStr">
         <is>
           <t>AVG</t>
         </is>
       </c>
-      <c r="N4" s="6" t="inlineStr">
+      <c r="P4" s="6" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="O4" s="6" t="inlineStr">
+      <c r="Q4" s="6" t="inlineStr">
         <is>
           <t>BONUS</t>
         </is>
@@ -7603,9 +7615,19 @@
           <t>05/11</t>
         </is>
       </c>
-      <c r="M5" s="7" t="inlineStr"/>
-      <c r="N5" s="7" t="inlineStr"/>
+      <c r="M5" s="9" t="inlineStr">
+        <is>
+          <t>05/14</t>
+        </is>
+      </c>
+      <c r="N5" s="9" t="inlineStr">
+        <is>
+          <t>05/16</t>
+        </is>
+      </c>
       <c r="O5" s="7" t="inlineStr"/>
+      <c r="P5" s="7" t="inlineStr"/>
+      <c r="Q5" s="7" t="inlineStr"/>
     </row>
     <row r="6" ht="14" customHeight="1">
       <c r="A6" s="7" t="inlineStr"/>
@@ -7664,9 +7686,19 @@
           <t>D</t>
         </is>
       </c>
-      <c r="M6" s="7" t="inlineStr"/>
-      <c r="N6" s="7" t="inlineStr"/>
+      <c r="M6" s="11" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="O6" s="7" t="inlineStr"/>
+      <c r="P6" s="7" t="inlineStr"/>
+      <c r="Q6" s="7" t="inlineStr"/>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="12" t="inlineStr"/>
@@ -7705,12 +7737,18 @@
       <c r="L7" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="M7" s="18">
-        <f>IFERROR(AVERAGE(C7:L7),"")</f>
-        <v/>
-      </c>
-      <c r="N7" s="12" t="inlineStr"/>
-      <c r="O7" s="12" t="inlineStr"/>
+      <c r="M7" s="17" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N7" s="16" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="O7" s="18">
+        <f>IFERROR(AVERAGE(C7:N7),"")</f>
+        <v/>
+      </c>
+      <c r="P7" s="12" t="inlineStr"/>
+      <c r="Q7" s="12" t="inlineStr"/>
     </row>
     <row r="8" ht="13" customHeight="1">
       <c r="A8" s="19" t="inlineStr"/>
@@ -7729,12 +7767,14 @@
       <c r="J8" s="19" t="inlineStr"/>
       <c r="K8" s="19" t="inlineStr"/>
       <c r="L8" s="19" t="inlineStr"/>
-      <c r="M8" s="21">
-        <f>IFERROR(AVERAGE(C8:L8),"")</f>
-        <v/>
-      </c>
+      <c r="M8" s="19" t="inlineStr"/>
       <c r="N8" s="19" t="inlineStr"/>
-      <c r="O8" s="19" t="inlineStr"/>
+      <c r="O8" s="21">
+        <f>IFERROR(AVERAGE(C8:N8),"")</f>
+        <v/>
+      </c>
+      <c r="P8" s="19" t="inlineStr"/>
+      <c r="Q8" s="19" t="inlineStr"/>
     </row>
     <row r="9" ht="13" customHeight="1">
       <c r="A9" s="19" t="inlineStr"/>
@@ -7753,12 +7793,14 @@
       <c r="J9" s="19" t="inlineStr"/>
       <c r="K9" s="19" t="inlineStr"/>
       <c r="L9" s="19" t="inlineStr"/>
-      <c r="M9" s="21">
-        <f>IFERROR(AVERAGE(C9:L9),"")</f>
-        <v/>
-      </c>
+      <c r="M9" s="19" t="inlineStr"/>
       <c r="N9" s="19" t="inlineStr"/>
-      <c r="O9" s="19" t="inlineStr"/>
+      <c r="O9" s="21">
+        <f>IFERROR(AVERAGE(C9:N9),"")</f>
+        <v/>
+      </c>
+      <c r="P9" s="19" t="inlineStr"/>
+      <c r="Q9" s="19" t="inlineStr"/>
     </row>
     <row r="10" ht="13" customHeight="1">
       <c r="A10" s="19" t="inlineStr"/>
@@ -7777,12 +7819,14 @@
       <c r="J10" s="19" t="inlineStr"/>
       <c r="K10" s="19" t="inlineStr"/>
       <c r="L10" s="19" t="inlineStr"/>
-      <c r="M10" s="21">
-        <f>IFERROR(AVERAGE(C10:L10),"")</f>
-        <v/>
-      </c>
+      <c r="M10" s="19" t="inlineStr"/>
       <c r="N10" s="19" t="inlineStr"/>
-      <c r="O10" s="19" t="inlineStr"/>
+      <c r="O10" s="21">
+        <f>IFERROR(AVERAGE(C10:N10),"")</f>
+        <v/>
+      </c>
+      <c r="P10" s="19" t="inlineStr"/>
+      <c r="Q10" s="19" t="inlineStr"/>
     </row>
     <row r="11" ht="13" customHeight="1">
       <c r="A11" s="19" t="inlineStr"/>
@@ -7801,12 +7845,14 @@
       <c r="J11" s="19" t="inlineStr"/>
       <c r="K11" s="19" t="inlineStr"/>
       <c r="L11" s="19" t="inlineStr"/>
-      <c r="M11" s="21">
-        <f>IFERROR(AVERAGE(C11:L11),"")</f>
-        <v/>
-      </c>
+      <c r="M11" s="19" t="inlineStr"/>
       <c r="N11" s="19" t="inlineStr"/>
-      <c r="O11" s="19" t="inlineStr"/>
+      <c r="O11" s="21">
+        <f>IFERROR(AVERAGE(C11:N11),"")</f>
+        <v/>
+      </c>
+      <c r="P11" s="19" t="inlineStr"/>
+      <c r="Q11" s="19" t="inlineStr"/>
     </row>
     <row r="12" ht="6" customHeight="1">
       <c r="A12" s="22" t="n"/>
@@ -7869,16 +7915,26 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M14" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C14:L14,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="N14" s="28">
-        <f>COUNTIF(C14:L14,"Y")</f>
-        <v/>
-      </c>
-      <c r="O14" s="29">
-        <f>SUMPRODUCT((C$7:$L$7=1)*(C14:L14="Y"))*50</f>
+      <c r="M14" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N14" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O14" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$N$7,C14:N14,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="P14" s="28">
+        <f>COUNTIF(C14:N14,"Y")</f>
+        <v/>
+      </c>
+      <c r="Q14" s="29">
+        <f>SUMPRODUCT((C$7:$N$7=1)*(C14:N14="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -7905,16 +7961,22 @@
         </is>
       </c>
       <c r="L15" s="27" t="n"/>
-      <c r="M15" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C15:L15,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="N15" s="28">
-        <f>COUNTIF(C15:L15,"Y")</f>
-        <v/>
-      </c>
-      <c r="O15" s="29">
-        <f>SUMPRODUCT((C$7:$L$7=1)*(C15:L15="Y"))*50</f>
+      <c r="M15" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N15" s="27" t="n"/>
+      <c r="O15" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$N$7,C15:N15,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="P15" s="28">
+        <f>COUNTIF(C15:N15,"Y")</f>
+        <v/>
+      </c>
+      <c r="Q15" s="29">
+        <f>SUMPRODUCT((C$7:$N$7=1)*(C15:N15="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -7937,16 +7999,18 @@
       <c r="J16" s="27" t="n"/>
       <c r="K16" s="27" t="n"/>
       <c r="L16" s="27" t="n"/>
-      <c r="M16" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C16:L16,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="N16" s="28">
-        <f>COUNTIF(C16:L16,"Y")</f>
-        <v/>
-      </c>
-      <c r="O16" s="29">
-        <f>SUMPRODUCT((C$7:$L$7=1)*(C16:L16="Y"))*50</f>
+      <c r="M16" s="27" t="n"/>
+      <c r="N16" s="27" t="n"/>
+      <c r="O16" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$N$7,C16:N16,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="P16" s="28">
+        <f>COUNTIF(C16:N16,"Y")</f>
+        <v/>
+      </c>
+      <c r="Q16" s="29">
+        <f>SUMPRODUCT((C$7:$N$7=1)*(C16:N16="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -7969,16 +8033,22 @@
       <c r="J17" s="27" t="n"/>
       <c r="K17" s="27" t="n"/>
       <c r="L17" s="27" t="n"/>
-      <c r="M17" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C17:L17,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="N17" s="28">
-        <f>COUNTIF(C17:L17,"Y")</f>
-        <v/>
-      </c>
-      <c r="O17" s="29">
-        <f>SUMPRODUCT((C$7:$L$7=1)*(C17:L17="Y"))*50</f>
+      <c r="M17" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N17" s="27" t="n"/>
+      <c r="O17" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$N$7,C17:N17,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="P17" s="28">
+        <f>COUNTIF(C17:N17,"Y")</f>
+        <v/>
+      </c>
+      <c r="Q17" s="29">
+        <f>SUMPRODUCT((C$7:$N$7=1)*(C17:N17="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8011,16 +8081,18 @@
       <c r="J20" s="33" t="n"/>
       <c r="K20" s="33" t="n"/>
       <c r="L20" s="33" t="n"/>
-      <c r="M20" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C20:L20,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="N20" s="28">
-        <f>COUNTIF(C20:L20,"Y")</f>
-        <v/>
-      </c>
-      <c r="O20" s="29">
-        <f>SUMPRODUCT((C$7:$L$7=1)*(C20:L20="Y"))*50</f>
+      <c r="M20" s="33" t="n"/>
+      <c r="N20" s="33" t="n"/>
+      <c r="O20" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$N$7,C20:N20,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="P20" s="28">
+        <f>COUNTIF(C20:N20,"Y")</f>
+        <v/>
+      </c>
+      <c r="Q20" s="29">
+        <f>SUMPRODUCT((C$7:$N$7=1)*(C20:N20="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8043,16 +8115,18 @@
       <c r="J21" s="19" t="n"/>
       <c r="K21" s="19" t="n"/>
       <c r="L21" s="19" t="n"/>
-      <c r="M21" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C21:L21,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="N21" s="28">
-        <f>COUNTIF(C21:L21,"Y")</f>
-        <v/>
-      </c>
-      <c r="O21" s="29">
-        <f>SUMPRODUCT((C$7:$L$7=1)*(C21:L21="Y"))*50</f>
+      <c r="M21" s="19" t="n"/>
+      <c r="N21" s="19" t="n"/>
+      <c r="O21" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$N$7,C21:N21,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="P21" s="28">
+        <f>COUNTIF(C21:N21,"Y")</f>
+        <v/>
+      </c>
+      <c r="Q21" s="29">
+        <f>SUMPRODUCT((C$7:$N$7=1)*(C21:N21="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8083,16 +8157,18 @@
       <c r="J22" s="33" t="n"/>
       <c r="K22" s="33" t="n"/>
       <c r="L22" s="33" t="n"/>
-      <c r="M22" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C22:L22,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="N22" s="28">
-        <f>COUNTIF(C22:L22,"Y")</f>
-        <v/>
-      </c>
-      <c r="O22" s="29">
-        <f>SUMPRODUCT((C$7:$L$7=1)*(C22:L22="Y"))*50</f>
+      <c r="M22" s="33" t="n"/>
+      <c r="N22" s="33" t="n"/>
+      <c r="O22" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$N$7,C22:N22,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="P22" s="28">
+        <f>COUNTIF(C22:N22,"Y")</f>
+        <v/>
+      </c>
+      <c r="Q22" s="29">
+        <f>SUMPRODUCT((C$7:$N$7=1)*(C22:N22="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8119,16 +8195,18 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M23" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C23:L23,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="N23" s="28">
-        <f>COUNTIF(C23:L23,"Y")</f>
-        <v/>
-      </c>
-      <c r="O23" s="29">
-        <f>SUMPRODUCT((C$7:$L$7=1)*(C23:L23="Y"))*50</f>
+      <c r="M23" s="19" t="n"/>
+      <c r="N23" s="19" t="n"/>
+      <c r="O23" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$N$7,C23:N23,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="P23" s="28">
+        <f>COUNTIF(C23:N23,"Y")</f>
+        <v/>
+      </c>
+      <c r="Q23" s="29">
+        <f>SUMPRODUCT((C$7:$N$7=1)*(C23:N23="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8155,16 +8233,18 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M24" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C24:L24,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="N24" s="28">
-        <f>COUNTIF(C24:L24,"Y")</f>
-        <v/>
-      </c>
-      <c r="O24" s="29">
-        <f>SUMPRODUCT((C$7:$L$7=1)*(C24:L24="Y"))*50</f>
+      <c r="M24" s="33" t="n"/>
+      <c r="N24" s="33" t="n"/>
+      <c r="O24" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$N$7,C24:N24,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="P24" s="28">
+        <f>COUNTIF(C24:N24,"Y")</f>
+        <v/>
+      </c>
+      <c r="Q24" s="29">
+        <f>SUMPRODUCT((C$7:$N$7=1)*(C24:N24="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8187,16 +8267,18 @@
       <c r="J25" s="19" t="n"/>
       <c r="K25" s="19" t="n"/>
       <c r="L25" s="19" t="n"/>
-      <c r="M25" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C25:L25,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="N25" s="28">
-        <f>COUNTIF(C25:L25,"Y")</f>
-        <v/>
-      </c>
-      <c r="O25" s="29">
-        <f>SUMPRODUCT((C$7:$L$7=1)*(C25:L25="Y"))*50</f>
+      <c r="M25" s="19" t="n"/>
+      <c r="N25" s="19" t="n"/>
+      <c r="O25" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$N$7,C25:N25,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="P25" s="28">
+        <f>COUNTIF(C25:N25,"Y")</f>
+        <v/>
+      </c>
+      <c r="Q25" s="29">
+        <f>SUMPRODUCT((C$7:$N$7=1)*(C25:N25="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8231,16 +8313,22 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M26" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C26:L26,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="N26" s="28">
-        <f>COUNTIF(C26:L26,"Y")</f>
-        <v/>
-      </c>
-      <c r="O26" s="29">
-        <f>SUMPRODUCT((C$7:$L$7=1)*(C26:L26="Y"))*50</f>
+      <c r="M26" s="33" t="n"/>
+      <c r="N26" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O26" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$N$7,C26:N26,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="P26" s="28">
+        <f>COUNTIF(C26:N26,"Y")</f>
+        <v/>
+      </c>
+      <c r="Q26" s="29">
+        <f>SUMPRODUCT((C$7:$N$7=1)*(C26:N26="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8263,16 +8351,18 @@
       <c r="J27" s="19" t="n"/>
       <c r="K27" s="19" t="n"/>
       <c r="L27" s="19" t="n"/>
-      <c r="M27" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C27:L27,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="N27" s="28">
-        <f>COUNTIF(C27:L27,"Y")</f>
-        <v/>
-      </c>
-      <c r="O27" s="29">
-        <f>SUMPRODUCT((C$7:$L$7=1)*(C27:L27="Y"))*50</f>
+      <c r="M27" s="19" t="n"/>
+      <c r="N27" s="19" t="n"/>
+      <c r="O27" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$N$7,C27:N27,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="P27" s="28">
+        <f>COUNTIF(C27:N27,"Y")</f>
+        <v/>
+      </c>
+      <c r="Q27" s="29">
+        <f>SUMPRODUCT((C$7:$N$7=1)*(C27:N27="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8295,16 +8385,22 @@
       <c r="J28" s="33" t="n"/>
       <c r="K28" s="33" t="n"/>
       <c r="L28" s="33" t="n"/>
-      <c r="M28" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C28:L28,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="N28" s="28">
-        <f>COUNTIF(C28:L28,"Y")</f>
-        <v/>
-      </c>
-      <c r="O28" s="29">
-        <f>SUMPRODUCT((C$7:$L$7=1)*(C28:L28="Y"))*50</f>
+      <c r="M28" s="33" t="n"/>
+      <c r="N28" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O28" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$N$7,C28:N28,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="P28" s="28">
+        <f>COUNTIF(C28:N28,"Y")</f>
+        <v/>
+      </c>
+      <c r="Q28" s="29">
+        <f>SUMPRODUCT((C$7:$N$7=1)*(C28:N28="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8355,16 +8451,26 @@
       </c>
       <c r="K29" s="19" t="n"/>
       <c r="L29" s="19" t="n"/>
-      <c r="M29" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C29:L29,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="N29" s="28">
-        <f>COUNTIF(C29:L29,"Y")</f>
-        <v/>
-      </c>
-      <c r="O29" s="29">
-        <f>SUMPRODUCT((C$7:$L$7=1)*(C29:L29="Y"))*50</f>
+      <c r="M29" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N29" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O29" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$N$7,C29:N29,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="P29" s="28">
+        <f>COUNTIF(C29:N29,"Y")</f>
+        <v/>
+      </c>
+      <c r="Q29" s="29">
+        <f>SUMPRODUCT((C$7:$N$7=1)*(C29:N29="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8387,16 +8493,18 @@
       <c r="J30" s="33" t="n"/>
       <c r="K30" s="33" t="n"/>
       <c r="L30" s="33" t="n"/>
-      <c r="M30" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C30:L30,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="N30" s="28">
-        <f>COUNTIF(C30:L30,"Y")</f>
-        <v/>
-      </c>
-      <c r="O30" s="29">
-        <f>SUMPRODUCT((C$7:$L$7=1)*(C30:L30="Y"))*50</f>
+      <c r="M30" s="33" t="n"/>
+      <c r="N30" s="33" t="n"/>
+      <c r="O30" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$N$7,C30:N30,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="P30" s="28">
+        <f>COUNTIF(C30:N30,"Y")</f>
+        <v/>
+      </c>
+      <c r="Q30" s="29">
+        <f>SUMPRODUCT((C$7:$N$7=1)*(C30:N30="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8419,16 +8527,18 @@
       <c r="J31" s="19" t="n"/>
       <c r="K31" s="19" t="n"/>
       <c r="L31" s="19" t="n"/>
-      <c r="M31" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C31:L31,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="N31" s="28">
-        <f>COUNTIF(C31:L31,"Y")</f>
-        <v/>
-      </c>
-      <c r="O31" s="29">
-        <f>SUMPRODUCT((C$7:$L$7=1)*(C31:L31="Y"))*50</f>
+      <c r="M31" s="19" t="n"/>
+      <c r="N31" s="19" t="n"/>
+      <c r="O31" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$N$7,C31:N31,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="P31" s="28">
+        <f>COUNTIF(C31:N31,"Y")</f>
+        <v/>
+      </c>
+      <c r="Q31" s="29">
+        <f>SUMPRODUCT((C$7:$N$7=1)*(C31:N31="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8451,16 +8561,18 @@
       <c r="J32" s="33" t="n"/>
       <c r="K32" s="33" t="n"/>
       <c r="L32" s="33" t="n"/>
-      <c r="M32" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C32:L32,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="N32" s="28">
-        <f>COUNTIF(C32:L32,"Y")</f>
-        <v/>
-      </c>
-      <c r="O32" s="29">
-        <f>SUMPRODUCT((C$7:$L$7=1)*(C32:L32="Y"))*50</f>
+      <c r="M32" s="33" t="n"/>
+      <c r="N32" s="33" t="n"/>
+      <c r="O32" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$N$7,C32:N32,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="P32" s="28">
+        <f>COUNTIF(C32:N32,"Y")</f>
+        <v/>
+      </c>
+      <c r="Q32" s="29">
+        <f>SUMPRODUCT((C$7:$N$7=1)*(C32:N32="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8495,16 +8607,22 @@
         </is>
       </c>
       <c r="L33" s="19" t="n"/>
-      <c r="M33" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C33:L33,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="N33" s="28">
-        <f>COUNTIF(C33:L33,"Y")</f>
-        <v/>
-      </c>
-      <c r="O33" s="29">
-        <f>SUMPRODUCT((C$7:$L$7=1)*(C33:L33="Y"))*50</f>
+      <c r="M33" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N33" s="19" t="n"/>
+      <c r="O33" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$N$7,C33:N33,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="P33" s="28">
+        <f>COUNTIF(C33:N33,"Y")</f>
+        <v/>
+      </c>
+      <c r="Q33" s="29">
+        <f>SUMPRODUCT((C$7:$N$7=1)*(C33:N33="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8535,16 +8653,18 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M34" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C34:L34,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="N34" s="28">
-        <f>COUNTIF(C34:L34,"Y")</f>
-        <v/>
-      </c>
-      <c r="O34" s="29">
-        <f>SUMPRODUCT((C$7:$L$7=1)*(C34:L34="Y"))*50</f>
+      <c r="M34" s="33" t="n"/>
+      <c r="N34" s="33" t="n"/>
+      <c r="O34" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$N$7,C34:N34,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="P34" s="28">
+        <f>COUNTIF(C34:N34,"Y")</f>
+        <v/>
+      </c>
+      <c r="Q34" s="29">
+        <f>SUMPRODUCT((C$7:$N$7=1)*(C34:N34="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8567,16 +8687,18 @@
       <c r="J35" s="19" t="n"/>
       <c r="K35" s="19" t="n"/>
       <c r="L35" s="19" t="n"/>
-      <c r="M35" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C35:L35,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="N35" s="28">
-        <f>COUNTIF(C35:L35,"Y")</f>
-        <v/>
-      </c>
-      <c r="O35" s="29">
-        <f>SUMPRODUCT((C$7:$L$7=1)*(C35:L35="Y"))*50</f>
+      <c r="M35" s="19" t="n"/>
+      <c r="N35" s="19" t="n"/>
+      <c r="O35" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$N$7,C35:N35,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="P35" s="28">
+        <f>COUNTIF(C35:N35,"Y")</f>
+        <v/>
+      </c>
+      <c r="Q35" s="29">
+        <f>SUMPRODUCT((C$7:$N$7=1)*(C35:N35="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8599,16 +8721,22 @@
       <c r="J36" s="33" t="n"/>
       <c r="K36" s="33" t="n"/>
       <c r="L36" s="33" t="n"/>
-      <c r="M36" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C36:L36,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="N36" s="28">
-        <f>COUNTIF(C36:L36,"Y")</f>
-        <v/>
-      </c>
-      <c r="O36" s="29">
-        <f>SUMPRODUCT((C$7:$L$7=1)*(C36:L36="Y"))*50</f>
+      <c r="M36" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N36" s="33" t="n"/>
+      <c r="O36" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$N$7,C36:N36,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="P36" s="28">
+        <f>COUNTIF(C36:N36,"Y")</f>
+        <v/>
+      </c>
+      <c r="Q36" s="29">
+        <f>SUMPRODUCT((C$7:$N$7=1)*(C36:N36="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8643,16 +8771,18 @@
       <c r="J37" s="19" t="n"/>
       <c r="K37" s="19" t="n"/>
       <c r="L37" s="19" t="n"/>
-      <c r="M37" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C37:L37,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="N37" s="28">
-        <f>COUNTIF(C37:L37,"Y")</f>
-        <v/>
-      </c>
-      <c r="O37" s="29">
-        <f>SUMPRODUCT((C$7:$L$7=1)*(C37:L37="Y"))*50</f>
+      <c r="M37" s="19" t="n"/>
+      <c r="N37" s="19" t="n"/>
+      <c r="O37" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$N$7,C37:N37,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="P37" s="28">
+        <f>COUNTIF(C37:N37,"Y")</f>
+        <v/>
+      </c>
+      <c r="Q37" s="29">
+        <f>SUMPRODUCT((C$7:$N$7=1)*(C37:N37="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8675,16 +8805,18 @@
       <c r="J38" s="33" t="n"/>
       <c r="K38" s="33" t="n"/>
       <c r="L38" s="33" t="n"/>
-      <c r="M38" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$L$7,C38:L38,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="N38" s="28">
-        <f>COUNTIF(C38:L38,"Y")</f>
-        <v/>
-      </c>
-      <c r="O38" s="29">
-        <f>SUMPRODUCT((C$7:$L$7=1)*(C38:L38="Y"))*50</f>
+      <c r="M38" s="33" t="n"/>
+      <c r="N38" s="33" t="n"/>
+      <c r="O38" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$N$7,C38:N38,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="P38" s="28">
+        <f>COUNTIF(C38:N38,"Y")</f>
+        <v/>
+      </c>
+      <c r="Q38" s="29">
+        <f>SUMPRODUCT((C$7:$N$7=1)*(C38:N38="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8735,13 +8867,21 @@
         <f>COUNTIF(L14:L38,"Y")</f>
         <v/>
       </c>
-      <c r="M39" s="3" t="inlineStr"/>
+      <c r="M39" s="6">
+        <f>COUNTIF(M14:M38,"Y")</f>
+        <v/>
+      </c>
       <c r="N39" s="6">
-        <f>SUM(N14:N38)</f>
-        <v/>
-      </c>
-      <c r="O39" s="37">
-        <f>SUM(O14:O38)</f>
+        <f>COUNTIF(N14:N38,"Y")</f>
+        <v/>
+      </c>
+      <c r="O39" s="3" t="inlineStr"/>
+      <c r="P39" s="6">
+        <f>SUM(P14:P38)</f>
+        <v/>
+      </c>
+      <c r="Q39" s="37">
+        <f>SUM(Q14:Q38)</f>
         <v/>
       </c>
     </row>
@@ -8754,13 +8894,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A12:O12"/>
-    <mergeCell ref="A2:O2"/>
-    <mergeCell ref="A13:O13"/>
-    <mergeCell ref="A19:O19"/>
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A40:O40"/>
-    <mergeCell ref="A18:O18"/>
+    <mergeCell ref="A40:Q40"/>
+    <mergeCell ref="A18:Q18"/>
+    <mergeCell ref="A12:Q12"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A19:Q19"/>
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A13:Q13"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Shop_Tracker_2065_2026.xlsx
+++ b/Shop_Tracker_2065_2026.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="January" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="February" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="March" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="April" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="May" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="January" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="February" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="March" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="April" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="May" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/Shop_Tracker_2065_2026.xlsx
+++ b/Shop_Tracker_2065_2026.xlsx
@@ -7438,7 +7438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q40"/>
+  <dimension ref="A1:R40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -7455,9 +7455,10 @@
     <col width="7" customWidth="1" min="12" max="12"/>
     <col width="7" customWidth="1" min="13" max="13"/>
     <col width="7" customWidth="1" min="14" max="14"/>
-    <col width="9" customWidth="1" min="15" max="15"/>
-    <col width="7" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="7" customWidth="1" min="15" max="15"/>
+    <col width="9" customWidth="1" min="16" max="16"/>
+    <col width="7" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -7470,7 +7471,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Five Guys Store 2065 · Louisville, KY · 12 shops · Source: Marketforce + CrunchTime</t>
+          <t>Five Guys Store 2065 · Louisville, KY · 13 shops · Source: Marketforce + CrunchTime</t>
         </is>
       </c>
     </row>
@@ -7542,17 +7543,22 @@
           <t>#12</t>
         </is>
       </c>
-      <c r="O4" s="6" t="inlineStr">
+      <c r="O4" s="5" t="inlineStr">
+        <is>
+          <t>#13</t>
+        </is>
+      </c>
+      <c r="P4" s="6" t="inlineStr">
         <is>
           <t>AVG</t>
         </is>
       </c>
-      <c r="P4" s="6" t="inlineStr">
+      <c r="Q4" s="6" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="Q4" s="6" t="inlineStr">
+      <c r="R4" s="6" t="inlineStr">
         <is>
           <t>BONUS</t>
         </is>
@@ -7625,9 +7631,14 @@
           <t>05/16</t>
         </is>
       </c>
-      <c r="O5" s="7" t="inlineStr"/>
+      <c r="O5" s="9" t="inlineStr">
+        <is>
+          <t>05/26</t>
+        </is>
+      </c>
       <c r="P5" s="7" t="inlineStr"/>
       <c r="Q5" s="7" t="inlineStr"/>
+      <c r="R5" s="7" t="inlineStr"/>
     </row>
     <row r="6" ht="14" customHeight="1">
       <c r="A6" s="7" t="inlineStr"/>
@@ -7696,9 +7707,14 @@
           <t>D</t>
         </is>
       </c>
-      <c r="O6" s="7" t="inlineStr"/>
+      <c r="O6" s="11" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="P6" s="7" t="inlineStr"/>
       <c r="Q6" s="7" t="inlineStr"/>
+      <c r="R6" s="7" t="inlineStr"/>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="12" t="inlineStr"/>
@@ -7743,12 +7759,15 @@
       <c r="N7" s="16" t="n">
         <v>0.75</v>
       </c>
-      <c r="O7" s="18">
-        <f>IFERROR(AVERAGE(C7:N7),"")</f>
-        <v/>
-      </c>
-      <c r="P7" s="12" t="inlineStr"/>
+      <c r="O7" s="16" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P7" s="18">
+        <f>IFERROR(AVERAGE(C7:O7),"")</f>
+        <v/>
+      </c>
       <c r="Q7" s="12" t="inlineStr"/>
+      <c r="R7" s="12" t="inlineStr"/>
     </row>
     <row r="8" ht="13" customHeight="1">
       <c r="A8" s="19" t="inlineStr"/>
@@ -7769,12 +7788,13 @@
       <c r="L8" s="19" t="inlineStr"/>
       <c r="M8" s="19" t="inlineStr"/>
       <c r="N8" s="19" t="inlineStr"/>
-      <c r="O8" s="21">
-        <f>IFERROR(AVERAGE(C8:N8),"")</f>
-        <v/>
-      </c>
-      <c r="P8" s="19" t="inlineStr"/>
+      <c r="O8" s="19" t="inlineStr"/>
+      <c r="P8" s="21">
+        <f>IFERROR(AVERAGE(C8:O8),"")</f>
+        <v/>
+      </c>
       <c r="Q8" s="19" t="inlineStr"/>
+      <c r="R8" s="19" t="inlineStr"/>
     </row>
     <row r="9" ht="13" customHeight="1">
       <c r="A9" s="19" t="inlineStr"/>
@@ -7795,12 +7815,13 @@
       <c r="L9" s="19" t="inlineStr"/>
       <c r="M9" s="19" t="inlineStr"/>
       <c r="N9" s="19" t="inlineStr"/>
-      <c r="O9" s="21">
-        <f>IFERROR(AVERAGE(C9:N9),"")</f>
-        <v/>
-      </c>
-      <c r="P9" s="19" t="inlineStr"/>
+      <c r="O9" s="19" t="inlineStr"/>
+      <c r="P9" s="21">
+        <f>IFERROR(AVERAGE(C9:O9),"")</f>
+        <v/>
+      </c>
       <c r="Q9" s="19" t="inlineStr"/>
+      <c r="R9" s="19" t="inlineStr"/>
     </row>
     <row r="10" ht="13" customHeight="1">
       <c r="A10" s="19" t="inlineStr"/>
@@ -7821,12 +7842,13 @@
       <c r="L10" s="19" t="inlineStr"/>
       <c r="M10" s="19" t="inlineStr"/>
       <c r="N10" s="19" t="inlineStr"/>
-      <c r="O10" s="21">
-        <f>IFERROR(AVERAGE(C10:N10),"")</f>
-        <v/>
-      </c>
-      <c r="P10" s="19" t="inlineStr"/>
+      <c r="O10" s="19" t="inlineStr"/>
+      <c r="P10" s="21">
+        <f>IFERROR(AVERAGE(C10:O10),"")</f>
+        <v/>
+      </c>
       <c r="Q10" s="19" t="inlineStr"/>
+      <c r="R10" s="19" t="inlineStr"/>
     </row>
     <row r="11" ht="13" customHeight="1">
       <c r="A11" s="19" t="inlineStr"/>
@@ -7847,12 +7869,13 @@
       <c r="L11" s="19" t="inlineStr"/>
       <c r="M11" s="19" t="inlineStr"/>
       <c r="N11" s="19" t="inlineStr"/>
-      <c r="O11" s="21">
-        <f>IFERROR(AVERAGE(C11:N11),"")</f>
-        <v/>
-      </c>
-      <c r="P11" s="19" t="inlineStr"/>
+      <c r="O11" s="19" t="inlineStr"/>
+      <c r="P11" s="21">
+        <f>IFERROR(AVERAGE(C11:O11),"")</f>
+        <v/>
+      </c>
       <c r="Q11" s="19" t="inlineStr"/>
+      <c r="R11" s="19" t="inlineStr"/>
     </row>
     <row r="12" ht="6" customHeight="1">
       <c r="A12" s="22" t="n"/>
@@ -7925,16 +7948,21 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="O14" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$N$7,C14:N14,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="P14" s="28">
-        <f>COUNTIF(C14:N14,"Y")</f>
-        <v/>
-      </c>
-      <c r="Q14" s="29">
-        <f>SUMPRODUCT((C$7:$N$7=1)*(C14:N14="Y"))*50</f>
+      <c r="O14" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P14" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$O$7,C14:O14,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="Q14" s="28">
+        <f>COUNTIF(C14:O14,"Y")</f>
+        <v/>
+      </c>
+      <c r="R14" s="29">
+        <f>SUMPRODUCT((C$7:$O$7=1)*(C14:O14="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -7967,16 +7995,21 @@
         </is>
       </c>
       <c r="N15" s="27" t="n"/>
-      <c r="O15" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$N$7,C15:N15,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="P15" s="28">
-        <f>COUNTIF(C15:N15,"Y")</f>
-        <v/>
-      </c>
-      <c r="Q15" s="29">
-        <f>SUMPRODUCT((C$7:$N$7=1)*(C15:N15="Y"))*50</f>
+      <c r="O15" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P15" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$O$7,C15:O15,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="Q15" s="28">
+        <f>COUNTIF(C15:O15,"Y")</f>
+        <v/>
+      </c>
+      <c r="R15" s="29">
+        <f>SUMPRODUCT((C$7:$O$7=1)*(C15:O15="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8001,16 +8034,17 @@
       <c r="L16" s="27" t="n"/>
       <c r="M16" s="27" t="n"/>
       <c r="N16" s="27" t="n"/>
-      <c r="O16" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$N$7,C16:N16,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="P16" s="28">
-        <f>COUNTIF(C16:N16,"Y")</f>
-        <v/>
-      </c>
-      <c r="Q16" s="29">
-        <f>SUMPRODUCT((C$7:$N$7=1)*(C16:N16="Y"))*50</f>
+      <c r="O16" s="27" t="n"/>
+      <c r="P16" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$O$7,C16:O16,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="Q16" s="28">
+        <f>COUNTIF(C16:O16,"Y")</f>
+        <v/>
+      </c>
+      <c r="R16" s="29">
+        <f>SUMPRODUCT((C$7:$O$7=1)*(C16:O16="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8039,16 +8073,17 @@
         </is>
       </c>
       <c r="N17" s="27" t="n"/>
-      <c r="O17" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$N$7,C17:N17,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="P17" s="28">
-        <f>COUNTIF(C17:N17,"Y")</f>
-        <v/>
-      </c>
-      <c r="Q17" s="29">
-        <f>SUMPRODUCT((C$7:$N$7=1)*(C17:N17="Y"))*50</f>
+      <c r="O17" s="27" t="n"/>
+      <c r="P17" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$O$7,C17:O17,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="Q17" s="28">
+        <f>COUNTIF(C17:O17,"Y")</f>
+        <v/>
+      </c>
+      <c r="R17" s="29">
+        <f>SUMPRODUCT((C$7:$O$7=1)*(C17:O17="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8083,16 +8118,17 @@
       <c r="L20" s="33" t="n"/>
       <c r="M20" s="33" t="n"/>
       <c r="N20" s="33" t="n"/>
-      <c r="O20" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$N$7,C20:N20,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="P20" s="28">
-        <f>COUNTIF(C20:N20,"Y")</f>
-        <v/>
-      </c>
-      <c r="Q20" s="29">
-        <f>SUMPRODUCT((C$7:$N$7=1)*(C20:N20="Y"))*50</f>
+      <c r="O20" s="33" t="n"/>
+      <c r="P20" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$O$7,C20:O20,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="Q20" s="28">
+        <f>COUNTIF(C20:O20,"Y")</f>
+        <v/>
+      </c>
+      <c r="R20" s="29">
+        <f>SUMPRODUCT((C$7:$O$7=1)*(C20:O20="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8117,16 +8153,17 @@
       <c r="L21" s="19" t="n"/>
       <c r="M21" s="19" t="n"/>
       <c r="N21" s="19" t="n"/>
-      <c r="O21" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$N$7,C21:N21,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="P21" s="28">
-        <f>COUNTIF(C21:N21,"Y")</f>
-        <v/>
-      </c>
-      <c r="Q21" s="29">
-        <f>SUMPRODUCT((C$7:$N$7=1)*(C21:N21="Y"))*50</f>
+      <c r="O21" s="19" t="n"/>
+      <c r="P21" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$O$7,C21:O21,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="Q21" s="28">
+        <f>COUNTIF(C21:O21,"Y")</f>
+        <v/>
+      </c>
+      <c r="R21" s="29">
+        <f>SUMPRODUCT((C$7:$O$7=1)*(C21:O21="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8159,16 +8196,17 @@
       <c r="L22" s="33" t="n"/>
       <c r="M22" s="33" t="n"/>
       <c r="N22" s="33" t="n"/>
-      <c r="O22" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$N$7,C22:N22,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="P22" s="28">
-        <f>COUNTIF(C22:N22,"Y")</f>
-        <v/>
-      </c>
-      <c r="Q22" s="29">
-        <f>SUMPRODUCT((C$7:$N$7=1)*(C22:N22="Y"))*50</f>
+      <c r="O22" s="33" t="n"/>
+      <c r="P22" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$O$7,C22:O22,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="Q22" s="28">
+        <f>COUNTIF(C22:O22,"Y")</f>
+        <v/>
+      </c>
+      <c r="R22" s="29">
+        <f>SUMPRODUCT((C$7:$O$7=1)*(C22:O22="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8197,16 +8235,17 @@
       </c>
       <c r="M23" s="19" t="n"/>
       <c r="N23" s="19" t="n"/>
-      <c r="O23" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$N$7,C23:N23,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="P23" s="28">
-        <f>COUNTIF(C23:N23,"Y")</f>
-        <v/>
-      </c>
-      <c r="Q23" s="29">
-        <f>SUMPRODUCT((C$7:$N$7=1)*(C23:N23="Y"))*50</f>
+      <c r="O23" s="19" t="n"/>
+      <c r="P23" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$O$7,C23:O23,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="Q23" s="28">
+        <f>COUNTIF(C23:O23,"Y")</f>
+        <v/>
+      </c>
+      <c r="R23" s="29">
+        <f>SUMPRODUCT((C$7:$O$7=1)*(C23:O23="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8235,16 +8274,17 @@
       </c>
       <c r="M24" s="33" t="n"/>
       <c r="N24" s="33" t="n"/>
-      <c r="O24" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$N$7,C24:N24,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="P24" s="28">
-        <f>COUNTIF(C24:N24,"Y")</f>
-        <v/>
-      </c>
-      <c r="Q24" s="29">
-        <f>SUMPRODUCT((C$7:$N$7=1)*(C24:N24="Y"))*50</f>
+      <c r="O24" s="33" t="n"/>
+      <c r="P24" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$O$7,C24:O24,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="Q24" s="28">
+        <f>COUNTIF(C24:O24,"Y")</f>
+        <v/>
+      </c>
+      <c r="R24" s="29">
+        <f>SUMPRODUCT((C$7:$O$7=1)*(C24:O24="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8269,16 +8309,17 @@
       <c r="L25" s="19" t="n"/>
       <c r="M25" s="19" t="n"/>
       <c r="N25" s="19" t="n"/>
-      <c r="O25" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$N$7,C25:N25,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="P25" s="28">
-        <f>COUNTIF(C25:N25,"Y")</f>
-        <v/>
-      </c>
-      <c r="Q25" s="29">
-        <f>SUMPRODUCT((C$7:$N$7=1)*(C25:N25="Y"))*50</f>
+      <c r="O25" s="19" t="n"/>
+      <c r="P25" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$O$7,C25:O25,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="Q25" s="28">
+        <f>COUNTIF(C25:O25,"Y")</f>
+        <v/>
+      </c>
+      <c r="R25" s="29">
+        <f>SUMPRODUCT((C$7:$O$7=1)*(C25:O25="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8319,16 +8360,21 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="O26" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$N$7,C26:N26,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="P26" s="28">
-        <f>COUNTIF(C26:N26,"Y")</f>
-        <v/>
-      </c>
-      <c r="Q26" s="29">
-        <f>SUMPRODUCT((C$7:$N$7=1)*(C26:N26="Y"))*50</f>
+      <c r="O26" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P26" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$O$7,C26:O26,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="Q26" s="28">
+        <f>COUNTIF(C26:O26,"Y")</f>
+        <v/>
+      </c>
+      <c r="R26" s="29">
+        <f>SUMPRODUCT((C$7:$O$7=1)*(C26:O26="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8353,16 +8399,17 @@
       <c r="L27" s="19" t="n"/>
       <c r="M27" s="19" t="n"/>
       <c r="N27" s="19" t="n"/>
-      <c r="O27" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$N$7,C27:N27,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="P27" s="28">
-        <f>COUNTIF(C27:N27,"Y")</f>
-        <v/>
-      </c>
-      <c r="Q27" s="29">
-        <f>SUMPRODUCT((C$7:$N$7=1)*(C27:N27="Y"))*50</f>
+      <c r="O27" s="19" t="n"/>
+      <c r="P27" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$O$7,C27:O27,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="Q27" s="28">
+        <f>COUNTIF(C27:O27,"Y")</f>
+        <v/>
+      </c>
+      <c r="R27" s="29">
+        <f>SUMPRODUCT((C$7:$O$7=1)*(C27:O27="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8391,16 +8438,17 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="O28" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$N$7,C28:N28,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="P28" s="28">
-        <f>COUNTIF(C28:N28,"Y")</f>
-        <v/>
-      </c>
-      <c r="Q28" s="29">
-        <f>SUMPRODUCT((C$7:$N$7=1)*(C28:N28="Y"))*50</f>
+      <c r="O28" s="33" t="n"/>
+      <c r="P28" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$O$7,C28:O28,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="Q28" s="28">
+        <f>COUNTIF(C28:O28,"Y")</f>
+        <v/>
+      </c>
+      <c r="R28" s="29">
+        <f>SUMPRODUCT((C$7:$O$7=1)*(C28:O28="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8461,16 +8509,17 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="O29" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$N$7,C29:N29,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="P29" s="28">
-        <f>COUNTIF(C29:N29,"Y")</f>
-        <v/>
-      </c>
-      <c r="Q29" s="29">
-        <f>SUMPRODUCT((C$7:$N$7=1)*(C29:N29="Y"))*50</f>
+      <c r="O29" s="19" t="n"/>
+      <c r="P29" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$O$7,C29:O29,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="Q29" s="28">
+        <f>COUNTIF(C29:O29,"Y")</f>
+        <v/>
+      </c>
+      <c r="R29" s="29">
+        <f>SUMPRODUCT((C$7:$O$7=1)*(C29:O29="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8495,16 +8544,17 @@
       <c r="L30" s="33" t="n"/>
       <c r="M30" s="33" t="n"/>
       <c r="N30" s="33" t="n"/>
-      <c r="O30" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$N$7,C30:N30,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="P30" s="28">
-        <f>COUNTIF(C30:N30,"Y")</f>
-        <v/>
-      </c>
-      <c r="Q30" s="29">
-        <f>SUMPRODUCT((C$7:$N$7=1)*(C30:N30="Y"))*50</f>
+      <c r="O30" s="33" t="n"/>
+      <c r="P30" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$O$7,C30:O30,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="Q30" s="28">
+        <f>COUNTIF(C30:O30,"Y")</f>
+        <v/>
+      </c>
+      <c r="R30" s="29">
+        <f>SUMPRODUCT((C$7:$O$7=1)*(C30:O30="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8529,16 +8579,17 @@
       <c r="L31" s="19" t="n"/>
       <c r="M31" s="19" t="n"/>
       <c r="N31" s="19" t="n"/>
-      <c r="O31" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$N$7,C31:N31,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="P31" s="28">
-        <f>COUNTIF(C31:N31,"Y")</f>
-        <v/>
-      </c>
-      <c r="Q31" s="29">
-        <f>SUMPRODUCT((C$7:$N$7=1)*(C31:N31="Y"))*50</f>
+      <c r="O31" s="19" t="n"/>
+      <c r="P31" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$O$7,C31:O31,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="Q31" s="28">
+        <f>COUNTIF(C31:O31,"Y")</f>
+        <v/>
+      </c>
+      <c r="R31" s="29">
+        <f>SUMPRODUCT((C$7:$O$7=1)*(C31:O31="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8563,16 +8614,17 @@
       <c r="L32" s="33" t="n"/>
       <c r="M32" s="33" t="n"/>
       <c r="N32" s="33" t="n"/>
-      <c r="O32" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$N$7,C32:N32,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="P32" s="28">
-        <f>COUNTIF(C32:N32,"Y")</f>
-        <v/>
-      </c>
-      <c r="Q32" s="29">
-        <f>SUMPRODUCT((C$7:$N$7=1)*(C32:N32="Y"))*50</f>
+      <c r="O32" s="33" t="n"/>
+      <c r="P32" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$O$7,C32:O32,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="Q32" s="28">
+        <f>COUNTIF(C32:O32,"Y")</f>
+        <v/>
+      </c>
+      <c r="R32" s="29">
+        <f>SUMPRODUCT((C$7:$O$7=1)*(C32:O32="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8613,16 +8665,21 @@
         </is>
       </c>
       <c r="N33" s="19" t="n"/>
-      <c r="O33" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$N$7,C33:N33,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="P33" s="28">
-        <f>COUNTIF(C33:N33,"Y")</f>
-        <v/>
-      </c>
-      <c r="Q33" s="29">
-        <f>SUMPRODUCT((C$7:$N$7=1)*(C33:N33="Y"))*50</f>
+      <c r="O33" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P33" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$O$7,C33:O33,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="Q33" s="28">
+        <f>COUNTIF(C33:O33,"Y")</f>
+        <v/>
+      </c>
+      <c r="R33" s="29">
+        <f>SUMPRODUCT((C$7:$O$7=1)*(C33:O33="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8655,16 +8712,21 @@
       </c>
       <c r="M34" s="33" t="n"/>
       <c r="N34" s="33" t="n"/>
-      <c r="O34" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$N$7,C34:N34,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="P34" s="28">
-        <f>COUNTIF(C34:N34,"Y")</f>
-        <v/>
-      </c>
-      <c r="Q34" s="29">
-        <f>SUMPRODUCT((C$7:$N$7=1)*(C34:N34="Y"))*50</f>
+      <c r="O34" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P34" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$O$7,C34:O34,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="Q34" s="28">
+        <f>COUNTIF(C34:O34,"Y")</f>
+        <v/>
+      </c>
+      <c r="R34" s="29">
+        <f>SUMPRODUCT((C$7:$O$7=1)*(C34:O34="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8689,16 +8751,17 @@
       <c r="L35" s="19" t="n"/>
       <c r="M35" s="19" t="n"/>
       <c r="N35" s="19" t="n"/>
-      <c r="O35" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$N$7,C35:N35,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="P35" s="28">
-        <f>COUNTIF(C35:N35,"Y")</f>
-        <v/>
-      </c>
-      <c r="Q35" s="29">
-        <f>SUMPRODUCT((C$7:$N$7=1)*(C35:N35="Y"))*50</f>
+      <c r="O35" s="19" t="n"/>
+      <c r="P35" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$O$7,C35:O35,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="Q35" s="28">
+        <f>COUNTIF(C35:O35,"Y")</f>
+        <v/>
+      </c>
+      <c r="R35" s="29">
+        <f>SUMPRODUCT((C$7:$O$7=1)*(C35:O35="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8727,16 +8790,17 @@
         </is>
       </c>
       <c r="N36" s="33" t="n"/>
-      <c r="O36" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$N$7,C36:N36,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="P36" s="28">
-        <f>COUNTIF(C36:N36,"Y")</f>
-        <v/>
-      </c>
-      <c r="Q36" s="29">
-        <f>SUMPRODUCT((C$7:$N$7=1)*(C36:N36="Y"))*50</f>
+      <c r="O36" s="33" t="n"/>
+      <c r="P36" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$O$7,C36:O36,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="Q36" s="28">
+        <f>COUNTIF(C36:O36,"Y")</f>
+        <v/>
+      </c>
+      <c r="R36" s="29">
+        <f>SUMPRODUCT((C$7:$O$7=1)*(C36:O36="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8773,16 +8837,17 @@
       <c r="L37" s="19" t="n"/>
       <c r="M37" s="19" t="n"/>
       <c r="N37" s="19" t="n"/>
-      <c r="O37" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$N$7,C37:N37,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="P37" s="28">
-        <f>COUNTIF(C37:N37,"Y")</f>
-        <v/>
-      </c>
-      <c r="Q37" s="29">
-        <f>SUMPRODUCT((C$7:$N$7=1)*(C37:N37="Y"))*50</f>
+      <c r="O37" s="19" t="n"/>
+      <c r="P37" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$O$7,C37:O37,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="Q37" s="28">
+        <f>COUNTIF(C37:O37,"Y")</f>
+        <v/>
+      </c>
+      <c r="R37" s="29">
+        <f>SUMPRODUCT((C$7:$O$7=1)*(C37:O37="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8807,16 +8872,17 @@
       <c r="L38" s="33" t="n"/>
       <c r="M38" s="33" t="n"/>
       <c r="N38" s="33" t="n"/>
-      <c r="O38" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$N$7,C38:N38,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="P38" s="28">
-        <f>COUNTIF(C38:N38,"Y")</f>
-        <v/>
-      </c>
-      <c r="Q38" s="29">
-        <f>SUMPRODUCT((C$7:$N$7=1)*(C38:N38="Y"))*50</f>
+      <c r="O38" s="33" t="n"/>
+      <c r="P38" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$O$7,C38:O38,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="Q38" s="28">
+        <f>COUNTIF(C38:O38,"Y")</f>
+        <v/>
+      </c>
+      <c r="R38" s="29">
+        <f>SUMPRODUCT((C$7:$O$7=1)*(C38:O38="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8875,13 +8941,17 @@
         <f>COUNTIF(N14:N38,"Y")</f>
         <v/>
       </c>
-      <c r="O39" s="3" t="inlineStr"/>
-      <c r="P39" s="6">
-        <f>SUM(P14:P38)</f>
-        <v/>
-      </c>
-      <c r="Q39" s="37">
+      <c r="O39" s="6">
+        <f>COUNTIF(O14:O38,"Y")</f>
+        <v/>
+      </c>
+      <c r="P39" s="3" t="inlineStr"/>
+      <c r="Q39" s="6">
         <f>SUM(Q14:Q38)</f>
+        <v/>
+      </c>
+      <c r="R39" s="37">
+        <f>SUM(R14:R38)</f>
         <v/>
       </c>
     </row>
@@ -8894,13 +8964,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A40:Q40"/>
-    <mergeCell ref="A18:Q18"/>
-    <mergeCell ref="A12:Q12"/>
-    <mergeCell ref="A2:Q2"/>
-    <mergeCell ref="A19:Q19"/>
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="A13:Q13"/>
+    <mergeCell ref="A18:R18"/>
+    <mergeCell ref="A2:R2"/>
+    <mergeCell ref="A19:R19"/>
+    <mergeCell ref="A13:R13"/>
+    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A40:R40"/>
+    <mergeCell ref="A12:R12"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Shop_Tracker_2065_2026.xlsx
+++ b/Shop_Tracker_2065_2026.xlsx
@@ -7438,7 +7438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R40"/>
+  <dimension ref="A1:S40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -7456,9 +7456,10 @@
     <col width="7" customWidth="1" min="13" max="13"/>
     <col width="7" customWidth="1" min="14" max="14"/>
     <col width="7" customWidth="1" min="15" max="15"/>
-    <col width="9" customWidth="1" min="16" max="16"/>
-    <col width="7" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="7" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="7" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -7471,7 +7472,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Five Guys Store 2065 · Louisville, KY · 13 shops · Source: Marketforce + CrunchTime</t>
+          <t>Five Guys Store 2065 · Louisville, KY · 14 shops · Source: Marketforce + CrunchTime</t>
         </is>
       </c>
     </row>
@@ -7548,17 +7549,22 @@
           <t>#13</t>
         </is>
       </c>
-      <c r="P4" s="6" t="inlineStr">
+      <c r="P4" s="5" t="inlineStr">
+        <is>
+          <t>#14</t>
+        </is>
+      </c>
+      <c r="Q4" s="6" t="inlineStr">
         <is>
           <t>AVG</t>
         </is>
       </c>
-      <c r="Q4" s="6" t="inlineStr">
+      <c r="R4" s="6" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R4" s="6" t="inlineStr">
+      <c r="S4" s="6" t="inlineStr">
         <is>
           <t>BONUS</t>
         </is>
@@ -7636,9 +7642,14 @@
           <t>05/26</t>
         </is>
       </c>
-      <c r="P5" s="7" t="inlineStr"/>
+      <c r="P5" s="9" t="inlineStr">
+        <is>
+          <t>05/31</t>
+        </is>
+      </c>
       <c r="Q5" s="7" t="inlineStr"/>
       <c r="R5" s="7" t="inlineStr"/>
+      <c r="S5" s="7" t="inlineStr"/>
     </row>
     <row r="6" ht="14" customHeight="1">
       <c r="A6" s="7" t="inlineStr"/>
@@ -7712,9 +7723,14 @@
           <t>L</t>
         </is>
       </c>
-      <c r="P6" s="7" t="inlineStr"/>
+      <c r="P6" s="10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="Q6" s="7" t="inlineStr"/>
       <c r="R6" s="7" t="inlineStr"/>
+      <c r="S6" s="7" t="inlineStr"/>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="12" t="inlineStr"/>
@@ -7762,12 +7778,15 @@
       <c r="O7" s="16" t="n">
         <v>0.6</v>
       </c>
-      <c r="P7" s="18">
-        <f>IFERROR(AVERAGE(C7:O7),"")</f>
-        <v/>
-      </c>
-      <c r="Q7" s="12" t="inlineStr"/>
+      <c r="P7" s="17" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="Q7" s="18">
+        <f>IFERROR(AVERAGE(C7:P7),"")</f>
+        <v/>
+      </c>
       <c r="R7" s="12" t="inlineStr"/>
+      <c r="S7" s="12" t="inlineStr"/>
     </row>
     <row r="8" ht="13" customHeight="1">
       <c r="A8" s="19" t="inlineStr"/>
@@ -7789,12 +7808,13 @@
       <c r="M8" s="19" t="inlineStr"/>
       <c r="N8" s="19" t="inlineStr"/>
       <c r="O8" s="19" t="inlineStr"/>
-      <c r="P8" s="21">
-        <f>IFERROR(AVERAGE(C8:O8),"")</f>
-        <v/>
-      </c>
-      <c r="Q8" s="19" t="inlineStr"/>
+      <c r="P8" s="19" t="inlineStr"/>
+      <c r="Q8" s="21">
+        <f>IFERROR(AVERAGE(C8:P8),"")</f>
+        <v/>
+      </c>
       <c r="R8" s="19" t="inlineStr"/>
+      <c r="S8" s="19" t="inlineStr"/>
     </row>
     <row r="9" ht="13" customHeight="1">
       <c r="A9" s="19" t="inlineStr"/>
@@ -7816,12 +7836,13 @@
       <c r="M9" s="19" t="inlineStr"/>
       <c r="N9" s="19" t="inlineStr"/>
       <c r="O9" s="19" t="inlineStr"/>
-      <c r="P9" s="21">
-        <f>IFERROR(AVERAGE(C9:O9),"")</f>
-        <v/>
-      </c>
-      <c r="Q9" s="19" t="inlineStr"/>
+      <c r="P9" s="19" t="inlineStr"/>
+      <c r="Q9" s="21">
+        <f>IFERROR(AVERAGE(C9:P9),"")</f>
+        <v/>
+      </c>
       <c r="R9" s="19" t="inlineStr"/>
+      <c r="S9" s="19" t="inlineStr"/>
     </row>
     <row r="10" ht="13" customHeight="1">
       <c r="A10" s="19" t="inlineStr"/>
@@ -7843,12 +7864,13 @@
       <c r="M10" s="19" t="inlineStr"/>
       <c r="N10" s="19" t="inlineStr"/>
       <c r="O10" s="19" t="inlineStr"/>
-      <c r="P10" s="21">
-        <f>IFERROR(AVERAGE(C10:O10),"")</f>
-        <v/>
-      </c>
-      <c r="Q10" s="19" t="inlineStr"/>
+      <c r="P10" s="19" t="inlineStr"/>
+      <c r="Q10" s="21">
+        <f>IFERROR(AVERAGE(C10:P10),"")</f>
+        <v/>
+      </c>
       <c r="R10" s="19" t="inlineStr"/>
+      <c r="S10" s="19" t="inlineStr"/>
     </row>
     <row r="11" ht="13" customHeight="1">
       <c r="A11" s="19" t="inlineStr"/>
@@ -7870,12 +7892,13 @@
       <c r="M11" s="19" t="inlineStr"/>
       <c r="N11" s="19" t="inlineStr"/>
       <c r="O11" s="19" t="inlineStr"/>
-      <c r="P11" s="21">
-        <f>IFERROR(AVERAGE(C11:O11),"")</f>
-        <v/>
-      </c>
-      <c r="Q11" s="19" t="inlineStr"/>
+      <c r="P11" s="19" t="inlineStr"/>
+      <c r="Q11" s="21">
+        <f>IFERROR(AVERAGE(C11:P11),"")</f>
+        <v/>
+      </c>
       <c r="R11" s="19" t="inlineStr"/>
+      <c r="S11" s="19" t="inlineStr"/>
     </row>
     <row r="12" ht="6" customHeight="1">
       <c r="A12" s="22" t="n"/>
@@ -7953,16 +7976,17 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="P14" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$O$7,C14:O14,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="Q14" s="28">
-        <f>COUNTIF(C14:O14,"Y")</f>
-        <v/>
-      </c>
-      <c r="R14" s="29">
-        <f>SUMPRODUCT((C$7:$O$7=1)*(C14:O14="Y"))*50</f>
+      <c r="P14" s="27" t="n"/>
+      <c r="Q14" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$P$7,C14:P14,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="R14" s="28">
+        <f>COUNTIF(C14:P14,"Y")</f>
+        <v/>
+      </c>
+      <c r="S14" s="29">
+        <f>SUMPRODUCT((C$7:$P$7=1)*(C14:P14="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8000,16 +8024,17 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="P15" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$O$7,C15:O15,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="Q15" s="28">
-        <f>COUNTIF(C15:O15,"Y")</f>
-        <v/>
-      </c>
-      <c r="R15" s="29">
-        <f>SUMPRODUCT((C$7:$O$7=1)*(C15:O15="Y"))*50</f>
+      <c r="P15" s="27" t="n"/>
+      <c r="Q15" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$P$7,C15:P15,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="R15" s="28">
+        <f>COUNTIF(C15:P15,"Y")</f>
+        <v/>
+      </c>
+      <c r="S15" s="29">
+        <f>SUMPRODUCT((C$7:$P$7=1)*(C15:P15="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8035,16 +8060,17 @@
       <c r="M16" s="27" t="n"/>
       <c r="N16" s="27" t="n"/>
       <c r="O16" s="27" t="n"/>
-      <c r="P16" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$O$7,C16:O16,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="Q16" s="28">
-        <f>COUNTIF(C16:O16,"Y")</f>
-        <v/>
-      </c>
-      <c r="R16" s="29">
-        <f>SUMPRODUCT((C$7:$O$7=1)*(C16:O16="Y"))*50</f>
+      <c r="P16" s="27" t="n"/>
+      <c r="Q16" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$P$7,C16:P16,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="R16" s="28">
+        <f>COUNTIF(C16:P16,"Y")</f>
+        <v/>
+      </c>
+      <c r="S16" s="29">
+        <f>SUMPRODUCT((C$7:$P$7=1)*(C16:P16="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8074,16 +8100,21 @@
       </c>
       <c r="N17" s="27" t="n"/>
       <c r="O17" s="27" t="n"/>
-      <c r="P17" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$O$7,C17:O17,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="Q17" s="28">
-        <f>COUNTIF(C17:O17,"Y")</f>
-        <v/>
-      </c>
-      <c r="R17" s="29">
-        <f>SUMPRODUCT((C$7:$O$7=1)*(C17:O17="Y"))*50</f>
+      <c r="P17" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q17" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$P$7,C17:P17,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="R17" s="28">
+        <f>COUNTIF(C17:P17,"Y")</f>
+        <v/>
+      </c>
+      <c r="S17" s="29">
+        <f>SUMPRODUCT((C$7:$P$7=1)*(C17:P17="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8119,16 +8150,17 @@
       <c r="M20" s="33" t="n"/>
       <c r="N20" s="33" t="n"/>
       <c r="O20" s="33" t="n"/>
-      <c r="P20" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$O$7,C20:O20,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="Q20" s="28">
-        <f>COUNTIF(C20:O20,"Y")</f>
-        <v/>
-      </c>
-      <c r="R20" s="29">
-        <f>SUMPRODUCT((C$7:$O$7=1)*(C20:O20="Y"))*50</f>
+      <c r="P20" s="33" t="n"/>
+      <c r="Q20" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$P$7,C20:P20,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="R20" s="28">
+        <f>COUNTIF(C20:P20,"Y")</f>
+        <v/>
+      </c>
+      <c r="S20" s="29">
+        <f>SUMPRODUCT((C$7:$P$7=1)*(C20:P20="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8154,16 +8186,17 @@
       <c r="M21" s="19" t="n"/>
       <c r="N21" s="19" t="n"/>
       <c r="O21" s="19" t="n"/>
-      <c r="P21" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$O$7,C21:O21,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="Q21" s="28">
-        <f>COUNTIF(C21:O21,"Y")</f>
-        <v/>
-      </c>
-      <c r="R21" s="29">
-        <f>SUMPRODUCT((C$7:$O$7=1)*(C21:O21="Y"))*50</f>
+      <c r="P21" s="19" t="n"/>
+      <c r="Q21" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$P$7,C21:P21,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="R21" s="28">
+        <f>COUNTIF(C21:P21,"Y")</f>
+        <v/>
+      </c>
+      <c r="S21" s="29">
+        <f>SUMPRODUCT((C$7:$P$7=1)*(C21:P21="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8197,16 +8230,21 @@
       <c r="M22" s="33" t="n"/>
       <c r="N22" s="33" t="n"/>
       <c r="O22" s="33" t="n"/>
-      <c r="P22" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$O$7,C22:O22,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="Q22" s="28">
-        <f>COUNTIF(C22:O22,"Y")</f>
-        <v/>
-      </c>
-      <c r="R22" s="29">
-        <f>SUMPRODUCT((C$7:$O$7=1)*(C22:O22="Y"))*50</f>
+      <c r="P22" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q22" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$P$7,C22:P22,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="R22" s="28">
+        <f>COUNTIF(C22:P22,"Y")</f>
+        <v/>
+      </c>
+      <c r="S22" s="29">
+        <f>SUMPRODUCT((C$7:$P$7=1)*(C22:P22="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8236,16 +8274,17 @@
       <c r="M23" s="19" t="n"/>
       <c r="N23" s="19" t="n"/>
       <c r="O23" s="19" t="n"/>
-      <c r="P23" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$O$7,C23:O23,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="Q23" s="28">
-        <f>COUNTIF(C23:O23,"Y")</f>
-        <v/>
-      </c>
-      <c r="R23" s="29">
-        <f>SUMPRODUCT((C$7:$O$7=1)*(C23:O23="Y"))*50</f>
+      <c r="P23" s="19" t="n"/>
+      <c r="Q23" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$P$7,C23:P23,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="R23" s="28">
+        <f>COUNTIF(C23:P23,"Y")</f>
+        <v/>
+      </c>
+      <c r="S23" s="29">
+        <f>SUMPRODUCT((C$7:$P$7=1)*(C23:P23="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8275,16 +8314,17 @@
       <c r="M24" s="33" t="n"/>
       <c r="N24" s="33" t="n"/>
       <c r="O24" s="33" t="n"/>
-      <c r="P24" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$O$7,C24:O24,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="Q24" s="28">
-        <f>COUNTIF(C24:O24,"Y")</f>
-        <v/>
-      </c>
-      <c r="R24" s="29">
-        <f>SUMPRODUCT((C$7:$O$7=1)*(C24:O24="Y"))*50</f>
+      <c r="P24" s="33" t="n"/>
+      <c r="Q24" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$P$7,C24:P24,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="R24" s="28">
+        <f>COUNTIF(C24:P24,"Y")</f>
+        <v/>
+      </c>
+      <c r="S24" s="29">
+        <f>SUMPRODUCT((C$7:$P$7=1)*(C24:P24="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8310,16 +8350,17 @@
       <c r="M25" s="19" t="n"/>
       <c r="N25" s="19" t="n"/>
       <c r="O25" s="19" t="n"/>
-      <c r="P25" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$O$7,C25:O25,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="Q25" s="28">
-        <f>COUNTIF(C25:O25,"Y")</f>
-        <v/>
-      </c>
-      <c r="R25" s="29">
-        <f>SUMPRODUCT((C$7:$O$7=1)*(C25:O25="Y"))*50</f>
+      <c r="P25" s="19" t="n"/>
+      <c r="Q25" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$P$7,C25:P25,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="R25" s="28">
+        <f>COUNTIF(C25:P25,"Y")</f>
+        <v/>
+      </c>
+      <c r="S25" s="29">
+        <f>SUMPRODUCT((C$7:$P$7=1)*(C25:P25="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8365,16 +8406,21 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="P26" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$O$7,C26:O26,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="Q26" s="28">
-        <f>COUNTIF(C26:O26,"Y")</f>
-        <v/>
-      </c>
-      <c r="R26" s="29">
-        <f>SUMPRODUCT((C$7:$O$7=1)*(C26:O26="Y"))*50</f>
+      <c r="P26" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q26" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$P$7,C26:P26,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="R26" s="28">
+        <f>COUNTIF(C26:P26,"Y")</f>
+        <v/>
+      </c>
+      <c r="S26" s="29">
+        <f>SUMPRODUCT((C$7:$P$7=1)*(C26:P26="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8400,16 +8446,17 @@
       <c r="M27" s="19" t="n"/>
       <c r="N27" s="19" t="n"/>
       <c r="O27" s="19" t="n"/>
-      <c r="P27" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$O$7,C27:O27,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="Q27" s="28">
-        <f>COUNTIF(C27:O27,"Y")</f>
-        <v/>
-      </c>
-      <c r="R27" s="29">
-        <f>SUMPRODUCT((C$7:$O$7=1)*(C27:O27="Y"))*50</f>
+      <c r="P27" s="19" t="n"/>
+      <c r="Q27" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$P$7,C27:P27,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="R27" s="28">
+        <f>COUNTIF(C27:P27,"Y")</f>
+        <v/>
+      </c>
+      <c r="S27" s="29">
+        <f>SUMPRODUCT((C$7:$P$7=1)*(C27:P27="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8439,16 +8486,21 @@
         </is>
       </c>
       <c r="O28" s="33" t="n"/>
-      <c r="P28" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$O$7,C28:O28,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="Q28" s="28">
-        <f>COUNTIF(C28:O28,"Y")</f>
-        <v/>
-      </c>
-      <c r="R28" s="29">
-        <f>SUMPRODUCT((C$7:$O$7=1)*(C28:O28="Y"))*50</f>
+      <c r="P28" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q28" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$P$7,C28:P28,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="R28" s="28">
+        <f>COUNTIF(C28:P28,"Y")</f>
+        <v/>
+      </c>
+      <c r="S28" s="29">
+        <f>SUMPRODUCT((C$7:$P$7=1)*(C28:P28="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8510,16 +8562,21 @@
         </is>
       </c>
       <c r="O29" s="19" t="n"/>
-      <c r="P29" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$O$7,C29:O29,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="Q29" s="28">
-        <f>COUNTIF(C29:O29,"Y")</f>
-        <v/>
-      </c>
-      <c r="R29" s="29">
-        <f>SUMPRODUCT((C$7:$O$7=1)*(C29:O29="Y"))*50</f>
+      <c r="P29" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q29" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$P$7,C29:P29,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="R29" s="28">
+        <f>COUNTIF(C29:P29,"Y")</f>
+        <v/>
+      </c>
+      <c r="S29" s="29">
+        <f>SUMPRODUCT((C$7:$P$7=1)*(C29:P29="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8545,16 +8602,17 @@
       <c r="M30" s="33" t="n"/>
       <c r="N30" s="33" t="n"/>
       <c r="O30" s="33" t="n"/>
-      <c r="P30" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$O$7,C30:O30,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="Q30" s="28">
-        <f>COUNTIF(C30:O30,"Y")</f>
-        <v/>
-      </c>
-      <c r="R30" s="29">
-        <f>SUMPRODUCT((C$7:$O$7=1)*(C30:O30="Y"))*50</f>
+      <c r="P30" s="33" t="n"/>
+      <c r="Q30" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$P$7,C30:P30,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="R30" s="28">
+        <f>COUNTIF(C30:P30,"Y")</f>
+        <v/>
+      </c>
+      <c r="S30" s="29">
+        <f>SUMPRODUCT((C$7:$P$7=1)*(C30:P30="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8580,16 +8638,17 @@
       <c r="M31" s="19" t="n"/>
       <c r="N31" s="19" t="n"/>
       <c r="O31" s="19" t="n"/>
-      <c r="P31" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$O$7,C31:O31,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="Q31" s="28">
-        <f>COUNTIF(C31:O31,"Y")</f>
-        <v/>
-      </c>
-      <c r="R31" s="29">
-        <f>SUMPRODUCT((C$7:$O$7=1)*(C31:O31="Y"))*50</f>
+      <c r="P31" s="19" t="n"/>
+      <c r="Q31" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$P$7,C31:P31,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="R31" s="28">
+        <f>COUNTIF(C31:P31,"Y")</f>
+        <v/>
+      </c>
+      <c r="S31" s="29">
+        <f>SUMPRODUCT((C$7:$P$7=1)*(C31:P31="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8615,16 +8674,17 @@
       <c r="M32" s="33" t="n"/>
       <c r="N32" s="33" t="n"/>
       <c r="O32" s="33" t="n"/>
-      <c r="P32" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$O$7,C32:O32,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="Q32" s="28">
-        <f>COUNTIF(C32:O32,"Y")</f>
-        <v/>
-      </c>
-      <c r="R32" s="29">
-        <f>SUMPRODUCT((C$7:$O$7=1)*(C32:O32="Y"))*50</f>
+      <c r="P32" s="33" t="n"/>
+      <c r="Q32" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$P$7,C32:P32,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="R32" s="28">
+        <f>COUNTIF(C32:P32,"Y")</f>
+        <v/>
+      </c>
+      <c r="S32" s="29">
+        <f>SUMPRODUCT((C$7:$P$7=1)*(C32:P32="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8670,16 +8730,17 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="P33" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$O$7,C33:O33,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="Q33" s="28">
-        <f>COUNTIF(C33:O33,"Y")</f>
-        <v/>
-      </c>
-      <c r="R33" s="29">
-        <f>SUMPRODUCT((C$7:$O$7=1)*(C33:O33="Y"))*50</f>
+      <c r="P33" s="19" t="n"/>
+      <c r="Q33" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$P$7,C33:P33,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="R33" s="28">
+        <f>COUNTIF(C33:P33,"Y")</f>
+        <v/>
+      </c>
+      <c r="S33" s="29">
+        <f>SUMPRODUCT((C$7:$P$7=1)*(C33:P33="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8717,16 +8778,21 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="P34" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$O$7,C34:O34,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="Q34" s="28">
-        <f>COUNTIF(C34:O34,"Y")</f>
-        <v/>
-      </c>
-      <c r="R34" s="29">
-        <f>SUMPRODUCT((C$7:$O$7=1)*(C34:O34="Y"))*50</f>
+      <c r="P34" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q34" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$P$7,C34:P34,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="R34" s="28">
+        <f>COUNTIF(C34:P34,"Y")</f>
+        <v/>
+      </c>
+      <c r="S34" s="29">
+        <f>SUMPRODUCT((C$7:$P$7=1)*(C34:P34="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8752,16 +8818,17 @@
       <c r="M35" s="19" t="n"/>
       <c r="N35" s="19" t="n"/>
       <c r="O35" s="19" t="n"/>
-      <c r="P35" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$O$7,C35:O35,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="Q35" s="28">
-        <f>COUNTIF(C35:O35,"Y")</f>
-        <v/>
-      </c>
-      <c r="R35" s="29">
-        <f>SUMPRODUCT((C$7:$O$7=1)*(C35:O35="Y"))*50</f>
+      <c r="P35" s="19" t="n"/>
+      <c r="Q35" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$P$7,C35:P35,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="R35" s="28">
+        <f>COUNTIF(C35:P35,"Y")</f>
+        <v/>
+      </c>
+      <c r="S35" s="29">
+        <f>SUMPRODUCT((C$7:$P$7=1)*(C35:P35="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8791,16 +8858,17 @@
       </c>
       <c r="N36" s="33" t="n"/>
       <c r="O36" s="33" t="n"/>
-      <c r="P36" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$O$7,C36:O36,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="Q36" s="28">
-        <f>COUNTIF(C36:O36,"Y")</f>
-        <v/>
-      </c>
-      <c r="R36" s="29">
-        <f>SUMPRODUCT((C$7:$O$7=1)*(C36:O36="Y"))*50</f>
+      <c r="P36" s="33" t="n"/>
+      <c r="Q36" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$P$7,C36:P36,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="R36" s="28">
+        <f>COUNTIF(C36:P36,"Y")</f>
+        <v/>
+      </c>
+      <c r="S36" s="29">
+        <f>SUMPRODUCT((C$7:$P$7=1)*(C36:P36="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8838,16 +8906,17 @@
       <c r="M37" s="19" t="n"/>
       <c r="N37" s="19" t="n"/>
       <c r="O37" s="19" t="n"/>
-      <c r="P37" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$O$7,C37:O37,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="Q37" s="28">
-        <f>COUNTIF(C37:O37,"Y")</f>
-        <v/>
-      </c>
-      <c r="R37" s="29">
-        <f>SUMPRODUCT((C$7:$O$7=1)*(C37:O37="Y"))*50</f>
+      <c r="P37" s="19" t="n"/>
+      <c r="Q37" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$P$7,C37:P37,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="R37" s="28">
+        <f>COUNTIF(C37:P37,"Y")</f>
+        <v/>
+      </c>
+      <c r="S37" s="29">
+        <f>SUMPRODUCT((C$7:$P$7=1)*(C37:P37="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8873,16 +8942,17 @@
       <c r="M38" s="33" t="n"/>
       <c r="N38" s="33" t="n"/>
       <c r="O38" s="33" t="n"/>
-      <c r="P38" s="18">
-        <f>IFERROR(AVERAGEIFS($C$7:$O$7,C38:O38,"Y"),"")</f>
-        <v/>
-      </c>
-      <c r="Q38" s="28">
-        <f>COUNTIF(C38:O38,"Y")</f>
-        <v/>
-      </c>
-      <c r="R38" s="29">
-        <f>SUMPRODUCT((C$7:$O$7=1)*(C38:O38="Y"))*50</f>
+      <c r="P38" s="33" t="n"/>
+      <c r="Q38" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$P$7,C38:P38,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="R38" s="28">
+        <f>COUNTIF(C38:P38,"Y")</f>
+        <v/>
+      </c>
+      <c r="S38" s="29">
+        <f>SUMPRODUCT((C$7:$P$7=1)*(C38:P38="Y"))*50</f>
         <v/>
       </c>
     </row>
@@ -8945,13 +9015,17 @@
         <f>COUNTIF(O14:O38,"Y")</f>
         <v/>
       </c>
-      <c r="P39" s="3" t="inlineStr"/>
-      <c r="Q39" s="6">
-        <f>SUM(Q14:Q38)</f>
-        <v/>
-      </c>
-      <c r="R39" s="37">
+      <c r="P39" s="6">
+        <f>COUNTIF(P14:P38,"Y")</f>
+        <v/>
+      </c>
+      <c r="Q39" s="3" t="inlineStr"/>
+      <c r="R39" s="6">
         <f>SUM(R14:R38)</f>
+        <v/>
+      </c>
+      <c r="S39" s="37">
+        <f>SUM(S14:S38)</f>
         <v/>
       </c>
     </row>
@@ -8964,13 +9038,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A18:R18"/>
-    <mergeCell ref="A2:R2"/>
-    <mergeCell ref="A19:R19"/>
-    <mergeCell ref="A13:R13"/>
-    <mergeCell ref="A1:R1"/>
-    <mergeCell ref="A40:R40"/>
-    <mergeCell ref="A12:R12"/>
+    <mergeCell ref="A19:S19"/>
+    <mergeCell ref="A13:S13"/>
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A40:S40"/>
+    <mergeCell ref="A18:S18"/>
+    <mergeCell ref="A12:S12"/>
+    <mergeCell ref="A2:S2"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Shop_Tracker_2065_2026.xlsx
+++ b/Shop_Tracker_2065_2026.xlsx
@@ -1,17 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="January" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="February" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="March" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="April" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="May" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="January" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="February" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="March" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="April" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="May" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="June" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -9050,4 +9051,1394 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="1" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:P40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
+    <col width="7" customWidth="1" min="12" max="12"/>
+    <col width="7" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="7" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>SECRET SHOPPER SCORES — JUNE 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="14" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Five Guys Store 2065 · Louisville, KY · 11 shops · Source: Marketforce + CrunchTime</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="4" customHeight="1"/>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="3" t="inlineStr"/>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>SHOP →</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>#8</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>#11</t>
+        </is>
+      </c>
+      <c r="N4" s="6" t="inlineStr">
+        <is>
+          <t>AVG</t>
+        </is>
+      </c>
+      <c r="O4" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P4" s="6" t="inlineStr">
+        <is>
+          <t>BONUS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="14" customHeight="1">
+      <c r="A5" s="7" t="inlineStr"/>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>06/02</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>06/06</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>06/11</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>06/14</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>06/19</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>06/20</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>06/21</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>06/26</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>06/28</t>
+        </is>
+      </c>
+      <c r="L5" s="9" t="inlineStr">
+        <is>
+          <t>06/02</t>
+        </is>
+      </c>
+      <c r="M5" s="9" t="inlineStr">
+        <is>
+          <t>06/04</t>
+        </is>
+      </c>
+      <c r="N5" s="7" t="inlineStr"/>
+      <c r="O5" s="7" t="inlineStr"/>
+      <c r="P5" s="7" t="inlineStr"/>
+    </row>
+    <row r="6" ht="14" customHeight="1">
+      <c r="A6" s="7" t="inlineStr"/>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Meal</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>LD</t>
+        </is>
+      </c>
+      <c r="J6" s="11" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="K6" s="10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="L6" s="11" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M6" s="11" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="N6" s="7" t="inlineStr"/>
+      <c r="O6" s="7" t="inlineStr"/>
+      <c r="P6" s="7" t="inlineStr"/>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="12" t="inlineStr"/>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Total Score</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="D7" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="16" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F7" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="16" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H7" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="16" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J7" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="17" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="M7" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" s="18">
+        <f>IFERROR(AVERAGE(C7:M7),"")</f>
+        <v/>
+      </c>
+      <c r="O7" s="12" t="inlineStr"/>
+      <c r="P7" s="12" t="inlineStr"/>
+    </row>
+    <row r="8" ht="13" customHeight="1">
+      <c r="A8" s="19" t="inlineStr"/>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="inlineStr"/>
+      <c r="D8" s="19" t="inlineStr"/>
+      <c r="E8" s="19" t="inlineStr"/>
+      <c r="F8" s="19" t="inlineStr"/>
+      <c r="G8" s="19" t="inlineStr"/>
+      <c r="H8" s="19" t="inlineStr"/>
+      <c r="I8" s="19" t="inlineStr"/>
+      <c r="J8" s="19" t="inlineStr"/>
+      <c r="K8" s="19" t="inlineStr"/>
+      <c r="L8" s="19" t="inlineStr"/>
+      <c r="M8" s="19" t="inlineStr"/>
+      <c r="N8" s="21">
+        <f>IFERROR(AVERAGE(C8:M8),"")</f>
+        <v/>
+      </c>
+      <c r="O8" s="19" t="inlineStr"/>
+      <c r="P8" s="19" t="inlineStr"/>
+    </row>
+    <row r="9" ht="13" customHeight="1">
+      <c r="A9" s="19" t="inlineStr"/>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="inlineStr"/>
+      <c r="D9" s="19" t="inlineStr"/>
+      <c r="E9" s="19" t="inlineStr"/>
+      <c r="F9" s="19" t="inlineStr"/>
+      <c r="G9" s="19" t="inlineStr"/>
+      <c r="H9" s="19" t="inlineStr"/>
+      <c r="I9" s="19" t="inlineStr"/>
+      <c r="J9" s="19" t="inlineStr"/>
+      <c r="K9" s="19" t="inlineStr"/>
+      <c r="L9" s="19" t="inlineStr"/>
+      <c r="M9" s="19" t="inlineStr"/>
+      <c r="N9" s="21">
+        <f>IFERROR(AVERAGE(C9:M9),"")</f>
+        <v/>
+      </c>
+      <c r="O9" s="19" t="inlineStr"/>
+      <c r="P9" s="19" t="inlineStr"/>
+    </row>
+    <row r="10" ht="13" customHeight="1">
+      <c r="A10" s="19" t="inlineStr"/>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>Cleanliness</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="inlineStr"/>
+      <c r="D10" s="19" t="inlineStr"/>
+      <c r="E10" s="19" t="inlineStr"/>
+      <c r="F10" s="19" t="inlineStr"/>
+      <c r="G10" s="19" t="inlineStr"/>
+      <c r="H10" s="19" t="inlineStr"/>
+      <c r="I10" s="19" t="inlineStr"/>
+      <c r="J10" s="19" t="inlineStr"/>
+      <c r="K10" s="19" t="inlineStr"/>
+      <c r="L10" s="19" t="inlineStr"/>
+      <c r="M10" s="19" t="inlineStr"/>
+      <c r="N10" s="21">
+        <f>IFERROR(AVERAGE(C10:M10),"")</f>
+        <v/>
+      </c>
+      <c r="O10" s="19" t="inlineStr"/>
+      <c r="P10" s="19" t="inlineStr"/>
+    </row>
+    <row r="11" ht="13" customHeight="1">
+      <c r="A11" s="19" t="inlineStr"/>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>Customer Sat</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="inlineStr"/>
+      <c r="D11" s="19" t="inlineStr"/>
+      <c r="E11" s="19" t="inlineStr"/>
+      <c r="F11" s="19" t="inlineStr"/>
+      <c r="G11" s="19" t="inlineStr"/>
+      <c r="H11" s="19" t="inlineStr"/>
+      <c r="I11" s="19" t="inlineStr"/>
+      <c r="J11" s="19" t="inlineStr"/>
+      <c r="K11" s="19" t="inlineStr"/>
+      <c r="L11" s="19" t="inlineStr"/>
+      <c r="M11" s="19" t="inlineStr"/>
+      <c r="N11" s="21">
+        <f>IFERROR(AVERAGE(C11:M11),"")</f>
+        <v/>
+      </c>
+      <c r="O11" s="19" t="inlineStr"/>
+      <c r="P11" s="19" t="inlineStr"/>
+    </row>
+    <row r="12" ht="6" customHeight="1">
+      <c r="A12" s="22" t="n"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="23" t="inlineStr">
+        <is>
+          <t>MANAGERS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" s="25" t="inlineStr">
+        <is>
+          <t>Madison C.</t>
+        </is>
+      </c>
+      <c r="C14" s="27" t="n"/>
+      <c r="D14" s="27" t="n"/>
+      <c r="E14" s="27" t="n"/>
+      <c r="F14" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G14" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H14" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I14" s="27" t="n"/>
+      <c r="J14" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K14" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L14" s="27" t="n"/>
+      <c r="M14" s="27" t="n"/>
+      <c r="N14" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$M$7,C14:M14,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="O14" s="28">
+        <f>COUNTIF(C14:M14,"Y")</f>
+        <v/>
+      </c>
+      <c r="P14" s="29">
+        <f>SUMPRODUCT((C$7:$M$7=1)*(C14:M14="Y"))*50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="B15" s="25" t="inlineStr">
+        <is>
+          <t>Vicki L.</t>
+        </is>
+      </c>
+      <c r="C15" s="27" t="n"/>
+      <c r="D15" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E15" s="27" t="n"/>
+      <c r="F15" s="27" t="n"/>
+      <c r="G15" s="27" t="n"/>
+      <c r="H15" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I15" s="27" t="n"/>
+      <c r="J15" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K15" s="27" t="n"/>
+      <c r="L15" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M15" s="27" t="n"/>
+      <c r="N15" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$M$7,C15:M15,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="O15" s="28">
+        <f>COUNTIF(C15:M15,"Y")</f>
+        <v/>
+      </c>
+      <c r="P15" s="29">
+        <f>SUMPRODUCT((C$7:$M$7=1)*(C15:M15="Y"))*50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="17" customHeight="1">
+      <c r="A16" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="B16" s="25" t="inlineStr">
+        <is>
+          <t>Kasey W.</t>
+        </is>
+      </c>
+      <c r="C16" s="27" t="n"/>
+      <c r="D16" s="27" t="n"/>
+      <c r="E16" s="27" t="n"/>
+      <c r="F16" s="27" t="n"/>
+      <c r="G16" s="27" t="n"/>
+      <c r="H16" s="27" t="n"/>
+      <c r="I16" s="27" t="n"/>
+      <c r="J16" s="27" t="n"/>
+      <c r="K16" s="27" t="n"/>
+      <c r="L16" s="27" t="n"/>
+      <c r="M16" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N16" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$M$7,C16:M16,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="O16" s="28">
+        <f>COUNTIF(C16:M16,"Y")</f>
+        <v/>
+      </c>
+      <c r="P16" s="29">
+        <f>SUMPRODUCT((C$7:$M$7=1)*(C16:M16="Y"))*50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="17" customHeight="1">
+      <c r="A17" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="B17" s="25" t="inlineStr">
+        <is>
+          <t>Nathan R.</t>
+        </is>
+      </c>
+      <c r="C17" s="27" t="n"/>
+      <c r="D17" s="27" t="n"/>
+      <c r="E17" s="27" t="n"/>
+      <c r="F17" s="27" t="n"/>
+      <c r="G17" s="27" t="n"/>
+      <c r="H17" s="27" t="n"/>
+      <c r="I17" s="27" t="n"/>
+      <c r="J17" s="27" t="n"/>
+      <c r="K17" s="27" t="n"/>
+      <c r="L17" s="27" t="n"/>
+      <c r="M17" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N17" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$M$7,C17:M17,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="O17" s="28">
+        <f>COUNTIF(C17:M17,"Y")</f>
+        <v/>
+      </c>
+      <c r="P17" s="29">
+        <f>SUMPRODUCT((C$7:$M$7=1)*(C17:M17="Y"))*50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="6" customHeight="1">
+      <c r="A18" s="22" t="n"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="30" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="17" customHeight="1">
+      <c r="A20" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" s="32" t="inlineStr">
+        <is>
+          <t>Alen</t>
+        </is>
+      </c>
+      <c r="C20" s="33" t="n"/>
+      <c r="D20" s="33" t="n"/>
+      <c r="E20" s="33" t="n"/>
+      <c r="F20" s="33" t="n"/>
+      <c r="G20" s="33" t="n"/>
+      <c r="H20" s="33" t="n"/>
+      <c r="I20" s="33" t="n"/>
+      <c r="J20" s="33" t="n"/>
+      <c r="K20" s="33" t="n"/>
+      <c r="L20" s="33" t="n"/>
+      <c r="M20" s="33" t="n"/>
+      <c r="N20" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$M$7,C20:M20,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="O20" s="28">
+        <f>COUNTIF(C20:M20,"Y")</f>
+        <v/>
+      </c>
+      <c r="P20" s="29">
+        <f>SUMPRODUCT((C$7:$M$7=1)*(C20:M20="Y"))*50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="17" customHeight="1">
+      <c r="A21" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="35" t="inlineStr">
+        <is>
+          <t>Ash</t>
+        </is>
+      </c>
+      <c r="C21" s="19" t="n"/>
+      <c r="D21" s="19" t="n"/>
+      <c r="E21" s="19" t="n"/>
+      <c r="F21" s="19" t="n"/>
+      <c r="G21" s="19" t="n"/>
+      <c r="H21" s="19" t="n"/>
+      <c r="I21" s="19" t="n"/>
+      <c r="J21" s="19" t="n"/>
+      <c r="K21" s="19" t="n"/>
+      <c r="L21" s="19" t="n"/>
+      <c r="M21" s="19" t="n"/>
+      <c r="N21" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$M$7,C21:M21,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="O21" s="28">
+        <f>COUNTIF(C21:M21,"Y")</f>
+        <v/>
+      </c>
+      <c r="P21" s="29">
+        <f>SUMPRODUCT((C$7:$M$7=1)*(C21:M21="Y"))*50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="17" customHeight="1">
+      <c r="A22" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="32" t="inlineStr">
+        <is>
+          <t>Autumn</t>
+        </is>
+      </c>
+      <c r="C22" s="33" t="n"/>
+      <c r="D22" s="33" t="n"/>
+      <c r="E22" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F22" s="33" t="n"/>
+      <c r="G22" s="33" t="n"/>
+      <c r="H22" s="33" t="n"/>
+      <c r="I22" s="33" t="n"/>
+      <c r="J22" s="33" t="n"/>
+      <c r="K22" s="33" t="n"/>
+      <c r="L22" s="33" t="n"/>
+      <c r="M22" s="33" t="n"/>
+      <c r="N22" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$M$7,C22:M22,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="O22" s="28">
+        <f>COUNTIF(C22:M22,"Y")</f>
+        <v/>
+      </c>
+      <c r="P22" s="29">
+        <f>SUMPRODUCT((C$7:$M$7=1)*(C22:M22="Y"))*50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="17" customHeight="1">
+      <c r="A23" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="35" t="inlineStr">
+        <is>
+          <t>Bri</t>
+        </is>
+      </c>
+      <c r="C23" s="19" t="n"/>
+      <c r="D23" s="19" t="n"/>
+      <c r="E23" s="19" t="n"/>
+      <c r="F23" s="19" t="n"/>
+      <c r="G23" s="19" t="n"/>
+      <c r="H23" s="19" t="n"/>
+      <c r="I23" s="19" t="n"/>
+      <c r="J23" s="19" t="n"/>
+      <c r="K23" s="19" t="n"/>
+      <c r="L23" s="19" t="n"/>
+      <c r="M23" s="19" t="n"/>
+      <c r="N23" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$M$7,C23:M23,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="O23" s="28">
+        <f>COUNTIF(C23:M23,"Y")</f>
+        <v/>
+      </c>
+      <c r="P23" s="29">
+        <f>SUMPRODUCT((C$7:$M$7=1)*(C23:M23="Y"))*50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="17" customHeight="1">
+      <c r="A24" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="32" t="inlineStr">
+        <is>
+          <t>Dakayla</t>
+        </is>
+      </c>
+      <c r="C24" s="33" t="n"/>
+      <c r="D24" s="33" t="n"/>
+      <c r="E24" s="33" t="n"/>
+      <c r="F24" s="33" t="n"/>
+      <c r="G24" s="33" t="n"/>
+      <c r="H24" s="33" t="n"/>
+      <c r="I24" s="33" t="n"/>
+      <c r="J24" s="33" t="n"/>
+      <c r="K24" s="33" t="n"/>
+      <c r="L24" s="33" t="n"/>
+      <c r="M24" s="33" t="n"/>
+      <c r="N24" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$M$7,C24:M24,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="O24" s="28">
+        <f>COUNTIF(C24:M24,"Y")</f>
+        <v/>
+      </c>
+      <c r="P24" s="29">
+        <f>SUMPRODUCT((C$7:$M$7=1)*(C24:M24="Y"))*50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="17" customHeight="1">
+      <c r="A25" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="35" t="inlineStr">
+        <is>
+          <t>Divan</t>
+        </is>
+      </c>
+      <c r="C25" s="19" t="n"/>
+      <c r="D25" s="19" t="n"/>
+      <c r="E25" s="19" t="n"/>
+      <c r="F25" s="19" t="n"/>
+      <c r="G25" s="19" t="n"/>
+      <c r="H25" s="19" t="n"/>
+      <c r="I25" s="19" t="n"/>
+      <c r="J25" s="19" t="n"/>
+      <c r="K25" s="19" t="n"/>
+      <c r="L25" s="19" t="n"/>
+      <c r="M25" s="19" t="n"/>
+      <c r="N25" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$M$7,C25:M25,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="O25" s="28">
+        <f>COUNTIF(C25:M25,"Y")</f>
+        <v/>
+      </c>
+      <c r="P25" s="29">
+        <f>SUMPRODUCT((C$7:$M$7=1)*(C25:M25="Y"))*50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="17" customHeight="1">
+      <c r="A26" s="31" t="n">
+        <v>7</v>
+      </c>
+      <c r="B26" s="32" t="inlineStr">
+        <is>
+          <t>Francisco</t>
+        </is>
+      </c>
+      <c r="C26" s="33" t="n"/>
+      <c r="D26" s="33" t="n"/>
+      <c r="E26" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F26" s="33" t="n"/>
+      <c r="G26" s="33" t="n"/>
+      <c r="H26" s="33" t="n"/>
+      <c r="I26" s="33" t="n"/>
+      <c r="J26" s="33" t="n"/>
+      <c r="K26" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L26" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M26" s="33" t="n"/>
+      <c r="N26" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$M$7,C26:M26,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="O26" s="28">
+        <f>COUNTIF(C26:M26,"Y")</f>
+        <v/>
+      </c>
+      <c r="P26" s="29">
+        <f>SUMPRODUCT((C$7:$M$7=1)*(C26:M26="Y"))*50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="17" customHeight="1">
+      <c r="A27" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="B27" s="35" t="inlineStr">
+        <is>
+          <t>Grace</t>
+        </is>
+      </c>
+      <c r="C27" s="19" t="n"/>
+      <c r="D27" s="19" t="n"/>
+      <c r="E27" s="19" t="n"/>
+      <c r="F27" s="19" t="n"/>
+      <c r="G27" s="19" t="n"/>
+      <c r="H27" s="19" t="n"/>
+      <c r="I27" s="19" t="n"/>
+      <c r="J27" s="19" t="n"/>
+      <c r="K27" s="19" t="n"/>
+      <c r="L27" s="19" t="n"/>
+      <c r="M27" s="19" t="n"/>
+      <c r="N27" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$M$7,C27:M27,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="O27" s="28">
+        <f>COUNTIF(C27:M27,"Y")</f>
+        <v/>
+      </c>
+      <c r="P27" s="29">
+        <f>SUMPRODUCT((C$7:$M$7=1)*(C27:M27="Y"))*50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="17" customHeight="1">
+      <c r="A28" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="B28" s="32" t="inlineStr">
+        <is>
+          <t>Jada</t>
+        </is>
+      </c>
+      <c r="C28" s="33" t="n"/>
+      <c r="D28" s="33" t="n"/>
+      <c r="E28" s="33" t="n"/>
+      <c r="F28" s="33" t="n"/>
+      <c r="G28" s="33" t="n"/>
+      <c r="H28" s="33" t="n"/>
+      <c r="I28" s="33" t="n"/>
+      <c r="J28" s="33" t="n"/>
+      <c r="K28" s="33" t="n"/>
+      <c r="L28" s="33" t="n"/>
+      <c r="M28" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N28" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$M$7,C28:M28,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="O28" s="28">
+        <f>COUNTIF(C28:M28,"Y")</f>
+        <v/>
+      </c>
+      <c r="P28" s="29">
+        <f>SUMPRODUCT((C$7:$M$7=1)*(C28:M28="Y"))*50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="17" customHeight="1">
+      <c r="A29" s="34" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" s="35" t="inlineStr">
+        <is>
+          <t>Jeremiah</t>
+        </is>
+      </c>
+      <c r="C29" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D29" s="19" t="n"/>
+      <c r="E29" s="19" t="n"/>
+      <c r="F29" s="19" t="n"/>
+      <c r="G29" s="19" t="n"/>
+      <c r="H29" s="19" t="n"/>
+      <c r="I29" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J29" s="19" t="n"/>
+      <c r="K29" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L29" s="19" t="n"/>
+      <c r="M29" s="19" t="n"/>
+      <c r="N29" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$M$7,C29:M29,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="O29" s="28">
+        <f>COUNTIF(C29:M29,"Y")</f>
+        <v/>
+      </c>
+      <c r="P29" s="29">
+        <f>SUMPRODUCT((C$7:$M$7=1)*(C29:M29="Y"))*50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="17" customHeight="1">
+      <c r="A30" s="31" t="n">
+        <v>11</v>
+      </c>
+      <c r="B30" s="32" t="inlineStr">
+        <is>
+          <t>Kable</t>
+        </is>
+      </c>
+      <c r="C30" s="33" t="n"/>
+      <c r="D30" s="33" t="n"/>
+      <c r="E30" s="33" t="n"/>
+      <c r="F30" s="33" t="n"/>
+      <c r="G30" s="33" t="n"/>
+      <c r="H30" s="33" t="n"/>
+      <c r="I30" s="33" t="n"/>
+      <c r="J30" s="33" t="n"/>
+      <c r="K30" s="33" t="n"/>
+      <c r="L30" s="33" t="n"/>
+      <c r="M30" s="33" t="n"/>
+      <c r="N30" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$M$7,C30:M30,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="O30" s="28">
+        <f>COUNTIF(C30:M30,"Y")</f>
+        <v/>
+      </c>
+      <c r="P30" s="29">
+        <f>SUMPRODUCT((C$7:$M$7=1)*(C30:M30="Y"))*50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="17" customHeight="1">
+      <c r="A31" s="34" t="n">
+        <v>12</v>
+      </c>
+      <c r="B31" s="35" t="inlineStr">
+        <is>
+          <t>Kayla</t>
+        </is>
+      </c>
+      <c r="C31" s="19" t="n"/>
+      <c r="D31" s="19" t="n"/>
+      <c r="E31" s="19" t="n"/>
+      <c r="F31" s="19" t="n"/>
+      <c r="G31" s="19" t="n"/>
+      <c r="H31" s="19" t="n"/>
+      <c r="I31" s="19" t="n"/>
+      <c r="J31" s="19" t="n"/>
+      <c r="K31" s="19" t="n"/>
+      <c r="L31" s="19" t="n"/>
+      <c r="M31" s="19" t="n"/>
+      <c r="N31" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$M$7,C31:M31,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="O31" s="28">
+        <f>COUNTIF(C31:M31,"Y")</f>
+        <v/>
+      </c>
+      <c r="P31" s="29">
+        <f>SUMPRODUCT((C$7:$M$7=1)*(C31:M31="Y"))*50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="17" customHeight="1">
+      <c r="A32" s="31" t="n">
+        <v>13</v>
+      </c>
+      <c r="B32" s="32" t="inlineStr">
+        <is>
+          <t>Kenzie</t>
+        </is>
+      </c>
+      <c r="C32" s="33" t="n"/>
+      <c r="D32" s="33" t="n"/>
+      <c r="E32" s="33" t="n"/>
+      <c r="F32" s="33" t="n"/>
+      <c r="G32" s="33" t="n"/>
+      <c r="H32" s="33" t="n"/>
+      <c r="I32" s="33" t="n"/>
+      <c r="J32" s="33" t="n"/>
+      <c r="K32" s="33" t="n"/>
+      <c r="L32" s="33" t="n"/>
+      <c r="M32" s="33" t="n"/>
+      <c r="N32" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$M$7,C32:M32,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="O32" s="28">
+        <f>COUNTIF(C32:M32,"Y")</f>
+        <v/>
+      </c>
+      <c r="P32" s="29">
+        <f>SUMPRODUCT((C$7:$M$7=1)*(C32:M32="Y"))*50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="17" customHeight="1">
+      <c r="A33" s="34" t="n">
+        <v>14</v>
+      </c>
+      <c r="B33" s="35" t="inlineStr">
+        <is>
+          <t>Lidy</t>
+        </is>
+      </c>
+      <c r="C33" s="19" t="n"/>
+      <c r="D33" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E33" s="19" t="n"/>
+      <c r="F33" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G33" s="19" t="n"/>
+      <c r="H33" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I33" s="19" t="n"/>
+      <c r="J33" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K33" s="19" t="n"/>
+      <c r="L33" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M33" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N33" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$M$7,C33:M33,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="O33" s="28">
+        <f>COUNTIF(C33:M33,"Y")</f>
+        <v/>
+      </c>
+      <c r="P33" s="29">
+        <f>SUMPRODUCT((C$7:$M$7=1)*(C33:M33="Y"))*50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="17" customHeight="1">
+      <c r="A34" s="31" t="n">
+        <v>15</v>
+      </c>
+      <c r="B34" s="32" t="inlineStr">
+        <is>
+          <t>Maylin</t>
+        </is>
+      </c>
+      <c r="C34" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D34" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E34" s="33" t="n"/>
+      <c r="F34" s="33" t="n"/>
+      <c r="G34" s="33" t="n"/>
+      <c r="H34" s="33" t="n"/>
+      <c r="I34" s="33" t="n"/>
+      <c r="J34" s="33" t="n"/>
+      <c r="K34" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L34" s="33" t="n"/>
+      <c r="M34" s="33" t="n"/>
+      <c r="N34" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$M$7,C34:M34,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="O34" s="28">
+        <f>COUNTIF(C34:M34,"Y")</f>
+        <v/>
+      </c>
+      <c r="P34" s="29">
+        <f>SUMPRODUCT((C$7:$M$7=1)*(C34:M34="Y"))*50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="17" customHeight="1">
+      <c r="A35" s="34" t="n">
+        <v>16</v>
+      </c>
+      <c r="B35" s="35" t="inlineStr">
+        <is>
+          <t>Mike</t>
+        </is>
+      </c>
+      <c r="C35" s="19" t="n"/>
+      <c r="D35" s="19" t="n"/>
+      <c r="E35" s="19" t="n"/>
+      <c r="F35" s="19" t="n"/>
+      <c r="G35" s="19" t="n"/>
+      <c r="H35" s="19" t="n"/>
+      <c r="I35" s="19" t="n"/>
+      <c r="J35" s="19" t="n"/>
+      <c r="K35" s="19" t="n"/>
+      <c r="L35" s="19" t="n"/>
+      <c r="M35" s="19" t="n"/>
+      <c r="N35" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$M$7,C35:M35,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="O35" s="28">
+        <f>COUNTIF(C35:M35,"Y")</f>
+        <v/>
+      </c>
+      <c r="P35" s="29">
+        <f>SUMPRODUCT((C$7:$M$7=1)*(C35:M35="Y"))*50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="17" customHeight="1">
+      <c r="A36" s="31" t="n">
+        <v>17</v>
+      </c>
+      <c r="B36" s="32" t="inlineStr">
+        <is>
+          <t>Richard</t>
+        </is>
+      </c>
+      <c r="C36" s="33" t="n"/>
+      <c r="D36" s="33" t="n"/>
+      <c r="E36" s="33" t="n"/>
+      <c r="F36" s="33" t="n"/>
+      <c r="G36" s="33" t="n"/>
+      <c r="H36" s="33" t="n"/>
+      <c r="I36" s="33" t="n"/>
+      <c r="J36" s="33" t="n"/>
+      <c r="K36" s="33" t="n"/>
+      <c r="L36" s="33" t="n"/>
+      <c r="M36" s="33" t="n"/>
+      <c r="N36" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$M$7,C36:M36,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="O36" s="28">
+        <f>COUNTIF(C36:M36,"Y")</f>
+        <v/>
+      </c>
+      <c r="P36" s="29">
+        <f>SUMPRODUCT((C$7:$M$7=1)*(C36:M36="Y"))*50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="17" customHeight="1">
+      <c r="A37" s="34" t="n">
+        <v>18</v>
+      </c>
+      <c r="B37" s="35" t="inlineStr">
+        <is>
+          <t>Samuel</t>
+        </is>
+      </c>
+      <c r="C37" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D37" s="19" t="n"/>
+      <c r="E37" s="19" t="n"/>
+      <c r="F37" s="19" t="n"/>
+      <c r="G37" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H37" s="19" t="n"/>
+      <c r="I37" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J37" s="19" t="n"/>
+      <c r="K37" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L37" s="19" t="n"/>
+      <c r="M37" s="19" t="n"/>
+      <c r="N37" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$M$7,C37:M37,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="O37" s="28">
+        <f>COUNTIF(C37:M37,"Y")</f>
+        <v/>
+      </c>
+      <c r="P37" s="29">
+        <f>SUMPRODUCT((C$7:$M$7=1)*(C37:M37="Y"))*50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="17" customHeight="1">
+      <c r="A38" s="31" t="n">
+        <v>19</v>
+      </c>
+      <c r="B38" s="32" t="inlineStr">
+        <is>
+          <t>Zach</t>
+        </is>
+      </c>
+      <c r="C38" s="33" t="n"/>
+      <c r="D38" s="33" t="n"/>
+      <c r="E38" s="33" t="n"/>
+      <c r="F38" s="33" t="n"/>
+      <c r="G38" s="33" t="n"/>
+      <c r="H38" s="33" t="n"/>
+      <c r="I38" s="33" t="n"/>
+      <c r="J38" s="33" t="n"/>
+      <c r="K38" s="33" t="n"/>
+      <c r="L38" s="33" t="n"/>
+      <c r="M38" s="33" t="n"/>
+      <c r="N38" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$M$7,C38:M38,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="O38" s="28">
+        <f>COUNTIF(C38:M38,"Y")</f>
+        <v/>
+      </c>
+      <c r="P38" s="29">
+        <f>SUMPRODUCT((C$7:$M$7=1)*(C38:M38="Y"))*50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="3" t="inlineStr"/>
+      <c r="B39" s="36" t="inlineStr">
+        <is>
+          <t>Total on shift</t>
+        </is>
+      </c>
+      <c r="C39" s="6">
+        <f>COUNTIF(C14:C38,"Y")</f>
+        <v/>
+      </c>
+      <c r="D39" s="6">
+        <f>COUNTIF(D14:D38,"Y")</f>
+        <v/>
+      </c>
+      <c r="E39" s="6">
+        <f>COUNTIF(E14:E38,"Y")</f>
+        <v/>
+      </c>
+      <c r="F39" s="6">
+        <f>COUNTIF(F14:F38,"Y")</f>
+        <v/>
+      </c>
+      <c r="G39" s="6">
+        <f>COUNTIF(G14:G38,"Y")</f>
+        <v/>
+      </c>
+      <c r="H39" s="6">
+        <f>COUNTIF(H14:H38,"Y")</f>
+        <v/>
+      </c>
+      <c r="I39" s="6">
+        <f>COUNTIF(I14:I38,"Y")</f>
+        <v/>
+      </c>
+      <c r="J39" s="6">
+        <f>COUNTIF(J14:J38,"Y")</f>
+        <v/>
+      </c>
+      <c r="K39" s="6">
+        <f>COUNTIF(K14:K38,"Y")</f>
+        <v/>
+      </c>
+      <c r="L39" s="6">
+        <f>COUNTIF(L14:L38,"Y")</f>
+        <v/>
+      </c>
+      <c r="M39" s="6">
+        <f>COUNTIF(M14:M38,"Y")</f>
+        <v/>
+      </c>
+      <c r="N39" s="3" t="inlineStr"/>
+      <c r="O39" s="6">
+        <f>SUM(O14:O38)</f>
+        <v/>
+      </c>
+      <c r="P39" s="37">
+        <f>SUM(P14:P38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="12" customHeight="1">
+      <c r="A40" s="38" t="inlineStr">
+        <is>
+          <t>Y = on shift during shop's meal window. Personal Avg = average score of shops worked. Bonus = $50 per 100% shop worked.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A13:P13"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A40:P40"/>
+    <mergeCell ref="A18:P18"/>
+    <mergeCell ref="A12:P12"/>
+    <mergeCell ref="A19:P19"/>
+    <mergeCell ref="A2:P2"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/Shop_Tracker_2065_2026.xlsx
+++ b/Shop_Tracker_2065_2026.xlsx
@@ -773,7 +773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:W40"/>
+  <dimension ref="A1:W41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2057,7 +2057,7 @@
       </c>
       <c r="B30" s="32" t="inlineStr">
         <is>
-          <t>Kable</t>
+          <t>Kaisha</t>
         </is>
       </c>
       <c r="C30" s="33" t="n"/>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="B31" s="35" t="inlineStr">
         <is>
-          <t>Kayla</t>
+          <t>Kable</t>
         </is>
       </c>
       <c r="C31" s="19" t="n"/>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="B32" s="32" t="inlineStr">
         <is>
-          <t>Kenzie</t>
+          <t>Kayla</t>
         </is>
       </c>
       <c r="C32" s="33" t="n"/>
@@ -2177,71 +2177,27 @@
       </c>
       <c r="B33" s="35" t="inlineStr">
         <is>
-          <t>Lidy</t>
-        </is>
-      </c>
-      <c r="C33" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D33" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E33" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F33" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G33" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>Kenzie</t>
+        </is>
+      </c>
+      <c r="C33" s="19" t="n"/>
+      <c r="D33" s="19" t="n"/>
+      <c r="E33" s="19" t="n"/>
+      <c r="F33" s="19" t="n"/>
+      <c r="G33" s="19" t="n"/>
       <c r="H33" s="19" t="n"/>
-      <c r="I33" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J33" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K33" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="I33" s="19" t="n"/>
+      <c r="J33" s="19" t="n"/>
+      <c r="K33" s="19" t="n"/>
       <c r="L33" s="19" t="n"/>
       <c r="M33" s="19" t="n"/>
       <c r="N33" s="19" t="n"/>
-      <c r="O33" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O33" s="19" t="n"/>
       <c r="P33" s="19" t="n"/>
-      <c r="Q33" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="Q33" s="19" t="n"/>
       <c r="R33" s="19" t="n"/>
       <c r="S33" s="19" t="n"/>
-      <c r="T33" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="T33" s="19" t="n"/>
       <c r="U33" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$T$7,C33:T33,"Y"),"")</f>
         <v/>
@@ -2261,25 +2217,45 @@
       </c>
       <c r="B34" s="32" t="inlineStr">
         <is>
-          <t>Maylin</t>
-        </is>
-      </c>
-      <c r="C34" s="33" t="n"/>
+          <t>Lidy</t>
+        </is>
+      </c>
+      <c r="C34" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="D34" s="26" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="E34" s="33" t="n"/>
-      <c r="F34" s="33" t="n"/>
-      <c r="G34" s="33" t="n"/>
+      <c r="E34" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F34" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G34" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="H34" s="33" t="n"/>
       <c r="I34" s="26" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J34" s="33" t="n"/>
+      <c r="J34" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="K34" s="26" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2287,29 +2263,25 @@
       </c>
       <c r="L34" s="33" t="n"/>
       <c r="M34" s="33" t="n"/>
-      <c r="N34" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O34" s="33" t="n"/>
-      <c r="P34" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="N34" s="33" t="n"/>
+      <c r="O34" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P34" s="33" t="n"/>
       <c r="Q34" s="26" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
       <c r="R34" s="33" t="n"/>
-      <c r="S34" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="T34" s="33" t="n"/>
+      <c r="S34" s="33" t="n"/>
+      <c r="T34" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="U34" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$T$7,C34:T34,"Y"),"")</f>
         <v/>
@@ -2329,47 +2301,55 @@
       </c>
       <c r="B35" s="35" t="inlineStr">
         <is>
-          <t>Mike</t>
+          <t>Maylin</t>
         </is>
       </c>
       <c r="C35" s="19" t="n"/>
-      <c r="D35" s="19" t="n"/>
+      <c r="D35" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E35" s="19" t="n"/>
       <c r="F35" s="19" t="n"/>
       <c r="G35" s="19" t="n"/>
       <c r="H35" s="19" t="n"/>
-      <c r="I35" s="19" t="n"/>
+      <c r="I35" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="J35" s="19" t="n"/>
-      <c r="K35" s="19" t="n"/>
+      <c r="K35" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L35" s="19" t="n"/>
-      <c r="M35" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N35" s="19" t="n"/>
-      <c r="O35" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="M35" s="19" t="n"/>
+      <c r="N35" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O35" s="19" t="n"/>
       <c r="P35" s="26" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="Q35" s="19" t="n"/>
+      <c r="Q35" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="R35" s="19" t="n"/>
       <c r="S35" s="26" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="T35" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="T35" s="19" t="n"/>
       <c r="U35" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$T$7,C35:T35,"Y"),"")</f>
         <v/>
@@ -2389,7 +2369,7 @@
       </c>
       <c r="B36" s="32" t="inlineStr">
         <is>
-          <t>Richard</t>
+          <t>Mike</t>
         </is>
       </c>
       <c r="C36" s="33" t="n"/>
@@ -2402,14 +2382,34 @@
       <c r="J36" s="33" t="n"/>
       <c r="K36" s="33" t="n"/>
       <c r="L36" s="33" t="n"/>
-      <c r="M36" s="33" t="n"/>
+      <c r="M36" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="N36" s="33" t="n"/>
-      <c r="O36" s="33" t="n"/>
-      <c r="P36" s="33" t="n"/>
+      <c r="O36" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P36" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="Q36" s="33" t="n"/>
       <c r="R36" s="33" t="n"/>
-      <c r="S36" s="33" t="n"/>
-      <c r="T36" s="33" t="n"/>
+      <c r="S36" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T36" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="U36" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$T$7,C36:T36,"Y"),"")</f>
         <v/>
@@ -2429,58 +2429,26 @@
       </c>
       <c r="B37" s="35" t="inlineStr">
         <is>
-          <t>Samuel</t>
-        </is>
-      </c>
-      <c r="C37" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>Richard</t>
+        </is>
+      </c>
+      <c r="C37" s="19" t="n"/>
       <c r="D37" s="19" t="n"/>
       <c r="E37" s="19" t="n"/>
       <c r="F37" s="19" t="n"/>
-      <c r="G37" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="G37" s="19" t="n"/>
       <c r="H37" s="19" t="n"/>
       <c r="I37" s="19" t="n"/>
-      <c r="J37" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="J37" s="19" t="n"/>
       <c r="K37" s="19" t="n"/>
-      <c r="L37" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="L37" s="19" t="n"/>
       <c r="M37" s="19" t="n"/>
-      <c r="N37" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="N37" s="19" t="n"/>
       <c r="O37" s="19" t="n"/>
-      <c r="P37" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="P37" s="19" t="n"/>
       <c r="Q37" s="19" t="n"/>
-      <c r="R37" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="S37" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="R37" s="19" t="n"/>
+      <c r="S37" s="19" t="n"/>
       <c r="T37" s="19" t="n"/>
       <c r="U37" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$T$7,C37:T37,"Y"),"")</f>
@@ -2501,26 +2469,58 @@
       </c>
       <c r="B38" s="32" t="inlineStr">
         <is>
-          <t>Zach</t>
-        </is>
-      </c>
-      <c r="C38" s="33" t="n"/>
+          <t>Samuel</t>
+        </is>
+      </c>
+      <c r="C38" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="D38" s="33" t="n"/>
       <c r="E38" s="33" t="n"/>
       <c r="F38" s="33" t="n"/>
-      <c r="G38" s="33" t="n"/>
+      <c r="G38" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="H38" s="33" t="n"/>
       <c r="I38" s="33" t="n"/>
-      <c r="J38" s="33" t="n"/>
+      <c r="J38" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="K38" s="33" t="n"/>
-      <c r="L38" s="33" t="n"/>
+      <c r="L38" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="M38" s="33" t="n"/>
-      <c r="N38" s="33" t="n"/>
+      <c r="N38" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="O38" s="33" t="n"/>
-      <c r="P38" s="33" t="n"/>
+      <c r="P38" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="Q38" s="33" t="n"/>
-      <c r="R38" s="33" t="n"/>
-      <c r="S38" s="33" t="n"/>
+      <c r="R38" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S38" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="T38" s="33" t="n"/>
       <c r="U38" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$T$7,C38:T38,"Y"),"")</f>
@@ -2535,97 +2535,137 @@
         <v/>
       </c>
     </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="3" t="inlineStr"/>
-      <c r="B39" s="36" t="inlineStr">
+    <row r="39" ht="17" customHeight="1">
+      <c r="A39" s="34" t="n">
+        <v>20</v>
+      </c>
+      <c r="B39" s="35" t="inlineStr">
+        <is>
+          <t>Zach</t>
+        </is>
+      </c>
+      <c r="C39" s="19" t="n"/>
+      <c r="D39" s="19" t="n"/>
+      <c r="E39" s="19" t="n"/>
+      <c r="F39" s="19" t="n"/>
+      <c r="G39" s="19" t="n"/>
+      <c r="H39" s="19" t="n"/>
+      <c r="I39" s="19" t="n"/>
+      <c r="J39" s="19" t="n"/>
+      <c r="K39" s="19" t="n"/>
+      <c r="L39" s="19" t="n"/>
+      <c r="M39" s="19" t="n"/>
+      <c r="N39" s="19" t="n"/>
+      <c r="O39" s="19" t="n"/>
+      <c r="P39" s="19" t="n"/>
+      <c r="Q39" s="19" t="n"/>
+      <c r="R39" s="19" t="n"/>
+      <c r="S39" s="19" t="n"/>
+      <c r="T39" s="19" t="n"/>
+      <c r="U39" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$T$7,C39:T39,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="V39" s="28">
+        <f>COUNTIF(C39:T39,"Y")</f>
+        <v/>
+      </c>
+      <c r="W39" s="29">
+        <f>SUMPRODUCT((C$7:$T$7=1)*(C39:T39="Y"))*50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="3" t="inlineStr"/>
+      <c r="B40" s="36" t="inlineStr">
         <is>
           <t>Total on shift</t>
         </is>
       </c>
-      <c r="C39" s="6">
-        <f>COUNTIF(C14:C38,"Y")</f>
-        <v/>
-      </c>
-      <c r="D39" s="6">
-        <f>COUNTIF(D14:D38,"Y")</f>
-        <v/>
-      </c>
-      <c r="E39" s="6">
-        <f>COUNTIF(E14:E38,"Y")</f>
-        <v/>
-      </c>
-      <c r="F39" s="6">
-        <f>COUNTIF(F14:F38,"Y")</f>
-        <v/>
-      </c>
-      <c r="G39" s="6">
-        <f>COUNTIF(G14:G38,"Y")</f>
-        <v/>
-      </c>
-      <c r="H39" s="6">
-        <f>COUNTIF(H14:H38,"Y")</f>
-        <v/>
-      </c>
-      <c r="I39" s="6">
-        <f>COUNTIF(I14:I38,"Y")</f>
-        <v/>
-      </c>
-      <c r="J39" s="6">
-        <f>COUNTIF(J14:J38,"Y")</f>
-        <v/>
-      </c>
-      <c r="K39" s="6">
-        <f>COUNTIF(K14:K38,"Y")</f>
-        <v/>
-      </c>
-      <c r="L39" s="6">
-        <f>COUNTIF(L14:L38,"Y")</f>
-        <v/>
-      </c>
-      <c r="M39" s="6">
-        <f>COUNTIF(M14:M38,"Y")</f>
-        <v/>
-      </c>
-      <c r="N39" s="6">
-        <f>COUNTIF(N14:N38,"Y")</f>
-        <v/>
-      </c>
-      <c r="O39" s="6">
-        <f>COUNTIF(O14:O38,"Y")</f>
-        <v/>
-      </c>
-      <c r="P39" s="6">
-        <f>COUNTIF(P14:P38,"Y")</f>
-        <v/>
-      </c>
-      <c r="Q39" s="6">
-        <f>COUNTIF(Q14:Q38,"Y")</f>
-        <v/>
-      </c>
-      <c r="R39" s="6">
-        <f>COUNTIF(R14:R38,"Y")</f>
-        <v/>
-      </c>
-      <c r="S39" s="6">
-        <f>COUNTIF(S14:S38,"Y")</f>
-        <v/>
-      </c>
-      <c r="T39" s="6">
-        <f>COUNTIF(T14:T38,"Y")</f>
-        <v/>
-      </c>
-      <c r="U39" s="3" t="inlineStr"/>
-      <c r="V39" s="6">
-        <f>SUM(V14:V38)</f>
-        <v/>
-      </c>
-      <c r="W39" s="37">
-        <f>SUM(W14:W38)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" ht="12" customHeight="1">
-      <c r="A40" s="38" t="inlineStr">
+      <c r="C40" s="6">
+        <f>COUNTIF(C14:C39,"Y")</f>
+        <v/>
+      </c>
+      <c r="D40" s="6">
+        <f>COUNTIF(D14:D39,"Y")</f>
+        <v/>
+      </c>
+      <c r="E40" s="6">
+        <f>COUNTIF(E14:E39,"Y")</f>
+        <v/>
+      </c>
+      <c r="F40" s="6">
+        <f>COUNTIF(F14:F39,"Y")</f>
+        <v/>
+      </c>
+      <c r="G40" s="6">
+        <f>COUNTIF(G14:G39,"Y")</f>
+        <v/>
+      </c>
+      <c r="H40" s="6">
+        <f>COUNTIF(H14:H39,"Y")</f>
+        <v/>
+      </c>
+      <c r="I40" s="6">
+        <f>COUNTIF(I14:I39,"Y")</f>
+        <v/>
+      </c>
+      <c r="J40" s="6">
+        <f>COUNTIF(J14:J39,"Y")</f>
+        <v/>
+      </c>
+      <c r="K40" s="6">
+        <f>COUNTIF(K14:K39,"Y")</f>
+        <v/>
+      </c>
+      <c r="L40" s="6">
+        <f>COUNTIF(L14:L39,"Y")</f>
+        <v/>
+      </c>
+      <c r="M40" s="6">
+        <f>COUNTIF(M14:M39,"Y")</f>
+        <v/>
+      </c>
+      <c r="N40" s="6">
+        <f>COUNTIF(N14:N39,"Y")</f>
+        <v/>
+      </c>
+      <c r="O40" s="6">
+        <f>COUNTIF(O14:O39,"Y")</f>
+        <v/>
+      </c>
+      <c r="P40" s="6">
+        <f>COUNTIF(P14:P39,"Y")</f>
+        <v/>
+      </c>
+      <c r="Q40" s="6">
+        <f>COUNTIF(Q14:Q39,"Y")</f>
+        <v/>
+      </c>
+      <c r="R40" s="6">
+        <f>COUNTIF(R14:R39,"Y")</f>
+        <v/>
+      </c>
+      <c r="S40" s="6">
+        <f>COUNTIF(S14:S39,"Y")</f>
+        <v/>
+      </c>
+      <c r="T40" s="6">
+        <f>COUNTIF(T14:T39,"Y")</f>
+        <v/>
+      </c>
+      <c r="U40" s="3" t="inlineStr"/>
+      <c r="V40" s="6">
+        <f>SUM(V14:V39)</f>
+        <v/>
+      </c>
+      <c r="W40" s="37">
+        <f>SUM(W14:W39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="12" customHeight="1">
+      <c r="A41" s="38" t="inlineStr">
         <is>
           <t>Y = on shift during shop's meal window. Personal Avg = average score of shops worked. Bonus = $50 per 100% shop worked.</t>
         </is>
@@ -2635,9 +2675,9 @@
   <mergeCells count="7">
     <mergeCell ref="A13:W13"/>
     <mergeCell ref="A1:W1"/>
-    <mergeCell ref="A40:W40"/>
     <mergeCell ref="A18:W18"/>
     <mergeCell ref="A12:W12"/>
+    <mergeCell ref="A41:W41"/>
     <mergeCell ref="A2:W2"/>
     <mergeCell ref="A19:W19"/>
   </mergeCells>
@@ -2653,7 +2693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q40"/>
+  <dimension ref="A1:Q41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3715,7 +3755,7 @@
       </c>
       <c r="B30" s="32" t="inlineStr">
         <is>
-          <t>Kable</t>
+          <t>Kaisha</t>
         </is>
       </c>
       <c r="C30" s="33" t="n"/>
@@ -3749,7 +3789,7 @@
       </c>
       <c r="B31" s="35" t="inlineStr">
         <is>
-          <t>Kayla</t>
+          <t>Kable</t>
         </is>
       </c>
       <c r="C31" s="19" t="n"/>
@@ -3783,7 +3823,7 @@
       </c>
       <c r="B32" s="32" t="inlineStr">
         <is>
-          <t>Kenzie</t>
+          <t>Kayla</t>
         </is>
       </c>
       <c r="C32" s="33" t="n"/>
@@ -3817,36 +3857,20 @@
       </c>
       <c r="B33" s="35" t="inlineStr">
         <is>
-          <t>Lidy</t>
+          <t>Kenzie</t>
         </is>
       </c>
       <c r="C33" s="19" t="n"/>
-      <c r="D33" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D33" s="19" t="n"/>
       <c r="E33" s="19" t="n"/>
       <c r="F33" s="19" t="n"/>
       <c r="G33" s="19" t="n"/>
       <c r="H33" s="19" t="n"/>
-      <c r="I33" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="I33" s="19" t="n"/>
       <c r="J33" s="19" t="n"/>
-      <c r="K33" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="K33" s="19" t="n"/>
       <c r="L33" s="19" t="n"/>
-      <c r="M33" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="M33" s="19" t="n"/>
       <c r="N33" s="19" t="n"/>
       <c r="O33" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$N$7,C33:N33,"Y"),"")</f>
@@ -3867,39 +3891,31 @@
       </c>
       <c r="B34" s="32" t="inlineStr">
         <is>
-          <t>Maylin</t>
+          <t>Lidy</t>
         </is>
       </c>
       <c r="C34" s="33" t="n"/>
-      <c r="D34" s="33" t="n"/>
-      <c r="E34" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F34" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D34" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E34" s="33" t="n"/>
+      <c r="F34" s="33" t="n"/>
       <c r="G34" s="33" t="n"/>
       <c r="H34" s="33" t="n"/>
-      <c r="I34" s="33" t="n"/>
-      <c r="J34" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="I34" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J34" s="33" t="n"/>
       <c r="K34" s="26" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="L34" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="L34" s="33" t="n"/>
       <c r="M34" s="26" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3925,37 +3941,45 @@
       </c>
       <c r="B35" s="35" t="inlineStr">
         <is>
-          <t>Mike</t>
+          <t>Maylin</t>
         </is>
       </c>
       <c r="C35" s="19" t="n"/>
       <c r="D35" s="19" t="n"/>
-      <c r="E35" s="19" t="n"/>
-      <c r="F35" s="19" t="n"/>
+      <c r="E35" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F35" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="G35" s="19" t="n"/>
       <c r="H35" s="19" t="n"/>
-      <c r="I35" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J35" s="19" t="n"/>
+      <c r="I35" s="19" t="n"/>
+      <c r="J35" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="K35" s="26" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="L35" s="19" t="n"/>
+      <c r="L35" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="M35" s="26" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="N35" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="N35" s="19" t="n"/>
       <c r="O35" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$N$7,C35:N35,"Y"),"")</f>
         <v/>
@@ -3975,7 +3999,7 @@
       </c>
       <c r="B36" s="32" t="inlineStr">
         <is>
-          <t>Richard</t>
+          <t>Mike</t>
         </is>
       </c>
       <c r="C36" s="33" t="n"/>
@@ -3984,12 +4008,28 @@
       <c r="F36" s="33" t="n"/>
       <c r="G36" s="33" t="n"/>
       <c r="H36" s="33" t="n"/>
-      <c r="I36" s="33" t="n"/>
+      <c r="I36" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="J36" s="33" t="n"/>
-      <c r="K36" s="33" t="n"/>
+      <c r="K36" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L36" s="33" t="n"/>
-      <c r="M36" s="33" t="n"/>
-      <c r="N36" s="33" t="n"/>
+      <c r="M36" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N36" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="O36" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$N$7,C36:N36,"Y"),"")</f>
         <v/>
@@ -4009,39 +4049,19 @@
       </c>
       <c r="B37" s="35" t="inlineStr">
         <is>
-          <t>Samuel</t>
+          <t>Richard</t>
         </is>
       </c>
       <c r="C37" s="19" t="n"/>
       <c r="D37" s="19" t="n"/>
-      <c r="E37" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="E37" s="19" t="n"/>
       <c r="F37" s="19" t="n"/>
-      <c r="G37" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H37" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="G37" s="19" t="n"/>
+      <c r="H37" s="19" t="n"/>
       <c r="I37" s="19" t="n"/>
-      <c r="J37" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="J37" s="19" t="n"/>
       <c r="K37" s="19" t="n"/>
-      <c r="L37" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="L37" s="19" t="n"/>
       <c r="M37" s="19" t="n"/>
       <c r="N37" s="19" t="n"/>
       <c r="O37" s="18">
@@ -4063,19 +4083,39 @@
       </c>
       <c r="B38" s="32" t="inlineStr">
         <is>
-          <t>Zach</t>
+          <t>Samuel</t>
         </is>
       </c>
       <c r="C38" s="33" t="n"/>
       <c r="D38" s="33" t="n"/>
-      <c r="E38" s="33" t="n"/>
+      <c r="E38" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F38" s="33" t="n"/>
-      <c r="G38" s="33" t="n"/>
-      <c r="H38" s="33" t="n"/>
+      <c r="G38" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H38" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I38" s="33" t="n"/>
-      <c r="J38" s="33" t="n"/>
+      <c r="J38" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="K38" s="33" t="n"/>
-      <c r="L38" s="33" t="n"/>
+      <c r="L38" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="M38" s="33" t="n"/>
       <c r="N38" s="33" t="n"/>
       <c r="O38" s="18">
@@ -4091,73 +4131,107 @@
         <v/>
       </c>
     </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="3" t="inlineStr"/>
-      <c r="B39" s="36" t="inlineStr">
+    <row r="39" ht="17" customHeight="1">
+      <c r="A39" s="34" t="n">
+        <v>20</v>
+      </c>
+      <c r="B39" s="35" t="inlineStr">
+        <is>
+          <t>Zach</t>
+        </is>
+      </c>
+      <c r="C39" s="19" t="n"/>
+      <c r="D39" s="19" t="n"/>
+      <c r="E39" s="19" t="n"/>
+      <c r="F39" s="19" t="n"/>
+      <c r="G39" s="19" t="n"/>
+      <c r="H39" s="19" t="n"/>
+      <c r="I39" s="19" t="n"/>
+      <c r="J39" s="19" t="n"/>
+      <c r="K39" s="19" t="n"/>
+      <c r="L39" s="19" t="n"/>
+      <c r="M39" s="19" t="n"/>
+      <c r="N39" s="19" t="n"/>
+      <c r="O39" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$N$7,C39:N39,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="P39" s="28">
+        <f>COUNTIF(C39:N39,"Y")</f>
+        <v/>
+      </c>
+      <c r="Q39" s="29">
+        <f>SUMPRODUCT((C$7:$N$7=1)*(C39:N39="Y"))*50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="3" t="inlineStr"/>
+      <c r="B40" s="36" t="inlineStr">
         <is>
           <t>Total on shift</t>
         </is>
       </c>
-      <c r="C39" s="6">
-        <f>COUNTIF(C14:C38,"Y")</f>
-        <v/>
-      </c>
-      <c r="D39" s="6">
-        <f>COUNTIF(D14:D38,"Y")</f>
-        <v/>
-      </c>
-      <c r="E39" s="6">
-        <f>COUNTIF(E14:E38,"Y")</f>
-        <v/>
-      </c>
-      <c r="F39" s="6">
-        <f>COUNTIF(F14:F38,"Y")</f>
-        <v/>
-      </c>
-      <c r="G39" s="6">
-        <f>COUNTIF(G14:G38,"Y")</f>
-        <v/>
-      </c>
-      <c r="H39" s="6">
-        <f>COUNTIF(H14:H38,"Y")</f>
-        <v/>
-      </c>
-      <c r="I39" s="6">
-        <f>COUNTIF(I14:I38,"Y")</f>
-        <v/>
-      </c>
-      <c r="J39" s="6">
-        <f>COUNTIF(J14:J38,"Y")</f>
-        <v/>
-      </c>
-      <c r="K39" s="6">
-        <f>COUNTIF(K14:K38,"Y")</f>
-        <v/>
-      </c>
-      <c r="L39" s="6">
-        <f>COUNTIF(L14:L38,"Y")</f>
-        <v/>
-      </c>
-      <c r="M39" s="6">
-        <f>COUNTIF(M14:M38,"Y")</f>
-        <v/>
-      </c>
-      <c r="N39" s="6">
-        <f>COUNTIF(N14:N38,"Y")</f>
-        <v/>
-      </c>
-      <c r="O39" s="3" t="inlineStr"/>
-      <c r="P39" s="6">
-        <f>SUM(P14:P38)</f>
-        <v/>
-      </c>
-      <c r="Q39" s="37">
-        <f>SUM(Q14:Q38)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" ht="12" customHeight="1">
-      <c r="A40" s="38" t="inlineStr">
+      <c r="C40" s="6">
+        <f>COUNTIF(C14:C39,"Y")</f>
+        <v/>
+      </c>
+      <c r="D40" s="6">
+        <f>COUNTIF(D14:D39,"Y")</f>
+        <v/>
+      </c>
+      <c r="E40" s="6">
+        <f>COUNTIF(E14:E39,"Y")</f>
+        <v/>
+      </c>
+      <c r="F40" s="6">
+        <f>COUNTIF(F14:F39,"Y")</f>
+        <v/>
+      </c>
+      <c r="G40" s="6">
+        <f>COUNTIF(G14:G39,"Y")</f>
+        <v/>
+      </c>
+      <c r="H40" s="6">
+        <f>COUNTIF(H14:H39,"Y")</f>
+        <v/>
+      </c>
+      <c r="I40" s="6">
+        <f>COUNTIF(I14:I39,"Y")</f>
+        <v/>
+      </c>
+      <c r="J40" s="6">
+        <f>COUNTIF(J14:J39,"Y")</f>
+        <v/>
+      </c>
+      <c r="K40" s="6">
+        <f>COUNTIF(K14:K39,"Y")</f>
+        <v/>
+      </c>
+      <c r="L40" s="6">
+        <f>COUNTIF(L14:L39,"Y")</f>
+        <v/>
+      </c>
+      <c r="M40" s="6">
+        <f>COUNTIF(M14:M39,"Y")</f>
+        <v/>
+      </c>
+      <c r="N40" s="6">
+        <f>COUNTIF(N14:N39,"Y")</f>
+        <v/>
+      </c>
+      <c r="O40" s="3" t="inlineStr"/>
+      <c r="P40" s="6">
+        <f>SUM(P14:P39)</f>
+        <v/>
+      </c>
+      <c r="Q40" s="37">
+        <f>SUM(Q14:Q39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="12" customHeight="1">
+      <c r="A41" s="38" t="inlineStr">
         <is>
           <t>Y = on shift during shop's meal window. Personal Avg = average score of shops worked. Bonus = $50 per 100% shop worked.</t>
         </is>
@@ -4165,10 +4239,10 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A40:Q40"/>
     <mergeCell ref="A18:Q18"/>
     <mergeCell ref="A12:Q12"/>
     <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A41:Q41"/>
     <mergeCell ref="A19:Q19"/>
     <mergeCell ref="A1:Q1"/>
     <mergeCell ref="A13:Q13"/>
@@ -4185,7 +4259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S40"/>
+  <dimension ref="A1:S41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -5349,7 +5423,7 @@
       </c>
       <c r="B30" s="32" t="inlineStr">
         <is>
-          <t>Kable</t>
+          <t>Kaisha</t>
         </is>
       </c>
       <c r="C30" s="33" t="n"/>
@@ -5385,7 +5459,7 @@
       </c>
       <c r="B31" s="35" t="inlineStr">
         <is>
-          <t>Kayla</t>
+          <t>Kable</t>
         </is>
       </c>
       <c r="C31" s="19" t="n"/>
@@ -5421,7 +5495,7 @@
       </c>
       <c r="B32" s="32" t="inlineStr">
         <is>
-          <t>Kenzie</t>
+          <t>Kayla</t>
         </is>
       </c>
       <c r="C32" s="33" t="n"/>
@@ -5457,43 +5531,23 @@
       </c>
       <c r="B33" s="35" t="inlineStr">
         <is>
-          <t>Lidy</t>
+          <t>Kenzie</t>
         </is>
       </c>
       <c r="C33" s="19" t="n"/>
       <c r="D33" s="19" t="n"/>
-      <c r="E33" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F33" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="E33" s="19" t="n"/>
+      <c r="F33" s="19" t="n"/>
       <c r="G33" s="19" t="n"/>
       <c r="H33" s="19" t="n"/>
       <c r="I33" s="19" t="n"/>
-      <c r="J33" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="J33" s="19" t="n"/>
       <c r="K33" s="19" t="n"/>
       <c r="L33" s="19" t="n"/>
-      <c r="M33" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="M33" s="19" t="n"/>
       <c r="N33" s="19" t="n"/>
       <c r="O33" s="19" t="n"/>
-      <c r="P33" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="P33" s="19" t="n"/>
       <c r="Q33" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$P$7,C33:P33,"Y"),"")</f>
         <v/>
@@ -5513,12 +5567,16 @@
       </c>
       <c r="B34" s="32" t="inlineStr">
         <is>
-          <t>Maylin</t>
+          <t>Lidy</t>
         </is>
       </c>
       <c r="C34" s="33" t="n"/>
       <c r="D34" s="33" t="n"/>
-      <c r="E34" s="33" t="n"/>
+      <c r="E34" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F34" s="26" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5533,26 +5591,14 @@
         </is>
       </c>
       <c r="K34" s="33" t="n"/>
-      <c r="L34" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="L34" s="33" t="n"/>
       <c r="M34" s="26" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="N34" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O34" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="N34" s="33" t="n"/>
+      <c r="O34" s="33" t="n"/>
       <c r="P34" s="26" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5577,23 +5623,51 @@
       </c>
       <c r="B35" s="35" t="inlineStr">
         <is>
-          <t>Mike</t>
+          <t>Maylin</t>
         </is>
       </c>
       <c r="C35" s="19" t="n"/>
       <c r="D35" s="19" t="n"/>
       <c r="E35" s="19" t="n"/>
-      <c r="F35" s="19" t="n"/>
+      <c r="F35" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="G35" s="19" t="n"/>
       <c r="H35" s="19" t="n"/>
       <c r="I35" s="19" t="n"/>
-      <c r="J35" s="19" t="n"/>
+      <c r="J35" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="K35" s="19" t="n"/>
-      <c r="L35" s="19" t="n"/>
-      <c r="M35" s="19" t="n"/>
-      <c r="N35" s="19" t="n"/>
-      <c r="O35" s="19" t="n"/>
-      <c r="P35" s="19" t="n"/>
+      <c r="L35" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M35" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N35" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O35" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P35" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="Q35" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$P$7,C35:P35,"Y"),"")</f>
         <v/>
@@ -5613,7 +5687,7 @@
       </c>
       <c r="B36" s="32" t="inlineStr">
         <is>
-          <t>Richard</t>
+          <t>Mike</t>
         </is>
       </c>
       <c r="C36" s="33" t="n"/>
@@ -5649,31 +5723,19 @@
       </c>
       <c r="B37" s="35" t="inlineStr">
         <is>
-          <t>Samuel</t>
+          <t>Richard</t>
         </is>
       </c>
       <c r="C37" s="19" t="n"/>
-      <c r="D37" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D37" s="19" t="n"/>
       <c r="E37" s="19" t="n"/>
       <c r="F37" s="19" t="n"/>
       <c r="G37" s="19" t="n"/>
-      <c r="H37" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="H37" s="19" t="n"/>
       <c r="I37" s="19" t="n"/>
       <c r="J37" s="19" t="n"/>
       <c r="K37" s="19" t="n"/>
-      <c r="L37" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="L37" s="19" t="n"/>
       <c r="M37" s="19" t="n"/>
       <c r="N37" s="19" t="n"/>
       <c r="O37" s="19" t="n"/>
@@ -5697,19 +5759,31 @@
       </c>
       <c r="B38" s="32" t="inlineStr">
         <is>
-          <t>Zach</t>
+          <t>Samuel</t>
         </is>
       </c>
       <c r="C38" s="33" t="n"/>
-      <c r="D38" s="33" t="n"/>
+      <c r="D38" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E38" s="33" t="n"/>
       <c r="F38" s="33" t="n"/>
       <c r="G38" s="33" t="n"/>
-      <c r="H38" s="33" t="n"/>
+      <c r="H38" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I38" s="33" t="n"/>
       <c r="J38" s="33" t="n"/>
       <c r="K38" s="33" t="n"/>
-      <c r="L38" s="33" t="n"/>
+      <c r="L38" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="M38" s="33" t="n"/>
       <c r="N38" s="33" t="n"/>
       <c r="O38" s="33" t="n"/>
@@ -5727,81 +5801,117 @@
         <v/>
       </c>
     </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="3" t="inlineStr"/>
-      <c r="B39" s="36" t="inlineStr">
+    <row r="39" ht="17" customHeight="1">
+      <c r="A39" s="34" t="n">
+        <v>20</v>
+      </c>
+      <c r="B39" s="35" t="inlineStr">
+        <is>
+          <t>Zach</t>
+        </is>
+      </c>
+      <c r="C39" s="19" t="n"/>
+      <c r="D39" s="19" t="n"/>
+      <c r="E39" s="19" t="n"/>
+      <c r="F39" s="19" t="n"/>
+      <c r="G39" s="19" t="n"/>
+      <c r="H39" s="19" t="n"/>
+      <c r="I39" s="19" t="n"/>
+      <c r="J39" s="19" t="n"/>
+      <c r="K39" s="19" t="n"/>
+      <c r="L39" s="19" t="n"/>
+      <c r="M39" s="19" t="n"/>
+      <c r="N39" s="19" t="n"/>
+      <c r="O39" s="19" t="n"/>
+      <c r="P39" s="19" t="n"/>
+      <c r="Q39" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$P$7,C39:P39,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="R39" s="28">
+        <f>COUNTIF(C39:P39,"Y")</f>
+        <v/>
+      </c>
+      <c r="S39" s="29">
+        <f>SUMPRODUCT((C$7:$P$7=1)*(C39:P39="Y"))*50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="3" t="inlineStr"/>
+      <c r="B40" s="36" t="inlineStr">
         <is>
           <t>Total on shift</t>
         </is>
       </c>
-      <c r="C39" s="6">
-        <f>COUNTIF(C14:C38,"Y")</f>
-        <v/>
-      </c>
-      <c r="D39" s="6">
-        <f>COUNTIF(D14:D38,"Y")</f>
-        <v/>
-      </c>
-      <c r="E39" s="6">
-        <f>COUNTIF(E14:E38,"Y")</f>
-        <v/>
-      </c>
-      <c r="F39" s="6">
-        <f>COUNTIF(F14:F38,"Y")</f>
-        <v/>
-      </c>
-      <c r="G39" s="6">
-        <f>COUNTIF(G14:G38,"Y")</f>
-        <v/>
-      </c>
-      <c r="H39" s="6">
-        <f>COUNTIF(H14:H38,"Y")</f>
-        <v/>
-      </c>
-      <c r="I39" s="6">
-        <f>COUNTIF(I14:I38,"Y")</f>
-        <v/>
-      </c>
-      <c r="J39" s="6">
-        <f>COUNTIF(J14:J38,"Y")</f>
-        <v/>
-      </c>
-      <c r="K39" s="6">
-        <f>COUNTIF(K14:K38,"Y")</f>
-        <v/>
-      </c>
-      <c r="L39" s="6">
-        <f>COUNTIF(L14:L38,"Y")</f>
-        <v/>
-      </c>
-      <c r="M39" s="6">
-        <f>COUNTIF(M14:M38,"Y")</f>
-        <v/>
-      </c>
-      <c r="N39" s="6">
-        <f>COUNTIF(N14:N38,"Y")</f>
-        <v/>
-      </c>
-      <c r="O39" s="6">
-        <f>COUNTIF(O14:O38,"Y")</f>
-        <v/>
-      </c>
-      <c r="P39" s="6">
-        <f>COUNTIF(P14:P38,"Y")</f>
-        <v/>
-      </c>
-      <c r="Q39" s="3" t="inlineStr"/>
-      <c r="R39" s="6">
-        <f>SUM(R14:R38)</f>
-        <v/>
-      </c>
-      <c r="S39" s="37">
-        <f>SUM(S14:S38)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" ht="12" customHeight="1">
-      <c r="A40" s="38" t="inlineStr">
+      <c r="C40" s="6">
+        <f>COUNTIF(C14:C39,"Y")</f>
+        <v/>
+      </c>
+      <c r="D40" s="6">
+        <f>COUNTIF(D14:D39,"Y")</f>
+        <v/>
+      </c>
+      <c r="E40" s="6">
+        <f>COUNTIF(E14:E39,"Y")</f>
+        <v/>
+      </c>
+      <c r="F40" s="6">
+        <f>COUNTIF(F14:F39,"Y")</f>
+        <v/>
+      </c>
+      <c r="G40" s="6">
+        <f>COUNTIF(G14:G39,"Y")</f>
+        <v/>
+      </c>
+      <c r="H40" s="6">
+        <f>COUNTIF(H14:H39,"Y")</f>
+        <v/>
+      </c>
+      <c r="I40" s="6">
+        <f>COUNTIF(I14:I39,"Y")</f>
+        <v/>
+      </c>
+      <c r="J40" s="6">
+        <f>COUNTIF(J14:J39,"Y")</f>
+        <v/>
+      </c>
+      <c r="K40" s="6">
+        <f>COUNTIF(K14:K39,"Y")</f>
+        <v/>
+      </c>
+      <c r="L40" s="6">
+        <f>COUNTIF(L14:L39,"Y")</f>
+        <v/>
+      </c>
+      <c r="M40" s="6">
+        <f>COUNTIF(M14:M39,"Y")</f>
+        <v/>
+      </c>
+      <c r="N40" s="6">
+        <f>COUNTIF(N14:N39,"Y")</f>
+        <v/>
+      </c>
+      <c r="O40" s="6">
+        <f>COUNTIF(O14:O39,"Y")</f>
+        <v/>
+      </c>
+      <c r="P40" s="6">
+        <f>COUNTIF(P14:P39,"Y")</f>
+        <v/>
+      </c>
+      <c r="Q40" s="3" t="inlineStr"/>
+      <c r="R40" s="6">
+        <f>SUM(R14:R39)</f>
+        <v/>
+      </c>
+      <c r="S40" s="37">
+        <f>SUM(S14:S39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="12" customHeight="1">
+      <c r="A41" s="38" t="inlineStr">
         <is>
           <t>Y = on shift during shop's meal window. Personal Avg = average score of shops worked. Bonus = $50 per 100% shop worked.</t>
         </is>
@@ -5809,10 +5919,10 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="A41:S41"/>
     <mergeCell ref="A19:S19"/>
     <mergeCell ref="A13:S13"/>
     <mergeCell ref="A1:S1"/>
-    <mergeCell ref="A40:S40"/>
     <mergeCell ref="A18:S18"/>
     <mergeCell ref="A12:S12"/>
     <mergeCell ref="A2:S2"/>
@@ -5829,7 +5939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R40"/>
+  <dimension ref="A1:R41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -6960,7 +7070,7 @@
       </c>
       <c r="B30" s="32" t="inlineStr">
         <is>
-          <t>Kable</t>
+          <t>Kaisha</t>
         </is>
       </c>
       <c r="C30" s="33" t="n"/>
@@ -6995,7 +7105,7 @@
       </c>
       <c r="B31" s="35" t="inlineStr">
         <is>
-          <t>Kayla</t>
+          <t>Kable</t>
         </is>
       </c>
       <c r="C31" s="19" t="n"/>
@@ -7030,7 +7140,7 @@
       </c>
       <c r="B32" s="32" t="inlineStr">
         <is>
-          <t>Kenzie</t>
+          <t>Kayla</t>
         </is>
       </c>
       <c r="C32" s="33" t="n"/>
@@ -7065,46 +7175,22 @@
       </c>
       <c r="B33" s="35" t="inlineStr">
         <is>
-          <t>Lidy</t>
-        </is>
-      </c>
-      <c r="C33" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>Kenzie</t>
+        </is>
+      </c>
+      <c r="C33" s="19" t="n"/>
       <c r="D33" s="19" t="n"/>
       <c r="E33" s="19" t="n"/>
-      <c r="F33" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="F33" s="19" t="n"/>
       <c r="G33" s="19" t="n"/>
       <c r="H33" s="19" t="n"/>
-      <c r="I33" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="I33" s="19" t="n"/>
       <c r="J33" s="19" t="n"/>
-      <c r="K33" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="K33" s="19" t="n"/>
       <c r="L33" s="19" t="n"/>
-      <c r="M33" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="M33" s="19" t="n"/>
       <c r="N33" s="19" t="n"/>
-      <c r="O33" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O33" s="19" t="n"/>
       <c r="P33" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$O$7,C33:O33,"Y"),"")</f>
         <v/>
@@ -7124,10 +7210,14 @@
       </c>
       <c r="B34" s="32" t="inlineStr">
         <is>
-          <t>Maylin</t>
-        </is>
-      </c>
-      <c r="C34" s="33" t="n"/>
+          <t>Lidy</t>
+        </is>
+      </c>
+      <c r="C34" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="D34" s="33" t="n"/>
       <c r="E34" s="33" t="n"/>
       <c r="F34" s="26" t="inlineStr">
@@ -7142,20 +7232,24 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="J34" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K34" s="33" t="n"/>
+      <c r="J34" s="33" t="n"/>
+      <c r="K34" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L34" s="33" t="n"/>
-      <c r="M34" s="33" t="n"/>
-      <c r="N34" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O34" s="33" t="n"/>
+      <c r="M34" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N34" s="33" t="n"/>
+      <c r="O34" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P34" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$O$7,C34:O34,"Y"),"")</f>
         <v/>
@@ -7175,21 +7269,37 @@
       </c>
       <c r="B35" s="35" t="inlineStr">
         <is>
-          <t>Mike</t>
+          <t>Maylin</t>
         </is>
       </c>
       <c r="C35" s="19" t="n"/>
       <c r="D35" s="19" t="n"/>
       <c r="E35" s="19" t="n"/>
-      <c r="F35" s="19" t="n"/>
+      <c r="F35" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="G35" s="19" t="n"/>
       <c r="H35" s="19" t="n"/>
-      <c r="I35" s="19" t="n"/>
-      <c r="J35" s="19" t="n"/>
+      <c r="I35" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J35" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="K35" s="19" t="n"/>
       <c r="L35" s="19" t="n"/>
       <c r="M35" s="19" t="n"/>
-      <c r="N35" s="19" t="n"/>
+      <c r="N35" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="O35" s="19" t="n"/>
       <c r="P35" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$O$7,C35:O35,"Y"),"")</f>
@@ -7210,7 +7320,7 @@
       </c>
       <c r="B36" s="32" t="inlineStr">
         <is>
-          <t>Richard</t>
+          <t>Mike</t>
         </is>
       </c>
       <c r="C36" s="33" t="n"/>
@@ -7220,27 +7330,11 @@
       <c r="G36" s="33" t="n"/>
       <c r="H36" s="33" t="n"/>
       <c r="I36" s="33" t="n"/>
-      <c r="J36" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="J36" s="33" t="n"/>
       <c r="K36" s="33" t="n"/>
-      <c r="L36" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M36" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N36" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="L36" s="33" t="n"/>
+      <c r="M36" s="33" t="n"/>
+      <c r="N36" s="33" t="n"/>
       <c r="O36" s="33" t="n"/>
       <c r="P36" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$O$7,C36:O36,"Y"),"")</f>
@@ -7261,27 +7355,15 @@
       </c>
       <c r="B37" s="35" t="inlineStr">
         <is>
-          <t>Samuel</t>
+          <t>Richard</t>
         </is>
       </c>
       <c r="C37" s="19" t="n"/>
       <c r="D37" s="19" t="n"/>
-      <c r="E37" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="E37" s="19" t="n"/>
       <c r="F37" s="19" t="n"/>
-      <c r="G37" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H37" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="G37" s="19" t="n"/>
+      <c r="H37" s="19" t="n"/>
       <c r="I37" s="19" t="n"/>
       <c r="J37" s="26" t="inlineStr">
         <is>
@@ -7289,9 +7371,21 @@
         </is>
       </c>
       <c r="K37" s="19" t="n"/>
-      <c r="L37" s="19" t="n"/>
-      <c r="M37" s="19" t="n"/>
-      <c r="N37" s="19" t="n"/>
+      <c r="L37" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M37" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N37" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="O37" s="19" t="n"/>
       <c r="P37" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$O$7,C37:O37,"Y"),"")</f>
@@ -7312,17 +7406,33 @@
       </c>
       <c r="B38" s="32" t="inlineStr">
         <is>
-          <t>Zach</t>
+          <t>Samuel</t>
         </is>
       </c>
       <c r="C38" s="33" t="n"/>
       <c r="D38" s="33" t="n"/>
-      <c r="E38" s="33" t="n"/>
+      <c r="E38" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F38" s="33" t="n"/>
-      <c r="G38" s="33" t="n"/>
-      <c r="H38" s="33" t="n"/>
+      <c r="G38" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H38" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I38" s="33" t="n"/>
-      <c r="J38" s="33" t="n"/>
+      <c r="J38" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="K38" s="33" t="n"/>
       <c r="L38" s="33" t="n"/>
       <c r="M38" s="33" t="n"/>
@@ -7341,77 +7451,112 @@
         <v/>
       </c>
     </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="3" t="inlineStr"/>
-      <c r="B39" s="36" t="inlineStr">
+    <row r="39" ht="17" customHeight="1">
+      <c r="A39" s="34" t="n">
+        <v>20</v>
+      </c>
+      <c r="B39" s="35" t="inlineStr">
+        <is>
+          <t>Zach</t>
+        </is>
+      </c>
+      <c r="C39" s="19" t="n"/>
+      <c r="D39" s="19" t="n"/>
+      <c r="E39" s="19" t="n"/>
+      <c r="F39" s="19" t="n"/>
+      <c r="G39" s="19" t="n"/>
+      <c r="H39" s="19" t="n"/>
+      <c r="I39" s="19" t="n"/>
+      <c r="J39" s="19" t="n"/>
+      <c r="K39" s="19" t="n"/>
+      <c r="L39" s="19" t="n"/>
+      <c r="M39" s="19" t="n"/>
+      <c r="N39" s="19" t="n"/>
+      <c r="O39" s="19" t="n"/>
+      <c r="P39" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$O$7,C39:O39,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="Q39" s="28">
+        <f>COUNTIF(C39:O39,"Y")</f>
+        <v/>
+      </c>
+      <c r="R39" s="29">
+        <f>SUMPRODUCT((C$7:$O$7=1)*(C39:O39="Y"))*50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="3" t="inlineStr"/>
+      <c r="B40" s="36" t="inlineStr">
         <is>
           <t>Total on shift</t>
         </is>
       </c>
-      <c r="C39" s="6">
-        <f>COUNTIF(C14:C38,"Y")</f>
-        <v/>
-      </c>
-      <c r="D39" s="6">
-        <f>COUNTIF(D14:D38,"Y")</f>
-        <v/>
-      </c>
-      <c r="E39" s="6">
-        <f>COUNTIF(E14:E38,"Y")</f>
-        <v/>
-      </c>
-      <c r="F39" s="6">
-        <f>COUNTIF(F14:F38,"Y")</f>
-        <v/>
-      </c>
-      <c r="G39" s="6">
-        <f>COUNTIF(G14:G38,"Y")</f>
-        <v/>
-      </c>
-      <c r="H39" s="6">
-        <f>COUNTIF(H14:H38,"Y")</f>
-        <v/>
-      </c>
-      <c r="I39" s="6">
-        <f>COUNTIF(I14:I38,"Y")</f>
-        <v/>
-      </c>
-      <c r="J39" s="6">
-        <f>COUNTIF(J14:J38,"Y")</f>
-        <v/>
-      </c>
-      <c r="K39" s="6">
-        <f>COUNTIF(K14:K38,"Y")</f>
-        <v/>
-      </c>
-      <c r="L39" s="6">
-        <f>COUNTIF(L14:L38,"Y")</f>
-        <v/>
-      </c>
-      <c r="M39" s="6">
-        <f>COUNTIF(M14:M38,"Y")</f>
-        <v/>
-      </c>
-      <c r="N39" s="6">
-        <f>COUNTIF(N14:N38,"Y")</f>
-        <v/>
-      </c>
-      <c r="O39" s="6">
-        <f>COUNTIF(O14:O38,"Y")</f>
-        <v/>
-      </c>
-      <c r="P39" s="3" t="inlineStr"/>
-      <c r="Q39" s="6">
-        <f>SUM(Q14:Q38)</f>
-        <v/>
-      </c>
-      <c r="R39" s="37">
-        <f>SUM(R14:R38)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" ht="12" customHeight="1">
-      <c r="A40" s="38" t="inlineStr">
+      <c r="C40" s="6">
+        <f>COUNTIF(C14:C39,"Y")</f>
+        <v/>
+      </c>
+      <c r="D40" s="6">
+        <f>COUNTIF(D14:D39,"Y")</f>
+        <v/>
+      </c>
+      <c r="E40" s="6">
+        <f>COUNTIF(E14:E39,"Y")</f>
+        <v/>
+      </c>
+      <c r="F40" s="6">
+        <f>COUNTIF(F14:F39,"Y")</f>
+        <v/>
+      </c>
+      <c r="G40" s="6">
+        <f>COUNTIF(G14:G39,"Y")</f>
+        <v/>
+      </c>
+      <c r="H40" s="6">
+        <f>COUNTIF(H14:H39,"Y")</f>
+        <v/>
+      </c>
+      <c r="I40" s="6">
+        <f>COUNTIF(I14:I39,"Y")</f>
+        <v/>
+      </c>
+      <c r="J40" s="6">
+        <f>COUNTIF(J14:J39,"Y")</f>
+        <v/>
+      </c>
+      <c r="K40" s="6">
+        <f>COUNTIF(K14:K39,"Y")</f>
+        <v/>
+      </c>
+      <c r="L40" s="6">
+        <f>COUNTIF(L14:L39,"Y")</f>
+        <v/>
+      </c>
+      <c r="M40" s="6">
+        <f>COUNTIF(M14:M39,"Y")</f>
+        <v/>
+      </c>
+      <c r="N40" s="6">
+        <f>COUNTIF(N14:N39,"Y")</f>
+        <v/>
+      </c>
+      <c r="O40" s="6">
+        <f>COUNTIF(O14:O39,"Y")</f>
+        <v/>
+      </c>
+      <c r="P40" s="3" t="inlineStr"/>
+      <c r="Q40" s="6">
+        <f>SUM(Q14:Q39)</f>
+        <v/>
+      </c>
+      <c r="R40" s="37">
+        <f>SUM(R14:R39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="12" customHeight="1">
+      <c r="A41" s="38" t="inlineStr">
         <is>
           <t>Y = on shift during shop's meal window. Personal Avg = average score of shops worked. Bonus = $50 per 100% shop worked.</t>
         </is>
@@ -7420,11 +7565,11 @@
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A18:R18"/>
+    <mergeCell ref="A41:R41"/>
     <mergeCell ref="A2:R2"/>
     <mergeCell ref="A19:R19"/>
     <mergeCell ref="A13:R13"/>
     <mergeCell ref="A1:R1"/>
-    <mergeCell ref="A40:R40"/>
     <mergeCell ref="A12:R12"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
@@ -7439,7 +7584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S40"/>
+  <dimension ref="A1:S41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -8587,7 +8732,7 @@
       </c>
       <c r="B30" s="32" t="inlineStr">
         <is>
-          <t>Kable</t>
+          <t>Kaisha</t>
         </is>
       </c>
       <c r="C30" s="33" t="n"/>
@@ -8623,7 +8768,7 @@
       </c>
       <c r="B31" s="35" t="inlineStr">
         <is>
-          <t>Kayla</t>
+          <t>Kable</t>
         </is>
       </c>
       <c r="C31" s="19" t="n"/>
@@ -8659,7 +8804,7 @@
       </c>
       <c r="B32" s="32" t="inlineStr">
         <is>
-          <t>Kenzie</t>
+          <t>Kayla</t>
         </is>
       </c>
       <c r="C32" s="33" t="n"/>
@@ -8695,42 +8840,22 @@
       </c>
       <c r="B33" s="35" t="inlineStr">
         <is>
-          <t>Lidy</t>
+          <t>Kenzie</t>
         </is>
       </c>
       <c r="C33" s="19" t="n"/>
-      <c r="D33" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D33" s="19" t="n"/>
       <c r="E33" s="19" t="n"/>
       <c r="F33" s="19" t="n"/>
       <c r="G33" s="19" t="n"/>
       <c r="H33" s="19" t="n"/>
       <c r="I33" s="19" t="n"/>
-      <c r="J33" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K33" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="J33" s="19" t="n"/>
+      <c r="K33" s="19" t="n"/>
       <c r="L33" s="19" t="n"/>
-      <c r="M33" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="M33" s="19" t="n"/>
       <c r="N33" s="19" t="n"/>
-      <c r="O33" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O33" s="19" t="n"/>
       <c r="P33" s="19" t="n"/>
       <c r="Q33" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$P$7,C33:P33,"Y"),"")</f>
@@ -8751,7 +8876,7 @@
       </c>
       <c r="B34" s="32" t="inlineStr">
         <is>
-          <t>Maylin</t>
+          <t>Lidy</t>
         </is>
       </c>
       <c r="C34" s="33" t="n"/>
@@ -8765,25 +8890,29 @@
       <c r="G34" s="33" t="n"/>
       <c r="H34" s="33" t="n"/>
       <c r="I34" s="33" t="n"/>
-      <c r="J34" s="33" t="n"/>
-      <c r="K34" s="33" t="n"/>
-      <c r="L34" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M34" s="33" t="n"/>
+      <c r="J34" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K34" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L34" s="33" t="n"/>
+      <c r="M34" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="N34" s="33" t="n"/>
       <c r="O34" s="26" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="P34" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="P34" s="33" t="n"/>
       <c r="Q34" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$P$7,C34:P34,"Y"),"")</f>
         <v/>
@@ -8803,11 +8932,15 @@
       </c>
       <c r="B35" s="35" t="inlineStr">
         <is>
-          <t>Mike</t>
+          <t>Maylin</t>
         </is>
       </c>
       <c r="C35" s="19" t="n"/>
-      <c r="D35" s="19" t="n"/>
+      <c r="D35" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E35" s="19" t="n"/>
       <c r="F35" s="19" t="n"/>
       <c r="G35" s="19" t="n"/>
@@ -8815,11 +8948,23 @@
       <c r="I35" s="19" t="n"/>
       <c r="J35" s="19" t="n"/>
       <c r="K35" s="19" t="n"/>
-      <c r="L35" s="19" t="n"/>
+      <c r="L35" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="M35" s="19" t="n"/>
       <c r="N35" s="19" t="n"/>
-      <c r="O35" s="19" t="n"/>
-      <c r="P35" s="19" t="n"/>
+      <c r="O35" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P35" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="Q35" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$P$7,C35:P35,"Y"),"")</f>
         <v/>
@@ -8839,7 +8984,7 @@
       </c>
       <c r="B36" s="32" t="inlineStr">
         <is>
-          <t>Richard</t>
+          <t>Mike</t>
         </is>
       </c>
       <c r="C36" s="33" t="n"/>
@@ -8852,11 +8997,7 @@
       <c r="J36" s="33" t="n"/>
       <c r="K36" s="33" t="n"/>
       <c r="L36" s="33" t="n"/>
-      <c r="M36" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="M36" s="33" t="n"/>
       <c r="N36" s="33" t="n"/>
       <c r="O36" s="33" t="n"/>
       <c r="P36" s="33" t="n"/>
@@ -8879,32 +9020,24 @@
       </c>
       <c r="B37" s="35" t="inlineStr">
         <is>
-          <t>Samuel</t>
-        </is>
-      </c>
-      <c r="C37" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>Richard</t>
+        </is>
+      </c>
+      <c r="C37" s="19" t="n"/>
       <c r="D37" s="19" t="n"/>
-      <c r="E37" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="E37" s="19" t="n"/>
       <c r="F37" s="19" t="n"/>
       <c r="G37" s="19" t="n"/>
       <c r="H37" s="19" t="n"/>
-      <c r="I37" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="I37" s="19" t="n"/>
       <c r="J37" s="19" t="n"/>
       <c r="K37" s="19" t="n"/>
       <c r="L37" s="19" t="n"/>
-      <c r="M37" s="19" t="n"/>
+      <c r="M37" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="N37" s="19" t="n"/>
       <c r="O37" s="19" t="n"/>
       <c r="P37" s="19" t="n"/>
@@ -8927,16 +9060,28 @@
       </c>
       <c r="B38" s="32" t="inlineStr">
         <is>
-          <t>Zach</t>
-        </is>
-      </c>
-      <c r="C38" s="33" t="n"/>
+          <t>Samuel</t>
+        </is>
+      </c>
+      <c r="C38" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="D38" s="33" t="n"/>
-      <c r="E38" s="33" t="n"/>
+      <c r="E38" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F38" s="33" t="n"/>
       <c r="G38" s="33" t="n"/>
       <c r="H38" s="33" t="n"/>
-      <c r="I38" s="33" t="n"/>
+      <c r="I38" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="J38" s="33" t="n"/>
       <c r="K38" s="33" t="n"/>
       <c r="L38" s="33" t="n"/>
@@ -8957,81 +9102,117 @@
         <v/>
       </c>
     </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="3" t="inlineStr"/>
-      <c r="B39" s="36" t="inlineStr">
+    <row r="39" ht="17" customHeight="1">
+      <c r="A39" s="34" t="n">
+        <v>20</v>
+      </c>
+      <c r="B39" s="35" t="inlineStr">
+        <is>
+          <t>Zach</t>
+        </is>
+      </c>
+      <c r="C39" s="19" t="n"/>
+      <c r="D39" s="19" t="n"/>
+      <c r="E39" s="19" t="n"/>
+      <c r="F39" s="19" t="n"/>
+      <c r="G39" s="19" t="n"/>
+      <c r="H39" s="19" t="n"/>
+      <c r="I39" s="19" t="n"/>
+      <c r="J39" s="19" t="n"/>
+      <c r="K39" s="19" t="n"/>
+      <c r="L39" s="19" t="n"/>
+      <c r="M39" s="19" t="n"/>
+      <c r="N39" s="19" t="n"/>
+      <c r="O39" s="19" t="n"/>
+      <c r="P39" s="19" t="n"/>
+      <c r="Q39" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$P$7,C39:P39,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="R39" s="28">
+        <f>COUNTIF(C39:P39,"Y")</f>
+        <v/>
+      </c>
+      <c r="S39" s="29">
+        <f>SUMPRODUCT((C$7:$P$7=1)*(C39:P39="Y"))*50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="3" t="inlineStr"/>
+      <c r="B40" s="36" t="inlineStr">
         <is>
           <t>Total on shift</t>
         </is>
       </c>
-      <c r="C39" s="6">
-        <f>COUNTIF(C14:C38,"Y")</f>
-        <v/>
-      </c>
-      <c r="D39" s="6">
-        <f>COUNTIF(D14:D38,"Y")</f>
-        <v/>
-      </c>
-      <c r="E39" s="6">
-        <f>COUNTIF(E14:E38,"Y")</f>
-        <v/>
-      </c>
-      <c r="F39" s="6">
-        <f>COUNTIF(F14:F38,"Y")</f>
-        <v/>
-      </c>
-      <c r="G39" s="6">
-        <f>COUNTIF(G14:G38,"Y")</f>
-        <v/>
-      </c>
-      <c r="H39" s="6">
-        <f>COUNTIF(H14:H38,"Y")</f>
-        <v/>
-      </c>
-      <c r="I39" s="6">
-        <f>COUNTIF(I14:I38,"Y")</f>
-        <v/>
-      </c>
-      <c r="J39" s="6">
-        <f>COUNTIF(J14:J38,"Y")</f>
-        <v/>
-      </c>
-      <c r="K39" s="6">
-        <f>COUNTIF(K14:K38,"Y")</f>
-        <v/>
-      </c>
-      <c r="L39" s="6">
-        <f>COUNTIF(L14:L38,"Y")</f>
-        <v/>
-      </c>
-      <c r="M39" s="6">
-        <f>COUNTIF(M14:M38,"Y")</f>
-        <v/>
-      </c>
-      <c r="N39" s="6">
-        <f>COUNTIF(N14:N38,"Y")</f>
-        <v/>
-      </c>
-      <c r="O39" s="6">
-        <f>COUNTIF(O14:O38,"Y")</f>
-        <v/>
-      </c>
-      <c r="P39" s="6">
-        <f>COUNTIF(P14:P38,"Y")</f>
-        <v/>
-      </c>
-      <c r="Q39" s="3" t="inlineStr"/>
-      <c r="R39" s="6">
-        <f>SUM(R14:R38)</f>
-        <v/>
-      </c>
-      <c r="S39" s="37">
-        <f>SUM(S14:S38)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" ht="12" customHeight="1">
-      <c r="A40" s="38" t="inlineStr">
+      <c r="C40" s="6">
+        <f>COUNTIF(C14:C39,"Y")</f>
+        <v/>
+      </c>
+      <c r="D40" s="6">
+        <f>COUNTIF(D14:D39,"Y")</f>
+        <v/>
+      </c>
+      <c r="E40" s="6">
+        <f>COUNTIF(E14:E39,"Y")</f>
+        <v/>
+      </c>
+      <c r="F40" s="6">
+        <f>COUNTIF(F14:F39,"Y")</f>
+        <v/>
+      </c>
+      <c r="G40" s="6">
+        <f>COUNTIF(G14:G39,"Y")</f>
+        <v/>
+      </c>
+      <c r="H40" s="6">
+        <f>COUNTIF(H14:H39,"Y")</f>
+        <v/>
+      </c>
+      <c r="I40" s="6">
+        <f>COUNTIF(I14:I39,"Y")</f>
+        <v/>
+      </c>
+      <c r="J40" s="6">
+        <f>COUNTIF(J14:J39,"Y")</f>
+        <v/>
+      </c>
+      <c r="K40" s="6">
+        <f>COUNTIF(K14:K39,"Y")</f>
+        <v/>
+      </c>
+      <c r="L40" s="6">
+        <f>COUNTIF(L14:L39,"Y")</f>
+        <v/>
+      </c>
+      <c r="M40" s="6">
+        <f>COUNTIF(M14:M39,"Y")</f>
+        <v/>
+      </c>
+      <c r="N40" s="6">
+        <f>COUNTIF(N14:N39,"Y")</f>
+        <v/>
+      </c>
+      <c r="O40" s="6">
+        <f>COUNTIF(O14:O39,"Y")</f>
+        <v/>
+      </c>
+      <c r="P40" s="6">
+        <f>COUNTIF(P14:P39,"Y")</f>
+        <v/>
+      </c>
+      <c r="Q40" s="3" t="inlineStr"/>
+      <c r="R40" s="6">
+        <f>SUM(R14:R39)</f>
+        <v/>
+      </c>
+      <c r="S40" s="37">
+        <f>SUM(S14:S39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="12" customHeight="1">
+      <c r="A41" s="38" t="inlineStr">
         <is>
           <t>Y = on shift during shop's meal window. Personal Avg = average score of shops worked. Bonus = $50 per 100% shop worked.</t>
         </is>
@@ -9039,10 +9220,10 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="A41:S41"/>
     <mergeCell ref="A19:S19"/>
     <mergeCell ref="A13:S13"/>
     <mergeCell ref="A1:S1"/>
-    <mergeCell ref="A40:S40"/>
     <mergeCell ref="A18:S18"/>
     <mergeCell ref="A12:S12"/>
     <mergeCell ref="A2:S2"/>
@@ -9059,7 +9240,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P40"/>
+  <dimension ref="A1:P41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -9550,7 +9731,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M15" s="27" t="n"/>
+      <c r="M15" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="N15" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$M$7,C15:M15,"Y"),"")</f>
         <v/>
@@ -9583,11 +9768,7 @@
       <c r="J16" s="27" t="n"/>
       <c r="K16" s="27" t="n"/>
       <c r="L16" s="27" t="n"/>
-      <c r="M16" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="M16" s="27" t="n"/>
       <c r="N16" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$M$7,C16:M16,"Y"),"")</f>
         <v/>
@@ -9620,11 +9801,7 @@
       <c r="J17" s="27" t="n"/>
       <c r="K17" s="27" t="n"/>
       <c r="L17" s="27" t="n"/>
-      <c r="M17" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="M17" s="27" t="n"/>
       <c r="N17" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$M$7,C17:M17,"Y"),"")</f>
         <v/>
@@ -9770,7 +9947,11 @@
       <c r="J23" s="19" t="n"/>
       <c r="K23" s="19" t="n"/>
       <c r="L23" s="19" t="n"/>
-      <c r="M23" s="19" t="n"/>
+      <c r="M23" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="N23" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$M$7,C23:M23,"Y"),"")</f>
         <v/>
@@ -9947,11 +10128,7 @@
       <c r="J28" s="33" t="n"/>
       <c r="K28" s="33" t="n"/>
       <c r="L28" s="33" t="n"/>
-      <c r="M28" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="M28" s="33" t="n"/>
       <c r="N28" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$M$7,C28:M28,"Y"),"")</f>
         <v/>
@@ -10016,7 +10193,7 @@
       </c>
       <c r="B30" s="32" t="inlineStr">
         <is>
-          <t>Kable</t>
+          <t>Kaisha</t>
         </is>
       </c>
       <c r="C30" s="33" t="n"/>
@@ -10029,7 +10206,11 @@
       <c r="J30" s="33" t="n"/>
       <c r="K30" s="33" t="n"/>
       <c r="L30" s="33" t="n"/>
-      <c r="M30" s="33" t="n"/>
+      <c r="M30" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="N30" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$M$7,C30:M30,"Y"),"")</f>
         <v/>
@@ -10049,7 +10230,7 @@
       </c>
       <c r="B31" s="35" t="inlineStr">
         <is>
-          <t>Kayla</t>
+          <t>Kable</t>
         </is>
       </c>
       <c r="C31" s="19" t="n"/>
@@ -10082,7 +10263,7 @@
       </c>
       <c r="B32" s="32" t="inlineStr">
         <is>
-          <t>Kenzie</t>
+          <t>Kayla</t>
         </is>
       </c>
       <c r="C32" s="33" t="n"/>
@@ -10115,44 +10296,20 @@
       </c>
       <c r="B33" s="35" t="inlineStr">
         <is>
-          <t>Lidy</t>
+          <t>Kenzie</t>
         </is>
       </c>
       <c r="C33" s="19" t="n"/>
-      <c r="D33" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D33" s="19" t="n"/>
       <c r="E33" s="19" t="n"/>
-      <c r="F33" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="F33" s="19" t="n"/>
       <c r="G33" s="19" t="n"/>
-      <c r="H33" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="H33" s="19" t="n"/>
       <c r="I33" s="19" t="n"/>
-      <c r="J33" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="J33" s="19" t="n"/>
       <c r="K33" s="19" t="n"/>
-      <c r="L33" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M33" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="L33" s="19" t="n"/>
+      <c r="M33" s="19" t="n"/>
       <c r="N33" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$M$7,C33:M33,"Y"),"")</f>
         <v/>
@@ -10172,32 +10329,44 @@
       </c>
       <c r="B34" s="32" t="inlineStr">
         <is>
-          <t>Maylin</t>
-        </is>
-      </c>
-      <c r="C34" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>Lidy</t>
+        </is>
+      </c>
+      <c r="C34" s="33" t="n"/>
       <c r="D34" s="26" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
       <c r="E34" s="33" t="n"/>
-      <c r="F34" s="33" t="n"/>
+      <c r="F34" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="G34" s="33" t="n"/>
-      <c r="H34" s="33" t="n"/>
+      <c r="H34" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I34" s="33" t="n"/>
-      <c r="J34" s="33" t="n"/>
-      <c r="K34" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L34" s="33" t="n"/>
-      <c r="M34" s="33" t="n"/>
+      <c r="J34" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K34" s="33" t="n"/>
+      <c r="L34" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M34" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="N34" s="18">
         <f>IFERROR(AVERAGEIFS($C$7:$M$7,C34:M34,"Y"),"")</f>
         <v/>
@@ -10217,18 +10386,30 @@
       </c>
       <c r="B35" s="35" t="inlineStr">
         <is>
-          <t>Mike</t>
-        </is>
-      </c>
-      <c r="C35" s="19" t="n"/>
-      <c r="D35" s="19" t="n"/>
+          <t>Maylin</t>
+        </is>
+      </c>
+      <c r="C35" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D35" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E35" s="19" t="n"/>
       <c r="F35" s="19" t="n"/>
       <c r="G35" s="19" t="n"/>
       <c r="H35" s="19" t="n"/>
       <c r="I35" s="19" t="n"/>
       <c r="J35" s="19" t="n"/>
-      <c r="K35" s="19" t="n"/>
+      <c r="K35" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L35" s="19" t="n"/>
       <c r="M35" s="19" t="n"/>
       <c r="N35" s="18">
@@ -10250,7 +10431,7 @@
       </c>
       <c r="B36" s="32" t="inlineStr">
         <is>
-          <t>Richard</t>
+          <t>Mike</t>
         </is>
       </c>
       <c r="C36" s="33" t="n"/>
@@ -10283,34 +10464,18 @@
       </c>
       <c r="B37" s="35" t="inlineStr">
         <is>
-          <t>Samuel</t>
-        </is>
-      </c>
-      <c r="C37" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>Richard</t>
+        </is>
+      </c>
+      <c r="C37" s="19" t="n"/>
       <c r="D37" s="19" t="n"/>
       <c r="E37" s="19" t="n"/>
       <c r="F37" s="19" t="n"/>
-      <c r="G37" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="G37" s="19" t="n"/>
       <c r="H37" s="19" t="n"/>
-      <c r="I37" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="I37" s="19" t="n"/>
       <c r="J37" s="19" t="n"/>
-      <c r="K37" s="26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="K37" s="19" t="n"/>
       <c r="L37" s="19" t="n"/>
       <c r="M37" s="19" t="n"/>
       <c r="N37" s="18">
@@ -10332,18 +10497,34 @@
       </c>
       <c r="B38" s="32" t="inlineStr">
         <is>
-          <t>Zach</t>
-        </is>
-      </c>
-      <c r="C38" s="33" t="n"/>
+          <t>Samuel</t>
+        </is>
+      </c>
+      <c r="C38" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="D38" s="33" t="n"/>
       <c r="E38" s="33" t="n"/>
       <c r="F38" s="33" t="n"/>
-      <c r="G38" s="33" t="n"/>
+      <c r="G38" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="H38" s="33" t="n"/>
-      <c r="I38" s="33" t="n"/>
+      <c r="I38" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="J38" s="33" t="n"/>
-      <c r="K38" s="33" t="n"/>
+      <c r="K38" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L38" s="33" t="n"/>
       <c r="M38" s="33" t="n"/>
       <c r="N38" s="18">
@@ -10359,69 +10540,102 @@
         <v/>
       </c>
     </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="3" t="inlineStr"/>
-      <c r="B39" s="36" t="inlineStr">
+    <row r="39" ht="17" customHeight="1">
+      <c r="A39" s="34" t="n">
+        <v>20</v>
+      </c>
+      <c r="B39" s="35" t="inlineStr">
+        <is>
+          <t>Zach</t>
+        </is>
+      </c>
+      <c r="C39" s="19" t="n"/>
+      <c r="D39" s="19" t="n"/>
+      <c r="E39" s="19" t="n"/>
+      <c r="F39" s="19" t="n"/>
+      <c r="G39" s="19" t="n"/>
+      <c r="H39" s="19" t="n"/>
+      <c r="I39" s="19" t="n"/>
+      <c r="J39" s="19" t="n"/>
+      <c r="K39" s="19" t="n"/>
+      <c r="L39" s="19" t="n"/>
+      <c r="M39" s="19" t="n"/>
+      <c r="N39" s="18">
+        <f>IFERROR(AVERAGEIFS($C$7:$M$7,C39:M39,"Y"),"")</f>
+        <v/>
+      </c>
+      <c r="O39" s="28">
+        <f>COUNTIF(C39:M39,"Y")</f>
+        <v/>
+      </c>
+      <c r="P39" s="29">
+        <f>SUMPRODUCT((C$7:$M$7=1)*(C39:M39="Y"))*50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="3" t="inlineStr"/>
+      <c r="B40" s="36" t="inlineStr">
         <is>
           <t>Total on shift</t>
         </is>
       </c>
-      <c r="C39" s="6">
-        <f>COUNTIF(C14:C38,"Y")</f>
-        <v/>
-      </c>
-      <c r="D39" s="6">
-        <f>COUNTIF(D14:D38,"Y")</f>
-        <v/>
-      </c>
-      <c r="E39" s="6">
-        <f>COUNTIF(E14:E38,"Y")</f>
-        <v/>
-      </c>
-      <c r="F39" s="6">
-        <f>COUNTIF(F14:F38,"Y")</f>
-        <v/>
-      </c>
-      <c r="G39" s="6">
-        <f>COUNTIF(G14:G38,"Y")</f>
-        <v/>
-      </c>
-      <c r="H39" s="6">
-        <f>COUNTIF(H14:H38,"Y")</f>
-        <v/>
-      </c>
-      <c r="I39" s="6">
-        <f>COUNTIF(I14:I38,"Y")</f>
-        <v/>
-      </c>
-      <c r="J39" s="6">
-        <f>COUNTIF(J14:J38,"Y")</f>
-        <v/>
-      </c>
-      <c r="K39" s="6">
-        <f>COUNTIF(K14:K38,"Y")</f>
-        <v/>
-      </c>
-      <c r="L39" s="6">
-        <f>COUNTIF(L14:L38,"Y")</f>
-        <v/>
-      </c>
-      <c r="M39" s="6">
-        <f>COUNTIF(M14:M38,"Y")</f>
-        <v/>
-      </c>
-      <c r="N39" s="3" t="inlineStr"/>
-      <c r="O39" s="6">
-        <f>SUM(O14:O38)</f>
-        <v/>
-      </c>
-      <c r="P39" s="37">
-        <f>SUM(P14:P38)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" ht="12" customHeight="1">
-      <c r="A40" s="38" t="inlineStr">
+      <c r="C40" s="6">
+        <f>COUNTIF(C14:C39,"Y")</f>
+        <v/>
+      </c>
+      <c r="D40" s="6">
+        <f>COUNTIF(D14:D39,"Y")</f>
+        <v/>
+      </c>
+      <c r="E40" s="6">
+        <f>COUNTIF(E14:E39,"Y")</f>
+        <v/>
+      </c>
+      <c r="F40" s="6">
+        <f>COUNTIF(F14:F39,"Y")</f>
+        <v/>
+      </c>
+      <c r="G40" s="6">
+        <f>COUNTIF(G14:G39,"Y")</f>
+        <v/>
+      </c>
+      <c r="H40" s="6">
+        <f>COUNTIF(H14:H39,"Y")</f>
+        <v/>
+      </c>
+      <c r="I40" s="6">
+        <f>COUNTIF(I14:I39,"Y")</f>
+        <v/>
+      </c>
+      <c r="J40" s="6">
+        <f>COUNTIF(J14:J39,"Y")</f>
+        <v/>
+      </c>
+      <c r="K40" s="6">
+        <f>COUNTIF(K14:K39,"Y")</f>
+        <v/>
+      </c>
+      <c r="L40" s="6">
+        <f>COUNTIF(L14:L39,"Y")</f>
+        <v/>
+      </c>
+      <c r="M40" s="6">
+        <f>COUNTIF(M14:M39,"Y")</f>
+        <v/>
+      </c>
+      <c r="N40" s="3" t="inlineStr"/>
+      <c r="O40" s="6">
+        <f>SUM(O14:O39)</f>
+        <v/>
+      </c>
+      <c r="P40" s="37">
+        <f>SUM(P14:P39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="12" customHeight="1">
+      <c r="A41" s="38" t="inlineStr">
         <is>
           <t>Y = on shift during shop's meal window. Personal Avg = average score of shops worked. Bonus = $50 per 100% shop worked.</t>
         </is>
@@ -10431,10 +10645,10 @@
   <mergeCells count="7">
     <mergeCell ref="A13:P13"/>
     <mergeCell ref="A1:P1"/>
-    <mergeCell ref="A40:P40"/>
     <mergeCell ref="A18:P18"/>
     <mergeCell ref="A12:P12"/>
     <mergeCell ref="A19:P19"/>
+    <mergeCell ref="A41:P41"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>

--- a/Shop_Tracker_2065_2026.xlsx
+++ b/Shop_Tracker_2065_2026.xlsx
@@ -716,7 +716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L38"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B28" s="27" t="inlineStr">
         <is>
-          <t>Kayla Valenzuela</t>
+          <t>Kaisha Brewer</t>
         </is>
       </c>
       <c r="C28" s="28" t="n"/>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="B29" s="27" t="inlineStr">
         <is>
-          <t>Kenzie</t>
+          <t>Kayla Valenzuela</t>
         </is>
       </c>
       <c r="C29" s="28" t="n"/>
@@ -1549,30 +1549,22 @@
       </c>
       <c r="B30" s="27" t="inlineStr">
         <is>
-          <t>Lidy Henry</t>
+          <t>Kenzie</t>
         </is>
       </c>
       <c r="C30" s="28" t="n"/>
       <c r="D30" s="28" t="n"/>
-      <c r="E30" s="30" t="n">
-        <v>80</v>
-      </c>
+      <c r="E30" s="28" t="n"/>
       <c r="F30" s="28" t="n"/>
-      <c r="G30" s="22" t="n">
-        <v>100</v>
-      </c>
+      <c r="G30" s="28" t="n"/>
       <c r="H30" s="28" t="n"/>
       <c r="I30" s="28" t="n"/>
-      <c r="J30" s="30" t="n">
-        <v>85</v>
-      </c>
+      <c r="J30" s="28" t="n"/>
       <c r="K30" s="23">
         <f>IFERROR(AVERAGE(C30:J30),"")</f>
         <v/>
       </c>
-      <c r="L30" s="24" t="n">
-        <v>38.33</v>
-      </c>
+      <c r="L30" s="28" t="n"/>
     </row>
     <row r="31" ht="17" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
@@ -1582,25 +1574,23 @@
       </c>
       <c r="B31" s="27" t="inlineStr">
         <is>
-          <t>Maylin Hernandez Rodriguez</t>
+          <t>Lidy Henry</t>
         </is>
       </c>
       <c r="C31" s="28" t="n"/>
-      <c r="D31" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="28" t="n"/>
-      <c r="F31" s="25" t="n">
-        <v>72</v>
-      </c>
+      <c r="D31" s="28" t="n"/>
+      <c r="E31" s="30" t="n">
+        <v>80</v>
+      </c>
+      <c r="F31" s="28" t="n"/>
       <c r="G31" s="22" t="n">
         <v>100</v>
       </c>
       <c r="H31" s="28" t="n"/>
-      <c r="I31" s="30" t="n">
-        <v>80</v>
-      </c>
-      <c r="J31" s="28" t="n"/>
+      <c r="I31" s="28" t="n"/>
+      <c r="J31" s="30" t="n">
+        <v>85</v>
+      </c>
       <c r="K31" s="23">
         <f>IFERROR(AVERAGE(C31:J31),"")</f>
         <v/>
@@ -1617,32 +1607,32 @@
       </c>
       <c r="B32" s="27" t="inlineStr">
         <is>
-          <t>Mike</t>
-        </is>
-      </c>
-      <c r="C32" s="29" t="n">
-        <v>92</v>
-      </c>
-      <c r="D32" s="28" t="n"/>
-      <c r="E32" s="30" t="n">
-        <v>80</v>
-      </c>
+          <t>Maylin Hernandez Rodriguez</t>
+        </is>
+      </c>
+      <c r="C32" s="28" t="n"/>
+      <c r="D32" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="28" t="n"/>
       <c r="F32" s="25" t="n">
         <v>72</v>
       </c>
-      <c r="G32" s="28" t="n"/>
+      <c r="G32" s="22" t="n">
+        <v>100</v>
+      </c>
       <c r="H32" s="28" t="n"/>
       <c r="I32" s="30" t="n">
         <v>80</v>
       </c>
-      <c r="J32" s="30" t="n">
-        <v>85</v>
-      </c>
+      <c r="J32" s="28" t="n"/>
       <c r="K32" s="23">
         <f>IFERROR(AVERAGE(C32:J32),"")</f>
         <v/>
       </c>
-      <c r="L32" s="28" t="n"/>
+      <c r="L32" s="24" t="n">
+        <v>38.33</v>
+      </c>
     </row>
     <row r="33" ht="17" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
@@ -1652,17 +1642,27 @@
       </c>
       <c r="B33" s="27" t="inlineStr">
         <is>
-          <t>Nyatiek Keah</t>
-        </is>
-      </c>
-      <c r="C33" s="28" t="n"/>
+          <t>Mike</t>
+        </is>
+      </c>
+      <c r="C33" s="29" t="n">
+        <v>92</v>
+      </c>
       <c r="D33" s="28" t="n"/>
-      <c r="E33" s="28" t="n"/>
-      <c r="F33" s="28" t="n"/>
+      <c r="E33" s="30" t="n">
+        <v>80</v>
+      </c>
+      <c r="F33" s="25" t="n">
+        <v>72</v>
+      </c>
       <c r="G33" s="28" t="n"/>
       <c r="H33" s="28" t="n"/>
-      <c r="I33" s="28" t="n"/>
-      <c r="J33" s="28" t="n"/>
+      <c r="I33" s="30" t="n">
+        <v>80</v>
+      </c>
+      <c r="J33" s="30" t="n">
+        <v>85</v>
+      </c>
       <c r="K33" s="23">
         <f>IFERROR(AVERAGE(C33:J33),"")</f>
         <v/>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="B34" s="27" t="inlineStr">
         <is>
-          <t>Richard Gibbs</t>
+          <t>Nyatiek Keah</t>
         </is>
       </c>
       <c r="C34" s="28" t="n"/>
@@ -1702,7 +1702,7 @@
       </c>
       <c r="B35" s="27" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Richard Gibbs</t>
         </is>
       </c>
       <c r="C35" s="28" t="n"/>
@@ -1727,32 +1727,22 @@
       </c>
       <c r="B36" s="27" t="inlineStr">
         <is>
-          <t>Samuel Galban Rocha</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="C36" s="28" t="n"/>
-      <c r="D36" s="25" t="n">
-        <v>0</v>
-      </c>
+      <c r="D36" s="28" t="n"/>
       <c r="E36" s="28" t="n"/>
-      <c r="F36" s="25" t="n">
-        <v>72</v>
-      </c>
+      <c r="F36" s="28" t="n"/>
       <c r="G36" s="28" t="n"/>
-      <c r="H36" s="22" t="n">
-        <v>100</v>
-      </c>
-      <c r="I36" s="30" t="n">
-        <v>80</v>
-      </c>
+      <c r="H36" s="28" t="n"/>
+      <c r="I36" s="28" t="n"/>
       <c r="J36" s="28" t="n"/>
       <c r="K36" s="23">
         <f>IFERROR(AVERAGE(C36:J36),"")</f>
         <v/>
       </c>
-      <c r="L36" s="24" t="n">
-        <v>46</v>
-      </c>
+      <c r="L36" s="28" t="n"/>
     </row>
     <row r="37" ht="17" customHeight="1">
       <c r="A37" s="26" t="inlineStr">
@@ -1762,25 +1752,60 @@
       </c>
       <c r="B37" s="27" t="inlineStr">
         <is>
-          <t>Zack Whitten</t>
+          <t>Samuel Galban Rocha</t>
         </is>
       </c>
       <c r="C37" s="28" t="n"/>
-      <c r="D37" s="28" t="n"/>
+      <c r="D37" s="25" t="n">
+        <v>0</v>
+      </c>
       <c r="E37" s="28" t="n"/>
-      <c r="F37" s="28" t="n"/>
+      <c r="F37" s="25" t="n">
+        <v>72</v>
+      </c>
       <c r="G37" s="28" t="n"/>
-      <c r="H37" s="28" t="n"/>
-      <c r="I37" s="28" t="n"/>
+      <c r="H37" s="22" t="n">
+        <v>100</v>
+      </c>
+      <c r="I37" s="30" t="n">
+        <v>80</v>
+      </c>
       <c r="J37" s="28" t="n"/>
       <c r="K37" s="23">
         <f>IFERROR(AVERAGE(C37:J37),"")</f>
         <v/>
       </c>
-      <c r="L37" s="28" t="n"/>
-    </row>
-    <row r="38" ht="12" customHeight="1">
-      <c r="A38" s="31" t="inlineStr">
+      <c r="L37" s="24" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="38" ht="17" customHeight="1">
+      <c r="A38" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B38" s="27" t="inlineStr">
+        <is>
+          <t>Zack Whitten</t>
+        </is>
+      </c>
+      <c r="C38" s="28" t="n"/>
+      <c r="D38" s="28" t="n"/>
+      <c r="E38" s="28" t="n"/>
+      <c r="F38" s="28" t="n"/>
+      <c r="G38" s="28" t="n"/>
+      <c r="H38" s="28" t="n"/>
+      <c r="I38" s="28" t="n"/>
+      <c r="J38" s="28" t="n"/>
+      <c r="K38" s="23">
+        <f>IFERROR(AVERAGE(C38:J38),"")</f>
+        <v/>
+      </c>
+      <c r="L38" s="28" t="n"/>
+    </row>
+    <row r="39" ht="12" customHeight="1">
+      <c r="A39" s="31" t="inlineStr">
         <is>
           <t>Score = shop score if on shift during meal window; blank if not. MTD SCORE = average of scores worked. MTD DOLLARS = $230 ÷ on-shift count per 100% shop.</t>
         </is>
@@ -1788,7 +1813,7 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A38:L38"/>
+    <mergeCell ref="A39:L39"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A1:L1"/>
   </mergeCells>
@@ -1804,7 +1829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2495,7 +2520,7 @@
       </c>
       <c r="B28" s="27" t="inlineStr">
         <is>
-          <t>Kayla Valenzuela</t>
+          <t>Kaisha Brewer</t>
         </is>
       </c>
       <c r="C28" s="28" t="n"/>
@@ -2518,7 +2543,7 @@
       </c>
       <c r="B29" s="27" t="inlineStr">
         <is>
-          <t>Kenzie</t>
+          <t>Kayla Valenzuela</t>
         </is>
       </c>
       <c r="C29" s="28" t="n"/>
@@ -2541,28 +2566,20 @@
       </c>
       <c r="B30" s="27" t="inlineStr">
         <is>
-          <t>Lidy Henry</t>
-        </is>
-      </c>
-      <c r="C30" s="22" t="n">
-        <v>100</v>
-      </c>
+          <t>Kenzie</t>
+        </is>
+      </c>
+      <c r="C30" s="28" t="n"/>
       <c r="D30" s="28" t="n"/>
-      <c r="E30" s="25" t="n">
-        <v>69</v>
-      </c>
+      <c r="E30" s="28" t="n"/>
       <c r="F30" s="28" t="n"/>
-      <c r="G30" s="22" t="n">
-        <v>100</v>
-      </c>
+      <c r="G30" s="28" t="n"/>
       <c r="H30" s="28" t="n"/>
       <c r="I30" s="23">
         <f>IFERROR(AVERAGE(C30:H30),"")</f>
         <v/>
       </c>
-      <c r="J30" s="24" t="n">
-        <v>84.33</v>
-      </c>
+      <c r="J30" s="28" t="n"/>
     </row>
     <row r="31" ht="17" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
@@ -2572,19 +2589,17 @@
       </c>
       <c r="B31" s="27" t="inlineStr">
         <is>
-          <t>Maylin Hernandez Rodriguez</t>
-        </is>
-      </c>
-      <c r="C31" s="28" t="n"/>
-      <c r="D31" s="22" t="n">
+          <t>Lidy Henry</t>
+        </is>
+      </c>
+      <c r="C31" s="22" t="n">
         <v>100</v>
       </c>
+      <c r="D31" s="28" t="n"/>
       <c r="E31" s="25" t="n">
         <v>69</v>
       </c>
-      <c r="F31" s="22" t="n">
-        <v>100</v>
-      </c>
+      <c r="F31" s="28" t="n"/>
       <c r="G31" s="22" t="n">
         <v>100</v>
       </c>
@@ -2594,7 +2609,7 @@
         <v/>
       </c>
       <c r="J31" s="24" t="n">
-        <v>153.33</v>
+        <v>84.33</v>
       </c>
     </row>
     <row r="32" ht="17" customHeight="1">
@@ -2605,29 +2620,29 @@
       </c>
       <c r="B32" s="27" t="inlineStr">
         <is>
-          <t>Mike</t>
-        </is>
-      </c>
-      <c r="C32" s="22" t="n">
+          <t>Maylin Hernandez Rodriguez</t>
+        </is>
+      </c>
+      <c r="C32" s="28" t="n"/>
+      <c r="D32" s="22" t="n">
         <v>100</v>
       </c>
-      <c r="D32" s="28" t="n"/>
       <c r="E32" s="25" t="n">
         <v>69</v>
       </c>
-      <c r="F32" s="28" t="n"/>
+      <c r="F32" s="22" t="n">
+        <v>100</v>
+      </c>
       <c r="G32" s="22" t="n">
         <v>100</v>
       </c>
-      <c r="H32" s="29" t="n">
-        <v>95</v>
-      </c>
+      <c r="H32" s="28" t="n"/>
       <c r="I32" s="23">
         <f>IFERROR(AVERAGE(C32:H32),"")</f>
         <v/>
       </c>
       <c r="J32" s="24" t="n">
-        <v>84.33</v>
+        <v>153.33</v>
       </c>
     </row>
     <row r="33" ht="17" customHeight="1">
@@ -2638,20 +2653,30 @@
       </c>
       <c r="B33" s="27" t="inlineStr">
         <is>
-          <t>Nyatiek Keah</t>
-        </is>
-      </c>
-      <c r="C33" s="28" t="n"/>
+          <t>Mike</t>
+        </is>
+      </c>
+      <c r="C33" s="22" t="n">
+        <v>100</v>
+      </c>
       <c r="D33" s="28" t="n"/>
-      <c r="E33" s="28" t="n"/>
+      <c r="E33" s="25" t="n">
+        <v>69</v>
+      </c>
       <c r="F33" s="28" t="n"/>
-      <c r="G33" s="28" t="n"/>
-      <c r="H33" s="28" t="n"/>
+      <c r="G33" s="22" t="n">
+        <v>100</v>
+      </c>
+      <c r="H33" s="29" t="n">
+        <v>95</v>
+      </c>
       <c r="I33" s="23">
         <f>IFERROR(AVERAGE(C33:H33),"")</f>
         <v/>
       </c>
-      <c r="J33" s="28" t="n"/>
+      <c r="J33" s="24" t="n">
+        <v>84.33</v>
+      </c>
     </row>
     <row r="34" ht="17" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
@@ -2661,7 +2686,7 @@
       </c>
       <c r="B34" s="27" t="inlineStr">
         <is>
-          <t>Richard Gibbs</t>
+          <t>Nyatiek Keah</t>
         </is>
       </c>
       <c r="C34" s="28" t="n"/>
@@ -2684,7 +2709,7 @@
       </c>
       <c r="B35" s="27" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Richard Gibbs</t>
         </is>
       </c>
       <c r="C35" s="28" t="n"/>
@@ -2707,26 +2732,20 @@
       </c>
       <c r="B36" s="27" t="inlineStr">
         <is>
-          <t>Samuel Galban Rocha</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="C36" s="28" t="n"/>
-      <c r="D36" s="22" t="n">
-        <v>100</v>
-      </c>
+      <c r="D36" s="28" t="n"/>
       <c r="E36" s="28" t="n"/>
-      <c r="F36" s="22" t="n">
-        <v>100</v>
-      </c>
+      <c r="F36" s="28" t="n"/>
       <c r="G36" s="28" t="n"/>
       <c r="H36" s="28" t="n"/>
       <c r="I36" s="23">
         <f>IFERROR(AVERAGE(C36:H36),"")</f>
         <v/>
       </c>
-      <c r="J36" s="24" t="n">
-        <v>115</v>
-      </c>
+      <c r="J36" s="28" t="n"/>
     </row>
     <row r="37" ht="17" customHeight="1">
       <c r="A37" s="26" t="inlineStr">
@@ -2736,23 +2755,52 @@
       </c>
       <c r="B37" s="27" t="inlineStr">
         <is>
-          <t>Zack Whitten</t>
+          <t>Samuel Galban Rocha</t>
         </is>
       </c>
       <c r="C37" s="28" t="n"/>
-      <c r="D37" s="28" t="n"/>
+      <c r="D37" s="22" t="n">
+        <v>100</v>
+      </c>
       <c r="E37" s="28" t="n"/>
-      <c r="F37" s="28" t="n"/>
+      <c r="F37" s="22" t="n">
+        <v>100</v>
+      </c>
       <c r="G37" s="28" t="n"/>
       <c r="H37" s="28" t="n"/>
       <c r="I37" s="23">
         <f>IFERROR(AVERAGE(C37:H37),"")</f>
         <v/>
       </c>
-      <c r="J37" s="28" t="n"/>
-    </row>
-    <row r="38" ht="12" customHeight="1">
-      <c r="A38" s="31" t="inlineStr">
+      <c r="J37" s="24" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="38" ht="17" customHeight="1">
+      <c r="A38" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B38" s="27" t="inlineStr">
+        <is>
+          <t>Zack Whitten</t>
+        </is>
+      </c>
+      <c r="C38" s="28" t="n"/>
+      <c r="D38" s="28" t="n"/>
+      <c r="E38" s="28" t="n"/>
+      <c r="F38" s="28" t="n"/>
+      <c r="G38" s="28" t="n"/>
+      <c r="H38" s="28" t="n"/>
+      <c r="I38" s="23">
+        <f>IFERROR(AVERAGE(C38:H38),"")</f>
+        <v/>
+      </c>
+      <c r="J38" s="28" t="n"/>
+    </row>
+    <row r="39" ht="12" customHeight="1">
+      <c r="A39" s="31" t="inlineStr">
         <is>
           <t>Score = shop score if on shift during meal window; blank if not. MTD SCORE = average of scores worked. MTD DOLLARS = $230 ÷ on-shift count per 100% shop.</t>
         </is>
@@ -2760,9 +2808,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A39:J39"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A38:J38"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2776,7 +2824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3424,7 +3472,7 @@
       </c>
       <c r="B28" s="27" t="inlineStr">
         <is>
-          <t>Kayla Valenzuela</t>
+          <t>Kaisha Brewer</t>
         </is>
       </c>
       <c r="C28" s="28" t="n"/>
@@ -3446,7 +3494,7 @@
       </c>
       <c r="B29" s="27" t="inlineStr">
         <is>
-          <t>Kenzie</t>
+          <t>Kayla Valenzuela</t>
         </is>
       </c>
       <c r="C29" s="28" t="n"/>
@@ -3468,25 +3516,19 @@
       </c>
       <c r="B30" s="27" t="inlineStr">
         <is>
-          <t>Lidy Henry</t>
+          <t>Kenzie</t>
         </is>
       </c>
       <c r="C30" s="28" t="n"/>
-      <c r="D30" s="30" t="n">
-        <v>80</v>
-      </c>
+      <c r="D30" s="28" t="n"/>
       <c r="E30" s="28" t="n"/>
       <c r="F30" s="28" t="n"/>
-      <c r="G30" s="22" t="n">
-        <v>100</v>
-      </c>
+      <c r="G30" s="28" t="n"/>
       <c r="H30" s="23">
         <f>IFERROR(AVERAGE(C30:G30),"")</f>
         <v/>
       </c>
-      <c r="I30" s="24" t="n">
-        <v>38.33</v>
-      </c>
+      <c r="I30" s="28" t="n"/>
     </row>
     <row r="31" ht="17" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
@@ -3496,21 +3538,15 @@
       </c>
       <c r="B31" s="27" t="inlineStr">
         <is>
-          <t>Maylin Hernandez Rodriguez</t>
-        </is>
-      </c>
-      <c r="C31" s="25" t="n">
-        <v>72</v>
-      </c>
+          <t>Lidy Henry</t>
+        </is>
+      </c>
+      <c r="C31" s="28" t="n"/>
       <c r="D31" s="30" t="n">
         <v>80</v>
       </c>
-      <c r="E31" s="25" t="n">
-        <v>72</v>
-      </c>
-      <c r="F31" s="25" t="n">
-        <v>49</v>
-      </c>
+      <c r="E31" s="28" t="n"/>
+      <c r="F31" s="28" t="n"/>
       <c r="G31" s="22" t="n">
         <v>100</v>
       </c>
@@ -3530,19 +3566,31 @@
       </c>
       <c r="B32" s="27" t="inlineStr">
         <is>
-          <t>Mike</t>
-        </is>
-      </c>
-      <c r="C32" s="28" t="n"/>
-      <c r="D32" s="28" t="n"/>
-      <c r="E32" s="28" t="n"/>
-      <c r="F32" s="28" t="n"/>
-      <c r="G32" s="28" t="n"/>
+          <t>Maylin Hernandez Rodriguez</t>
+        </is>
+      </c>
+      <c r="C32" s="25" t="n">
+        <v>72</v>
+      </c>
+      <c r="D32" s="30" t="n">
+        <v>80</v>
+      </c>
+      <c r="E32" s="25" t="n">
+        <v>72</v>
+      </c>
+      <c r="F32" s="25" t="n">
+        <v>49</v>
+      </c>
+      <c r="G32" s="22" t="n">
+        <v>100</v>
+      </c>
       <c r="H32" s="23">
         <f>IFERROR(AVERAGE(C32:G32),"")</f>
         <v/>
       </c>
-      <c r="I32" s="28" t="n"/>
+      <c r="I32" s="24" t="n">
+        <v>38.33</v>
+      </c>
     </row>
     <row r="33" ht="17" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
@@ -3552,7 +3600,7 @@
       </c>
       <c r="B33" s="27" t="inlineStr">
         <is>
-          <t>Nyatiek Keah</t>
+          <t>Mike</t>
         </is>
       </c>
       <c r="C33" s="28" t="n"/>
@@ -3574,7 +3622,7 @@
       </c>
       <c r="B34" s="27" t="inlineStr">
         <is>
-          <t>Richard Gibbs</t>
+          <t>Nyatiek Keah</t>
         </is>
       </c>
       <c r="C34" s="28" t="n"/>
@@ -3596,7 +3644,7 @@
       </c>
       <c r="B35" s="27" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Richard Gibbs</t>
         </is>
       </c>
       <c r="C35" s="28" t="n"/>
@@ -3618,12 +3666,10 @@
       </c>
       <c r="B36" s="27" t="inlineStr">
         <is>
-          <t>Samuel Galban Rocha</t>
-        </is>
-      </c>
-      <c r="C36" s="25" t="n">
-        <v>72</v>
-      </c>
+          <t>Ryan</t>
+        </is>
+      </c>
+      <c r="C36" s="28" t="n"/>
       <c r="D36" s="28" t="n"/>
       <c r="E36" s="28" t="n"/>
       <c r="F36" s="28" t="n"/>
@@ -3642,10 +3688,12 @@
       </c>
       <c r="B37" s="27" t="inlineStr">
         <is>
-          <t>Zack Whitten</t>
-        </is>
-      </c>
-      <c r="C37" s="28" t="n"/>
+          <t>Samuel Galban Rocha</t>
+        </is>
+      </c>
+      <c r="C37" s="25" t="n">
+        <v>72</v>
+      </c>
       <c r="D37" s="28" t="n"/>
       <c r="E37" s="28" t="n"/>
       <c r="F37" s="28" t="n"/>
@@ -3656,8 +3704,30 @@
       </c>
       <c r="I37" s="28" t="n"/>
     </row>
-    <row r="38" ht="12" customHeight="1">
-      <c r="A38" s="31" t="inlineStr">
+    <row r="38" ht="17" customHeight="1">
+      <c r="A38" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B38" s="27" t="inlineStr">
+        <is>
+          <t>Zack Whitten</t>
+        </is>
+      </c>
+      <c r="C38" s="28" t="n"/>
+      <c r="D38" s="28" t="n"/>
+      <c r="E38" s="28" t="n"/>
+      <c r="F38" s="28" t="n"/>
+      <c r="G38" s="28" t="n"/>
+      <c r="H38" s="23">
+        <f>IFERROR(AVERAGE(C38:G38),"")</f>
+        <v/>
+      </c>
+      <c r="I38" s="28" t="n"/>
+    </row>
+    <row r="39" ht="12" customHeight="1">
+      <c r="A39" s="31" t="inlineStr">
         <is>
           <t>Score = shop score if on shift during meal window; blank if not. MTD SCORE = average of scores worked. MTD DOLLARS = $230 ÷ on-shift count per 100% shop.</t>
         </is>
@@ -3667,7 +3737,7 @@
   <mergeCells count="3">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A38:I38"/>
+    <mergeCell ref="A39:I39"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3681,7 +3751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -4376,7 +4446,7 @@
       </c>
       <c r="B28" s="27" t="inlineStr">
         <is>
-          <t>Kayla Valenzuela</t>
+          <t>Kaisha Brewer</t>
         </is>
       </c>
       <c r="C28" s="28" t="n"/>
@@ -4399,7 +4469,7 @@
       </c>
       <c r="B29" s="27" t="inlineStr">
         <is>
-          <t>Kenzie</t>
+          <t>Kayla Valenzuela</t>
         </is>
       </c>
       <c r="C29" s="28" t="n"/>
@@ -4422,21 +4492,15 @@
       </c>
       <c r="B30" s="27" t="inlineStr">
         <is>
-          <t>Lidy Henry</t>
+          <t>Kenzie</t>
         </is>
       </c>
       <c r="C30" s="28" t="n"/>
-      <c r="D30" s="30" t="n">
-        <v>87</v>
-      </c>
+      <c r="D30" s="28" t="n"/>
       <c r="E30" s="28" t="n"/>
-      <c r="F30" s="25" t="n">
-        <v>47</v>
-      </c>
+      <c r="F30" s="28" t="n"/>
       <c r="G30" s="28" t="n"/>
-      <c r="H30" s="30" t="n">
-        <v>87</v>
-      </c>
+      <c r="H30" s="28" t="n"/>
       <c r="I30" s="23">
         <f>IFERROR(AVERAGE(C30:H30),"")</f>
         <v/>
@@ -4451,26 +4515,26 @@
       </c>
       <c r="B31" s="27" t="inlineStr">
         <is>
-          <t>Maylin Hernandez Rodriguez</t>
-        </is>
-      </c>
-      <c r="C31" s="29" t="n">
-        <v>97</v>
-      </c>
-      <c r="D31" s="28" t="n"/>
+          <t>Lidy Henry</t>
+        </is>
+      </c>
+      <c r="C31" s="28" t="n"/>
+      <c r="D31" s="30" t="n">
+        <v>87</v>
+      </c>
       <c r="E31" s="28" t="n"/>
-      <c r="F31" s="28" t="n"/>
-      <c r="G31" s="22" t="n">
-        <v>100</v>
-      </c>
-      <c r="H31" s="28" t="n"/>
+      <c r="F31" s="25" t="n">
+        <v>47</v>
+      </c>
+      <c r="G31" s="28" t="n"/>
+      <c r="H31" s="30" t="n">
+        <v>87</v>
+      </c>
       <c r="I31" s="23">
         <f>IFERROR(AVERAGE(C31:H31),"")</f>
         <v/>
       </c>
-      <c r="J31" s="24" t="n">
-        <v>38.33</v>
-      </c>
+      <c r="J31" s="28" t="n"/>
     </row>
     <row r="32" ht="17" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
@@ -4480,20 +4544,26 @@
       </c>
       <c r="B32" s="27" t="inlineStr">
         <is>
-          <t>Mike</t>
-        </is>
-      </c>
-      <c r="C32" s="28" t="n"/>
+          <t>Maylin Hernandez Rodriguez</t>
+        </is>
+      </c>
+      <c r="C32" s="29" t="n">
+        <v>97</v>
+      </c>
       <c r="D32" s="28" t="n"/>
       <c r="E32" s="28" t="n"/>
       <c r="F32" s="28" t="n"/>
-      <c r="G32" s="28" t="n"/>
+      <c r="G32" s="22" t="n">
+        <v>100</v>
+      </c>
       <c r="H32" s="28" t="n"/>
       <c r="I32" s="23">
         <f>IFERROR(AVERAGE(C32:H32),"")</f>
         <v/>
       </c>
-      <c r="J32" s="28" t="n"/>
+      <c r="J32" s="24" t="n">
+        <v>38.33</v>
+      </c>
     </row>
     <row r="33" ht="17" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
@@ -4503,7 +4573,7 @@
       </c>
       <c r="B33" s="27" t="inlineStr">
         <is>
-          <t>Nyatiek Keah</t>
+          <t>Mike</t>
         </is>
       </c>
       <c r="C33" s="28" t="n"/>
@@ -4526,30 +4596,20 @@
       </c>
       <c r="B34" s="27" t="inlineStr">
         <is>
-          <t>Richard Gibbs</t>
-        </is>
-      </c>
-      <c r="C34" s="29" t="n">
-        <v>97</v>
-      </c>
+          <t>Nyatiek Keah</t>
+        </is>
+      </c>
+      <c r="C34" s="28" t="n"/>
       <c r="D34" s="28" t="n"/>
-      <c r="E34" s="29" t="n">
-        <v>95</v>
-      </c>
-      <c r="F34" s="25" t="n">
-        <v>47</v>
-      </c>
-      <c r="G34" s="22" t="n">
-        <v>100</v>
-      </c>
+      <c r="E34" s="28" t="n"/>
+      <c r="F34" s="28" t="n"/>
+      <c r="G34" s="28" t="n"/>
       <c r="H34" s="28" t="n"/>
       <c r="I34" s="23">
         <f>IFERROR(AVERAGE(C34:H34),"")</f>
         <v/>
       </c>
-      <c r="J34" s="24" t="n">
-        <v>38.33</v>
-      </c>
+      <c r="J34" s="28" t="n"/>
     </row>
     <row r="35" ht="17" customHeight="1">
       <c r="A35" s="26" t="inlineStr">
@@ -4559,20 +4619,30 @@
       </c>
       <c r="B35" s="27" t="inlineStr">
         <is>
-          <t>Ryan</t>
-        </is>
-      </c>
-      <c r="C35" s="28" t="n"/>
+          <t>Richard Gibbs</t>
+        </is>
+      </c>
+      <c r="C35" s="29" t="n">
+        <v>97</v>
+      </c>
       <c r="D35" s="28" t="n"/>
-      <c r="E35" s="28" t="n"/>
-      <c r="F35" s="28" t="n"/>
-      <c r="G35" s="28" t="n"/>
+      <c r="E35" s="29" t="n">
+        <v>95</v>
+      </c>
+      <c r="F35" s="25" t="n">
+        <v>47</v>
+      </c>
+      <c r="G35" s="22" t="n">
+        <v>100</v>
+      </c>
       <c r="H35" s="28" t="n"/>
       <c r="I35" s="23">
         <f>IFERROR(AVERAGE(C35:H35),"")</f>
         <v/>
       </c>
-      <c r="J35" s="28" t="n"/>
+      <c r="J35" s="24" t="n">
+        <v>38.33</v>
+      </c>
     </row>
     <row r="36" ht="17" customHeight="1">
       <c r="A36" s="26" t="inlineStr">
@@ -4582,12 +4652,10 @@
       </c>
       <c r="B36" s="27" t="inlineStr">
         <is>
-          <t>Samuel Galban Rocha</t>
-        </is>
-      </c>
-      <c r="C36" s="29" t="n">
-        <v>97</v>
-      </c>
+          <t>Ryan</t>
+        </is>
+      </c>
+      <c r="C36" s="28" t="n"/>
       <c r="D36" s="28" t="n"/>
       <c r="E36" s="28" t="n"/>
       <c r="F36" s="28" t="n"/>
@@ -4607,10 +4675,12 @@
       </c>
       <c r="B37" s="27" t="inlineStr">
         <is>
-          <t>Zack Whitten</t>
-        </is>
-      </c>
-      <c r="C37" s="28" t="n"/>
+          <t>Samuel Galban Rocha</t>
+        </is>
+      </c>
+      <c r="C37" s="29" t="n">
+        <v>97</v>
+      </c>
       <c r="D37" s="28" t="n"/>
       <c r="E37" s="28" t="n"/>
       <c r="F37" s="28" t="n"/>
@@ -4622,8 +4692,31 @@
       </c>
       <c r="J37" s="28" t="n"/>
     </row>
-    <row r="38" ht="12" customHeight="1">
-      <c r="A38" s="31" t="inlineStr">
+    <row r="38" ht="17" customHeight="1">
+      <c r="A38" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B38" s="27" t="inlineStr">
+        <is>
+          <t>Zack Whitten</t>
+        </is>
+      </c>
+      <c r="C38" s="28" t="n"/>
+      <c r="D38" s="28" t="n"/>
+      <c r="E38" s="28" t="n"/>
+      <c r="F38" s="28" t="n"/>
+      <c r="G38" s="28" t="n"/>
+      <c r="H38" s="28" t="n"/>
+      <c r="I38" s="23">
+        <f>IFERROR(AVERAGE(C38:H38),"")</f>
+        <v/>
+      </c>
+      <c r="J38" s="28" t="n"/>
+    </row>
+    <row r="39" ht="12" customHeight="1">
+      <c r="A39" s="31" t="inlineStr">
         <is>
           <t>Score = shop score if on shift during meal window; blank if not. MTD SCORE = average of scores worked. MTD DOLLARS = $230 ÷ on-shift count per 100% shop.</t>
         </is>
@@ -4631,9 +4724,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A39:J39"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A38:J38"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4647,7 +4740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -5344,7 +5437,7 @@
       </c>
       <c r="B28" s="27" t="inlineStr">
         <is>
-          <t>Kayla Valenzuela</t>
+          <t>Kaisha Brewer</t>
         </is>
       </c>
       <c r="C28" s="28" t="n"/>
@@ -5367,7 +5460,7 @@
       </c>
       <c r="B29" s="27" t="inlineStr">
         <is>
-          <t>Kenzie</t>
+          <t>Kayla Valenzuela</t>
         </is>
       </c>
       <c r="C29" s="28" t="n"/>
@@ -5390,28 +5483,20 @@
       </c>
       <c r="B30" s="27" t="inlineStr">
         <is>
-          <t>Lidy Henry</t>
-        </is>
-      </c>
-      <c r="C30" s="22" t="n">
-        <v>100</v>
-      </c>
+          <t>Kenzie</t>
+        </is>
+      </c>
+      <c r="C30" s="28" t="n"/>
       <c r="D30" s="28" t="n"/>
-      <c r="E30" s="29" t="n">
-        <v>95</v>
-      </c>
+      <c r="E30" s="28" t="n"/>
       <c r="F30" s="28" t="n"/>
-      <c r="G30" s="25" t="n">
-        <v>60</v>
-      </c>
+      <c r="G30" s="28" t="n"/>
       <c r="H30" s="28" t="n"/>
       <c r="I30" s="23">
         <f>IFERROR(AVERAGE(C30:H30),"")</f>
         <v/>
       </c>
-      <c r="J30" s="24" t="n">
-        <v>46</v>
-      </c>
+      <c r="J30" s="28" t="n"/>
     </row>
     <row r="31" ht="17" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
@@ -5421,27 +5506,27 @@
       </c>
       <c r="B31" s="27" t="inlineStr">
         <is>
-          <t>Maylin Hernandez Rodriguez</t>
-        </is>
-      </c>
-      <c r="C31" s="28" t="n"/>
-      <c r="D31" s="22" t="n">
+          <t>Lidy Henry</t>
+        </is>
+      </c>
+      <c r="C31" s="22" t="n">
         <v>100</v>
       </c>
-      <c r="E31" s="28" t="n"/>
+      <c r="D31" s="28" t="n"/>
+      <c r="E31" s="29" t="n">
+        <v>95</v>
+      </c>
       <c r="F31" s="28" t="n"/>
       <c r="G31" s="25" t="n">
         <v>60</v>
       </c>
-      <c r="H31" s="29" t="n">
-        <v>92</v>
-      </c>
+      <c r="H31" s="28" t="n"/>
       <c r="I31" s="23">
         <f>IFERROR(AVERAGE(C31:H31),"")</f>
         <v/>
       </c>
       <c r="J31" s="24" t="n">
-        <v>38.33</v>
+        <v>46</v>
       </c>
     </row>
     <row r="32" ht="17" customHeight="1">
@@ -5452,20 +5537,28 @@
       </c>
       <c r="B32" s="27" t="inlineStr">
         <is>
-          <t>Mike</t>
+          <t>Maylin Hernandez Rodriguez</t>
         </is>
       </c>
       <c r="C32" s="28" t="n"/>
-      <c r="D32" s="28" t="n"/>
+      <c r="D32" s="22" t="n">
+        <v>100</v>
+      </c>
       <c r="E32" s="28" t="n"/>
       <c r="F32" s="28" t="n"/>
-      <c r="G32" s="28" t="n"/>
-      <c r="H32" s="28" t="n"/>
+      <c r="G32" s="25" t="n">
+        <v>60</v>
+      </c>
+      <c r="H32" s="29" t="n">
+        <v>92</v>
+      </c>
       <c r="I32" s="23">
         <f>IFERROR(AVERAGE(C32:H32),"")</f>
         <v/>
       </c>
-      <c r="J32" s="28" t="n"/>
+      <c r="J32" s="24" t="n">
+        <v>38.33</v>
+      </c>
     </row>
     <row r="33" ht="17" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
@@ -5475,7 +5568,7 @@
       </c>
       <c r="B33" s="27" t="inlineStr">
         <is>
-          <t>Nyatiek Keah</t>
+          <t>Mike</t>
         </is>
       </c>
       <c r="C33" s="28" t="n"/>
@@ -5498,14 +5591,12 @@
       </c>
       <c r="B34" s="27" t="inlineStr">
         <is>
-          <t>Richard Gibbs</t>
+          <t>Nyatiek Keah</t>
         </is>
       </c>
       <c r="C34" s="28" t="n"/>
       <c r="D34" s="28" t="n"/>
-      <c r="E34" s="29" t="n">
-        <v>95</v>
-      </c>
+      <c r="E34" s="28" t="n"/>
       <c r="F34" s="28" t="n"/>
       <c r="G34" s="28" t="n"/>
       <c r="H34" s="28" t="n"/>
@@ -5523,12 +5614,14 @@
       </c>
       <c r="B35" s="27" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Richard Gibbs</t>
         </is>
       </c>
       <c r="C35" s="28" t="n"/>
       <c r="D35" s="28" t="n"/>
-      <c r="E35" s="28" t="n"/>
+      <c r="E35" s="29" t="n">
+        <v>95</v>
+      </c>
       <c r="F35" s="28" t="n"/>
       <c r="G35" s="28" t="n"/>
       <c r="H35" s="28" t="n"/>
@@ -5546,7 +5639,7 @@
       </c>
       <c r="B36" s="27" t="inlineStr">
         <is>
-          <t>Samuel Galban Rocha</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="C36" s="28" t="n"/>
@@ -5569,7 +5662,7 @@
       </c>
       <c r="B37" s="27" t="inlineStr">
         <is>
-          <t>Zack Whitten</t>
+          <t>Samuel Galban Rocha</t>
         </is>
       </c>
       <c r="C37" s="28" t="n"/>
@@ -5584,8 +5677,31 @@
       </c>
       <c r="J37" s="28" t="n"/>
     </row>
-    <row r="38" ht="12" customHeight="1">
-      <c r="A38" s="31" t="inlineStr">
+    <row r="38" ht="17" customHeight="1">
+      <c r="A38" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B38" s="27" t="inlineStr">
+        <is>
+          <t>Zack Whitten</t>
+        </is>
+      </c>
+      <c r="C38" s="28" t="n"/>
+      <c r="D38" s="28" t="n"/>
+      <c r="E38" s="28" t="n"/>
+      <c r="F38" s="28" t="n"/>
+      <c r="G38" s="28" t="n"/>
+      <c r="H38" s="28" t="n"/>
+      <c r="I38" s="23">
+        <f>IFERROR(AVERAGE(C38:H38),"")</f>
+        <v/>
+      </c>
+      <c r="J38" s="28" t="n"/>
+    </row>
+    <row r="39" ht="12" customHeight="1">
+      <c r="A39" s="31" t="inlineStr">
         <is>
           <t>Score = shop score if on shift during meal window; blank if not. MTD SCORE = average of scores worked. MTD DOLLARS = $230 ÷ on-shift count per 100% shop.</t>
         </is>
@@ -5593,9 +5709,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A39:J39"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A38:J38"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5609,7 +5725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -6110,16 +6226,20 @@
       </c>
       <c r="B28" s="27" t="inlineStr">
         <is>
-          <t>Kayla Valenzuela</t>
+          <t>Kaisha Brewer</t>
         </is>
       </c>
       <c r="C28" s="28" t="n"/>
-      <c r="D28" s="28" t="n"/>
+      <c r="D28" s="22" t="n">
+        <v>100</v>
+      </c>
       <c r="E28" s="23">
         <f>IFERROR(AVERAGE(C28:D28),"")</f>
         <v/>
       </c>
-      <c r="F28" s="28" t="n"/>
+      <c r="F28" s="24" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="29" ht="17" customHeight="1">
       <c r="A29" s="26" t="inlineStr">
@@ -6129,7 +6249,7 @@
       </c>
       <c r="B29" s="27" t="inlineStr">
         <is>
-          <t>Kenzie</t>
+          <t>Kayla Valenzuela</t>
         </is>
       </c>
       <c r="C29" s="28" t="n"/>
@@ -6148,22 +6268,16 @@
       </c>
       <c r="B30" s="27" t="inlineStr">
         <is>
-          <t>Lidy Henry</t>
-        </is>
-      </c>
-      <c r="C30" s="29" t="n">
-        <v>95</v>
-      </c>
-      <c r="D30" s="22" t="n">
-        <v>100</v>
-      </c>
+          <t>Kenzie</t>
+        </is>
+      </c>
+      <c r="C30" s="28" t="n"/>
+      <c r="D30" s="28" t="n"/>
       <c r="E30" s="23">
         <f>IFERROR(AVERAGE(C30:D30),"")</f>
         <v/>
       </c>
-      <c r="F30" s="24" t="n">
-        <v>46</v>
-      </c>
+      <c r="F30" s="28" t="n"/>
     </row>
     <row r="31" ht="17" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
@@ -6173,16 +6287,22 @@
       </c>
       <c r="B31" s="27" t="inlineStr">
         <is>
-          <t>Maylin Hernandez Rodriguez</t>
-        </is>
-      </c>
-      <c r="C31" s="28" t="n"/>
-      <c r="D31" s="28" t="n"/>
+          <t>Lidy Henry</t>
+        </is>
+      </c>
+      <c r="C31" s="29" t="n">
+        <v>95</v>
+      </c>
+      <c r="D31" s="22" t="n">
+        <v>100</v>
+      </c>
       <c r="E31" s="23">
         <f>IFERROR(AVERAGE(C31:D31),"")</f>
         <v/>
       </c>
-      <c r="F31" s="28" t="n"/>
+      <c r="F31" s="24" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="32" ht="17" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
@@ -6192,7 +6312,7 @@
       </c>
       <c r="B32" s="27" t="inlineStr">
         <is>
-          <t>Mike</t>
+          <t>Maylin Hernandez Rodriguez</t>
         </is>
       </c>
       <c r="C32" s="28" t="n"/>
@@ -6211,7 +6331,7 @@
       </c>
       <c r="B33" s="27" t="inlineStr">
         <is>
-          <t>Nyatiek Keah</t>
+          <t>Mike</t>
         </is>
       </c>
       <c r="C33" s="28" t="n"/>
@@ -6230,7 +6350,7 @@
       </c>
       <c r="B34" s="27" t="inlineStr">
         <is>
-          <t>Richard Gibbs</t>
+          <t>Nyatiek Keah</t>
         </is>
       </c>
       <c r="C34" s="28" t="n"/>
@@ -6249,7 +6369,7 @@
       </c>
       <c r="B35" s="27" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Richard Gibbs</t>
         </is>
       </c>
       <c r="C35" s="28" t="n"/>
@@ -6268,7 +6388,7 @@
       </c>
       <c r="B36" s="27" t="inlineStr">
         <is>
-          <t>Samuel Galban Rocha</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="C36" s="28" t="n"/>
@@ -6287,23 +6407,42 @@
       </c>
       <c r="B37" s="27" t="inlineStr">
         <is>
-          <t>Zack Whitten</t>
+          <t>Samuel Galban Rocha</t>
         </is>
       </c>
       <c r="C37" s="28" t="n"/>
-      <c r="D37" s="22" t="n">
-        <v>100</v>
-      </c>
+      <c r="D37" s="28" t="n"/>
       <c r="E37" s="23">
         <f>IFERROR(AVERAGE(C37:D37),"")</f>
         <v/>
       </c>
-      <c r="F37" s="24" t="n">
+      <c r="F37" s="28" t="n"/>
+    </row>
+    <row r="38" ht="17" customHeight="1">
+      <c r="A38" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B38" s="27" t="inlineStr">
+        <is>
+          <t>Zack Whitten</t>
+        </is>
+      </c>
+      <c r="C38" s="28" t="n"/>
+      <c r="D38" s="22" t="n">
+        <v>100</v>
+      </c>
+      <c r="E38" s="23">
+        <f>IFERROR(AVERAGE(C38:D38),"")</f>
+        <v/>
+      </c>
+      <c r="F38" s="24" t="n">
         <v>46</v>
       </c>
     </row>
-    <row r="38" ht="12" customHeight="1">
-      <c r="A38" s="31" t="inlineStr">
+    <row r="39" ht="12" customHeight="1">
+      <c r="A39" s="31" t="inlineStr">
         <is>
           <t>Score = shop score if on shift during meal window; blank if not. MTD SCORE = average of scores worked. MTD DOLLARS = $230 ÷ on-shift count per 100% shop.</t>
         </is>
@@ -6311,8 +6450,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A38:F38"/>
     <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A39:F39"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>

--- a/Shop_Tracker_2065_2026.xlsx
+++ b/Shop_Tracker_2065_2026.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="January" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="February" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="March" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="April" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="May" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="June" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="January" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="February" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="March" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="April" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="May" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="June" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/Shop_Tracker_2065_2026.xlsx
+++ b/Shop_Tracker_2065_2026.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="January" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="February" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="March" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="April" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="May" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="June" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="January" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="February" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="March" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="April" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="May" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="June" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5725,15 +5725,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -5758,10 +5759,15 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
+          <t>WEEK 3</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
           <t>MTD SCORE</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>MTD DOLLARS</t>
         </is>
@@ -5784,8 +5790,13 @@
           <t>06/04</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr"/>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>06/14</t>
+        </is>
+      </c>
       <c r="F3" s="4" t="inlineStr"/>
+      <c r="G3" s="4" t="inlineStr"/>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="4" t="inlineStr"/>
@@ -5804,8 +5815,13 @@
           <t>Lunch</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr"/>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
       <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="9" t="inlineStr"/>
@@ -5820,8 +5836,11 @@
       <c r="D5" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="E5" s="9" t="inlineStr"/>
+      <c r="E5" s="13" t="n">
+        <v>80</v>
+      </c>
       <c r="F5" s="9" t="inlineStr"/>
+      <c r="G5" s="9" t="inlineStr"/>
     </row>
     <row r="6" ht="14" customHeight="1">
       <c r="A6" s="15" t="inlineStr"/>
@@ -5834,6 +5853,7 @@
       <c r="D6" s="17" t="n"/>
       <c r="E6" s="17" t="n"/>
       <c r="F6" s="17" t="n"/>
+      <c r="G6" s="17" t="n"/>
     </row>
     <row r="7" ht="14" customHeight="1">
       <c r="A7" s="15" t="inlineStr"/>
@@ -5846,6 +5866,7 @@
       <c r="D7" s="17" t="n"/>
       <c r="E7" s="17" t="n"/>
       <c r="F7" s="17" t="n"/>
+      <c r="G7" s="17" t="n"/>
     </row>
     <row r="8" ht="14" customHeight="1">
       <c r="A8" s="15" t="inlineStr"/>
@@ -5858,6 +5879,7 @@
       <c r="D8" s="17" t="n"/>
       <c r="E8" s="17" t="n"/>
       <c r="F8" s="17" t="n"/>
+      <c r="G8" s="17" t="n"/>
     </row>
     <row r="9" ht="14" customHeight="1">
       <c r="A9" s="15" t="inlineStr"/>
@@ -5870,6 +5892,7 @@
       <c r="D9" s="17" t="n"/>
       <c r="E9" s="17" t="n"/>
       <c r="F9" s="17" t="n"/>
+      <c r="G9" s="17" t="n"/>
     </row>
     <row r="10" ht="14" customHeight="1">
       <c r="A10" s="15" t="inlineStr"/>
@@ -5882,6 +5905,7 @@
       <c r="D10" s="17" t="n"/>
       <c r="E10" s="17" t="n"/>
       <c r="F10" s="17" t="n"/>
+      <c r="G10" s="17" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="18" t="inlineStr">
@@ -5891,12 +5915,13 @@
       </c>
       <c r="C11" s="2" t="inlineStr"/>
       <c r="D11" s="2" t="inlineStr"/>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>MTD SCORE</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>MTD DOLLARS</t>
         </is>
@@ -5919,11 +5944,12 @@
       <c r="D12" s="22" t="n">
         <v>100</v>
       </c>
-      <c r="E12" s="23">
-        <f>IFERROR(AVERAGE(C12:D12),"")</f>
-        <v/>
-      </c>
-      <c r="F12" s="24" t="n">
+      <c r="E12" s="21" t="n"/>
+      <c r="F12" s="23">
+        <f>IFERROR(AVERAGE(C12:E12),"")</f>
+        <v/>
+      </c>
+      <c r="G12" s="24" t="n">
         <v>46</v>
       </c>
     </row>
@@ -5940,11 +5966,12 @@
       </c>
       <c r="C13" s="21" t="n"/>
       <c r="D13" s="21" t="n"/>
-      <c r="E13" s="23">
-        <f>IFERROR(AVERAGE(C13:D13),"")</f>
-        <v/>
-      </c>
-      <c r="F13" s="21" t="n"/>
+      <c r="E13" s="21" t="n"/>
+      <c r="F13" s="23">
+        <f>IFERROR(AVERAGE(C13:E13),"")</f>
+        <v/>
+      </c>
+      <c r="G13" s="21" t="n"/>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
@@ -5959,11 +5986,12 @@
       </c>
       <c r="C14" s="21" t="n"/>
       <c r="D14" s="21" t="n"/>
-      <c r="E14" s="23">
-        <f>IFERROR(AVERAGE(C14:D14),"")</f>
-        <v/>
-      </c>
-      <c r="F14" s="21" t="n"/>
+      <c r="E14" s="21" t="n"/>
+      <c r="F14" s="23">
+        <f>IFERROR(AVERAGE(C14:E14),"")</f>
+        <v/>
+      </c>
+      <c r="G14" s="21" t="n"/>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
@@ -5978,11 +6006,12 @@
       </c>
       <c r="C15" s="28" t="n"/>
       <c r="D15" s="28" t="n"/>
-      <c r="E15" s="23">
-        <f>IFERROR(AVERAGE(C15:D15),"")</f>
-        <v/>
-      </c>
-      <c r="F15" s="28" t="n"/>
+      <c r="E15" s="28" t="n"/>
+      <c r="F15" s="23">
+        <f>IFERROR(AVERAGE(C15:E15),"")</f>
+        <v/>
+      </c>
+      <c r="G15" s="28" t="n"/>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
@@ -5997,11 +6026,12 @@
       </c>
       <c r="C16" s="28" t="n"/>
       <c r="D16" s="28" t="n"/>
-      <c r="E16" s="23">
-        <f>IFERROR(AVERAGE(C16:D16),"")</f>
-        <v/>
-      </c>
-      <c r="F16" s="28" t="n"/>
+      <c r="E16" s="28" t="n"/>
+      <c r="F16" s="23">
+        <f>IFERROR(AVERAGE(C16:E16),"")</f>
+        <v/>
+      </c>
+      <c r="G16" s="28" t="n"/>
     </row>
     <row r="17" ht="17" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
@@ -6016,11 +6046,12 @@
       </c>
       <c r="C17" s="28" t="n"/>
       <c r="D17" s="28" t="n"/>
-      <c r="E17" s="23">
-        <f>IFERROR(AVERAGE(C17:D17),"")</f>
-        <v/>
-      </c>
-      <c r="F17" s="28" t="n"/>
+      <c r="E17" s="28" t="n"/>
+      <c r="F17" s="23">
+        <f>IFERROR(AVERAGE(C17:E17),"")</f>
+        <v/>
+      </c>
+      <c r="G17" s="28" t="n"/>
     </row>
     <row r="18" ht="17" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
@@ -6035,11 +6066,12 @@
       </c>
       <c r="C18" s="28" t="n"/>
       <c r="D18" s="28" t="n"/>
-      <c r="E18" s="23">
-        <f>IFERROR(AVERAGE(C18:D18),"")</f>
-        <v/>
-      </c>
-      <c r="F18" s="28" t="n"/>
+      <c r="E18" s="28" t="n"/>
+      <c r="F18" s="23">
+        <f>IFERROR(AVERAGE(C18:E18),"")</f>
+        <v/>
+      </c>
+      <c r="G18" s="28" t="n"/>
     </row>
     <row r="19" ht="17" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
@@ -6056,11 +6088,12 @@
       <c r="D19" s="22" t="n">
         <v>100</v>
       </c>
-      <c r="E19" s="23">
-        <f>IFERROR(AVERAGE(C19:D19),"")</f>
-        <v/>
-      </c>
-      <c r="F19" s="24" t="n">
+      <c r="E19" s="28" t="n"/>
+      <c r="F19" s="23">
+        <f>IFERROR(AVERAGE(C19:E19),"")</f>
+        <v/>
+      </c>
+      <c r="G19" s="24" t="n">
         <v>46</v>
       </c>
     </row>
@@ -6077,11 +6110,12 @@
       </c>
       <c r="C20" s="28" t="n"/>
       <c r="D20" s="28" t="n"/>
-      <c r="E20" s="23">
-        <f>IFERROR(AVERAGE(C20:D20),"")</f>
-        <v/>
-      </c>
-      <c r="F20" s="28" t="n"/>
+      <c r="E20" s="28" t="n"/>
+      <c r="F20" s="23">
+        <f>IFERROR(AVERAGE(C20:E20),"")</f>
+        <v/>
+      </c>
+      <c r="G20" s="28" t="n"/>
     </row>
     <row r="21" ht="17" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
@@ -6096,11 +6130,12 @@
       </c>
       <c r="C21" s="28" t="n"/>
       <c r="D21" s="28" t="n"/>
-      <c r="E21" s="23">
-        <f>IFERROR(AVERAGE(C21:D21),"")</f>
-        <v/>
-      </c>
-      <c r="F21" s="28" t="n"/>
+      <c r="E21" s="28" t="n"/>
+      <c r="F21" s="23">
+        <f>IFERROR(AVERAGE(C21:E21),"")</f>
+        <v/>
+      </c>
+      <c r="G21" s="28" t="n"/>
     </row>
     <row r="22" ht="17" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
@@ -6115,11 +6150,12 @@
       </c>
       <c r="C22" s="28" t="n"/>
       <c r="D22" s="28" t="n"/>
-      <c r="E22" s="23">
-        <f>IFERROR(AVERAGE(C22:D22),"")</f>
-        <v/>
-      </c>
-      <c r="F22" s="28" t="n"/>
+      <c r="E22" s="28" t="n"/>
+      <c r="F22" s="23">
+        <f>IFERROR(AVERAGE(C22:E22),"")</f>
+        <v/>
+      </c>
+      <c r="G22" s="28" t="n"/>
     </row>
     <row r="23" ht="17" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
@@ -6136,11 +6172,12 @@
         <v>95</v>
       </c>
       <c r="D23" s="28" t="n"/>
-      <c r="E23" s="23">
-        <f>IFERROR(AVERAGE(C23:D23),"")</f>
-        <v/>
-      </c>
-      <c r="F23" s="28" t="n"/>
+      <c r="E23" s="28" t="n"/>
+      <c r="F23" s="23">
+        <f>IFERROR(AVERAGE(C23:E23),"")</f>
+        <v/>
+      </c>
+      <c r="G23" s="28" t="n"/>
     </row>
     <row r="24" ht="17" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
@@ -6155,11 +6192,12 @@
       </c>
       <c r="C24" s="28" t="n"/>
       <c r="D24" s="28" t="n"/>
-      <c r="E24" s="23">
-        <f>IFERROR(AVERAGE(C24:D24),"")</f>
-        <v/>
-      </c>
-      <c r="F24" s="28" t="n"/>
+      <c r="E24" s="28" t="n"/>
+      <c r="F24" s="23">
+        <f>IFERROR(AVERAGE(C24:E24),"")</f>
+        <v/>
+      </c>
+      <c r="G24" s="28" t="n"/>
     </row>
     <row r="25" ht="17" customHeight="1">
       <c r="A25" s="26" t="inlineStr">
@@ -6174,11 +6212,12 @@
       </c>
       <c r="C25" s="28" t="n"/>
       <c r="D25" s="28" t="n"/>
-      <c r="E25" s="23">
-        <f>IFERROR(AVERAGE(C25:D25),"")</f>
-        <v/>
-      </c>
-      <c r="F25" s="28" t="n"/>
+      <c r="E25" s="28" t="n"/>
+      <c r="F25" s="23">
+        <f>IFERROR(AVERAGE(C25:E25),"")</f>
+        <v/>
+      </c>
+      <c r="G25" s="28" t="n"/>
     </row>
     <row r="26" ht="17" customHeight="1">
       <c r="A26" s="26" t="inlineStr">
@@ -6193,11 +6232,12 @@
       </c>
       <c r="C26" s="28" t="n"/>
       <c r="D26" s="28" t="n"/>
-      <c r="E26" s="23">
-        <f>IFERROR(AVERAGE(C26:D26),"")</f>
-        <v/>
-      </c>
-      <c r="F26" s="28" t="n"/>
+      <c r="E26" s="28" t="n"/>
+      <c r="F26" s="23">
+        <f>IFERROR(AVERAGE(C26:E26),"")</f>
+        <v/>
+      </c>
+      <c r="G26" s="28" t="n"/>
     </row>
     <row r="27" ht="17" customHeight="1">
       <c r="A27" s="26" t="inlineStr">
@@ -6212,11 +6252,12 @@
       </c>
       <c r="C27" s="28" t="n"/>
       <c r="D27" s="28" t="n"/>
-      <c r="E27" s="23">
-        <f>IFERROR(AVERAGE(C27:D27),"")</f>
-        <v/>
-      </c>
-      <c r="F27" s="28" t="n"/>
+      <c r="E27" s="28" t="n"/>
+      <c r="F27" s="23">
+        <f>IFERROR(AVERAGE(C27:E27),"")</f>
+        <v/>
+      </c>
+      <c r="G27" s="28" t="n"/>
     </row>
     <row r="28" ht="17" customHeight="1">
       <c r="A28" s="26" t="inlineStr">
@@ -6233,11 +6274,12 @@
       <c r="D28" s="22" t="n">
         <v>100</v>
       </c>
-      <c r="E28" s="23">
-        <f>IFERROR(AVERAGE(C28:D28),"")</f>
-        <v/>
-      </c>
-      <c r="F28" s="24" t="n">
+      <c r="E28" s="28" t="n"/>
+      <c r="F28" s="23">
+        <f>IFERROR(AVERAGE(C28:E28),"")</f>
+        <v/>
+      </c>
+      <c r="G28" s="24" t="n">
         <v>46</v>
       </c>
     </row>
@@ -6254,11 +6296,12 @@
       </c>
       <c r="C29" s="28" t="n"/>
       <c r="D29" s="28" t="n"/>
-      <c r="E29" s="23">
-        <f>IFERROR(AVERAGE(C29:D29),"")</f>
-        <v/>
-      </c>
-      <c r="F29" s="28" t="n"/>
+      <c r="E29" s="28" t="n"/>
+      <c r="F29" s="23">
+        <f>IFERROR(AVERAGE(C29:E29),"")</f>
+        <v/>
+      </c>
+      <c r="G29" s="28" t="n"/>
     </row>
     <row r="30" ht="17" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
@@ -6273,11 +6316,12 @@
       </c>
       <c r="C30" s="28" t="n"/>
       <c r="D30" s="28" t="n"/>
-      <c r="E30" s="23">
-        <f>IFERROR(AVERAGE(C30:D30),"")</f>
-        <v/>
-      </c>
-      <c r="F30" s="28" t="n"/>
+      <c r="E30" s="28" t="n"/>
+      <c r="F30" s="23">
+        <f>IFERROR(AVERAGE(C30:E30),"")</f>
+        <v/>
+      </c>
+      <c r="G30" s="28" t="n"/>
     </row>
     <row r="31" ht="17" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
@@ -6296,11 +6340,12 @@
       <c r="D31" s="22" t="n">
         <v>100</v>
       </c>
-      <c r="E31" s="23">
-        <f>IFERROR(AVERAGE(C31:D31),"")</f>
-        <v/>
-      </c>
-      <c r="F31" s="24" t="n">
+      <c r="E31" s="28" t="n"/>
+      <c r="F31" s="23">
+        <f>IFERROR(AVERAGE(C31:E31),"")</f>
+        <v/>
+      </c>
+      <c r="G31" s="24" t="n">
         <v>46</v>
       </c>
     </row>
@@ -6317,11 +6362,12 @@
       </c>
       <c r="C32" s="28" t="n"/>
       <c r="D32" s="28" t="n"/>
-      <c r="E32" s="23">
-        <f>IFERROR(AVERAGE(C32:D32),"")</f>
-        <v/>
-      </c>
-      <c r="F32" s="28" t="n"/>
+      <c r="E32" s="28" t="n"/>
+      <c r="F32" s="23">
+        <f>IFERROR(AVERAGE(C32:E32),"")</f>
+        <v/>
+      </c>
+      <c r="G32" s="28" t="n"/>
     </row>
     <row r="33" ht="17" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
@@ -6336,11 +6382,12 @@
       </c>
       <c r="C33" s="28" t="n"/>
       <c r="D33" s="28" t="n"/>
-      <c r="E33" s="23">
-        <f>IFERROR(AVERAGE(C33:D33),"")</f>
-        <v/>
-      </c>
-      <c r="F33" s="28" t="n"/>
+      <c r="E33" s="28" t="n"/>
+      <c r="F33" s="23">
+        <f>IFERROR(AVERAGE(C33:E33),"")</f>
+        <v/>
+      </c>
+      <c r="G33" s="28" t="n"/>
     </row>
     <row r="34" ht="17" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
@@ -6355,11 +6402,12 @@
       </c>
       <c r="C34" s="28" t="n"/>
       <c r="D34" s="28" t="n"/>
-      <c r="E34" s="23">
-        <f>IFERROR(AVERAGE(C34:D34),"")</f>
-        <v/>
-      </c>
-      <c r="F34" s="28" t="n"/>
+      <c r="E34" s="28" t="n"/>
+      <c r="F34" s="23">
+        <f>IFERROR(AVERAGE(C34:E34),"")</f>
+        <v/>
+      </c>
+      <c r="G34" s="28" t="n"/>
     </row>
     <row r="35" ht="17" customHeight="1">
       <c r="A35" s="26" t="inlineStr">
@@ -6374,11 +6422,12 @@
       </c>
       <c r="C35" s="28" t="n"/>
       <c r="D35" s="28" t="n"/>
-      <c r="E35" s="23">
-        <f>IFERROR(AVERAGE(C35:D35),"")</f>
-        <v/>
-      </c>
-      <c r="F35" s="28" t="n"/>
+      <c r="E35" s="28" t="n"/>
+      <c r="F35" s="23">
+        <f>IFERROR(AVERAGE(C35:E35),"")</f>
+        <v/>
+      </c>
+      <c r="G35" s="28" t="n"/>
     </row>
     <row r="36" ht="17" customHeight="1">
       <c r="A36" s="26" t="inlineStr">
@@ -6393,11 +6442,12 @@
       </c>
       <c r="C36" s="28" t="n"/>
       <c r="D36" s="28" t="n"/>
-      <c r="E36" s="23">
-        <f>IFERROR(AVERAGE(C36:D36),"")</f>
-        <v/>
-      </c>
-      <c r="F36" s="28" t="n"/>
+      <c r="E36" s="28" t="n"/>
+      <c r="F36" s="23">
+        <f>IFERROR(AVERAGE(C36:E36),"")</f>
+        <v/>
+      </c>
+      <c r="G36" s="28" t="n"/>
     </row>
     <row r="37" ht="17" customHeight="1">
       <c r="A37" s="26" t="inlineStr">
@@ -6412,11 +6462,12 @@
       </c>
       <c r="C37" s="28" t="n"/>
       <c r="D37" s="28" t="n"/>
-      <c r="E37" s="23">
-        <f>IFERROR(AVERAGE(C37:D37),"")</f>
-        <v/>
-      </c>
-      <c r="F37" s="28" t="n"/>
+      <c r="E37" s="28" t="n"/>
+      <c r="F37" s="23">
+        <f>IFERROR(AVERAGE(C37:E37),"")</f>
+        <v/>
+      </c>
+      <c r="G37" s="28" t="n"/>
     </row>
     <row r="38" ht="17" customHeight="1">
       <c r="A38" s="26" t="inlineStr">
@@ -6433,11 +6484,12 @@
       <c r="D38" s="22" t="n">
         <v>100</v>
       </c>
-      <c r="E38" s="23">
-        <f>IFERROR(AVERAGE(C38:D38),"")</f>
-        <v/>
-      </c>
-      <c r="F38" s="24" t="n">
+      <c r="E38" s="28" t="n"/>
+      <c r="F38" s="23">
+        <f>IFERROR(AVERAGE(C38:E38),"")</f>
+        <v/>
+      </c>
+      <c r="G38" s="24" t="n">
         <v>46</v>
       </c>
     </row>
@@ -6451,8 +6503,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A39:F39"/>
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A39:G39"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Shop_Tracker_2065_2026.xlsx
+++ b/Shop_Tracker_2065_2026.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="January" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="February" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="March" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="April" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="May" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="June" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="January" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="February" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="March" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="April" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="May" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="June" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6172,7 +6172,9 @@
         <v>95</v>
       </c>
       <c r="D23" s="28" t="n"/>
-      <c r="E23" s="28" t="n"/>
+      <c r="E23" s="30" t="n">
+        <v>80</v>
+      </c>
       <c r="F23" s="23">
         <f>IFERROR(AVERAGE(C23:E23),"")</f>
         <v/>
@@ -6232,7 +6234,9 @@
       </c>
       <c r="C26" s="28" t="n"/>
       <c r="D26" s="28" t="n"/>
-      <c r="E26" s="28" t="n"/>
+      <c r="E26" s="30" t="n">
+        <v>80</v>
+      </c>
       <c r="F26" s="23">
         <f>IFERROR(AVERAGE(C26:E26),"")</f>
         <v/>
@@ -6362,7 +6366,9 @@
       </c>
       <c r="C32" s="28" t="n"/>
       <c r="D32" s="28" t="n"/>
-      <c r="E32" s="28" t="n"/>
+      <c r="E32" s="30" t="n">
+        <v>80</v>
+      </c>
       <c r="F32" s="23">
         <f>IFERROR(AVERAGE(C32:E32),"")</f>
         <v/>
@@ -6422,7 +6428,9 @@
       </c>
       <c r="C35" s="28" t="n"/>
       <c r="D35" s="28" t="n"/>
-      <c r="E35" s="28" t="n"/>
+      <c r="E35" s="30" t="n">
+        <v>80</v>
+      </c>
       <c r="F35" s="23">
         <f>IFERROR(AVERAGE(C35:E35),"")</f>
         <v/>

--- a/Shop_Tracker_2065_2026.xlsx
+++ b/Shop_Tracker_2065_2026.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="January" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="February" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="March" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="April" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="May" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="June" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="January" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="February" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="March" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="April" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="May" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="June" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/Shop_Tracker_2065_2026.xlsx
+++ b/Shop_Tracker_2065_2026.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="January" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="February" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="March" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="April" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="May" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="June" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="January" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="February" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="March" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="April" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="May" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="June" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5725,7 +5725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -5733,8 +5733,10 @@
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -5764,10 +5766,20 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
+          <t>WEEK 4</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>WEEK 5</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
           <t>MTD SCORE</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>MTD DOLLARS</t>
         </is>
@@ -5795,8 +5807,18 @@
           <t>06/14</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr"/>
-      <c r="G3" s="4" t="inlineStr"/>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>06/21</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>06/24</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr"/>
+      <c r="I3" s="4" t="inlineStr"/>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="4" t="inlineStr"/>
@@ -5820,8 +5842,18 @@
           <t>Dinner</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="9" t="inlineStr"/>
@@ -5839,8 +5871,14 @@
       <c r="E5" s="13" t="n">
         <v>80</v>
       </c>
-      <c r="F5" s="9" t="inlineStr"/>
-      <c r="G5" s="9" t="inlineStr"/>
+      <c r="F5" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="G5" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="H5" s="9" t="inlineStr"/>
+      <c r="I5" s="9" t="inlineStr"/>
     </row>
     <row r="6" ht="14" customHeight="1">
       <c r="A6" s="15" t="inlineStr"/>
@@ -5854,6 +5892,8 @@
       <c r="E6" s="17" t="n"/>
       <c r="F6" s="17" t="n"/>
       <c r="G6" s="17" t="n"/>
+      <c r="H6" s="17" t="n"/>
+      <c r="I6" s="17" t="n"/>
     </row>
     <row r="7" ht="14" customHeight="1">
       <c r="A7" s="15" t="inlineStr"/>
@@ -5867,6 +5907,8 @@
       <c r="E7" s="17" t="n"/>
       <c r="F7" s="17" t="n"/>
       <c r="G7" s="17" t="n"/>
+      <c r="H7" s="17" t="n"/>
+      <c r="I7" s="17" t="n"/>
     </row>
     <row r="8" ht="14" customHeight="1">
       <c r="A8" s="15" t="inlineStr"/>
@@ -5880,6 +5922,8 @@
       <c r="E8" s="17" t="n"/>
       <c r="F8" s="17" t="n"/>
       <c r="G8" s="17" t="n"/>
+      <c r="H8" s="17" t="n"/>
+      <c r="I8" s="17" t="n"/>
     </row>
     <row r="9" ht="14" customHeight="1">
       <c r="A9" s="15" t="inlineStr"/>
@@ -5893,6 +5937,8 @@
       <c r="E9" s="17" t="n"/>
       <c r="F9" s="17" t="n"/>
       <c r="G9" s="17" t="n"/>
+      <c r="H9" s="17" t="n"/>
+      <c r="I9" s="17" t="n"/>
     </row>
     <row r="10" ht="14" customHeight="1">
       <c r="A10" s="15" t="inlineStr"/>
@@ -5906,6 +5952,8 @@
       <c r="E10" s="17" t="n"/>
       <c r="F10" s="17" t="n"/>
       <c r="G10" s="17" t="n"/>
+      <c r="H10" s="17" t="n"/>
+      <c r="I10" s="17" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="18" t="inlineStr">
@@ -5916,12 +5964,14 @@
       <c r="C11" s="2" t="inlineStr"/>
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>MTD SCORE</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>MTD DOLLARS</t>
         </is>
@@ -5945,11 +5995,13 @@
         <v>100</v>
       </c>
       <c r="E12" s="21" t="n"/>
-      <c r="F12" s="23">
-        <f>IFERROR(AVERAGE(C12:E12),"")</f>
-        <v/>
-      </c>
-      <c r="G12" s="24" t="n">
+      <c r="F12" s="21" t="n"/>
+      <c r="G12" s="21" t="n"/>
+      <c r="H12" s="23">
+        <f>IFERROR(AVERAGE(C12:G12),"")</f>
+        <v/>
+      </c>
+      <c r="I12" s="24" t="n">
         <v>46</v>
       </c>
     </row>
@@ -5967,11 +6019,13 @@
       <c r="C13" s="21" t="n"/>
       <c r="D13" s="21" t="n"/>
       <c r="E13" s="21" t="n"/>
-      <c r="F13" s="23">
-        <f>IFERROR(AVERAGE(C13:E13),"")</f>
-        <v/>
-      </c>
+      <c r="F13" s="21" t="n"/>
       <c r="G13" s="21" t="n"/>
+      <c r="H13" s="23">
+        <f>IFERROR(AVERAGE(C13:G13),"")</f>
+        <v/>
+      </c>
+      <c r="I13" s="21" t="n"/>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
@@ -5987,11 +6041,13 @@
       <c r="C14" s="21" t="n"/>
       <c r="D14" s="21" t="n"/>
       <c r="E14" s="21" t="n"/>
-      <c r="F14" s="23">
-        <f>IFERROR(AVERAGE(C14:E14),"")</f>
-        <v/>
-      </c>
+      <c r="F14" s="21" t="n"/>
       <c r="G14" s="21" t="n"/>
+      <c r="H14" s="23">
+        <f>IFERROR(AVERAGE(C14:G14),"")</f>
+        <v/>
+      </c>
+      <c r="I14" s="21" t="n"/>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
@@ -6007,11 +6063,13 @@
       <c r="C15" s="28" t="n"/>
       <c r="D15" s="28" t="n"/>
       <c r="E15" s="28" t="n"/>
-      <c r="F15" s="23">
-        <f>IFERROR(AVERAGE(C15:E15),"")</f>
-        <v/>
-      </c>
+      <c r="F15" s="28" t="n"/>
       <c r="G15" s="28" t="n"/>
+      <c r="H15" s="23">
+        <f>IFERROR(AVERAGE(C15:G15),"")</f>
+        <v/>
+      </c>
+      <c r="I15" s="28" t="n"/>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
@@ -6027,11 +6085,13 @@
       <c r="C16" s="28" t="n"/>
       <c r="D16" s="28" t="n"/>
       <c r="E16" s="28" t="n"/>
-      <c r="F16" s="23">
-        <f>IFERROR(AVERAGE(C16:E16),"")</f>
-        <v/>
-      </c>
+      <c r="F16" s="28" t="n"/>
       <c r="G16" s="28" t="n"/>
+      <c r="H16" s="23">
+        <f>IFERROR(AVERAGE(C16:G16),"")</f>
+        <v/>
+      </c>
+      <c r="I16" s="28" t="n"/>
     </row>
     <row r="17" ht="17" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
@@ -6047,11 +6107,13 @@
       <c r="C17" s="28" t="n"/>
       <c r="D17" s="28" t="n"/>
       <c r="E17" s="28" t="n"/>
-      <c r="F17" s="23">
-        <f>IFERROR(AVERAGE(C17:E17),"")</f>
-        <v/>
-      </c>
+      <c r="F17" s="28" t="n"/>
       <c r="G17" s="28" t="n"/>
+      <c r="H17" s="23">
+        <f>IFERROR(AVERAGE(C17:G17),"")</f>
+        <v/>
+      </c>
+      <c r="I17" s="28" t="n"/>
     </row>
     <row r="18" ht="17" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
@@ -6067,11 +6129,13 @@
       <c r="C18" s="28" t="n"/>
       <c r="D18" s="28" t="n"/>
       <c r="E18" s="28" t="n"/>
-      <c r="F18" s="23">
-        <f>IFERROR(AVERAGE(C18:E18),"")</f>
-        <v/>
-      </c>
+      <c r="F18" s="28" t="n"/>
       <c r="G18" s="28" t="n"/>
+      <c r="H18" s="23">
+        <f>IFERROR(AVERAGE(C18:G18),"")</f>
+        <v/>
+      </c>
+      <c r="I18" s="28" t="n"/>
     </row>
     <row r="19" ht="17" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
@@ -6089,11 +6153,13 @@
         <v>100</v>
       </c>
       <c r="E19" s="28" t="n"/>
-      <c r="F19" s="23">
-        <f>IFERROR(AVERAGE(C19:E19),"")</f>
-        <v/>
-      </c>
-      <c r="G19" s="24" t="n">
+      <c r="F19" s="28" t="n"/>
+      <c r="G19" s="28" t="n"/>
+      <c r="H19" s="23">
+        <f>IFERROR(AVERAGE(C19:G19),"")</f>
+        <v/>
+      </c>
+      <c r="I19" s="24" t="n">
         <v>46</v>
       </c>
     </row>
@@ -6111,11 +6177,13 @@
       <c r="C20" s="28" t="n"/>
       <c r="D20" s="28" t="n"/>
       <c r="E20" s="28" t="n"/>
-      <c r="F20" s="23">
-        <f>IFERROR(AVERAGE(C20:E20),"")</f>
-        <v/>
-      </c>
+      <c r="F20" s="28" t="n"/>
       <c r="G20" s="28" t="n"/>
+      <c r="H20" s="23">
+        <f>IFERROR(AVERAGE(C20:G20),"")</f>
+        <v/>
+      </c>
+      <c r="I20" s="28" t="n"/>
     </row>
     <row r="21" ht="17" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
@@ -6131,11 +6199,13 @@
       <c r="C21" s="28" t="n"/>
       <c r="D21" s="28" t="n"/>
       <c r="E21" s="28" t="n"/>
-      <c r="F21" s="23">
-        <f>IFERROR(AVERAGE(C21:E21),"")</f>
-        <v/>
-      </c>
+      <c r="F21" s="28" t="n"/>
       <c r="G21" s="28" t="n"/>
+      <c r="H21" s="23">
+        <f>IFERROR(AVERAGE(C21:G21),"")</f>
+        <v/>
+      </c>
+      <c r="I21" s="28" t="n"/>
     </row>
     <row r="22" ht="17" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
@@ -6151,11 +6221,13 @@
       <c r="C22" s="28" t="n"/>
       <c r="D22" s="28" t="n"/>
       <c r="E22" s="28" t="n"/>
-      <c r="F22" s="23">
-        <f>IFERROR(AVERAGE(C22:E22),"")</f>
-        <v/>
-      </c>
+      <c r="F22" s="28" t="n"/>
       <c r="G22" s="28" t="n"/>
+      <c r="H22" s="23">
+        <f>IFERROR(AVERAGE(C22:G22),"")</f>
+        <v/>
+      </c>
+      <c r="I22" s="28" t="n"/>
     </row>
     <row r="23" ht="17" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
@@ -6175,11 +6247,13 @@
       <c r="E23" s="30" t="n">
         <v>80</v>
       </c>
-      <c r="F23" s="23">
-        <f>IFERROR(AVERAGE(C23:E23),"")</f>
-        <v/>
-      </c>
+      <c r="F23" s="28" t="n"/>
       <c r="G23" s="28" t="n"/>
+      <c r="H23" s="23">
+        <f>IFERROR(AVERAGE(C23:G23),"")</f>
+        <v/>
+      </c>
+      <c r="I23" s="28" t="n"/>
     </row>
     <row r="24" ht="17" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
@@ -6195,11 +6269,13 @@
       <c r="C24" s="28" t="n"/>
       <c r="D24" s="28" t="n"/>
       <c r="E24" s="28" t="n"/>
-      <c r="F24" s="23">
-        <f>IFERROR(AVERAGE(C24:E24),"")</f>
-        <v/>
-      </c>
+      <c r="F24" s="28" t="n"/>
       <c r="G24" s="28" t="n"/>
+      <c r="H24" s="23">
+        <f>IFERROR(AVERAGE(C24:G24),"")</f>
+        <v/>
+      </c>
+      <c r="I24" s="28" t="n"/>
     </row>
     <row r="25" ht="17" customHeight="1">
       <c r="A25" s="26" t="inlineStr">
@@ -6215,11 +6291,13 @@
       <c r="C25" s="28" t="n"/>
       <c r="D25" s="28" t="n"/>
       <c r="E25" s="28" t="n"/>
-      <c r="F25" s="23">
-        <f>IFERROR(AVERAGE(C25:E25),"")</f>
-        <v/>
-      </c>
+      <c r="F25" s="28" t="n"/>
       <c r="G25" s="28" t="n"/>
+      <c r="H25" s="23">
+        <f>IFERROR(AVERAGE(C25:G25),"")</f>
+        <v/>
+      </c>
+      <c r="I25" s="28" t="n"/>
     </row>
     <row r="26" ht="17" customHeight="1">
       <c r="A26" s="26" t="inlineStr">
@@ -6237,11 +6315,13 @@
       <c r="E26" s="30" t="n">
         <v>80</v>
       </c>
-      <c r="F26" s="23">
-        <f>IFERROR(AVERAGE(C26:E26),"")</f>
-        <v/>
-      </c>
+      <c r="F26" s="28" t="n"/>
       <c r="G26" s="28" t="n"/>
+      <c r="H26" s="23">
+        <f>IFERROR(AVERAGE(C26:G26),"")</f>
+        <v/>
+      </c>
+      <c r="I26" s="28" t="n"/>
     </row>
     <row r="27" ht="17" customHeight="1">
       <c r="A27" s="26" t="inlineStr">
@@ -6257,11 +6337,13 @@
       <c r="C27" s="28" t="n"/>
       <c r="D27" s="28" t="n"/>
       <c r="E27" s="28" t="n"/>
-      <c r="F27" s="23">
-        <f>IFERROR(AVERAGE(C27:E27),"")</f>
-        <v/>
-      </c>
+      <c r="F27" s="28" t="n"/>
       <c r="G27" s="28" t="n"/>
+      <c r="H27" s="23">
+        <f>IFERROR(AVERAGE(C27:G27),"")</f>
+        <v/>
+      </c>
+      <c r="I27" s="28" t="n"/>
     </row>
     <row r="28" ht="17" customHeight="1">
       <c r="A28" s="26" t="inlineStr">
@@ -6279,11 +6361,13 @@
         <v>100</v>
       </c>
       <c r="E28" s="28" t="n"/>
-      <c r="F28" s="23">
-        <f>IFERROR(AVERAGE(C28:E28),"")</f>
-        <v/>
-      </c>
-      <c r="G28" s="24" t="n">
+      <c r="F28" s="28" t="n"/>
+      <c r="G28" s="28" t="n"/>
+      <c r="H28" s="23">
+        <f>IFERROR(AVERAGE(C28:G28),"")</f>
+        <v/>
+      </c>
+      <c r="I28" s="24" t="n">
         <v>46</v>
       </c>
     </row>
@@ -6301,11 +6385,13 @@
       <c r="C29" s="28" t="n"/>
       <c r="D29" s="28" t="n"/>
       <c r="E29" s="28" t="n"/>
-      <c r="F29" s="23">
-        <f>IFERROR(AVERAGE(C29:E29),"")</f>
-        <v/>
-      </c>
+      <c r="F29" s="28" t="n"/>
       <c r="G29" s="28" t="n"/>
+      <c r="H29" s="23">
+        <f>IFERROR(AVERAGE(C29:G29),"")</f>
+        <v/>
+      </c>
+      <c r="I29" s="28" t="n"/>
     </row>
     <row r="30" ht="17" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
@@ -6321,11 +6407,13 @@
       <c r="C30" s="28" t="n"/>
       <c r="D30" s="28" t="n"/>
       <c r="E30" s="28" t="n"/>
-      <c r="F30" s="23">
-        <f>IFERROR(AVERAGE(C30:E30),"")</f>
-        <v/>
-      </c>
+      <c r="F30" s="28" t="n"/>
       <c r="G30" s="28" t="n"/>
+      <c r="H30" s="23">
+        <f>IFERROR(AVERAGE(C30:G30),"")</f>
+        <v/>
+      </c>
+      <c r="I30" s="28" t="n"/>
     </row>
     <row r="31" ht="17" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
@@ -6345,11 +6433,13 @@
         <v>100</v>
       </c>
       <c r="E31" s="28" t="n"/>
-      <c r="F31" s="23">
-        <f>IFERROR(AVERAGE(C31:E31),"")</f>
-        <v/>
-      </c>
-      <c r="G31" s="24" t="n">
+      <c r="F31" s="28" t="n"/>
+      <c r="G31" s="28" t="n"/>
+      <c r="H31" s="23">
+        <f>IFERROR(AVERAGE(C31:G31),"")</f>
+        <v/>
+      </c>
+      <c r="I31" s="24" t="n">
         <v>46</v>
       </c>
     </row>
@@ -6369,11 +6459,13 @@
       <c r="E32" s="30" t="n">
         <v>80</v>
       </c>
-      <c r="F32" s="23">
-        <f>IFERROR(AVERAGE(C32:E32),"")</f>
-        <v/>
-      </c>
+      <c r="F32" s="28" t="n"/>
       <c r="G32" s="28" t="n"/>
+      <c r="H32" s="23">
+        <f>IFERROR(AVERAGE(C32:G32),"")</f>
+        <v/>
+      </c>
+      <c r="I32" s="28" t="n"/>
     </row>
     <row r="33" ht="17" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
@@ -6389,11 +6481,13 @@
       <c r="C33" s="28" t="n"/>
       <c r="D33" s="28" t="n"/>
       <c r="E33" s="28" t="n"/>
-      <c r="F33" s="23">
-        <f>IFERROR(AVERAGE(C33:E33),"")</f>
-        <v/>
-      </c>
+      <c r="F33" s="28" t="n"/>
       <c r="G33" s="28" t="n"/>
+      <c r="H33" s="23">
+        <f>IFERROR(AVERAGE(C33:G33),"")</f>
+        <v/>
+      </c>
+      <c r="I33" s="28" t="n"/>
     </row>
     <row r="34" ht="17" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
@@ -6409,11 +6503,13 @@
       <c r="C34" s="28" t="n"/>
       <c r="D34" s="28" t="n"/>
       <c r="E34" s="28" t="n"/>
-      <c r="F34" s="23">
-        <f>IFERROR(AVERAGE(C34:E34),"")</f>
-        <v/>
-      </c>
+      <c r="F34" s="28" t="n"/>
       <c r="G34" s="28" t="n"/>
+      <c r="H34" s="23">
+        <f>IFERROR(AVERAGE(C34:G34),"")</f>
+        <v/>
+      </c>
+      <c r="I34" s="28" t="n"/>
     </row>
     <row r="35" ht="17" customHeight="1">
       <c r="A35" s="26" t="inlineStr">
@@ -6431,11 +6527,13 @@
       <c r="E35" s="30" t="n">
         <v>80</v>
       </c>
-      <c r="F35" s="23">
-        <f>IFERROR(AVERAGE(C35:E35),"")</f>
-        <v/>
-      </c>
+      <c r="F35" s="28" t="n"/>
       <c r="G35" s="28" t="n"/>
+      <c r="H35" s="23">
+        <f>IFERROR(AVERAGE(C35:G35),"")</f>
+        <v/>
+      </c>
+      <c r="I35" s="28" t="n"/>
     </row>
     <row r="36" ht="17" customHeight="1">
       <c r="A36" s="26" t="inlineStr">
@@ -6451,11 +6549,13 @@
       <c r="C36" s="28" t="n"/>
       <c r="D36" s="28" t="n"/>
       <c r="E36" s="28" t="n"/>
-      <c r="F36" s="23">
-        <f>IFERROR(AVERAGE(C36:E36),"")</f>
-        <v/>
-      </c>
+      <c r="F36" s="28" t="n"/>
       <c r="G36" s="28" t="n"/>
+      <c r="H36" s="23">
+        <f>IFERROR(AVERAGE(C36:G36),"")</f>
+        <v/>
+      </c>
+      <c r="I36" s="28" t="n"/>
     </row>
     <row r="37" ht="17" customHeight="1">
       <c r="A37" s="26" t="inlineStr">
@@ -6471,11 +6571,13 @@
       <c r="C37" s="28" t="n"/>
       <c r="D37" s="28" t="n"/>
       <c r="E37" s="28" t="n"/>
-      <c r="F37" s="23">
-        <f>IFERROR(AVERAGE(C37:E37),"")</f>
-        <v/>
-      </c>
+      <c r="F37" s="28" t="n"/>
       <c r="G37" s="28" t="n"/>
+      <c r="H37" s="23">
+        <f>IFERROR(AVERAGE(C37:G37),"")</f>
+        <v/>
+      </c>
+      <c r="I37" s="28" t="n"/>
     </row>
     <row r="38" ht="17" customHeight="1">
       <c r="A38" s="26" t="inlineStr">
@@ -6493,11 +6595,13 @@
         <v>100</v>
       </c>
       <c r="E38" s="28" t="n"/>
-      <c r="F38" s="23">
-        <f>IFERROR(AVERAGE(C38:E38),"")</f>
-        <v/>
-      </c>
-      <c r="G38" s="24" t="n">
+      <c r="F38" s="28" t="n"/>
+      <c r="G38" s="28" t="n"/>
+      <c r="H38" s="23">
+        <f>IFERROR(AVERAGE(C38:G38),"")</f>
+        <v/>
+      </c>
+      <c r="I38" s="24" t="n">
         <v>46</v>
       </c>
     </row>
@@ -6510,9 +6614,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A39:I39"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Shop_Tracker_2065_2026.xlsx
+++ b/Shop_Tracker_2065_2026.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="January" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="February" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="March" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="April" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="May" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="June" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="January" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="February" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="March" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="April" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="May" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="June" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5995,14 +5995,16 @@
         <v>100</v>
       </c>
       <c r="E12" s="21" t="n"/>
-      <c r="F12" s="21" t="n"/>
+      <c r="F12" s="22" t="n">
+        <v>100</v>
+      </c>
       <c r="G12" s="21" t="n"/>
       <c r="H12" s="23">
         <f>IFERROR(AVERAGE(C12:G12),"")</f>
         <v/>
       </c>
       <c r="I12" s="24" t="n">
-        <v>46</v>
+        <v>122.67</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
@@ -6459,13 +6461,19 @@
       <c r="E32" s="30" t="n">
         <v>80</v>
       </c>
-      <c r="F32" s="28" t="n"/>
-      <c r="G32" s="28" t="n"/>
+      <c r="F32" s="22" t="n">
+        <v>100</v>
+      </c>
+      <c r="G32" s="22" t="n">
+        <v>100</v>
+      </c>
       <c r="H32" s="23">
         <f>IFERROR(AVERAGE(C32:G32),"")</f>
         <v/>
       </c>
-      <c r="I32" s="28" t="n"/>
+      <c r="I32" s="24" t="n">
+        <v>191.67</v>
+      </c>
     </row>
     <row r="33" ht="17" customHeight="1">
       <c r="A33" s="26" t="inlineStr">

--- a/Shop_Tracker_2065_2026.xlsx
+++ b/Shop_Tracker_2065_2026.xlsx
@@ -5725,7 +5725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -5735,8 +5735,9 @@
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -5776,10 +5777,15 @@
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
+          <t>WEEK 6</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
           <t>MTD SCORE</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>MTD DOLLARS</t>
         </is>
@@ -5817,8 +5823,13 @@
           <t>06/24</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr"/>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>06/25</t>
+        </is>
+      </c>
       <c r="I3" s="4" t="inlineStr"/>
+      <c r="J3" s="4" t="inlineStr"/>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="4" t="inlineStr"/>
@@ -5852,8 +5863,13 @@
           <t>Dinner</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr"/>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
       <c r="I4" s="4" t="inlineStr"/>
+      <c r="J4" s="4" t="inlineStr"/>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="9" t="inlineStr"/>
@@ -5877,8 +5893,11 @@
       <c r="G5" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="H5" s="9" t="inlineStr"/>
+      <c r="H5" s="14" t="n">
+        <v>100</v>
+      </c>
       <c r="I5" s="9" t="inlineStr"/>
+      <c r="J5" s="9" t="inlineStr"/>
     </row>
     <row r="6" ht="14" customHeight="1">
       <c r="A6" s="15" t="inlineStr"/>
@@ -5894,6 +5913,7 @@
       <c r="G6" s="17" t="n"/>
       <c r="H6" s="17" t="n"/>
       <c r="I6" s="17" t="n"/>
+      <c r="J6" s="17" t="n"/>
     </row>
     <row r="7" ht="14" customHeight="1">
       <c r="A7" s="15" t="inlineStr"/>
@@ -5909,6 +5929,7 @@
       <c r="G7" s="17" t="n"/>
       <c r="H7" s="17" t="n"/>
       <c r="I7" s="17" t="n"/>
+      <c r="J7" s="17" t="n"/>
     </row>
     <row r="8" ht="14" customHeight="1">
       <c r="A8" s="15" t="inlineStr"/>
@@ -5924,6 +5945,7 @@
       <c r="G8" s="17" t="n"/>
       <c r="H8" s="17" t="n"/>
       <c r="I8" s="17" t="n"/>
+      <c r="J8" s="17" t="n"/>
     </row>
     <row r="9" ht="14" customHeight="1">
       <c r="A9" s="15" t="inlineStr"/>
@@ -5939,6 +5961,7 @@
       <c r="G9" s="17" t="n"/>
       <c r="H9" s="17" t="n"/>
       <c r="I9" s="17" t="n"/>
+      <c r="J9" s="17" t="n"/>
     </row>
     <row r="10" ht="14" customHeight="1">
       <c r="A10" s="15" t="inlineStr"/>
@@ -5954,6 +5977,7 @@
       <c r="G10" s="17" t="n"/>
       <c r="H10" s="17" t="n"/>
       <c r="I10" s="17" t="n"/>
+      <c r="J10" s="17" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="18" t="inlineStr">
@@ -5966,12 +5990,13 @@
       <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>MTD SCORE</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>MTD DOLLARS</t>
         </is>
@@ -5999,11 +6024,12 @@
         <v>100</v>
       </c>
       <c r="G12" s="21" t="n"/>
-      <c r="H12" s="23">
-        <f>IFERROR(AVERAGE(C12:G12),"")</f>
-        <v/>
-      </c>
-      <c r="I12" s="24" t="n">
+      <c r="H12" s="21" t="n"/>
+      <c r="I12" s="23">
+        <f>IFERROR(AVERAGE(C12:H12),"")</f>
+        <v/>
+      </c>
+      <c r="J12" s="24" t="n">
         <v>122.67</v>
       </c>
     </row>
@@ -6023,11 +6049,12 @@
       <c r="E13" s="21" t="n"/>
       <c r="F13" s="21" t="n"/>
       <c r="G13" s="21" t="n"/>
-      <c r="H13" s="23">
-        <f>IFERROR(AVERAGE(C13:G13),"")</f>
-        <v/>
-      </c>
-      <c r="I13" s="21" t="n"/>
+      <c r="H13" s="21" t="n"/>
+      <c r="I13" s="23">
+        <f>IFERROR(AVERAGE(C13:H13),"")</f>
+        <v/>
+      </c>
+      <c r="J13" s="21" t="n"/>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
@@ -6045,11 +6072,12 @@
       <c r="E14" s="21" t="n"/>
       <c r="F14" s="21" t="n"/>
       <c r="G14" s="21" t="n"/>
-      <c r="H14" s="23">
-        <f>IFERROR(AVERAGE(C14:G14),"")</f>
-        <v/>
-      </c>
-      <c r="I14" s="21" t="n"/>
+      <c r="H14" s="21" t="n"/>
+      <c r="I14" s="23">
+        <f>IFERROR(AVERAGE(C14:H14),"")</f>
+        <v/>
+      </c>
+      <c r="J14" s="21" t="n"/>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
@@ -6067,11 +6095,12 @@
       <c r="E15" s="28" t="n"/>
       <c r="F15" s="28" t="n"/>
       <c r="G15" s="28" t="n"/>
-      <c r="H15" s="23">
-        <f>IFERROR(AVERAGE(C15:G15),"")</f>
-        <v/>
-      </c>
-      <c r="I15" s="28" t="n"/>
+      <c r="H15" s="28" t="n"/>
+      <c r="I15" s="23">
+        <f>IFERROR(AVERAGE(C15:H15),"")</f>
+        <v/>
+      </c>
+      <c r="J15" s="28" t="n"/>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
@@ -6089,11 +6118,12 @@
       <c r="E16" s="28" t="n"/>
       <c r="F16" s="28" t="n"/>
       <c r="G16" s="28" t="n"/>
-      <c r="H16" s="23">
-        <f>IFERROR(AVERAGE(C16:G16),"")</f>
-        <v/>
-      </c>
-      <c r="I16" s="28" t="n"/>
+      <c r="H16" s="28" t="n"/>
+      <c r="I16" s="23">
+        <f>IFERROR(AVERAGE(C16:H16),"")</f>
+        <v/>
+      </c>
+      <c r="J16" s="28" t="n"/>
     </row>
     <row r="17" ht="17" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
@@ -6111,11 +6141,12 @@
       <c r="E17" s="28" t="n"/>
       <c r="F17" s="28" t="n"/>
       <c r="G17" s="28" t="n"/>
-      <c r="H17" s="23">
-        <f>IFERROR(AVERAGE(C17:G17),"")</f>
-        <v/>
-      </c>
-      <c r="I17" s="28" t="n"/>
+      <c r="H17" s="28" t="n"/>
+      <c r="I17" s="23">
+        <f>IFERROR(AVERAGE(C17:H17),"")</f>
+        <v/>
+      </c>
+      <c r="J17" s="28" t="n"/>
     </row>
     <row r="18" ht="17" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
@@ -6133,11 +6164,12 @@
       <c r="E18" s="28" t="n"/>
       <c r="F18" s="28" t="n"/>
       <c r="G18" s="28" t="n"/>
-      <c r="H18" s="23">
-        <f>IFERROR(AVERAGE(C18:G18),"")</f>
-        <v/>
-      </c>
-      <c r="I18" s="28" t="n"/>
+      <c r="H18" s="28" t="n"/>
+      <c r="I18" s="23">
+        <f>IFERROR(AVERAGE(C18:H18),"")</f>
+        <v/>
+      </c>
+      <c r="J18" s="28" t="n"/>
     </row>
     <row r="19" ht="17" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
@@ -6157,11 +6189,12 @@
       <c r="E19" s="28" t="n"/>
       <c r="F19" s="28" t="n"/>
       <c r="G19" s="28" t="n"/>
-      <c r="H19" s="23">
-        <f>IFERROR(AVERAGE(C19:G19),"")</f>
-        <v/>
-      </c>
-      <c r="I19" s="24" t="n">
+      <c r="H19" s="28" t="n"/>
+      <c r="I19" s="23">
+        <f>IFERROR(AVERAGE(C19:H19),"")</f>
+        <v/>
+      </c>
+      <c r="J19" s="24" t="n">
         <v>46</v>
       </c>
     </row>
@@ -6181,11 +6214,12 @@
       <c r="E20" s="28" t="n"/>
       <c r="F20" s="28" t="n"/>
       <c r="G20" s="28" t="n"/>
-      <c r="H20" s="23">
-        <f>IFERROR(AVERAGE(C20:G20),"")</f>
-        <v/>
-      </c>
-      <c r="I20" s="28" t="n"/>
+      <c r="H20" s="28" t="n"/>
+      <c r="I20" s="23">
+        <f>IFERROR(AVERAGE(C20:H20),"")</f>
+        <v/>
+      </c>
+      <c r="J20" s="28" t="n"/>
     </row>
     <row r="21" ht="17" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
@@ -6203,11 +6237,12 @@
       <c r="E21" s="28" t="n"/>
       <c r="F21" s="28" t="n"/>
       <c r="G21" s="28" t="n"/>
-      <c r="H21" s="23">
-        <f>IFERROR(AVERAGE(C21:G21),"")</f>
-        <v/>
-      </c>
-      <c r="I21" s="28" t="n"/>
+      <c r="H21" s="28" t="n"/>
+      <c r="I21" s="23">
+        <f>IFERROR(AVERAGE(C21:H21),"")</f>
+        <v/>
+      </c>
+      <c r="J21" s="28" t="n"/>
     </row>
     <row r="22" ht="17" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
@@ -6225,11 +6260,12 @@
       <c r="E22" s="28" t="n"/>
       <c r="F22" s="28" t="n"/>
       <c r="G22" s="28" t="n"/>
-      <c r="H22" s="23">
-        <f>IFERROR(AVERAGE(C22:G22),"")</f>
-        <v/>
-      </c>
-      <c r="I22" s="28" t="n"/>
+      <c r="H22" s="28" t="n"/>
+      <c r="I22" s="23">
+        <f>IFERROR(AVERAGE(C22:H22),"")</f>
+        <v/>
+      </c>
+      <c r="J22" s="28" t="n"/>
     </row>
     <row r="23" ht="17" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
@@ -6251,11 +6287,16 @@
       </c>
       <c r="F23" s="28" t="n"/>
       <c r="G23" s="28" t="n"/>
-      <c r="H23" s="23">
-        <f>IFERROR(AVERAGE(C23:G23),"")</f>
-        <v/>
-      </c>
-      <c r="I23" s="28" t="n"/>
+      <c r="H23" s="22" t="n">
+        <v>100</v>
+      </c>
+      <c r="I23" s="23">
+        <f>IFERROR(AVERAGE(C23:H23),"")</f>
+        <v/>
+      </c>
+      <c r="J23" s="24" t="n">
+        <v>38.33</v>
+      </c>
     </row>
     <row r="24" ht="17" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
@@ -6273,11 +6314,12 @@
       <c r="E24" s="28" t="n"/>
       <c r="F24" s="28" t="n"/>
       <c r="G24" s="28" t="n"/>
-      <c r="H24" s="23">
-        <f>IFERROR(AVERAGE(C24:G24),"")</f>
-        <v/>
-      </c>
-      <c r="I24" s="28" t="n"/>
+      <c r="H24" s="28" t="n"/>
+      <c r="I24" s="23">
+        <f>IFERROR(AVERAGE(C24:H24),"")</f>
+        <v/>
+      </c>
+      <c r="J24" s="28" t="n"/>
     </row>
     <row r="25" ht="17" customHeight="1">
       <c r="A25" s="26" t="inlineStr">
@@ -6295,11 +6337,12 @@
       <c r="E25" s="28" t="n"/>
       <c r="F25" s="28" t="n"/>
       <c r="G25" s="28" t="n"/>
-      <c r="H25" s="23">
-        <f>IFERROR(AVERAGE(C25:G25),"")</f>
-        <v/>
-      </c>
-      <c r="I25" s="28" t="n"/>
+      <c r="H25" s="28" t="n"/>
+      <c r="I25" s="23">
+        <f>IFERROR(AVERAGE(C25:H25),"")</f>
+        <v/>
+      </c>
+      <c r="J25" s="28" t="n"/>
     </row>
     <row r="26" ht="17" customHeight="1">
       <c r="A26" s="26" t="inlineStr">
@@ -6319,11 +6362,16 @@
       </c>
       <c r="F26" s="28" t="n"/>
       <c r="G26" s="28" t="n"/>
-      <c r="H26" s="23">
-        <f>IFERROR(AVERAGE(C26:G26),"")</f>
-        <v/>
-      </c>
-      <c r="I26" s="28" t="n"/>
+      <c r="H26" s="22" t="n">
+        <v>100</v>
+      </c>
+      <c r="I26" s="23">
+        <f>IFERROR(AVERAGE(C26:H26),"")</f>
+        <v/>
+      </c>
+      <c r="J26" s="24" t="n">
+        <v>38.33</v>
+      </c>
     </row>
     <row r="27" ht="17" customHeight="1">
       <c r="A27" s="26" t="inlineStr">
@@ -6341,11 +6389,12 @@
       <c r="E27" s="28" t="n"/>
       <c r="F27" s="28" t="n"/>
       <c r="G27" s="28" t="n"/>
-      <c r="H27" s="23">
-        <f>IFERROR(AVERAGE(C27:G27),"")</f>
-        <v/>
-      </c>
-      <c r="I27" s="28" t="n"/>
+      <c r="H27" s="28" t="n"/>
+      <c r="I27" s="23">
+        <f>IFERROR(AVERAGE(C27:H27),"")</f>
+        <v/>
+      </c>
+      <c r="J27" s="28" t="n"/>
     </row>
     <row r="28" ht="17" customHeight="1">
       <c r="A28" s="26" t="inlineStr">
@@ -6365,11 +6414,12 @@
       <c r="E28" s="28" t="n"/>
       <c r="F28" s="28" t="n"/>
       <c r="G28" s="28" t="n"/>
-      <c r="H28" s="23">
-        <f>IFERROR(AVERAGE(C28:G28),"")</f>
-        <v/>
-      </c>
-      <c r="I28" s="24" t="n">
+      <c r="H28" s="28" t="n"/>
+      <c r="I28" s="23">
+        <f>IFERROR(AVERAGE(C28:H28),"")</f>
+        <v/>
+      </c>
+      <c r="J28" s="24" t="n">
         <v>46</v>
       </c>
     </row>
@@ -6389,11 +6439,12 @@
       <c r="E29" s="28" t="n"/>
       <c r="F29" s="28" t="n"/>
       <c r="G29" s="28" t="n"/>
-      <c r="H29" s="23">
-        <f>IFERROR(AVERAGE(C29:G29),"")</f>
-        <v/>
-      </c>
-      <c r="I29" s="28" t="n"/>
+      <c r="H29" s="28" t="n"/>
+      <c r="I29" s="23">
+        <f>IFERROR(AVERAGE(C29:H29),"")</f>
+        <v/>
+      </c>
+      <c r="J29" s="28" t="n"/>
     </row>
     <row r="30" ht="17" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
@@ -6411,11 +6462,12 @@
       <c r="E30" s="28" t="n"/>
       <c r="F30" s="28" t="n"/>
       <c r="G30" s="28" t="n"/>
-      <c r="H30" s="23">
-        <f>IFERROR(AVERAGE(C30:G30),"")</f>
-        <v/>
-      </c>
-      <c r="I30" s="28" t="n"/>
+      <c r="H30" s="28" t="n"/>
+      <c r="I30" s="23">
+        <f>IFERROR(AVERAGE(C30:H30),"")</f>
+        <v/>
+      </c>
+      <c r="J30" s="28" t="n"/>
     </row>
     <row r="31" ht="17" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
@@ -6437,11 +6489,12 @@
       <c r="E31" s="28" t="n"/>
       <c r="F31" s="28" t="n"/>
       <c r="G31" s="28" t="n"/>
-      <c r="H31" s="23">
-        <f>IFERROR(AVERAGE(C31:G31),"")</f>
-        <v/>
-      </c>
-      <c r="I31" s="24" t="n">
+      <c r="H31" s="28" t="n"/>
+      <c r="I31" s="23">
+        <f>IFERROR(AVERAGE(C31:H31),"")</f>
+        <v/>
+      </c>
+      <c r="J31" s="24" t="n">
         <v>46</v>
       </c>
     </row>
@@ -6467,12 +6520,15 @@
       <c r="G32" s="22" t="n">
         <v>100</v>
       </c>
-      <c r="H32" s="23">
-        <f>IFERROR(AVERAGE(C32:G32),"")</f>
-        <v/>
-      </c>
-      <c r="I32" s="24" t="n">
-        <v>191.67</v>
+      <c r="H32" s="22" t="n">
+        <v>100</v>
+      </c>
+      <c r="I32" s="23">
+        <f>IFERROR(AVERAGE(C32:H32),"")</f>
+        <v/>
+      </c>
+      <c r="J32" s="24" t="n">
+        <v>230</v>
       </c>
     </row>
     <row r="33" ht="17" customHeight="1">
@@ -6491,11 +6547,12 @@
       <c r="E33" s="28" t="n"/>
       <c r="F33" s="28" t="n"/>
       <c r="G33" s="28" t="n"/>
-      <c r="H33" s="23">
-        <f>IFERROR(AVERAGE(C33:G33),"")</f>
-        <v/>
-      </c>
-      <c r="I33" s="28" t="n"/>
+      <c r="H33" s="28" t="n"/>
+      <c r="I33" s="23">
+        <f>IFERROR(AVERAGE(C33:H33),"")</f>
+        <v/>
+      </c>
+      <c r="J33" s="28" t="n"/>
     </row>
     <row r="34" ht="17" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
@@ -6513,11 +6570,12 @@
       <c r="E34" s="28" t="n"/>
       <c r="F34" s="28" t="n"/>
       <c r="G34" s="28" t="n"/>
-      <c r="H34" s="23">
-        <f>IFERROR(AVERAGE(C34:G34),"")</f>
-        <v/>
-      </c>
-      <c r="I34" s="28" t="n"/>
+      <c r="H34" s="28" t="n"/>
+      <c r="I34" s="23">
+        <f>IFERROR(AVERAGE(C34:H34),"")</f>
+        <v/>
+      </c>
+      <c r="J34" s="28" t="n"/>
     </row>
     <row r="35" ht="17" customHeight="1">
       <c r="A35" s="26" t="inlineStr">
@@ -6537,11 +6595,16 @@
       </c>
       <c r="F35" s="28" t="n"/>
       <c r="G35" s="28" t="n"/>
-      <c r="H35" s="23">
-        <f>IFERROR(AVERAGE(C35:G35),"")</f>
-        <v/>
-      </c>
-      <c r="I35" s="28" t="n"/>
+      <c r="H35" s="22" t="n">
+        <v>100</v>
+      </c>
+      <c r="I35" s="23">
+        <f>IFERROR(AVERAGE(C35:H35),"")</f>
+        <v/>
+      </c>
+      <c r="J35" s="24" t="n">
+        <v>38.33</v>
+      </c>
     </row>
     <row r="36" ht="17" customHeight="1">
       <c r="A36" s="26" t="inlineStr">
@@ -6559,11 +6622,12 @@
       <c r="E36" s="28" t="n"/>
       <c r="F36" s="28" t="n"/>
       <c r="G36" s="28" t="n"/>
-      <c r="H36" s="23">
-        <f>IFERROR(AVERAGE(C36:G36),"")</f>
-        <v/>
-      </c>
-      <c r="I36" s="28" t="n"/>
+      <c r="H36" s="28" t="n"/>
+      <c r="I36" s="23">
+        <f>IFERROR(AVERAGE(C36:H36),"")</f>
+        <v/>
+      </c>
+      <c r="J36" s="28" t="n"/>
     </row>
     <row r="37" ht="17" customHeight="1">
       <c r="A37" s="26" t="inlineStr">
@@ -6581,11 +6645,12 @@
       <c r="E37" s="28" t="n"/>
       <c r="F37" s="28" t="n"/>
       <c r="G37" s="28" t="n"/>
-      <c r="H37" s="23">
-        <f>IFERROR(AVERAGE(C37:G37),"")</f>
-        <v/>
-      </c>
-      <c r="I37" s="28" t="n"/>
+      <c r="H37" s="28" t="n"/>
+      <c r="I37" s="23">
+        <f>IFERROR(AVERAGE(C37:H37),"")</f>
+        <v/>
+      </c>
+      <c r="J37" s="28" t="n"/>
     </row>
     <row r="38" ht="17" customHeight="1">
       <c r="A38" s="26" t="inlineStr">
@@ -6605,11 +6670,12 @@
       <c r="E38" s="28" t="n"/>
       <c r="F38" s="28" t="n"/>
       <c r="G38" s="28" t="n"/>
-      <c r="H38" s="23">
-        <f>IFERROR(AVERAGE(C38:G38),"")</f>
-        <v/>
-      </c>
-      <c r="I38" s="24" t="n">
+      <c r="H38" s="28" t="n"/>
+      <c r="I38" s="23">
+        <f>IFERROR(AVERAGE(C38:H38),"")</f>
+        <v/>
+      </c>
+      <c r="J38" s="24" t="n">
         <v>46</v>
       </c>
     </row>
@@ -6622,9 +6688,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A39:J39"/>
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A39:I39"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Shop_Tracker_2065_2026.xlsx
+++ b/Shop_Tracker_2065_2026.xlsx
@@ -1,18 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="January" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="February" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="March" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="April" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="May" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="June" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="January" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="February" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="March" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="April" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="May" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="June" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="July" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6696,4 +6697,667 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>SECRET SHOPPER SCORES — JULY 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr"/>
+      <c r="B2" s="2" t="inlineStr"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>WEEK 1</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>MTD SCORE</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>MTD DOLLARS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="4" t="inlineStr"/>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>07/03</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr"/>
+      <c r="E3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="4" t="inlineStr"/>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Meal Period</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="9" t="inlineStr"/>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>TOTAL SCORE</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="n">
+        <v>85</v>
+      </c>
+      <c r="D5" s="9" t="inlineStr"/>
+      <c r="E5" s="9" t="inlineStr"/>
+    </row>
+    <row r="6" ht="14" customHeight="1">
+      <c r="A6" s="15" t="inlineStr"/>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>Overall Experience</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="n"/>
+      <c r="D6" s="17" t="n"/>
+      <c r="E6" s="17" t="n"/>
+    </row>
+    <row r="7" ht="14" customHeight="1">
+      <c r="A7" s="15" t="inlineStr"/>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>Enthusiasm</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n"/>
+    </row>
+    <row r="8" ht="14" customHeight="1">
+      <c r="A8" s="15" t="inlineStr"/>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>Likely to Return</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="n"/>
+      <c r="D8" s="17" t="n"/>
+      <c r="E8" s="17" t="n"/>
+    </row>
+    <row r="9" ht="14" customHeight="1">
+      <c r="A9" s="15" t="inlineStr"/>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>Likely to Recommend</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="17" t="n"/>
+      <c r="E9" s="17" t="n"/>
+    </row>
+    <row r="10" ht="14" customHeight="1">
+      <c r="A10" s="15" t="inlineStr"/>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>Exceptional Act?</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="17" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t>INDIVIDUAL PERFORMANCE</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr"/>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>MTD SCORE</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>MTD DOLLARS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="17" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>Vicki Lucey</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="n"/>
+      <c r="D12" s="23">
+        <f>IFERROR(AVERAGE(C12:C12),"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="21" t="n"/>
+    </row>
+    <row r="13" ht="17" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>Kasey Wilson</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="n"/>
+      <c r="D13" s="23">
+        <f>IFERROR(AVERAGE(C13:C13),"")</f>
+        <v/>
+      </c>
+      <c r="E13" s="21" t="n"/>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>Nathan Roberts</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="n"/>
+      <c r="D14" s="23">
+        <f>IFERROR(AVERAGE(C14:C14),"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="21" t="n"/>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B15" s="27" t="inlineStr">
+        <is>
+          <t>Ailen Gonzalez Cardero</t>
+        </is>
+      </c>
+      <c r="C15" s="28" t="n"/>
+      <c r="D15" s="23">
+        <f>IFERROR(AVERAGE(C15:C15),"")</f>
+        <v/>
+      </c>
+      <c r="E15" s="28" t="n"/>
+    </row>
+    <row r="16" ht="17" customHeight="1">
+      <c r="A16" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B16" s="27" t="inlineStr">
+        <is>
+          <t>Anthony Pirtle</t>
+        </is>
+      </c>
+      <c r="C16" s="28" t="n"/>
+      <c r="D16" s="23">
+        <f>IFERROR(AVERAGE(C16:C16),"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="28" t="n"/>
+    </row>
+    <row r="17" ht="17" customHeight="1">
+      <c r="A17" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B17" s="27" t="inlineStr">
+        <is>
+          <t>Ash</t>
+        </is>
+      </c>
+      <c r="C17" s="28" t="n"/>
+      <c r="D17" s="23">
+        <f>IFERROR(AVERAGE(C17:C17),"")</f>
+        <v/>
+      </c>
+      <c r="E17" s="28" t="n"/>
+    </row>
+    <row r="18" ht="17" customHeight="1">
+      <c r="A18" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B18" s="27" t="inlineStr">
+        <is>
+          <t>Autumn Hearn</t>
+        </is>
+      </c>
+      <c r="C18" s="28" t="n"/>
+      <c r="D18" s="23">
+        <f>IFERROR(AVERAGE(C18:C18),"")</f>
+        <v/>
+      </c>
+      <c r="E18" s="28" t="n"/>
+    </row>
+    <row r="19" ht="17" customHeight="1">
+      <c r="A19" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B19" s="27" t="inlineStr">
+        <is>
+          <t>Brianna Gatewood</t>
+        </is>
+      </c>
+      <c r="C19" s="28" t="n"/>
+      <c r="D19" s="23">
+        <f>IFERROR(AVERAGE(C19:C19),"")</f>
+        <v/>
+      </c>
+      <c r="E19" s="28" t="n"/>
+    </row>
+    <row r="20" ht="17" customHeight="1">
+      <c r="A20" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B20" s="27" t="inlineStr">
+        <is>
+          <t>DaKayla Dorsey</t>
+        </is>
+      </c>
+      <c r="C20" s="28" t="n"/>
+      <c r="D20" s="23">
+        <f>IFERROR(AVERAGE(C20:C20),"")</f>
+        <v/>
+      </c>
+      <c r="E20" s="28" t="n"/>
+    </row>
+    <row r="21" ht="17" customHeight="1">
+      <c r="A21" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B21" s="27" t="inlineStr">
+        <is>
+          <t>Damon</t>
+        </is>
+      </c>
+      <c r="C21" s="28" t="n"/>
+      <c r="D21" s="23">
+        <f>IFERROR(AVERAGE(C21:C21),"")</f>
+        <v/>
+      </c>
+      <c r="E21" s="28" t="n"/>
+    </row>
+    <row r="22" ht="17" customHeight="1">
+      <c r="A22" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B22" s="27" t="inlineStr">
+        <is>
+          <t>Divan</t>
+        </is>
+      </c>
+      <c r="C22" s="28" t="n"/>
+      <c r="D22" s="23">
+        <f>IFERROR(AVERAGE(C22:C22),"")</f>
+        <v/>
+      </c>
+      <c r="E22" s="28" t="n"/>
+    </row>
+    <row r="23" ht="17" customHeight="1">
+      <c r="A23" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B23" s="27" t="inlineStr">
+        <is>
+          <t>Francisco Llorente Mejias</t>
+        </is>
+      </c>
+      <c r="C23" s="28" t="n"/>
+      <c r="D23" s="23">
+        <f>IFERROR(AVERAGE(C23:C23),"")</f>
+        <v/>
+      </c>
+      <c r="E23" s="28" t="n"/>
+    </row>
+    <row r="24" ht="17" customHeight="1">
+      <c r="A24" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B24" s="27" t="inlineStr">
+        <is>
+          <t>Grace</t>
+        </is>
+      </c>
+      <c r="C24" s="28" t="n"/>
+      <c r="D24" s="23">
+        <f>IFERROR(AVERAGE(C24:C24),"")</f>
+        <v/>
+      </c>
+      <c r="E24" s="28" t="n"/>
+    </row>
+    <row r="25" ht="17" customHeight="1">
+      <c r="A25" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B25" s="27" t="inlineStr">
+        <is>
+          <t>Jada Cox</t>
+        </is>
+      </c>
+      <c r="C25" s="28" t="n"/>
+      <c r="D25" s="23">
+        <f>IFERROR(AVERAGE(C25:C25),"")</f>
+        <v/>
+      </c>
+      <c r="E25" s="28" t="n"/>
+    </row>
+    <row r="26" ht="17" customHeight="1">
+      <c r="A26" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B26" s="27" t="inlineStr">
+        <is>
+          <t>Jeremiah Matthews</t>
+        </is>
+      </c>
+      <c r="C26" s="28" t="n"/>
+      <c r="D26" s="23">
+        <f>IFERROR(AVERAGE(C26:C26),"")</f>
+        <v/>
+      </c>
+      <c r="E26" s="28" t="n"/>
+    </row>
+    <row r="27" ht="17" customHeight="1">
+      <c r="A27" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B27" s="27" t="inlineStr">
+        <is>
+          <t>Kable</t>
+        </is>
+      </c>
+      <c r="C27" s="28" t="n"/>
+      <c r="D27" s="23">
+        <f>IFERROR(AVERAGE(C27:C27),"")</f>
+        <v/>
+      </c>
+      <c r="E27" s="28" t="n"/>
+    </row>
+    <row r="28" ht="17" customHeight="1">
+      <c r="A28" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B28" s="27" t="inlineStr">
+        <is>
+          <t>Kaisha Brewer</t>
+        </is>
+      </c>
+      <c r="C28" s="28" t="n"/>
+      <c r="D28" s="23">
+        <f>IFERROR(AVERAGE(C28:C28),"")</f>
+        <v/>
+      </c>
+      <c r="E28" s="28" t="n"/>
+    </row>
+    <row r="29" ht="17" customHeight="1">
+      <c r="A29" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B29" s="27" t="inlineStr">
+        <is>
+          <t>Kayla Valenzuela</t>
+        </is>
+      </c>
+      <c r="C29" s="28" t="n"/>
+      <c r="D29" s="23">
+        <f>IFERROR(AVERAGE(C29:C29),"")</f>
+        <v/>
+      </c>
+      <c r="E29" s="28" t="n"/>
+    </row>
+    <row r="30" ht="17" customHeight="1">
+      <c r="A30" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B30" s="27" t="inlineStr">
+        <is>
+          <t>Kenzie</t>
+        </is>
+      </c>
+      <c r="C30" s="28" t="n"/>
+      <c r="D30" s="23">
+        <f>IFERROR(AVERAGE(C30:C30),"")</f>
+        <v/>
+      </c>
+      <c r="E30" s="28" t="n"/>
+    </row>
+    <row r="31" ht="17" customHeight="1">
+      <c r="A31" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B31" s="27" t="inlineStr">
+        <is>
+          <t>Lidy Henry</t>
+        </is>
+      </c>
+      <c r="C31" s="28" t="n"/>
+      <c r="D31" s="23">
+        <f>IFERROR(AVERAGE(C31:C31),"")</f>
+        <v/>
+      </c>
+      <c r="E31" s="28" t="n"/>
+    </row>
+    <row r="32" ht="17" customHeight="1">
+      <c r="A32" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B32" s="27" t="inlineStr">
+        <is>
+          <t>Maylin Hernandez Rodriguez</t>
+        </is>
+      </c>
+      <c r="C32" s="28" t="n"/>
+      <c r="D32" s="23">
+        <f>IFERROR(AVERAGE(C32:C32),"")</f>
+        <v/>
+      </c>
+      <c r="E32" s="28" t="n"/>
+    </row>
+    <row r="33" ht="17" customHeight="1">
+      <c r="A33" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B33" s="27" t="inlineStr">
+        <is>
+          <t>Mike</t>
+        </is>
+      </c>
+      <c r="C33" s="28" t="n"/>
+      <c r="D33" s="23">
+        <f>IFERROR(AVERAGE(C33:C33),"")</f>
+        <v/>
+      </c>
+      <c r="E33" s="28" t="n"/>
+    </row>
+    <row r="34" ht="17" customHeight="1">
+      <c r="A34" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B34" s="27" t="inlineStr">
+        <is>
+          <t>Nyatiek Keah</t>
+        </is>
+      </c>
+      <c r="C34" s="28" t="n"/>
+      <c r="D34" s="23">
+        <f>IFERROR(AVERAGE(C34:C34),"")</f>
+        <v/>
+      </c>
+      <c r="E34" s="28" t="n"/>
+    </row>
+    <row r="35" ht="17" customHeight="1">
+      <c r="A35" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B35" s="27" t="inlineStr">
+        <is>
+          <t>Richard Gibbs</t>
+        </is>
+      </c>
+      <c r="C35" s="28" t="n"/>
+      <c r="D35" s="23">
+        <f>IFERROR(AVERAGE(C35:C35),"")</f>
+        <v/>
+      </c>
+      <c r="E35" s="28" t="n"/>
+    </row>
+    <row r="36" ht="17" customHeight="1">
+      <c r="A36" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B36" s="27" t="inlineStr">
+        <is>
+          <t>Ryan</t>
+        </is>
+      </c>
+      <c r="C36" s="28" t="n"/>
+      <c r="D36" s="23">
+        <f>IFERROR(AVERAGE(C36:C36),"")</f>
+        <v/>
+      </c>
+      <c r="E36" s="28" t="n"/>
+    </row>
+    <row r="37" ht="17" customHeight="1">
+      <c r="A37" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B37" s="27" t="inlineStr">
+        <is>
+          <t>Samuel Galban Rocha</t>
+        </is>
+      </c>
+      <c r="C37" s="28" t="n"/>
+      <c r="D37" s="23">
+        <f>IFERROR(AVERAGE(C37:C37),"")</f>
+        <v/>
+      </c>
+      <c r="E37" s="28" t="n"/>
+    </row>
+    <row r="38" ht="17" customHeight="1">
+      <c r="A38" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B38" s="27" t="inlineStr">
+        <is>
+          <t>Zack Whitten</t>
+        </is>
+      </c>
+      <c r="C38" s="28" t="n"/>
+      <c r="D38" s="23">
+        <f>IFERROR(AVERAGE(C38:C38),"")</f>
+        <v/>
+      </c>
+      <c r="E38" s="28" t="n"/>
+    </row>
+    <row r="39" ht="12" customHeight="1">
+      <c r="A39" s="31" t="inlineStr">
+        <is>
+          <t>Score = shop score if on shift during meal window; blank if not. MTD SCORE = average of scores worked. MTD DOLLARS = $230 ÷ on-shift count per 100% shop.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A11:B11"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/Shop_Tracker_2065_2026.xlsx
+++ b/Shop_Tracker_2065_2026.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="January" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="February" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="March" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="April" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="May" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="June" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="July" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="January" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="February" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="March" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="April" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="May" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="June" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="July" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6868,7 +6868,9 @@
           <t>Vicki Lucey</t>
         </is>
       </c>
-      <c r="C12" s="21" t="n"/>
+      <c r="C12" s="30" t="n">
+        <v>85</v>
+      </c>
       <c r="D12" s="23">
         <f>IFERROR(AVERAGE(C12:C12),"")</f>
         <v/>
@@ -7066,7 +7068,9 @@
           <t>Francisco Llorente Mejias</t>
         </is>
       </c>
-      <c r="C23" s="28" t="n"/>
+      <c r="C23" s="30" t="n">
+        <v>85</v>
+      </c>
       <c r="D23" s="23">
         <f>IFERROR(AVERAGE(C23:C23),"")</f>
         <v/>
@@ -7120,7 +7124,9 @@
           <t>Jeremiah Matthews</t>
         </is>
       </c>
-      <c r="C26" s="28" t="n"/>
+      <c r="C26" s="30" t="n">
+        <v>85</v>
+      </c>
       <c r="D26" s="23">
         <f>IFERROR(AVERAGE(C26:C26),"")</f>
         <v/>
@@ -7210,7 +7216,9 @@
           <t>Lidy Henry</t>
         </is>
       </c>
-      <c r="C31" s="28" t="n"/>
+      <c r="C31" s="30" t="n">
+        <v>85</v>
+      </c>
       <c r="D31" s="23">
         <f>IFERROR(AVERAGE(C31:C31),"")</f>
         <v/>
@@ -7228,7 +7236,9 @@
           <t>Maylin Hernandez Rodriguez</t>
         </is>
       </c>
-      <c r="C32" s="28" t="n"/>
+      <c r="C32" s="30" t="n">
+        <v>85</v>
+      </c>
       <c r="D32" s="23">
         <f>IFERROR(AVERAGE(C32:C32),"")</f>
         <v/>

--- a/Shop_Tracker_2065_2026.xlsx
+++ b/Shop_Tracker_2065_2026.xlsx
@@ -6705,14 +6705,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -6732,10 +6734,20 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
+          <t>WEEK 2</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>WEEK 3</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
           <t>MTD SCORE</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>MTD DOLLARS</t>
         </is>
@@ -6753,8 +6765,18 @@
           <t>07/03</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr"/>
-      <c r="E3" s="4" t="inlineStr"/>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>07/11</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>07/12</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr"/>
+      <c r="G3" s="4" t="inlineStr"/>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="4" t="inlineStr"/>
@@ -6768,8 +6790,18 @@
           <t>Lunch</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr"/>
-      <c r="E4" s="4" t="inlineStr"/>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="9" t="inlineStr"/>
@@ -6781,8 +6813,14 @@
       <c r="C5" s="13" t="n">
         <v>85</v>
       </c>
-      <c r="D5" s="9" t="inlineStr"/>
-      <c r="E5" s="9" t="inlineStr"/>
+      <c r="D5" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="13" t="n">
+        <v>87</v>
+      </c>
+      <c r="F5" s="9" t="inlineStr"/>
+      <c r="G5" s="9" t="inlineStr"/>
     </row>
     <row r="6" ht="14" customHeight="1">
       <c r="A6" s="15" t="inlineStr"/>
@@ -6794,6 +6832,8 @@
       <c r="C6" s="17" t="n"/>
       <c r="D6" s="17" t="n"/>
       <c r="E6" s="17" t="n"/>
+      <c r="F6" s="17" t="n"/>
+      <c r="G6" s="17" t="n"/>
     </row>
     <row r="7" ht="14" customHeight="1">
       <c r="A7" s="15" t="inlineStr"/>
@@ -6805,6 +6845,8 @@
       <c r="C7" s="17" t="n"/>
       <c r="D7" s="17" t="n"/>
       <c r="E7" s="17" t="n"/>
+      <c r="F7" s="17" t="n"/>
+      <c r="G7" s="17" t="n"/>
     </row>
     <row r="8" ht="14" customHeight="1">
       <c r="A8" s="15" t="inlineStr"/>
@@ -6816,6 +6858,8 @@
       <c r="C8" s="17" t="n"/>
       <c r="D8" s="17" t="n"/>
       <c r="E8" s="17" t="n"/>
+      <c r="F8" s="17" t="n"/>
+      <c r="G8" s="17" t="n"/>
     </row>
     <row r="9" ht="14" customHeight="1">
       <c r="A9" s="15" t="inlineStr"/>
@@ -6827,6 +6871,8 @@
       <c r="C9" s="17" t="n"/>
       <c r="D9" s="17" t="n"/>
       <c r="E9" s="17" t="n"/>
+      <c r="F9" s="17" t="n"/>
+      <c r="G9" s="17" t="n"/>
     </row>
     <row r="10" ht="14" customHeight="1">
       <c r="A10" s="15" t="inlineStr"/>
@@ -6838,6 +6884,8 @@
       <c r="C10" s="17" t="n"/>
       <c r="D10" s="17" t="n"/>
       <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n"/>
+      <c r="G10" s="17" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="18" t="inlineStr">
@@ -6846,12 +6894,14 @@
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr"/>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr"/>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>MTD SCORE</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>MTD DOLLARS</t>
         </is>
@@ -6871,11 +6921,15 @@
       <c r="C12" s="30" t="n">
         <v>85</v>
       </c>
-      <c r="D12" s="23">
-        <f>IFERROR(AVERAGE(C12:C12),"")</f>
-        <v/>
-      </c>
-      <c r="E12" s="21" t="n"/>
+      <c r="D12" s="21" t="n"/>
+      <c r="E12" s="30" t="n">
+        <v>87</v>
+      </c>
+      <c r="F12" s="23">
+        <f>IFERROR(AVERAGE(C12:E12),"")</f>
+        <v/>
+      </c>
+      <c r="G12" s="21" t="n"/>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
@@ -6889,11 +6943,13 @@
         </is>
       </c>
       <c r="C13" s="21" t="n"/>
-      <c r="D13" s="23">
-        <f>IFERROR(AVERAGE(C13:C13),"")</f>
-        <v/>
-      </c>
+      <c r="D13" s="21" t="n"/>
       <c r="E13" s="21" t="n"/>
+      <c r="F13" s="23">
+        <f>IFERROR(AVERAGE(C13:E13),"")</f>
+        <v/>
+      </c>
+      <c r="G13" s="21" t="n"/>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
@@ -6907,11 +6963,13 @@
         </is>
       </c>
       <c r="C14" s="21" t="n"/>
-      <c r="D14" s="23">
-        <f>IFERROR(AVERAGE(C14:C14),"")</f>
-        <v/>
-      </c>
+      <c r="D14" s="21" t="n"/>
       <c r="E14" s="21" t="n"/>
+      <c r="F14" s="23">
+        <f>IFERROR(AVERAGE(C14:E14),"")</f>
+        <v/>
+      </c>
+      <c r="G14" s="21" t="n"/>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
@@ -6925,11 +6983,13 @@
         </is>
       </c>
       <c r="C15" s="28" t="n"/>
-      <c r="D15" s="23">
-        <f>IFERROR(AVERAGE(C15:C15),"")</f>
-        <v/>
-      </c>
+      <c r="D15" s="28" t="n"/>
       <c r="E15" s="28" t="n"/>
+      <c r="F15" s="23">
+        <f>IFERROR(AVERAGE(C15:E15),"")</f>
+        <v/>
+      </c>
+      <c r="G15" s="28" t="n"/>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
@@ -6943,11 +7003,13 @@
         </is>
       </c>
       <c r="C16" s="28" t="n"/>
-      <c r="D16" s="23">
-        <f>IFERROR(AVERAGE(C16:C16),"")</f>
-        <v/>
-      </c>
+      <c r="D16" s="28" t="n"/>
       <c r="E16" s="28" t="n"/>
+      <c r="F16" s="23">
+        <f>IFERROR(AVERAGE(C16:E16),"")</f>
+        <v/>
+      </c>
+      <c r="G16" s="28" t="n"/>
     </row>
     <row r="17" ht="17" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
@@ -6961,11 +7023,13 @@
         </is>
       </c>
       <c r="C17" s="28" t="n"/>
-      <c r="D17" s="23">
-        <f>IFERROR(AVERAGE(C17:C17),"")</f>
-        <v/>
-      </c>
+      <c r="D17" s="28" t="n"/>
       <c r="E17" s="28" t="n"/>
+      <c r="F17" s="23">
+        <f>IFERROR(AVERAGE(C17:E17),"")</f>
+        <v/>
+      </c>
+      <c r="G17" s="28" t="n"/>
     </row>
     <row r="18" ht="17" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
@@ -6979,11 +7043,13 @@
         </is>
       </c>
       <c r="C18" s="28" t="n"/>
-      <c r="D18" s="23">
-        <f>IFERROR(AVERAGE(C18:C18),"")</f>
-        <v/>
-      </c>
+      <c r="D18" s="28" t="n"/>
       <c r="E18" s="28" t="n"/>
+      <c r="F18" s="23">
+        <f>IFERROR(AVERAGE(C18:E18),"")</f>
+        <v/>
+      </c>
+      <c r="G18" s="28" t="n"/>
     </row>
     <row r="19" ht="17" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
@@ -6997,11 +7063,13 @@
         </is>
       </c>
       <c r="C19" s="28" t="n"/>
-      <c r="D19" s="23">
-        <f>IFERROR(AVERAGE(C19:C19),"")</f>
-        <v/>
-      </c>
+      <c r="D19" s="28" t="n"/>
       <c r="E19" s="28" t="n"/>
+      <c r="F19" s="23">
+        <f>IFERROR(AVERAGE(C19:E19),"")</f>
+        <v/>
+      </c>
+      <c r="G19" s="28" t="n"/>
     </row>
     <row r="20" ht="17" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
@@ -7015,11 +7083,13 @@
         </is>
       </c>
       <c r="C20" s="28" t="n"/>
-      <c r="D20" s="23">
-        <f>IFERROR(AVERAGE(C20:C20),"")</f>
-        <v/>
-      </c>
+      <c r="D20" s="28" t="n"/>
       <c r="E20" s="28" t="n"/>
+      <c r="F20" s="23">
+        <f>IFERROR(AVERAGE(C20:E20),"")</f>
+        <v/>
+      </c>
+      <c r="G20" s="28" t="n"/>
     </row>
     <row r="21" ht="17" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
@@ -7033,11 +7103,13 @@
         </is>
       </c>
       <c r="C21" s="28" t="n"/>
-      <c r="D21" s="23">
-        <f>IFERROR(AVERAGE(C21:C21),"")</f>
-        <v/>
-      </c>
+      <c r="D21" s="28" t="n"/>
       <c r="E21" s="28" t="n"/>
+      <c r="F21" s="23">
+        <f>IFERROR(AVERAGE(C21:E21),"")</f>
+        <v/>
+      </c>
+      <c r="G21" s="28" t="n"/>
     </row>
     <row r="22" ht="17" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
@@ -7051,11 +7123,13 @@
         </is>
       </c>
       <c r="C22" s="28" t="n"/>
-      <c r="D22" s="23">
-        <f>IFERROR(AVERAGE(C22:C22),"")</f>
-        <v/>
-      </c>
+      <c r="D22" s="28" t="n"/>
       <c r="E22" s="28" t="n"/>
+      <c r="F22" s="23">
+        <f>IFERROR(AVERAGE(C22:E22),"")</f>
+        <v/>
+      </c>
+      <c r="G22" s="28" t="n"/>
     </row>
     <row r="23" ht="17" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
@@ -7071,11 +7145,15 @@
       <c r="C23" s="30" t="n">
         <v>85</v>
       </c>
-      <c r="D23" s="23">
-        <f>IFERROR(AVERAGE(C23:C23),"")</f>
-        <v/>
-      </c>
-      <c r="E23" s="28" t="n"/>
+      <c r="D23" s="28" t="n"/>
+      <c r="E23" s="30" t="n">
+        <v>87</v>
+      </c>
+      <c r="F23" s="23">
+        <f>IFERROR(AVERAGE(C23:E23),"")</f>
+        <v/>
+      </c>
+      <c r="G23" s="28" t="n"/>
     </row>
     <row r="24" ht="17" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
@@ -7089,11 +7167,13 @@
         </is>
       </c>
       <c r="C24" s="28" t="n"/>
-      <c r="D24" s="23">
-        <f>IFERROR(AVERAGE(C24:C24),"")</f>
-        <v/>
-      </c>
+      <c r="D24" s="28" t="n"/>
       <c r="E24" s="28" t="n"/>
+      <c r="F24" s="23">
+        <f>IFERROR(AVERAGE(C24:E24),"")</f>
+        <v/>
+      </c>
+      <c r="G24" s="28" t="n"/>
     </row>
     <row r="25" ht="17" customHeight="1">
       <c r="A25" s="26" t="inlineStr">
@@ -7107,11 +7187,13 @@
         </is>
       </c>
       <c r="C25" s="28" t="n"/>
-      <c r="D25" s="23">
-        <f>IFERROR(AVERAGE(C25:C25),"")</f>
-        <v/>
-      </c>
+      <c r="D25" s="28" t="n"/>
       <c r="E25" s="28" t="n"/>
+      <c r="F25" s="23">
+        <f>IFERROR(AVERAGE(C25:E25),"")</f>
+        <v/>
+      </c>
+      <c r="G25" s="28" t="n"/>
     </row>
     <row r="26" ht="17" customHeight="1">
       <c r="A26" s="26" t="inlineStr">
@@ -7127,11 +7209,15 @@
       <c r="C26" s="30" t="n">
         <v>85</v>
       </c>
-      <c r="D26" s="23">
-        <f>IFERROR(AVERAGE(C26:C26),"")</f>
-        <v/>
+      <c r="D26" s="25" t="n">
+        <v>0</v>
       </c>
       <c r="E26" s="28" t="n"/>
+      <c r="F26" s="23">
+        <f>IFERROR(AVERAGE(C26:E26),"")</f>
+        <v/>
+      </c>
+      <c r="G26" s="28" t="n"/>
     </row>
     <row r="27" ht="17" customHeight="1">
       <c r="A27" s="26" t="inlineStr">
@@ -7145,11 +7231,13 @@
         </is>
       </c>
       <c r="C27" s="28" t="n"/>
-      <c r="D27" s="23">
-        <f>IFERROR(AVERAGE(C27:C27),"")</f>
-        <v/>
-      </c>
+      <c r="D27" s="28" t="n"/>
       <c r="E27" s="28" t="n"/>
+      <c r="F27" s="23">
+        <f>IFERROR(AVERAGE(C27:E27),"")</f>
+        <v/>
+      </c>
+      <c r="G27" s="28" t="n"/>
     </row>
     <row r="28" ht="17" customHeight="1">
       <c r="A28" s="26" t="inlineStr">
@@ -7163,11 +7251,13 @@
         </is>
       </c>
       <c r="C28" s="28" t="n"/>
-      <c r="D28" s="23">
-        <f>IFERROR(AVERAGE(C28:C28),"")</f>
-        <v/>
-      </c>
+      <c r="D28" s="28" t="n"/>
       <c r="E28" s="28" t="n"/>
+      <c r="F28" s="23">
+        <f>IFERROR(AVERAGE(C28:E28),"")</f>
+        <v/>
+      </c>
+      <c r="G28" s="28" t="n"/>
     </row>
     <row r="29" ht="17" customHeight="1">
       <c r="A29" s="26" t="inlineStr">
@@ -7181,11 +7271,13 @@
         </is>
       </c>
       <c r="C29" s="28" t="n"/>
-      <c r="D29" s="23">
-        <f>IFERROR(AVERAGE(C29:C29),"")</f>
-        <v/>
-      </c>
+      <c r="D29" s="28" t="n"/>
       <c r="E29" s="28" t="n"/>
+      <c r="F29" s="23">
+        <f>IFERROR(AVERAGE(C29:E29),"")</f>
+        <v/>
+      </c>
+      <c r="G29" s="28" t="n"/>
     </row>
     <row r="30" ht="17" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
@@ -7199,11 +7291,13 @@
         </is>
       </c>
       <c r="C30" s="28" t="n"/>
-      <c r="D30" s="23">
-        <f>IFERROR(AVERAGE(C30:C30),"")</f>
-        <v/>
-      </c>
+      <c r="D30" s="28" t="n"/>
       <c r="E30" s="28" t="n"/>
+      <c r="F30" s="23">
+        <f>IFERROR(AVERAGE(C30:E30),"")</f>
+        <v/>
+      </c>
+      <c r="G30" s="28" t="n"/>
     </row>
     <row r="31" ht="17" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
@@ -7219,11 +7313,13 @@
       <c r="C31" s="30" t="n">
         <v>85</v>
       </c>
-      <c r="D31" s="23">
-        <f>IFERROR(AVERAGE(C31:C31),"")</f>
-        <v/>
-      </c>
+      <c r="D31" s="28" t="n"/>
       <c r="E31" s="28" t="n"/>
+      <c r="F31" s="23">
+        <f>IFERROR(AVERAGE(C31:E31),"")</f>
+        <v/>
+      </c>
+      <c r="G31" s="28" t="n"/>
     </row>
     <row r="32" ht="17" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
@@ -7239,11 +7335,13 @@
       <c r="C32" s="30" t="n">
         <v>85</v>
       </c>
-      <c r="D32" s="23">
-        <f>IFERROR(AVERAGE(C32:C32),"")</f>
-        <v/>
-      </c>
+      <c r="D32" s="28" t="n"/>
       <c r="E32" s="28" t="n"/>
+      <c r="F32" s="23">
+        <f>IFERROR(AVERAGE(C32:E32),"")</f>
+        <v/>
+      </c>
+      <c r="G32" s="28" t="n"/>
     </row>
     <row r="33" ht="17" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
@@ -7257,11 +7355,13 @@
         </is>
       </c>
       <c r="C33" s="28" t="n"/>
-      <c r="D33" s="23">
-        <f>IFERROR(AVERAGE(C33:C33),"")</f>
-        <v/>
-      </c>
+      <c r="D33" s="28" t="n"/>
       <c r="E33" s="28" t="n"/>
+      <c r="F33" s="23">
+        <f>IFERROR(AVERAGE(C33:E33),"")</f>
+        <v/>
+      </c>
+      <c r="G33" s="28" t="n"/>
     </row>
     <row r="34" ht="17" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
@@ -7275,11 +7375,13 @@
         </is>
       </c>
       <c r="C34" s="28" t="n"/>
-      <c r="D34" s="23">
-        <f>IFERROR(AVERAGE(C34:C34),"")</f>
-        <v/>
-      </c>
+      <c r="D34" s="28" t="n"/>
       <c r="E34" s="28" t="n"/>
+      <c r="F34" s="23">
+        <f>IFERROR(AVERAGE(C34:E34),"")</f>
+        <v/>
+      </c>
+      <c r="G34" s="28" t="n"/>
     </row>
     <row r="35" ht="17" customHeight="1">
       <c r="A35" s="26" t="inlineStr">
@@ -7293,11 +7395,15 @@
         </is>
       </c>
       <c r="C35" s="28" t="n"/>
-      <c r="D35" s="23">
-        <f>IFERROR(AVERAGE(C35:C35),"")</f>
-        <v/>
+      <c r="D35" s="25" t="n">
+        <v>0</v>
       </c>
       <c r="E35" s="28" t="n"/>
+      <c r="F35" s="23">
+        <f>IFERROR(AVERAGE(C35:E35),"")</f>
+        <v/>
+      </c>
+      <c r="G35" s="28" t="n"/>
     </row>
     <row r="36" ht="17" customHeight="1">
       <c r="A36" s="26" t="inlineStr">
@@ -7311,11 +7417,13 @@
         </is>
       </c>
       <c r="C36" s="28" t="n"/>
-      <c r="D36" s="23">
-        <f>IFERROR(AVERAGE(C36:C36),"")</f>
-        <v/>
-      </c>
+      <c r="D36" s="28" t="n"/>
       <c r="E36" s="28" t="n"/>
+      <c r="F36" s="23">
+        <f>IFERROR(AVERAGE(C36:E36),"")</f>
+        <v/>
+      </c>
+      <c r="G36" s="28" t="n"/>
     </row>
     <row r="37" ht="17" customHeight="1">
       <c r="A37" s="26" t="inlineStr">
@@ -7329,11 +7437,13 @@
         </is>
       </c>
       <c r="C37" s="28" t="n"/>
-      <c r="D37" s="23">
-        <f>IFERROR(AVERAGE(C37:C37),"")</f>
-        <v/>
-      </c>
+      <c r="D37" s="28" t="n"/>
       <c r="E37" s="28" t="n"/>
+      <c r="F37" s="23">
+        <f>IFERROR(AVERAGE(C37:E37),"")</f>
+        <v/>
+      </c>
+      <c r="G37" s="28" t="n"/>
     </row>
     <row r="38" ht="17" customHeight="1">
       <c r="A38" s="26" t="inlineStr">
@@ -7347,11 +7457,13 @@
         </is>
       </c>
       <c r="C38" s="28" t="n"/>
-      <c r="D38" s="23">
-        <f>IFERROR(AVERAGE(C38:C38),"")</f>
-        <v/>
-      </c>
+      <c r="D38" s="28" t="n"/>
       <c r="E38" s="28" t="n"/>
+      <c r="F38" s="23">
+        <f>IFERROR(AVERAGE(C38:E38),"")</f>
+        <v/>
+      </c>
+      <c r="G38" s="28" t="n"/>
     </row>
     <row r="39" ht="12" customHeight="1">
       <c r="A39" s="31" t="inlineStr">
@@ -7362,9 +7474,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A39:E39"/>
-    <mergeCell ref="A1:E1"/>
     <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A39:G39"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Shop_Tracker_2065_2026.xlsx
+++ b/Shop_Tracker_2065_2026.xlsx
@@ -6705,7 +6705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -6713,8 +6713,9 @@
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -6744,10 +6745,15 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
+          <t>WEEK 4</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
           <t>MTD SCORE</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>MTD DOLLARS</t>
         </is>
@@ -6775,8 +6781,13 @@
           <t>07/12</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr"/>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>07/16</t>
+        </is>
+      </c>
       <c r="G3" s="4" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr"/>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="4" t="inlineStr"/>
@@ -6800,8 +6811,13 @@
           <t>Lunch</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr"/>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
       <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="9" t="inlineStr"/>
@@ -6819,8 +6835,11 @@
       <c r="E5" s="13" t="n">
         <v>87</v>
       </c>
-      <c r="F5" s="9" t="inlineStr"/>
+      <c r="F5" s="11" t="n">
+        <v>95</v>
+      </c>
       <c r="G5" s="9" t="inlineStr"/>
+      <c r="H5" s="9" t="inlineStr"/>
     </row>
     <row r="6" ht="14" customHeight="1">
       <c r="A6" s="15" t="inlineStr"/>
@@ -6834,6 +6853,7 @@
       <c r="E6" s="17" t="n"/>
       <c r="F6" s="17" t="n"/>
       <c r="G6" s="17" t="n"/>
+      <c r="H6" s="17" t="n"/>
     </row>
     <row r="7" ht="14" customHeight="1">
       <c r="A7" s="15" t="inlineStr"/>
@@ -6847,6 +6867,7 @@
       <c r="E7" s="17" t="n"/>
       <c r="F7" s="17" t="n"/>
       <c r="G7" s="17" t="n"/>
+      <c r="H7" s="17" t="n"/>
     </row>
     <row r="8" ht="14" customHeight="1">
       <c r="A8" s="15" t="inlineStr"/>
@@ -6860,6 +6881,7 @@
       <c r="E8" s="17" t="n"/>
       <c r="F8" s="17" t="n"/>
       <c r="G8" s="17" t="n"/>
+      <c r="H8" s="17" t="n"/>
     </row>
     <row r="9" ht="14" customHeight="1">
       <c r="A9" s="15" t="inlineStr"/>
@@ -6873,6 +6895,7 @@
       <c r="E9" s="17" t="n"/>
       <c r="F9" s="17" t="n"/>
       <c r="G9" s="17" t="n"/>
+      <c r="H9" s="17" t="n"/>
     </row>
     <row r="10" ht="14" customHeight="1">
       <c r="A10" s="15" t="inlineStr"/>
@@ -6886,6 +6909,7 @@
       <c r="E10" s="17" t="n"/>
       <c r="F10" s="17" t="n"/>
       <c r="G10" s="17" t="n"/>
+      <c r="H10" s="17" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="18" t="inlineStr">
@@ -6896,12 +6920,13 @@
       <c r="C11" s="2" t="inlineStr"/>
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>MTD SCORE</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>MTD DOLLARS</t>
         </is>
@@ -6925,11 +6950,12 @@
       <c r="E12" s="30" t="n">
         <v>87</v>
       </c>
-      <c r="F12" s="23">
-        <f>IFERROR(AVERAGE(C12:E12),"")</f>
-        <v/>
-      </c>
-      <c r="G12" s="21" t="n"/>
+      <c r="F12" s="21" t="n"/>
+      <c r="G12" s="23">
+        <f>IFERROR(AVERAGE(C12:F12),"")</f>
+        <v/>
+      </c>
+      <c r="H12" s="21" t="n"/>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
@@ -6945,11 +6971,12 @@
       <c r="C13" s="21" t="n"/>
       <c r="D13" s="21" t="n"/>
       <c r="E13" s="21" t="n"/>
-      <c r="F13" s="23">
-        <f>IFERROR(AVERAGE(C13:E13),"")</f>
-        <v/>
-      </c>
-      <c r="G13" s="21" t="n"/>
+      <c r="F13" s="21" t="n"/>
+      <c r="G13" s="23">
+        <f>IFERROR(AVERAGE(C13:F13),"")</f>
+        <v/>
+      </c>
+      <c r="H13" s="21" t="n"/>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
@@ -6965,11 +6992,12 @@
       <c r="C14" s="21" t="n"/>
       <c r="D14" s="21" t="n"/>
       <c r="E14" s="21" t="n"/>
-      <c r="F14" s="23">
-        <f>IFERROR(AVERAGE(C14:E14),"")</f>
-        <v/>
-      </c>
-      <c r="G14" s="21" t="n"/>
+      <c r="F14" s="21" t="n"/>
+      <c r="G14" s="23">
+        <f>IFERROR(AVERAGE(C14:F14),"")</f>
+        <v/>
+      </c>
+      <c r="H14" s="21" t="n"/>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
@@ -6985,11 +7013,12 @@
       <c r="C15" s="28" t="n"/>
       <c r="D15" s="28" t="n"/>
       <c r="E15" s="28" t="n"/>
-      <c r="F15" s="23">
-        <f>IFERROR(AVERAGE(C15:E15),"")</f>
-        <v/>
-      </c>
-      <c r="G15" s="28" t="n"/>
+      <c r="F15" s="28" t="n"/>
+      <c r="G15" s="23">
+        <f>IFERROR(AVERAGE(C15:F15),"")</f>
+        <v/>
+      </c>
+      <c r="H15" s="28" t="n"/>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
@@ -7005,11 +7034,12 @@
       <c r="C16" s="28" t="n"/>
       <c r="D16" s="28" t="n"/>
       <c r="E16" s="28" t="n"/>
-      <c r="F16" s="23">
-        <f>IFERROR(AVERAGE(C16:E16),"")</f>
-        <v/>
-      </c>
-      <c r="G16" s="28" t="n"/>
+      <c r="F16" s="28" t="n"/>
+      <c r="G16" s="23">
+        <f>IFERROR(AVERAGE(C16:F16),"")</f>
+        <v/>
+      </c>
+      <c r="H16" s="28" t="n"/>
     </row>
     <row r="17" ht="17" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
@@ -7025,11 +7055,12 @@
       <c r="C17" s="28" t="n"/>
       <c r="D17" s="28" t="n"/>
       <c r="E17" s="28" t="n"/>
-      <c r="F17" s="23">
-        <f>IFERROR(AVERAGE(C17:E17),"")</f>
-        <v/>
-      </c>
-      <c r="G17" s="28" t="n"/>
+      <c r="F17" s="28" t="n"/>
+      <c r="G17" s="23">
+        <f>IFERROR(AVERAGE(C17:F17),"")</f>
+        <v/>
+      </c>
+      <c r="H17" s="28" t="n"/>
     </row>
     <row r="18" ht="17" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
@@ -7045,11 +7076,12 @@
       <c r="C18" s="28" t="n"/>
       <c r="D18" s="28" t="n"/>
       <c r="E18" s="28" t="n"/>
-      <c r="F18" s="23">
-        <f>IFERROR(AVERAGE(C18:E18),"")</f>
-        <v/>
-      </c>
-      <c r="G18" s="28" t="n"/>
+      <c r="F18" s="28" t="n"/>
+      <c r="G18" s="23">
+        <f>IFERROR(AVERAGE(C18:F18),"")</f>
+        <v/>
+      </c>
+      <c r="H18" s="28" t="n"/>
     </row>
     <row r="19" ht="17" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
@@ -7065,11 +7097,12 @@
       <c r="C19" s="28" t="n"/>
       <c r="D19" s="28" t="n"/>
       <c r="E19" s="28" t="n"/>
-      <c r="F19" s="23">
-        <f>IFERROR(AVERAGE(C19:E19),"")</f>
-        <v/>
-      </c>
-      <c r="G19" s="28" t="n"/>
+      <c r="F19" s="28" t="n"/>
+      <c r="G19" s="23">
+        <f>IFERROR(AVERAGE(C19:F19),"")</f>
+        <v/>
+      </c>
+      <c r="H19" s="28" t="n"/>
     </row>
     <row r="20" ht="17" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
@@ -7085,11 +7118,12 @@
       <c r="C20" s="28" t="n"/>
       <c r="D20" s="28" t="n"/>
       <c r="E20" s="28" t="n"/>
-      <c r="F20" s="23">
-        <f>IFERROR(AVERAGE(C20:E20),"")</f>
-        <v/>
-      </c>
-      <c r="G20" s="28" t="n"/>
+      <c r="F20" s="28" t="n"/>
+      <c r="G20" s="23">
+        <f>IFERROR(AVERAGE(C20:F20),"")</f>
+        <v/>
+      </c>
+      <c r="H20" s="28" t="n"/>
     </row>
     <row r="21" ht="17" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
@@ -7105,11 +7139,12 @@
       <c r="C21" s="28" t="n"/>
       <c r="D21" s="28" t="n"/>
       <c r="E21" s="28" t="n"/>
-      <c r="F21" s="23">
-        <f>IFERROR(AVERAGE(C21:E21),"")</f>
-        <v/>
-      </c>
-      <c r="G21" s="28" t="n"/>
+      <c r="F21" s="28" t="n"/>
+      <c r="G21" s="23">
+        <f>IFERROR(AVERAGE(C21:F21),"")</f>
+        <v/>
+      </c>
+      <c r="H21" s="28" t="n"/>
     </row>
     <row r="22" ht="17" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
@@ -7125,11 +7160,12 @@
       <c r="C22" s="28" t="n"/>
       <c r="D22" s="28" t="n"/>
       <c r="E22" s="28" t="n"/>
-      <c r="F22" s="23">
-        <f>IFERROR(AVERAGE(C22:E22),"")</f>
-        <v/>
-      </c>
-      <c r="G22" s="28" t="n"/>
+      <c r="F22" s="28" t="n"/>
+      <c r="G22" s="23">
+        <f>IFERROR(AVERAGE(C22:F22),"")</f>
+        <v/>
+      </c>
+      <c r="H22" s="28" t="n"/>
     </row>
     <row r="23" ht="17" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
@@ -7149,11 +7185,14 @@
       <c r="E23" s="30" t="n">
         <v>87</v>
       </c>
-      <c r="F23" s="23">
-        <f>IFERROR(AVERAGE(C23:E23),"")</f>
-        <v/>
-      </c>
-      <c r="G23" s="28" t="n"/>
+      <c r="F23" s="29" t="n">
+        <v>95</v>
+      </c>
+      <c r="G23" s="23">
+        <f>IFERROR(AVERAGE(C23:F23),"")</f>
+        <v/>
+      </c>
+      <c r="H23" s="28" t="n"/>
     </row>
     <row r="24" ht="17" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
@@ -7169,11 +7208,12 @@
       <c r="C24" s="28" t="n"/>
       <c r="D24" s="28" t="n"/>
       <c r="E24" s="28" t="n"/>
-      <c r="F24" s="23">
-        <f>IFERROR(AVERAGE(C24:E24),"")</f>
-        <v/>
-      </c>
-      <c r="G24" s="28" t="n"/>
+      <c r="F24" s="28" t="n"/>
+      <c r="G24" s="23">
+        <f>IFERROR(AVERAGE(C24:F24),"")</f>
+        <v/>
+      </c>
+      <c r="H24" s="28" t="n"/>
     </row>
     <row r="25" ht="17" customHeight="1">
       <c r="A25" s="26" t="inlineStr">
@@ -7189,11 +7229,12 @@
       <c r="C25" s="28" t="n"/>
       <c r="D25" s="28" t="n"/>
       <c r="E25" s="28" t="n"/>
-      <c r="F25" s="23">
-        <f>IFERROR(AVERAGE(C25:E25),"")</f>
-        <v/>
-      </c>
-      <c r="G25" s="28" t="n"/>
+      <c r="F25" s="28" t="n"/>
+      <c r="G25" s="23">
+        <f>IFERROR(AVERAGE(C25:F25),"")</f>
+        <v/>
+      </c>
+      <c r="H25" s="28" t="n"/>
     </row>
     <row r="26" ht="17" customHeight="1">
       <c r="A26" s="26" t="inlineStr">
@@ -7213,11 +7254,14 @@
         <v>0</v>
       </c>
       <c r="E26" s="28" t="n"/>
-      <c r="F26" s="23">
-        <f>IFERROR(AVERAGE(C26:E26),"")</f>
-        <v/>
-      </c>
-      <c r="G26" s="28" t="n"/>
+      <c r="F26" s="29" t="n">
+        <v>95</v>
+      </c>
+      <c r="G26" s="23">
+        <f>IFERROR(AVERAGE(C26:F26),"")</f>
+        <v/>
+      </c>
+      <c r="H26" s="28" t="n"/>
     </row>
     <row r="27" ht="17" customHeight="1">
       <c r="A27" s="26" t="inlineStr">
@@ -7233,11 +7277,12 @@
       <c r="C27" s="28" t="n"/>
       <c r="D27" s="28" t="n"/>
       <c r="E27" s="28" t="n"/>
-      <c r="F27" s="23">
-        <f>IFERROR(AVERAGE(C27:E27),"")</f>
-        <v/>
-      </c>
-      <c r="G27" s="28" t="n"/>
+      <c r="F27" s="28" t="n"/>
+      <c r="G27" s="23">
+        <f>IFERROR(AVERAGE(C27:F27),"")</f>
+        <v/>
+      </c>
+      <c r="H27" s="28" t="n"/>
     </row>
     <row r="28" ht="17" customHeight="1">
       <c r="A28" s="26" t="inlineStr">
@@ -7253,11 +7298,12 @@
       <c r="C28" s="28" t="n"/>
       <c r="D28" s="28" t="n"/>
       <c r="E28" s="28" t="n"/>
-      <c r="F28" s="23">
-        <f>IFERROR(AVERAGE(C28:E28),"")</f>
-        <v/>
-      </c>
-      <c r="G28" s="28" t="n"/>
+      <c r="F28" s="28" t="n"/>
+      <c r="G28" s="23">
+        <f>IFERROR(AVERAGE(C28:F28),"")</f>
+        <v/>
+      </c>
+      <c r="H28" s="28" t="n"/>
     </row>
     <row r="29" ht="17" customHeight="1">
       <c r="A29" s="26" t="inlineStr">
@@ -7273,11 +7319,12 @@
       <c r="C29" s="28" t="n"/>
       <c r="D29" s="28" t="n"/>
       <c r="E29" s="28" t="n"/>
-      <c r="F29" s="23">
-        <f>IFERROR(AVERAGE(C29:E29),"")</f>
-        <v/>
-      </c>
-      <c r="G29" s="28" t="n"/>
+      <c r="F29" s="28" t="n"/>
+      <c r="G29" s="23">
+        <f>IFERROR(AVERAGE(C29:F29),"")</f>
+        <v/>
+      </c>
+      <c r="H29" s="28" t="n"/>
     </row>
     <row r="30" ht="17" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
@@ -7293,11 +7340,12 @@
       <c r="C30" s="28" t="n"/>
       <c r="D30" s="28" t="n"/>
       <c r="E30" s="28" t="n"/>
-      <c r="F30" s="23">
-        <f>IFERROR(AVERAGE(C30:E30),"")</f>
-        <v/>
-      </c>
-      <c r="G30" s="28" t="n"/>
+      <c r="F30" s="28" t="n"/>
+      <c r="G30" s="23">
+        <f>IFERROR(AVERAGE(C30:F30),"")</f>
+        <v/>
+      </c>
+      <c r="H30" s="28" t="n"/>
     </row>
     <row r="31" ht="17" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
@@ -7315,11 +7363,12 @@
       </c>
       <c r="D31" s="28" t="n"/>
       <c r="E31" s="28" t="n"/>
-      <c r="F31" s="23">
-        <f>IFERROR(AVERAGE(C31:E31),"")</f>
-        <v/>
-      </c>
-      <c r="G31" s="28" t="n"/>
+      <c r="F31" s="28" t="n"/>
+      <c r="G31" s="23">
+        <f>IFERROR(AVERAGE(C31:F31),"")</f>
+        <v/>
+      </c>
+      <c r="H31" s="28" t="n"/>
     </row>
     <row r="32" ht="17" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
@@ -7337,11 +7386,12 @@
       </c>
       <c r="D32" s="28" t="n"/>
       <c r="E32" s="28" t="n"/>
-      <c r="F32" s="23">
-        <f>IFERROR(AVERAGE(C32:E32),"")</f>
-        <v/>
-      </c>
-      <c r="G32" s="28" t="n"/>
+      <c r="F32" s="28" t="n"/>
+      <c r="G32" s="23">
+        <f>IFERROR(AVERAGE(C32:F32),"")</f>
+        <v/>
+      </c>
+      <c r="H32" s="28" t="n"/>
     </row>
     <row r="33" ht="17" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
@@ -7357,11 +7407,12 @@
       <c r="C33" s="28" t="n"/>
       <c r="D33" s="28" t="n"/>
       <c r="E33" s="28" t="n"/>
-      <c r="F33" s="23">
-        <f>IFERROR(AVERAGE(C33:E33),"")</f>
-        <v/>
-      </c>
-      <c r="G33" s="28" t="n"/>
+      <c r="F33" s="28" t="n"/>
+      <c r="G33" s="23">
+        <f>IFERROR(AVERAGE(C33:F33),"")</f>
+        <v/>
+      </c>
+      <c r="H33" s="28" t="n"/>
     </row>
     <row r="34" ht="17" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
@@ -7377,11 +7428,12 @@
       <c r="C34" s="28" t="n"/>
       <c r="D34" s="28" t="n"/>
       <c r="E34" s="28" t="n"/>
-      <c r="F34" s="23">
-        <f>IFERROR(AVERAGE(C34:E34),"")</f>
-        <v/>
-      </c>
-      <c r="G34" s="28" t="n"/>
+      <c r="F34" s="28" t="n"/>
+      <c r="G34" s="23">
+        <f>IFERROR(AVERAGE(C34:F34),"")</f>
+        <v/>
+      </c>
+      <c r="H34" s="28" t="n"/>
     </row>
     <row r="35" ht="17" customHeight="1">
       <c r="A35" s="26" t="inlineStr">
@@ -7399,11 +7451,12 @@
         <v>0</v>
       </c>
       <c r="E35" s="28" t="n"/>
-      <c r="F35" s="23">
-        <f>IFERROR(AVERAGE(C35:E35),"")</f>
-        <v/>
-      </c>
-      <c r="G35" s="28" t="n"/>
+      <c r="F35" s="28" t="n"/>
+      <c r="G35" s="23">
+        <f>IFERROR(AVERAGE(C35:F35),"")</f>
+        <v/>
+      </c>
+      <c r="H35" s="28" t="n"/>
     </row>
     <row r="36" ht="17" customHeight="1">
       <c r="A36" s="26" t="inlineStr">
@@ -7419,11 +7472,12 @@
       <c r="C36" s="28" t="n"/>
       <c r="D36" s="28" t="n"/>
       <c r="E36" s="28" t="n"/>
-      <c r="F36" s="23">
-        <f>IFERROR(AVERAGE(C36:E36),"")</f>
-        <v/>
-      </c>
-      <c r="G36" s="28" t="n"/>
+      <c r="F36" s="28" t="n"/>
+      <c r="G36" s="23">
+        <f>IFERROR(AVERAGE(C36:F36),"")</f>
+        <v/>
+      </c>
+      <c r="H36" s="28" t="n"/>
     </row>
     <row r="37" ht="17" customHeight="1">
       <c r="A37" s="26" t="inlineStr">
@@ -7439,11 +7493,12 @@
       <c r="C37" s="28" t="n"/>
       <c r="D37" s="28" t="n"/>
       <c r="E37" s="28" t="n"/>
-      <c r="F37" s="23">
-        <f>IFERROR(AVERAGE(C37:E37),"")</f>
-        <v/>
-      </c>
-      <c r="G37" s="28" t="n"/>
+      <c r="F37" s="28" t="n"/>
+      <c r="G37" s="23">
+        <f>IFERROR(AVERAGE(C37:F37),"")</f>
+        <v/>
+      </c>
+      <c r="H37" s="28" t="n"/>
     </row>
     <row r="38" ht="17" customHeight="1">
       <c r="A38" s="26" t="inlineStr">
@@ -7459,11 +7514,12 @@
       <c r="C38" s="28" t="n"/>
       <c r="D38" s="28" t="n"/>
       <c r="E38" s="28" t="n"/>
-      <c r="F38" s="23">
-        <f>IFERROR(AVERAGE(C38:E38),"")</f>
-        <v/>
-      </c>
-      <c r="G38" s="28" t="n"/>
+      <c r="F38" s="28" t="n"/>
+      <c r="G38" s="23">
+        <f>IFERROR(AVERAGE(C38:F38),"")</f>
+        <v/>
+      </c>
+      <c r="H38" s="28" t="n"/>
     </row>
     <row r="39" ht="12" customHeight="1">
       <c r="A39" s="31" t="inlineStr">
@@ -7475,8 +7531,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A39:H39"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Shop_Tracker_2065_2026.xlsx
+++ b/Shop_Tracker_2065_2026.xlsx
@@ -6705,7 +6705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -6714,8 +6714,9 @@
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -6750,10 +6751,15 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
+          <t>WEEK 5</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
           <t>MTD SCORE</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>MTD DOLLARS</t>
         </is>
@@ -6786,8 +6792,13 @@
           <t>07/16</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr"/>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>07/23</t>
+        </is>
+      </c>
       <c r="H3" s="4" t="inlineStr"/>
+      <c r="I3" s="4" t="inlineStr"/>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="4" t="inlineStr"/>
@@ -6816,8 +6827,13 @@
           <t>Dinner</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr"/>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
       <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="9" t="inlineStr"/>
@@ -6838,8 +6854,11 @@
       <c r="F5" s="11" t="n">
         <v>95</v>
       </c>
-      <c r="G5" s="9" t="inlineStr"/>
+      <c r="G5" s="14" t="n">
+        <v>100</v>
+      </c>
       <c r="H5" s="9" t="inlineStr"/>
+      <c r="I5" s="9" t="inlineStr"/>
     </row>
     <row r="6" ht="14" customHeight="1">
       <c r="A6" s="15" t="inlineStr"/>
@@ -6854,6 +6873,7 @@
       <c r="F6" s="17" t="n"/>
       <c r="G6" s="17" t="n"/>
       <c r="H6" s="17" t="n"/>
+      <c r="I6" s="17" t="n"/>
     </row>
     <row r="7" ht="14" customHeight="1">
       <c r="A7" s="15" t="inlineStr"/>
@@ -6868,6 +6888,7 @@
       <c r="F7" s="17" t="n"/>
       <c r="G7" s="17" t="n"/>
       <c r="H7" s="17" t="n"/>
+      <c r="I7" s="17" t="n"/>
     </row>
     <row r="8" ht="14" customHeight="1">
       <c r="A8" s="15" t="inlineStr"/>
@@ -6882,6 +6903,7 @@
       <c r="F8" s="17" t="n"/>
       <c r="G8" s="17" t="n"/>
       <c r="H8" s="17" t="n"/>
+      <c r="I8" s="17" t="n"/>
     </row>
     <row r="9" ht="14" customHeight="1">
       <c r="A9" s="15" t="inlineStr"/>
@@ -6896,6 +6918,7 @@
       <c r="F9" s="17" t="n"/>
       <c r="G9" s="17" t="n"/>
       <c r="H9" s="17" t="n"/>
+      <c r="I9" s="17" t="n"/>
     </row>
     <row r="10" ht="14" customHeight="1">
       <c r="A10" s="15" t="inlineStr"/>
@@ -6910,6 +6933,7 @@
       <c r="F10" s="17" t="n"/>
       <c r="G10" s="17" t="n"/>
       <c r="H10" s="17" t="n"/>
+      <c r="I10" s="17" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="18" t="inlineStr">
@@ -6921,12 +6945,13 @@
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>MTD SCORE</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>MTD DOLLARS</t>
         </is>
@@ -6951,11 +6976,12 @@
         <v>87</v>
       </c>
       <c r="F12" s="21" t="n"/>
-      <c r="G12" s="23">
-        <f>IFERROR(AVERAGE(C12:F12),"")</f>
-        <v/>
-      </c>
-      <c r="H12" s="21" t="n"/>
+      <c r="G12" s="21" t="n"/>
+      <c r="H12" s="23">
+        <f>IFERROR(AVERAGE(C12:G12),"")</f>
+        <v/>
+      </c>
+      <c r="I12" s="21" t="n"/>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
@@ -6972,11 +6998,12 @@
       <c r="D13" s="21" t="n"/>
       <c r="E13" s="21" t="n"/>
       <c r="F13" s="21" t="n"/>
-      <c r="G13" s="23">
-        <f>IFERROR(AVERAGE(C13:F13),"")</f>
-        <v/>
-      </c>
-      <c r="H13" s="21" t="n"/>
+      <c r="G13" s="21" t="n"/>
+      <c r="H13" s="23">
+        <f>IFERROR(AVERAGE(C13:G13),"")</f>
+        <v/>
+      </c>
+      <c r="I13" s="21" t="n"/>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
@@ -6993,11 +7020,12 @@
       <c r="D14" s="21" t="n"/>
       <c r="E14" s="21" t="n"/>
       <c r="F14" s="21" t="n"/>
-      <c r="G14" s="23">
-        <f>IFERROR(AVERAGE(C14:F14),"")</f>
-        <v/>
-      </c>
-      <c r="H14" s="21" t="n"/>
+      <c r="G14" s="21" t="n"/>
+      <c r="H14" s="23">
+        <f>IFERROR(AVERAGE(C14:G14),"")</f>
+        <v/>
+      </c>
+      <c r="I14" s="21" t="n"/>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
@@ -7014,11 +7042,12 @@
       <c r="D15" s="28" t="n"/>
       <c r="E15" s="28" t="n"/>
       <c r="F15" s="28" t="n"/>
-      <c r="G15" s="23">
-        <f>IFERROR(AVERAGE(C15:F15),"")</f>
-        <v/>
-      </c>
-      <c r="H15" s="28" t="n"/>
+      <c r="G15" s="28" t="n"/>
+      <c r="H15" s="23">
+        <f>IFERROR(AVERAGE(C15:G15),"")</f>
+        <v/>
+      </c>
+      <c r="I15" s="28" t="n"/>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
@@ -7035,11 +7064,12 @@
       <c r="D16" s="28" t="n"/>
       <c r="E16" s="28" t="n"/>
       <c r="F16" s="28" t="n"/>
-      <c r="G16" s="23">
-        <f>IFERROR(AVERAGE(C16:F16),"")</f>
-        <v/>
-      </c>
-      <c r="H16" s="28" t="n"/>
+      <c r="G16" s="28" t="n"/>
+      <c r="H16" s="23">
+        <f>IFERROR(AVERAGE(C16:G16),"")</f>
+        <v/>
+      </c>
+      <c r="I16" s="28" t="n"/>
     </row>
     <row r="17" ht="17" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
@@ -7056,11 +7086,12 @@
       <c r="D17" s="28" t="n"/>
       <c r="E17" s="28" t="n"/>
       <c r="F17" s="28" t="n"/>
-      <c r="G17" s="23">
-        <f>IFERROR(AVERAGE(C17:F17),"")</f>
-        <v/>
-      </c>
-      <c r="H17" s="28" t="n"/>
+      <c r="G17" s="28" t="n"/>
+      <c r="H17" s="23">
+        <f>IFERROR(AVERAGE(C17:G17),"")</f>
+        <v/>
+      </c>
+      <c r="I17" s="28" t="n"/>
     </row>
     <row r="18" ht="17" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
@@ -7077,11 +7108,12 @@
       <c r="D18" s="28" t="n"/>
       <c r="E18" s="28" t="n"/>
       <c r="F18" s="28" t="n"/>
-      <c r="G18" s="23">
-        <f>IFERROR(AVERAGE(C18:F18),"")</f>
-        <v/>
-      </c>
-      <c r="H18" s="28" t="n"/>
+      <c r="G18" s="28" t="n"/>
+      <c r="H18" s="23">
+        <f>IFERROR(AVERAGE(C18:G18),"")</f>
+        <v/>
+      </c>
+      <c r="I18" s="28" t="n"/>
     </row>
     <row r="19" ht="17" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
@@ -7098,11 +7130,12 @@
       <c r="D19" s="28" t="n"/>
       <c r="E19" s="28" t="n"/>
       <c r="F19" s="28" t="n"/>
-      <c r="G19" s="23">
-        <f>IFERROR(AVERAGE(C19:F19),"")</f>
-        <v/>
-      </c>
-      <c r="H19" s="28" t="n"/>
+      <c r="G19" s="28" t="n"/>
+      <c r="H19" s="23">
+        <f>IFERROR(AVERAGE(C19:G19),"")</f>
+        <v/>
+      </c>
+      <c r="I19" s="28" t="n"/>
     </row>
     <row r="20" ht="17" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
@@ -7119,11 +7152,12 @@
       <c r="D20" s="28" t="n"/>
       <c r="E20" s="28" t="n"/>
       <c r="F20" s="28" t="n"/>
-      <c r="G20" s="23">
-        <f>IFERROR(AVERAGE(C20:F20),"")</f>
-        <v/>
-      </c>
-      <c r="H20" s="28" t="n"/>
+      <c r="G20" s="28" t="n"/>
+      <c r="H20" s="23">
+        <f>IFERROR(AVERAGE(C20:G20),"")</f>
+        <v/>
+      </c>
+      <c r="I20" s="28" t="n"/>
     </row>
     <row r="21" ht="17" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
@@ -7140,11 +7174,12 @@
       <c r="D21" s="28" t="n"/>
       <c r="E21" s="28" t="n"/>
       <c r="F21" s="28" t="n"/>
-      <c r="G21" s="23">
-        <f>IFERROR(AVERAGE(C21:F21),"")</f>
-        <v/>
-      </c>
-      <c r="H21" s="28" t="n"/>
+      <c r="G21" s="28" t="n"/>
+      <c r="H21" s="23">
+        <f>IFERROR(AVERAGE(C21:G21),"")</f>
+        <v/>
+      </c>
+      <c r="I21" s="28" t="n"/>
     </row>
     <row r="22" ht="17" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
@@ -7161,11 +7196,12 @@
       <c r="D22" s="28" t="n"/>
       <c r="E22" s="28" t="n"/>
       <c r="F22" s="28" t="n"/>
-      <c r="G22" s="23">
-        <f>IFERROR(AVERAGE(C22:F22),"")</f>
-        <v/>
-      </c>
-      <c r="H22" s="28" t="n"/>
+      <c r="G22" s="28" t="n"/>
+      <c r="H22" s="23">
+        <f>IFERROR(AVERAGE(C22:G22),"")</f>
+        <v/>
+      </c>
+      <c r="I22" s="28" t="n"/>
     </row>
     <row r="23" ht="17" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
@@ -7188,11 +7224,16 @@
       <c r="F23" s="29" t="n">
         <v>95</v>
       </c>
-      <c r="G23" s="23">
-        <f>IFERROR(AVERAGE(C23:F23),"")</f>
-        <v/>
-      </c>
-      <c r="H23" s="28" t="n"/>
+      <c r="G23" s="22" t="n">
+        <v>100</v>
+      </c>
+      <c r="H23" s="23">
+        <f>IFERROR(AVERAGE(C23:G23),"")</f>
+        <v/>
+      </c>
+      <c r="I23" s="24" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="24" ht="17" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
@@ -7209,11 +7250,12 @@
       <c r="D24" s="28" t="n"/>
       <c r="E24" s="28" t="n"/>
       <c r="F24" s="28" t="n"/>
-      <c r="G24" s="23">
-        <f>IFERROR(AVERAGE(C24:F24),"")</f>
-        <v/>
-      </c>
-      <c r="H24" s="28" t="n"/>
+      <c r="G24" s="28" t="n"/>
+      <c r="H24" s="23">
+        <f>IFERROR(AVERAGE(C24:G24),"")</f>
+        <v/>
+      </c>
+      <c r="I24" s="28" t="n"/>
     </row>
     <row r="25" ht="17" customHeight="1">
       <c r="A25" s="26" t="inlineStr">
@@ -7230,11 +7272,12 @@
       <c r="D25" s="28" t="n"/>
       <c r="E25" s="28" t="n"/>
       <c r="F25" s="28" t="n"/>
-      <c r="G25" s="23">
-        <f>IFERROR(AVERAGE(C25:F25),"")</f>
-        <v/>
-      </c>
-      <c r="H25" s="28" t="n"/>
+      <c r="G25" s="28" t="n"/>
+      <c r="H25" s="23">
+        <f>IFERROR(AVERAGE(C25:G25),"")</f>
+        <v/>
+      </c>
+      <c r="I25" s="28" t="n"/>
     </row>
     <row r="26" ht="17" customHeight="1">
       <c r="A26" s="26" t="inlineStr">
@@ -7257,11 +7300,16 @@
       <c r="F26" s="29" t="n">
         <v>95</v>
       </c>
-      <c r="G26" s="23">
-        <f>IFERROR(AVERAGE(C26:F26),"")</f>
-        <v/>
-      </c>
-      <c r="H26" s="28" t="n"/>
+      <c r="G26" s="22" t="n">
+        <v>100</v>
+      </c>
+      <c r="H26" s="23">
+        <f>IFERROR(AVERAGE(C26:G26),"")</f>
+        <v/>
+      </c>
+      <c r="I26" s="24" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="27" ht="17" customHeight="1">
       <c r="A27" s="26" t="inlineStr">
@@ -7278,11 +7326,12 @@
       <c r="D27" s="28" t="n"/>
       <c r="E27" s="28" t="n"/>
       <c r="F27" s="28" t="n"/>
-      <c r="G27" s="23">
-        <f>IFERROR(AVERAGE(C27:F27),"")</f>
-        <v/>
-      </c>
-      <c r="H27" s="28" t="n"/>
+      <c r="G27" s="28" t="n"/>
+      <c r="H27" s="23">
+        <f>IFERROR(AVERAGE(C27:G27),"")</f>
+        <v/>
+      </c>
+      <c r="I27" s="28" t="n"/>
     </row>
     <row r="28" ht="17" customHeight="1">
       <c r="A28" s="26" t="inlineStr">
@@ -7299,11 +7348,12 @@
       <c r="D28" s="28" t="n"/>
       <c r="E28" s="28" t="n"/>
       <c r="F28" s="28" t="n"/>
-      <c r="G28" s="23">
-        <f>IFERROR(AVERAGE(C28:F28),"")</f>
-        <v/>
-      </c>
-      <c r="H28" s="28" t="n"/>
+      <c r="G28" s="28" t="n"/>
+      <c r="H28" s="23">
+        <f>IFERROR(AVERAGE(C28:G28),"")</f>
+        <v/>
+      </c>
+      <c r="I28" s="28" t="n"/>
     </row>
     <row r="29" ht="17" customHeight="1">
       <c r="A29" s="26" t="inlineStr">
@@ -7320,11 +7370,12 @@
       <c r="D29" s="28" t="n"/>
       <c r="E29" s="28" t="n"/>
       <c r="F29" s="28" t="n"/>
-      <c r="G29" s="23">
-        <f>IFERROR(AVERAGE(C29:F29),"")</f>
-        <v/>
-      </c>
-      <c r="H29" s="28" t="n"/>
+      <c r="G29" s="28" t="n"/>
+      <c r="H29" s="23">
+        <f>IFERROR(AVERAGE(C29:G29),"")</f>
+        <v/>
+      </c>
+      <c r="I29" s="28" t="n"/>
     </row>
     <row r="30" ht="17" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
@@ -7341,11 +7392,12 @@
       <c r="D30" s="28" t="n"/>
       <c r="E30" s="28" t="n"/>
       <c r="F30" s="28" t="n"/>
-      <c r="G30" s="23">
-        <f>IFERROR(AVERAGE(C30:F30),"")</f>
-        <v/>
-      </c>
-      <c r="H30" s="28" t="n"/>
+      <c r="G30" s="28" t="n"/>
+      <c r="H30" s="23">
+        <f>IFERROR(AVERAGE(C30:G30),"")</f>
+        <v/>
+      </c>
+      <c r="I30" s="28" t="n"/>
     </row>
     <row r="31" ht="17" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
@@ -7364,11 +7416,12 @@
       <c r="D31" s="28" t="n"/>
       <c r="E31" s="28" t="n"/>
       <c r="F31" s="28" t="n"/>
-      <c r="G31" s="23">
-        <f>IFERROR(AVERAGE(C31:F31),"")</f>
-        <v/>
-      </c>
-      <c r="H31" s="28" t="n"/>
+      <c r="G31" s="28" t="n"/>
+      <c r="H31" s="23">
+        <f>IFERROR(AVERAGE(C31:G31),"")</f>
+        <v/>
+      </c>
+      <c r="I31" s="28" t="n"/>
     </row>
     <row r="32" ht="17" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
@@ -7387,11 +7440,12 @@
       <c r="D32" s="28" t="n"/>
       <c r="E32" s="28" t="n"/>
       <c r="F32" s="28" t="n"/>
-      <c r="G32" s="23">
-        <f>IFERROR(AVERAGE(C32:F32),"")</f>
-        <v/>
-      </c>
-      <c r="H32" s="28" t="n"/>
+      <c r="G32" s="28" t="n"/>
+      <c r="H32" s="23">
+        <f>IFERROR(AVERAGE(C32:G32),"")</f>
+        <v/>
+      </c>
+      <c r="I32" s="28" t="n"/>
     </row>
     <row r="33" ht="17" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
@@ -7408,11 +7462,12 @@
       <c r="D33" s="28" t="n"/>
       <c r="E33" s="28" t="n"/>
       <c r="F33" s="28" t="n"/>
-      <c r="G33" s="23">
-        <f>IFERROR(AVERAGE(C33:F33),"")</f>
-        <v/>
-      </c>
-      <c r="H33" s="28" t="n"/>
+      <c r="G33" s="28" t="n"/>
+      <c r="H33" s="23">
+        <f>IFERROR(AVERAGE(C33:G33),"")</f>
+        <v/>
+      </c>
+      <c r="I33" s="28" t="n"/>
     </row>
     <row r="34" ht="17" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
@@ -7429,11 +7484,12 @@
       <c r="D34" s="28" t="n"/>
       <c r="E34" s="28" t="n"/>
       <c r="F34" s="28" t="n"/>
-      <c r="G34" s="23">
-        <f>IFERROR(AVERAGE(C34:F34),"")</f>
-        <v/>
-      </c>
-      <c r="H34" s="28" t="n"/>
+      <c r="G34" s="28" t="n"/>
+      <c r="H34" s="23">
+        <f>IFERROR(AVERAGE(C34:G34),"")</f>
+        <v/>
+      </c>
+      <c r="I34" s="28" t="n"/>
     </row>
     <row r="35" ht="17" customHeight="1">
       <c r="A35" s="26" t="inlineStr">
@@ -7452,11 +7508,16 @@
       </c>
       <c r="E35" s="28" t="n"/>
       <c r="F35" s="28" t="n"/>
-      <c r="G35" s="23">
-        <f>IFERROR(AVERAGE(C35:F35),"")</f>
-        <v/>
-      </c>
-      <c r="H35" s="28" t="n"/>
+      <c r="G35" s="22" t="n">
+        <v>100</v>
+      </c>
+      <c r="H35" s="23">
+        <f>IFERROR(AVERAGE(C35:G35),"")</f>
+        <v/>
+      </c>
+      <c r="I35" s="24" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="36" ht="17" customHeight="1">
       <c r="A36" s="26" t="inlineStr">
@@ -7473,11 +7534,12 @@
       <c r="D36" s="28" t="n"/>
       <c r="E36" s="28" t="n"/>
       <c r="F36" s="28" t="n"/>
-      <c r="G36" s="23">
-        <f>IFERROR(AVERAGE(C36:F36),"")</f>
-        <v/>
-      </c>
-      <c r="H36" s="28" t="n"/>
+      <c r="G36" s="28" t="n"/>
+      <c r="H36" s="23">
+        <f>IFERROR(AVERAGE(C36:G36),"")</f>
+        <v/>
+      </c>
+      <c r="I36" s="28" t="n"/>
     </row>
     <row r="37" ht="17" customHeight="1">
       <c r="A37" s="26" t="inlineStr">
@@ -7494,11 +7556,12 @@
       <c r="D37" s="28" t="n"/>
       <c r="E37" s="28" t="n"/>
       <c r="F37" s="28" t="n"/>
-      <c r="G37" s="23">
-        <f>IFERROR(AVERAGE(C37:F37),"")</f>
-        <v/>
-      </c>
-      <c r="H37" s="28" t="n"/>
+      <c r="G37" s="28" t="n"/>
+      <c r="H37" s="23">
+        <f>IFERROR(AVERAGE(C37:G37),"")</f>
+        <v/>
+      </c>
+      <c r="I37" s="28" t="n"/>
     </row>
     <row r="38" ht="17" customHeight="1">
       <c r="A38" s="26" t="inlineStr">
@@ -7515,11 +7578,12 @@
       <c r="D38" s="28" t="n"/>
       <c r="E38" s="28" t="n"/>
       <c r="F38" s="28" t="n"/>
-      <c r="G38" s="23">
-        <f>IFERROR(AVERAGE(C38:F38),"")</f>
-        <v/>
-      </c>
-      <c r="H38" s="28" t="n"/>
+      <c r="G38" s="28" t="n"/>
+      <c r="H38" s="23">
+        <f>IFERROR(AVERAGE(C38:G38),"")</f>
+        <v/>
+      </c>
+      <c r="I38" s="28" t="n"/>
     </row>
     <row r="39" ht="12" customHeight="1">
       <c r="A39" s="31" t="inlineStr">
@@ -7530,9 +7594,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A39:H39"/>
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A39:I39"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Shop_Tracker_2065_2026.xlsx
+++ b/Shop_Tracker_2065_2026.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="January" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="February" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="March" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="April" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="May" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="June" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="July" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="January" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="February" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="March" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="April" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="May" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="June" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="July" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/Shop_Tracker_2065_2026.xlsx
+++ b/Shop_Tracker_2065_2026.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="January" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="February" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="March" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="April" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="May" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="June" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="July" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="January" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="February" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="March" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="April" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="May" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="June" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="July" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/Shop_Tracker_2065_2026.xlsx
+++ b/Shop_Tracker_2065_2026.xlsx
@@ -14,6 +14,7 @@
     <sheet name="May" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="June" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="July" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="August" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6705,7 +6706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -6715,8 +6716,9 @@
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -6756,10 +6758,15 @@
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
+          <t>WEEK 6</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
           <t>MTD SCORE</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>MTD DOLLARS</t>
         </is>
@@ -6797,8 +6804,13 @@
           <t>07/23</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr"/>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>07/31</t>
+        </is>
+      </c>
       <c r="I3" s="4" t="inlineStr"/>
+      <c r="J3" s="4" t="inlineStr"/>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="4" t="inlineStr"/>
@@ -6832,8 +6844,13 @@
           <t>Dinner</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr"/>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>Lunch</t>
+        </is>
+      </c>
       <c r="I4" s="4" t="inlineStr"/>
+      <c r="J4" s="4" t="inlineStr"/>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="9" t="inlineStr"/>
@@ -6857,8 +6874,11 @@
       <c r="G5" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="H5" s="9" t="inlineStr"/>
+      <c r="H5" s="14" t="n">
+        <v>100</v>
+      </c>
       <c r="I5" s="9" t="inlineStr"/>
+      <c r="J5" s="9" t="inlineStr"/>
     </row>
     <row r="6" ht="14" customHeight="1">
       <c r="A6" s="15" t="inlineStr"/>
@@ -6874,6 +6894,7 @@
       <c r="G6" s="17" t="n"/>
       <c r="H6" s="17" t="n"/>
       <c r="I6" s="17" t="n"/>
+      <c r="J6" s="17" t="n"/>
     </row>
     <row r="7" ht="14" customHeight="1">
       <c r="A7" s="15" t="inlineStr"/>
@@ -6889,6 +6910,7 @@
       <c r="G7" s="17" t="n"/>
       <c r="H7" s="17" t="n"/>
       <c r="I7" s="17" t="n"/>
+      <c r="J7" s="17" t="n"/>
     </row>
     <row r="8" ht="14" customHeight="1">
       <c r="A8" s="15" t="inlineStr"/>
@@ -6904,6 +6926,7 @@
       <c r="G8" s="17" t="n"/>
       <c r="H8" s="17" t="n"/>
       <c r="I8" s="17" t="n"/>
+      <c r="J8" s="17" t="n"/>
     </row>
     <row r="9" ht="14" customHeight="1">
       <c r="A9" s="15" t="inlineStr"/>
@@ -6919,6 +6942,7 @@
       <c r="G9" s="17" t="n"/>
       <c r="H9" s="17" t="n"/>
       <c r="I9" s="17" t="n"/>
+      <c r="J9" s="17" t="n"/>
     </row>
     <row r="10" ht="14" customHeight="1">
       <c r="A10" s="15" t="inlineStr"/>
@@ -6934,6 +6958,7 @@
       <c r="G10" s="17" t="n"/>
       <c r="H10" s="17" t="n"/>
       <c r="I10" s="17" t="n"/>
+      <c r="J10" s="17" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="18" t="inlineStr">
@@ -6946,12 +6971,13 @@
       <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>MTD SCORE</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>MTD DOLLARS</t>
         </is>
@@ -6977,11 +7003,12 @@
       </c>
       <c r="F12" s="21" t="n"/>
       <c r="G12" s="21" t="n"/>
-      <c r="H12" s="23">
-        <f>IFERROR(AVERAGE(C12:G12),"")</f>
-        <v/>
-      </c>
-      <c r="I12" s="21" t="n"/>
+      <c r="H12" s="21" t="n"/>
+      <c r="I12" s="23">
+        <f>IFERROR(AVERAGE(C12:H12),"")</f>
+        <v/>
+      </c>
+      <c r="J12" s="21" t="n"/>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
@@ -6999,11 +7026,12 @@
       <c r="E13" s="21" t="n"/>
       <c r="F13" s="21" t="n"/>
       <c r="G13" s="21" t="n"/>
-      <c r="H13" s="23">
-        <f>IFERROR(AVERAGE(C13:G13),"")</f>
-        <v/>
-      </c>
-      <c r="I13" s="21" t="n"/>
+      <c r="H13" s="21" t="n"/>
+      <c r="I13" s="23">
+        <f>IFERROR(AVERAGE(C13:H13),"")</f>
+        <v/>
+      </c>
+      <c r="J13" s="21" t="n"/>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
@@ -7021,11 +7049,12 @@
       <c r="E14" s="21" t="n"/>
       <c r="F14" s="21" t="n"/>
       <c r="G14" s="21" t="n"/>
-      <c r="H14" s="23">
-        <f>IFERROR(AVERAGE(C14:G14),"")</f>
-        <v/>
-      </c>
-      <c r="I14" s="21" t="n"/>
+      <c r="H14" s="21" t="n"/>
+      <c r="I14" s="23">
+        <f>IFERROR(AVERAGE(C14:H14),"")</f>
+        <v/>
+      </c>
+      <c r="J14" s="21" t="n"/>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
@@ -7043,11 +7072,12 @@
       <c r="E15" s="28" t="n"/>
       <c r="F15" s="28" t="n"/>
       <c r="G15" s="28" t="n"/>
-      <c r="H15" s="23">
-        <f>IFERROR(AVERAGE(C15:G15),"")</f>
-        <v/>
-      </c>
-      <c r="I15" s="28" t="n"/>
+      <c r="H15" s="28" t="n"/>
+      <c r="I15" s="23">
+        <f>IFERROR(AVERAGE(C15:H15),"")</f>
+        <v/>
+      </c>
+      <c r="J15" s="28" t="n"/>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
@@ -7065,11 +7095,12 @@
       <c r="E16" s="28" t="n"/>
       <c r="F16" s="28" t="n"/>
       <c r="G16" s="28" t="n"/>
-      <c r="H16" s="23">
-        <f>IFERROR(AVERAGE(C16:G16),"")</f>
-        <v/>
-      </c>
-      <c r="I16" s="28" t="n"/>
+      <c r="H16" s="28" t="n"/>
+      <c r="I16" s="23">
+        <f>IFERROR(AVERAGE(C16:H16),"")</f>
+        <v/>
+      </c>
+      <c r="J16" s="28" t="n"/>
     </row>
     <row r="17" ht="17" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
@@ -7087,11 +7118,12 @@
       <c r="E17" s="28" t="n"/>
       <c r="F17" s="28" t="n"/>
       <c r="G17" s="28" t="n"/>
-      <c r="H17" s="23">
-        <f>IFERROR(AVERAGE(C17:G17),"")</f>
-        <v/>
-      </c>
-      <c r="I17" s="28" t="n"/>
+      <c r="H17" s="28" t="n"/>
+      <c r="I17" s="23">
+        <f>IFERROR(AVERAGE(C17:H17),"")</f>
+        <v/>
+      </c>
+      <c r="J17" s="28" t="n"/>
     </row>
     <row r="18" ht="17" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
@@ -7109,11 +7141,12 @@
       <c r="E18" s="28" t="n"/>
       <c r="F18" s="28" t="n"/>
       <c r="G18" s="28" t="n"/>
-      <c r="H18" s="23">
-        <f>IFERROR(AVERAGE(C18:G18),"")</f>
-        <v/>
-      </c>
-      <c r="I18" s="28" t="n"/>
+      <c r="H18" s="28" t="n"/>
+      <c r="I18" s="23">
+        <f>IFERROR(AVERAGE(C18:H18),"")</f>
+        <v/>
+      </c>
+      <c r="J18" s="28" t="n"/>
     </row>
     <row r="19" ht="17" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
@@ -7131,11 +7164,12 @@
       <c r="E19" s="28" t="n"/>
       <c r="F19" s="28" t="n"/>
       <c r="G19" s="28" t="n"/>
-      <c r="H19" s="23">
-        <f>IFERROR(AVERAGE(C19:G19),"")</f>
-        <v/>
-      </c>
-      <c r="I19" s="28" t="n"/>
+      <c r="H19" s="28" t="n"/>
+      <c r="I19" s="23">
+        <f>IFERROR(AVERAGE(C19:H19),"")</f>
+        <v/>
+      </c>
+      <c r="J19" s="28" t="n"/>
     </row>
     <row r="20" ht="17" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
@@ -7153,11 +7187,12 @@
       <c r="E20" s="28" t="n"/>
       <c r="F20" s="28" t="n"/>
       <c r="G20" s="28" t="n"/>
-      <c r="H20" s="23">
-        <f>IFERROR(AVERAGE(C20:G20),"")</f>
-        <v/>
-      </c>
-      <c r="I20" s="28" t="n"/>
+      <c r="H20" s="28" t="n"/>
+      <c r="I20" s="23">
+        <f>IFERROR(AVERAGE(C20:H20),"")</f>
+        <v/>
+      </c>
+      <c r="J20" s="28" t="n"/>
     </row>
     <row r="21" ht="17" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
@@ -7175,11 +7210,12 @@
       <c r="E21" s="28" t="n"/>
       <c r="F21" s="28" t="n"/>
       <c r="G21" s="28" t="n"/>
-      <c r="H21" s="23">
-        <f>IFERROR(AVERAGE(C21:G21),"")</f>
-        <v/>
-      </c>
-      <c r="I21" s="28" t="n"/>
+      <c r="H21" s="28" t="n"/>
+      <c r="I21" s="23">
+        <f>IFERROR(AVERAGE(C21:H21),"")</f>
+        <v/>
+      </c>
+      <c r="J21" s="28" t="n"/>
     </row>
     <row r="22" ht="17" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
@@ -7197,11 +7233,12 @@
       <c r="E22" s="28" t="n"/>
       <c r="F22" s="28" t="n"/>
       <c r="G22" s="28" t="n"/>
-      <c r="H22" s="23">
-        <f>IFERROR(AVERAGE(C22:G22),"")</f>
-        <v/>
-      </c>
-      <c r="I22" s="28" t="n"/>
+      <c r="H22" s="28" t="n"/>
+      <c r="I22" s="23">
+        <f>IFERROR(AVERAGE(C22:H22),"")</f>
+        <v/>
+      </c>
+      <c r="J22" s="28" t="n"/>
     </row>
     <row r="23" ht="17" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
@@ -7227,11 +7264,12 @@
       <c r="G23" s="22" t="n">
         <v>100</v>
       </c>
-      <c r="H23" s="23">
-        <f>IFERROR(AVERAGE(C23:G23),"")</f>
-        <v/>
-      </c>
-      <c r="I23" s="24" t="n">
+      <c r="H23" s="28" t="n"/>
+      <c r="I23" s="23">
+        <f>IFERROR(AVERAGE(C23:H23),"")</f>
+        <v/>
+      </c>
+      <c r="J23" s="24" t="n">
         <v>46</v>
       </c>
     </row>
@@ -7251,11 +7289,12 @@
       <c r="E24" s="28" t="n"/>
       <c r="F24" s="28" t="n"/>
       <c r="G24" s="28" t="n"/>
-      <c r="H24" s="23">
-        <f>IFERROR(AVERAGE(C24:G24),"")</f>
-        <v/>
-      </c>
-      <c r="I24" s="28" t="n"/>
+      <c r="H24" s="28" t="n"/>
+      <c r="I24" s="23">
+        <f>IFERROR(AVERAGE(C24:H24),"")</f>
+        <v/>
+      </c>
+      <c r="J24" s="28" t="n"/>
     </row>
     <row r="25" ht="17" customHeight="1">
       <c r="A25" s="26" t="inlineStr">
@@ -7273,11 +7312,12 @@
       <c r="E25" s="28" t="n"/>
       <c r="F25" s="28" t="n"/>
       <c r="G25" s="28" t="n"/>
-      <c r="H25" s="23">
-        <f>IFERROR(AVERAGE(C25:G25),"")</f>
-        <v/>
-      </c>
-      <c r="I25" s="28" t="n"/>
+      <c r="H25" s="28" t="n"/>
+      <c r="I25" s="23">
+        <f>IFERROR(AVERAGE(C25:H25),"")</f>
+        <v/>
+      </c>
+      <c r="J25" s="28" t="n"/>
     </row>
     <row r="26" ht="17" customHeight="1">
       <c r="A26" s="26" t="inlineStr">
@@ -7303,11 +7343,12 @@
       <c r="G26" s="22" t="n">
         <v>100</v>
       </c>
-      <c r="H26" s="23">
-        <f>IFERROR(AVERAGE(C26:G26),"")</f>
-        <v/>
-      </c>
-      <c r="I26" s="24" t="n">
+      <c r="H26" s="28" t="n"/>
+      <c r="I26" s="23">
+        <f>IFERROR(AVERAGE(C26:H26),"")</f>
+        <v/>
+      </c>
+      <c r="J26" s="24" t="n">
         <v>46</v>
       </c>
     </row>
@@ -7327,11 +7368,12 @@
       <c r="E27" s="28" t="n"/>
       <c r="F27" s="28" t="n"/>
       <c r="G27" s="28" t="n"/>
-      <c r="H27" s="23">
-        <f>IFERROR(AVERAGE(C27:G27),"")</f>
-        <v/>
-      </c>
-      <c r="I27" s="28" t="n"/>
+      <c r="H27" s="28" t="n"/>
+      <c r="I27" s="23">
+        <f>IFERROR(AVERAGE(C27:H27),"")</f>
+        <v/>
+      </c>
+      <c r="J27" s="28" t="n"/>
     </row>
     <row r="28" ht="17" customHeight="1">
       <c r="A28" s="26" t="inlineStr">
@@ -7349,11 +7391,12 @@
       <c r="E28" s="28" t="n"/>
       <c r="F28" s="28" t="n"/>
       <c r="G28" s="28" t="n"/>
-      <c r="H28" s="23">
-        <f>IFERROR(AVERAGE(C28:G28),"")</f>
-        <v/>
-      </c>
-      <c r="I28" s="28" t="n"/>
+      <c r="H28" s="28" t="n"/>
+      <c r="I28" s="23">
+        <f>IFERROR(AVERAGE(C28:H28),"")</f>
+        <v/>
+      </c>
+      <c r="J28" s="28" t="n"/>
     </row>
     <row r="29" ht="17" customHeight="1">
       <c r="A29" s="26" t="inlineStr">
@@ -7371,11 +7414,12 @@
       <c r="E29" s="28" t="n"/>
       <c r="F29" s="28" t="n"/>
       <c r="G29" s="28" t="n"/>
-      <c r="H29" s="23">
-        <f>IFERROR(AVERAGE(C29:G29),"")</f>
-        <v/>
-      </c>
-      <c r="I29" s="28" t="n"/>
+      <c r="H29" s="28" t="n"/>
+      <c r="I29" s="23">
+        <f>IFERROR(AVERAGE(C29:H29),"")</f>
+        <v/>
+      </c>
+      <c r="J29" s="28" t="n"/>
     </row>
     <row r="30" ht="17" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
@@ -7393,11 +7437,12 @@
       <c r="E30" s="28" t="n"/>
       <c r="F30" s="28" t="n"/>
       <c r="G30" s="28" t="n"/>
-      <c r="H30" s="23">
-        <f>IFERROR(AVERAGE(C30:G30),"")</f>
-        <v/>
-      </c>
-      <c r="I30" s="28" t="n"/>
+      <c r="H30" s="28" t="n"/>
+      <c r="I30" s="23">
+        <f>IFERROR(AVERAGE(C30:H30),"")</f>
+        <v/>
+      </c>
+      <c r="J30" s="28" t="n"/>
     </row>
     <row r="31" ht="17" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
@@ -7417,11 +7462,16 @@
       <c r="E31" s="28" t="n"/>
       <c r="F31" s="28" t="n"/>
       <c r="G31" s="28" t="n"/>
-      <c r="H31" s="23">
-        <f>IFERROR(AVERAGE(C31:G31),"")</f>
-        <v/>
-      </c>
-      <c r="I31" s="28" t="n"/>
+      <c r="H31" s="22" t="n">
+        <v>100</v>
+      </c>
+      <c r="I31" s="23">
+        <f>IFERROR(AVERAGE(C31:H31),"")</f>
+        <v/>
+      </c>
+      <c r="J31" s="24" t="n">
+        <v>76.67</v>
+      </c>
     </row>
     <row r="32" ht="17" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
@@ -7441,11 +7491,12 @@
       <c r="E32" s="28" t="n"/>
       <c r="F32" s="28" t="n"/>
       <c r="G32" s="28" t="n"/>
-      <c r="H32" s="23">
-        <f>IFERROR(AVERAGE(C32:G32),"")</f>
-        <v/>
-      </c>
-      <c r="I32" s="28" t="n"/>
+      <c r="H32" s="28" t="n"/>
+      <c r="I32" s="23">
+        <f>IFERROR(AVERAGE(C32:H32),"")</f>
+        <v/>
+      </c>
+      <c r="J32" s="28" t="n"/>
     </row>
     <row r="33" ht="17" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
@@ -7463,11 +7514,12 @@
       <c r="E33" s="28" t="n"/>
       <c r="F33" s="28" t="n"/>
       <c r="G33" s="28" t="n"/>
-      <c r="H33" s="23">
-        <f>IFERROR(AVERAGE(C33:G33),"")</f>
-        <v/>
-      </c>
-      <c r="I33" s="28" t="n"/>
+      <c r="H33" s="28" t="n"/>
+      <c r="I33" s="23">
+        <f>IFERROR(AVERAGE(C33:H33),"")</f>
+        <v/>
+      </c>
+      <c r="J33" s="28" t="n"/>
     </row>
     <row r="34" ht="17" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
@@ -7485,11 +7537,12 @@
       <c r="E34" s="28" t="n"/>
       <c r="F34" s="28" t="n"/>
       <c r="G34" s="28" t="n"/>
-      <c r="H34" s="23">
-        <f>IFERROR(AVERAGE(C34:G34),"")</f>
-        <v/>
-      </c>
-      <c r="I34" s="28" t="n"/>
+      <c r="H34" s="28" t="n"/>
+      <c r="I34" s="23">
+        <f>IFERROR(AVERAGE(C34:H34),"")</f>
+        <v/>
+      </c>
+      <c r="J34" s="28" t="n"/>
     </row>
     <row r="35" ht="17" customHeight="1">
       <c r="A35" s="26" t="inlineStr">
@@ -7511,11 +7564,12 @@
       <c r="G35" s="22" t="n">
         <v>100</v>
       </c>
-      <c r="H35" s="23">
-        <f>IFERROR(AVERAGE(C35:G35),"")</f>
-        <v/>
-      </c>
-      <c r="I35" s="24" t="n">
+      <c r="H35" s="28" t="n"/>
+      <c r="I35" s="23">
+        <f>IFERROR(AVERAGE(C35:H35),"")</f>
+        <v/>
+      </c>
+      <c r="J35" s="24" t="n">
         <v>46</v>
       </c>
     </row>
@@ -7535,11 +7589,12 @@
       <c r="E36" s="28" t="n"/>
       <c r="F36" s="28" t="n"/>
       <c r="G36" s="28" t="n"/>
-      <c r="H36" s="23">
-        <f>IFERROR(AVERAGE(C36:G36),"")</f>
-        <v/>
-      </c>
-      <c r="I36" s="28" t="n"/>
+      <c r="H36" s="28" t="n"/>
+      <c r="I36" s="23">
+        <f>IFERROR(AVERAGE(C36:H36),"")</f>
+        <v/>
+      </c>
+      <c r="J36" s="28" t="n"/>
     </row>
     <row r="37" ht="17" customHeight="1">
       <c r="A37" s="26" t="inlineStr">
@@ -7557,11 +7612,12 @@
       <c r="E37" s="28" t="n"/>
       <c r="F37" s="28" t="n"/>
       <c r="G37" s="28" t="n"/>
-      <c r="H37" s="23">
-        <f>IFERROR(AVERAGE(C37:G37),"")</f>
-        <v/>
-      </c>
-      <c r="I37" s="28" t="n"/>
+      <c r="H37" s="28" t="n"/>
+      <c r="I37" s="23">
+        <f>IFERROR(AVERAGE(C37:H37),"")</f>
+        <v/>
+      </c>
+      <c r="J37" s="28" t="n"/>
     </row>
     <row r="38" ht="17" customHeight="1">
       <c r="A38" s="26" t="inlineStr">
@@ -7579,11 +7635,12 @@
       <c r="E38" s="28" t="n"/>
       <c r="F38" s="28" t="n"/>
       <c r="G38" s="28" t="n"/>
-      <c r="H38" s="23">
-        <f>IFERROR(AVERAGE(C38:G38),"")</f>
-        <v/>
-      </c>
-      <c r="I38" s="28" t="n"/>
+      <c r="H38" s="28" t="n"/>
+      <c r="I38" s="23">
+        <f>IFERROR(AVERAGE(C38:H38),"")</f>
+        <v/>
+      </c>
+      <c r="J38" s="28" t="n"/>
     </row>
     <row r="39" ht="12" customHeight="1">
       <c r="A39" s="31" t="inlineStr">
@@ -7594,9 +7651,672 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A39:J39"/>
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A39:I39"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>SECRET SHOPPER SCORES — AUGUST 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr"/>
+      <c r="B2" s="2" t="inlineStr"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>WEEK 1</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>MTD SCORE</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>MTD DOLLARS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="4" t="inlineStr"/>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>08/01</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr"/>
+      <c r="E3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="4" t="inlineStr"/>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Meal Period</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="9" t="inlineStr"/>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>TOTAL SCORE</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="D5" s="9" t="inlineStr"/>
+      <c r="E5" s="9" t="inlineStr"/>
+    </row>
+    <row r="6" ht="14" customHeight="1">
+      <c r="A6" s="15" t="inlineStr"/>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>Overall Experience</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="n"/>
+      <c r="D6" s="17" t="n"/>
+      <c r="E6" s="17" t="n"/>
+    </row>
+    <row r="7" ht="14" customHeight="1">
+      <c r="A7" s="15" t="inlineStr"/>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>Enthusiasm</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n"/>
+    </row>
+    <row r="8" ht="14" customHeight="1">
+      <c r="A8" s="15" t="inlineStr"/>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>Likely to Return</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="n"/>
+      <c r="D8" s="17" t="n"/>
+      <c r="E8" s="17" t="n"/>
+    </row>
+    <row r="9" ht="14" customHeight="1">
+      <c r="A9" s="15" t="inlineStr"/>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>Likely to Recommend</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="17" t="n"/>
+      <c r="E9" s="17" t="n"/>
+    </row>
+    <row r="10" ht="14" customHeight="1">
+      <c r="A10" s="15" t="inlineStr"/>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>Exceptional Act?</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="17" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t>INDIVIDUAL PERFORMANCE</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr"/>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>MTD SCORE</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>MTD DOLLARS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="17" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>Vicki Lucey</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="n"/>
+      <c r="D12" s="23">
+        <f>IFERROR(AVERAGE(C12:C12),"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="21" t="n"/>
+    </row>
+    <row r="13" ht="17" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>Kasey Wilson</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="n"/>
+      <c r="D13" s="23">
+        <f>IFERROR(AVERAGE(C13:C13),"")</f>
+        <v/>
+      </c>
+      <c r="E13" s="21" t="n"/>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>Nathan Roberts</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="n"/>
+      <c r="D14" s="23">
+        <f>IFERROR(AVERAGE(C14:C14),"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="21" t="n"/>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B15" s="27" t="inlineStr">
+        <is>
+          <t>Ailen Gonzalez Cardero</t>
+        </is>
+      </c>
+      <c r="C15" s="28" t="n"/>
+      <c r="D15" s="23">
+        <f>IFERROR(AVERAGE(C15:C15),"")</f>
+        <v/>
+      </c>
+      <c r="E15" s="28" t="n"/>
+    </row>
+    <row r="16" ht="17" customHeight="1">
+      <c r="A16" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B16" s="27" t="inlineStr">
+        <is>
+          <t>Anthony Pirtle</t>
+        </is>
+      </c>
+      <c r="C16" s="28" t="n"/>
+      <c r="D16" s="23">
+        <f>IFERROR(AVERAGE(C16:C16),"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="28" t="n"/>
+    </row>
+    <row r="17" ht="17" customHeight="1">
+      <c r="A17" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B17" s="27" t="inlineStr">
+        <is>
+          <t>Ash</t>
+        </is>
+      </c>
+      <c r="C17" s="28" t="n"/>
+      <c r="D17" s="23">
+        <f>IFERROR(AVERAGE(C17:C17),"")</f>
+        <v/>
+      </c>
+      <c r="E17" s="28" t="n"/>
+    </row>
+    <row r="18" ht="17" customHeight="1">
+      <c r="A18" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B18" s="27" t="inlineStr">
+        <is>
+          <t>Autumn Hearn</t>
+        </is>
+      </c>
+      <c r="C18" s="28" t="n"/>
+      <c r="D18" s="23">
+        <f>IFERROR(AVERAGE(C18:C18),"")</f>
+        <v/>
+      </c>
+      <c r="E18" s="28" t="n"/>
+    </row>
+    <row r="19" ht="17" customHeight="1">
+      <c r="A19" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B19" s="27" t="inlineStr">
+        <is>
+          <t>Brianna Gatewood</t>
+        </is>
+      </c>
+      <c r="C19" s="28" t="n"/>
+      <c r="D19" s="23">
+        <f>IFERROR(AVERAGE(C19:C19),"")</f>
+        <v/>
+      </c>
+      <c r="E19" s="28" t="n"/>
+    </row>
+    <row r="20" ht="17" customHeight="1">
+      <c r="A20" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B20" s="27" t="inlineStr">
+        <is>
+          <t>DaKayla Dorsey</t>
+        </is>
+      </c>
+      <c r="C20" s="28" t="n"/>
+      <c r="D20" s="23">
+        <f>IFERROR(AVERAGE(C20:C20),"")</f>
+        <v/>
+      </c>
+      <c r="E20" s="28" t="n"/>
+    </row>
+    <row r="21" ht="17" customHeight="1">
+      <c r="A21" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B21" s="27" t="inlineStr">
+        <is>
+          <t>Damon</t>
+        </is>
+      </c>
+      <c r="C21" s="28" t="n"/>
+      <c r="D21" s="23">
+        <f>IFERROR(AVERAGE(C21:C21),"")</f>
+        <v/>
+      </c>
+      <c r="E21" s="28" t="n"/>
+    </row>
+    <row r="22" ht="17" customHeight="1">
+      <c r="A22" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B22" s="27" t="inlineStr">
+        <is>
+          <t>Divan</t>
+        </is>
+      </c>
+      <c r="C22" s="28" t="n"/>
+      <c r="D22" s="23">
+        <f>IFERROR(AVERAGE(C22:C22),"")</f>
+        <v/>
+      </c>
+      <c r="E22" s="28" t="n"/>
+    </row>
+    <row r="23" ht="17" customHeight="1">
+      <c r="A23" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B23" s="27" t="inlineStr">
+        <is>
+          <t>Francisco Llorente Mejias</t>
+        </is>
+      </c>
+      <c r="C23" s="28" t="n"/>
+      <c r="D23" s="23">
+        <f>IFERROR(AVERAGE(C23:C23),"")</f>
+        <v/>
+      </c>
+      <c r="E23" s="28" t="n"/>
+    </row>
+    <row r="24" ht="17" customHeight="1">
+      <c r="A24" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B24" s="27" t="inlineStr">
+        <is>
+          <t>Grace</t>
+        </is>
+      </c>
+      <c r="C24" s="28" t="n"/>
+      <c r="D24" s="23">
+        <f>IFERROR(AVERAGE(C24:C24),"")</f>
+        <v/>
+      </c>
+      <c r="E24" s="28" t="n"/>
+    </row>
+    <row r="25" ht="17" customHeight="1">
+      <c r="A25" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B25" s="27" t="inlineStr">
+        <is>
+          <t>Jada Cox</t>
+        </is>
+      </c>
+      <c r="C25" s="28" t="n"/>
+      <c r="D25" s="23">
+        <f>IFERROR(AVERAGE(C25:C25),"")</f>
+        <v/>
+      </c>
+      <c r="E25" s="28" t="n"/>
+    </row>
+    <row r="26" ht="17" customHeight="1">
+      <c r="A26" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B26" s="27" t="inlineStr">
+        <is>
+          <t>Jeremiah Matthews</t>
+        </is>
+      </c>
+      <c r="C26" s="28" t="n"/>
+      <c r="D26" s="23">
+        <f>IFERROR(AVERAGE(C26:C26),"")</f>
+        <v/>
+      </c>
+      <c r="E26" s="28" t="n"/>
+    </row>
+    <row r="27" ht="17" customHeight="1">
+      <c r="A27" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B27" s="27" t="inlineStr">
+        <is>
+          <t>Kable</t>
+        </is>
+      </c>
+      <c r="C27" s="28" t="n"/>
+      <c r="D27" s="23">
+        <f>IFERROR(AVERAGE(C27:C27),"")</f>
+        <v/>
+      </c>
+      <c r="E27" s="28" t="n"/>
+    </row>
+    <row r="28" ht="17" customHeight="1">
+      <c r="A28" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B28" s="27" t="inlineStr">
+        <is>
+          <t>Kaisha Brewer</t>
+        </is>
+      </c>
+      <c r="C28" s="28" t="n"/>
+      <c r="D28" s="23">
+        <f>IFERROR(AVERAGE(C28:C28),"")</f>
+        <v/>
+      </c>
+      <c r="E28" s="28" t="n"/>
+    </row>
+    <row r="29" ht="17" customHeight="1">
+      <c r="A29" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B29" s="27" t="inlineStr">
+        <is>
+          <t>Kayla Valenzuela</t>
+        </is>
+      </c>
+      <c r="C29" s="28" t="n"/>
+      <c r="D29" s="23">
+        <f>IFERROR(AVERAGE(C29:C29),"")</f>
+        <v/>
+      </c>
+      <c r="E29" s="28" t="n"/>
+    </row>
+    <row r="30" ht="17" customHeight="1">
+      <c r="A30" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B30" s="27" t="inlineStr">
+        <is>
+          <t>Kenzie</t>
+        </is>
+      </c>
+      <c r="C30" s="28" t="n"/>
+      <c r="D30" s="23">
+        <f>IFERROR(AVERAGE(C30:C30),"")</f>
+        <v/>
+      </c>
+      <c r="E30" s="28" t="n"/>
+    </row>
+    <row r="31" ht="17" customHeight="1">
+      <c r="A31" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B31" s="27" t="inlineStr">
+        <is>
+          <t>Lidy Henry</t>
+        </is>
+      </c>
+      <c r="C31" s="28" t="n"/>
+      <c r="D31" s="23">
+        <f>IFERROR(AVERAGE(C31:C31),"")</f>
+        <v/>
+      </c>
+      <c r="E31" s="28" t="n"/>
+    </row>
+    <row r="32" ht="17" customHeight="1">
+      <c r="A32" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B32" s="27" t="inlineStr">
+        <is>
+          <t>Maylin Hernandez Rodriguez</t>
+        </is>
+      </c>
+      <c r="C32" s="28" t="n"/>
+      <c r="D32" s="23">
+        <f>IFERROR(AVERAGE(C32:C32),"")</f>
+        <v/>
+      </c>
+      <c r="E32" s="28" t="n"/>
+    </row>
+    <row r="33" ht="17" customHeight="1">
+      <c r="A33" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B33" s="27" t="inlineStr">
+        <is>
+          <t>Mike</t>
+        </is>
+      </c>
+      <c r="C33" s="28" t="n"/>
+      <c r="D33" s="23">
+        <f>IFERROR(AVERAGE(C33:C33),"")</f>
+        <v/>
+      </c>
+      <c r="E33" s="28" t="n"/>
+    </row>
+    <row r="34" ht="17" customHeight="1">
+      <c r="A34" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B34" s="27" t="inlineStr">
+        <is>
+          <t>Nyatiek Keah</t>
+        </is>
+      </c>
+      <c r="C34" s="28" t="n"/>
+      <c r="D34" s="23">
+        <f>IFERROR(AVERAGE(C34:C34),"")</f>
+        <v/>
+      </c>
+      <c r="E34" s="28" t="n"/>
+    </row>
+    <row r="35" ht="17" customHeight="1">
+      <c r="A35" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B35" s="27" t="inlineStr">
+        <is>
+          <t>Richard Gibbs</t>
+        </is>
+      </c>
+      <c r="C35" s="28" t="n"/>
+      <c r="D35" s="23">
+        <f>IFERROR(AVERAGE(C35:C35),"")</f>
+        <v/>
+      </c>
+      <c r="E35" s="28" t="n"/>
+    </row>
+    <row r="36" ht="17" customHeight="1">
+      <c r="A36" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B36" s="27" t="inlineStr">
+        <is>
+          <t>Ryan</t>
+        </is>
+      </c>
+      <c r="C36" s="28" t="n"/>
+      <c r="D36" s="23">
+        <f>IFERROR(AVERAGE(C36:C36),"")</f>
+        <v/>
+      </c>
+      <c r="E36" s="28" t="n"/>
+    </row>
+    <row r="37" ht="17" customHeight="1">
+      <c r="A37" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B37" s="27" t="inlineStr">
+        <is>
+          <t>Samuel Galban Rocha</t>
+        </is>
+      </c>
+      <c r="C37" s="28" t="n"/>
+      <c r="D37" s="23">
+        <f>IFERROR(AVERAGE(C37:C37),"")</f>
+        <v/>
+      </c>
+      <c r="E37" s="28" t="n"/>
+    </row>
+    <row r="38" ht="17" customHeight="1">
+      <c r="A38" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B38" s="27" t="inlineStr">
+        <is>
+          <t>Zack Whitten</t>
+        </is>
+      </c>
+      <c r="C38" s="28" t="n"/>
+      <c r="D38" s="23">
+        <f>IFERROR(AVERAGE(C38:C38),"")</f>
+        <v/>
+      </c>
+      <c r="E38" s="28" t="n"/>
+    </row>
+    <row r="39" ht="12" customHeight="1">
+      <c r="A39" s="31" t="inlineStr">
+        <is>
+          <t>Score = shop score if on shift during meal window; blank if not. MTD SCORE = average of scores worked. MTD DOLLARS = $230 ÷ on-shift count per 100% shop.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A11:B11"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Shop_Tracker_2065_2026.xlsx
+++ b/Shop_Tracker_2065_2026.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="January" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="February" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="March" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="April" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="May" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="June" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="July" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="August" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="January" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="February" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="March" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="April" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="May" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="June" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="July" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="August" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/Shop_Tracker_2065_2026.xlsx
+++ b/Shop_Tracker_2065_2026.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="January" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="February" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="March" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="April" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="May" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="June" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="July" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="August" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="January" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="February" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="March" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="April" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="May" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="June" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="July" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="August" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/Shop_Tracker_2065_2026.xlsx
+++ b/Shop_Tracker_2065_2026.xlsx
@@ -7667,14 +7667,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -7694,10 +7695,15 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
+          <t>WEEK 2</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
           <t>MTD SCORE</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>MTD DOLLARS</t>
         </is>
@@ -7715,8 +7721,13 @@
           <t>08/01</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr"/>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>08/08</t>
+        </is>
+      </c>
       <c r="E3" s="4" t="inlineStr"/>
+      <c r="F3" s="4" t="inlineStr"/>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="4" t="inlineStr"/>
@@ -7730,8 +7741,13 @@
           <t>Dinner</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr"/>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Lunch</t>
+        </is>
+      </c>
       <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="9" t="inlineStr"/>
@@ -7743,8 +7759,11 @@
       <c r="C5" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="D5" s="9" t="inlineStr"/>
+      <c r="D5" s="11" t="n">
+        <v>95</v>
+      </c>
       <c r="E5" s="9" t="inlineStr"/>
+      <c r="F5" s="9" t="inlineStr"/>
     </row>
     <row r="6" ht="14" customHeight="1">
       <c r="A6" s="15" t="inlineStr"/>
@@ -7756,6 +7775,7 @@
       <c r="C6" s="17" t="n"/>
       <c r="D6" s="17" t="n"/>
       <c r="E6" s="17" t="n"/>
+      <c r="F6" s="17" t="n"/>
     </row>
     <row r="7" ht="14" customHeight="1">
       <c r="A7" s="15" t="inlineStr"/>
@@ -7767,6 +7787,7 @@
       <c r="C7" s="17" t="n"/>
       <c r="D7" s="17" t="n"/>
       <c r="E7" s="17" t="n"/>
+      <c r="F7" s="17" t="n"/>
     </row>
     <row r="8" ht="14" customHeight="1">
       <c r="A8" s="15" t="inlineStr"/>
@@ -7778,6 +7799,7 @@
       <c r="C8" s="17" t="n"/>
       <c r="D8" s="17" t="n"/>
       <c r="E8" s="17" t="n"/>
+      <c r="F8" s="17" t="n"/>
     </row>
     <row r="9" ht="14" customHeight="1">
       <c r="A9" s="15" t="inlineStr"/>
@@ -7789,6 +7811,7 @@
       <c r="C9" s="17" t="n"/>
       <c r="D9" s="17" t="n"/>
       <c r="E9" s="17" t="n"/>
+      <c r="F9" s="17" t="n"/>
     </row>
     <row r="10" ht="14" customHeight="1">
       <c r="A10" s="15" t="inlineStr"/>
@@ -7800,6 +7823,7 @@
       <c r="C10" s="17" t="n"/>
       <c r="D10" s="17" t="n"/>
       <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="18" t="inlineStr">
@@ -7808,12 +7832,13 @@
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr"/>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr"/>
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>MTD SCORE</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>MTD DOLLARS</t>
         </is>
@@ -7831,11 +7856,12 @@
         </is>
       </c>
       <c r="C12" s="21" t="n"/>
-      <c r="D12" s="23">
-        <f>IFERROR(AVERAGE(C12:C12),"")</f>
-        <v/>
-      </c>
-      <c r="E12" s="21" t="n"/>
+      <c r="D12" s="21" t="n"/>
+      <c r="E12" s="23">
+        <f>IFERROR(AVERAGE(C12:D12),"")</f>
+        <v/>
+      </c>
+      <c r="F12" s="21" t="n"/>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
@@ -7849,11 +7875,12 @@
         </is>
       </c>
       <c r="C13" s="21" t="n"/>
-      <c r="D13" s="23">
-        <f>IFERROR(AVERAGE(C13:C13),"")</f>
-        <v/>
-      </c>
-      <c r="E13" s="21" t="n"/>
+      <c r="D13" s="21" t="n"/>
+      <c r="E13" s="23">
+        <f>IFERROR(AVERAGE(C13:D13),"")</f>
+        <v/>
+      </c>
+      <c r="F13" s="21" t="n"/>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
@@ -7867,11 +7894,12 @@
         </is>
       </c>
       <c r="C14" s="21" t="n"/>
-      <c r="D14" s="23">
-        <f>IFERROR(AVERAGE(C14:C14),"")</f>
-        <v/>
-      </c>
-      <c r="E14" s="21" t="n"/>
+      <c r="D14" s="21" t="n"/>
+      <c r="E14" s="23">
+        <f>IFERROR(AVERAGE(C14:D14),"")</f>
+        <v/>
+      </c>
+      <c r="F14" s="21" t="n"/>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
@@ -7885,11 +7913,12 @@
         </is>
       </c>
       <c r="C15" s="28" t="n"/>
-      <c r="D15" s="23">
-        <f>IFERROR(AVERAGE(C15:C15),"")</f>
-        <v/>
-      </c>
-      <c r="E15" s="28" t="n"/>
+      <c r="D15" s="28" t="n"/>
+      <c r="E15" s="23">
+        <f>IFERROR(AVERAGE(C15:D15),"")</f>
+        <v/>
+      </c>
+      <c r="F15" s="28" t="n"/>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
@@ -7903,11 +7932,12 @@
         </is>
       </c>
       <c r="C16" s="28" t="n"/>
-      <c r="D16" s="23">
-        <f>IFERROR(AVERAGE(C16:C16),"")</f>
-        <v/>
-      </c>
-      <c r="E16" s="28" t="n"/>
+      <c r="D16" s="28" t="n"/>
+      <c r="E16" s="23">
+        <f>IFERROR(AVERAGE(C16:D16),"")</f>
+        <v/>
+      </c>
+      <c r="F16" s="28" t="n"/>
     </row>
     <row r="17" ht="17" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
@@ -7921,11 +7951,12 @@
         </is>
       </c>
       <c r="C17" s="28" t="n"/>
-      <c r="D17" s="23">
-        <f>IFERROR(AVERAGE(C17:C17),"")</f>
-        <v/>
-      </c>
-      <c r="E17" s="28" t="n"/>
+      <c r="D17" s="28" t="n"/>
+      <c r="E17" s="23">
+        <f>IFERROR(AVERAGE(C17:D17),"")</f>
+        <v/>
+      </c>
+      <c r="F17" s="28" t="n"/>
     </row>
     <row r="18" ht="17" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
@@ -7939,11 +7970,12 @@
         </is>
       </c>
       <c r="C18" s="28" t="n"/>
-      <c r="D18" s="23">
-        <f>IFERROR(AVERAGE(C18:C18),"")</f>
-        <v/>
-      </c>
-      <c r="E18" s="28" t="n"/>
+      <c r="D18" s="28" t="n"/>
+      <c r="E18" s="23">
+        <f>IFERROR(AVERAGE(C18:D18),"")</f>
+        <v/>
+      </c>
+      <c r="F18" s="28" t="n"/>
     </row>
     <row r="19" ht="17" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
@@ -7957,11 +7989,12 @@
         </is>
       </c>
       <c r="C19" s="28" t="n"/>
-      <c r="D19" s="23">
-        <f>IFERROR(AVERAGE(C19:C19),"")</f>
-        <v/>
-      </c>
-      <c r="E19" s="28" t="n"/>
+      <c r="D19" s="28" t="n"/>
+      <c r="E19" s="23">
+        <f>IFERROR(AVERAGE(C19:D19),"")</f>
+        <v/>
+      </c>
+      <c r="F19" s="28" t="n"/>
     </row>
     <row r="20" ht="17" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
@@ -7975,11 +8008,12 @@
         </is>
       </c>
       <c r="C20" s="28" t="n"/>
-      <c r="D20" s="23">
-        <f>IFERROR(AVERAGE(C20:C20),"")</f>
-        <v/>
-      </c>
-      <c r="E20" s="28" t="n"/>
+      <c r="D20" s="28" t="n"/>
+      <c r="E20" s="23">
+        <f>IFERROR(AVERAGE(C20:D20),"")</f>
+        <v/>
+      </c>
+      <c r="F20" s="28" t="n"/>
     </row>
     <row r="21" ht="17" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
@@ -7993,11 +8027,12 @@
         </is>
       </c>
       <c r="C21" s="28" t="n"/>
-      <c r="D21" s="23">
-        <f>IFERROR(AVERAGE(C21:C21),"")</f>
-        <v/>
-      </c>
-      <c r="E21" s="28" t="n"/>
+      <c r="D21" s="28" t="n"/>
+      <c r="E21" s="23">
+        <f>IFERROR(AVERAGE(C21:D21),"")</f>
+        <v/>
+      </c>
+      <c r="F21" s="28" t="n"/>
     </row>
     <row r="22" ht="17" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
@@ -8011,11 +8046,12 @@
         </is>
       </c>
       <c r="C22" s="28" t="n"/>
-      <c r="D22" s="23">
-        <f>IFERROR(AVERAGE(C22:C22),"")</f>
-        <v/>
-      </c>
-      <c r="E22" s="28" t="n"/>
+      <c r="D22" s="28" t="n"/>
+      <c r="E22" s="23">
+        <f>IFERROR(AVERAGE(C22:D22),"")</f>
+        <v/>
+      </c>
+      <c r="F22" s="28" t="n"/>
     </row>
     <row r="23" ht="17" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
@@ -8029,11 +8065,12 @@
         </is>
       </c>
       <c r="C23" s="28" t="n"/>
-      <c r="D23" s="23">
-        <f>IFERROR(AVERAGE(C23:C23),"")</f>
-        <v/>
-      </c>
-      <c r="E23" s="28" t="n"/>
+      <c r="D23" s="28" t="n"/>
+      <c r="E23" s="23">
+        <f>IFERROR(AVERAGE(C23:D23),"")</f>
+        <v/>
+      </c>
+      <c r="F23" s="28" t="n"/>
     </row>
     <row r="24" ht="17" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
@@ -8047,11 +8084,12 @@
         </is>
       </c>
       <c r="C24" s="28" t="n"/>
-      <c r="D24" s="23">
-        <f>IFERROR(AVERAGE(C24:C24),"")</f>
-        <v/>
-      </c>
-      <c r="E24" s="28" t="n"/>
+      <c r="D24" s="28" t="n"/>
+      <c r="E24" s="23">
+        <f>IFERROR(AVERAGE(C24:D24),"")</f>
+        <v/>
+      </c>
+      <c r="F24" s="28" t="n"/>
     </row>
     <row r="25" ht="17" customHeight="1">
       <c r="A25" s="26" t="inlineStr">
@@ -8065,11 +8103,12 @@
         </is>
       </c>
       <c r="C25" s="28" t="n"/>
-      <c r="D25" s="23">
-        <f>IFERROR(AVERAGE(C25:C25),"")</f>
-        <v/>
-      </c>
-      <c r="E25" s="28" t="n"/>
+      <c r="D25" s="28" t="n"/>
+      <c r="E25" s="23">
+        <f>IFERROR(AVERAGE(C25:D25),"")</f>
+        <v/>
+      </c>
+      <c r="F25" s="28" t="n"/>
     </row>
     <row r="26" ht="17" customHeight="1">
       <c r="A26" s="26" t="inlineStr">
@@ -8083,11 +8122,12 @@
         </is>
       </c>
       <c r="C26" s="28" t="n"/>
-      <c r="D26" s="23">
-        <f>IFERROR(AVERAGE(C26:C26),"")</f>
-        <v/>
-      </c>
-      <c r="E26" s="28" t="n"/>
+      <c r="D26" s="28" t="n"/>
+      <c r="E26" s="23">
+        <f>IFERROR(AVERAGE(C26:D26),"")</f>
+        <v/>
+      </c>
+      <c r="F26" s="28" t="n"/>
     </row>
     <row r="27" ht="17" customHeight="1">
       <c r="A27" s="26" t="inlineStr">
@@ -8101,11 +8141,12 @@
         </is>
       </c>
       <c r="C27" s="28" t="n"/>
-      <c r="D27" s="23">
-        <f>IFERROR(AVERAGE(C27:C27),"")</f>
-        <v/>
-      </c>
-      <c r="E27" s="28" t="n"/>
+      <c r="D27" s="28" t="n"/>
+      <c r="E27" s="23">
+        <f>IFERROR(AVERAGE(C27:D27),"")</f>
+        <v/>
+      </c>
+      <c r="F27" s="28" t="n"/>
     </row>
     <row r="28" ht="17" customHeight="1">
       <c r="A28" s="26" t="inlineStr">
@@ -8119,11 +8160,12 @@
         </is>
       </c>
       <c r="C28" s="28" t="n"/>
-      <c r="D28" s="23">
-        <f>IFERROR(AVERAGE(C28:C28),"")</f>
-        <v/>
-      </c>
-      <c r="E28" s="28" t="n"/>
+      <c r="D28" s="28" t="n"/>
+      <c r="E28" s="23">
+        <f>IFERROR(AVERAGE(C28:D28),"")</f>
+        <v/>
+      </c>
+      <c r="F28" s="28" t="n"/>
     </row>
     <row r="29" ht="17" customHeight="1">
       <c r="A29" s="26" t="inlineStr">
@@ -8137,11 +8179,12 @@
         </is>
       </c>
       <c r="C29" s="28" t="n"/>
-      <c r="D29" s="23">
-        <f>IFERROR(AVERAGE(C29:C29),"")</f>
-        <v/>
-      </c>
-      <c r="E29" s="28" t="n"/>
+      <c r="D29" s="28" t="n"/>
+      <c r="E29" s="23">
+        <f>IFERROR(AVERAGE(C29:D29),"")</f>
+        <v/>
+      </c>
+      <c r="F29" s="28" t="n"/>
     </row>
     <row r="30" ht="17" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
@@ -8155,11 +8198,12 @@
         </is>
       </c>
       <c r="C30" s="28" t="n"/>
-      <c r="D30" s="23">
-        <f>IFERROR(AVERAGE(C30:C30),"")</f>
-        <v/>
-      </c>
-      <c r="E30" s="28" t="n"/>
+      <c r="D30" s="28" t="n"/>
+      <c r="E30" s="23">
+        <f>IFERROR(AVERAGE(C30:D30),"")</f>
+        <v/>
+      </c>
+      <c r="F30" s="28" t="n"/>
     </row>
     <row r="31" ht="17" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
@@ -8173,11 +8217,14 @@
         </is>
       </c>
       <c r="C31" s="28" t="n"/>
-      <c r="D31" s="23">
-        <f>IFERROR(AVERAGE(C31:C31),"")</f>
-        <v/>
-      </c>
-      <c r="E31" s="28" t="n"/>
+      <c r="D31" s="29" t="n">
+        <v>95</v>
+      </c>
+      <c r="E31" s="23">
+        <f>IFERROR(AVERAGE(C31:D31),"")</f>
+        <v/>
+      </c>
+      <c r="F31" s="28" t="n"/>
     </row>
     <row r="32" ht="17" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
@@ -8191,11 +8238,12 @@
         </is>
       </c>
       <c r="C32" s="28" t="n"/>
-      <c r="D32" s="23">
-        <f>IFERROR(AVERAGE(C32:C32),"")</f>
-        <v/>
-      </c>
-      <c r="E32" s="28" t="n"/>
+      <c r="D32" s="28" t="n"/>
+      <c r="E32" s="23">
+        <f>IFERROR(AVERAGE(C32:D32),"")</f>
+        <v/>
+      </c>
+      <c r="F32" s="28" t="n"/>
     </row>
     <row r="33" ht="17" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
@@ -8209,11 +8257,12 @@
         </is>
       </c>
       <c r="C33" s="28" t="n"/>
-      <c r="D33" s="23">
-        <f>IFERROR(AVERAGE(C33:C33),"")</f>
-        <v/>
-      </c>
-      <c r="E33" s="28" t="n"/>
+      <c r="D33" s="28" t="n"/>
+      <c r="E33" s="23">
+        <f>IFERROR(AVERAGE(C33:D33),"")</f>
+        <v/>
+      </c>
+      <c r="F33" s="28" t="n"/>
     </row>
     <row r="34" ht="17" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
@@ -8227,11 +8276,12 @@
         </is>
       </c>
       <c r="C34" s="28" t="n"/>
-      <c r="D34" s="23">
-        <f>IFERROR(AVERAGE(C34:C34),"")</f>
-        <v/>
-      </c>
-      <c r="E34" s="28" t="n"/>
+      <c r="D34" s="28" t="n"/>
+      <c r="E34" s="23">
+        <f>IFERROR(AVERAGE(C34:D34),"")</f>
+        <v/>
+      </c>
+      <c r="F34" s="28" t="n"/>
     </row>
     <row r="35" ht="17" customHeight="1">
       <c r="A35" s="26" t="inlineStr">
@@ -8245,11 +8295,12 @@
         </is>
       </c>
       <c r="C35" s="28" t="n"/>
-      <c r="D35" s="23">
-        <f>IFERROR(AVERAGE(C35:C35),"")</f>
-        <v/>
-      </c>
-      <c r="E35" s="28" t="n"/>
+      <c r="D35" s="28" t="n"/>
+      <c r="E35" s="23">
+        <f>IFERROR(AVERAGE(C35:D35),"")</f>
+        <v/>
+      </c>
+      <c r="F35" s="28" t="n"/>
     </row>
     <row r="36" ht="17" customHeight="1">
       <c r="A36" s="26" t="inlineStr">
@@ -8263,11 +8314,12 @@
         </is>
       </c>
       <c r="C36" s="28" t="n"/>
-      <c r="D36" s="23">
-        <f>IFERROR(AVERAGE(C36:C36),"")</f>
-        <v/>
-      </c>
-      <c r="E36" s="28" t="n"/>
+      <c r="D36" s="28" t="n"/>
+      <c r="E36" s="23">
+        <f>IFERROR(AVERAGE(C36:D36),"")</f>
+        <v/>
+      </c>
+      <c r="F36" s="28" t="n"/>
     </row>
     <row r="37" ht="17" customHeight="1">
       <c r="A37" s="26" t="inlineStr">
@@ -8281,11 +8333,12 @@
         </is>
       </c>
       <c r="C37" s="28" t="n"/>
-      <c r="D37" s="23">
-        <f>IFERROR(AVERAGE(C37:C37),"")</f>
-        <v/>
-      </c>
-      <c r="E37" s="28" t="n"/>
+      <c r="D37" s="28" t="n"/>
+      <c r="E37" s="23">
+        <f>IFERROR(AVERAGE(C37:D37),"")</f>
+        <v/>
+      </c>
+      <c r="F37" s="28" t="n"/>
     </row>
     <row r="38" ht="17" customHeight="1">
       <c r="A38" s="26" t="inlineStr">
@@ -8299,11 +8352,12 @@
         </is>
       </c>
       <c r="C38" s="28" t="n"/>
-      <c r="D38" s="23">
-        <f>IFERROR(AVERAGE(C38:C38),"")</f>
-        <v/>
-      </c>
-      <c r="E38" s="28" t="n"/>
+      <c r="D38" s="28" t="n"/>
+      <c r="E38" s="23">
+        <f>IFERROR(AVERAGE(C38:D38),"")</f>
+        <v/>
+      </c>
+      <c r="F38" s="28" t="n"/>
     </row>
     <row r="39" ht="12" customHeight="1">
       <c r="A39" s="31" t="inlineStr">
@@ -8314,9 +8368,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A39:E39"/>
-    <mergeCell ref="A1:E1"/>
     <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Shop_Tracker_2065_2026.xlsx
+++ b/Shop_Tracker_2065_2026.xlsx
@@ -7667,15 +7667,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -7700,10 +7701,15 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
+          <t>WEEK 3</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
           <t>MTD SCORE</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>MTD DOLLARS</t>
         </is>
@@ -7726,8 +7732,13 @@
           <t>08/08</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr"/>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>08/15</t>
+        </is>
+      </c>
       <c r="F3" s="4" t="inlineStr"/>
+      <c r="G3" s="4" t="inlineStr"/>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="4" t="inlineStr"/>
@@ -7746,8 +7757,13 @@
           <t>Lunch</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr"/>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
       <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="9" t="inlineStr"/>
@@ -7762,8 +7778,11 @@
       <c r="D5" s="11" t="n">
         <v>95</v>
       </c>
-      <c r="E5" s="9" t="inlineStr"/>
+      <c r="E5" s="11" t="n">
+        <v>95</v>
+      </c>
       <c r="F5" s="9" t="inlineStr"/>
+      <c r="G5" s="9" t="inlineStr"/>
     </row>
     <row r="6" ht="14" customHeight="1">
       <c r="A6" s="15" t="inlineStr"/>
@@ -7776,6 +7795,7 @@
       <c r="D6" s="17" t="n"/>
       <c r="E6" s="17" t="n"/>
       <c r="F6" s="17" t="n"/>
+      <c r="G6" s="17" t="n"/>
     </row>
     <row r="7" ht="14" customHeight="1">
       <c r="A7" s="15" t="inlineStr"/>
@@ -7788,6 +7808,7 @@
       <c r="D7" s="17" t="n"/>
       <c r="E7" s="17" t="n"/>
       <c r="F7" s="17" t="n"/>
+      <c r="G7" s="17" t="n"/>
     </row>
     <row r="8" ht="14" customHeight="1">
       <c r="A8" s="15" t="inlineStr"/>
@@ -7800,6 +7821,7 @@
       <c r="D8" s="17" t="n"/>
       <c r="E8" s="17" t="n"/>
       <c r="F8" s="17" t="n"/>
+      <c r="G8" s="17" t="n"/>
     </row>
     <row r="9" ht="14" customHeight="1">
       <c r="A9" s="15" t="inlineStr"/>
@@ -7812,6 +7834,7 @@
       <c r="D9" s="17" t="n"/>
       <c r="E9" s="17" t="n"/>
       <c r="F9" s="17" t="n"/>
+      <c r="G9" s="17" t="n"/>
     </row>
     <row r="10" ht="14" customHeight="1">
       <c r="A10" s="15" t="inlineStr"/>
@@ -7824,6 +7847,7 @@
       <c r="D10" s="17" t="n"/>
       <c r="E10" s="17" t="n"/>
       <c r="F10" s="17" t="n"/>
+      <c r="G10" s="17" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="18" t="inlineStr">
@@ -7833,12 +7857,13 @@
       </c>
       <c r="C11" s="2" t="inlineStr"/>
       <c r="D11" s="2" t="inlineStr"/>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>MTD SCORE</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>MTD DOLLARS</t>
         </is>
@@ -7857,11 +7882,12 @@
       </c>
       <c r="C12" s="21" t="n"/>
       <c r="D12" s="21" t="n"/>
-      <c r="E12" s="23">
-        <f>IFERROR(AVERAGE(C12:D12),"")</f>
-        <v/>
-      </c>
-      <c r="F12" s="21" t="n"/>
+      <c r="E12" s="21" t="n"/>
+      <c r="F12" s="23">
+        <f>IFERROR(AVERAGE(C12:E12),"")</f>
+        <v/>
+      </c>
+      <c r="G12" s="21" t="n"/>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
@@ -7876,11 +7902,12 @@
       </c>
       <c r="C13" s="21" t="n"/>
       <c r="D13" s="21" t="n"/>
-      <c r="E13" s="23">
-        <f>IFERROR(AVERAGE(C13:D13),"")</f>
-        <v/>
-      </c>
-      <c r="F13" s="21" t="n"/>
+      <c r="E13" s="21" t="n"/>
+      <c r="F13" s="23">
+        <f>IFERROR(AVERAGE(C13:E13),"")</f>
+        <v/>
+      </c>
+      <c r="G13" s="21" t="n"/>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
@@ -7895,11 +7922,12 @@
       </c>
       <c r="C14" s="21" t="n"/>
       <c r="D14" s="21" t="n"/>
-      <c r="E14" s="23">
-        <f>IFERROR(AVERAGE(C14:D14),"")</f>
-        <v/>
-      </c>
-      <c r="F14" s="21" t="n"/>
+      <c r="E14" s="21" t="n"/>
+      <c r="F14" s="23">
+        <f>IFERROR(AVERAGE(C14:E14),"")</f>
+        <v/>
+      </c>
+      <c r="G14" s="21" t="n"/>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
@@ -7914,11 +7942,12 @@
       </c>
       <c r="C15" s="28" t="n"/>
       <c r="D15" s="28" t="n"/>
-      <c r="E15" s="23">
-        <f>IFERROR(AVERAGE(C15:D15),"")</f>
-        <v/>
-      </c>
-      <c r="F15" s="28" t="n"/>
+      <c r="E15" s="28" t="n"/>
+      <c r="F15" s="23">
+        <f>IFERROR(AVERAGE(C15:E15),"")</f>
+        <v/>
+      </c>
+      <c r="G15" s="28" t="n"/>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
@@ -7933,11 +7962,12 @@
       </c>
       <c r="C16" s="28" t="n"/>
       <c r="D16" s="28" t="n"/>
-      <c r="E16" s="23">
-        <f>IFERROR(AVERAGE(C16:D16),"")</f>
-        <v/>
-      </c>
-      <c r="F16" s="28" t="n"/>
+      <c r="E16" s="28" t="n"/>
+      <c r="F16" s="23">
+        <f>IFERROR(AVERAGE(C16:E16),"")</f>
+        <v/>
+      </c>
+      <c r="G16" s="28" t="n"/>
     </row>
     <row r="17" ht="17" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
@@ -7952,11 +7982,12 @@
       </c>
       <c r="C17" s="28" t="n"/>
       <c r="D17" s="28" t="n"/>
-      <c r="E17" s="23">
-        <f>IFERROR(AVERAGE(C17:D17),"")</f>
-        <v/>
-      </c>
-      <c r="F17" s="28" t="n"/>
+      <c r="E17" s="28" t="n"/>
+      <c r="F17" s="23">
+        <f>IFERROR(AVERAGE(C17:E17),"")</f>
+        <v/>
+      </c>
+      <c r="G17" s="28" t="n"/>
     </row>
     <row r="18" ht="17" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
@@ -7971,11 +8002,12 @@
       </c>
       <c r="C18" s="28" t="n"/>
       <c r="D18" s="28" t="n"/>
-      <c r="E18" s="23">
-        <f>IFERROR(AVERAGE(C18:D18),"")</f>
-        <v/>
-      </c>
-      <c r="F18" s="28" t="n"/>
+      <c r="E18" s="28" t="n"/>
+      <c r="F18" s="23">
+        <f>IFERROR(AVERAGE(C18:E18),"")</f>
+        <v/>
+      </c>
+      <c r="G18" s="28" t="n"/>
     </row>
     <row r="19" ht="17" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
@@ -7990,11 +8022,12 @@
       </c>
       <c r="C19" s="28" t="n"/>
       <c r="D19" s="28" t="n"/>
-      <c r="E19" s="23">
-        <f>IFERROR(AVERAGE(C19:D19),"")</f>
-        <v/>
-      </c>
-      <c r="F19" s="28" t="n"/>
+      <c r="E19" s="28" t="n"/>
+      <c r="F19" s="23">
+        <f>IFERROR(AVERAGE(C19:E19),"")</f>
+        <v/>
+      </c>
+      <c r="G19" s="28" t="n"/>
     </row>
     <row r="20" ht="17" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
@@ -8009,11 +8042,12 @@
       </c>
       <c r="C20" s="28" t="n"/>
       <c r="D20" s="28" t="n"/>
-      <c r="E20" s="23">
-        <f>IFERROR(AVERAGE(C20:D20),"")</f>
-        <v/>
-      </c>
-      <c r="F20" s="28" t="n"/>
+      <c r="E20" s="28" t="n"/>
+      <c r="F20" s="23">
+        <f>IFERROR(AVERAGE(C20:E20),"")</f>
+        <v/>
+      </c>
+      <c r="G20" s="28" t="n"/>
     </row>
     <row r="21" ht="17" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
@@ -8028,11 +8062,12 @@
       </c>
       <c r="C21" s="28" t="n"/>
       <c r="D21" s="28" t="n"/>
-      <c r="E21" s="23">
-        <f>IFERROR(AVERAGE(C21:D21),"")</f>
-        <v/>
-      </c>
-      <c r="F21" s="28" t="n"/>
+      <c r="E21" s="28" t="n"/>
+      <c r="F21" s="23">
+        <f>IFERROR(AVERAGE(C21:E21),"")</f>
+        <v/>
+      </c>
+      <c r="G21" s="28" t="n"/>
     </row>
     <row r="22" ht="17" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
@@ -8047,11 +8082,12 @@
       </c>
       <c r="C22" s="28" t="n"/>
       <c r="D22" s="28" t="n"/>
-      <c r="E22" s="23">
-        <f>IFERROR(AVERAGE(C22:D22),"")</f>
-        <v/>
-      </c>
-      <c r="F22" s="28" t="n"/>
+      <c r="E22" s="28" t="n"/>
+      <c r="F22" s="23">
+        <f>IFERROR(AVERAGE(C22:E22),"")</f>
+        <v/>
+      </c>
+      <c r="G22" s="28" t="n"/>
     </row>
     <row r="23" ht="17" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
@@ -8066,11 +8102,12 @@
       </c>
       <c r="C23" s="28" t="n"/>
       <c r="D23" s="28" t="n"/>
-      <c r="E23" s="23">
-        <f>IFERROR(AVERAGE(C23:D23),"")</f>
-        <v/>
-      </c>
-      <c r="F23" s="28" t="n"/>
+      <c r="E23" s="28" t="n"/>
+      <c r="F23" s="23">
+        <f>IFERROR(AVERAGE(C23:E23),"")</f>
+        <v/>
+      </c>
+      <c r="G23" s="28" t="n"/>
     </row>
     <row r="24" ht="17" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
@@ -8085,11 +8122,12 @@
       </c>
       <c r="C24" s="28" t="n"/>
       <c r="D24" s="28" t="n"/>
-      <c r="E24" s="23">
-        <f>IFERROR(AVERAGE(C24:D24),"")</f>
-        <v/>
-      </c>
-      <c r="F24" s="28" t="n"/>
+      <c r="E24" s="28" t="n"/>
+      <c r="F24" s="23">
+        <f>IFERROR(AVERAGE(C24:E24),"")</f>
+        <v/>
+      </c>
+      <c r="G24" s="28" t="n"/>
     </row>
     <row r="25" ht="17" customHeight="1">
       <c r="A25" s="26" t="inlineStr">
@@ -8104,11 +8142,12 @@
       </c>
       <c r="C25" s="28" t="n"/>
       <c r="D25" s="28" t="n"/>
-      <c r="E25" s="23">
-        <f>IFERROR(AVERAGE(C25:D25),"")</f>
-        <v/>
-      </c>
-      <c r="F25" s="28" t="n"/>
+      <c r="E25" s="28" t="n"/>
+      <c r="F25" s="23">
+        <f>IFERROR(AVERAGE(C25:E25),"")</f>
+        <v/>
+      </c>
+      <c r="G25" s="28" t="n"/>
     </row>
     <row r="26" ht="17" customHeight="1">
       <c r="A26" s="26" t="inlineStr">
@@ -8123,11 +8162,12 @@
       </c>
       <c r="C26" s="28" t="n"/>
       <c r="D26" s="28" t="n"/>
-      <c r="E26" s="23">
-        <f>IFERROR(AVERAGE(C26:D26),"")</f>
-        <v/>
-      </c>
-      <c r="F26" s="28" t="n"/>
+      <c r="E26" s="28" t="n"/>
+      <c r="F26" s="23">
+        <f>IFERROR(AVERAGE(C26:E26),"")</f>
+        <v/>
+      </c>
+      <c r="G26" s="28" t="n"/>
     </row>
     <row r="27" ht="17" customHeight="1">
       <c r="A27" s="26" t="inlineStr">
@@ -8142,11 +8182,12 @@
       </c>
       <c r="C27" s="28" t="n"/>
       <c r="D27" s="28" t="n"/>
-      <c r="E27" s="23">
-        <f>IFERROR(AVERAGE(C27:D27),"")</f>
-        <v/>
-      </c>
-      <c r="F27" s="28" t="n"/>
+      <c r="E27" s="28" t="n"/>
+      <c r="F27" s="23">
+        <f>IFERROR(AVERAGE(C27:E27),"")</f>
+        <v/>
+      </c>
+      <c r="G27" s="28" t="n"/>
     </row>
     <row r="28" ht="17" customHeight="1">
       <c r="A28" s="26" t="inlineStr">
@@ -8161,11 +8202,12 @@
       </c>
       <c r="C28" s="28" t="n"/>
       <c r="D28" s="28" t="n"/>
-      <c r="E28" s="23">
-        <f>IFERROR(AVERAGE(C28:D28),"")</f>
-        <v/>
-      </c>
-      <c r="F28" s="28" t="n"/>
+      <c r="E28" s="28" t="n"/>
+      <c r="F28" s="23">
+        <f>IFERROR(AVERAGE(C28:E28),"")</f>
+        <v/>
+      </c>
+      <c r="G28" s="28" t="n"/>
     </row>
     <row r="29" ht="17" customHeight="1">
       <c r="A29" s="26" t="inlineStr">
@@ -8180,11 +8222,12 @@
       </c>
       <c r="C29" s="28" t="n"/>
       <c r="D29" s="28" t="n"/>
-      <c r="E29" s="23">
-        <f>IFERROR(AVERAGE(C29:D29),"")</f>
-        <v/>
-      </c>
-      <c r="F29" s="28" t="n"/>
+      <c r="E29" s="28" t="n"/>
+      <c r="F29" s="23">
+        <f>IFERROR(AVERAGE(C29:E29),"")</f>
+        <v/>
+      </c>
+      <c r="G29" s="28" t="n"/>
     </row>
     <row r="30" ht="17" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
@@ -8199,11 +8242,12 @@
       </c>
       <c r="C30" s="28" t="n"/>
       <c r="D30" s="28" t="n"/>
-      <c r="E30" s="23">
-        <f>IFERROR(AVERAGE(C30:D30),"")</f>
-        <v/>
-      </c>
-      <c r="F30" s="28" t="n"/>
+      <c r="E30" s="28" t="n"/>
+      <c r="F30" s="23">
+        <f>IFERROR(AVERAGE(C30:E30),"")</f>
+        <v/>
+      </c>
+      <c r="G30" s="28" t="n"/>
     </row>
     <row r="31" ht="17" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
@@ -8220,11 +8264,12 @@
       <c r="D31" s="29" t="n">
         <v>95</v>
       </c>
-      <c r="E31" s="23">
-        <f>IFERROR(AVERAGE(C31:D31),"")</f>
-        <v/>
-      </c>
-      <c r="F31" s="28" t="n"/>
+      <c r="E31" s="28" t="n"/>
+      <c r="F31" s="23">
+        <f>IFERROR(AVERAGE(C31:E31),"")</f>
+        <v/>
+      </c>
+      <c r="G31" s="28" t="n"/>
     </row>
     <row r="32" ht="17" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
@@ -8239,11 +8284,12 @@
       </c>
       <c r="C32" s="28" t="n"/>
       <c r="D32" s="28" t="n"/>
-      <c r="E32" s="23">
-        <f>IFERROR(AVERAGE(C32:D32),"")</f>
-        <v/>
-      </c>
-      <c r="F32" s="28" t="n"/>
+      <c r="E32" s="28" t="n"/>
+      <c r="F32" s="23">
+        <f>IFERROR(AVERAGE(C32:E32),"")</f>
+        <v/>
+      </c>
+      <c r="G32" s="28" t="n"/>
     </row>
     <row r="33" ht="17" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
@@ -8258,11 +8304,12 @@
       </c>
       <c r="C33" s="28" t="n"/>
       <c r="D33" s="28" t="n"/>
-      <c r="E33" s="23">
-        <f>IFERROR(AVERAGE(C33:D33),"")</f>
-        <v/>
-      </c>
-      <c r="F33" s="28" t="n"/>
+      <c r="E33" s="28" t="n"/>
+      <c r="F33" s="23">
+        <f>IFERROR(AVERAGE(C33:E33),"")</f>
+        <v/>
+      </c>
+      <c r="G33" s="28" t="n"/>
     </row>
     <row r="34" ht="17" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
@@ -8277,11 +8324,12 @@
       </c>
       <c r="C34" s="28" t="n"/>
       <c r="D34" s="28" t="n"/>
-      <c r="E34" s="23">
-        <f>IFERROR(AVERAGE(C34:D34),"")</f>
-        <v/>
-      </c>
-      <c r="F34" s="28" t="n"/>
+      <c r="E34" s="28" t="n"/>
+      <c r="F34" s="23">
+        <f>IFERROR(AVERAGE(C34:E34),"")</f>
+        <v/>
+      </c>
+      <c r="G34" s="28" t="n"/>
     </row>
     <row r="35" ht="17" customHeight="1">
       <c r="A35" s="26" t="inlineStr">
@@ -8296,11 +8344,12 @@
       </c>
       <c r="C35" s="28" t="n"/>
       <c r="D35" s="28" t="n"/>
-      <c r="E35" s="23">
-        <f>IFERROR(AVERAGE(C35:D35),"")</f>
-        <v/>
-      </c>
-      <c r="F35" s="28" t="n"/>
+      <c r="E35" s="28" t="n"/>
+      <c r="F35" s="23">
+        <f>IFERROR(AVERAGE(C35:E35),"")</f>
+        <v/>
+      </c>
+      <c r="G35" s="28" t="n"/>
     </row>
     <row r="36" ht="17" customHeight="1">
       <c r="A36" s="26" t="inlineStr">
@@ -8315,11 +8364,12 @@
       </c>
       <c r="C36" s="28" t="n"/>
       <c r="D36" s="28" t="n"/>
-      <c r="E36" s="23">
-        <f>IFERROR(AVERAGE(C36:D36),"")</f>
-        <v/>
-      </c>
-      <c r="F36" s="28" t="n"/>
+      <c r="E36" s="28" t="n"/>
+      <c r="F36" s="23">
+        <f>IFERROR(AVERAGE(C36:E36),"")</f>
+        <v/>
+      </c>
+      <c r="G36" s="28" t="n"/>
     </row>
     <row r="37" ht="17" customHeight="1">
       <c r="A37" s="26" t="inlineStr">
@@ -8334,11 +8384,12 @@
       </c>
       <c r="C37" s="28" t="n"/>
       <c r="D37" s="28" t="n"/>
-      <c r="E37" s="23">
-        <f>IFERROR(AVERAGE(C37:D37),"")</f>
-        <v/>
-      </c>
-      <c r="F37" s="28" t="n"/>
+      <c r="E37" s="28" t="n"/>
+      <c r="F37" s="23">
+        <f>IFERROR(AVERAGE(C37:E37),"")</f>
+        <v/>
+      </c>
+      <c r="G37" s="28" t="n"/>
     </row>
     <row r="38" ht="17" customHeight="1">
       <c r="A38" s="26" t="inlineStr">
@@ -8353,11 +8404,12 @@
       </c>
       <c r="C38" s="28" t="n"/>
       <c r="D38" s="28" t="n"/>
-      <c r="E38" s="23">
-        <f>IFERROR(AVERAGE(C38:D38),"")</f>
-        <v/>
-      </c>
-      <c r="F38" s="28" t="n"/>
+      <c r="E38" s="28" t="n"/>
+      <c r="F38" s="23">
+        <f>IFERROR(AVERAGE(C38:E38),"")</f>
+        <v/>
+      </c>
+      <c r="G38" s="28" t="n"/>
     </row>
     <row r="39" ht="12" customHeight="1">
       <c r="A39" s="31" t="inlineStr">
@@ -8369,8 +8421,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A39:F39"/>
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A39:G39"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Shop_Tracker_2065_2026.xlsx
+++ b/Shop_Tracker_2065_2026.xlsx
@@ -7667,7 +7667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -7675,8 +7675,9 @@
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -7706,10 +7707,15 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
+          <t>WEEK 4</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
           <t>MTD SCORE</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>MTD DOLLARS</t>
         </is>
@@ -7737,8 +7743,13 @@
           <t>08/15</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr"/>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>08/21</t>
+        </is>
+      </c>
       <c r="G3" s="4" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr"/>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="4" t="inlineStr"/>
@@ -7762,8 +7773,13 @@
           <t>Dinner</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr"/>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>Lunch</t>
+        </is>
+      </c>
       <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="9" t="inlineStr"/>
@@ -7781,8 +7797,11 @@
       <c r="E5" s="11" t="n">
         <v>95</v>
       </c>
-      <c r="F5" s="9" t="inlineStr"/>
+      <c r="F5" s="14" t="n">
+        <v>100</v>
+      </c>
       <c r="G5" s="9" t="inlineStr"/>
+      <c r="H5" s="9" t="inlineStr"/>
     </row>
     <row r="6" ht="14" customHeight="1">
       <c r="A6" s="15" t="inlineStr"/>
@@ -7796,6 +7815,7 @@
       <c r="E6" s="17" t="n"/>
       <c r="F6" s="17" t="n"/>
       <c r="G6" s="17" t="n"/>
+      <c r="H6" s="17" t="n"/>
     </row>
     <row r="7" ht="14" customHeight="1">
       <c r="A7" s="15" t="inlineStr"/>
@@ -7809,6 +7829,7 @@
       <c r="E7" s="17" t="n"/>
       <c r="F7" s="17" t="n"/>
       <c r="G7" s="17" t="n"/>
+      <c r="H7" s="17" t="n"/>
     </row>
     <row r="8" ht="14" customHeight="1">
       <c r="A8" s="15" t="inlineStr"/>
@@ -7822,6 +7843,7 @@
       <c r="E8" s="17" t="n"/>
       <c r="F8" s="17" t="n"/>
       <c r="G8" s="17" t="n"/>
+      <c r="H8" s="17" t="n"/>
     </row>
     <row r="9" ht="14" customHeight="1">
       <c r="A9" s="15" t="inlineStr"/>
@@ -7835,6 +7857,7 @@
       <c r="E9" s="17" t="n"/>
       <c r="F9" s="17" t="n"/>
       <c r="G9" s="17" t="n"/>
+      <c r="H9" s="17" t="n"/>
     </row>
     <row r="10" ht="14" customHeight="1">
       <c r="A10" s="15" t="inlineStr"/>
@@ -7848,6 +7871,7 @@
       <c r="E10" s="17" t="n"/>
       <c r="F10" s="17" t="n"/>
       <c r="G10" s="17" t="n"/>
+      <c r="H10" s="17" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="18" t="inlineStr">
@@ -7858,12 +7882,13 @@
       <c r="C11" s="2" t="inlineStr"/>
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>MTD SCORE</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>MTD DOLLARS</t>
         </is>
@@ -7883,11 +7908,16 @@
       <c r="C12" s="21" t="n"/>
       <c r="D12" s="21" t="n"/>
       <c r="E12" s="21" t="n"/>
-      <c r="F12" s="23">
-        <f>IFERROR(AVERAGE(C12:E12),"")</f>
-        <v/>
-      </c>
-      <c r="G12" s="21" t="n"/>
+      <c r="F12" s="22" t="n">
+        <v>100</v>
+      </c>
+      <c r="G12" s="23">
+        <f>IFERROR(AVERAGE(C12:F12),"")</f>
+        <v/>
+      </c>
+      <c r="H12" s="24" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
@@ -7903,11 +7933,12 @@
       <c r="C13" s="21" t="n"/>
       <c r="D13" s="21" t="n"/>
       <c r="E13" s="21" t="n"/>
-      <c r="F13" s="23">
-        <f>IFERROR(AVERAGE(C13:E13),"")</f>
-        <v/>
-      </c>
-      <c r="G13" s="21" t="n"/>
+      <c r="F13" s="21" t="n"/>
+      <c r="G13" s="23">
+        <f>IFERROR(AVERAGE(C13:F13),"")</f>
+        <v/>
+      </c>
+      <c r="H13" s="21" t="n"/>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
@@ -7923,11 +7954,12 @@
       <c r="C14" s="21" t="n"/>
       <c r="D14" s="21" t="n"/>
       <c r="E14" s="21" t="n"/>
-      <c r="F14" s="23">
-        <f>IFERROR(AVERAGE(C14:E14),"")</f>
-        <v/>
-      </c>
-      <c r="G14" s="21" t="n"/>
+      <c r="F14" s="21" t="n"/>
+      <c r="G14" s="23">
+        <f>IFERROR(AVERAGE(C14:F14),"")</f>
+        <v/>
+      </c>
+      <c r="H14" s="21" t="n"/>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
@@ -7943,11 +7975,12 @@
       <c r="C15" s="28" t="n"/>
       <c r="D15" s="28" t="n"/>
       <c r="E15" s="28" t="n"/>
-      <c r="F15" s="23">
-        <f>IFERROR(AVERAGE(C15:E15),"")</f>
-        <v/>
-      </c>
-      <c r="G15" s="28" t="n"/>
+      <c r="F15" s="28" t="n"/>
+      <c r="G15" s="23">
+        <f>IFERROR(AVERAGE(C15:F15),"")</f>
+        <v/>
+      </c>
+      <c r="H15" s="28" t="n"/>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
@@ -7963,11 +7996,12 @@
       <c r="C16" s="28" t="n"/>
       <c r="D16" s="28" t="n"/>
       <c r="E16" s="28" t="n"/>
-      <c r="F16" s="23">
-        <f>IFERROR(AVERAGE(C16:E16),"")</f>
-        <v/>
-      </c>
-      <c r="G16" s="28" t="n"/>
+      <c r="F16" s="28" t="n"/>
+      <c r="G16" s="23">
+        <f>IFERROR(AVERAGE(C16:F16),"")</f>
+        <v/>
+      </c>
+      <c r="H16" s="28" t="n"/>
     </row>
     <row r="17" ht="17" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
@@ -7983,11 +8017,12 @@
       <c r="C17" s="28" t="n"/>
       <c r="D17" s="28" t="n"/>
       <c r="E17" s="28" t="n"/>
-      <c r="F17" s="23">
-        <f>IFERROR(AVERAGE(C17:E17),"")</f>
-        <v/>
-      </c>
-      <c r="G17" s="28" t="n"/>
+      <c r="F17" s="28" t="n"/>
+      <c r="G17" s="23">
+        <f>IFERROR(AVERAGE(C17:F17),"")</f>
+        <v/>
+      </c>
+      <c r="H17" s="28" t="n"/>
     </row>
     <row r="18" ht="17" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
@@ -8003,11 +8038,12 @@
       <c r="C18" s="28" t="n"/>
       <c r="D18" s="28" t="n"/>
       <c r="E18" s="28" t="n"/>
-      <c r="F18" s="23">
-        <f>IFERROR(AVERAGE(C18:E18),"")</f>
-        <v/>
-      </c>
-      <c r="G18" s="28" t="n"/>
+      <c r="F18" s="28" t="n"/>
+      <c r="G18" s="23">
+        <f>IFERROR(AVERAGE(C18:F18),"")</f>
+        <v/>
+      </c>
+      <c r="H18" s="28" t="n"/>
     </row>
     <row r="19" ht="17" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
@@ -8023,11 +8059,12 @@
       <c r="C19" s="28" t="n"/>
       <c r="D19" s="28" t="n"/>
       <c r="E19" s="28" t="n"/>
-      <c r="F19" s="23">
-        <f>IFERROR(AVERAGE(C19:E19),"")</f>
-        <v/>
-      </c>
-      <c r="G19" s="28" t="n"/>
+      <c r="F19" s="28" t="n"/>
+      <c r="G19" s="23">
+        <f>IFERROR(AVERAGE(C19:F19),"")</f>
+        <v/>
+      </c>
+      <c r="H19" s="28" t="n"/>
     </row>
     <row r="20" ht="17" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
@@ -8043,11 +8080,12 @@
       <c r="C20" s="28" t="n"/>
       <c r="D20" s="28" t="n"/>
       <c r="E20" s="28" t="n"/>
-      <c r="F20" s="23">
-        <f>IFERROR(AVERAGE(C20:E20),"")</f>
-        <v/>
-      </c>
-      <c r="G20" s="28" t="n"/>
+      <c r="F20" s="28" t="n"/>
+      <c r="G20" s="23">
+        <f>IFERROR(AVERAGE(C20:F20),"")</f>
+        <v/>
+      </c>
+      <c r="H20" s="28" t="n"/>
     </row>
     <row r="21" ht="17" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
@@ -8063,11 +8101,12 @@
       <c r="C21" s="28" t="n"/>
       <c r="D21" s="28" t="n"/>
       <c r="E21" s="28" t="n"/>
-      <c r="F21" s="23">
-        <f>IFERROR(AVERAGE(C21:E21),"")</f>
-        <v/>
-      </c>
-      <c r="G21" s="28" t="n"/>
+      <c r="F21" s="28" t="n"/>
+      <c r="G21" s="23">
+        <f>IFERROR(AVERAGE(C21:F21),"")</f>
+        <v/>
+      </c>
+      <c r="H21" s="28" t="n"/>
     </row>
     <row r="22" ht="17" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
@@ -8083,11 +8122,12 @@
       <c r="C22" s="28" t="n"/>
       <c r="D22" s="28" t="n"/>
       <c r="E22" s="28" t="n"/>
-      <c r="F22" s="23">
-        <f>IFERROR(AVERAGE(C22:E22),"")</f>
-        <v/>
-      </c>
-      <c r="G22" s="28" t="n"/>
+      <c r="F22" s="28" t="n"/>
+      <c r="G22" s="23">
+        <f>IFERROR(AVERAGE(C22:F22),"")</f>
+        <v/>
+      </c>
+      <c r="H22" s="28" t="n"/>
     </row>
     <row r="23" ht="17" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
@@ -8103,11 +8143,16 @@
       <c r="C23" s="28" t="n"/>
       <c r="D23" s="28" t="n"/>
       <c r="E23" s="28" t="n"/>
-      <c r="F23" s="23">
-        <f>IFERROR(AVERAGE(C23:E23),"")</f>
-        <v/>
-      </c>
-      <c r="G23" s="28" t="n"/>
+      <c r="F23" s="22" t="n">
+        <v>100</v>
+      </c>
+      <c r="G23" s="23">
+        <f>IFERROR(AVERAGE(C23:F23),"")</f>
+        <v/>
+      </c>
+      <c r="H23" s="24" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="24" ht="17" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
@@ -8123,11 +8168,12 @@
       <c r="C24" s="28" t="n"/>
       <c r="D24" s="28" t="n"/>
       <c r="E24" s="28" t="n"/>
-      <c r="F24" s="23">
-        <f>IFERROR(AVERAGE(C24:E24),"")</f>
-        <v/>
-      </c>
-      <c r="G24" s="28" t="n"/>
+      <c r="F24" s="28" t="n"/>
+      <c r="G24" s="23">
+        <f>IFERROR(AVERAGE(C24:F24),"")</f>
+        <v/>
+      </c>
+      <c r="H24" s="28" t="n"/>
     </row>
     <row r="25" ht="17" customHeight="1">
       <c r="A25" s="26" t="inlineStr">
@@ -8143,11 +8189,12 @@
       <c r="C25" s="28" t="n"/>
       <c r="D25" s="28" t="n"/>
       <c r="E25" s="28" t="n"/>
-      <c r="F25" s="23">
-        <f>IFERROR(AVERAGE(C25:E25),"")</f>
-        <v/>
-      </c>
-      <c r="G25" s="28" t="n"/>
+      <c r="F25" s="28" t="n"/>
+      <c r="G25" s="23">
+        <f>IFERROR(AVERAGE(C25:F25),"")</f>
+        <v/>
+      </c>
+      <c r="H25" s="28" t="n"/>
     </row>
     <row r="26" ht="17" customHeight="1">
       <c r="A26" s="26" t="inlineStr">
@@ -8163,11 +8210,12 @@
       <c r="C26" s="28" t="n"/>
       <c r="D26" s="28" t="n"/>
       <c r="E26" s="28" t="n"/>
-      <c r="F26" s="23">
-        <f>IFERROR(AVERAGE(C26:E26),"")</f>
-        <v/>
-      </c>
-      <c r="G26" s="28" t="n"/>
+      <c r="F26" s="28" t="n"/>
+      <c r="G26" s="23">
+        <f>IFERROR(AVERAGE(C26:F26),"")</f>
+        <v/>
+      </c>
+      <c r="H26" s="28" t="n"/>
     </row>
     <row r="27" ht="17" customHeight="1">
       <c r="A27" s="26" t="inlineStr">
@@ -8183,11 +8231,12 @@
       <c r="C27" s="28" t="n"/>
       <c r="D27" s="28" t="n"/>
       <c r="E27" s="28" t="n"/>
-      <c r="F27" s="23">
-        <f>IFERROR(AVERAGE(C27:E27),"")</f>
-        <v/>
-      </c>
-      <c r="G27" s="28" t="n"/>
+      <c r="F27" s="28" t="n"/>
+      <c r="G27" s="23">
+        <f>IFERROR(AVERAGE(C27:F27),"")</f>
+        <v/>
+      </c>
+      <c r="H27" s="28" t="n"/>
     </row>
     <row r="28" ht="17" customHeight="1">
       <c r="A28" s="26" t="inlineStr">
@@ -8203,11 +8252,12 @@
       <c r="C28" s="28" t="n"/>
       <c r="D28" s="28" t="n"/>
       <c r="E28" s="28" t="n"/>
-      <c r="F28" s="23">
-        <f>IFERROR(AVERAGE(C28:E28),"")</f>
-        <v/>
-      </c>
-      <c r="G28" s="28" t="n"/>
+      <c r="F28" s="28" t="n"/>
+      <c r="G28" s="23">
+        <f>IFERROR(AVERAGE(C28:F28),"")</f>
+        <v/>
+      </c>
+      <c r="H28" s="28" t="n"/>
     </row>
     <row r="29" ht="17" customHeight="1">
       <c r="A29" s="26" t="inlineStr">
@@ -8223,11 +8273,12 @@
       <c r="C29" s="28" t="n"/>
       <c r="D29" s="28" t="n"/>
       <c r="E29" s="28" t="n"/>
-      <c r="F29" s="23">
-        <f>IFERROR(AVERAGE(C29:E29),"")</f>
-        <v/>
-      </c>
-      <c r="G29" s="28" t="n"/>
+      <c r="F29" s="28" t="n"/>
+      <c r="G29" s="23">
+        <f>IFERROR(AVERAGE(C29:F29),"")</f>
+        <v/>
+      </c>
+      <c r="H29" s="28" t="n"/>
     </row>
     <row r="30" ht="17" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
@@ -8243,11 +8294,12 @@
       <c r="C30" s="28" t="n"/>
       <c r="D30" s="28" t="n"/>
       <c r="E30" s="28" t="n"/>
-      <c r="F30" s="23">
-        <f>IFERROR(AVERAGE(C30:E30),"")</f>
-        <v/>
-      </c>
-      <c r="G30" s="28" t="n"/>
+      <c r="F30" s="28" t="n"/>
+      <c r="G30" s="23">
+        <f>IFERROR(AVERAGE(C30:F30),"")</f>
+        <v/>
+      </c>
+      <c r="H30" s="28" t="n"/>
     </row>
     <row r="31" ht="17" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
@@ -8265,11 +8317,16 @@
         <v>95</v>
       </c>
       <c r="E31" s="28" t="n"/>
-      <c r="F31" s="23">
-        <f>IFERROR(AVERAGE(C31:E31),"")</f>
-        <v/>
-      </c>
-      <c r="G31" s="28" t="n"/>
+      <c r="F31" s="22" t="n">
+        <v>100</v>
+      </c>
+      <c r="G31" s="23">
+        <f>IFERROR(AVERAGE(C31:F31),"")</f>
+        <v/>
+      </c>
+      <c r="H31" s="24" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="32" ht="17" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
@@ -8285,11 +8342,12 @@
       <c r="C32" s="28" t="n"/>
       <c r="D32" s="28" t="n"/>
       <c r="E32" s="28" t="n"/>
-      <c r="F32" s="23">
-        <f>IFERROR(AVERAGE(C32:E32),"")</f>
-        <v/>
-      </c>
-      <c r="G32" s="28" t="n"/>
+      <c r="F32" s="28" t="n"/>
+      <c r="G32" s="23">
+        <f>IFERROR(AVERAGE(C32:F32),"")</f>
+        <v/>
+      </c>
+      <c r="H32" s="28" t="n"/>
     </row>
     <row r="33" ht="17" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
@@ -8305,11 +8363,12 @@
       <c r="C33" s="28" t="n"/>
       <c r="D33" s="28" t="n"/>
       <c r="E33" s="28" t="n"/>
-      <c r="F33" s="23">
-        <f>IFERROR(AVERAGE(C33:E33),"")</f>
-        <v/>
-      </c>
-      <c r="G33" s="28" t="n"/>
+      <c r="F33" s="28" t="n"/>
+      <c r="G33" s="23">
+        <f>IFERROR(AVERAGE(C33:F33),"")</f>
+        <v/>
+      </c>
+      <c r="H33" s="28" t="n"/>
     </row>
     <row r="34" ht="17" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
@@ -8325,11 +8384,12 @@
       <c r="C34" s="28" t="n"/>
       <c r="D34" s="28" t="n"/>
       <c r="E34" s="28" t="n"/>
-      <c r="F34" s="23">
-        <f>IFERROR(AVERAGE(C34:E34),"")</f>
-        <v/>
-      </c>
-      <c r="G34" s="28" t="n"/>
+      <c r="F34" s="28" t="n"/>
+      <c r="G34" s="23">
+        <f>IFERROR(AVERAGE(C34:F34),"")</f>
+        <v/>
+      </c>
+      <c r="H34" s="28" t="n"/>
     </row>
     <row r="35" ht="17" customHeight="1">
       <c r="A35" s="26" t="inlineStr">
@@ -8345,11 +8405,12 @@
       <c r="C35" s="28" t="n"/>
       <c r="D35" s="28" t="n"/>
       <c r="E35" s="28" t="n"/>
-      <c r="F35" s="23">
-        <f>IFERROR(AVERAGE(C35:E35),"")</f>
-        <v/>
-      </c>
-      <c r="G35" s="28" t="n"/>
+      <c r="F35" s="28" t="n"/>
+      <c r="G35" s="23">
+        <f>IFERROR(AVERAGE(C35:F35),"")</f>
+        <v/>
+      </c>
+      <c r="H35" s="28" t="n"/>
     </row>
     <row r="36" ht="17" customHeight="1">
       <c r="A36" s="26" t="inlineStr">
@@ -8365,11 +8426,12 @@
       <c r="C36" s="28" t="n"/>
       <c r="D36" s="28" t="n"/>
       <c r="E36" s="28" t="n"/>
-      <c r="F36" s="23">
-        <f>IFERROR(AVERAGE(C36:E36),"")</f>
-        <v/>
-      </c>
-      <c r="G36" s="28" t="n"/>
+      <c r="F36" s="28" t="n"/>
+      <c r="G36" s="23">
+        <f>IFERROR(AVERAGE(C36:F36),"")</f>
+        <v/>
+      </c>
+      <c r="H36" s="28" t="n"/>
     </row>
     <row r="37" ht="17" customHeight="1">
       <c r="A37" s="26" t="inlineStr">
@@ -8385,11 +8447,12 @@
       <c r="C37" s="28" t="n"/>
       <c r="D37" s="28" t="n"/>
       <c r="E37" s="28" t="n"/>
-      <c r="F37" s="23">
-        <f>IFERROR(AVERAGE(C37:E37),"")</f>
-        <v/>
-      </c>
-      <c r="G37" s="28" t="n"/>
+      <c r="F37" s="28" t="n"/>
+      <c r="G37" s="23">
+        <f>IFERROR(AVERAGE(C37:F37),"")</f>
+        <v/>
+      </c>
+      <c r="H37" s="28" t="n"/>
     </row>
     <row r="38" ht="17" customHeight="1">
       <c r="A38" s="26" t="inlineStr">
@@ -8405,11 +8468,12 @@
       <c r="C38" s="28" t="n"/>
       <c r="D38" s="28" t="n"/>
       <c r="E38" s="28" t="n"/>
-      <c r="F38" s="23">
-        <f>IFERROR(AVERAGE(C38:E38),"")</f>
-        <v/>
-      </c>
-      <c r="G38" s="28" t="n"/>
+      <c r="F38" s="28" t="n"/>
+      <c r="G38" s="23">
+        <f>IFERROR(AVERAGE(C38:F38),"")</f>
+        <v/>
+      </c>
+      <c r="H38" s="28" t="n"/>
     </row>
     <row r="39" ht="12" customHeight="1">
       <c r="A39" s="31" t="inlineStr">
@@ -8421,8 +8485,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A39:H39"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Shop_Tracker_2065_2026.xlsx
+++ b/Shop_Tracker_2065_2026.xlsx
@@ -7667,7 +7667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -7676,8 +7676,10 @@
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -7712,10 +7714,20 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
+          <t>WEEK 5</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>WEEK 6</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
           <t>MTD SCORE</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>MTD DOLLARS</t>
         </is>
@@ -7748,8 +7760,18 @@
           <t>08/21</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr"/>
-      <c r="H3" s="4" t="inlineStr"/>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>08/27</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>08/30</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
+      <c r="J3" s="4" t="inlineStr"/>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="4" t="inlineStr"/>
@@ -7778,8 +7800,18 @@
           <t>Lunch</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr"/>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
+      <c r="J4" s="4" t="inlineStr"/>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="9" t="inlineStr"/>
@@ -7800,8 +7832,14 @@
       <c r="F5" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="G5" s="9" t="inlineStr"/>
-      <c r="H5" s="9" t="inlineStr"/>
+      <c r="G5" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="H5" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="9" t="inlineStr"/>
+      <c r="J5" s="9" t="inlineStr"/>
     </row>
     <row r="6" ht="14" customHeight="1">
       <c r="A6" s="15" t="inlineStr"/>
@@ -7816,6 +7854,8 @@
       <c r="F6" s="17" t="n"/>
       <c r="G6" s="17" t="n"/>
       <c r="H6" s="17" t="n"/>
+      <c r="I6" s="17" t="n"/>
+      <c r="J6" s="17" t="n"/>
     </row>
     <row r="7" ht="14" customHeight="1">
       <c r="A7" s="15" t="inlineStr"/>
@@ -7830,6 +7870,8 @@
       <c r="F7" s="17" t="n"/>
       <c r="G7" s="17" t="n"/>
       <c r="H7" s="17" t="n"/>
+      <c r="I7" s="17" t="n"/>
+      <c r="J7" s="17" t="n"/>
     </row>
     <row r="8" ht="14" customHeight="1">
       <c r="A8" s="15" t="inlineStr"/>
@@ -7844,6 +7886,8 @@
       <c r="F8" s="17" t="n"/>
       <c r="G8" s="17" t="n"/>
       <c r="H8" s="17" t="n"/>
+      <c r="I8" s="17" t="n"/>
+      <c r="J8" s="17" t="n"/>
     </row>
     <row r="9" ht="14" customHeight="1">
       <c r="A9" s="15" t="inlineStr"/>
@@ -7858,6 +7902,8 @@
       <c r="F9" s="17" t="n"/>
       <c r="G9" s="17" t="n"/>
       <c r="H9" s="17" t="n"/>
+      <c r="I9" s="17" t="n"/>
+      <c r="J9" s="17" t="n"/>
     </row>
     <row r="10" ht="14" customHeight="1">
       <c r="A10" s="15" t="inlineStr"/>
@@ -7872,6 +7918,8 @@
       <c r="F10" s="17" t="n"/>
       <c r="G10" s="17" t="n"/>
       <c r="H10" s="17" t="n"/>
+      <c r="I10" s="17" t="n"/>
+      <c r="J10" s="17" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="18" t="inlineStr">
@@ -7883,12 +7931,14 @@
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>MTD SCORE</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>MTD DOLLARS</t>
         </is>
@@ -7911,11 +7961,15 @@
       <c r="F12" s="22" t="n">
         <v>100</v>
       </c>
-      <c r="G12" s="23">
-        <f>IFERROR(AVERAGE(C12:F12),"")</f>
-        <v/>
-      </c>
-      <c r="H12" s="24" t="n">
+      <c r="G12" s="21" t="n"/>
+      <c r="H12" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="23">
+        <f>IFERROR(AVERAGE(C12:H12),"")</f>
+        <v/>
+      </c>
+      <c r="J12" s="24" t="n">
         <v>46</v>
       </c>
     </row>
@@ -7934,11 +7988,13 @@
       <c r="D13" s="21" t="n"/>
       <c r="E13" s="21" t="n"/>
       <c r="F13" s="21" t="n"/>
-      <c r="G13" s="23">
-        <f>IFERROR(AVERAGE(C13:F13),"")</f>
-        <v/>
-      </c>
+      <c r="G13" s="21" t="n"/>
       <c r="H13" s="21" t="n"/>
+      <c r="I13" s="23">
+        <f>IFERROR(AVERAGE(C13:H13),"")</f>
+        <v/>
+      </c>
+      <c r="J13" s="21" t="n"/>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
@@ -7955,11 +8011,13 @@
       <c r="D14" s="21" t="n"/>
       <c r="E14" s="21" t="n"/>
       <c r="F14" s="21" t="n"/>
-      <c r="G14" s="23">
-        <f>IFERROR(AVERAGE(C14:F14),"")</f>
-        <v/>
-      </c>
+      <c r="G14" s="21" t="n"/>
       <c r="H14" s="21" t="n"/>
+      <c r="I14" s="23">
+        <f>IFERROR(AVERAGE(C14:H14),"")</f>
+        <v/>
+      </c>
+      <c r="J14" s="21" t="n"/>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
@@ -7976,11 +8034,13 @@
       <c r="D15" s="28" t="n"/>
       <c r="E15" s="28" t="n"/>
       <c r="F15" s="28" t="n"/>
-      <c r="G15" s="23">
-        <f>IFERROR(AVERAGE(C15:F15),"")</f>
-        <v/>
-      </c>
+      <c r="G15" s="28" t="n"/>
       <c r="H15" s="28" t="n"/>
+      <c r="I15" s="23">
+        <f>IFERROR(AVERAGE(C15:H15),"")</f>
+        <v/>
+      </c>
+      <c r="J15" s="28" t="n"/>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
@@ -7997,11 +8057,13 @@
       <c r="D16" s="28" t="n"/>
       <c r="E16" s="28" t="n"/>
       <c r="F16" s="28" t="n"/>
-      <c r="G16" s="23">
-        <f>IFERROR(AVERAGE(C16:F16),"")</f>
-        <v/>
-      </c>
+      <c r="G16" s="28" t="n"/>
       <c r="H16" s="28" t="n"/>
+      <c r="I16" s="23">
+        <f>IFERROR(AVERAGE(C16:H16),"")</f>
+        <v/>
+      </c>
+      <c r="J16" s="28" t="n"/>
     </row>
     <row r="17" ht="17" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
@@ -8018,11 +8080,13 @@
       <c r="D17" s="28" t="n"/>
       <c r="E17" s="28" t="n"/>
       <c r="F17" s="28" t="n"/>
-      <c r="G17" s="23">
-        <f>IFERROR(AVERAGE(C17:F17),"")</f>
-        <v/>
-      </c>
+      <c r="G17" s="28" t="n"/>
       <c r="H17" s="28" t="n"/>
+      <c r="I17" s="23">
+        <f>IFERROR(AVERAGE(C17:H17),"")</f>
+        <v/>
+      </c>
+      <c r="J17" s="28" t="n"/>
     </row>
     <row r="18" ht="17" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
@@ -8039,11 +8103,13 @@
       <c r="D18" s="28" t="n"/>
       <c r="E18" s="28" t="n"/>
       <c r="F18" s="28" t="n"/>
-      <c r="G18" s="23">
-        <f>IFERROR(AVERAGE(C18:F18),"")</f>
-        <v/>
-      </c>
+      <c r="G18" s="28" t="n"/>
       <c r="H18" s="28" t="n"/>
+      <c r="I18" s="23">
+        <f>IFERROR(AVERAGE(C18:H18),"")</f>
+        <v/>
+      </c>
+      <c r="J18" s="28" t="n"/>
     </row>
     <row r="19" ht="17" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
@@ -8060,11 +8126,15 @@
       <c r="D19" s="28" t="n"/>
       <c r="E19" s="28" t="n"/>
       <c r="F19" s="28" t="n"/>
-      <c r="G19" s="23">
-        <f>IFERROR(AVERAGE(C19:F19),"")</f>
-        <v/>
-      </c>
-      <c r="H19" s="28" t="n"/>
+      <c r="G19" s="28" t="n"/>
+      <c r="H19" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="23">
+        <f>IFERROR(AVERAGE(C19:H19),"")</f>
+        <v/>
+      </c>
+      <c r="J19" s="28" t="n"/>
     </row>
     <row r="20" ht="17" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
@@ -8081,11 +8151,13 @@
       <c r="D20" s="28" t="n"/>
       <c r="E20" s="28" t="n"/>
       <c r="F20" s="28" t="n"/>
-      <c r="G20" s="23">
-        <f>IFERROR(AVERAGE(C20:F20),"")</f>
-        <v/>
-      </c>
+      <c r="G20" s="28" t="n"/>
       <c r="H20" s="28" t="n"/>
+      <c r="I20" s="23">
+        <f>IFERROR(AVERAGE(C20:H20),"")</f>
+        <v/>
+      </c>
+      <c r="J20" s="28" t="n"/>
     </row>
     <row r="21" ht="17" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
@@ -8102,11 +8174,13 @@
       <c r="D21" s="28" t="n"/>
       <c r="E21" s="28" t="n"/>
       <c r="F21" s="28" t="n"/>
-      <c r="G21" s="23">
-        <f>IFERROR(AVERAGE(C21:F21),"")</f>
-        <v/>
-      </c>
+      <c r="G21" s="28" t="n"/>
       <c r="H21" s="28" t="n"/>
+      <c r="I21" s="23">
+        <f>IFERROR(AVERAGE(C21:H21),"")</f>
+        <v/>
+      </c>
+      <c r="J21" s="28" t="n"/>
     </row>
     <row r="22" ht="17" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
@@ -8123,11 +8197,13 @@
       <c r="D22" s="28" t="n"/>
       <c r="E22" s="28" t="n"/>
       <c r="F22" s="28" t="n"/>
-      <c r="G22" s="23">
-        <f>IFERROR(AVERAGE(C22:F22),"")</f>
-        <v/>
-      </c>
+      <c r="G22" s="28" t="n"/>
       <c r="H22" s="28" t="n"/>
+      <c r="I22" s="23">
+        <f>IFERROR(AVERAGE(C22:H22),"")</f>
+        <v/>
+      </c>
+      <c r="J22" s="28" t="n"/>
     </row>
     <row r="23" ht="17" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
@@ -8146,11 +8222,13 @@
       <c r="F23" s="22" t="n">
         <v>100</v>
       </c>
-      <c r="G23" s="23">
-        <f>IFERROR(AVERAGE(C23:F23),"")</f>
-        <v/>
-      </c>
-      <c r="H23" s="24" t="n">
+      <c r="G23" s="28" t="n"/>
+      <c r="H23" s="28" t="n"/>
+      <c r="I23" s="23">
+        <f>IFERROR(AVERAGE(C23:H23),"")</f>
+        <v/>
+      </c>
+      <c r="J23" s="24" t="n">
         <v>46</v>
       </c>
     </row>
@@ -8169,11 +8247,13 @@
       <c r="D24" s="28" t="n"/>
       <c r="E24" s="28" t="n"/>
       <c r="F24" s="28" t="n"/>
-      <c r="G24" s="23">
-        <f>IFERROR(AVERAGE(C24:F24),"")</f>
-        <v/>
-      </c>
+      <c r="G24" s="28" t="n"/>
       <c r="H24" s="28" t="n"/>
+      <c r="I24" s="23">
+        <f>IFERROR(AVERAGE(C24:H24),"")</f>
+        <v/>
+      </c>
+      <c r="J24" s="28" t="n"/>
     </row>
     <row r="25" ht="17" customHeight="1">
       <c r="A25" s="26" t="inlineStr">
@@ -8190,11 +8270,13 @@
       <c r="D25" s="28" t="n"/>
       <c r="E25" s="28" t="n"/>
       <c r="F25" s="28" t="n"/>
-      <c r="G25" s="23">
-        <f>IFERROR(AVERAGE(C25:F25),"")</f>
-        <v/>
-      </c>
+      <c r="G25" s="28" t="n"/>
       <c r="H25" s="28" t="n"/>
+      <c r="I25" s="23">
+        <f>IFERROR(AVERAGE(C25:H25),"")</f>
+        <v/>
+      </c>
+      <c r="J25" s="28" t="n"/>
     </row>
     <row r="26" ht="17" customHeight="1">
       <c r="A26" s="26" t="inlineStr">
@@ -8211,11 +8293,13 @@
       <c r="D26" s="28" t="n"/>
       <c r="E26" s="28" t="n"/>
       <c r="F26" s="28" t="n"/>
-      <c r="G26" s="23">
-        <f>IFERROR(AVERAGE(C26:F26),"")</f>
-        <v/>
-      </c>
+      <c r="G26" s="28" t="n"/>
       <c r="H26" s="28" t="n"/>
+      <c r="I26" s="23">
+        <f>IFERROR(AVERAGE(C26:H26),"")</f>
+        <v/>
+      </c>
+      <c r="J26" s="28" t="n"/>
     </row>
     <row r="27" ht="17" customHeight="1">
       <c r="A27" s="26" t="inlineStr">
@@ -8232,11 +8316,13 @@
       <c r="D27" s="28" t="n"/>
       <c r="E27" s="28" t="n"/>
       <c r="F27" s="28" t="n"/>
-      <c r="G27" s="23">
-        <f>IFERROR(AVERAGE(C27:F27),"")</f>
-        <v/>
-      </c>
+      <c r="G27" s="28" t="n"/>
       <c r="H27" s="28" t="n"/>
+      <c r="I27" s="23">
+        <f>IFERROR(AVERAGE(C27:H27),"")</f>
+        <v/>
+      </c>
+      <c r="J27" s="28" t="n"/>
     </row>
     <row r="28" ht="17" customHeight="1">
       <c r="A28" s="26" t="inlineStr">
@@ -8253,11 +8339,13 @@
       <c r="D28" s="28" t="n"/>
       <c r="E28" s="28" t="n"/>
       <c r="F28" s="28" t="n"/>
-      <c r="G28" s="23">
-        <f>IFERROR(AVERAGE(C28:F28),"")</f>
-        <v/>
-      </c>
+      <c r="G28" s="28" t="n"/>
       <c r="H28" s="28" t="n"/>
+      <c r="I28" s="23">
+        <f>IFERROR(AVERAGE(C28:H28),"")</f>
+        <v/>
+      </c>
+      <c r="J28" s="28" t="n"/>
     </row>
     <row r="29" ht="17" customHeight="1">
       <c r="A29" s="26" t="inlineStr">
@@ -8274,11 +8362,13 @@
       <c r="D29" s="28" t="n"/>
       <c r="E29" s="28" t="n"/>
       <c r="F29" s="28" t="n"/>
-      <c r="G29" s="23">
-        <f>IFERROR(AVERAGE(C29:F29),"")</f>
-        <v/>
-      </c>
+      <c r="G29" s="28" t="n"/>
       <c r="H29" s="28" t="n"/>
+      <c r="I29" s="23">
+        <f>IFERROR(AVERAGE(C29:H29),"")</f>
+        <v/>
+      </c>
+      <c r="J29" s="28" t="n"/>
     </row>
     <row r="30" ht="17" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
@@ -8295,11 +8385,13 @@
       <c r="D30" s="28" t="n"/>
       <c r="E30" s="28" t="n"/>
       <c r="F30" s="28" t="n"/>
-      <c r="G30" s="23">
-        <f>IFERROR(AVERAGE(C30:F30),"")</f>
-        <v/>
-      </c>
+      <c r="G30" s="28" t="n"/>
       <c r="H30" s="28" t="n"/>
+      <c r="I30" s="23">
+        <f>IFERROR(AVERAGE(C30:H30),"")</f>
+        <v/>
+      </c>
+      <c r="J30" s="28" t="n"/>
     </row>
     <row r="31" ht="17" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
@@ -8320,11 +8412,13 @@
       <c r="F31" s="22" t="n">
         <v>100</v>
       </c>
-      <c r="G31" s="23">
-        <f>IFERROR(AVERAGE(C31:F31),"")</f>
-        <v/>
-      </c>
-      <c r="H31" s="24" t="n">
+      <c r="G31" s="28" t="n"/>
+      <c r="H31" s="28" t="n"/>
+      <c r="I31" s="23">
+        <f>IFERROR(AVERAGE(C31:H31),"")</f>
+        <v/>
+      </c>
+      <c r="J31" s="24" t="n">
         <v>46</v>
       </c>
     </row>
@@ -8343,11 +8437,13 @@
       <c r="D32" s="28" t="n"/>
       <c r="E32" s="28" t="n"/>
       <c r="F32" s="28" t="n"/>
-      <c r="G32" s="23">
-        <f>IFERROR(AVERAGE(C32:F32),"")</f>
-        <v/>
-      </c>
+      <c r="G32" s="28" t="n"/>
       <c r="H32" s="28" t="n"/>
+      <c r="I32" s="23">
+        <f>IFERROR(AVERAGE(C32:H32),"")</f>
+        <v/>
+      </c>
+      <c r="J32" s="28" t="n"/>
     </row>
     <row r="33" ht="17" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
@@ -8364,11 +8460,13 @@
       <c r="D33" s="28" t="n"/>
       <c r="E33" s="28" t="n"/>
       <c r="F33" s="28" t="n"/>
-      <c r="G33" s="23">
-        <f>IFERROR(AVERAGE(C33:F33),"")</f>
-        <v/>
-      </c>
+      <c r="G33" s="28" t="n"/>
       <c r="H33" s="28" t="n"/>
+      <c r="I33" s="23">
+        <f>IFERROR(AVERAGE(C33:H33),"")</f>
+        <v/>
+      </c>
+      <c r="J33" s="28" t="n"/>
     </row>
     <row r="34" ht="17" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
@@ -8385,11 +8483,13 @@
       <c r="D34" s="28" t="n"/>
       <c r="E34" s="28" t="n"/>
       <c r="F34" s="28" t="n"/>
-      <c r="G34" s="23">
-        <f>IFERROR(AVERAGE(C34:F34),"")</f>
-        <v/>
-      </c>
+      <c r="G34" s="28" t="n"/>
       <c r="H34" s="28" t="n"/>
+      <c r="I34" s="23">
+        <f>IFERROR(AVERAGE(C34:H34),"")</f>
+        <v/>
+      </c>
+      <c r="J34" s="28" t="n"/>
     </row>
     <row r="35" ht="17" customHeight="1">
       <c r="A35" s="26" t="inlineStr">
@@ -8406,11 +8506,13 @@
       <c r="D35" s="28" t="n"/>
       <c r="E35" s="28" t="n"/>
       <c r="F35" s="28" t="n"/>
-      <c r="G35" s="23">
-        <f>IFERROR(AVERAGE(C35:F35),"")</f>
-        <v/>
-      </c>
+      <c r="G35" s="28" t="n"/>
       <c r="H35" s="28" t="n"/>
+      <c r="I35" s="23">
+        <f>IFERROR(AVERAGE(C35:H35),"")</f>
+        <v/>
+      </c>
+      <c r="J35" s="28" t="n"/>
     </row>
     <row r="36" ht="17" customHeight="1">
       <c r="A36" s="26" t="inlineStr">
@@ -8427,11 +8529,13 @@
       <c r="D36" s="28" t="n"/>
       <c r="E36" s="28" t="n"/>
       <c r="F36" s="28" t="n"/>
-      <c r="G36" s="23">
-        <f>IFERROR(AVERAGE(C36:F36),"")</f>
-        <v/>
-      </c>
+      <c r="G36" s="28" t="n"/>
       <c r="H36" s="28" t="n"/>
+      <c r="I36" s="23">
+        <f>IFERROR(AVERAGE(C36:H36),"")</f>
+        <v/>
+      </c>
+      <c r="J36" s="28" t="n"/>
     </row>
     <row r="37" ht="17" customHeight="1">
       <c r="A37" s="26" t="inlineStr">
@@ -8448,11 +8552,13 @@
       <c r="D37" s="28" t="n"/>
       <c r="E37" s="28" t="n"/>
       <c r="F37" s="28" t="n"/>
-      <c r="G37" s="23">
-        <f>IFERROR(AVERAGE(C37:F37),"")</f>
-        <v/>
-      </c>
+      <c r="G37" s="28" t="n"/>
       <c r="H37" s="28" t="n"/>
+      <c r="I37" s="23">
+        <f>IFERROR(AVERAGE(C37:H37),"")</f>
+        <v/>
+      </c>
+      <c r="J37" s="28" t="n"/>
     </row>
     <row r="38" ht="17" customHeight="1">
       <c r="A38" s="26" t="inlineStr">
@@ -8469,11 +8575,13 @@
       <c r="D38" s="28" t="n"/>
       <c r="E38" s="28" t="n"/>
       <c r="F38" s="28" t="n"/>
-      <c r="G38" s="23">
-        <f>IFERROR(AVERAGE(C38:F38),"")</f>
-        <v/>
-      </c>
+      <c r="G38" s="28" t="n"/>
       <c r="H38" s="28" t="n"/>
+      <c r="I38" s="23">
+        <f>IFERROR(AVERAGE(C38:H38),"")</f>
+        <v/>
+      </c>
+      <c r="J38" s="28" t="n"/>
     </row>
     <row r="39" ht="12" customHeight="1">
       <c r="A39" s="31" t="inlineStr">
@@ -8484,9 +8592,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A39:J39"/>
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A39:H39"/>
-    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
